--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="14_{75CD4994-79C5-4B44-86C2-66D5A9B83F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EB35C7C-6FBE-40D4-BF89-299FA603B446}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="14_{75CD4994-79C5-4B44-86C2-66D5A9B83F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA372C58-372A-4EBC-8869-2649BAE71056}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="14184" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="U2" s="19"/>
     </row>
-    <row r="3" spans="1:21" ht="62.4" hidden="1" customHeight="1">
+    <row r="3" spans="1:21" ht="62.4" customHeight="1">
       <c r="A3" s="136">
         <v>1</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="62.4" hidden="1" customHeight="1">
+    <row r="4" spans="1:21" ht="62.4" customHeight="1">
       <c r="A4" s="136"/>
       <c r="B4" s="74" t="s">
         <v>19</v>
@@ -5186,7 +5186,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="61.2" hidden="1">
+    <row r="5" spans="1:21" ht="61.2">
       <c r="A5" s="136"/>
       <c r="B5" s="41" t="s">
         <v>19</v>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="S281" s="74"/>
     </row>
-    <row r="282" spans="1:19" ht="61.2">
+    <row r="282" spans="1:19" ht="61.2" hidden="1">
       <c r="A282" s="34"/>
       <c r="B282" s="74" t="s">
         <v>660</v>
@@ -19571,7 +19571,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="283" spans="1:19" ht="142.80000000000001">
+    <row r="283" spans="1:19" ht="142.80000000000001" hidden="1">
       <c r="A283" s="130">
         <v>77</v>
       </c>
@@ -19631,7 +19631,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="284" spans="1:19" ht="40.799999999999997">
+    <row r="284" spans="1:19" ht="40.799999999999997" hidden="1">
       <c r="A284" s="130"/>
       <c r="B284" s="74" t="s">
         <v>660</v>
@@ -19689,7 +19689,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="285" spans="1:19" ht="20.399999999999999">
+    <row r="285" spans="1:19" ht="20.399999999999999" hidden="1">
       <c r="A285" s="130"/>
       <c r="B285" s="74" t="s">
         <v>660</v>
@@ -30280,7 +30280,7 @@
   <autoFilter ref="A2:S490" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Nechí"/>
+        <filter val="Abejorral"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBAA6F33-E123-4741-9E4E-F2DC1BD31D73}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F7CD536-740E-40E7-8EAB-34CD61E1A2F4}"/>
   <bookViews>
-    <workbookView xWindow="11184" yWindow="672" windowWidth="14184" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
@@ -4589,40 +4589,25 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4637,13 +4622,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4990,8 +4990,8 @@
     <col min="13" max="13" width="24.33203125" style="44" customWidth="1"/>
     <col min="14" max="14" width="26" style="44" customWidth="1"/>
     <col min="15" max="15" width="32.5546875" style="44" customWidth="1"/>
-    <col min="16" max="16" width="19.109375" style="44" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5546875" style="44" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="19.109375" style="44" customWidth="1"/>
+    <col min="17" max="17" width="20.5546875" style="44" customWidth="1"/>
     <col min="18" max="18" width="19.109375" style="103" customWidth="1"/>
     <col min="19" max="19" width="39.5546875" style="44" customWidth="1"/>
     <col min="20" max="20" width="16.6640625" style="36" customWidth="1"/>
@@ -5000,10 +5000,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="125"/>
+      <c r="C1" s="130"/>
       <c r="D1" s="45"/>
       <c r="E1" s="46"/>
       <c r="F1" s="45"/>
@@ -5080,7 +5080,7 @@
       <c r="U2" s="54"/>
     </row>
     <row r="3" spans="1:21" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="122">
+      <c r="A3" s="117">
         <v>1</v>
       </c>
       <c r="B3" s="55" t="s">
@@ -5141,7 +5141,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="122"/>
+      <c r="A4" s="117"/>
       <c r="B4" s="61" t="s">
         <v>19</v>
       </c>
@@ -5200,7 +5200,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="61.2" hidden="1">
-      <c r="A5" s="122"/>
+      <c r="A5" s="117"/>
       <c r="B5" s="47" t="s">
         <v>19</v>
       </c>
@@ -5336,8 +5336,8 @@
       <c r="R7" s="62"/>
       <c r="S7" s="62"/>
     </row>
-    <row r="8" spans="1:21" ht="40.799999999999997" hidden="1">
-      <c r="A8" s="126"/>
+    <row r="8" spans="1:21" ht="40.799999999999997">
+      <c r="A8" s="116"/>
       <c r="B8" s="61" t="s">
         <v>38</v>
       </c>
@@ -5387,7 +5387,7 @@
       <c r="S8" s="62"/>
     </row>
     <row r="9" spans="1:21" ht="61.2" hidden="1">
-      <c r="A9" s="126"/>
+      <c r="A9" s="116"/>
       <c r="B9" s="61" t="s">
         <v>38</v>
       </c>
@@ -5443,7 +5443,7 @@
       <c r="S9" s="62"/>
     </row>
     <row r="10" spans="1:21" ht="61.2" hidden="1">
-      <c r="A10" s="122"/>
+      <c r="A10" s="117"/>
       <c r="B10" s="62" t="s">
         <v>38</v>
       </c>
@@ -5499,7 +5499,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.799999999999997" hidden="1">
-      <c r="A11" s="116">
+      <c r="A11" s="115">
         <v>3</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -5560,7 +5560,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="116"/>
+      <c r="A12" s="115"/>
       <c r="B12" s="61" t="s">
         <v>55</v>
       </c>
@@ -5614,7 +5614,7 @@
       <c r="S12" s="60"/>
     </row>
     <row r="13" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A13" s="116"/>
+      <c r="A13" s="115"/>
       <c r="B13" s="61" t="s">
         <v>55</v>
       </c>
@@ -5668,7 +5668,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A14" s="116"/>
+      <c r="A14" s="115"/>
       <c r="B14" s="61" t="s">
         <v>55</v>
       </c>
@@ -5722,7 +5722,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A15" s="116"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="83" t="s">
         <v>55</v>
       </c>
@@ -5768,7 +5768,7 @@
       <c r="S15" s="71"/>
     </row>
     <row r="16" spans="1:21" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="116"/>
+      <c r="A16" s="115"/>
       <c r="B16" s="61" t="s">
         <v>55</v>
       </c>
@@ -5973,7 +5973,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="116">
+      <c r="A20" s="115">
         <v>5</v>
       </c>
       <c r="B20" s="61" t="s">
@@ -6033,7 +6033,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="116"/>
+      <c r="A21" s="115"/>
       <c r="B21" s="61" t="s">
         <v>84</v>
       </c>
@@ -6089,7 +6089,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A22" s="116"/>
+      <c r="A22" s="115"/>
       <c r="B22" s="61" t="s">
         <v>84</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
     </row>
     <row r="23" spans="1:19" ht="61.2" hidden="1">
-      <c r="A23" s="116"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="61" t="s">
         <v>84</v>
       </c>
@@ -6203,7 +6203,7 @@
       </c>
     </row>
     <row r="24" spans="1:19" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="116">
+      <c r="A24" s="115">
         <v>6</v>
       </c>
       <c r="B24" s="61" t="s">
@@ -6262,7 +6262,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A25" s="116"/>
+      <c r="A25" s="115"/>
       <c r="B25" s="61" t="s">
         <v>101</v>
       </c>
@@ -6316,7 +6316,7 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="116"/>
+      <c r="A26" s="115"/>
       <c r="B26" s="61" t="s">
         <v>101</v>
       </c>
@@ -6370,7 +6370,7 @@
       </c>
     </row>
     <row r="27" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="116"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="61" t="s">
         <v>101</v>
       </c>
@@ -6425,8 +6425,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A28" s="116"/>
+    <row r="28" spans="1:19" ht="20.399999999999999">
+      <c r="A28" s="115"/>
       <c r="B28" s="61" t="s">
         <v>101</v>
       </c>
@@ -6478,7 +6478,7 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="116"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="61" t="s">
         <v>101</v>
       </c>
@@ -6531,8 +6531,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="116"/>
+    <row r="30" spans="1:19" ht="40.950000000000003" customHeight="1">
+      <c r="A30" s="115"/>
       <c r="B30" s="61" t="s">
         <v>101</v>
       </c>
@@ -6582,7 +6582,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="116"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="61" t="s">
         <v>101</v>
       </c>
@@ -6638,7 +6638,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="116"/>
+      <c r="A32" s="115"/>
       <c r="B32" s="61" t="s">
         <v>101</v>
       </c>
@@ -6696,7 +6696,7 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="116"/>
+      <c r="A33" s="115"/>
       <c r="B33" s="61" t="s">
         <v>101</v>
       </c>
@@ -6750,7 +6750,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="116"/>
+      <c r="A34" s="115"/>
       <c r="B34" s="61" t="s">
         <v>101</v>
       </c>
@@ -6804,7 +6804,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A35" s="126"/>
+      <c r="A35" s="116"/>
       <c r="B35" s="61" t="s">
         <v>137</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="S35" s="61"/>
     </row>
     <row r="36" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="122"/>
+      <c r="A36" s="117"/>
       <c r="B36" s="61" t="s">
         <v>137</v>
       </c>
@@ -6945,7 +6945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="116">
+      <c r="A38" s="115">
         <v>8</v>
       </c>
       <c r="B38" s="61" t="s">
@@ -7004,7 +7004,7 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="116"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="61" t="s">
         <v>140</v>
       </c>
@@ -7058,7 +7058,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="116"/>
+      <c r="A40" s="115"/>
       <c r="B40" s="61" t="s">
         <v>140</v>
       </c>
@@ -7113,7 +7113,7 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="116">
+      <c r="A41" s="115">
         <v>9</v>
       </c>
       <c r="B41" s="61" t="s">
@@ -7169,7 +7169,7 @@
       <c r="S41" s="61"/>
     </row>
     <row r="42" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="116"/>
+      <c r="A42" s="115"/>
       <c r="B42" s="61" t="s">
         <v>149</v>
       </c>
@@ -7216,7 +7216,7 @@
       </c>
     </row>
     <row r="43" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="116"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="61" t="s">
         <v>149</v>
       </c>
@@ -7265,7 +7265,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="116"/>
+      <c r="A44" s="115"/>
       <c r="B44" s="61" t="s">
         <v>149</v>
       </c>
@@ -7311,7 +7311,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A45" s="116"/>
+      <c r="A45" s="115"/>
       <c r="B45" s="61" t="s">
         <v>149</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="116">
+      <c r="A46" s="115">
         <v>10</v>
       </c>
       <c r="B46" s="61" t="s">
@@ -7471,7 +7471,7 @@
       <c r="S47" s="61"/>
     </row>
     <row r="48" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A48" s="116"/>
+      <c r="A48" s="115"/>
       <c r="B48" s="61" t="s">
         <v>167</v>
       </c>
@@ -7504,7 +7504,7 @@
       <c r="S48" s="61"/>
     </row>
     <row r="49" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A49" s="116"/>
+      <c r="A49" s="115"/>
       <c r="B49" s="61" t="s">
         <v>167</v>
       </c>
@@ -7540,8 +7540,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A50" s="116"/>
+    <row r="50" spans="1:19" ht="20.399999999999999">
+      <c r="A50" s="115"/>
       <c r="B50" s="61" t="s">
         <v>167</v>
       </c>
@@ -7590,8 +7590,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="102" hidden="1">
-      <c r="A51" s="116"/>
+    <row r="51" spans="1:19" ht="102">
+      <c r="A51" s="115"/>
       <c r="B51" s="61" t="s">
         <v>167</v>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
     </row>
     <row r="52" spans="1:19" ht="61.2" hidden="1">
-      <c r="A52" s="116"/>
+      <c r="A52" s="115"/>
       <c r="B52" s="61" t="s">
         <v>167</v>
       </c>
@@ -7688,8 +7688,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="116"/>
+    <row r="53" spans="1:19" ht="45.6" customHeight="1">
+      <c r="A53" s="115"/>
       <c r="B53" s="61" t="s">
         <v>167</v>
       </c>
@@ -7741,7 +7741,7 @@
       </c>
     </row>
     <row r="54" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="116"/>
+      <c r="A54" s="115"/>
       <c r="B54" s="61" t="s">
         <v>183</v>
       </c>
@@ -7791,8 +7791,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="116"/>
+    <row r="55" spans="1:19" ht="40.950000000000003" customHeight="1">
+      <c r="A55" s="115"/>
       <c r="B55" s="61" t="s">
         <v>183</v>
       </c>
@@ -7844,7 +7844,7 @@
       <c r="S55" s="62"/>
     </row>
     <row r="56" spans="1:19" ht="61.2" hidden="1">
-      <c r="A56" s="116"/>
+      <c r="A56" s="115"/>
       <c r="B56" s="61" t="s">
         <v>183</v>
       </c>
@@ -7900,7 +7900,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="116"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="61" t="s">
         <v>183</v>
       </c>
@@ -7954,7 +7954,7 @@
       <c r="S57" s="61"/>
     </row>
     <row r="58" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="116"/>
+      <c r="A58" s="115"/>
       <c r="B58" s="61" t="s">
         <v>183</v>
       </c>
@@ -8011,7 +8011,7 @@
       </c>
     </row>
     <row r="59" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A59" s="122"/>
+      <c r="A59" s="117"/>
       <c r="B59" s="61" t="s">
         <v>193</v>
       </c>
@@ -8065,7 +8065,7 @@
       </c>
     </row>
     <row r="60" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A60" s="122"/>
+      <c r="A60" s="117"/>
       <c r="B60" s="61" t="s">
         <v>193</v>
       </c>
@@ -8118,7 +8118,7 @@
       </c>
     </row>
     <row r="61" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A61" s="116"/>
+      <c r="A61" s="115"/>
       <c r="B61" s="61" t="s">
         <v>193</v>
       </c>
@@ -8224,7 +8224,7 @@
       </c>
     </row>
     <row r="63" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A63" s="126"/>
+      <c r="A63" s="116"/>
       <c r="B63" s="61" t="s">
         <v>199</v>
       </c>
@@ -8276,7 +8276,7 @@
       </c>
     </row>
     <row r="64" spans="1:19" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="122"/>
+      <c r="A64" s="117"/>
       <c r="B64" s="61" t="s">
         <v>199</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="102" hidden="1" customHeight="1">
+    <row r="67" spans="1:19" ht="102" customHeight="1">
       <c r="A67" s="121">
         <v>16</v>
       </c>
@@ -8485,7 +8485,7 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A68" s="122"/>
+      <c r="A68" s="117"/>
       <c r="B68" s="61" t="s">
         <v>213</v>
       </c>
@@ -8588,7 +8588,7 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A70" s="126"/>
+      <c r="A70" s="116"/>
       <c r="B70" s="61" t="s">
         <v>219</v>
       </c>
@@ -8640,7 +8640,7 @@
       </c>
     </row>
     <row r="71" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A71" s="126"/>
+      <c r="A71" s="116"/>
       <c r="B71" s="61" t="s">
         <v>225</v>
       </c>
@@ -8690,7 +8690,7 @@
       </c>
     </row>
     <row r="72" spans="1:19" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="126"/>
+      <c r="A72" s="116"/>
       <c r="B72" s="61" t="s">
         <v>228</v>
       </c>
@@ -8743,7 +8743,7 @@
       </c>
     </row>
     <row r="73" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="126"/>
+      <c r="A73" s="116"/>
       <c r="B73" s="61" t="s">
         <v>228</v>
       </c>
@@ -8791,7 +8791,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="126"/>
+      <c r="A74" s="116"/>
       <c r="B74" s="61" t="s">
         <v>228</v>
       </c>
@@ -8843,7 +8843,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="126"/>
+      <c r="A75" s="116"/>
       <c r="B75" s="61" t="s">
         <v>228</v>
       </c>
@@ -8901,7 +8901,7 @@
       </c>
     </row>
     <row r="76" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A76" s="126"/>
+      <c r="A76" s="116"/>
       <c r="B76" s="61" t="s">
         <v>228</v>
       </c>
@@ -8953,7 +8953,7 @@
       <c r="S76" s="61"/>
     </row>
     <row r="77" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A77" s="122"/>
+      <c r="A77" s="117"/>
       <c r="B77" s="61" t="s">
         <v>228</v>
       </c>
@@ -9007,7 +9007,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="126"/>
+      <c r="A78" s="116"/>
       <c r="B78" s="61" t="s">
         <v>238</v>
       </c>
@@ -9065,7 +9065,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A79" s="126"/>
+      <c r="A79" s="116"/>
       <c r="B79" s="61" t="s">
         <v>238</v>
       </c>
@@ -9117,7 +9117,7 @@
       <c r="S79" s="62"/>
     </row>
     <row r="80" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A80" s="126"/>
+      <c r="A80" s="116"/>
       <c r="B80" s="61" t="s">
         <v>238</v>
       </c>
@@ -9169,7 +9169,7 @@
       <c r="S80" s="62"/>
     </row>
     <row r="81" spans="1:19" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="126"/>
+      <c r="A81" s="116"/>
       <c r="B81" s="61" t="s">
         <v>238</v>
       </c>
@@ -9222,7 +9222,7 @@
       </c>
     </row>
     <row r="82" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="126"/>
+      <c r="A82" s="116"/>
       <c r="B82" s="75" t="s">
         <v>247</v>
       </c>
@@ -9276,7 +9276,7 @@
       </c>
     </row>
     <row r="83" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A83" s="126"/>
+      <c r="A83" s="116"/>
       <c r="B83" s="75" t="s">
         <v>247</v>
       </c>
@@ -9325,7 +9325,7 @@
       </c>
     </row>
     <row r="84" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A84" s="126"/>
+      <c r="A84" s="116"/>
       <c r="B84" s="61" t="s">
         <v>247</v>
       </c>
@@ -9377,7 +9377,7 @@
       </c>
     </row>
     <row r="85" spans="1:19" s="80" customFormat="1" ht="55.2" hidden="1">
-      <c r="A85" s="126"/>
+      <c r="A85" s="116"/>
       <c r="B85" s="75" t="s">
         <v>247</v>
       </c>
@@ -9427,7 +9427,7 @@
       </c>
     </row>
     <row r="86" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="126"/>
+      <c r="A86" s="116"/>
       <c r="B86" s="75" t="s">
         <v>247</v>
       </c>
@@ -9481,7 +9481,7 @@
       </c>
     </row>
     <row r="87" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="126"/>
+      <c r="A87" s="116"/>
       <c r="B87" s="75" t="s">
         <v>247</v>
       </c>
@@ -9535,7 +9535,7 @@
       </c>
     </row>
     <row r="88" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1">
-      <c r="A88" s="126"/>
+      <c r="A88" s="116"/>
       <c r="B88" s="75" t="s">
         <v>247</v>
       </c>
@@ -9589,7 +9589,7 @@
       </c>
     </row>
     <row r="89" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1">
-      <c r="A89" s="126"/>
+      <c r="A89" s="116"/>
       <c r="B89" s="75" t="s">
         <v>247</v>
       </c>
@@ -9641,7 +9641,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="1:19" s="80" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="126"/>
+      <c r="A90" s="116"/>
       <c r="B90" s="77" t="s">
         <v>247</v>
       </c>
@@ -9687,7 +9687,7 @@
       </c>
     </row>
     <row r="91" spans="1:19" s="80" customFormat="1" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="126"/>
+      <c r="A91" s="116"/>
       <c r="B91" s="61" t="s">
         <v>266</v>
       </c>
@@ -9711,37 +9711,37 @@
       </c>
       <c r="I91" s="61"/>
       <c r="J91" s="61"/>
-      <c r="K91" s="115">
+      <c r="K91" s="131">
         <v>4572000000</v>
       </c>
-      <c r="L91" s="115">
+      <c r="L91" s="131">
         <v>0</v>
       </c>
-      <c r="M91" s="115">
+      <c r="M91" s="131">
         <f>+K91</f>
         <v>4572000000</v>
       </c>
-      <c r="N91" s="116" t="s">
+      <c r="N91" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="116" t="s">
+      <c r="O91" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="P91" s="116">
+      <c r="P91" s="115">
         <v>2026</v>
       </c>
-      <c r="Q91" s="117" t="s">
+      <c r="Q91" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="R91" s="118">
+      <c r="R91" s="132">
         <v>0</v>
       </c>
-      <c r="S91" s="117" t="s">
+      <c r="S91" s="120" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A92" s="126"/>
+      <c r="A92" s="116"/>
       <c r="B92" s="61" t="s">
         <v>266</v>
       </c>
@@ -9765,18 +9765,18 @@
       </c>
       <c r="I92" s="61"/>
       <c r="J92" s="61"/>
-      <c r="K92" s="115"/>
-      <c r="L92" s="115"/>
-      <c r="M92" s="115"/>
-      <c r="N92" s="116"/>
-      <c r="O92" s="116"/>
-      <c r="P92" s="116"/>
-      <c r="Q92" s="117"/>
-      <c r="R92" s="118"/>
-      <c r="S92" s="117"/>
+      <c r="K92" s="131"/>
+      <c r="L92" s="131"/>
+      <c r="M92" s="131"/>
+      <c r="N92" s="115"/>
+      <c r="O92" s="115"/>
+      <c r="P92" s="115"/>
+      <c r="Q92" s="120"/>
+      <c r="R92" s="132"/>
+      <c r="S92" s="120"/>
     </row>
     <row r="93" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="126"/>
+      <c r="A93" s="116"/>
       <c r="B93" s="61" t="s">
         <v>266</v>
       </c>
@@ -9830,7 +9830,7 @@
       </c>
     </row>
     <row r="94" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="126"/>
+      <c r="A94" s="116"/>
       <c r="B94" s="61" t="s">
         <v>266</v>
       </c>
@@ -9882,7 +9882,7 @@
       </c>
     </row>
     <row r="95" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A95" s="126"/>
+      <c r="A95" s="116"/>
       <c r="B95" s="61" t="s">
         <v>266</v>
       </c>
@@ -9935,7 +9935,7 @@
       </c>
     </row>
     <row r="96" spans="1:19" ht="61.2" hidden="1">
-      <c r="A96" s="126"/>
+      <c r="A96" s="116"/>
       <c r="B96" s="61" t="s">
         <v>275</v>
       </c>
@@ -9992,7 +9992,7 @@
       </c>
     </row>
     <row r="97" spans="1:19" ht="99.6" hidden="1" customHeight="1">
-      <c r="A97" s="126"/>
+      <c r="A97" s="116"/>
       <c r="B97" s="61" t="s">
         <v>275</v>
       </c>
@@ -10050,7 +10050,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A98" s="126"/>
+      <c r="A98" s="116"/>
       <c r="B98" s="61" t="s">
         <v>285</v>
       </c>
@@ -10104,7 +10104,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="126"/>
+      <c r="A99" s="116"/>
       <c r="B99" s="61" t="s">
         <v>285</v>
       </c>
@@ -10158,7 +10158,7 @@
       </c>
     </row>
     <row r="100" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A100" s="126"/>
+      <c r="A100" s="116"/>
       <c r="B100" s="61" t="s">
         <v>285</v>
       </c>
@@ -10212,7 +10212,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="126"/>
+      <c r="A101" s="116"/>
       <c r="B101" s="61" t="s">
         <v>285</v>
       </c>
@@ -10266,7 +10266,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="126"/>
+      <c r="A102" s="116"/>
       <c r="B102" s="61" t="s">
         <v>285</v>
       </c>
@@ -10315,7 +10315,7 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="126"/>
+      <c r="A103" s="116"/>
       <c r="B103" s="61" t="s">
         <v>285</v>
       </c>
@@ -10363,7 +10363,7 @@
       </c>
     </row>
     <row r="104" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A104" s="126"/>
+      <c r="A104" s="116"/>
       <c r="B104" s="61" t="s">
         <v>285</v>
       </c>
@@ -10414,8 +10414,8 @@
       </c>
       <c r="S104" s="62"/>
     </row>
-    <row r="105" spans="1:19" ht="34.5" hidden="1" customHeight="1">
-      <c r="A105" s="126"/>
+    <row r="105" spans="1:19" ht="34.5" customHeight="1">
+      <c r="A105" s="116"/>
       <c r="B105" s="61" t="s">
         <v>285</v>
       </c>
@@ -10467,7 +10467,7 @@
       </c>
     </row>
     <row r="106" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A106" s="126"/>
+      <c r="A106" s="116"/>
       <c r="B106" s="61" t="s">
         <v>296</v>
       </c>
@@ -10516,7 +10516,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A107" s="126"/>
+      <c r="A107" s="116"/>
       <c r="B107" s="61" t="s">
         <v>303</v>
       </c>
@@ -10559,7 +10559,7 @@
       </c>
     </row>
     <row r="108" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A108" s="126"/>
+      <c r="A108" s="116"/>
       <c r="B108" s="61" t="s">
         <v>303</v>
       </c>
@@ -10609,7 +10609,7 @@
       <c r="S108" s="62"/>
     </row>
     <row r="109" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A109" s="126"/>
+      <c r="A109" s="116"/>
       <c r="B109" s="61" t="s">
         <v>303</v>
       </c>
@@ -10661,7 +10661,7 @@
       <c r="S109" s="61"/>
     </row>
     <row r="110" spans="1:19" ht="60.6" hidden="1" customHeight="1">
-      <c r="A110" s="126"/>
+      <c r="A110" s="116"/>
       <c r="B110" s="61" t="s">
         <v>307</v>
       </c>
@@ -10716,8 +10716,8 @@
       </c>
       <c r="S110" s="61"/>
     </row>
-    <row r="111" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A111" s="126"/>
+    <row r="111" spans="1:19" ht="20.399999999999999">
+      <c r="A111" s="116"/>
       <c r="B111" s="61" t="s">
         <v>309</v>
       </c>
@@ -10766,8 +10766,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A112" s="126"/>
+    <row r="112" spans="1:19" ht="40.799999999999997">
+      <c r="A112" s="116"/>
       <c r="B112" s="61" t="s">
         <v>309</v>
       </c>
@@ -10817,7 +10817,7 @@
       </c>
     </row>
     <row r="113" spans="1:19" ht="61.2" hidden="1">
-      <c r="A113" s="126"/>
+      <c r="A113" s="116"/>
       <c r="B113" s="61" t="s">
         <v>309</v>
       </c>
@@ -10856,7 +10856,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="22.95" hidden="1" customHeight="1">
-      <c r="A114" s="126"/>
+      <c r="A114" s="116"/>
       <c r="B114" s="61" t="s">
         <v>309</v>
       </c>
@@ -10910,7 +10910,7 @@
       </c>
     </row>
     <row r="115" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A115" s="126"/>
+      <c r="A115" s="116"/>
       <c r="B115" s="61" t="s">
         <v>319</v>
       </c>
@@ -10968,7 +10968,7 @@
       </c>
     </row>
     <row r="116" spans="1:19" ht="136.19999999999999" hidden="1" customHeight="1">
-      <c r="A116" s="122"/>
+      <c r="A116" s="117"/>
       <c r="B116" s="61" t="s">
         <v>324</v>
       </c>
@@ -11073,8 +11073,8 @@
       </c>
       <c r="S117" s="61"/>
     </row>
-    <row r="118" spans="1:19" ht="39.6" hidden="1" customHeight="1">
-      <c r="A118" s="116">
+    <row r="118" spans="1:19" ht="39.6" customHeight="1">
+      <c r="A118" s="115">
         <v>30</v>
       </c>
       <c r="B118" s="61" t="s">
@@ -11126,7 +11126,7 @@
       <c r="S118" s="61"/>
     </row>
     <row r="119" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A119" s="116"/>
+      <c r="A119" s="115"/>
       <c r="B119" s="61" t="s">
         <v>329</v>
       </c>
@@ -11178,7 +11178,7 @@
       <c r="S119" s="62"/>
     </row>
     <row r="120" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A120" s="131">
+      <c r="A120" s="129">
         <v>31</v>
       </c>
       <c r="B120" s="61" t="s">
@@ -11231,7 +11231,7 @@
       </c>
     </row>
     <row r="121" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="117"/>
+      <c r="A121" s="120"/>
       <c r="B121" s="61" t="s">
         <v>332</v>
       </c>
@@ -11282,7 +11282,7 @@
       </c>
     </row>
     <row r="122" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A122" s="117"/>
+      <c r="A122" s="120"/>
       <c r="B122" s="61" t="s">
         <v>332</v>
       </c>
@@ -11334,7 +11334,7 @@
       </c>
     </row>
     <row r="123" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A123" s="117"/>
+      <c r="A123" s="120"/>
       <c r="B123" s="61" t="s">
         <v>332</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="131.25" hidden="1" customHeight="1">
+    <row r="124" spans="1:19" ht="131.25" customHeight="1">
       <c r="A124" s="62"/>
       <c r="B124" s="61" t="s">
         <v>341</v>
@@ -11801,7 +11801,7 @@
       <c r="S131" s="62"/>
     </row>
     <row r="132" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A132" s="116">
+      <c r="A132" s="115">
         <v>35</v>
       </c>
       <c r="B132" s="61" t="s">
@@ -11857,7 +11857,7 @@
       </c>
     </row>
     <row r="133" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A133" s="116"/>
+      <c r="A133" s="115"/>
       <c r="B133" s="61" t="s">
         <v>353</v>
       </c>
@@ -11909,7 +11909,7 @@
       <c r="S133" s="62"/>
     </row>
     <row r="134" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A134" s="116"/>
+      <c r="A134" s="115"/>
       <c r="B134" s="61" t="s">
         <v>353</v>
       </c>
@@ -11967,7 +11967,7 @@
       </c>
     </row>
     <row r="135" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A135" s="116"/>
+      <c r="A135" s="115"/>
       <c r="B135" s="61" t="s">
         <v>353</v>
       </c>
@@ -12076,7 +12076,7 @@
       <c r="S136" s="61"/>
     </row>
     <row r="137" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A137" s="116">
+      <c r="A137" s="115">
         <v>36</v>
       </c>
       <c r="B137" s="61" t="s">
@@ -12130,7 +12130,7 @@
       <c r="S137" s="61"/>
     </row>
     <row r="138" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A138" s="116"/>
+      <c r="A138" s="115"/>
       <c r="B138" s="61" t="s">
         <v>362</v>
       </c>
@@ -12181,8 +12181,8 @@
       </c>
       <c r="S138" s="61"/>
     </row>
-    <row r="139" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A139" s="116"/>
+    <row r="139" spans="1:19" ht="40.950000000000003" customHeight="1">
+      <c r="A139" s="115"/>
       <c r="B139" s="61" t="s">
         <v>362</v>
       </c>
@@ -12234,7 +12234,7 @@
       <c r="S139" s="61"/>
     </row>
     <row r="140" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A140" s="116"/>
+      <c r="A140" s="115"/>
       <c r="B140" s="61" t="s">
         <v>362</v>
       </c>
@@ -12285,7 +12285,7 @@
       <c r="S140" s="61"/>
     </row>
     <row r="141" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A141" s="116"/>
+      <c r="A141" s="115"/>
       <c r="B141" s="61" t="s">
         <v>362</v>
       </c>
@@ -12337,7 +12337,7 @@
       <c r="S141" s="61"/>
     </row>
     <row r="142" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A142" s="116"/>
+      <c r="A142" s="115"/>
       <c r="B142" s="61" t="s">
         <v>362</v>
       </c>
@@ -12389,7 +12389,7 @@
       <c r="S142" s="62"/>
     </row>
     <row r="143" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A143" s="116"/>
+      <c r="A143" s="115"/>
       <c r="B143" s="61" t="s">
         <v>362</v>
       </c>
@@ -12441,7 +12441,7 @@
       <c r="S143" s="61"/>
     </row>
     <row r="144" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A144" s="116">
+      <c r="A144" s="115">
         <v>37</v>
       </c>
       <c r="B144" s="61" t="s">
@@ -12497,7 +12497,7 @@
       </c>
     </row>
     <row r="145" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A145" s="116"/>
+      <c r="A145" s="115"/>
       <c r="B145" s="61" t="s">
         <v>378</v>
       </c>
@@ -12547,7 +12547,7 @@
       </c>
     </row>
     <row r="146" spans="1:19" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A146" s="116"/>
+      <c r="A146" s="115"/>
       <c r="B146" s="61" t="s">
         <v>378</v>
       </c>
@@ -12651,7 +12651,7 @@
       </c>
     </row>
     <row r="148" spans="1:19" ht="35.4" hidden="1" customHeight="1">
-      <c r="A148" s="126"/>
+      <c r="A148" s="116"/>
       <c r="B148" s="61" t="s">
         <v>383</v>
       </c>
@@ -12702,7 +12702,7 @@
       </c>
     </row>
     <row r="149" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A149" s="122"/>
+      <c r="A149" s="117"/>
       <c r="B149" s="61" t="s">
         <v>383</v>
       </c>
@@ -12919,7 +12919,7 @@
       </c>
     </row>
     <row r="153" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A153" s="126"/>
+      <c r="A153" s="116"/>
       <c r="B153" s="61" t="s">
         <v>394</v>
       </c>
@@ -12968,7 +12968,7 @@
       </c>
     </row>
     <row r="154" spans="1:19" ht="183.6" hidden="1" customHeight="1">
-      <c r="A154" s="126"/>
+      <c r="A154" s="116"/>
       <c r="B154" s="61" t="s">
         <v>394</v>
       </c>
@@ -13015,7 +13015,7 @@
       </c>
     </row>
     <row r="155" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A155" s="126"/>
+      <c r="A155" s="116"/>
       <c r="B155" s="61" t="s">
         <v>394</v>
       </c>
@@ -13064,7 +13064,7 @@
       </c>
     </row>
     <row r="156" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="126"/>
+      <c r="A156" s="116"/>
       <c r="B156" s="61" t="s">
         <v>394</v>
       </c>
@@ -13118,7 +13118,7 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A157" s="126"/>
+      <c r="A157" s="116"/>
       <c r="B157" s="61" t="s">
         <v>394</v>
       </c>
@@ -13172,7 +13172,7 @@
       </c>
     </row>
     <row r="158" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A158" s="126"/>
+      <c r="A158" s="116"/>
       <c r="B158" s="61" t="s">
         <v>394</v>
       </c>
@@ -13226,7 +13226,7 @@
       </c>
     </row>
     <row r="159" spans="1:19" ht="102" hidden="1">
-      <c r="A159" s="126"/>
+      <c r="A159" s="116"/>
       <c r="B159" s="61" t="s">
         <v>408</v>
       </c>
@@ -13276,7 +13276,7 @@
       <c r="S159" s="61"/>
     </row>
     <row r="160" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A160" s="126"/>
+      <c r="A160" s="116"/>
       <c r="B160" s="61" t="s">
         <v>408</v>
       </c>
@@ -13328,8 +13328,8 @@
       </c>
       <c r="S160" s="61"/>
     </row>
-    <row r="161" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A161" s="126"/>
+    <row r="161" spans="1:19" ht="40.799999999999997">
+      <c r="A161" s="116"/>
       <c r="B161" s="61" t="s">
         <v>408</v>
       </c>
@@ -13379,7 +13379,7 @@
       <c r="S161" s="61"/>
     </row>
     <row r="162" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A162" s="126"/>
+      <c r="A162" s="116"/>
       <c r="B162" s="61" t="s">
         <v>408</v>
       </c>
@@ -13433,7 +13433,7 @@
       </c>
     </row>
     <row r="163" spans="1:19" ht="27.75" hidden="1" customHeight="1">
-      <c r="A163" s="122"/>
+      <c r="A163" s="117"/>
       <c r="B163" s="61" t="s">
         <v>416</v>
       </c>
@@ -13484,7 +13484,7 @@
       </c>
     </row>
     <row r="164" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A164" s="126"/>
+      <c r="A164" s="116"/>
       <c r="B164" s="61" t="s">
         <v>416</v>
       </c>
@@ -13535,7 +13535,7 @@
       </c>
     </row>
     <row r="165" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A165" s="122"/>
+      <c r="A165" s="117"/>
       <c r="B165" s="61" t="s">
         <v>416</v>
       </c>
@@ -13704,7 +13704,7 @@
       </c>
     </row>
     <row r="168" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A168" s="127">
+      <c r="A168" s="122">
         <v>44</v>
       </c>
       <c r="B168" s="61" t="s">
@@ -13762,7 +13762,7 @@
       </c>
     </row>
     <row r="169" spans="1:19" ht="45" hidden="1" customHeight="1">
-      <c r="A169" s="128"/>
+      <c r="A169" s="123"/>
       <c r="B169" s="61" t="s">
         <v>430</v>
       </c>
@@ -13811,7 +13811,7 @@
       </c>
     </row>
     <row r="170" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A170" s="128"/>
+      <c r="A170" s="123"/>
       <c r="B170" s="61" t="s">
         <v>430</v>
       </c>
@@ -13867,7 +13867,7 @@
       </c>
     </row>
     <row r="171" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A171" s="128"/>
+      <c r="A171" s="123"/>
       <c r="B171" s="61" t="s">
         <v>430</v>
       </c>
@@ -13921,7 +13921,7 @@
       </c>
     </row>
     <row r="172" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A172" s="129"/>
+      <c r="A172" s="124"/>
       <c r="B172" s="61" t="s">
         <v>438</v>
       </c>
@@ -13975,7 +13975,7 @@
       </c>
     </row>
     <row r="173" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A173" s="116">
+      <c r="A173" s="115">
         <v>45</v>
       </c>
       <c r="B173" s="61" t="s">
@@ -14030,7 +14030,7 @@
       </c>
     </row>
     <row r="174" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A174" s="116"/>
+      <c r="A174" s="115"/>
       <c r="B174" s="61" t="s">
         <v>440</v>
       </c>
@@ -14084,7 +14084,7 @@
       </c>
     </row>
     <row r="175" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A175" s="116"/>
+      <c r="A175" s="115"/>
       <c r="B175" s="61" t="s">
         <v>440</v>
       </c>
@@ -14136,7 +14136,7 @@
       <c r="S175" s="61"/>
     </row>
     <row r="176" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A176" s="116"/>
+      <c r="A176" s="115"/>
       <c r="B176" s="61" t="s">
         <v>440</v>
       </c>
@@ -14190,7 +14190,7 @@
       </c>
     </row>
     <row r="177" spans="1:19" ht="61.2" hidden="1">
-      <c r="A177" s="116"/>
+      <c r="A177" s="115"/>
       <c r="B177" s="61" t="s">
         <v>440</v>
       </c>
@@ -14242,7 +14242,7 @@
       <c r="S177" s="61"/>
     </row>
     <row r="178" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A178" s="116"/>
+      <c r="A178" s="115"/>
       <c r="B178" s="61" t="s">
         <v>448</v>
       </c>
@@ -14296,7 +14296,7 @@
       </c>
     </row>
     <row r="179" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A179" s="116"/>
+      <c r="A179" s="115"/>
       <c r="B179" s="61" t="s">
         <v>450</v>
       </c>
@@ -14451,7 +14451,7 @@
       <c r="S181" s="62"/>
     </row>
     <row r="182" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A182" s="130">
+      <c r="A182" s="125">
         <v>46</v>
       </c>
       <c r="B182" s="61" t="s">
@@ -14503,7 +14503,7 @@
       </c>
     </row>
     <row r="183" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A183" s="130"/>
+      <c r="A183" s="125"/>
       <c r="B183" s="61" t="s">
         <v>453</v>
       </c>
@@ -14553,7 +14553,7 @@
       </c>
     </row>
     <row r="184" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A184" s="130"/>
+      <c r="A184" s="125"/>
       <c r="B184" s="61" t="s">
         <v>453</v>
       </c>
@@ -14663,7 +14663,7 @@
       </c>
     </row>
     <row r="186" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A186" s="128"/>
+      <c r="A186" s="123"/>
       <c r="B186" s="61" t="s">
         <v>460</v>
       </c>
@@ -14711,7 +14711,7 @@
       </c>
     </row>
     <row r="187" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A187" s="128"/>
+      <c r="A187" s="123"/>
       <c r="B187" s="83" t="s">
         <v>460</v>
       </c>
@@ -14757,7 +14757,7 @@
       <c r="S187" s="83"/>
     </row>
     <row r="188" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A188" s="129"/>
+      <c r="A188" s="124"/>
       <c r="B188" s="61" t="s">
         <v>460</v>
       </c>
@@ -14857,7 +14857,7 @@
       </c>
     </row>
     <row r="190" spans="1:19" ht="64.95" hidden="1" customHeight="1">
-      <c r="A190" s="116">
+      <c r="A190" s="115">
         <v>48</v>
       </c>
       <c r="B190" s="61" t="s">
@@ -14910,7 +14910,7 @@
       </c>
     </row>
     <row r="191" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A191" s="116"/>
+      <c r="A191" s="115"/>
       <c r="B191" s="61" t="s">
         <v>467</v>
       </c>
@@ -14961,7 +14961,7 @@
       </c>
     </row>
     <row r="192" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A192" s="116"/>
+      <c r="A192" s="115"/>
       <c r="B192" s="61" t="s">
         <v>467</v>
       </c>
@@ -15042,7 +15042,7 @@
       <c r="S193" s="62"/>
     </row>
     <row r="194" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A194" s="126"/>
+      <c r="A194" s="116"/>
       <c r="B194" s="61" t="s">
         <v>478</v>
       </c>
@@ -15094,7 +15094,7 @@
       </c>
     </row>
     <row r="195" spans="1:19" ht="24.6" hidden="1" customHeight="1">
-      <c r="A195" s="122"/>
+      <c r="A195" s="117"/>
       <c r="B195" s="61" t="s">
         <v>478</v>
       </c>
@@ -15146,7 +15146,7 @@
       </c>
     </row>
     <row r="196" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A196" s="116">
+      <c r="A196" s="115">
         <v>51</v>
       </c>
       <c r="B196" s="61" t="s">
@@ -15199,7 +15199,7 @@
       </c>
     </row>
     <row r="197" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A197" s="116"/>
+      <c r="A197" s="115"/>
       <c r="B197" s="61" t="s">
         <v>482</v>
       </c>
@@ -15253,7 +15253,7 @@
       </c>
     </row>
     <row r="198" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A198" s="116"/>
+      <c r="A198" s="115"/>
       <c r="B198" s="61" t="s">
         <v>482</v>
       </c>
@@ -15307,7 +15307,7 @@
       </c>
     </row>
     <row r="199" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A199" s="116"/>
+      <c r="A199" s="115"/>
       <c r="B199" s="61" t="s">
         <v>482</v>
       </c>
@@ -15514,7 +15514,7 @@
       </c>
     </row>
     <row r="203" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A203" s="116">
+      <c r="A203" s="115">
         <v>53</v>
       </c>
       <c r="B203" s="61" t="s">
@@ -15569,7 +15569,7 @@
       </c>
     </row>
     <row r="204" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A204" s="116"/>
+      <c r="A204" s="115"/>
       <c r="B204" s="61" t="s">
         <v>494</v>
       </c>
@@ -15623,7 +15623,7 @@
       </c>
     </row>
     <row r="205" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A205" s="116"/>
+      <c r="A205" s="115"/>
       <c r="B205" s="62" t="s">
         <v>498</v>
       </c>
@@ -15677,7 +15677,7 @@
       </c>
     </row>
     <row r="206" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A206" s="116">
+      <c r="A206" s="115">
         <v>54</v>
       </c>
       <c r="B206" s="61" t="s">
@@ -15731,7 +15731,7 @@
       </c>
     </row>
     <row r="207" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A207" s="116"/>
+      <c r="A207" s="115"/>
       <c r="B207" s="61" t="s">
         <v>501</v>
       </c>
@@ -15787,7 +15787,7 @@
       </c>
     </row>
     <row r="208" spans="1:19" ht="32.4" hidden="1" customHeight="1">
-      <c r="A208" s="116">
+      <c r="A208" s="115">
         <v>55</v>
       </c>
       <c r="B208" s="61" t="s">
@@ -15842,7 +15842,7 @@
       </c>
     </row>
     <row r="209" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A209" s="116"/>
+      <c r="A209" s="115"/>
       <c r="B209" s="61" t="s">
         <v>504</v>
       </c>
@@ -15894,7 +15894,7 @@
       <c r="S209" s="61"/>
     </row>
     <row r="210" spans="1:19" ht="16.2" hidden="1" customHeight="1">
-      <c r="A210" s="116"/>
+      <c r="A210" s="115"/>
       <c r="B210" s="61" t="s">
         <v>504</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="S210" s="62"/>
     </row>
     <row r="211" spans="1:19" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A211" s="116">
+      <c r="A211" s="115">
         <v>56</v>
       </c>
       <c r="B211" s="61" t="s">
@@ -15999,7 +15999,7 @@
       </c>
     </row>
     <row r="212" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A212" s="116"/>
+      <c r="A212" s="115"/>
       <c r="B212" s="61" t="s">
         <v>513</v>
       </c>
@@ -16055,7 +16055,7 @@
       </c>
     </row>
     <row r="213" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A213" s="127">
+      <c r="A213" s="122">
         <v>57</v>
       </c>
       <c r="B213" s="61" t="s">
@@ -16108,7 +16108,7 @@
       </c>
     </row>
     <row r="214" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A214" s="128"/>
+      <c r="A214" s="123"/>
       <c r="B214" s="61" t="s">
         <v>515</v>
       </c>
@@ -16162,7 +16162,7 @@
       </c>
     </row>
     <row r="215" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A215" s="128"/>
+      <c r="A215" s="123"/>
       <c r="B215" s="61" t="s">
         <v>515</v>
       </c>
@@ -16216,7 +16216,7 @@
       </c>
     </row>
     <row r="216" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A216" s="126"/>
+      <c r="A216" s="116"/>
       <c r="B216" s="61" t="s">
         <v>515</v>
       </c>
@@ -16269,7 +16269,7 @@
       </c>
     </row>
     <row r="217" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A217" s="129"/>
+      <c r="A217" s="124"/>
       <c r="B217" s="61" t="s">
         <v>515</v>
       </c>
@@ -16534,7 +16534,7 @@
       </c>
     </row>
     <row r="222" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A222" s="116">
+      <c r="A222" s="115">
         <v>59</v>
       </c>
       <c r="B222" s="61" t="s">
@@ -16587,7 +16587,7 @@
       </c>
     </row>
     <row r="223" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A223" s="116"/>
+      <c r="A223" s="115"/>
       <c r="B223" s="61" t="s">
         <v>535</v>
       </c>
@@ -16641,7 +16641,7 @@
       </c>
     </row>
     <row r="224" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A224" s="116"/>
+      <c r="A224" s="115"/>
       <c r="B224" s="61" t="s">
         <v>535</v>
       </c>
@@ -16690,7 +16690,7 @@
       <c r="S224" s="61"/>
     </row>
     <row r="225" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A225" s="116"/>
+      <c r="A225" s="115"/>
       <c r="B225" s="61" t="s">
         <v>535</v>
       </c>
@@ -16744,7 +16744,7 @@
       </c>
     </row>
     <row r="226" spans="1:19" ht="61.2" hidden="1">
-      <c r="A226" s="116"/>
+      <c r="A226" s="115"/>
       <c r="B226" s="61" t="s">
         <v>535</v>
       </c>
@@ -16792,7 +16792,7 @@
       <c r="S226" s="62"/>
     </row>
     <row r="227" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A227" s="116"/>
+      <c r="A227" s="115"/>
       <c r="B227" s="61" t="s">
         <v>535</v>
       </c>
@@ -17184,7 +17184,7 @@
       </c>
     </row>
     <row r="235" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="126"/>
+      <c r="A235" s="116"/>
       <c r="B235" s="61" t="s">
         <v>553</v>
       </c>
@@ -17236,7 +17236,7 @@
       </c>
     </row>
     <row r="236" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="126"/>
+      <c r="A236" s="116"/>
       <c r="B236" s="61" t="s">
         <v>553</v>
       </c>
@@ -17288,7 +17288,7 @@
       </c>
     </row>
     <row r="237" spans="1:19" ht="39.6" hidden="1" customHeight="1">
-      <c r="A237" s="126"/>
+      <c r="A237" s="116"/>
       <c r="B237" s="61" t="s">
         <v>553</v>
       </c>
@@ -17337,7 +17337,7 @@
       </c>
     </row>
     <row r="238" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A238" s="126"/>
+      <c r="A238" s="116"/>
       <c r="B238" s="61" t="s">
         <v>553</v>
       </c>
@@ -17389,8 +17389,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="239" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A239" s="122"/>
+    <row r="239" spans="1:19" ht="40.950000000000003" customHeight="1">
+      <c r="A239" s="117"/>
       <c r="B239" s="61" t="s">
         <v>566</v>
       </c>
@@ -17440,7 +17440,7 @@
       </c>
     </row>
     <row r="240" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="116">
+      <c r="A240" s="115">
         <v>64</v>
       </c>
       <c r="B240" s="61" t="s">
@@ -17493,7 +17493,7 @@
       <c r="S240" s="61"/>
     </row>
     <row r="241" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="116"/>
+      <c r="A241" s="115"/>
       <c r="B241" s="61" t="s">
         <v>569</v>
       </c>
@@ -17543,7 +17543,7 @@
       </c>
     </row>
     <row r="242" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="116"/>
+      <c r="A242" s="115"/>
       <c r="B242" s="61" t="s">
         <v>569</v>
       </c>
@@ -17600,8 +17600,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="243" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A243" s="116"/>
+    <row r="243" spans="1:19" ht="81.599999999999994">
+      <c r="A243" s="115"/>
       <c r="B243" s="61" t="s">
         <v>569</v>
       </c>
@@ -17651,7 +17651,7 @@
       </c>
     </row>
     <row r="244" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A244" s="116"/>
+      <c r="A244" s="115"/>
       <c r="B244" s="61" t="s">
         <v>569</v>
       </c>
@@ -17684,7 +17684,7 @@
       <c r="S244" s="61"/>
     </row>
     <row r="245" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A245" s="116"/>
+      <c r="A245" s="115"/>
       <c r="B245" s="61" t="s">
         <v>569</v>
       </c>
@@ -17734,7 +17734,7 @@
       </c>
     </row>
     <row r="246" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A246" s="116"/>
+      <c r="A246" s="115"/>
       <c r="B246" s="61" t="s">
         <v>569</v>
       </c>
@@ -17839,7 +17839,7 @@
       <c r="S247" s="61"/>
     </row>
     <row r="248" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A248" s="116">
+      <c r="A248" s="115">
         <v>65</v>
       </c>
       <c r="B248" s="61" t="s">
@@ -17891,8 +17891,8 @@
         <v>583</v>
       </c>
     </row>
-    <row r="249" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="116"/>
+    <row r="249" spans="1:19" ht="81.599999999999994" customHeight="1">
+      <c r="A249" s="115"/>
       <c r="B249" s="61" t="s">
         <v>577</v>
       </c>
@@ -17942,7 +17942,7 @@
       </c>
     </row>
     <row r="250" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A250" s="116"/>
+      <c r="A250" s="115"/>
       <c r="B250" s="61" t="s">
         <v>577</v>
       </c>
@@ -18021,7 +18021,7 @@
       <c r="R251" s="62"/>
       <c r="S251" s="62"/>
     </row>
-    <row r="252" spans="1:19" ht="20.399999999999999" hidden="1">
+    <row r="252" spans="1:19" ht="20.399999999999999">
       <c r="A252" s="62"/>
       <c r="B252" s="61" t="s">
         <v>586</v>
@@ -18174,7 +18174,7 @@
       </c>
     </row>
     <row r="255" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A255" s="126"/>
+      <c r="A255" s="116"/>
       <c r="B255" s="61" t="s">
         <v>590</v>
       </c>
@@ -18227,7 +18227,7 @@
       </c>
     </row>
     <row r="256" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A256" s="126"/>
+      <c r="A256" s="116"/>
       <c r="B256" s="61" t="s">
         <v>590</v>
       </c>
@@ -18281,7 +18281,7 @@
       </c>
     </row>
     <row r="257" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A257" s="126"/>
+      <c r="A257" s="116"/>
       <c r="B257" s="61" t="s">
         <v>590</v>
       </c>
@@ -18335,7 +18335,7 @@
       </c>
     </row>
     <row r="258" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A258" s="126"/>
+      <c r="A258" s="116"/>
       <c r="B258" s="61" t="s">
         <v>590</v>
       </c>
@@ -18387,7 +18387,7 @@
       </c>
     </row>
     <row r="259" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A259" s="122"/>
+      <c r="A259" s="117"/>
       <c r="B259" s="61" t="s">
         <v>590</v>
       </c>
@@ -18490,7 +18490,7 @@
       </c>
     </row>
     <row r="261" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A261" s="126"/>
+      <c r="A261" s="116"/>
       <c r="B261" s="61" t="s">
         <v>600</v>
       </c>
@@ -18538,7 +18538,7 @@
       </c>
     </row>
     <row r="262" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="126"/>
+      <c r="A262" s="116"/>
       <c r="B262" s="61" t="s">
         <v>605</v>
       </c>
@@ -18584,7 +18584,7 @@
       </c>
     </row>
     <row r="263" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A263" s="126"/>
+      <c r="A263" s="116"/>
       <c r="B263" s="61" t="s">
         <v>605</v>
       </c>
@@ -18632,7 +18632,7 @@
       </c>
     </row>
     <row r="264" spans="1:19" ht="46.2" hidden="1" customHeight="1">
-      <c r="A264" s="126"/>
+      <c r="A264" s="116"/>
       <c r="B264" s="61" t="s">
         <v>600</v>
       </c>
@@ -18739,7 +18739,7 @@
       <c r="S265" s="61"/>
     </row>
     <row r="266" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A266" s="116">
+      <c r="A266" s="115">
         <v>70</v>
       </c>
       <c r="B266" s="61" t="s">
@@ -18795,7 +18795,7 @@
       <c r="S266" s="61"/>
     </row>
     <row r="267" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="116"/>
+      <c r="A267" s="115"/>
       <c r="B267" s="61" t="s">
         <v>611</v>
       </c>
@@ -18849,7 +18849,7 @@
       <c r="S267" s="61"/>
     </row>
     <row r="268" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="116"/>
+      <c r="A268" s="115"/>
       <c r="B268" s="61" t="s">
         <v>611</v>
       </c>
@@ -18903,7 +18903,7 @@
       <c r="S268" s="61"/>
     </row>
     <row r="269" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A269" s="116"/>
+      <c r="A269" s="115"/>
       <c r="B269" s="61" t="s">
         <v>611</v>
       </c>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="S269" s="62"/>
     </row>
-    <row r="270" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="270" spans="1:19" ht="40.950000000000003" customHeight="1">
       <c r="A270" s="62"/>
       <c r="B270" s="61" t="s">
         <v>622</v>
@@ -19009,7 +19009,7 @@
       </c>
     </row>
     <row r="271" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A271" s="116">
+      <c r="A271" s="115">
         <v>71</v>
       </c>
       <c r="B271" s="61" t="s">
@@ -19063,7 +19063,7 @@
       <c r="S271" s="61"/>
     </row>
     <row r="272" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="116"/>
+      <c r="A272" s="115"/>
       <c r="B272" s="61" t="s">
         <v>622</v>
       </c>
@@ -19115,7 +19115,7 @@
       <c r="S272" s="61"/>
     </row>
     <row r="273" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A273" s="116"/>
+      <c r="A273" s="115"/>
       <c r="B273" s="61" t="s">
         <v>622</v>
       </c>
@@ -19169,7 +19169,7 @@
       </c>
     </row>
     <row r="274" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A274" s="116"/>
+      <c r="A274" s="115"/>
       <c r="B274" s="61" t="s">
         <v>622</v>
       </c>
@@ -19221,7 +19221,7 @@
       <c r="S274" s="61"/>
     </row>
     <row r="275" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A275" s="116"/>
+      <c r="A275" s="115"/>
       <c r="B275" s="62" t="s">
         <v>629</v>
       </c>
@@ -19274,7 +19274,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="276" spans="1:19" ht="20.399999999999999" hidden="1">
+    <row r="276" spans="1:19" ht="20.399999999999999">
       <c r="A276" s="62">
         <v>72</v>
       </c>
@@ -19482,8 +19482,8 @@
       </c>
       <c r="S279" s="62"/>
     </row>
-    <row r="280" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A280" s="116">
+    <row r="280" spans="1:19" ht="40.799999999999997">
+      <c r="A280" s="115">
         <v>74</v>
       </c>
       <c r="B280" s="61" t="s">
@@ -19535,7 +19535,7 @@
       </c>
     </row>
     <row r="281" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A281" s="116"/>
+      <c r="A281" s="115"/>
       <c r="B281" s="61" t="s">
         <v>637</v>
       </c>
@@ -19582,7 +19582,7 @@
       <c r="S281" s="62"/>
     </row>
     <row r="282" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A282" s="116">
+      <c r="A282" s="115">
         <v>75</v>
       </c>
       <c r="B282" s="61" t="s">
@@ -19635,7 +19635,7 @@
       </c>
     </row>
     <row r="283" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A283" s="116"/>
+      <c r="A283" s="115"/>
       <c r="B283" s="61" t="s">
         <v>640</v>
       </c>
@@ -19687,7 +19687,7 @@
       <c r="S283" s="61"/>
     </row>
     <row r="284" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A284" s="122">
+      <c r="A284" s="117">
         <v>76</v>
       </c>
       <c r="B284" s="61" t="s">
@@ -19743,7 +19743,7 @@
       </c>
     </row>
     <row r="285" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A285" s="122"/>
+      <c r="A285" s="117"/>
       <c r="B285" s="61" t="s">
         <v>644</v>
       </c>
@@ -19797,7 +19797,7 @@
       </c>
     </row>
     <row r="286" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A286" s="122"/>
+      <c r="A286" s="117"/>
       <c r="B286" s="61" t="s">
         <v>644</v>
       </c>
@@ -19851,7 +19851,7 @@
       </c>
     </row>
     <row r="287" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A287" s="122"/>
+      <c r="A287" s="117"/>
       <c r="B287" s="61" t="s">
         <v>644</v>
       </c>
@@ -19905,7 +19905,7 @@
       </c>
     </row>
     <row r="288" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A288" s="116"/>
+      <c r="A288" s="115"/>
       <c r="B288" s="61" t="s">
         <v>644</v>
       </c>
@@ -19956,7 +19956,7 @@
       </c>
     </row>
     <row r="289" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A289" s="116"/>
+      <c r="A289" s="115"/>
       <c r="B289" s="61" t="s">
         <v>644</v>
       </c>
@@ -20008,7 +20008,7 @@
       </c>
     </row>
     <row r="290" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A290" s="116"/>
+      <c r="A290" s="115"/>
       <c r="B290" s="61" t="s">
         <v>644</v>
       </c>
@@ -20062,7 +20062,7 @@
       </c>
     </row>
     <row r="291" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A291" s="116"/>
+      <c r="A291" s="115"/>
       <c r="B291" s="83" t="s">
         <v>644</v>
       </c>
@@ -20110,7 +20110,7 @@
       <c r="S291" s="83"/>
     </row>
     <row r="292" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A292" s="116"/>
+      <c r="A292" s="115"/>
       <c r="B292" s="61" t="s">
         <v>644</v>
       </c>
@@ -20220,7 +20220,7 @@
       </c>
     </row>
     <row r="294" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A294" s="116">
+      <c r="A294" s="115">
         <v>77</v>
       </c>
       <c r="B294" s="61" t="s">
@@ -20280,7 +20280,7 @@
       </c>
     </row>
     <row r="295" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A295" s="116"/>
+      <c r="A295" s="115"/>
       <c r="B295" s="61" t="s">
         <v>658</v>
       </c>
@@ -20338,7 +20338,7 @@
       </c>
     </row>
     <row r="296" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A296" s="116"/>
+      <c r="A296" s="115"/>
       <c r="B296" s="61" t="s">
         <v>658</v>
       </c>
@@ -20396,7 +20396,7 @@
       </c>
     </row>
     <row r="297" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A297" s="116">
+      <c r="A297" s="115">
         <v>78</v>
       </c>
       <c r="B297" s="61" t="s">
@@ -20449,7 +20449,7 @@
       </c>
     </row>
     <row r="298" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A298" s="116"/>
+      <c r="A298" s="115"/>
       <c r="B298" s="61" t="s">
         <v>669</v>
       </c>
@@ -20501,7 +20501,7 @@
       <c r="S298" s="61"/>
     </row>
     <row r="299" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A299" s="116"/>
+      <c r="A299" s="115"/>
       <c r="B299" s="61" t="s">
         <v>669</v>
       </c>
@@ -20555,7 +20555,7 @@
       </c>
     </row>
     <row r="300" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A300" s="126"/>
+      <c r="A300" s="116"/>
       <c r="B300" s="61" t="s">
         <v>605</v>
       </c>
@@ -20607,7 +20607,7 @@
       <c r="S300" s="61"/>
     </row>
     <row r="301" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A301" s="122"/>
+      <c r="A301" s="117"/>
       <c r="B301" s="61" t="s">
         <v>605</v>
       </c>
@@ -20712,7 +20712,7 @@
       </c>
     </row>
     <row r="303" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A303" s="126"/>
+      <c r="A303" s="116"/>
       <c r="B303" s="61" t="s">
         <v>682</v>
       </c>
@@ -20816,7 +20816,7 @@
       </c>
     </row>
     <row r="305" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="126"/>
+      <c r="A305" s="116"/>
       <c r="B305" s="61" t="s">
         <v>684</v>
       </c>
@@ -20868,7 +20868,7 @@
       </c>
     </row>
     <row r="306" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="126"/>
+      <c r="A306" s="116"/>
       <c r="B306" s="61" t="s">
         <v>684</v>
       </c>
@@ -20919,7 +20919,7 @@
       </c>
     </row>
     <row r="307" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A307" s="122"/>
+      <c r="A307" s="117"/>
       <c r="B307" s="61" t="s">
         <v>684</v>
       </c>
@@ -21041,16 +21041,16 @@
       <c r="D309" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E309" s="123">
+      <c r="E309" s="127">
         <v>4600018191</v>
       </c>
-      <c r="F309" s="132" t="s">
+      <c r="F309" s="126" t="s">
         <v>695</v>
       </c>
-      <c r="G309" s="116" t="s">
+      <c r="G309" s="115" t="s">
         <v>696</v>
       </c>
-      <c r="H309" s="116">
+      <c r="H309" s="115">
         <v>13.3</v>
       </c>
       <c r="I309" s="121" t="s">
@@ -21059,36 +21059,36 @@
       <c r="J309" s="121" t="s">
         <v>516</v>
       </c>
-      <c r="K309" s="120">
+      <c r="K309" s="118">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L309" s="120">
+      <c r="L309" s="118">
         <v>0</v>
       </c>
-      <c r="M309" s="120">
+      <c r="M309" s="118">
         <f>+K309</f>
         <v>988077089</v>
       </c>
-      <c r="N309" s="117" t="s">
+      <c r="N309" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="O309" s="117" t="s">
+      <c r="O309" s="120" t="s">
         <v>697</v>
       </c>
-      <c r="P309" s="116">
+      <c r="P309" s="115">
         <v>2025</v>
       </c>
-      <c r="Q309" s="117" t="s">
+      <c r="Q309" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="R309" s="116"/>
-      <c r="S309" s="116" t="s">
+      <c r="R309" s="115"/>
+      <c r="S309" s="115" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A310" s="116">
+      <c r="A310" s="115">
         <v>84</v>
       </c>
       <c r="B310" s="61" t="s">
@@ -21100,24 +21100,24 @@
       <c r="D310" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E310" s="124"/>
-      <c r="F310" s="117"/>
-      <c r="G310" s="116"/>
-      <c r="H310" s="116"/>
-      <c r="I310" s="122"/>
-      <c r="J310" s="122"/>
-      <c r="K310" s="120"/>
-      <c r="L310" s="120"/>
-      <c r="M310" s="120"/>
-      <c r="N310" s="117"/>
-      <c r="O310" s="117"/>
-      <c r="P310" s="116"/>
-      <c r="Q310" s="117"/>
-      <c r="R310" s="116"/>
-      <c r="S310" s="116"/>
+      <c r="E310" s="128"/>
+      <c r="F310" s="120"/>
+      <c r="G310" s="115"/>
+      <c r="H310" s="115"/>
+      <c r="I310" s="117"/>
+      <c r="J310" s="117"/>
+      <c r="K310" s="118"/>
+      <c r="L310" s="118"/>
+      <c r="M310" s="118"/>
+      <c r="N310" s="120"/>
+      <c r="O310" s="120"/>
+      <c r="P310" s="115"/>
+      <c r="Q310" s="120"/>
+      <c r="R310" s="115"/>
+      <c r="S310" s="115"/>
     </row>
     <row r="311" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="116"/>
+      <c r="A311" s="115"/>
       <c r="B311" s="61" t="s">
         <v>694</v>
       </c>
@@ -21127,16 +21127,16 @@
       <c r="D311" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E311" s="123">
+      <c r="E311" s="127">
         <v>4600009793</v>
       </c>
-      <c r="F311" s="117" t="s">
+      <c r="F311" s="120" t="s">
         <v>699</v>
       </c>
-      <c r="G311" s="116" t="s">
+      <c r="G311" s="115" t="s">
         <v>700</v>
       </c>
-      <c r="H311" s="116">
+      <c r="H311" s="115">
         <v>31.12</v>
       </c>
       <c r="I311" s="121" t="s">
@@ -21145,37 +21145,37 @@
       <c r="J311" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="K311" s="120">
+      <c r="K311" s="118">
         <f>+M311</f>
         <v>73907566008</v>
       </c>
-      <c r="L311" s="120">
+      <c r="L311" s="118">
         <v>0</v>
       </c>
-      <c r="M311" s="120">
+      <c r="M311" s="118">
         <v>73907566008</v>
       </c>
-      <c r="N311" s="117" t="s">
+      <c r="N311" s="120" t="s">
         <v>701</v>
       </c>
-      <c r="O311" s="117" t="s">
+      <c r="O311" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="P311" s="116">
+      <c r="P311" s="115">
         <v>2019</v>
       </c>
-      <c r="Q311" s="117" t="s">
+      <c r="Q311" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="R311" s="133">
+      <c r="R311" s="119">
         <v>1</v>
       </c>
-      <c r="S311" s="116" t="s">
+      <c r="S311" s="115" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="116"/>
+      <c r="A312" s="115"/>
       <c r="B312" s="61" t="s">
         <v>698</v>
       </c>
@@ -21185,24 +21185,24 @@
       <c r="D312" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E312" s="124"/>
-      <c r="F312" s="117"/>
-      <c r="G312" s="116"/>
-      <c r="H312" s="116"/>
-      <c r="I312" s="122"/>
-      <c r="J312" s="122"/>
-      <c r="K312" s="120"/>
-      <c r="L312" s="120"/>
-      <c r="M312" s="120"/>
-      <c r="N312" s="117"/>
-      <c r="O312" s="117"/>
-      <c r="P312" s="116"/>
-      <c r="Q312" s="117"/>
-      <c r="R312" s="133"/>
-      <c r="S312" s="116"/>
+      <c r="E312" s="128"/>
+      <c r="F312" s="120"/>
+      <c r="G312" s="115"/>
+      <c r="H312" s="115"/>
+      <c r="I312" s="117"/>
+      <c r="J312" s="117"/>
+      <c r="K312" s="118"/>
+      <c r="L312" s="118"/>
+      <c r="M312" s="118"/>
+      <c r="N312" s="120"/>
+      <c r="O312" s="120"/>
+      <c r="P312" s="115"/>
+      <c r="Q312" s="120"/>
+      <c r="R312" s="119"/>
+      <c r="S312" s="115"/>
     </row>
     <row r="313" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="116"/>
+      <c r="A313" s="115"/>
       <c r="B313" s="61" t="s">
         <v>698</v>
       </c>
@@ -21258,7 +21258,7 @@
       </c>
     </row>
     <row r="314" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="116"/>
+      <c r="A314" s="115"/>
       <c r="B314" s="61" t="s">
         <v>698</v>
       </c>
@@ -21312,7 +21312,7 @@
       <c r="S314" s="61"/>
     </row>
     <row r="315" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A315" s="116"/>
+      <c r="A315" s="115"/>
       <c r="B315" s="61" t="s">
         <v>698</v>
       </c>
@@ -21505,7 +21505,7 @@
       <c r="S318" s="61"/>
     </row>
     <row r="319" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A319" s="122"/>
+      <c r="A319" s="117"/>
       <c r="B319" s="61" t="s">
         <v>704</v>
       </c>
@@ -21556,7 +21556,7 @@
       </c>
     </row>
     <row r="320" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A320" s="127">
+      <c r="A320" s="122">
         <v>86</v>
       </c>
       <c r="B320" s="61" t="s">
@@ -21608,7 +21608,7 @@
       </c>
     </row>
     <row r="321" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A321" s="128"/>
+      <c r="A321" s="123"/>
       <c r="B321" s="62" t="s">
         <v>710</v>
       </c>
@@ -21656,7 +21656,7 @@
       </c>
     </row>
     <row r="322" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A322" s="128"/>
+      <c r="A322" s="123"/>
       <c r="B322" s="62" t="s">
         <v>710</v>
       </c>
@@ -21707,8 +21707,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="323" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A323" s="128"/>
+    <row r="323" spans="1:19" ht="61.2" customHeight="1">
+      <c r="A323" s="123"/>
       <c r="B323" s="62" t="s">
         <v>710</v>
       </c>
@@ -21758,7 +21758,7 @@
       </c>
     </row>
     <row r="324" spans="1:19" ht="93" hidden="1" customHeight="1">
-      <c r="A324" s="126"/>
+      <c r="A324" s="116"/>
       <c r="B324" s="62" t="s">
         <v>710</v>
       </c>
@@ -21808,7 +21808,7 @@
       </c>
     </row>
     <row r="325" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A325" s="126"/>
+      <c r="A325" s="116"/>
       <c r="B325" s="62" t="s">
         <v>710</v>
       </c>
@@ -21858,7 +21858,7 @@
       </c>
     </row>
     <row r="326" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A326" s="128"/>
+      <c r="A326" s="123"/>
       <c r="B326" s="62" t="s">
         <v>710</v>
       </c>
@@ -21912,7 +21912,7 @@
       </c>
     </row>
     <row r="327" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A327" s="128"/>
+      <c r="A327" s="123"/>
       <c r="B327" s="61" t="s">
         <v>710</v>
       </c>
@@ -21962,7 +21962,7 @@
       </c>
     </row>
     <row r="328" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A328" s="128"/>
+      <c r="A328" s="123"/>
       <c r="B328" s="61" t="s">
         <v>710</v>
       </c>
@@ -22014,7 +22014,7 @@
       <c r="S328" s="61"/>
     </row>
     <row r="329" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A329" s="129"/>
+      <c r="A329" s="124"/>
       <c r="B329" s="61" t="s">
         <v>710</v>
       </c>
@@ -22292,7 +22292,7 @@
       </c>
     </row>
     <row r="335" spans="1:19" ht="44.4" hidden="1" customHeight="1">
-      <c r="A335" s="126"/>
+      <c r="A335" s="116"/>
       <c r="B335" s="61" t="s">
         <v>726</v>
       </c>
@@ -22343,7 +22343,7 @@
       </c>
     </row>
     <row r="336" spans="1:19" ht="155.4" hidden="1" customHeight="1">
-      <c r="A336" s="126"/>
+      <c r="A336" s="116"/>
       <c r="B336" s="61" t="s">
         <v>726</v>
       </c>
@@ -22394,7 +22394,7 @@
       </c>
     </row>
     <row r="337" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A337" s="122"/>
+      <c r="A337" s="117"/>
       <c r="B337" s="61" t="s">
         <v>726</v>
       </c>
@@ -22490,7 +22490,7 @@
       </c>
     </row>
     <row r="339" spans="1:19" s="80" customFormat="1" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A339" s="116">
+      <c r="A339" s="115">
         <v>90</v>
       </c>
       <c r="B339" s="75" t="s">
@@ -22545,7 +22545,7 @@
       </c>
     </row>
     <row r="340" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A340" s="116"/>
+      <c r="A340" s="115"/>
       <c r="B340" s="75" t="s">
         <v>734</v>
       </c>
@@ -22597,7 +22597,7 @@
       <c r="S340" s="77"/>
     </row>
     <row r="341" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A341" s="116">
+      <c r="A341" s="115">
         <v>91</v>
       </c>
       <c r="B341" s="61" t="s">
@@ -22653,7 +22653,7 @@
       </c>
     </row>
     <row r="342" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A342" s="116"/>
+      <c r="A342" s="115"/>
       <c r="B342" s="61" t="s">
         <v>737</v>
       </c>
@@ -22707,7 +22707,7 @@
       </c>
     </row>
     <row r="343" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A343" s="116"/>
+      <c r="A343" s="115"/>
       <c r="B343" s="61" t="s">
         <v>737</v>
       </c>
@@ -22755,7 +22755,7 @@
       </c>
     </row>
     <row r="344" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A344" s="116"/>
+      <c r="A344" s="115"/>
       <c r="B344" s="61" t="s">
         <v>737</v>
       </c>
@@ -22809,7 +22809,7 @@
       </c>
     </row>
     <row r="345" spans="1:19" ht="61.2" hidden="1">
-      <c r="A345" s="116"/>
+      <c r="A345" s="115"/>
       <c r="B345" s="61" t="s">
         <v>737</v>
       </c>
@@ -22860,7 +22860,7 @@
       </c>
     </row>
     <row r="346" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A346" s="116"/>
+      <c r="A346" s="115"/>
       <c r="B346" s="106" t="s">
         <v>737</v>
       </c>
@@ -22904,7 +22904,7 @@
       </c>
     </row>
     <row r="347" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A347" s="116"/>
+      <c r="A347" s="115"/>
       <c r="B347" s="61" t="s">
         <v>737</v>
       </c>
@@ -22958,7 +22958,7 @@
       </c>
     </row>
     <row r="348" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A348" s="116">
+      <c r="A348" s="115">
         <v>92</v>
       </c>
       <c r="B348" s="61" t="s">
@@ -23013,7 +23013,7 @@
       <c r="S348" s="61"/>
     </row>
     <row r="349" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="116"/>
+      <c r="A349" s="115"/>
       <c r="B349" s="61" t="s">
         <v>746</v>
       </c>
@@ -23065,7 +23065,7 @@
       </c>
     </row>
     <row r="350" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A350" s="116"/>
+      <c r="A350" s="115"/>
       <c r="B350" s="61" t="s">
         <v>746</v>
       </c>
@@ -23119,7 +23119,7 @@
       </c>
     </row>
     <row r="351" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A351" s="116">
+      <c r="A351" s="115">
         <v>93</v>
       </c>
       <c r="B351" s="61" t="s">
@@ -23171,7 +23171,7 @@
       </c>
     </row>
     <row r="352" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="116"/>
+      <c r="A352" s="115"/>
       <c r="B352" s="61" t="s">
         <v>751</v>
       </c>
@@ -23222,7 +23222,7 @@
       </c>
     </row>
     <row r="353" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="116"/>
+      <c r="A353" s="115"/>
       <c r="B353" s="61" t="s">
         <v>751</v>
       </c>
@@ -23276,7 +23276,7 @@
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.95" hidden="1" customHeight="1">
-      <c r="A354" s="116"/>
+      <c r="A354" s="115"/>
       <c r="B354" s="61" t="s">
         <v>751</v>
       </c>
@@ -23334,7 +23334,7 @@
       </c>
     </row>
     <row r="355" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A355" s="116"/>
+      <c r="A355" s="115"/>
       <c r="B355" s="61" t="s">
         <v>751</v>
       </c>
@@ -23386,7 +23386,7 @@
       </c>
     </row>
     <row r="356" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A356" s="116"/>
+      <c r="A356" s="115"/>
       <c r="B356" s="61" t="s">
         <v>751</v>
       </c>
@@ -23705,7 +23705,7 @@
       </c>
     </row>
     <row r="362" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A362" s="116"/>
+      <c r="A362" s="115"/>
       <c r="B362" s="61" t="s">
         <v>771</v>
       </c>
@@ -23758,7 +23758,7 @@
       <c r="S362" s="61"/>
     </row>
     <row r="363" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A363" s="116"/>
+      <c r="A363" s="115"/>
       <c r="B363" s="61" t="s">
         <v>771</v>
       </c>
@@ -24019,7 +24019,7 @@
       </c>
     </row>
     <row r="368" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A368" s="126"/>
+      <c r="A368" s="116"/>
       <c r="B368" s="61" t="s">
         <v>778</v>
       </c>
@@ -24077,7 +24077,7 @@
       </c>
     </row>
     <row r="369" spans="1:19" ht="61.2" hidden="1">
-      <c r="A369" s="126"/>
+      <c r="A369" s="116"/>
       <c r="B369" s="61" t="s">
         <v>778</v>
       </c>
@@ -24128,7 +24128,7 @@
       </c>
     </row>
     <row r="370" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A370" s="126"/>
+      <c r="A370" s="116"/>
       <c r="B370" s="61" t="s">
         <v>778</v>
       </c>
@@ -24182,7 +24182,7 @@
       </c>
     </row>
     <row r="371" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A371" s="122"/>
+      <c r="A371" s="117"/>
       <c r="B371" s="61" t="s">
         <v>778</v>
       </c>
@@ -24235,7 +24235,7 @@
       <c r="S371" s="61"/>
     </row>
     <row r="372" spans="1:19" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A372" s="116">
+      <c r="A372" s="115">
         <v>98</v>
       </c>
       <c r="B372" s="61" t="s">
@@ -24288,7 +24288,7 @@
       </c>
     </row>
     <row r="373" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A373" s="116"/>
+      <c r="A373" s="115"/>
       <c r="B373" s="61" t="s">
         <v>784</v>
       </c>
@@ -24339,7 +24339,7 @@
       </c>
     </row>
     <row r="374" spans="1:19" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="116"/>
+      <c r="A374" s="115"/>
       <c r="B374" s="61" t="s">
         <v>784</v>
       </c>
@@ -24390,7 +24390,7 @@
       </c>
     </row>
     <row r="375" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="116"/>
+      <c r="A375" s="115"/>
       <c r="B375" s="61" t="s">
         <v>784</v>
       </c>
@@ -24441,7 +24441,7 @@
       </c>
     </row>
     <row r="376" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A376" s="116"/>
+      <c r="A376" s="115"/>
       <c r="B376" s="61" t="s">
         <v>784</v>
       </c>
@@ -24482,7 +24482,7 @@
       </c>
     </row>
     <row r="377" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A377" s="116"/>
+      <c r="A377" s="115"/>
       <c r="B377" s="61" t="s">
         <v>784</v>
       </c>
@@ -24532,7 +24532,7 @@
       </c>
     </row>
     <row r="378" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A378" s="116"/>
+      <c r="A378" s="115"/>
       <c r="B378" s="61" t="s">
         <v>784</v>
       </c>
@@ -24582,7 +24582,7 @@
       </c>
     </row>
     <row r="379" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A379" s="116"/>
+      <c r="A379" s="115"/>
       <c r="B379" s="61" t="s">
         <v>784</v>
       </c>
@@ -24626,7 +24626,7 @@
       </c>
     </row>
     <row r="380" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A380" s="116"/>
+      <c r="A380" s="115"/>
       <c r="B380" s="61" t="s">
         <v>784</v>
       </c>
@@ -24673,7 +24673,7 @@
       <c r="S380" s="61"/>
     </row>
     <row r="381" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A381" s="116"/>
+      <c r="A381" s="115"/>
       <c r="B381" s="61" t="s">
         <v>784</v>
       </c>
@@ -24725,7 +24725,7 @@
       <c r="S381" s="61"/>
     </row>
     <row r="382" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A382" s="116"/>
+      <c r="A382" s="115"/>
       <c r="B382" s="61" t="s">
         <v>784</v>
       </c>
@@ -24775,7 +24775,7 @@
       </c>
     </row>
     <row r="383" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A383" s="116"/>
+      <c r="A383" s="115"/>
       <c r="B383" s="61" t="s">
         <v>784</v>
       </c>
@@ -24827,7 +24827,7 @@
       <c r="S383" s="61"/>
     </row>
     <row r="384" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A384" s="122">
+      <c r="A384" s="117">
         <v>99</v>
       </c>
       <c r="B384" s="61" t="s">
@@ -24880,7 +24880,7 @@
       </c>
     </row>
     <row r="385" spans="1:19" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A385" s="116"/>
+      <c r="A385" s="115"/>
       <c r="B385" s="61" t="s">
         <v>812</v>
       </c>
@@ -24931,7 +24931,7 @@
       </c>
     </row>
     <row r="386" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A386" s="116"/>
+      <c r="A386" s="115"/>
       <c r="B386" s="61" t="s">
         <v>812</v>
       </c>
@@ -24985,7 +24985,7 @@
       <c r="S386" s="61"/>
     </row>
     <row r="387" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A387" s="116"/>
+      <c r="A387" s="115"/>
       <c r="B387" s="61" t="s">
         <v>812</v>
       </c>
@@ -25037,7 +25037,7 @@
       </c>
     </row>
     <row r="388" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A388" s="116"/>
+      <c r="A388" s="115"/>
       <c r="B388" s="61" t="s">
         <v>811</v>
       </c>
@@ -25089,7 +25089,7 @@
       </c>
     </row>
     <row r="389" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A389" s="116"/>
+      <c r="A389" s="115"/>
       <c r="B389" s="61" t="s">
         <v>811</v>
       </c>
@@ -25143,7 +25143,7 @@
       </c>
     </row>
     <row r="390" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A390" s="116"/>
+      <c r="A390" s="115"/>
       <c r="B390" s="61" t="s">
         <v>811</v>
       </c>
@@ -25182,7 +25182,7 @@
       </c>
     </row>
     <row r="391" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A391" s="116"/>
+      <c r="A391" s="115"/>
       <c r="B391" s="62" t="s">
         <v>811</v>
       </c>
@@ -25285,7 +25285,7 @@
       </c>
     </row>
     <row r="393" spans="1:19" ht="58.2" hidden="1" customHeight="1">
-      <c r="A393" s="116">
+      <c r="A393" s="115">
         <v>100</v>
       </c>
       <c r="B393" s="62" t="s">
@@ -25338,7 +25338,7 @@
       </c>
     </row>
     <row r="394" spans="1:19" ht="61.2" hidden="1">
-      <c r="A394" s="116"/>
+      <c r="A394" s="115"/>
       <c r="B394" s="62" t="s">
         <v>820</v>
       </c>
@@ -25389,7 +25389,7 @@
       </c>
     </row>
     <row r="395" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A395" s="116"/>
+      <c r="A395" s="115"/>
       <c r="B395" s="61" t="s">
         <v>820</v>
       </c>
@@ -25443,7 +25443,7 @@
       </c>
     </row>
     <row r="396" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="116"/>
+      <c r="A396" s="115"/>
       <c r="B396" s="61" t="s">
         <v>820</v>
       </c>
@@ -25491,7 +25491,7 @@
       </c>
     </row>
     <row r="397" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A397" s="116"/>
+      <c r="A397" s="115"/>
       <c r="B397" s="61" t="s">
         <v>820</v>
       </c>
@@ -25543,7 +25543,7 @@
       <c r="S397" s="61"/>
     </row>
     <row r="398" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A398" s="116"/>
+      <c r="A398" s="115"/>
       <c r="B398" s="61" t="s">
         <v>820</v>
       </c>
@@ -25595,7 +25595,7 @@
       <c r="S398" s="61"/>
     </row>
     <row r="399" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A399" s="130">
+      <c r="A399" s="125">
         <v>101</v>
       </c>
       <c r="B399" s="61" t="s">
@@ -25649,8 +25649,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="400" spans="1:19" ht="31.95" hidden="1" customHeight="1">
-      <c r="A400" s="130"/>
+    <row r="400" spans="1:19" ht="31.95" customHeight="1">
+      <c r="A400" s="125"/>
       <c r="B400" s="61" t="s">
         <v>829</v>
       </c>
@@ -25689,7 +25689,7 @@
       <c r="S400" s="62"/>
     </row>
     <row r="401" spans="1:19" ht="31.95" hidden="1" customHeight="1">
-      <c r="A401" s="130"/>
+      <c r="A401" s="125"/>
       <c r="B401" s="61" t="s">
         <v>829</v>
       </c>
@@ -25741,7 +25741,7 @@
       </c>
     </row>
     <row r="402" spans="1:19" ht="31.95" hidden="1" customHeight="1">
-      <c r="A402" s="130"/>
+      <c r="A402" s="125"/>
       <c r="B402" s="61" t="s">
         <v>829</v>
       </c>
@@ -25795,7 +25795,7 @@
       </c>
     </row>
     <row r="403" spans="1:19" ht="31.95" hidden="1" customHeight="1">
-      <c r="A403" s="130"/>
+      <c r="A403" s="125"/>
       <c r="B403" s="83" t="s">
         <v>829</v>
       </c>
@@ -25843,7 +25843,7 @@
       <c r="S403" s="83"/>
     </row>
     <row r="404" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A404" s="130"/>
+      <c r="A404" s="125"/>
       <c r="B404" s="61" t="s">
         <v>829</v>
       </c>
@@ -25897,7 +25897,7 @@
       </c>
     </row>
     <row r="405" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A405" s="116">
+      <c r="A405" s="115">
         <v>102</v>
       </c>
       <c r="B405" s="62" t="s">
@@ -25950,7 +25950,7 @@
       </c>
     </row>
     <row r="406" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A406" s="116"/>
+      <c r="A406" s="115"/>
       <c r="B406" s="61" t="s">
         <v>836</v>
       </c>
@@ -26004,7 +26004,7 @@
       </c>
     </row>
     <row r="407" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A407" s="116">
+      <c r="A407" s="115">
         <v>103</v>
       </c>
       <c r="B407" s="61" t="s">
@@ -26058,7 +26058,7 @@
       </c>
     </row>
     <row r="408" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="116"/>
+      <c r="A408" s="115"/>
       <c r="B408" s="61" t="s">
         <v>840</v>
       </c>
@@ -26112,7 +26112,7 @@
       </c>
     </row>
     <row r="409" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="116"/>
+      <c r="A409" s="115"/>
       <c r="B409" s="61" t="s">
         <v>840</v>
       </c>
@@ -26165,7 +26165,7 @@
       </c>
     </row>
     <row r="410" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A410" s="116"/>
+      <c r="A410" s="115"/>
       <c r="B410" s="61" t="s">
         <v>840</v>
       </c>
@@ -26219,7 +26219,7 @@
       </c>
     </row>
     <row r="411" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A411" s="116">
+      <c r="A411" s="115">
         <v>104</v>
       </c>
       <c r="B411" s="61" t="s">
@@ -26272,7 +26272,7 @@
       </c>
     </row>
     <row r="412" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="116"/>
+      <c r="A412" s="115"/>
       <c r="B412" s="61" t="s">
         <v>845</v>
       </c>
@@ -26330,7 +26330,7 @@
       </c>
     </row>
     <row r="413" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="116"/>
+      <c r="A413" s="115"/>
       <c r="B413" s="61"/>
       <c r="C413" s="62"/>
       <c r="D413" s="62"/>
@@ -26351,7 +26351,7 @@
       <c r="S413" s="61"/>
     </row>
     <row r="414" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A414" s="116"/>
+      <c r="A414" s="115"/>
       <c r="B414" s="61" t="s">
         <v>845</v>
       </c>
@@ -26400,7 +26400,7 @@
       </c>
     </row>
     <row r="415" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A415" s="116"/>
+      <c r="A415" s="115"/>
       <c r="B415" s="61" t="s">
         <v>845</v>
       </c>
@@ -26453,7 +26453,7 @@
       </c>
     </row>
     <row r="416" spans="1:19" ht="61.2" hidden="1">
-      <c r="A416" s="116">
+      <c r="A416" s="115">
         <v>105</v>
       </c>
       <c r="B416" s="61" t="s">
@@ -26506,7 +26506,7 @@
       </c>
     </row>
     <row r="417" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A417" s="116"/>
+      <c r="A417" s="115"/>
       <c r="B417" s="61" t="s">
         <v>852</v>
       </c>
@@ -26551,7 +26551,7 @@
       </c>
     </row>
     <row r="418" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A418" s="116"/>
+      <c r="A418" s="115"/>
       <c r="B418" s="61" t="s">
         <v>852</v>
       </c>
@@ -26605,7 +26605,7 @@
       </c>
     </row>
     <row r="419" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A419" s="116"/>
+      <c r="A419" s="115"/>
       <c r="B419" s="61" t="s">
         <v>852</v>
       </c>
@@ -26659,7 +26659,7 @@
       </c>
     </row>
     <row r="420" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A420" s="116"/>
+      <c r="A420" s="115"/>
       <c r="B420" s="61" t="s">
         <v>852</v>
       </c>
@@ -26713,7 +26713,7 @@
       </c>
     </row>
     <row r="421" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A421" s="116"/>
+      <c r="A421" s="115"/>
       <c r="B421" s="61" t="s">
         <v>852</v>
       </c>
@@ -26754,7 +26754,7 @@
       </c>
     </row>
     <row r="422" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A422" s="116"/>
+      <c r="A422" s="115"/>
       <c r="B422" s="61" t="s">
         <v>852</v>
       </c>
@@ -26802,7 +26802,7 @@
       </c>
     </row>
     <row r="423" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A423" s="116"/>
+      <c r="A423" s="115"/>
       <c r="B423" s="61" t="s">
         <v>852</v>
       </c>
@@ -26950,7 +26950,7 @@
       </c>
     </row>
     <row r="426" spans="1:19" ht="61.2" hidden="1">
-      <c r="A426" s="116">
+      <c r="A426" s="115">
         <v>107</v>
       </c>
       <c r="B426" s="61" t="s">
@@ -27005,7 +27005,7 @@
       </c>
     </row>
     <row r="427" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A427" s="116"/>
+      <c r="A427" s="115"/>
       <c r="B427" s="61" t="s">
         <v>870</v>
       </c>
@@ -27056,8 +27056,8 @@
       </c>
       <c r="S427" s="61"/>
     </row>
-    <row r="428" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A428" s="116"/>
+    <row r="428" spans="1:19" ht="40.950000000000003" customHeight="1">
+      <c r="A428" s="115"/>
       <c r="B428" s="61" t="s">
         <v>870</v>
       </c>
@@ -27107,7 +27107,7 @@
       </c>
     </row>
     <row r="429" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="116"/>
+      <c r="A429" s="115"/>
       <c r="B429" s="61" t="s">
         <v>868</v>
       </c>
@@ -27155,7 +27155,7 @@
       </c>
     </row>
     <row r="430" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="116"/>
+      <c r="A430" s="115"/>
       <c r="B430" s="61" t="s">
         <v>868</v>
       </c>
@@ -27203,7 +27203,7 @@
       </c>
     </row>
     <row r="431" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A431" s="116"/>
+      <c r="A431" s="115"/>
       <c r="B431" s="61" t="s">
         <v>870</v>
       </c>
@@ -27255,7 +27255,7 @@
       <c r="S431" s="61"/>
     </row>
     <row r="432" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A432" s="116"/>
+      <c r="A432" s="115"/>
       <c r="B432" s="61" t="s">
         <v>868</v>
       </c>
@@ -27307,7 +27307,7 @@
       <c r="S432" s="62"/>
     </row>
     <row r="433" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A433" s="126"/>
+      <c r="A433" s="116"/>
       <c r="B433" s="61" t="s">
         <v>880</v>
       </c>
@@ -27329,35 +27329,35 @@
       </c>
       <c r="I433" s="61"/>
       <c r="J433" s="61"/>
-      <c r="K433" s="120">
+      <c r="K433" s="118">
         <v>12746524997</v>
       </c>
-      <c r="L433" s="120">
+      <c r="L433" s="118">
         <v>1000000000</v>
       </c>
-      <c r="M433" s="120">
+      <c r="M433" s="118">
         <f>+K433+L433</f>
         <v>13746524997</v>
       </c>
-      <c r="N433" s="117" t="s">
+      <c r="N433" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="O433" s="117" t="s">
+      <c r="O433" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="P433" s="116">
+      <c r="P433" s="115">
         <v>2025</v>
       </c>
       <c r="Q433" s="62"/>
-      <c r="R433" s="133">
+      <c r="R433" s="119">
         <v>0.65</v>
       </c>
-      <c r="S433" s="116" t="s">
+      <c r="S433" s="115" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="434" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A434" s="126"/>
+      <c r="A434" s="116"/>
       <c r="B434" s="61" t="s">
         <v>880</v>
       </c>
@@ -27379,18 +27379,18 @@
       </c>
       <c r="I434" s="61"/>
       <c r="J434" s="61"/>
-      <c r="K434" s="120"/>
-      <c r="L434" s="120"/>
-      <c r="M434" s="120"/>
-      <c r="N434" s="117"/>
-      <c r="O434" s="117"/>
-      <c r="P434" s="116"/>
+      <c r="K434" s="118"/>
+      <c r="L434" s="118"/>
+      <c r="M434" s="118"/>
+      <c r="N434" s="120"/>
+      <c r="O434" s="120"/>
+      <c r="P434" s="115"/>
       <c r="Q434" s="62"/>
-      <c r="R434" s="133"/>
-      <c r="S434" s="116"/>
+      <c r="R434" s="119"/>
+      <c r="S434" s="115"/>
     </row>
     <row r="435" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A435" s="126"/>
+      <c r="A435" s="116"/>
       <c r="B435" s="61" t="s">
         <v>880</v>
       </c>
@@ -27442,7 +27442,7 @@
       </c>
     </row>
     <row r="436" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A436" s="126"/>
+      <c r="A436" s="116"/>
       <c r="B436" s="61" t="s">
         <v>884</v>
       </c>
@@ -27494,7 +27494,7 @@
       </c>
     </row>
     <row r="437" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A437" s="126"/>
+      <c r="A437" s="116"/>
       <c r="B437" s="61" t="s">
         <v>880</v>
       </c>
@@ -27544,7 +27544,7 @@
       </c>
     </row>
     <row r="438" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A438" s="122"/>
+      <c r="A438" s="117"/>
       <c r="B438" s="61" t="s">
         <v>880</v>
       </c>
@@ -27647,7 +27647,7 @@
       </c>
     </row>
     <row r="440" spans="1:19" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="126"/>
+      <c r="A440" s="116"/>
       <c r="B440" s="61" t="s">
         <v>892</v>
       </c>
@@ -27696,7 +27696,7 @@
       </c>
     </row>
     <row r="441" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A441" s="126"/>
+      <c r="A441" s="116"/>
       <c r="B441" s="61" t="s">
         <v>892</v>
       </c>
@@ -27749,7 +27749,7 @@
       </c>
     </row>
     <row r="442" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="126"/>
+      <c r="A442" s="116"/>
       <c r="B442" s="61" t="s">
         <v>892</v>
       </c>
@@ -27801,7 +27801,7 @@
       </c>
     </row>
     <row r="443" spans="1:19" ht="64.95" hidden="1" customHeight="1">
-      <c r="A443" s="126"/>
+      <c r="A443" s="116"/>
       <c r="B443" s="61" t="s">
         <v>892</v>
       </c>
@@ -27848,8 +27848,8 @@
         <v>898</v>
       </c>
     </row>
-    <row r="444" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A444" s="126"/>
+    <row r="444" spans="1:19" ht="36.6" customHeight="1">
+      <c r="A444" s="116"/>
       <c r="B444" s="61" t="s">
         <v>892</v>
       </c>
@@ -27897,7 +27897,7 @@
       </c>
     </row>
     <row r="445" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="126"/>
+      <c r="A445" s="116"/>
       <c r="B445" s="112" t="s">
         <v>892</v>
       </c>
@@ -27932,7 +27932,7 @@
       <c r="S445" s="112"/>
     </row>
     <row r="446" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A446" s="122"/>
+      <c r="A446" s="117"/>
       <c r="B446" s="61" t="s">
         <v>892</v>
       </c>
@@ -27984,7 +27984,7 @@
       <c r="S446" s="76"/>
     </row>
     <row r="447" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A447" s="116"/>
+      <c r="A447" s="115"/>
       <c r="B447" s="61" t="s">
         <v>901</v>
       </c>
@@ -28038,7 +28038,7 @@
       </c>
     </row>
     <row r="448" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A448" s="116"/>
+      <c r="A448" s="115"/>
       <c r="B448" s="93" t="s">
         <v>901</v>
       </c>
@@ -28148,7 +28148,7 @@
       </c>
     </row>
     <row r="450" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A450" s="126"/>
+      <c r="A450" s="116"/>
       <c r="B450" s="61" t="s">
         <v>908</v>
       </c>
@@ -28200,7 +28200,7 @@
       </c>
     </row>
     <row r="451" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="126"/>
+      <c r="A451" s="116"/>
       <c r="B451" s="61" t="s">
         <v>908</v>
       </c>
@@ -28256,7 +28256,7 @@
       </c>
     </row>
     <row r="452" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="122"/>
+      <c r="A452" s="117"/>
       <c r="B452" s="61" t="s">
         <v>908</v>
       </c>
@@ -28308,7 +28308,7 @@
       </c>
     </row>
     <row r="453" spans="1:19" ht="42.6" hidden="1" customHeight="1">
-      <c r="A453" s="116">
+      <c r="A453" s="115">
         <v>112</v>
       </c>
       <c r="B453" s="61" t="s">
@@ -28367,7 +28367,7 @@
       </c>
     </row>
     <row r="454" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A454" s="116"/>
+      <c r="A454" s="115"/>
       <c r="B454" s="61" t="s">
         <v>915</v>
       </c>
@@ -28420,7 +28420,7 @@
       <c r="S454" s="61"/>
     </row>
     <row r="455" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A455" s="116"/>
+      <c r="A455" s="115"/>
       <c r="B455" s="61" t="s">
         <v>915</v>
       </c>
@@ -28474,8 +28474,8 @@
       </c>
       <c r="S455" s="61"/>
     </row>
-    <row r="456" spans="1:19" ht="40.799999999999997">
-      <c r="A456" s="116">
+    <row r="456" spans="1:19" ht="40.799999999999997" hidden="1">
+      <c r="A456" s="115">
         <v>113</v>
       </c>
       <c r="B456" s="61" t="s">
@@ -28523,8 +28523,8 @@
         <v>562</v>
       </c>
     </row>
-    <row r="457" spans="1:19" ht="20.399999999999999">
-      <c r="A457" s="116"/>
+    <row r="457" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A457" s="115"/>
       <c r="B457" s="61" t="s">
         <v>919</v>
       </c>
@@ -28574,8 +28574,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="458" spans="1:19" ht="37.950000000000003" customHeight="1">
-      <c r="A458" s="116"/>
+    <row r="458" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A458" s="115"/>
       <c r="B458" s="61" t="s">
         <v>919</v>
       </c>
@@ -28626,8 +28626,8 @@
       </c>
       <c r="S458" s="62"/>
     </row>
-    <row r="459" spans="1:19" ht="37.950000000000003" customHeight="1">
-      <c r="A459" s="116"/>
+    <row r="459" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A459" s="115"/>
       <c r="B459" s="112" t="s">
         <v>919</v>
       </c>
@@ -28672,8 +28672,8 @@
       <c r="R459" s="113"/>
       <c r="S459" s="110"/>
     </row>
-    <row r="460" spans="1:19" ht="15" customHeight="1">
-      <c r="A460" s="116"/>
+    <row r="460" spans="1:19" ht="15" hidden="1" customHeight="1">
+      <c r="A460" s="115"/>
       <c r="B460" s="61" t="s">
         <v>919</v>
       </c>
@@ -29044,7 +29044,7 @@
       </c>
     </row>
     <row r="467" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A467" s="126"/>
+      <c r="A467" s="116"/>
       <c r="B467" s="61" t="s">
         <v>936</v>
       </c>
@@ -29093,7 +29093,7 @@
       </c>
     </row>
     <row r="468" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="126"/>
+      <c r="A468" s="116"/>
       <c r="B468" s="61" t="s">
         <v>309</v>
       </c>
@@ -29145,7 +29145,7 @@
       <c r="S468" s="61"/>
     </row>
     <row r="469" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="126"/>
+      <c r="A469" s="116"/>
       <c r="B469" s="61" t="s">
         <v>309</v>
       </c>
@@ -29197,7 +29197,7 @@
       <c r="S469" s="61"/>
     </row>
     <row r="470" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="126"/>
+      <c r="A470" s="116"/>
       <c r="B470" s="61" t="s">
         <v>309</v>
       </c>
@@ -29249,7 +29249,7 @@
       <c r="S470" s="61"/>
     </row>
     <row r="471" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="126"/>
+      <c r="A471" s="116"/>
       <c r="B471" s="61" t="s">
         <v>309</v>
       </c>
@@ -29303,7 +29303,7 @@
       </c>
     </row>
     <row r="472" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="126"/>
+      <c r="A472" s="116"/>
       <c r="B472" s="61" t="s">
         <v>309</v>
       </c>
@@ -29353,7 +29353,7 @@
       </c>
     </row>
     <row r="473" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A473" s="122"/>
+      <c r="A473" s="117"/>
       <c r="B473" s="61" t="s">
         <v>936</v>
       </c>
@@ -29401,7 +29401,7 @@
       </c>
     </row>
     <row r="474" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="116">
+      <c r="A474" s="115">
         <v>116</v>
       </c>
       <c r="B474" s="61" t="s">
@@ -29413,7 +29413,7 @@
       <c r="D474" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="E474" s="119">
+      <c r="E474" s="133">
         <v>2025003050036</v>
       </c>
       <c r="F474" s="61" t="s">
@@ -29427,14 +29427,14 @@
       </c>
       <c r="I474" s="61"/>
       <c r="J474" s="61"/>
-      <c r="K474" s="115">
+      <c r="K474" s="131">
         <f>+M474</f>
         <v>14202451801</v>
       </c>
-      <c r="L474" s="115">
+      <c r="L474" s="131">
         <v>0</v>
       </c>
-      <c r="M474" s="120">
+      <c r="M474" s="118">
         <v>14202451801</v>
       </c>
       <c r="N474" s="61" t="s">
@@ -29450,12 +29450,12 @@
         <v>540</v>
       </c>
       <c r="R474" s="61"/>
-      <c r="S474" s="117" t="s">
+      <c r="S474" s="120" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="475" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="116"/>
+      <c r="A475" s="115"/>
       <c r="B475" s="61" t="s">
         <v>947</v>
       </c>
@@ -29465,7 +29465,7 @@
       <c r="D475" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="E475" s="119"/>
+      <c r="E475" s="133"/>
       <c r="F475" s="61" t="s">
         <v>162</v>
       </c>
@@ -29477,9 +29477,9 @@
       </c>
       <c r="I475" s="61"/>
       <c r="J475" s="61"/>
-      <c r="K475" s="115"/>
-      <c r="L475" s="115"/>
-      <c r="M475" s="120"/>
+      <c r="K475" s="131"/>
+      <c r="L475" s="131"/>
+      <c r="M475" s="118"/>
       <c r="N475" s="61" t="s">
         <v>35</v>
       </c>
@@ -29493,10 +29493,10 @@
         <v>540</v>
       </c>
       <c r="R475" s="61"/>
-      <c r="S475" s="117"/>
+      <c r="S475" s="120"/>
     </row>
     <row r="476" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="116"/>
+      <c r="A476" s="115"/>
       <c r="B476" s="61" t="s">
         <v>947</v>
       </c>
@@ -29552,7 +29552,7 @@
       </c>
     </row>
     <row r="477" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A477" s="116"/>
+      <c r="A477" s="115"/>
       <c r="B477" s="61" t="s">
         <v>947</v>
       </c>
@@ -29707,7 +29707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="480" spans="1:19" ht="36" hidden="1" customHeight="1">
+    <row r="480" spans="1:19" ht="36" customHeight="1">
       <c r="A480" s="62"/>
       <c r="B480" s="61" t="s">
         <v>954</v>
@@ -29967,7 +29967,7 @@
       <c r="S484" s="62"/>
     </row>
     <row r="485" spans="1:19" ht="35.25" hidden="1" customHeight="1">
-      <c r="A485" s="116">
+      <c r="A485" s="115">
         <v>121</v>
       </c>
       <c r="B485" s="61" t="s">
@@ -30021,7 +30021,7 @@
       <c r="S485" s="61"/>
     </row>
     <row r="486" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A486" s="116"/>
+      <c r="A486" s="115"/>
       <c r="B486" s="61" t="s">
         <v>963</v>
       </c>
@@ -30071,7 +30071,7 @@
       </c>
     </row>
     <row r="487" spans="1:19" ht="163.19999999999999" hidden="1">
-      <c r="A487" s="116"/>
+      <c r="A487" s="115"/>
       <c r="B487" s="61" t="s">
         <v>963</v>
       </c>
@@ -30227,7 +30227,7 @@
       <c r="S489" s="61"/>
     </row>
     <row r="490" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A490" s="126"/>
+      <c r="A490" s="116"/>
       <c r="B490" s="61" t="s">
         <v>973</v>
       </c>
@@ -30279,7 +30279,7 @@
       <c r="S490" s="61"/>
     </row>
     <row r="491" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A491" s="126"/>
+      <c r="A491" s="116"/>
       <c r="B491" s="61" t="s">
         <v>973</v>
       </c>
@@ -30331,7 +30331,7 @@
       <c r="S491" s="61"/>
     </row>
     <row r="492" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A492" s="126"/>
+      <c r="A492" s="116"/>
       <c r="B492" s="61" t="s">
         <v>973</v>
       </c>
@@ -30378,7 +30378,7 @@
       </c>
     </row>
     <row r="493" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A493" s="122"/>
+      <c r="A493" s="117"/>
       <c r="B493" s="61" t="s">
         <v>973</v>
       </c>
@@ -30430,7 +30430,7 @@
       <c r="S493" s="61"/>
     </row>
     <row r="494" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="116">
+      <c r="A494" s="115">
         <v>124</v>
       </c>
       <c r="B494" s="61" t="s">
@@ -30486,7 +30486,7 @@
       </c>
     </row>
     <row r="495" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A495" s="116"/>
+      <c r="A495" s="115"/>
       <c r="B495" s="61" t="s">
         <v>980</v>
       </c>
@@ -30535,8 +30535,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="496" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A496" s="116"/>
+    <row r="496" spans="1:19" ht="20.399999999999999">
+      <c r="A496" s="115"/>
       <c r="B496" s="61" t="s">
         <v>980</v>
       </c>
@@ -30588,7 +30588,7 @@
       </c>
     </row>
     <row r="497" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A497" s="116"/>
+      <c r="A497" s="115"/>
       <c r="B497" s="61" t="s">
         <v>986</v>
       </c>
@@ -30699,7 +30699,7 @@
       </c>
     </row>
     <row r="499" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A499" s="117">
+      <c r="A499" s="120">
         <v>126</v>
       </c>
       <c r="B499" s="61" t="s">
@@ -30758,7 +30758,7 @@
       </c>
     </row>
     <row r="500" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A500" s="117"/>
+      <c r="A500" s="120"/>
       <c r="B500" s="61" t="s">
         <v>987</v>
       </c>
@@ -30807,7 +30807,7 @@
       <c r="S500" s="61"/>
     </row>
     <row r="501" spans="1:19" ht="78" hidden="1" customHeight="1">
-      <c r="A501" s="117"/>
+      <c r="A501" s="120"/>
       <c r="B501" s="61" t="s">
         <v>987</v>
       </c>
@@ -30861,7 +30861,7 @@
       </c>
     </row>
     <row r="502" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A502" s="116">
+      <c r="A502" s="115">
         <v>127</v>
       </c>
       <c r="B502" s="61" t="s">
@@ -30921,7 +30921,7 @@
       </c>
     </row>
     <row r="503" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A503" s="116"/>
+      <c r="A503" s="115"/>
       <c r="B503" s="61" t="s">
         <v>995</v>
       </c>
@@ -30977,7 +30977,7 @@
       <c r="S503" s="61"/>
     </row>
     <row r="504" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A504" s="116"/>
+      <c r="A504" s="115"/>
       <c r="B504" s="93" t="s">
         <v>995</v>
       </c>
@@ -31100,25 +31100,115 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:S506" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Toledo"/>
+        <filter val="Equipamiento"/>
+        <filter val="Espacio Público"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A407:A410"/>
-    <mergeCell ref="A411:A415"/>
-    <mergeCell ref="A416:A423"/>
-    <mergeCell ref="A426:A432"/>
-    <mergeCell ref="A433:A438"/>
-    <mergeCell ref="K433:K434"/>
-    <mergeCell ref="R433:R434"/>
-    <mergeCell ref="L433:L434"/>
-    <mergeCell ref="M433:M434"/>
-    <mergeCell ref="N433:N434"/>
-    <mergeCell ref="O433:O434"/>
-    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="R91:R92"/>
+    <mergeCell ref="E474:E475"/>
+    <mergeCell ref="S91:S92"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="M474:M475"/>
+    <mergeCell ref="K474:K475"/>
+    <mergeCell ref="L474:L475"/>
+    <mergeCell ref="S474:S475"/>
+    <mergeCell ref="S433:S434"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="H311:H312"/>
+    <mergeCell ref="J309:J310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="I311:I312"/>
+    <mergeCell ref="J311:J312"/>
+    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A116"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A190:A192"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A152:A163"/>
+    <mergeCell ref="A213:A217"/>
+    <mergeCell ref="A222:A227"/>
+    <mergeCell ref="A234:A239"/>
+    <mergeCell ref="A240:A246"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A254:A259"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A294:A296"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A304:A307"/>
+    <mergeCell ref="F309:F310"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A275"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A284:A292"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A399:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="P309:P310"/>
+    <mergeCell ref="S309:S310"/>
+    <mergeCell ref="R309:R310"/>
+    <mergeCell ref="A310:A315"/>
+    <mergeCell ref="F311:F312"/>
+    <mergeCell ref="G311:G312"/>
+    <mergeCell ref="K311:K312"/>
+    <mergeCell ref="L311:L312"/>
+    <mergeCell ref="M311:M312"/>
+    <mergeCell ref="N311:N312"/>
+    <mergeCell ref="G309:G310"/>
+    <mergeCell ref="K309:K310"/>
+    <mergeCell ref="L309:L310"/>
+    <mergeCell ref="M309:M310"/>
+    <mergeCell ref="N309:N310"/>
+    <mergeCell ref="O309:O310"/>
+    <mergeCell ref="Q309:Q310"/>
+    <mergeCell ref="Q311:Q312"/>
+    <mergeCell ref="O311:O312"/>
+    <mergeCell ref="P311:P312"/>
+    <mergeCell ref="S311:S312"/>
+    <mergeCell ref="R311:R312"/>
     <mergeCell ref="A318:A319"/>
     <mergeCell ref="A320:A329"/>
     <mergeCell ref="A334:A337"/>
@@ -31143,107 +31233,18 @@
     <mergeCell ref="A372:A383"/>
     <mergeCell ref="A384:A391"/>
     <mergeCell ref="A393:A398"/>
-    <mergeCell ref="A399:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="P309:P310"/>
-    <mergeCell ref="S309:S310"/>
-    <mergeCell ref="R309:R310"/>
-    <mergeCell ref="A310:A315"/>
-    <mergeCell ref="F311:F312"/>
-    <mergeCell ref="G311:G312"/>
-    <mergeCell ref="K311:K312"/>
-    <mergeCell ref="L311:L312"/>
-    <mergeCell ref="M311:M312"/>
-    <mergeCell ref="N311:N312"/>
-    <mergeCell ref="G309:G310"/>
-    <mergeCell ref="K309:K310"/>
-    <mergeCell ref="L309:L310"/>
-    <mergeCell ref="M309:M310"/>
-    <mergeCell ref="N309:N310"/>
-    <mergeCell ref="O309:O310"/>
-    <mergeCell ref="Q309:Q310"/>
-    <mergeCell ref="Q311:Q312"/>
-    <mergeCell ref="O311:O312"/>
-    <mergeCell ref="P311:P312"/>
-    <mergeCell ref="S311:S312"/>
-    <mergeCell ref="R311:R312"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A304:A307"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A275"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A284:A292"/>
-    <mergeCell ref="E309:E310"/>
-    <mergeCell ref="A213:A217"/>
-    <mergeCell ref="A222:A227"/>
-    <mergeCell ref="A234:A239"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A254:A259"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A208:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A152:A163"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="R91:R92"/>
-    <mergeCell ref="E474:E475"/>
-    <mergeCell ref="S91:S92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="M474:M475"/>
-    <mergeCell ref="K474:K475"/>
-    <mergeCell ref="L474:L475"/>
-    <mergeCell ref="S474:S475"/>
-    <mergeCell ref="S433:S434"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="H311:H312"/>
-    <mergeCell ref="J309:J310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="I311:I312"/>
-    <mergeCell ref="J311:J312"/>
-    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="A407:A410"/>
+    <mergeCell ref="A411:A415"/>
+    <mergeCell ref="A416:A423"/>
+    <mergeCell ref="A426:A432"/>
+    <mergeCell ref="A433:A438"/>
+    <mergeCell ref="K433:K434"/>
+    <mergeCell ref="R433:R434"/>
+    <mergeCell ref="L433:L434"/>
+    <mergeCell ref="M433:M434"/>
+    <mergeCell ref="N433:N434"/>
+    <mergeCell ref="O433:O434"/>
+    <mergeCell ref="P433:P434"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -31640,20 +31641,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31675,6 +31676,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -31682,12 +31691,4 @@
     <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E33905E-5F5C-4A71-A9F6-7F6E75B5FD26}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB7622E6-5F7F-413D-A32D-84057E4DC1AD}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3660" yWindow="3660" windowWidth="14184" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos SIF'!$A$2:$S$506</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Proyectos SIF'!$A$2:$T$506</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4586,40 +4586,40 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4634,31 +4634,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5012,10 +5012,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="125"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="45"/>
       <c r="E1" s="46"/>
       <c r="F1" s="45"/>
@@ -5316,7 +5316,7 @@
       <c r="S6" s="62"/>
     </row>
     <row r="7" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A7" s="121">
+      <c r="A7" s="126">
         <v>2</v>
       </c>
       <c r="B7" s="61" t="s">
@@ -5349,7 +5349,7 @@
       <c r="S7" s="62"/>
     </row>
     <row r="8" spans="1:21" ht="40.799999999999997" hidden="1">
-      <c r="A8" s="126"/>
+      <c r="A8" s="121"/>
       <c r="B8" s="61" t="s">
         <v>38</v>
       </c>
@@ -5399,7 +5399,7 @@
       <c r="S8" s="62"/>
     </row>
     <row r="9" spans="1:21" ht="61.2" hidden="1">
-      <c r="A9" s="126"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="61" t="s">
         <v>38</v>
       </c>
@@ -5511,7 +5511,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.799999999999997" hidden="1">
-      <c r="A11" s="116">
+      <c r="A11" s="120">
         <v>3</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -5572,7 +5572,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="116"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="61" t="s">
         <v>55</v>
       </c>
@@ -5626,7 +5626,7 @@
       <c r="S12" s="60"/>
     </row>
     <row r="13" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A13" s="116"/>
+      <c r="A13" s="120"/>
       <c r="B13" s="61" t="s">
         <v>55</v>
       </c>
@@ -5680,7 +5680,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="20.399999999999999" hidden="1">
-      <c r="A14" s="116"/>
+      <c r="A14" s="120"/>
       <c r="B14" s="61" t="s">
         <v>55</v>
       </c>
@@ -5733,8 +5733,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20.399999999999999">
-      <c r="A15" s="116"/>
+    <row r="15" spans="1:21" ht="20.399999999999999" hidden="1">
+      <c r="A15" s="120"/>
       <c r="B15" s="83" t="s">
         <v>55</v>
       </c>
@@ -5788,7 +5788,7 @@
       <c r="S15" s="71"/>
     </row>
     <row r="16" spans="1:21" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="116"/>
+      <c r="A16" s="120"/>
       <c r="B16" s="61" t="s">
         <v>55</v>
       </c>
@@ -5880,7 +5880,7 @@
       <c r="R17" s="41"/>
       <c r="S17" s="61"/>
     </row>
-    <row r="18" spans="1:19" ht="61.2" customHeight="1">
+    <row r="18" spans="1:19" ht="61.2" hidden="1" customHeight="1">
       <c r="A18" s="62">
         <v>4</v>
       </c>
@@ -5997,7 +5997,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="116">
+      <c r="A20" s="120">
         <v>5</v>
       </c>
       <c r="B20" s="61" t="s">
@@ -6057,7 +6057,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="116"/>
+      <c r="A21" s="120"/>
       <c r="B21" s="61" t="s">
         <v>84</v>
       </c>
@@ -6113,7 +6113,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A22" s="116"/>
+      <c r="A22" s="120"/>
       <c r="B22" s="61" t="s">
         <v>84</v>
       </c>
@@ -6169,8 +6169,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="40.799999999999997">
-      <c r="A23" s="116"/>
+    <row r="23" spans="1:19" ht="40.799999999999997" hidden="1">
+      <c r="A23" s="120"/>
       <c r="B23" s="61" t="s">
         <v>84</v>
       </c>
@@ -6225,7 +6225,7 @@
       <c r="S23" s="61"/>
     </row>
     <row r="24" spans="1:19" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="116">
+      <c r="A24" s="120">
         <v>6</v>
       </c>
       <c r="B24" s="61" t="s">
@@ -6284,7 +6284,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A25" s="116"/>
+      <c r="A25" s="120"/>
       <c r="B25" s="61" t="s">
         <v>100</v>
       </c>
@@ -6338,7 +6338,7 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="116"/>
+      <c r="A26" s="120"/>
       <c r="B26" s="61" t="s">
         <v>100</v>
       </c>
@@ -6392,7 +6392,7 @@
       </c>
     </row>
     <row r="27" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="116"/>
+      <c r="A27" s="120"/>
       <c r="B27" s="61" t="s">
         <v>100</v>
       </c>
@@ -6448,7 +6448,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A28" s="116"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="61" t="s">
         <v>100</v>
       </c>
@@ -6500,7 +6500,7 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="116"/>
+      <c r="A29" s="120"/>
       <c r="B29" s="61" t="s">
         <v>100</v>
       </c>
@@ -6554,7 +6554,7 @@
       </c>
     </row>
     <row r="30" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="116"/>
+      <c r="A30" s="120"/>
       <c r="B30" s="61" t="s">
         <v>100</v>
       </c>
@@ -6604,7 +6604,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="116"/>
+      <c r="A31" s="120"/>
       <c r="B31" s="61" t="s">
         <v>100</v>
       </c>
@@ -6660,7 +6660,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="116"/>
+      <c r="A32" s="120"/>
       <c r="B32" s="61" t="s">
         <v>100</v>
       </c>
@@ -6718,7 +6718,7 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="116"/>
+      <c r="A33" s="120"/>
       <c r="B33" s="61" t="s">
         <v>100</v>
       </c>
@@ -6771,8 +6771,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="40.950000000000003" customHeight="1">
-      <c r="A34" s="116"/>
+    <row r="34" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A34" s="120"/>
       <c r="B34" s="61" t="s">
         <v>100</v>
       </c>
@@ -6830,7 +6830,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A35" s="126"/>
+      <c r="A35" s="121"/>
       <c r="B35" s="61" t="s">
         <v>136</v>
       </c>
@@ -6971,7 +6971,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="116">
+      <c r="A38" s="120">
         <v>8</v>
       </c>
       <c r="B38" s="61" t="s">
@@ -7029,8 +7029,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="40.950000000000003" customHeight="1">
-      <c r="A39" s="116"/>
+    <row r="39" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A39" s="120"/>
       <c r="B39" s="61" t="s">
         <v>139</v>
       </c>
@@ -7088,7 +7088,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="116"/>
+      <c r="A40" s="120"/>
       <c r="B40" s="61" t="s">
         <v>139</v>
       </c>
@@ -7142,8 +7142,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="61.2" customHeight="1">
-      <c r="A41" s="116">
+    <row r="41" spans="1:19" ht="61.2" hidden="1" customHeight="1">
+      <c r="A41" s="120">
         <v>9</v>
       </c>
       <c r="B41" s="61" t="s">
@@ -7201,7 +7201,7 @@
       <c r="S41" s="61"/>
     </row>
     <row r="42" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="116"/>
+      <c r="A42" s="120"/>
       <c r="B42" s="61" t="s">
         <v>147</v>
       </c>
@@ -7248,7 +7248,7 @@
       </c>
     </row>
     <row r="43" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="116"/>
+      <c r="A43" s="120"/>
       <c r="B43" s="61" t="s">
         <v>147</v>
       </c>
@@ -7297,7 +7297,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="116"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="61" t="s">
         <v>147</v>
       </c>
@@ -7343,7 +7343,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A45" s="116"/>
+      <c r="A45" s="120"/>
       <c r="B45" s="61" t="s">
         <v>147</v>
       </c>
@@ -7397,7 +7397,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="116">
+      <c r="A46" s="120">
         <v>10</v>
       </c>
       <c r="B46" s="61" t="s">
@@ -7451,7 +7451,7 @@
       </c>
     </row>
     <row r="47" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A47" s="121"/>
+      <c r="A47" s="126"/>
       <c r="B47" s="61" t="s">
         <v>158</v>
       </c>
@@ -7503,7 +7503,7 @@
       <c r="S47" s="61"/>
     </row>
     <row r="48" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A48" s="116"/>
+      <c r="A48" s="120"/>
       <c r="B48" s="61" t="s">
         <v>165</v>
       </c>
@@ -7536,7 +7536,7 @@
       <c r="S48" s="61"/>
     </row>
     <row r="49" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A49" s="116"/>
+      <c r="A49" s="120"/>
       <c r="B49" s="61" t="s">
         <v>165</v>
       </c>
@@ -7573,7 +7573,7 @@
       </c>
     </row>
     <row r="50" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A50" s="116"/>
+      <c r="A50" s="120"/>
       <c r="B50" s="61" t="s">
         <v>165</v>
       </c>
@@ -7623,7 +7623,7 @@
       </c>
     </row>
     <row r="51" spans="1:19" ht="102" hidden="1">
-      <c r="A51" s="116"/>
+      <c r="A51" s="120"/>
       <c r="B51" s="61" t="s">
         <v>165</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="52" spans="1:19" ht="61.2" hidden="1">
-      <c r="A52" s="116"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="61" t="s">
         <v>165</v>
       </c>
@@ -7721,7 +7721,7 @@
       </c>
     </row>
     <row r="53" spans="1:19" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="116"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="61" t="s">
         <v>165</v>
       </c>
@@ -7773,7 +7773,7 @@
       </c>
     </row>
     <row r="54" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="116"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="61" t="s">
         <v>181</v>
       </c>
@@ -7824,7 +7824,7 @@
       </c>
     </row>
     <row r="55" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="116"/>
+      <c r="A55" s="120"/>
       <c r="B55" s="61" t="s">
         <v>181</v>
       </c>
@@ -7876,7 +7876,7 @@
       <c r="S55" s="62"/>
     </row>
     <row r="56" spans="1:19" ht="61.2" hidden="1">
-      <c r="A56" s="116"/>
+      <c r="A56" s="120"/>
       <c r="B56" s="61" t="s">
         <v>181</v>
       </c>
@@ -7932,7 +7932,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="116"/>
+      <c r="A57" s="120"/>
       <c r="B57" s="61" t="s">
         <v>181</v>
       </c>
@@ -7986,7 +7986,7 @@
       <c r="S57" s="61"/>
     </row>
     <row r="58" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="116"/>
+      <c r="A58" s="120"/>
       <c r="B58" s="61" t="s">
         <v>181</v>
       </c>
@@ -8149,59 +8149,59 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="102" customHeight="1">
-      <c r="A61" s="116"/>
-      <c r="B61" s="135" t="s">
+    <row r="61" spans="1:19" ht="102" hidden="1" customHeight="1">
+      <c r="A61" s="120"/>
+      <c r="B61" s="115" t="s">
         <v>191</v>
       </c>
-      <c r="C61" s="136" t="s">
+      <c r="C61" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="136" t="s">
+      <c r="D61" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="E61" s="137" t="s">
+      <c r="E61" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="F61" s="135" t="s">
+      <c r="F61" s="115" t="s">
         <v>195</v>
       </c>
-      <c r="G61" s="136" t="s">
+      <c r="G61" s="116" t="s">
         <v>135</v>
       </c>
-      <c r="H61" s="136">
+      <c r="H61" s="116">
         <v>6</v>
       </c>
-      <c r="I61" s="136"/>
-      <c r="J61" s="136"/>
-      <c r="K61" s="138">
+      <c r="I61" s="116"/>
+      <c r="J61" s="116"/>
+      <c r="K61" s="118">
         <v>14386750676</v>
       </c>
-      <c r="L61" s="138">
+      <c r="L61" s="118">
         <v>0</v>
       </c>
-      <c r="M61" s="138">
+      <c r="M61" s="118">
         <v>14386750676</v>
       </c>
-      <c r="N61" s="139" t="s">
+      <c r="N61" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="O61" s="135" t="s">
+      <c r="O61" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="P61" s="136">
+      <c r="P61" s="116">
         <v>2025</v>
       </c>
-      <c r="Q61" s="136" t="s">
+      <c r="Q61" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="R61" s="136"/>
-      <c r="S61" s="135" t="s">
+      <c r="R61" s="116"/>
+      <c r="S61" s="115" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="121">
+      <c r="A62" s="126">
         <v>14</v>
       </c>
       <c r="B62" s="61" t="s">
@@ -8256,7 +8256,7 @@
       </c>
     </row>
     <row r="63" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A63" s="126"/>
+      <c r="A63" s="121"/>
       <c r="B63" s="61" t="s">
         <v>197</v>
       </c>
@@ -8464,7 +8464,7 @@
       </c>
     </row>
     <row r="67" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="121">
+      <c r="A67" s="126">
         <v>16</v>
       </c>
       <c r="B67" s="61" t="s">
@@ -8567,7 +8567,7 @@
       </c>
     </row>
     <row r="69" spans="1:19" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="121">
+      <c r="A69" s="126">
         <v>17</v>
       </c>
       <c r="B69" s="61" t="s">
@@ -8620,7 +8620,7 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A70" s="126"/>
+      <c r="A70" s="121"/>
       <c r="B70" s="61" t="s">
         <v>217</v>
       </c>
@@ -8672,7 +8672,7 @@
       </c>
     </row>
     <row r="71" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A71" s="126"/>
+      <c r="A71" s="121"/>
       <c r="B71" s="61" t="s">
         <v>223</v>
       </c>
@@ -8722,7 +8722,7 @@
       </c>
     </row>
     <row r="72" spans="1:19" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="126"/>
+      <c r="A72" s="121"/>
       <c r="B72" s="61" t="s">
         <v>226</v>
       </c>
@@ -8775,7 +8775,7 @@
       </c>
     </row>
     <row r="73" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="126"/>
+      <c r="A73" s="121"/>
       <c r="B73" s="61" t="s">
         <v>226</v>
       </c>
@@ -8823,7 +8823,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="126"/>
+      <c r="A74" s="121"/>
       <c r="B74" s="61" t="s">
         <v>226</v>
       </c>
@@ -8875,7 +8875,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="126"/>
+      <c r="A75" s="121"/>
       <c r="B75" s="61" t="s">
         <v>226</v>
       </c>
@@ -8932,8 +8932,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="40.950000000000003" customHeight="1">
-      <c r="A76" s="126"/>
+    <row r="76" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A76" s="121"/>
       <c r="B76" s="61" t="s">
         <v>226</v>
       </c>
@@ -9037,7 +9037,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="126"/>
+      <c r="A78" s="121"/>
       <c r="B78" s="61" t="s">
         <v>236</v>
       </c>
@@ -9095,7 +9095,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A79" s="126"/>
+      <c r="A79" s="121"/>
       <c r="B79" s="61" t="s">
         <v>236</v>
       </c>
@@ -9147,7 +9147,7 @@
       <c r="S79" s="62"/>
     </row>
     <row r="80" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A80" s="126"/>
+      <c r="A80" s="121"/>
       <c r="B80" s="61" t="s">
         <v>236</v>
       </c>
@@ -9199,7 +9199,7 @@
       <c r="S80" s="62"/>
     </row>
     <row r="81" spans="1:19" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="126"/>
+      <c r="A81" s="121"/>
       <c r="B81" s="61" t="s">
         <v>236</v>
       </c>
@@ -9252,7 +9252,7 @@
       </c>
     </row>
     <row r="82" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="126"/>
+      <c r="A82" s="121"/>
       <c r="B82" s="75" t="s">
         <v>245</v>
       </c>
@@ -9306,7 +9306,7 @@
       </c>
     </row>
     <row r="83" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A83" s="126"/>
+      <c r="A83" s="121"/>
       <c r="B83" s="75" t="s">
         <v>245</v>
       </c>
@@ -9355,7 +9355,7 @@
       </c>
     </row>
     <row r="84" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A84" s="126"/>
+      <c r="A84" s="121"/>
       <c r="B84" s="61" t="s">
         <v>245</v>
       </c>
@@ -9407,7 +9407,7 @@
       </c>
     </row>
     <row r="85" spans="1:19" s="80" customFormat="1" ht="55.2" hidden="1">
-      <c r="A85" s="126"/>
+      <c r="A85" s="121"/>
       <c r="B85" s="75" t="s">
         <v>245</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="86" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="126"/>
+      <c r="A86" s="121"/>
       <c r="B86" s="75" t="s">
         <v>245</v>
       </c>
@@ -9511,7 +9511,7 @@
       </c>
     </row>
     <row r="87" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="126"/>
+      <c r="A87" s="121"/>
       <c r="B87" s="75" t="s">
         <v>245</v>
       </c>
@@ -9564,8 +9564,8 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19" s="80" customFormat="1" ht="20.399999999999999">
-      <c r="A88" s="126"/>
+    <row r="88" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1">
+      <c r="A88" s="121"/>
       <c r="B88" s="75" t="s">
         <v>245</v>
       </c>
@@ -9618,8 +9618,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:19" s="80" customFormat="1" ht="20.399999999999999">
-      <c r="A89" s="126"/>
+    <row r="89" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1">
+      <c r="A89" s="121"/>
       <c r="B89" s="75" t="s">
         <v>245</v>
       </c>
@@ -9671,7 +9671,7 @@
       <c r="S89" s="75"/>
     </row>
     <row r="90" spans="1:19" s="80" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="126"/>
+      <c r="A90" s="121"/>
       <c r="B90" s="77" t="s">
         <v>245</v>
       </c>
@@ -9717,7 +9717,7 @@
       </c>
     </row>
     <row r="91" spans="1:19" s="80" customFormat="1" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="126"/>
+      <c r="A91" s="121"/>
       <c r="B91" s="61" t="s">
         <v>264</v>
       </c>
@@ -9741,37 +9741,37 @@
       </c>
       <c r="I91" s="61"/>
       <c r="J91" s="61"/>
-      <c r="K91" s="115">
+      <c r="K91" s="136">
         <v>4572000000</v>
       </c>
-      <c r="L91" s="115">
+      <c r="L91" s="136">
         <v>0</v>
       </c>
-      <c r="M91" s="115">
+      <c r="M91" s="136">
         <f>+K91</f>
         <v>4572000000</v>
       </c>
-      <c r="N91" s="116" t="s">
+      <c r="N91" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="116" t="s">
+      <c r="O91" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="P91" s="116">
+      <c r="P91" s="120">
         <v>2026</v>
       </c>
-      <c r="Q91" s="117" t="s">
+      <c r="Q91" s="125" t="s">
         <v>120</v>
       </c>
-      <c r="R91" s="118">
+      <c r="R91" s="137">
         <v>0</v>
       </c>
-      <c r="S91" s="117" t="s">
+      <c r="S91" s="125" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A92" s="126"/>
+      <c r="A92" s="121"/>
       <c r="B92" s="61" t="s">
         <v>264</v>
       </c>
@@ -9795,18 +9795,18 @@
       </c>
       <c r="I92" s="61"/>
       <c r="J92" s="61"/>
-      <c r="K92" s="115"/>
-      <c r="L92" s="115"/>
-      <c r="M92" s="115"/>
-      <c r="N92" s="116"/>
-      <c r="O92" s="116"/>
-      <c r="P92" s="116"/>
-      <c r="Q92" s="117"/>
-      <c r="R92" s="118"/>
-      <c r="S92" s="117"/>
+      <c r="K92" s="136"/>
+      <c r="L92" s="136"/>
+      <c r="M92" s="136"/>
+      <c r="N92" s="120"/>
+      <c r="O92" s="120"/>
+      <c r="P92" s="120"/>
+      <c r="Q92" s="125"/>
+      <c r="R92" s="137"/>
+      <c r="S92" s="125"/>
     </row>
     <row r="93" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="126"/>
+      <c r="A93" s="121"/>
       <c r="B93" s="61" t="s">
         <v>264</v>
       </c>
@@ -9860,7 +9860,7 @@
       </c>
     </row>
     <row r="94" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="126"/>
+      <c r="A94" s="121"/>
       <c r="B94" s="61" t="s">
         <v>264</v>
       </c>
@@ -9912,7 +9912,7 @@
       </c>
     </row>
     <row r="95" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A95" s="126"/>
+      <c r="A95" s="121"/>
       <c r="B95" s="61" t="s">
         <v>264</v>
       </c>
@@ -9964,8 +9964,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="61.2" hidden="1">
-      <c r="A96" s="126"/>
+    <row r="96" spans="1:19" ht="61.2">
+      <c r="A96" s="121"/>
       <c r="B96" s="61" t="s">
         <v>273</v>
       </c>
@@ -10021,8 +10021,8 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="99.6" hidden="1" customHeight="1">
-      <c r="A97" s="126"/>
+    <row r="97" spans="1:19" ht="99.6" customHeight="1">
+      <c r="A97" s="121"/>
       <c r="B97" s="61" t="s">
         <v>273</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A98" s="126"/>
+      <c r="A98" s="121"/>
       <c r="B98" s="61" t="s">
         <v>283</v>
       </c>
@@ -10134,7 +10134,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="126"/>
+      <c r="A99" s="121"/>
       <c r="B99" s="61" t="s">
         <v>283</v>
       </c>
@@ -10188,7 +10188,7 @@
       </c>
     </row>
     <row r="100" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A100" s="126"/>
+      <c r="A100" s="121"/>
       <c r="B100" s="61" t="s">
         <v>283</v>
       </c>
@@ -10242,7 +10242,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="126"/>
+      <c r="A101" s="121"/>
       <c r="B101" s="61" t="s">
         <v>283</v>
       </c>
@@ -10296,7 +10296,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="126"/>
+      <c r="A102" s="121"/>
       <c r="B102" s="61" t="s">
         <v>283</v>
       </c>
@@ -10345,7 +10345,7 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="126"/>
+      <c r="A103" s="121"/>
       <c r="B103" s="61" t="s">
         <v>283</v>
       </c>
@@ -10392,8 +10392,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="53.4" customHeight="1">
-      <c r="A104" s="126"/>
+    <row r="104" spans="1:19" ht="53.4" hidden="1" customHeight="1">
+      <c r="A104" s="121"/>
       <c r="B104" s="61" t="s">
         <v>283</v>
       </c>
@@ -10445,7 +10445,7 @@
       <c r="S104" s="62"/>
     </row>
     <row r="105" spans="1:19" ht="34.5" hidden="1" customHeight="1">
-      <c r="A105" s="126"/>
+      <c r="A105" s="121"/>
       <c r="B105" s="61" t="s">
         <v>283</v>
       </c>
@@ -10497,7 +10497,7 @@
       </c>
     </row>
     <row r="106" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A106" s="126"/>
+      <c r="A106" s="121"/>
       <c r="B106" s="61" t="s">
         <v>294</v>
       </c>
@@ -10546,7 +10546,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A107" s="126"/>
+      <c r="A107" s="121"/>
       <c r="B107" s="61" t="s">
         <v>301</v>
       </c>
@@ -10588,8 +10588,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="20.399999999999999">
-      <c r="A108" s="126"/>
+    <row r="108" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A108" s="121"/>
       <c r="B108" s="61" t="s">
         <v>301</v>
       </c>
@@ -10639,7 +10639,7 @@
       <c r="S108" s="62"/>
     </row>
     <row r="109" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A109" s="126"/>
+      <c r="A109" s="121"/>
       <c r="B109" s="61" t="s">
         <v>301</v>
       </c>
@@ -10691,7 +10691,7 @@
       <c r="S109" s="61"/>
     </row>
     <row r="110" spans="1:19" ht="60.6" customHeight="1">
-      <c r="A110" s="126"/>
+      <c r="A110" s="121"/>
       <c r="B110" s="61" t="s">
         <v>305</v>
       </c>
@@ -10747,7 +10747,7 @@
       <c r="S110" s="61"/>
     </row>
     <row r="111" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A111" s="126"/>
+      <c r="A111" s="121"/>
       <c r="B111" s="61" t="s">
         <v>307</v>
       </c>
@@ -10797,7 +10797,7 @@
       </c>
     </row>
     <row r="112" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A112" s="126"/>
+      <c r="A112" s="121"/>
       <c r="B112" s="61" t="s">
         <v>307</v>
       </c>
@@ -10847,7 +10847,7 @@
       </c>
     </row>
     <row r="113" spans="1:19" ht="61.2" hidden="1">
-      <c r="A113" s="126"/>
+      <c r="A113" s="121"/>
       <c r="B113" s="61" t="s">
         <v>307</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="22.95" hidden="1" customHeight="1">
-      <c r="A114" s="126"/>
+      <c r="A114" s="121"/>
       <c r="B114" s="61" t="s">
         <v>307</v>
       </c>
@@ -10940,7 +10940,7 @@
       </c>
     </row>
     <row r="115" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A115" s="126"/>
+      <c r="A115" s="121"/>
       <c r="B115" s="61" t="s">
         <v>317</v>
       </c>
@@ -11049,7 +11049,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="20.399999999999999">
+    <row r="117" spans="1:19" ht="20.399999999999999" hidden="1">
       <c r="A117" s="47">
         <v>29</v>
       </c>
@@ -11104,7 +11104,7 @@
       <c r="S117" s="61"/>
     </row>
     <row r="118" spans="1:19" ht="39.6" hidden="1" customHeight="1">
-      <c r="A118" s="116">
+      <c r="A118" s="120">
         <v>30</v>
       </c>
       <c r="B118" s="61" t="s">
@@ -11156,7 +11156,7 @@
       <c r="S118" s="61"/>
     </row>
     <row r="119" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A119" s="116"/>
+      <c r="A119" s="120"/>
       <c r="B119" s="61" t="s">
         <v>327</v>
       </c>
@@ -11208,7 +11208,7 @@
       <c r="S119" s="62"/>
     </row>
     <row r="120" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A120" s="131">
+      <c r="A120" s="134">
         <v>31</v>
       </c>
       <c r="B120" s="61" t="s">
@@ -11261,7 +11261,7 @@
       </c>
     </row>
     <row r="121" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="117"/>
+      <c r="A121" s="125"/>
       <c r="B121" s="61" t="s">
         <v>330</v>
       </c>
@@ -11312,7 +11312,7 @@
       </c>
     </row>
     <row r="122" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A122" s="117"/>
+      <c r="A122" s="125"/>
       <c r="B122" s="61" t="s">
         <v>330</v>
       </c>
@@ -11363,8 +11363,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="20.399999999999999">
-      <c r="A123" s="117"/>
+    <row r="123" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A123" s="125"/>
       <c r="B123" s="61" t="s">
         <v>330</v>
       </c>
@@ -11519,7 +11519,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="40.799999999999997">
+    <row r="126" spans="1:19" ht="40.799999999999997" hidden="1">
       <c r="A126" s="62"/>
       <c r="B126" s="61" t="s">
         <v>339</v>
@@ -11831,7 +11831,7 @@
       <c r="S131" s="62"/>
     </row>
     <row r="132" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A132" s="116">
+      <c r="A132" s="120">
         <v>35</v>
       </c>
       <c r="B132" s="61" t="s">
@@ -11887,7 +11887,7 @@
       </c>
     </row>
     <row r="133" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A133" s="116"/>
+      <c r="A133" s="120"/>
       <c r="B133" s="61" t="s">
         <v>351</v>
       </c>
@@ -11939,7 +11939,7 @@
       <c r="S133" s="62"/>
     </row>
     <row r="134" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A134" s="116"/>
+      <c r="A134" s="120"/>
       <c r="B134" s="61" t="s">
         <v>351</v>
       </c>
@@ -11996,8 +11996,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="20.399999999999999">
-      <c r="A135" s="116"/>
+    <row r="135" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A135" s="120"/>
       <c r="B135" s="61" t="s">
         <v>351</v>
       </c>
@@ -12106,7 +12106,7 @@
       <c r="S136" s="61"/>
     </row>
     <row r="137" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A137" s="116">
+      <c r="A137" s="120">
         <v>36</v>
       </c>
       <c r="B137" s="61" t="s">
@@ -12160,7 +12160,7 @@
       <c r="S137" s="61"/>
     </row>
     <row r="138" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A138" s="116"/>
+      <c r="A138" s="120"/>
       <c r="B138" s="61" t="s">
         <v>360</v>
       </c>
@@ -12212,7 +12212,7 @@
       <c r="S138" s="61"/>
     </row>
     <row r="139" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A139" s="116"/>
+      <c r="A139" s="120"/>
       <c r="B139" s="61" t="s">
         <v>360</v>
       </c>
@@ -12264,7 +12264,7 @@
       <c r="S139" s="61"/>
     </row>
     <row r="140" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A140" s="116"/>
+      <c r="A140" s="120"/>
       <c r="B140" s="61" t="s">
         <v>360</v>
       </c>
@@ -12315,7 +12315,7 @@
       <c r="S140" s="61"/>
     </row>
     <row r="141" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A141" s="116"/>
+      <c r="A141" s="120"/>
       <c r="B141" s="61" t="s">
         <v>360</v>
       </c>
@@ -12367,7 +12367,7 @@
       <c r="S141" s="61"/>
     </row>
     <row r="142" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A142" s="116"/>
+      <c r="A142" s="120"/>
       <c r="B142" s="61" t="s">
         <v>360</v>
       </c>
@@ -12418,8 +12418,8 @@
       </c>
       <c r="S142" s="62"/>
     </row>
-    <row r="143" spans="1:19" ht="20.399999999999999">
-      <c r="A143" s="116"/>
+    <row r="143" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A143" s="120"/>
       <c r="B143" s="61" t="s">
         <v>360</v>
       </c>
@@ -12471,7 +12471,7 @@
       <c r="S143" s="61"/>
     </row>
     <row r="144" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A144" s="116">
+      <c r="A144" s="120">
         <v>37</v>
       </c>
       <c r="B144" s="61" t="s">
@@ -12527,7 +12527,7 @@
       </c>
     </row>
     <row r="145" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A145" s="116"/>
+      <c r="A145" s="120"/>
       <c r="B145" s="61" t="s">
         <v>376</v>
       </c>
@@ -12577,7 +12577,7 @@
       </c>
     </row>
     <row r="146" spans="1:19" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A146" s="116"/>
+      <c r="A146" s="120"/>
       <c r="B146" s="61" t="s">
         <v>376</v>
       </c>
@@ -12681,7 +12681,7 @@
       </c>
     </row>
     <row r="148" spans="1:19" ht="35.4" hidden="1" customHeight="1">
-      <c r="A148" s="126"/>
+      <c r="A148" s="121"/>
       <c r="B148" s="61" t="s">
         <v>381</v>
       </c>
@@ -12893,7 +12893,7 @@
       </c>
     </row>
     <row r="152" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A152" s="121">
+      <c r="A152" s="126">
         <v>40</v>
       </c>
       <c r="B152" s="61" t="s">
@@ -12949,7 +12949,7 @@
       </c>
     </row>
     <row r="153" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A153" s="126"/>
+      <c r="A153" s="121"/>
       <c r="B153" s="61" t="s">
         <v>392</v>
       </c>
@@ -12998,7 +12998,7 @@
       </c>
     </row>
     <row r="154" spans="1:19" ht="183.6" hidden="1" customHeight="1">
-      <c r="A154" s="126"/>
+      <c r="A154" s="121"/>
       <c r="B154" s="61" t="s">
         <v>392</v>
       </c>
@@ -13045,7 +13045,7 @@
       </c>
     </row>
     <row r="155" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A155" s="126"/>
+      <c r="A155" s="121"/>
       <c r="B155" s="61" t="s">
         <v>392</v>
       </c>
@@ -13094,7 +13094,7 @@
       </c>
     </row>
     <row r="156" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="126"/>
+      <c r="A156" s="121"/>
       <c r="B156" s="61" t="s">
         <v>392</v>
       </c>
@@ -13148,7 +13148,7 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A157" s="126"/>
+      <c r="A157" s="121"/>
       <c r="B157" s="61" t="s">
         <v>392</v>
       </c>
@@ -13202,7 +13202,7 @@
       </c>
     </row>
     <row r="158" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A158" s="126"/>
+      <c r="A158" s="121"/>
       <c r="B158" s="61" t="s">
         <v>392</v>
       </c>
@@ -13256,7 +13256,7 @@
       </c>
     </row>
     <row r="159" spans="1:19" ht="102" hidden="1">
-      <c r="A159" s="126"/>
+      <c r="A159" s="121"/>
       <c r="B159" s="61" t="s">
         <v>406</v>
       </c>
@@ -13305,8 +13305,8 @@
       </c>
       <c r="S159" s="61"/>
     </row>
-    <row r="160" spans="1:19" ht="40.799999999999997">
-      <c r="A160" s="126"/>
+    <row r="160" spans="1:19" ht="40.799999999999997" hidden="1">
+      <c r="A160" s="121"/>
       <c r="B160" s="61" t="s">
         <v>406</v>
       </c>
@@ -13359,7 +13359,7 @@
       <c r="S160" s="61"/>
     </row>
     <row r="161" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A161" s="126"/>
+      <c r="A161" s="121"/>
       <c r="B161" s="61" t="s">
         <v>406</v>
       </c>
@@ -13409,7 +13409,7 @@
       <c r="S161" s="61"/>
     </row>
     <row r="162" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A162" s="126"/>
+      <c r="A162" s="121"/>
       <c r="B162" s="61" t="s">
         <v>406</v>
       </c>
@@ -13514,7 +13514,7 @@
       </c>
     </row>
     <row r="164" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A164" s="126"/>
+      <c r="A164" s="121"/>
       <c r="B164" s="61" t="s">
         <v>414</v>
       </c>
@@ -13617,7 +13617,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="20.399999999999999" hidden="1">
+    <row r="166" spans="1:19" ht="20.399999999999999">
       <c r="A166" s="55"/>
       <c r="B166" s="61" t="s">
         <v>421</v>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="S166" s="61"/>
     </row>
-    <row r="167" spans="1:19" ht="40.799999999999997" hidden="1">
+    <row r="167" spans="1:19" ht="40.799999999999997">
       <c r="A167" s="62">
         <v>43</v>
       </c>
@@ -14005,7 +14005,7 @@
       </c>
     </row>
     <row r="173" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A173" s="116">
+      <c r="A173" s="120">
         <v>45</v>
       </c>
       <c r="B173" s="61" t="s">
@@ -14060,7 +14060,7 @@
       </c>
     </row>
     <row r="174" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A174" s="116"/>
+      <c r="A174" s="120"/>
       <c r="B174" s="61" t="s">
         <v>438</v>
       </c>
@@ -14113,8 +14113,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="20.399999999999999">
-      <c r="A175" s="116"/>
+    <row r="175" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A175" s="120"/>
       <c r="B175" s="61" t="s">
         <v>438</v>
       </c>
@@ -14166,7 +14166,7 @@
       <c r="S175" s="61"/>
     </row>
     <row r="176" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A176" s="116"/>
+      <c r="A176" s="120"/>
       <c r="B176" s="61" t="s">
         <v>438</v>
       </c>
@@ -14220,7 +14220,7 @@
       </c>
     </row>
     <row r="177" spans="1:19" ht="61.2" hidden="1">
-      <c r="A177" s="116"/>
+      <c r="A177" s="120"/>
       <c r="B177" s="61" t="s">
         <v>438</v>
       </c>
@@ -14272,7 +14272,7 @@
       <c r="S177" s="61"/>
     </row>
     <row r="178" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A178" s="116"/>
+      <c r="A178" s="120"/>
       <c r="B178" s="61" t="s">
         <v>446</v>
       </c>
@@ -14326,7 +14326,7 @@
       </c>
     </row>
     <row r="179" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A179" s="116"/>
+      <c r="A179" s="120"/>
       <c r="B179" s="61" t="s">
         <v>448</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="61.2" customHeight="1">
+    <row r="183" spans="1:19" ht="61.2" hidden="1" customHeight="1">
       <c r="A183" s="130"/>
       <c r="B183" s="61" t="s">
         <v>451</v>
@@ -14887,7 +14887,7 @@
       </c>
     </row>
     <row r="190" spans="1:19" ht="64.95" hidden="1" customHeight="1">
-      <c r="A190" s="116">
+      <c r="A190" s="120">
         <v>48</v>
       </c>
       <c r="B190" s="61" t="s">
@@ -14940,7 +14940,7 @@
       </c>
     </row>
     <row r="191" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A191" s="116"/>
+      <c r="A191" s="120"/>
       <c r="B191" s="61" t="s">
         <v>465</v>
       </c>
@@ -14990,8 +14990,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="20.399999999999999">
-      <c r="A192" s="116"/>
+    <row r="192" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A192" s="120"/>
       <c r="B192" s="61" t="s">
         <v>465</v>
       </c>
@@ -15072,7 +15072,7 @@
       <c r="S193" s="62"/>
     </row>
     <row r="194" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A194" s="126"/>
+      <c r="A194" s="121"/>
       <c r="B194" s="61" t="s">
         <v>476</v>
       </c>
@@ -15176,7 +15176,7 @@
       </c>
     </row>
     <row r="196" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A196" s="116">
+      <c r="A196" s="120">
         <v>51</v>
       </c>
       <c r="B196" s="61" t="s">
@@ -15229,7 +15229,7 @@
       </c>
     </row>
     <row r="197" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A197" s="116"/>
+      <c r="A197" s="120"/>
       <c r="B197" s="61" t="s">
         <v>480</v>
       </c>
@@ -15283,7 +15283,7 @@
       </c>
     </row>
     <row r="198" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A198" s="116"/>
+      <c r="A198" s="120"/>
       <c r="B198" s="61" t="s">
         <v>480</v>
       </c>
@@ -15337,7 +15337,7 @@
       </c>
     </row>
     <row r="199" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A199" s="116"/>
+      <c r="A199" s="120"/>
       <c r="B199" s="61" t="s">
         <v>480</v>
       </c>
@@ -15487,7 +15487,7 @@
       <c r="R201" s="40"/>
       <c r="S201" s="62"/>
     </row>
-    <row r="202" spans="1:19" ht="20.399999999999999">
+    <row r="202" spans="1:19" ht="20.399999999999999" hidden="1">
       <c r="A202" s="62">
         <v>52</v>
       </c>
@@ -15544,7 +15544,7 @@
       </c>
     </row>
     <row r="203" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A203" s="116">
+      <c r="A203" s="120">
         <v>53</v>
       </c>
       <c r="B203" s="61" t="s">
@@ -15599,7 +15599,7 @@
       </c>
     </row>
     <row r="204" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A204" s="116"/>
+      <c r="A204" s="120"/>
       <c r="B204" s="61" t="s">
         <v>492</v>
       </c>
@@ -15653,7 +15653,7 @@
       </c>
     </row>
     <row r="205" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A205" s="116"/>
+      <c r="A205" s="120"/>
       <c r="B205" s="62" t="s">
         <v>496</v>
       </c>
@@ -15707,7 +15707,7 @@
       </c>
     </row>
     <row r="206" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A206" s="116">
+      <c r="A206" s="120">
         <v>54</v>
       </c>
       <c r="B206" s="61" t="s">
@@ -15760,8 +15760,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="20.399999999999999">
-      <c r="A207" s="116"/>
+    <row r="207" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A207" s="120"/>
       <c r="B207" s="61" t="s">
         <v>499</v>
       </c>
@@ -15817,7 +15817,7 @@
       </c>
     </row>
     <row r="208" spans="1:19" ht="32.4" hidden="1" customHeight="1">
-      <c r="A208" s="116">
+      <c r="A208" s="120">
         <v>55</v>
       </c>
       <c r="B208" s="61" t="s">
@@ -15871,8 +15871,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="209" spans="1:19" ht="20.399999999999999">
-      <c r="A209" s="116"/>
+    <row r="209" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A209" s="120"/>
       <c r="B209" s="61" t="s">
         <v>502</v>
       </c>
@@ -15924,7 +15924,7 @@
       <c r="S209" s="61"/>
     </row>
     <row r="210" spans="1:19" ht="16.2" hidden="1" customHeight="1">
-      <c r="A210" s="116"/>
+      <c r="A210" s="120"/>
       <c r="B210" s="61" t="s">
         <v>502</v>
       </c>
@@ -15976,7 +15976,7 @@
       <c r="S210" s="62"/>
     </row>
     <row r="211" spans="1:19" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A211" s="116">
+      <c r="A211" s="120">
         <v>56</v>
       </c>
       <c r="B211" s="61" t="s">
@@ -16028,8 +16028,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="20.399999999999999">
-      <c r="A212" s="116"/>
+    <row r="212" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A212" s="120"/>
       <c r="B212" s="61" t="s">
         <v>511</v>
       </c>
@@ -16246,7 +16246,7 @@
       </c>
     </row>
     <row r="216" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A216" s="126"/>
+      <c r="A216" s="121"/>
       <c r="B216" s="61" t="s">
         <v>513</v>
       </c>
@@ -16564,7 +16564,7 @@
       </c>
     </row>
     <row r="222" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A222" s="116">
+      <c r="A222" s="120">
         <v>59</v>
       </c>
       <c r="B222" s="61" t="s">
@@ -16617,7 +16617,7 @@
       </c>
     </row>
     <row r="223" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A223" s="116"/>
+      <c r="A223" s="120"/>
       <c r="B223" s="61" t="s">
         <v>533</v>
       </c>
@@ -16671,7 +16671,7 @@
       </c>
     </row>
     <row r="224" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A224" s="116"/>
+      <c r="A224" s="120"/>
       <c r="B224" s="61" t="s">
         <v>533</v>
       </c>
@@ -16720,7 +16720,7 @@
       <c r="S224" s="61"/>
     </row>
     <row r="225" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A225" s="116"/>
+      <c r="A225" s="120"/>
       <c r="B225" s="61" t="s">
         <v>533</v>
       </c>
@@ -16773,8 +16773,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="226" spans="1:19" ht="61.2">
-      <c r="A226" s="116"/>
+    <row r="226" spans="1:19" ht="61.2" hidden="1">
+      <c r="A226" s="120"/>
       <c r="B226" s="61" t="s">
         <v>533</v>
       </c>
@@ -16822,7 +16822,7 @@
       <c r="S226" s="62"/>
     </row>
     <row r="227" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A227" s="116"/>
+      <c r="A227" s="120"/>
       <c r="B227" s="61" t="s">
         <v>533</v>
       </c>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="S229" s="62"/>
     </row>
-    <row r="230" spans="1:19" ht="20.399999999999999" customHeight="1">
+    <row r="230" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A230" s="62"/>
       <c r="B230" s="61" t="s">
         <v>543</v>
@@ -17164,7 +17164,7 @@
       </c>
     </row>
     <row r="234" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A234" s="121">
+      <c r="A234" s="126">
         <v>63</v>
       </c>
       <c r="B234" s="61" t="s">
@@ -17214,7 +17214,7 @@
       </c>
     </row>
     <row r="235" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="126"/>
+      <c r="A235" s="121"/>
       <c r="B235" s="61" t="s">
         <v>551</v>
       </c>
@@ -17266,7 +17266,7 @@
       </c>
     </row>
     <row r="236" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="126"/>
+      <c r="A236" s="121"/>
       <c r="B236" s="61" t="s">
         <v>551</v>
       </c>
@@ -17318,7 +17318,7 @@
       </c>
     </row>
     <row r="237" spans="1:19" ht="39.6" hidden="1" customHeight="1">
-      <c r="A237" s="126"/>
+      <c r="A237" s="121"/>
       <c r="B237" s="61" t="s">
         <v>551</v>
       </c>
@@ -17367,7 +17367,7 @@
       </c>
     </row>
     <row r="238" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A238" s="126"/>
+      <c r="A238" s="121"/>
       <c r="B238" s="61" t="s">
         <v>551</v>
       </c>
@@ -17470,7 +17470,7 @@
       </c>
     </row>
     <row r="240" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="116">
+      <c r="A240" s="120">
         <v>64</v>
       </c>
       <c r="B240" s="61" t="s">
@@ -17523,7 +17523,7 @@
       <c r="S240" s="61"/>
     </row>
     <row r="241" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="116"/>
+      <c r="A241" s="120"/>
       <c r="B241" s="61" t="s">
         <v>567</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="242" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="116"/>
+      <c r="A242" s="120"/>
       <c r="B242" s="61" t="s">
         <v>567</v>
       </c>
@@ -17631,7 +17631,7 @@
       </c>
     </row>
     <row r="243" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A243" s="116"/>
+      <c r="A243" s="120"/>
       <c r="B243" s="61" t="s">
         <v>567</v>
       </c>
@@ -17681,7 +17681,7 @@
       </c>
     </row>
     <row r="244" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A244" s="116"/>
+      <c r="A244" s="120"/>
       <c r="B244" s="61" t="s">
         <v>567</v>
       </c>
@@ -17714,7 +17714,7 @@
       <c r="S244" s="61"/>
     </row>
     <row r="245" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A245" s="116"/>
+      <c r="A245" s="120"/>
       <c r="B245" s="61" t="s">
         <v>567</v>
       </c>
@@ -17764,7 +17764,7 @@
       </c>
     </row>
     <row r="246" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A246" s="116"/>
+      <c r="A246" s="120"/>
       <c r="B246" s="61" t="s">
         <v>567</v>
       </c>
@@ -17869,7 +17869,7 @@
       <c r="S247" s="61"/>
     </row>
     <row r="248" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A248" s="116">
+      <c r="A248" s="120">
         <v>65</v>
       </c>
       <c r="B248" s="61" t="s">
@@ -17922,7 +17922,7 @@
       </c>
     </row>
     <row r="249" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="116"/>
+      <c r="A249" s="120"/>
       <c r="B249" s="61" t="s">
         <v>575</v>
       </c>
@@ -17972,7 +17972,7 @@
       </c>
     </row>
     <row r="250" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A250" s="116"/>
+      <c r="A250" s="120"/>
       <c r="B250" s="61" t="s">
         <v>575</v>
       </c>
@@ -18153,8 +18153,8 @@
       </c>
       <c r="S253" s="62"/>
     </row>
-    <row r="254" spans="1:19" ht="40.799999999999997">
-      <c r="A254" s="121">
+    <row r="254" spans="1:19" ht="40.799999999999997" hidden="1">
+      <c r="A254" s="126">
         <v>68</v>
       </c>
       <c r="B254" s="61" t="s">
@@ -18204,7 +18204,7 @@
       </c>
     </row>
     <row r="255" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A255" s="126"/>
+      <c r="A255" s="121"/>
       <c r="B255" s="61" t="s">
         <v>588</v>
       </c>
@@ -18257,7 +18257,7 @@
       </c>
     </row>
     <row r="256" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A256" s="126"/>
+      <c r="A256" s="121"/>
       <c r="B256" s="61" t="s">
         <v>588</v>
       </c>
@@ -18311,7 +18311,7 @@
       </c>
     </row>
     <row r="257" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A257" s="126"/>
+      <c r="A257" s="121"/>
       <c r="B257" s="61" t="s">
         <v>588</v>
       </c>
@@ -18365,7 +18365,7 @@
       </c>
     </row>
     <row r="258" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A258" s="126"/>
+      <c r="A258" s="121"/>
       <c r="B258" s="61" t="s">
         <v>588</v>
       </c>
@@ -18471,7 +18471,7 @@
       </c>
     </row>
     <row r="260" spans="1:19" ht="154.19999999999999" hidden="1" customHeight="1">
-      <c r="A260" s="121">
+      <c r="A260" s="126">
         <v>69</v>
       </c>
       <c r="B260" s="61" t="s">
@@ -18520,7 +18520,7 @@
       </c>
     </row>
     <row r="261" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A261" s="126"/>
+      <c r="A261" s="121"/>
       <c r="B261" s="61" t="s">
         <v>598</v>
       </c>
@@ -18568,7 +18568,7 @@
       </c>
     </row>
     <row r="262" spans="1:19" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="126"/>
+      <c r="A262" s="121"/>
       <c r="B262" s="61" t="s">
         <v>603</v>
       </c>
@@ -18614,7 +18614,7 @@
       </c>
     </row>
     <row r="263" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A263" s="126"/>
+      <c r="A263" s="121"/>
       <c r="B263" s="61" t="s">
         <v>603</v>
       </c>
@@ -18662,7 +18662,7 @@
       </c>
     </row>
     <row r="264" spans="1:19" ht="46.2" hidden="1" customHeight="1">
-      <c r="A264" s="126"/>
+      <c r="A264" s="121"/>
       <c r="B264" s="61" t="s">
         <v>598</v>
       </c>
@@ -18769,7 +18769,7 @@
       <c r="S265" s="61"/>
     </row>
     <row r="266" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A266" s="116">
+      <c r="A266" s="120">
         <v>70</v>
       </c>
       <c r="B266" s="61" t="s">
@@ -18825,7 +18825,7 @@
       <c r="S266" s="61"/>
     </row>
     <row r="267" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="116"/>
+      <c r="A267" s="120"/>
       <c r="B267" s="61" t="s">
         <v>609</v>
       </c>
@@ -18879,7 +18879,7 @@
       <c r="S267" s="61"/>
     </row>
     <row r="268" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="116"/>
+      <c r="A268" s="120"/>
       <c r="B268" s="61" t="s">
         <v>609</v>
       </c>
@@ -18932,8 +18932,8 @@
       </c>
       <c r="S268" s="61"/>
     </row>
-    <row r="269" spans="1:19" ht="40.950000000000003" customHeight="1">
-      <c r="A269" s="116"/>
+    <row r="269" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A269" s="120"/>
       <c r="B269" s="61" t="s">
         <v>609</v>
       </c>
@@ -19038,8 +19038,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="271" spans="1:19" ht="61.2" customHeight="1">
-      <c r="A271" s="116">
+    <row r="271" spans="1:19" ht="61.2" hidden="1" customHeight="1">
+      <c r="A271" s="120">
         <v>71</v>
       </c>
       <c r="B271" s="61" t="s">
@@ -19093,7 +19093,7 @@
       <c r="S271" s="61"/>
     </row>
     <row r="272" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="116"/>
+      <c r="A272" s="120"/>
       <c r="B272" s="61" t="s">
         <v>620</v>
       </c>
@@ -19145,7 +19145,7 @@
       <c r="S272" s="61"/>
     </row>
     <row r="273" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A273" s="116"/>
+      <c r="A273" s="120"/>
       <c r="B273" s="61" t="s">
         <v>620</v>
       </c>
@@ -19199,7 +19199,7 @@
       </c>
     </row>
     <row r="274" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A274" s="116"/>
+      <c r="A274" s="120"/>
       <c r="B274" s="61" t="s">
         <v>620</v>
       </c>
@@ -19251,7 +19251,7 @@
       <c r="S274" s="61"/>
     </row>
     <row r="275" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A275" s="116"/>
+      <c r="A275" s="120"/>
       <c r="B275" s="62" t="s">
         <v>627</v>
       </c>
@@ -19513,7 +19513,7 @@
       <c r="S279" s="62"/>
     </row>
     <row r="280" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A280" s="116">
+      <c r="A280" s="120">
         <v>74</v>
       </c>
       <c r="B280" s="61" t="s">
@@ -19565,7 +19565,7 @@
       </c>
     </row>
     <row r="281" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A281" s="116"/>
+      <c r="A281" s="120"/>
       <c r="B281" s="61" t="s">
         <v>635</v>
       </c>
@@ -19612,7 +19612,7 @@
       <c r="S281" s="62"/>
     </row>
     <row r="282" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A282" s="116">
+      <c r="A282" s="120">
         <v>75</v>
       </c>
       <c r="B282" s="61" t="s">
@@ -19665,7 +19665,7 @@
       </c>
     </row>
     <row r="283" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A283" s="116"/>
+      <c r="A283" s="120"/>
       <c r="B283" s="61" t="s">
         <v>638</v>
       </c>
@@ -19935,7 +19935,7 @@
       </c>
     </row>
     <row r="288" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A288" s="116"/>
+      <c r="A288" s="120"/>
       <c r="B288" s="61" t="s">
         <v>642</v>
       </c>
@@ -19986,7 +19986,7 @@
       </c>
     </row>
     <row r="289" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A289" s="116"/>
+      <c r="A289" s="120"/>
       <c r="B289" s="61" t="s">
         <v>642</v>
       </c>
@@ -20038,7 +20038,7 @@
       </c>
     </row>
     <row r="290" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A290" s="116"/>
+      <c r="A290" s="120"/>
       <c r="B290" s="61" t="s">
         <v>642</v>
       </c>
@@ -20092,7 +20092,7 @@
       </c>
     </row>
     <row r="291" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A291" s="116"/>
+      <c r="A291" s="120"/>
       <c r="B291" s="83" t="s">
         <v>642</v>
       </c>
@@ -20139,8 +20139,8 @@
       </c>
       <c r="S291" s="83"/>
     </row>
-    <row r="292" spans="1:19" ht="20.399999999999999">
-      <c r="A292" s="116"/>
+    <row r="292" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A292" s="120"/>
       <c r="B292" s="61" t="s">
         <v>642</v>
       </c>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="S292" s="61"/>
     </row>
-    <row r="293" spans="1:19" ht="61.2" hidden="1">
+    <row r="293" spans="1:19" ht="61.2">
       <c r="A293" s="62"/>
       <c r="B293" s="61" t="s">
         <v>656</v>
@@ -20249,8 +20249,8 @@
         <v>660</v>
       </c>
     </row>
-    <row r="294" spans="1:19" ht="142.80000000000001" hidden="1">
-      <c r="A294" s="116">
+    <row r="294" spans="1:19" ht="142.80000000000001">
+      <c r="A294" s="120">
         <v>77</v>
       </c>
       <c r="B294" s="61" t="s">
@@ -20309,8 +20309,8 @@
         <v>663</v>
       </c>
     </row>
-    <row r="295" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A295" s="116"/>
+    <row r="295" spans="1:19" ht="40.799999999999997">
+      <c r="A295" s="120"/>
       <c r="B295" s="61" t="s">
         <v>656</v>
       </c>
@@ -20367,8 +20367,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="296" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A296" s="116"/>
+    <row r="296" spans="1:19" ht="20.399999999999999">
+      <c r="A296" s="120"/>
       <c r="B296" s="61" t="s">
         <v>656</v>
       </c>
@@ -20426,7 +20426,7 @@
       </c>
     </row>
     <row r="297" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A297" s="116">
+      <c r="A297" s="120">
         <v>78</v>
       </c>
       <c r="B297" s="61" t="s">
@@ -20479,7 +20479,7 @@
       </c>
     </row>
     <row r="298" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A298" s="116"/>
+      <c r="A298" s="120"/>
       <c r="B298" s="61" t="s">
         <v>667</v>
       </c>
@@ -20531,7 +20531,7 @@
       <c r="S298" s="61"/>
     </row>
     <row r="299" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A299" s="116"/>
+      <c r="A299" s="120"/>
       <c r="B299" s="61" t="s">
         <v>667</v>
       </c>
@@ -20585,7 +20585,7 @@
       </c>
     </row>
     <row r="300" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A300" s="126"/>
+      <c r="A300" s="121"/>
       <c r="B300" s="61" t="s">
         <v>603</v>
       </c>
@@ -20691,7 +20691,7 @@
       </c>
     </row>
     <row r="302" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A302" s="121">
+      <c r="A302" s="126">
         <v>80</v>
       </c>
       <c r="B302" s="61" t="s">
@@ -20742,7 +20742,7 @@
       </c>
     </row>
     <row r="303" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A303" s="126"/>
+      <c r="A303" s="121"/>
       <c r="B303" s="61" t="s">
         <v>680</v>
       </c>
@@ -20794,7 +20794,7 @@
       <c r="S303" s="61"/>
     </row>
     <row r="304" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A304" s="121">
+      <c r="A304" s="126">
         <v>81</v>
       </c>
       <c r="B304" s="61" t="s">
@@ -20846,7 +20846,7 @@
       </c>
     </row>
     <row r="305" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="126"/>
+      <c r="A305" s="121"/>
       <c r="B305" s="61" t="s">
         <v>682</v>
       </c>
@@ -20898,7 +20898,7 @@
       </c>
     </row>
     <row r="306" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="126"/>
+      <c r="A306" s="121"/>
       <c r="B306" s="61" t="s">
         <v>682</v>
       </c>
@@ -21071,54 +21071,54 @@
       <c r="D309" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E309" s="123">
+      <c r="E309" s="132">
         <v>4600018191</v>
       </c>
-      <c r="F309" s="132" t="s">
+      <c r="F309" s="131" t="s">
         <v>693</v>
       </c>
-      <c r="G309" s="116" t="s">
+      <c r="G309" s="120" t="s">
         <v>694</v>
       </c>
-      <c r="H309" s="116">
+      <c r="H309" s="120">
         <v>13.3</v>
       </c>
-      <c r="I309" s="121" t="s">
+      <c r="I309" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="J309" s="121" t="s">
+      <c r="J309" s="126" t="s">
         <v>514</v>
       </c>
-      <c r="K309" s="120">
+      <c r="K309" s="123">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L309" s="120">
+      <c r="L309" s="123">
         <v>0</v>
       </c>
-      <c r="M309" s="120">
+      <c r="M309" s="123">
         <f>+K309</f>
         <v>988077089</v>
       </c>
-      <c r="N309" s="117" t="s">
+      <c r="N309" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="O309" s="117" t="s">
+      <c r="O309" s="125" t="s">
         <v>695</v>
       </c>
-      <c r="P309" s="116">
+      <c r="P309" s="120">
         <v>2025</v>
       </c>
-      <c r="Q309" s="117" t="s">
+      <c r="Q309" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="R309" s="116"/>
-      <c r="S309" s="116" t="s">
+      <c r="R309" s="120"/>
+      <c r="S309" s="120" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A310" s="116">
+      <c r="A310" s="120">
         <v>84</v>
       </c>
       <c r="B310" s="61" t="s">
@@ -21130,24 +21130,24 @@
       <c r="D310" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E310" s="124"/>
-      <c r="F310" s="117"/>
-      <c r="G310" s="116"/>
-      <c r="H310" s="116"/>
+      <c r="E310" s="133"/>
+      <c r="F310" s="125"/>
+      <c r="G310" s="120"/>
+      <c r="H310" s="120"/>
       <c r="I310" s="122"/>
       <c r="J310" s="122"/>
-      <c r="K310" s="120"/>
-      <c r="L310" s="120"/>
-      <c r="M310" s="120"/>
-      <c r="N310" s="117"/>
-      <c r="O310" s="117"/>
-      <c r="P310" s="116"/>
-      <c r="Q310" s="117"/>
-      <c r="R310" s="116"/>
-      <c r="S310" s="116"/>
+      <c r="K310" s="123"/>
+      <c r="L310" s="123"/>
+      <c r="M310" s="123"/>
+      <c r="N310" s="125"/>
+      <c r="O310" s="125"/>
+      <c r="P310" s="120"/>
+      <c r="Q310" s="125"/>
+      <c r="R310" s="120"/>
+      <c r="S310" s="120"/>
     </row>
     <row r="311" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="116"/>
+      <c r="A311" s="120"/>
       <c r="B311" s="61" t="s">
         <v>692</v>
       </c>
@@ -21157,55 +21157,55 @@
       <c r="D311" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E311" s="123">
+      <c r="E311" s="132">
         <v>4600009793</v>
       </c>
-      <c r="F311" s="117" t="s">
+      <c r="F311" s="125" t="s">
         <v>697</v>
       </c>
-      <c r="G311" s="116" t="s">
+      <c r="G311" s="120" t="s">
         <v>698</v>
       </c>
-      <c r="H311" s="116">
+      <c r="H311" s="120">
         <v>31.12</v>
       </c>
-      <c r="I311" s="121" t="s">
+      <c r="I311" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="J311" s="121" t="s">
+      <c r="J311" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="K311" s="120">
+      <c r="K311" s="123">
         <f>+M311</f>
         <v>73907566008</v>
       </c>
-      <c r="L311" s="120">
+      <c r="L311" s="123">
         <v>0</v>
       </c>
-      <c r="M311" s="120">
+      <c r="M311" s="123">
         <v>73907566008</v>
       </c>
-      <c r="N311" s="117" t="s">
+      <c r="N311" s="125" t="s">
         <v>699</v>
       </c>
-      <c r="O311" s="117" t="s">
+      <c r="O311" s="125" t="s">
         <v>91</v>
       </c>
-      <c r="P311" s="116">
+      <c r="P311" s="120">
         <v>2019</v>
       </c>
-      <c r="Q311" s="117" t="s">
+      <c r="Q311" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="R311" s="133">
+      <c r="R311" s="124">
         <v>1</v>
       </c>
-      <c r="S311" s="116" t="s">
+      <c r="S311" s="120" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="116"/>
+      <c r="A312" s="120"/>
       <c r="B312" s="61" t="s">
         <v>696</v>
       </c>
@@ -21215,24 +21215,24 @@
       <c r="D312" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E312" s="124"/>
-      <c r="F312" s="117"/>
-      <c r="G312" s="116"/>
-      <c r="H312" s="116"/>
+      <c r="E312" s="133"/>
+      <c r="F312" s="125"/>
+      <c r="G312" s="120"/>
+      <c r="H312" s="120"/>
       <c r="I312" s="122"/>
       <c r="J312" s="122"/>
-      <c r="K312" s="120"/>
-      <c r="L312" s="120"/>
-      <c r="M312" s="120"/>
-      <c r="N312" s="117"/>
-      <c r="O312" s="117"/>
-      <c r="P312" s="116"/>
-      <c r="Q312" s="117"/>
-      <c r="R312" s="133"/>
-      <c r="S312" s="116"/>
+      <c r="K312" s="123"/>
+      <c r="L312" s="123"/>
+      <c r="M312" s="123"/>
+      <c r="N312" s="125"/>
+      <c r="O312" s="125"/>
+      <c r="P312" s="120"/>
+      <c r="Q312" s="125"/>
+      <c r="R312" s="124"/>
+      <c r="S312" s="120"/>
     </row>
     <row r="313" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="116"/>
+      <c r="A313" s="120"/>
       <c r="B313" s="61" t="s">
         <v>696</v>
       </c>
@@ -21288,7 +21288,7 @@
       </c>
     </row>
     <row r="314" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="116"/>
+      <c r="A314" s="120"/>
       <c r="B314" s="61" t="s">
         <v>696</v>
       </c>
@@ -21341,8 +21341,8 @@
       </c>
       <c r="S314" s="61"/>
     </row>
-    <row r="315" spans="1:19" ht="40.950000000000003" customHeight="1">
-      <c r="A315" s="116"/>
+    <row r="315" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A315" s="120"/>
       <c r="B315" s="61" t="s">
         <v>696</v>
       </c>
@@ -21488,7 +21488,7 @@
       </c>
     </row>
     <row r="318" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A318" s="121">
+      <c r="A318" s="126">
         <v>85</v>
       </c>
       <c r="B318" s="61" t="s">
@@ -21788,7 +21788,7 @@
       </c>
     </row>
     <row r="324" spans="1:19" ht="93" hidden="1" customHeight="1">
-      <c r="A324" s="126"/>
+      <c r="A324" s="121"/>
       <c r="B324" s="62" t="s">
         <v>708</v>
       </c>
@@ -21838,7 +21838,7 @@
       </c>
     </row>
     <row r="325" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A325" s="126"/>
+      <c r="A325" s="121"/>
       <c r="B325" s="62" t="s">
         <v>708</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="328" spans="1:19" ht="61.2" customHeight="1">
+    <row r="328" spans="1:19" ht="61.2" hidden="1" customHeight="1">
       <c r="A328" s="128"/>
       <c r="B328" s="61" t="s">
         <v>708</v>
@@ -22262,7 +22262,7 @@
       </c>
     </row>
     <row r="334" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A334" s="121">
+      <c r="A334" s="126">
         <v>89</v>
       </c>
       <c r="B334" s="61" t="s">
@@ -22322,7 +22322,7 @@
       </c>
     </row>
     <row r="335" spans="1:19" ht="44.4" hidden="1" customHeight="1">
-      <c r="A335" s="126"/>
+      <c r="A335" s="121"/>
       <c r="B335" s="61" t="s">
         <v>724</v>
       </c>
@@ -22373,7 +22373,7 @@
       </c>
     </row>
     <row r="336" spans="1:19" ht="155.4" hidden="1" customHeight="1">
-      <c r="A336" s="126"/>
+      <c r="A336" s="121"/>
       <c r="B336" s="61" t="s">
         <v>724</v>
       </c>
@@ -22520,7 +22520,7 @@
       </c>
     </row>
     <row r="339" spans="1:19" s="80" customFormat="1" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A339" s="116">
+      <c r="A339" s="120">
         <v>90</v>
       </c>
       <c r="B339" s="75" t="s">
@@ -22575,7 +22575,7 @@
       </c>
     </row>
     <row r="340" spans="1:19" s="80" customFormat="1" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A340" s="116"/>
+      <c r="A340" s="120"/>
       <c r="B340" s="75" t="s">
         <v>732</v>
       </c>
@@ -22627,7 +22627,7 @@
       <c r="S340" s="77"/>
     </row>
     <row r="341" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A341" s="116">
+      <c r="A341" s="120">
         <v>91</v>
       </c>
       <c r="B341" s="61" t="s">
@@ -22683,7 +22683,7 @@
       </c>
     </row>
     <row r="342" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A342" s="116"/>
+      <c r="A342" s="120"/>
       <c r="B342" s="61" t="s">
         <v>735</v>
       </c>
@@ -22737,7 +22737,7 @@
       </c>
     </row>
     <row r="343" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A343" s="116"/>
+      <c r="A343" s="120"/>
       <c r="B343" s="61" t="s">
         <v>735</v>
       </c>
@@ -22785,7 +22785,7 @@
       </c>
     </row>
     <row r="344" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A344" s="116"/>
+      <c r="A344" s="120"/>
       <c r="B344" s="61" t="s">
         <v>735</v>
       </c>
@@ -22839,7 +22839,7 @@
       </c>
     </row>
     <row r="345" spans="1:19" ht="61.2" hidden="1">
-      <c r="A345" s="116"/>
+      <c r="A345" s="120"/>
       <c r="B345" s="61" t="s">
         <v>735</v>
       </c>
@@ -22890,7 +22890,7 @@
       </c>
     </row>
     <row r="346" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A346" s="116"/>
+      <c r="A346" s="120"/>
       <c r="B346" s="106" t="s">
         <v>735</v>
       </c>
@@ -22933,8 +22933,8 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="347" spans="1:19" ht="20.399999999999999">
-      <c r="A347" s="116"/>
+    <row r="347" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A347" s="120"/>
       <c r="B347" s="61" t="s">
         <v>735</v>
       </c>
@@ -22987,8 +22987,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="348" spans="1:19" ht="61.2" customHeight="1">
-      <c r="A348" s="116">
+    <row r="348" spans="1:19" ht="61.2" hidden="1" customHeight="1">
+      <c r="A348" s="120">
         <v>92</v>
       </c>
       <c r="B348" s="61" t="s">
@@ -23043,7 +23043,7 @@
       <c r="S348" s="61"/>
     </row>
     <row r="349" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="116"/>
+      <c r="A349" s="120"/>
       <c r="B349" s="61" t="s">
         <v>744</v>
       </c>
@@ -23095,7 +23095,7 @@
       </c>
     </row>
     <row r="350" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A350" s="116"/>
+      <c r="A350" s="120"/>
       <c r="B350" s="61" t="s">
         <v>744</v>
       </c>
@@ -23149,7 +23149,7 @@
       </c>
     </row>
     <row r="351" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A351" s="116">
+      <c r="A351" s="120">
         <v>93</v>
       </c>
       <c r="B351" s="61" t="s">
@@ -23201,7 +23201,7 @@
       </c>
     </row>
     <row r="352" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="116"/>
+      <c r="A352" s="120"/>
       <c r="B352" s="61" t="s">
         <v>749</v>
       </c>
@@ -23252,7 +23252,7 @@
       </c>
     </row>
     <row r="353" spans="1:19" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="116"/>
+      <c r="A353" s="120"/>
       <c r="B353" s="61" t="s">
         <v>749</v>
       </c>
@@ -23306,7 +23306,7 @@
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.95" hidden="1" customHeight="1">
-      <c r="A354" s="116"/>
+      <c r="A354" s="120"/>
       <c r="B354" s="61" t="s">
         <v>749</v>
       </c>
@@ -23364,7 +23364,7 @@
       </c>
     </row>
     <row r="355" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A355" s="116"/>
+      <c r="A355" s="120"/>
       <c r="B355" s="61" t="s">
         <v>749</v>
       </c>
@@ -23416,7 +23416,7 @@
       </c>
     </row>
     <row r="356" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A356" s="116"/>
+      <c r="A356" s="120"/>
       <c r="B356" s="61" t="s">
         <v>749</v>
       </c>
@@ -23679,7 +23679,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="361" spans="1:19" ht="40.799999999999997">
+    <row r="361" spans="1:19" ht="40.799999999999997" hidden="1">
       <c r="A361" s="90"/>
       <c r="B361" s="61" t="s">
         <v>758</v>
@@ -23734,8 +23734,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="362" spans="1:19" ht="20.399999999999999">
-      <c r="A362" s="116"/>
+    <row r="362" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A362" s="120"/>
       <c r="B362" s="61" t="s">
         <v>769</v>
       </c>
@@ -23788,7 +23788,7 @@
       <c r="S362" s="61"/>
     </row>
     <row r="363" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A363" s="116"/>
+      <c r="A363" s="120"/>
       <c r="B363" s="61" t="s">
         <v>769</v>
       </c>
@@ -23947,7 +23947,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="366" spans="1:19" ht="20.399999999999999">
+    <row r="366" spans="1:19" ht="20.399999999999999" hidden="1">
       <c r="A366" s="62">
         <v>96</v>
       </c>
@@ -24002,7 +24002,7 @@
       <c r="S366" s="61"/>
     </row>
     <row r="367" spans="1:19" ht="61.2" hidden="1">
-      <c r="A367" s="121">
+      <c r="A367" s="126">
         <v>97</v>
       </c>
       <c r="B367" s="61" t="s">
@@ -24049,7 +24049,7 @@
       </c>
     </row>
     <row r="368" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A368" s="126"/>
+      <c r="A368" s="121"/>
       <c r="B368" s="61" t="s">
         <v>776</v>
       </c>
@@ -24107,7 +24107,7 @@
       </c>
     </row>
     <row r="369" spans="1:19" ht="61.2" hidden="1">
-      <c r="A369" s="126"/>
+      <c r="A369" s="121"/>
       <c r="B369" s="61" t="s">
         <v>776</v>
       </c>
@@ -24158,7 +24158,7 @@
       </c>
     </row>
     <row r="370" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A370" s="126"/>
+      <c r="A370" s="121"/>
       <c r="B370" s="61" t="s">
         <v>776</v>
       </c>
@@ -24211,7 +24211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="371" spans="1:19" ht="40.799999999999997">
+    <row r="371" spans="1:19" ht="40.799999999999997" hidden="1">
       <c r="A371" s="122"/>
       <c r="B371" s="61" t="s">
         <v>776</v>
@@ -24265,7 +24265,7 @@
       <c r="S371" s="61"/>
     </row>
     <row r="372" spans="1:19" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A372" s="116">
+      <c r="A372" s="120">
         <v>98</v>
       </c>
       <c r="B372" s="61" t="s">
@@ -24318,7 +24318,7 @@
       </c>
     </row>
     <row r="373" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A373" s="116"/>
+      <c r="A373" s="120"/>
       <c r="B373" s="61" t="s">
         <v>782</v>
       </c>
@@ -24369,7 +24369,7 @@
       </c>
     </row>
     <row r="374" spans="1:19" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="116"/>
+      <c r="A374" s="120"/>
       <c r="B374" s="61" t="s">
         <v>782</v>
       </c>
@@ -24420,7 +24420,7 @@
       </c>
     </row>
     <row r="375" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="116"/>
+      <c r="A375" s="120"/>
       <c r="B375" s="61" t="s">
         <v>782</v>
       </c>
@@ -24471,7 +24471,7 @@
       </c>
     </row>
     <row r="376" spans="1:19" ht="122.4" hidden="1" customHeight="1">
-      <c r="A376" s="116"/>
+      <c r="A376" s="120"/>
       <c r="B376" s="61" t="s">
         <v>782</v>
       </c>
@@ -24512,7 +24512,7 @@
       </c>
     </row>
     <row r="377" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A377" s="116"/>
+      <c r="A377" s="120"/>
       <c r="B377" s="61" t="s">
         <v>782</v>
       </c>
@@ -24562,7 +24562,7 @@
       </c>
     </row>
     <row r="378" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A378" s="116"/>
+      <c r="A378" s="120"/>
       <c r="B378" s="61" t="s">
         <v>782</v>
       </c>
@@ -24612,7 +24612,7 @@
       </c>
     </row>
     <row r="379" spans="1:19" ht="61.2" hidden="1" customHeight="1">
-      <c r="A379" s="116"/>
+      <c r="A379" s="120"/>
       <c r="B379" s="61" t="s">
         <v>782</v>
       </c>
@@ -24656,7 +24656,7 @@
       </c>
     </row>
     <row r="380" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A380" s="116"/>
+      <c r="A380" s="120"/>
       <c r="B380" s="61" t="s">
         <v>782</v>
       </c>
@@ -24703,7 +24703,7 @@
       <c r="S380" s="61"/>
     </row>
     <row r="381" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A381" s="116"/>
+      <c r="A381" s="120"/>
       <c r="B381" s="61" t="s">
         <v>782</v>
       </c>
@@ -24755,7 +24755,7 @@
       <c r="S381" s="61"/>
     </row>
     <row r="382" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A382" s="116"/>
+      <c r="A382" s="120"/>
       <c r="B382" s="61" t="s">
         <v>782</v>
       </c>
@@ -24805,7 +24805,7 @@
       </c>
     </row>
     <row r="383" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A383" s="116"/>
+      <c r="A383" s="120"/>
       <c r="B383" s="61" t="s">
         <v>782</v>
       </c>
@@ -24910,7 +24910,7 @@
       </c>
     </row>
     <row r="385" spans="1:19" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A385" s="116"/>
+      <c r="A385" s="120"/>
       <c r="B385" s="61" t="s">
         <v>810</v>
       </c>
@@ -24960,8 +24960,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="386" spans="1:19" ht="61.2" customHeight="1">
-      <c r="A386" s="116"/>
+    <row r="386" spans="1:19" ht="61.2" hidden="1" customHeight="1">
+      <c r="A386" s="120"/>
       <c r="B386" s="61" t="s">
         <v>810</v>
       </c>
@@ -25015,7 +25015,7 @@
       <c r="S386" s="61"/>
     </row>
     <row r="387" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A387" s="116"/>
+      <c r="A387" s="120"/>
       <c r="B387" s="61" t="s">
         <v>810</v>
       </c>
@@ -25067,7 +25067,7 @@
       </c>
     </row>
     <row r="388" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A388" s="116"/>
+      <c r="A388" s="120"/>
       <c r="B388" s="61" t="s">
         <v>809</v>
       </c>
@@ -25119,7 +25119,7 @@
       </c>
     </row>
     <row r="389" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A389" s="116"/>
+      <c r="A389" s="120"/>
       <c r="B389" s="61" t="s">
         <v>809</v>
       </c>
@@ -25173,7 +25173,7 @@
       </c>
     </row>
     <row r="390" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A390" s="116"/>
+      <c r="A390" s="120"/>
       <c r="B390" s="61" t="s">
         <v>809</v>
       </c>
@@ -25212,7 +25212,7 @@
       </c>
     </row>
     <row r="391" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A391" s="116"/>
+      <c r="A391" s="120"/>
       <c r="B391" s="62" t="s">
         <v>809</v>
       </c>
@@ -25315,7 +25315,7 @@
       </c>
     </row>
     <row r="393" spans="1:19" ht="58.2" hidden="1" customHeight="1">
-      <c r="A393" s="116">
+      <c r="A393" s="120">
         <v>100</v>
       </c>
       <c r="B393" s="62" t="s">
@@ -25368,7 +25368,7 @@
       </c>
     </row>
     <row r="394" spans="1:19" ht="61.2" hidden="1">
-      <c r="A394" s="116"/>
+      <c r="A394" s="120"/>
       <c r="B394" s="62" t="s">
         <v>818</v>
       </c>
@@ -25419,7 +25419,7 @@
       </c>
     </row>
     <row r="395" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A395" s="116"/>
+      <c r="A395" s="120"/>
       <c r="B395" s="61" t="s">
         <v>818</v>
       </c>
@@ -25473,7 +25473,7 @@
       </c>
     </row>
     <row r="396" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="116"/>
+      <c r="A396" s="120"/>
       <c r="B396" s="61" t="s">
         <v>818</v>
       </c>
@@ -25521,7 +25521,7 @@
       </c>
     </row>
     <row r="397" spans="1:19" ht="18" hidden="1" customHeight="1">
-      <c r="A397" s="116"/>
+      <c r="A397" s="120"/>
       <c r="B397" s="61" t="s">
         <v>818</v>
       </c>
@@ -25573,7 +25573,7 @@
       <c r="S397" s="61"/>
     </row>
     <row r="398" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A398" s="116"/>
+      <c r="A398" s="120"/>
       <c r="B398" s="61" t="s">
         <v>818</v>
       </c>
@@ -25927,7 +25927,7 @@
       </c>
     </row>
     <row r="405" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A405" s="116">
+      <c r="A405" s="120">
         <v>102</v>
       </c>
       <c r="B405" s="62" t="s">
@@ -25980,7 +25980,7 @@
       </c>
     </row>
     <row r="406" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A406" s="116"/>
+      <c r="A406" s="120"/>
       <c r="B406" s="61" t="s">
         <v>834</v>
       </c>
@@ -26034,7 +26034,7 @@
       </c>
     </row>
     <row r="407" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A407" s="116">
+      <c r="A407" s="120">
         <v>103</v>
       </c>
       <c r="B407" s="61" t="s">
@@ -26088,7 +26088,7 @@
       </c>
     </row>
     <row r="408" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="116"/>
+      <c r="A408" s="120"/>
       <c r="B408" s="61" t="s">
         <v>838</v>
       </c>
@@ -26142,7 +26142,7 @@
       </c>
     </row>
     <row r="409" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="116"/>
+      <c r="A409" s="120"/>
       <c r="B409" s="61" t="s">
         <v>838</v>
       </c>
@@ -26195,7 +26195,7 @@
       </c>
     </row>
     <row r="410" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A410" s="116"/>
+      <c r="A410" s="120"/>
       <c r="B410" s="61" t="s">
         <v>838</v>
       </c>
@@ -26249,7 +26249,7 @@
       </c>
     </row>
     <row r="411" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A411" s="116">
+      <c r="A411" s="120">
         <v>104</v>
       </c>
       <c r="B411" s="61" t="s">
@@ -26302,7 +26302,7 @@
       </c>
     </row>
     <row r="412" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="116"/>
+      <c r="A412" s="120"/>
       <c r="B412" s="61" t="s">
         <v>843</v>
       </c>
@@ -26360,7 +26360,7 @@
       </c>
     </row>
     <row r="413" spans="1:19" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="116"/>
+      <c r="A413" s="120"/>
       <c r="B413" s="61"/>
       <c r="C413" s="62"/>
       <c r="D413" s="62"/>
@@ -26381,7 +26381,7 @@
       <c r="S413" s="61"/>
     </row>
     <row r="414" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A414" s="116"/>
+      <c r="A414" s="120"/>
       <c r="B414" s="61" t="s">
         <v>843</v>
       </c>
@@ -26430,7 +26430,7 @@
       </c>
     </row>
     <row r="415" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A415" s="116"/>
+      <c r="A415" s="120"/>
       <c r="B415" s="61" t="s">
         <v>843</v>
       </c>
@@ -26483,7 +26483,7 @@
       </c>
     </row>
     <row r="416" spans="1:19" ht="61.2" hidden="1">
-      <c r="A416" s="116">
+      <c r="A416" s="120">
         <v>105</v>
       </c>
       <c r="B416" s="61" t="s">
@@ -26536,7 +26536,7 @@
       </c>
     </row>
     <row r="417" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A417" s="116"/>
+      <c r="A417" s="120"/>
       <c r="B417" s="61" t="s">
         <v>850</v>
       </c>
@@ -26581,7 +26581,7 @@
       </c>
     </row>
     <row r="418" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A418" s="116"/>
+      <c r="A418" s="120"/>
       <c r="B418" s="61" t="s">
         <v>850</v>
       </c>
@@ -26635,7 +26635,7 @@
       </c>
     </row>
     <row r="419" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A419" s="116"/>
+      <c r="A419" s="120"/>
       <c r="B419" s="61" t="s">
         <v>850</v>
       </c>
@@ -26689,7 +26689,7 @@
       </c>
     </row>
     <row r="420" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A420" s="116"/>
+      <c r="A420" s="120"/>
       <c r="B420" s="61" t="s">
         <v>850</v>
       </c>
@@ -26743,7 +26743,7 @@
       </c>
     </row>
     <row r="421" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A421" s="116"/>
+      <c r="A421" s="120"/>
       <c r="B421" s="61" t="s">
         <v>850</v>
       </c>
@@ -26784,7 +26784,7 @@
       </c>
     </row>
     <row r="422" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A422" s="116"/>
+      <c r="A422" s="120"/>
       <c r="B422" s="61" t="s">
         <v>850</v>
       </c>
@@ -26832,7 +26832,7 @@
       </c>
     </row>
     <row r="423" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A423" s="116"/>
+      <c r="A423" s="120"/>
       <c r="B423" s="61" t="s">
         <v>850</v>
       </c>
@@ -26980,7 +26980,7 @@
       </c>
     </row>
     <row r="426" spans="1:19" ht="61.2" hidden="1">
-      <c r="A426" s="116">
+      <c r="A426" s="120">
         <v>107</v>
       </c>
       <c r="B426" s="61" t="s">
@@ -27035,7 +27035,7 @@
       </c>
     </row>
     <row r="427" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A427" s="116"/>
+      <c r="A427" s="120"/>
       <c r="B427" s="61" t="s">
         <v>867</v>
       </c>
@@ -27087,7 +27087,7 @@
       <c r="S427" s="61"/>
     </row>
     <row r="428" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A428" s="116"/>
+      <c r="A428" s="120"/>
       <c r="B428" s="61" t="s">
         <v>867</v>
       </c>
@@ -27137,7 +27137,7 @@
       </c>
     </row>
     <row r="429" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="116"/>
+      <c r="A429" s="120"/>
       <c r="B429" s="61" t="s">
         <v>866</v>
       </c>
@@ -27185,7 +27185,7 @@
       </c>
     </row>
     <row r="430" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="116"/>
+      <c r="A430" s="120"/>
       <c r="B430" s="61" t="s">
         <v>866</v>
       </c>
@@ -27232,8 +27232,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="431" spans="1:19" ht="20.399999999999999">
-      <c r="A431" s="116"/>
+    <row r="431" spans="1:19" ht="20.399999999999999" hidden="1">
+      <c r="A431" s="120"/>
       <c r="B431" s="61" t="s">
         <v>867</v>
       </c>
@@ -27285,7 +27285,7 @@
       <c r="S431" s="61"/>
     </row>
     <row r="432" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A432" s="116"/>
+      <c r="A432" s="120"/>
       <c r="B432" s="61" t="s">
         <v>866</v>
       </c>
@@ -27337,7 +27337,7 @@
       <c r="S432" s="62"/>
     </row>
     <row r="433" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A433" s="126"/>
+      <c r="A433" s="121"/>
       <c r="B433" s="61" t="s">
         <v>877</v>
       </c>
@@ -27359,35 +27359,35 @@
       </c>
       <c r="I433" s="61"/>
       <c r="J433" s="61"/>
-      <c r="K433" s="120">
+      <c r="K433" s="123">
         <v>12746524997</v>
       </c>
-      <c r="L433" s="120">
+      <c r="L433" s="123">
         <v>1000000000</v>
       </c>
-      <c r="M433" s="120">
+      <c r="M433" s="123">
         <f>+K433+L433</f>
         <v>13746524997</v>
       </c>
-      <c r="N433" s="117" t="s">
+      <c r="N433" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="O433" s="117" t="s">
+      <c r="O433" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="P433" s="116">
+      <c r="P433" s="120">
         <v>2025</v>
       </c>
       <c r="Q433" s="62"/>
-      <c r="R433" s="133">
+      <c r="R433" s="124">
         <v>0.65</v>
       </c>
-      <c r="S433" s="116" t="s">
+      <c r="S433" s="120" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="434" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A434" s="126"/>
+      <c r="A434" s="121"/>
       <c r="B434" s="61" t="s">
         <v>877</v>
       </c>
@@ -27409,18 +27409,18 @@
       </c>
       <c r="I434" s="61"/>
       <c r="J434" s="61"/>
-      <c r="K434" s="120"/>
-      <c r="L434" s="120"/>
-      <c r="M434" s="120"/>
-      <c r="N434" s="117"/>
-      <c r="O434" s="117"/>
-      <c r="P434" s="116"/>
+      <c r="K434" s="123"/>
+      <c r="L434" s="123"/>
+      <c r="M434" s="123"/>
+      <c r="N434" s="125"/>
+      <c r="O434" s="125"/>
+      <c r="P434" s="120"/>
       <c r="Q434" s="62"/>
-      <c r="R434" s="133"/>
-      <c r="S434" s="116"/>
+      <c r="R434" s="124"/>
+      <c r="S434" s="120"/>
     </row>
     <row r="435" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A435" s="126"/>
+      <c r="A435" s="121"/>
       <c r="B435" s="61" t="s">
         <v>877</v>
       </c>
@@ -27472,7 +27472,7 @@
       </c>
     </row>
     <row r="436" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A436" s="126"/>
+      <c r="A436" s="121"/>
       <c r="B436" s="61" t="s">
         <v>881</v>
       </c>
@@ -27524,7 +27524,7 @@
       </c>
     </row>
     <row r="437" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A437" s="126"/>
+      <c r="A437" s="121"/>
       <c r="B437" s="61" t="s">
         <v>877</v>
       </c>
@@ -27625,7 +27625,7 @@
       </c>
     </row>
     <row r="439" spans="1:19" ht="57" hidden="1" customHeight="1">
-      <c r="A439" s="121">
+      <c r="A439" s="126">
         <v>109</v>
       </c>
       <c r="B439" s="61" t="s">
@@ -27677,7 +27677,7 @@
       </c>
     </row>
     <row r="440" spans="1:19" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="126"/>
+      <c r="A440" s="121"/>
       <c r="B440" s="61" t="s">
         <v>889</v>
       </c>
@@ -27726,7 +27726,7 @@
       </c>
     </row>
     <row r="441" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A441" s="126"/>
+      <c r="A441" s="121"/>
       <c r="B441" s="61" t="s">
         <v>889</v>
       </c>
@@ -27779,7 +27779,7 @@
       </c>
     </row>
     <row r="442" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="126"/>
+      <c r="A442" s="121"/>
       <c r="B442" s="61" t="s">
         <v>889</v>
       </c>
@@ -27831,7 +27831,7 @@
       </c>
     </row>
     <row r="443" spans="1:19" ht="64.95" hidden="1" customHeight="1">
-      <c r="A443" s="126"/>
+      <c r="A443" s="121"/>
       <c r="B443" s="61" t="s">
         <v>889</v>
       </c>
@@ -27879,7 +27879,7 @@
       </c>
     </row>
     <row r="444" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A444" s="126"/>
+      <c r="A444" s="121"/>
       <c r="B444" s="61" t="s">
         <v>889</v>
       </c>
@@ -27927,7 +27927,7 @@
       </c>
     </row>
     <row r="445" spans="1:19" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="126"/>
+      <c r="A445" s="121"/>
       <c r="B445" s="112" t="s">
         <v>889</v>
       </c>
@@ -27961,7 +27961,7 @@
       <c r="R445" s="113"/>
       <c r="S445" s="112"/>
     </row>
-    <row r="446" spans="1:19" ht="15" customHeight="1">
+    <row r="446" spans="1:19" ht="15" hidden="1" customHeight="1">
       <c r="A446" s="122"/>
       <c r="B446" s="61" t="s">
         <v>889</v>
@@ -28013,8 +28013,8 @@
       </c>
       <c r="S446" s="76"/>
     </row>
-    <row r="447" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A447" s="116"/>
+    <row r="447" spans="1:19" ht="40.799999999999997">
+      <c r="A447" s="120"/>
       <c r="B447" s="61" t="s">
         <v>898</v>
       </c>
@@ -28067,8 +28067,8 @@
         <v>901</v>
       </c>
     </row>
-    <row r="448" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A448" s="116"/>
+    <row r="448" spans="1:19" ht="81.599999999999994">
+      <c r="A448" s="120"/>
       <c r="B448" s="93" t="s">
         <v>898</v>
       </c>
@@ -28126,7 +28126,7 @@
       </c>
     </row>
     <row r="449" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A449" s="121">
+      <c r="A449" s="126">
         <v>111</v>
       </c>
       <c r="B449" s="61" t="s">
@@ -28178,7 +28178,7 @@
       </c>
     </row>
     <row r="450" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A450" s="126"/>
+      <c r="A450" s="121"/>
       <c r="B450" s="61" t="s">
         <v>905</v>
       </c>
@@ -28230,7 +28230,7 @@
       </c>
     </row>
     <row r="451" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="126"/>
+      <c r="A451" s="121"/>
       <c r="B451" s="61" t="s">
         <v>905</v>
       </c>
@@ -28338,7 +28338,7 @@
       </c>
     </row>
     <row r="453" spans="1:19" ht="42.6" hidden="1" customHeight="1">
-      <c r="A453" s="116">
+      <c r="A453" s="120">
         <v>112</v>
       </c>
       <c r="B453" s="61" t="s">
@@ -28397,7 +28397,7 @@
       </c>
     </row>
     <row r="454" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A454" s="116"/>
+      <c r="A454" s="120"/>
       <c r="B454" s="61" t="s">
         <v>912</v>
       </c>
@@ -28449,8 +28449,8 @@
       </c>
       <c r="S454" s="61"/>
     </row>
-    <row r="455" spans="1:19" ht="15" customHeight="1">
-      <c r="A455" s="116"/>
+    <row r="455" spans="1:19" ht="15" hidden="1" customHeight="1">
+      <c r="A455" s="120"/>
       <c r="B455" s="61" t="s">
         <v>912</v>
       </c>
@@ -28505,7 +28505,7 @@
       <c r="S455" s="61"/>
     </row>
     <row r="456" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A456" s="116">
+      <c r="A456" s="120">
         <v>113</v>
       </c>
       <c r="B456" s="61" t="s">
@@ -28554,7 +28554,7 @@
       </c>
     </row>
     <row r="457" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A457" s="116"/>
+      <c r="A457" s="120"/>
       <c r="B457" s="61" t="s">
         <v>916</v>
       </c>
@@ -28605,7 +28605,7 @@
       </c>
     </row>
     <row r="458" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A458" s="116"/>
+      <c r="A458" s="120"/>
       <c r="B458" s="61" t="s">
         <v>916</v>
       </c>
@@ -28657,7 +28657,7 @@
       <c r="S458" s="62"/>
     </row>
     <row r="459" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A459" s="116"/>
+      <c r="A459" s="120"/>
       <c r="B459" s="112" t="s">
         <v>916</v>
       </c>
@@ -28703,7 +28703,7 @@
       <c r="S459" s="110"/>
     </row>
     <row r="460" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A460" s="116"/>
+      <c r="A460" s="120"/>
       <c r="B460" s="61" t="s">
         <v>916</v>
       </c>
@@ -29074,7 +29074,7 @@
       </c>
     </row>
     <row r="467" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A467" s="126"/>
+      <c r="A467" s="121"/>
       <c r="B467" s="61" t="s">
         <v>933</v>
       </c>
@@ -29123,7 +29123,7 @@
       </c>
     </row>
     <row r="468" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="126"/>
+      <c r="A468" s="121"/>
       <c r="B468" s="61" t="s">
         <v>307</v>
       </c>
@@ -29175,7 +29175,7 @@
       <c r="S468" s="61"/>
     </row>
     <row r="469" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="126"/>
+      <c r="A469" s="121"/>
       <c r="B469" s="61" t="s">
         <v>307</v>
       </c>
@@ -29227,7 +29227,7 @@
       <c r="S469" s="61"/>
     </row>
     <row r="470" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="126"/>
+      <c r="A470" s="121"/>
       <c r="B470" s="61" t="s">
         <v>307</v>
       </c>
@@ -29279,7 +29279,7 @@
       <c r="S470" s="61"/>
     </row>
     <row r="471" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="126"/>
+      <c r="A471" s="121"/>
       <c r="B471" s="61" t="s">
         <v>307</v>
       </c>
@@ -29333,7 +29333,7 @@
       </c>
     </row>
     <row r="472" spans="1:19" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="126"/>
+      <c r="A472" s="121"/>
       <c r="B472" s="61" t="s">
         <v>307</v>
       </c>
@@ -29431,7 +29431,7 @@
       </c>
     </row>
     <row r="474" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="116">
+      <c r="A474" s="120">
         <v>116</v>
       </c>
       <c r="B474" s="61" t="s">
@@ -29443,7 +29443,7 @@
       <c r="D474" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="E474" s="119">
+      <c r="E474" s="138">
         <v>2025003050036</v>
       </c>
       <c r="F474" s="61" t="s">
@@ -29457,14 +29457,14 @@
       </c>
       <c r="I474" s="61"/>
       <c r="J474" s="61"/>
-      <c r="K474" s="115">
+      <c r="K474" s="136">
         <f>+M474</f>
         <v>14202451801</v>
       </c>
-      <c r="L474" s="115">
+      <c r="L474" s="136">
         <v>0</v>
       </c>
-      <c r="M474" s="120">
+      <c r="M474" s="123">
         <v>14202451801</v>
       </c>
       <c r="N474" s="61" t="s">
@@ -29480,12 +29480,12 @@
         <v>538</v>
       </c>
       <c r="R474" s="61"/>
-      <c r="S474" s="117" t="s">
+      <c r="S474" s="125" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="475" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="116"/>
+      <c r="A475" s="120"/>
       <c r="B475" s="61" t="s">
         <v>944</v>
       </c>
@@ -29495,7 +29495,7 @@
       <c r="D475" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="E475" s="119"/>
+      <c r="E475" s="138"/>
       <c r="F475" s="61" t="s">
         <v>160</v>
       </c>
@@ -29507,9 +29507,9 @@
       </c>
       <c r="I475" s="61"/>
       <c r="J475" s="61"/>
-      <c r="K475" s="115"/>
-      <c r="L475" s="115"/>
-      <c r="M475" s="120"/>
+      <c r="K475" s="136"/>
+      <c r="L475" s="136"/>
+      <c r="M475" s="123"/>
       <c r="N475" s="61" t="s">
         <v>35</v>
       </c>
@@ -29523,10 +29523,10 @@
         <v>538</v>
       </c>
       <c r="R475" s="61"/>
-      <c r="S475" s="117"/>
+      <c r="S475" s="125"/>
     </row>
     <row r="476" spans="1:19" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="116"/>
+      <c r="A476" s="120"/>
       <c r="B476" s="61" t="s">
         <v>944</v>
       </c>
@@ -29582,7 +29582,7 @@
       </c>
     </row>
     <row r="477" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A477" s="116"/>
+      <c r="A477" s="120"/>
       <c r="B477" s="61" t="s">
         <v>944</v>
       </c>
@@ -29997,7 +29997,7 @@
       <c r="S484" s="62"/>
     </row>
     <row r="485" spans="1:19" ht="35.25" hidden="1" customHeight="1">
-      <c r="A485" s="116">
+      <c r="A485" s="120">
         <v>121</v>
       </c>
       <c r="B485" s="61" t="s">
@@ -30051,7 +30051,7 @@
       <c r="S485" s="61"/>
     </row>
     <row r="486" spans="1:19" ht="36" hidden="1" customHeight="1">
-      <c r="A486" s="116"/>
+      <c r="A486" s="120"/>
       <c r="B486" s="61" t="s">
         <v>960</v>
       </c>
@@ -30101,7 +30101,7 @@
       </c>
     </row>
     <row r="487" spans="1:19" ht="163.19999999999999" hidden="1">
-      <c r="A487" s="116"/>
+      <c r="A487" s="120"/>
       <c r="B487" s="61" t="s">
         <v>960</v>
       </c>
@@ -30257,7 +30257,7 @@
       <c r="S489" s="61"/>
     </row>
     <row r="490" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A490" s="126"/>
+      <c r="A490" s="121"/>
       <c r="B490" s="61" t="s">
         <v>970</v>
       </c>
@@ -30309,7 +30309,7 @@
       <c r="S490" s="61"/>
     </row>
     <row r="491" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A491" s="126"/>
+      <c r="A491" s="121"/>
       <c r="B491" s="61" t="s">
         <v>970</v>
       </c>
@@ -30361,7 +30361,7 @@
       <c r="S491" s="61"/>
     </row>
     <row r="492" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A492" s="126"/>
+      <c r="A492" s="121"/>
       <c r="B492" s="61" t="s">
         <v>970</v>
       </c>
@@ -30460,7 +30460,7 @@
       <c r="S493" s="61"/>
     </row>
     <row r="494" spans="1:19" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="116">
+      <c r="A494" s="120">
         <v>124</v>
       </c>
       <c r="B494" s="61" t="s">
@@ -30516,7 +30516,7 @@
       </c>
     </row>
     <row r="495" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A495" s="116"/>
+      <c r="A495" s="120"/>
       <c r="B495" s="61" t="s">
         <v>977</v>
       </c>
@@ -30566,7 +30566,7 @@
       </c>
     </row>
     <row r="496" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A496" s="116"/>
+      <c r="A496" s="120"/>
       <c r="B496" s="61" t="s">
         <v>977</v>
       </c>
@@ -30618,7 +30618,7 @@
       </c>
     </row>
     <row r="497" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A497" s="116"/>
+      <c r="A497" s="120"/>
       <c r="B497" s="61" t="s">
         <v>983</v>
       </c>
@@ -30729,7 +30729,7 @@
       </c>
     </row>
     <row r="499" spans="1:19" ht="40.799999999999997" hidden="1">
-      <c r="A499" s="117">
+      <c r="A499" s="125">
         <v>126</v>
       </c>
       <c r="B499" s="61" t="s">
@@ -30788,7 +30788,7 @@
       </c>
     </row>
     <row r="500" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A500" s="117"/>
+      <c r="A500" s="125"/>
       <c r="B500" s="61" t="s">
         <v>984</v>
       </c>
@@ -30837,7 +30837,7 @@
       <c r="S500" s="61"/>
     </row>
     <row r="501" spans="1:19" ht="78" hidden="1" customHeight="1">
-      <c r="A501" s="117"/>
+      <c r="A501" s="125"/>
       <c r="B501" s="61" t="s">
         <v>984</v>
       </c>
@@ -30890,8 +30890,8 @@
         <v>991</v>
       </c>
     </row>
-    <row r="502" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A502" s="116">
+    <row r="502" spans="1:19" ht="81.599999999999994">
+      <c r="A502" s="120">
         <v>127</v>
       </c>
       <c r="B502" s="61" t="s">
@@ -30950,8 +30950,8 @@
         <v>995</v>
       </c>
     </row>
-    <row r="503" spans="1:19" ht="20.399999999999999" hidden="1">
-      <c r="A503" s="116"/>
+    <row r="503" spans="1:19" ht="20.399999999999999">
+      <c r="A503" s="120"/>
       <c r="B503" s="61" t="s">
         <v>992</v>
       </c>
@@ -31006,8 +31006,8 @@
       </c>
       <c r="S503" s="61"/>
     </row>
-    <row r="504" spans="1:19" ht="81.599999999999994" hidden="1">
-      <c r="A504" s="116"/>
+    <row r="504" spans="1:19" ht="81.599999999999994">
+      <c r="A504" s="120"/>
       <c r="B504" s="93" t="s">
         <v>992</v>
       </c>
@@ -31130,37 +31130,114 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:S506" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-    <filterColumn colId="3">
+    <filterColumn colId="2">
       <filters>
-        <filter val="RVT"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="Regalías"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="15">
-      <filters>
-        <filter val="2024"/>
-        <filter val="2025"/>
-        <filter val="2026"/>
+        <filter val="Bajo Cauca"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A407:A410"/>
-    <mergeCell ref="A411:A415"/>
-    <mergeCell ref="A416:A423"/>
-    <mergeCell ref="A426:A432"/>
-    <mergeCell ref="A433:A438"/>
-    <mergeCell ref="K433:K434"/>
-    <mergeCell ref="R433:R434"/>
-    <mergeCell ref="L433:L434"/>
-    <mergeCell ref="M433:M434"/>
-    <mergeCell ref="N433:N434"/>
-    <mergeCell ref="O433:O434"/>
-    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="R91:R92"/>
+    <mergeCell ref="E474:E475"/>
+    <mergeCell ref="S91:S92"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="M474:M475"/>
+    <mergeCell ref="K474:K475"/>
+    <mergeCell ref="L474:L475"/>
+    <mergeCell ref="S474:S475"/>
+    <mergeCell ref="S433:S434"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="H311:H312"/>
+    <mergeCell ref="J309:J310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="I311:I312"/>
+    <mergeCell ref="J311:J312"/>
+    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A116"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A190:A192"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A152:A163"/>
+    <mergeCell ref="A213:A217"/>
+    <mergeCell ref="A222:A227"/>
+    <mergeCell ref="A234:A239"/>
+    <mergeCell ref="A240:A246"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A254:A259"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A294:A296"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A304:A307"/>
+    <mergeCell ref="F309:F310"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A275"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A284:A292"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A399:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="P309:P310"/>
+    <mergeCell ref="S309:S310"/>
+    <mergeCell ref="R309:R310"/>
+    <mergeCell ref="A310:A315"/>
+    <mergeCell ref="F311:F312"/>
+    <mergeCell ref="G311:G312"/>
+    <mergeCell ref="K311:K312"/>
+    <mergeCell ref="L311:L312"/>
+    <mergeCell ref="M311:M312"/>
+    <mergeCell ref="N311:N312"/>
+    <mergeCell ref="G309:G310"/>
+    <mergeCell ref="K309:K310"/>
+    <mergeCell ref="L309:L310"/>
+    <mergeCell ref="M309:M310"/>
+    <mergeCell ref="N309:N310"/>
+    <mergeCell ref="O309:O310"/>
+    <mergeCell ref="Q309:Q310"/>
+    <mergeCell ref="Q311:Q312"/>
+    <mergeCell ref="O311:O312"/>
+    <mergeCell ref="P311:P312"/>
+    <mergeCell ref="S311:S312"/>
+    <mergeCell ref="R311:R312"/>
     <mergeCell ref="A318:A319"/>
     <mergeCell ref="A320:A329"/>
     <mergeCell ref="A334:A337"/>
@@ -31185,107 +31262,18 @@
     <mergeCell ref="A372:A383"/>
     <mergeCell ref="A384:A391"/>
     <mergeCell ref="A393:A398"/>
-    <mergeCell ref="A399:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="P309:P310"/>
-    <mergeCell ref="S309:S310"/>
-    <mergeCell ref="R309:R310"/>
-    <mergeCell ref="A310:A315"/>
-    <mergeCell ref="F311:F312"/>
-    <mergeCell ref="G311:G312"/>
-    <mergeCell ref="K311:K312"/>
-    <mergeCell ref="L311:L312"/>
-    <mergeCell ref="M311:M312"/>
-    <mergeCell ref="N311:N312"/>
-    <mergeCell ref="G309:G310"/>
-    <mergeCell ref="K309:K310"/>
-    <mergeCell ref="L309:L310"/>
-    <mergeCell ref="M309:M310"/>
-    <mergeCell ref="N309:N310"/>
-    <mergeCell ref="O309:O310"/>
-    <mergeCell ref="Q309:Q310"/>
-    <mergeCell ref="Q311:Q312"/>
-    <mergeCell ref="O311:O312"/>
-    <mergeCell ref="P311:P312"/>
-    <mergeCell ref="S311:S312"/>
-    <mergeCell ref="R311:R312"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A304:A307"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A275"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A284:A292"/>
-    <mergeCell ref="E309:E310"/>
-    <mergeCell ref="A213:A217"/>
-    <mergeCell ref="A222:A227"/>
-    <mergeCell ref="A234:A239"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A254:A259"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A208:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A152:A163"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="R91:R92"/>
-    <mergeCell ref="E474:E475"/>
-    <mergeCell ref="S91:S92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="M474:M475"/>
-    <mergeCell ref="K474:K475"/>
-    <mergeCell ref="L474:L475"/>
-    <mergeCell ref="S474:S475"/>
-    <mergeCell ref="S433:S434"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="H311:H312"/>
-    <mergeCell ref="J309:J310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="I311:I312"/>
-    <mergeCell ref="J311:J312"/>
-    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="A407:A410"/>
+    <mergeCell ref="A411:A415"/>
+    <mergeCell ref="A416:A423"/>
+    <mergeCell ref="A426:A432"/>
+    <mergeCell ref="A433:A438"/>
+    <mergeCell ref="K433:K434"/>
+    <mergeCell ref="R433:R434"/>
+    <mergeCell ref="L433:L434"/>
+    <mergeCell ref="M433:M434"/>
+    <mergeCell ref="N433:N434"/>
+    <mergeCell ref="O433:O434"/>
+    <mergeCell ref="P433:P434"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -31316,10 +31304,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="40.799999999999997">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="139" t="s">
         <v>1000</v>
       </c>
-      <c r="C2" s="134"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="28" t="s">
         <v>1001</v>
       </c>
@@ -31526,23 +31514,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -31698,25 +31669,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31732,4 +31702,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB4FBCE6-6A7E-4696-B65B-DE2BB4BDEE17}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B7762D2-9A41-41B1-81EE-84F87E8850C5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4008" yWindow="4008" windowWidth="14184" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4696" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="1069">
   <si>
     <t>PROYECTOS SIF</t>
   </si>
@@ -3991,6 +3991,18 @@
       </rPr>
       <t>(Obra e interventoría )</t>
     </r>
+  </si>
+  <si>
+    <t>26OO111B2810</t>
+  </si>
+  <si>
+    <t>25OO111B2446</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Liborina - Partidas San Jose de la Montaña: L=2,00 km</t>
+  </si>
+  <si>
+    <t>23OO111B1477</t>
   </si>
 </sst>
 </file>
@@ -4227,7 +4239,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4491,40 +4503,31 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4539,20 +4542,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4577,10 +4601,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4909,10 +4929,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="101"/>
+      <c r="C1" s="108"/>
       <c r="D1" s="87"/>
       <c r="E1" s="37"/>
       <c r="F1" s="87"/>
@@ -4989,7 +5009,7 @@
       <c r="U2" s="14"/>
     </row>
     <row r="3" spans="1:21" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="98">
+      <c r="A3" s="95">
         <v>1</v>
       </c>
       <c r="B3" s="77" t="s">
@@ -5050,7 +5070,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
+      <c r="A4" s="95"/>
       <c r="B4" s="80" t="s">
         <v>19</v>
       </c>
@@ -5108,8 +5128,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="98"/>
+    <row r="5" spans="1:21" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="95"/>
       <c r="B5" s="81" t="s">
         <v>19</v>
       </c>
@@ -5162,7 +5182,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A6" s="81"/>
       <c r="B6" s="80" t="s">
         <v>38</v>
@@ -5213,7 +5233,7 @@
       <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="97">
+      <c r="A7" s="99">
         <v>2</v>
       </c>
       <c r="B7" s="80" t="s">
@@ -5246,7 +5266,7 @@
       <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="102"/>
+      <c r="A8" s="94"/>
       <c r="B8" s="80" t="s">
         <v>38</v>
       </c>
@@ -5296,7 +5316,7 @@
       <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="102"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="80" t="s">
         <v>38</v>
       </c>
@@ -5352,7 +5372,7 @@
       <c r="S9" s="75"/>
     </row>
     <row r="10" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="75" t="s">
         <v>38</v>
       </c>
@@ -5408,7 +5428,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92">
+      <c r="A11" s="93">
         <v>3</v>
       </c>
       <c r="B11" s="86" t="s">
@@ -5469,7 +5489,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="52.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="92"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="80" t="s">
         <v>56</v>
       </c>
@@ -5523,7 +5543,7 @@
       <c r="S12" s="85"/>
     </row>
     <row r="13" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="92"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="80" t="s">
         <v>56</v>
       </c>
@@ -5577,7 +5597,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="92"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="80" t="s">
         <v>56</v>
       </c>
@@ -5630,8 +5650,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="92"/>
+    <row r="15" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="93"/>
       <c r="B15" s="80" t="s">
         <v>56</v>
       </c>
@@ -5685,7 +5705,7 @@
       <c r="S15" s="75"/>
     </row>
     <row r="16" spans="1:21" ht="66.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="92"/>
+      <c r="A16" s="93"/>
       <c r="B16" s="80" t="s">
         <v>56</v>
       </c>
@@ -5777,7 +5797,7 @@
       <c r="R17" s="89"/>
       <c r="S17" s="80"/>
     </row>
-    <row r="18" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="75">
         <v>4</v>
       </c>
@@ -5835,7 +5855,7 @@
       </c>
       <c r="S18" s="80"/>
     </row>
-    <row r="19" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A19" s="75"/>
       <c r="B19" s="80" t="s">
         <v>89</v>
@@ -5894,7 +5914,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="97.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92">
+      <c r="A20" s="93">
         <v>5</v>
       </c>
       <c r="B20" s="80" t="s">
@@ -5954,7 +5974,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
+      <c r="A21" s="93"/>
       <c r="B21" s="80" t="s">
         <v>89</v>
       </c>
@@ -6010,7 +6030,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
+      <c r="A22" s="93"/>
       <c r="B22" s="80" t="s">
         <v>89</v>
       </c>
@@ -6066,8 +6086,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
+    <row r="23" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A23" s="93"/>
       <c r="B23" s="80" t="s">
         <v>89</v>
       </c>
@@ -6122,7 +6142,7 @@
       <c r="S23" s="80"/>
     </row>
     <row r="24" spans="1:19" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92">
+      <c r="A24" s="93">
         <v>6</v>
       </c>
       <c r="B24" s="80" t="s">
@@ -6181,7 +6201,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="80" t="s">
         <v>106</v>
       </c>
@@ -6235,7 +6255,7 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
+      <c r="A26" s="93"/>
       <c r="B26" s="80" t="s">
         <v>106</v>
       </c>
@@ -6288,8 +6308,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
+    <row r="27" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="93"/>
       <c r="B27" s="80" t="s">
         <v>106</v>
       </c>
@@ -6345,7 +6365,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="92"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="80" t="s">
         <v>106</v>
       </c>
@@ -6397,7 +6417,7 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="92"/>
+      <c r="A29" s="93"/>
       <c r="B29" s="80" t="s">
         <v>106</v>
       </c>
@@ -6451,7 +6471,7 @@
       </c>
     </row>
     <row r="30" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="92"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="80" t="s">
         <v>106</v>
       </c>
@@ -6501,7 +6521,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92"/>
+      <c r="A31" s="93"/>
       <c r="B31" s="80" t="s">
         <v>106</v>
       </c>
@@ -6557,7 +6577,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+      <c r="A32" s="93"/>
       <c r="B32" s="80" t="s">
         <v>106</v>
       </c>
@@ -6615,7 +6635,7 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
+      <c r="A33" s="93"/>
       <c r="B33" s="80" t="s">
         <v>106</v>
       </c>
@@ -6668,8 +6688,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
+    <row r="34" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="93"/>
       <c r="B34" s="80" t="s">
         <v>106</v>
       </c>
@@ -6727,7 +6747,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="102"/>
+      <c r="A35" s="94"/>
       <c r="B35" s="80" t="s">
         <v>144</v>
       </c>
@@ -6760,7 +6780,7 @@
       <c r="S35" s="80"/>
     </row>
     <row r="36" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="98"/>
+      <c r="A36" s="95"/>
       <c r="B36" s="80" t="s">
         <v>144</v>
       </c>
@@ -6868,7 +6888,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92">
+      <c r="A38" s="93">
         <v>8</v>
       </c>
       <c r="B38" s="80" t="s">
@@ -6926,8 +6946,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="93"/>
       <c r="B39" s="80" t="s">
         <v>147</v>
       </c>
@@ -6985,7 +7005,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="92"/>
+      <c r="A40" s="93"/>
       <c r="B40" s="80" t="s">
         <v>147</v>
       </c>
@@ -7039,8 +7059,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="92">
+    <row r="41" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="93">
         <v>9</v>
       </c>
       <c r="B41" s="80" t="s">
@@ -7098,7 +7118,7 @@
       <c r="S41" s="80"/>
     </row>
     <row r="42" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="92"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="80" t="s">
         <v>157</v>
       </c>
@@ -7145,7 +7165,7 @@
       </c>
     </row>
     <row r="43" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="92"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="80" t="s">
         <v>157</v>
       </c>
@@ -7194,7 +7214,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="92"/>
+      <c r="A44" s="93"/>
       <c r="B44" s="80" t="s">
         <v>157</v>
       </c>
@@ -7240,7 +7260,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="92"/>
+      <c r="A45" s="93"/>
       <c r="B45" s="80" t="s">
         <v>157</v>
       </c>
@@ -7293,8 +7313,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="92">
+    <row r="46" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="93">
         <v>10</v>
       </c>
       <c r="B46" s="80" t="s">
@@ -7348,7 +7368,7 @@
       </c>
     </row>
     <row r="47" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="97"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="80" t="s">
         <v>172</v>
       </c>
@@ -7400,7 +7420,7 @@
       <c r="S47" s="80"/>
     </row>
     <row r="48" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="92"/>
+      <c r="A48" s="93"/>
       <c r="B48" s="80" t="s">
         <v>179</v>
       </c>
@@ -7433,7 +7453,7 @@
       <c r="S48" s="80"/>
     </row>
     <row r="49" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="92"/>
+      <c r="A49" s="93"/>
       <c r="B49" s="80" t="s">
         <v>179</v>
       </c>
@@ -7469,8 +7489,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="92"/>
+    <row r="50" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="93"/>
       <c r="B50" s="80" t="s">
         <v>179</v>
       </c>
@@ -7480,7 +7500,9 @@
       <c r="D50" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="E50" s="90"/>
+      <c r="E50" s="90">
+        <v>2022050450076</v>
+      </c>
       <c r="F50" s="80" t="s">
         <v>184</v>
       </c>
@@ -7519,8 +7541,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="92"/>
+    <row r="51" spans="1:19" ht="102" x14ac:dyDescent="0.3">
+      <c r="A51" s="93"/>
       <c r="B51" s="80" t="s">
         <v>179</v>
       </c>
@@ -7571,8 +7593,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
+    <row r="52" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="93"/>
       <c r="B52" s="80" t="s">
         <v>179</v>
       </c>
@@ -7624,7 +7646,7 @@
       </c>
     </row>
     <row r="53" spans="1:19" ht="45.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
+      <c r="A53" s="93"/>
       <c r="B53" s="80" t="s">
         <v>179</v>
       </c>
@@ -7675,8 +7697,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
+    <row r="54" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="93"/>
       <c r="B54" s="80" t="s">
         <v>194</v>
       </c>
@@ -7727,7 +7749,7 @@
       </c>
     </row>
     <row r="55" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="92"/>
+      <c r="A55" s="93"/>
       <c r="B55" s="80" t="s">
         <v>194</v>
       </c>
@@ -7778,8 +7800,8 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
+    <row r="56" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="93"/>
       <c r="B56" s="80" t="s">
         <v>194</v>
       </c>
@@ -7835,7 +7857,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
+      <c r="A57" s="93"/>
       <c r="B57" s="80" t="s">
         <v>194</v>
       </c>
@@ -7889,7 +7911,7 @@
       <c r="S57" s="80"/>
     </row>
     <row r="58" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
+      <c r="A58" s="93"/>
       <c r="B58" s="80" t="s">
         <v>194</v>
       </c>
@@ -7946,7 +7968,7 @@
       </c>
     </row>
     <row r="59" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="98"/>
+      <c r="A59" s="95"/>
       <c r="B59" s="80" t="s">
         <v>206</v>
       </c>
@@ -7999,8 +8021,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="98"/>
+    <row r="60" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="95"/>
       <c r="B60" s="80" t="s">
         <v>206</v>
       </c>
@@ -8052,8 +8074,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
+    <row r="61" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="93"/>
       <c r="B61" s="70" t="s">
         <v>206</v>
       </c>
@@ -8104,7 +8126,7 @@
       </c>
     </row>
     <row r="62" spans="1:19" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="97">
+      <c r="A62" s="99">
         <v>14</v>
       </c>
       <c r="B62" s="80" t="s">
@@ -8158,8 +8180,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="102"/>
+    <row r="63" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="94"/>
       <c r="B63" s="80" t="s">
         <v>212</v>
       </c>
@@ -8213,7 +8235,7 @@
       </c>
     </row>
     <row r="64" spans="1:19" ht="107.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="98"/>
+      <c r="A64" s="95"/>
       <c r="B64" s="80" t="s">
         <v>212</v>
       </c>
@@ -8369,7 +8391,7 @@
       </c>
     </row>
     <row r="67" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="97">
+      <c r="A67" s="99">
         <v>16</v>
       </c>
       <c r="B67" s="80" t="s">
@@ -8422,7 +8444,7 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="98"/>
+      <c r="A68" s="95"/>
       <c r="B68" s="80" t="s">
         <v>227</v>
       </c>
@@ -8472,7 +8494,7 @@
       </c>
     </row>
     <row r="69" spans="1:19" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="97">
+      <c r="A69" s="99">
         <v>17</v>
       </c>
       <c r="B69" s="80" t="s">
@@ -8525,7 +8547,7 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="102"/>
+      <c r="A70" s="94"/>
       <c r="B70" s="80" t="s">
         <v>233</v>
       </c>
@@ -8576,8 +8598,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="67.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="102"/>
+    <row r="71" spans="1:19" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="94"/>
       <c r="B71" s="80" t="s">
         <v>239</v>
       </c>
@@ -8629,7 +8651,7 @@
       </c>
     </row>
     <row r="72" spans="1:19" ht="174.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="102"/>
+      <c r="A72" s="94"/>
       <c r="B72" s="80" t="s">
         <v>242</v>
       </c>
@@ -8681,8 +8703,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="102"/>
+    <row r="73" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="94"/>
       <c r="B73" s="80" t="s">
         <v>242</v>
       </c>
@@ -8692,7 +8714,9 @@
       <c r="D73" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E73" s="90"/>
+      <c r="E73" s="90" t="s">
+        <v>61</v>
+      </c>
       <c r="F73" s="80" t="s">
         <v>174</v>
       </c>
@@ -8730,7 +8754,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="102"/>
+      <c r="A74" s="94"/>
       <c r="B74" s="80" t="s">
         <v>242</v>
       </c>
@@ -8782,7 +8806,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="102"/>
+      <c r="A75" s="94"/>
       <c r="B75" s="80" t="s">
         <v>242</v>
       </c>
@@ -8839,8 +8863,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="102"/>
+    <row r="76" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="94"/>
       <c r="B76" s="80" t="s">
         <v>242</v>
       </c>
@@ -8890,7 +8914,7 @@
       <c r="S76" s="80"/>
     </row>
     <row r="77" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="98"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="80" t="s">
         <v>242</v>
       </c>
@@ -8944,7 +8968,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="102"/>
+      <c r="A78" s="94"/>
       <c r="B78" s="80" t="s">
         <v>253</v>
       </c>
@@ -9002,7 +9026,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="102"/>
+      <c r="A79" s="94"/>
       <c r="B79" s="80" t="s">
         <v>253</v>
       </c>
@@ -9054,7 +9078,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="102"/>
+      <c r="A80" s="94"/>
       <c r="B80" s="80" t="s">
         <v>253</v>
       </c>
@@ -9106,7 +9130,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="1:20" ht="150.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="102"/>
+      <c r="A81" s="94"/>
       <c r="B81" s="80" t="s">
         <v>253</v>
       </c>
@@ -9159,7 +9183,7 @@
       </c>
     </row>
     <row r="82" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="102"/>
+      <c r="A82" s="94"/>
       <c r="B82" s="80" t="s">
         <v>262</v>
       </c>
@@ -9213,8 +9237,8 @@
       </c>
       <c r="T82" s="36"/>
     </row>
-    <row r="83" spans="1:20" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="102"/>
+    <row r="83" spans="1:20" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="94"/>
       <c r="B83" s="80" t="s">
         <v>262</v>
       </c>
@@ -9265,8 +9289,8 @@
       </c>
       <c r="T83" s="36"/>
     </row>
-    <row r="84" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="102"/>
+    <row r="84" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A84" s="94"/>
       <c r="B84" s="80" t="s">
         <v>262</v>
       </c>
@@ -9317,8 +9341,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="102"/>
+    <row r="85" spans="1:20" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A85" s="94"/>
       <c r="B85" s="80" t="s">
         <v>262</v>
       </c>
@@ -9369,7 +9393,7 @@
       <c r="T85" s="36"/>
     </row>
     <row r="86" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="102"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="80" t="s">
         <v>262</v>
       </c>
@@ -9424,7 +9448,7 @@
       <c r="T86" s="36"/>
     </row>
     <row r="87" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="102"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="80" t="s">
         <v>262</v>
       </c>
@@ -9478,8 +9502,8 @@
       </c>
       <c r="T87" s="36"/>
     </row>
-    <row r="88" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="102"/>
+    <row r="88" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A88" s="94"/>
       <c r="B88" s="80" t="s">
         <v>262</v>
       </c>
@@ -9533,8 +9557,8 @@
       </c>
       <c r="T88" s="36"/>
     </row>
-    <row r="89" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="102"/>
+    <row r="89" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A89" s="94"/>
       <c r="B89" s="80" t="s">
         <v>262</v>
       </c>
@@ -9587,7 +9611,7 @@
       <c r="T89" s="36"/>
     </row>
     <row r="90" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="102"/>
+      <c r="A90" s="94"/>
       <c r="B90" s="75" t="s">
         <v>262</v>
       </c>
@@ -9633,8 +9657,8 @@
       </c>
       <c r="T90" s="36"/>
     </row>
-    <row r="91" spans="1:20" ht="43.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="102"/>
+    <row r="91" spans="1:20" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="94"/>
       <c r="B91" s="80" t="s">
         <v>282</v>
       </c>
@@ -9644,8 +9668,8 @@
       <c r="D91" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E91" s="90" t="s">
-        <v>61</v>
+      <c r="E91" s="90">
+        <v>2026003050020</v>
       </c>
       <c r="F91" s="80" t="s">
         <v>283</v>
@@ -9658,38 +9682,38 @@
       </c>
       <c r="I91" s="80"/>
       <c r="J91" s="80"/>
-      <c r="K91" s="91">
-        <v>4572000000</v>
-      </c>
-      <c r="L91" s="91">
+      <c r="K91" s="113">
+        <v>12438994717</v>
+      </c>
+      <c r="L91" s="113">
         <v>0</v>
       </c>
-      <c r="M91" s="91">
+      <c r="M91" s="113">
         <f>+K91</f>
-        <v>4572000000</v>
-      </c>
-      <c r="N91" s="92" t="s">
+        <v>12438994717</v>
+      </c>
+      <c r="N91" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="92" t="s">
+      <c r="O91" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="P91" s="92">
+      <c r="P91" s="93">
         <v>2026</v>
       </c>
-      <c r="Q91" s="93" t="s">
+      <c r="Q91" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="R91" s="94">
+      <c r="R91" s="110">
         <v>0</v>
       </c>
-      <c r="S91" s="93" t="s">
+      <c r="S91" s="98" t="s">
         <v>285</v>
       </c>
       <c r="T91" s="36"/>
     </row>
-    <row r="92" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="102"/>
+    <row r="92" spans="1:20" ht="40.799999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="94"/>
       <c r="B92" s="80" t="s">
         <v>282</v>
       </c>
@@ -9713,18 +9737,18 @@
       </c>
       <c r="I92" s="80"/>
       <c r="J92" s="80"/>
-      <c r="K92" s="91"/>
-      <c r="L92" s="91"/>
-      <c r="M92" s="91"/>
-      <c r="N92" s="92"/>
-      <c r="O92" s="92"/>
-      <c r="P92" s="92"/>
-      <c r="Q92" s="93"/>
-      <c r="R92" s="94"/>
-      <c r="S92" s="93"/>
+      <c r="K92" s="114"/>
+      <c r="L92" s="114"/>
+      <c r="M92" s="114"/>
+      <c r="N92" s="93"/>
+      <c r="O92" s="93"/>
+      <c r="P92" s="93"/>
+      <c r="Q92" s="98"/>
+      <c r="R92" s="110"/>
+      <c r="S92" s="98"/>
     </row>
     <row r="93" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="102"/>
+      <c r="A93" s="94"/>
       <c r="B93" s="80" t="s">
         <v>282</v>
       </c>
@@ -9748,16 +9772,9 @@
       </c>
       <c r="I93" s="80"/>
       <c r="J93" s="80"/>
-      <c r="K93" s="88">
-        <v>2400000000</v>
-      </c>
-      <c r="L93" s="88">
-        <v>1200000000</v>
-      </c>
-      <c r="M93" s="88">
-        <f>+K93+L93</f>
-        <v>3600000000</v>
-      </c>
+      <c r="K93" s="114"/>
+      <c r="L93" s="114"/>
+      <c r="M93" s="114"/>
       <c r="N93" s="75" t="s">
         <v>26</v>
       </c>
@@ -9778,7 +9795,7 @@
       </c>
     </row>
     <row r="94" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="102"/>
+      <c r="A94" s="94"/>
       <c r="B94" s="80" t="s">
         <v>282</v>
       </c>
@@ -9800,16 +9817,9 @@
       </c>
       <c r="I94" s="80"/>
       <c r="J94" s="80"/>
-      <c r="K94" s="3">
-        <v>35050287</v>
-      </c>
-      <c r="L94" s="88">
-        <v>0</v>
-      </c>
-      <c r="M94" s="88">
-        <f>+K94</f>
-        <v>35050287</v>
-      </c>
+      <c r="K94" s="114"/>
+      <c r="L94" s="114"/>
+      <c r="M94" s="114"/>
       <c r="N94" s="75" t="s">
         <v>26</v>
       </c>
@@ -9829,8 +9839,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="102"/>
+    <row r="95" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="94"/>
       <c r="B95" s="80" t="s">
         <v>282</v>
       </c>
@@ -9854,15 +9864,9 @@
       </c>
       <c r="I95" s="75"/>
       <c r="J95" s="75"/>
-      <c r="K95" s="78">
-        <v>285851423</v>
-      </c>
-      <c r="L95" s="78">
-        <v>552538529</v>
-      </c>
-      <c r="M95" s="2">
-        <v>1023389952</v>
-      </c>
+      <c r="K95" s="114"/>
+      <c r="L95" s="114"/>
+      <c r="M95" s="114"/>
       <c r="N95" s="75" t="s">
         <v>146</v>
       </c>
@@ -9882,8 +9886,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="102"/>
+    <row r="96" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="94"/>
       <c r="B96" s="80" t="s">
         <v>290</v>
       </c>
@@ -9911,17 +9915,9 @@
       <c r="J96" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="K96" s="2">
-        <f>'Estabilización datos '!G9*25</f>
-        <v>28216418691.000004</v>
-      </c>
-      <c r="L96" s="78">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2">
-        <f>+K96</f>
-        <v>28216418691.000004</v>
-      </c>
+      <c r="K96" s="114"/>
+      <c r="L96" s="114"/>
+      <c r="M96" s="114"/>
       <c r="N96" s="75" t="s">
         <v>26</v>
       </c>
@@ -9940,7 +9936,7 @@
       </c>
     </row>
     <row r="97" spans="1:19" ht="99.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="102"/>
+      <c r="A97" s="94"/>
       <c r="B97" s="80" t="s">
         <v>290</v>
       </c>
@@ -9968,16 +9964,9 @@
       <c r="J97" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="K97" s="2">
-        <f>+M97</f>
-        <v>18346622061</v>
-      </c>
-      <c r="L97" s="78">
-        <v>0</v>
-      </c>
-      <c r="M97" s="78">
-        <v>18346622061</v>
-      </c>
+      <c r="K97" s="114"/>
+      <c r="L97" s="114"/>
+      <c r="M97" s="114"/>
       <c r="N97" s="75" t="s">
         <v>98</v>
       </c>
@@ -9998,7 +9987,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="102"/>
+      <c r="A98" s="94"/>
       <c r="B98" s="80" t="s">
         <v>299</v>
       </c>
@@ -10022,16 +10011,9 @@
       </c>
       <c r="I98" s="75"/>
       <c r="J98" s="75"/>
-      <c r="K98" s="2">
-        <v>350000000</v>
-      </c>
-      <c r="L98" s="2">
-        <v>463793974</v>
-      </c>
-      <c r="M98" s="78">
-        <f>+K98+L98</f>
-        <v>813793974</v>
-      </c>
+      <c r="K98" s="114"/>
+      <c r="L98" s="114"/>
+      <c r="M98" s="114"/>
       <c r="N98" s="75" t="s">
         <v>146</v>
       </c>
@@ -10052,7 +10034,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="102"/>
+      <c r="A99" s="94"/>
       <c r="B99" s="80" t="s">
         <v>299</v>
       </c>
@@ -10076,16 +10058,9 @@
       </c>
       <c r="I99" s="75"/>
       <c r="J99" s="75"/>
-      <c r="K99" s="2">
-        <v>70000000</v>
-      </c>
-      <c r="L99" s="2">
-        <v>124517130</v>
-      </c>
-      <c r="M99" s="78">
-        <f>+K99+L99</f>
-        <v>194517130</v>
-      </c>
+      <c r="K99" s="114"/>
+      <c r="L99" s="114"/>
+      <c r="M99" s="114"/>
       <c r="N99" s="75" t="s">
         <v>72</v>
       </c>
@@ -10105,8 +10080,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="102"/>
+    <row r="100" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="94"/>
       <c r="B100" s="80" t="s">
         <v>299</v>
       </c>
@@ -10116,8 +10091,8 @@
       <c r="D100" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E100" s="90" t="s">
-        <v>61</v>
+      <c r="E100" s="90">
+        <v>2026003050020</v>
       </c>
       <c r="F100" s="75" t="s">
         <v>301</v>
@@ -10130,16 +10105,9 @@
       </c>
       <c r="I100" s="80"/>
       <c r="J100" s="80"/>
-      <c r="K100" s="2">
-        <v>5847441427</v>
-      </c>
-      <c r="L100" s="78">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2">
-        <f>+K100</f>
-        <v>5847441427</v>
-      </c>
+      <c r="K100" s="115"/>
+      <c r="L100" s="115"/>
+      <c r="M100" s="115"/>
       <c r="N100" s="75" t="s">
         <v>35</v>
       </c>
@@ -10160,7 +10128,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="102"/>
+      <c r="A101" s="94"/>
       <c r="B101" s="80" t="s">
         <v>299</v>
       </c>
@@ -10214,7 +10182,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="102"/>
+      <c r="A102" s="94"/>
       <c r="B102" s="80" t="s">
         <v>299</v>
       </c>
@@ -10262,8 +10230,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="102"/>
+    <row r="103" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="94"/>
       <c r="B103" s="80" t="s">
         <v>299</v>
       </c>
@@ -10312,8 +10280,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="102"/>
+    <row r="104" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="94"/>
       <c r="B104" s="80" t="s">
         <v>299</v>
       </c>
@@ -10365,7 +10333,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="1:19" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="102"/>
+      <c r="A105" s="94"/>
       <c r="B105" s="80" t="s">
         <v>299</v>
       </c>
@@ -10416,8 +10384,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="102"/>
+    <row r="106" spans="1:19" ht="142.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A106" s="94"/>
       <c r="B106" s="80" t="s">
         <v>311</v>
       </c>
@@ -10466,7 +10434,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="102"/>
+      <c r="A107" s="94"/>
       <c r="B107" s="80" t="s">
         <v>317</v>
       </c>
@@ -10508,8 +10476,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="102"/>
+    <row r="108" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A108" s="94"/>
       <c r="B108" s="80" t="s">
         <v>317</v>
       </c>
@@ -10559,7 +10527,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="102"/>
+      <c r="A109" s="94"/>
       <c r="B109" s="80" t="s">
         <v>317</v>
       </c>
@@ -10610,8 +10578,8 @@
       </c>
       <c r="S109" s="80"/>
     </row>
-    <row r="110" spans="1:19" ht="60.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="102"/>
+    <row r="110" spans="1:19" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="94"/>
       <c r="B110" s="80" t="s">
         <v>322</v>
       </c>
@@ -10667,7 +10635,7 @@
       <c r="S110" s="80"/>
     </row>
     <row r="111" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="102"/>
+      <c r="A111" s="94"/>
       <c r="B111" s="80" t="s">
         <v>324</v>
       </c>
@@ -10717,7 +10685,7 @@
       </c>
     </row>
     <row r="112" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="102"/>
+      <c r="A112" s="94"/>
       <c r="B112" s="80" t="s">
         <v>324</v>
       </c>
@@ -10767,7 +10735,7 @@
       </c>
     </row>
     <row r="113" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="102"/>
+      <c r="A113" s="94"/>
       <c r="B113" s="80" t="s">
         <v>324</v>
       </c>
@@ -10806,7 +10774,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="22.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="102"/>
+      <c r="A114" s="94"/>
       <c r="B114" s="80" t="s">
         <v>324</v>
       </c>
@@ -10859,8 +10827,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="102"/>
+    <row r="115" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="94"/>
       <c r="B115" s="80" t="s">
         <v>334</v>
       </c>
@@ -10917,8 +10885,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="98"/>
+    <row r="116" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A116" s="95"/>
       <c r="B116" s="80" t="s">
         <v>339</v>
       </c>
@@ -10971,7 +10939,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A117" s="81">
         <v>29</v>
       </c>
@@ -11026,7 +10994,7 @@
       <c r="S117" s="80"/>
     </row>
     <row r="118" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="92">
+      <c r="A118" s="93">
         <v>30</v>
       </c>
       <c r="B118" s="80" t="s">
@@ -11078,7 +11046,7 @@
       <c r="S118" s="80"/>
     </row>
     <row r="119" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="92"/>
+      <c r="A119" s="93"/>
       <c r="B119" s="80" t="s">
         <v>344</v>
       </c>
@@ -11183,7 +11151,7 @@
       </c>
     </row>
     <row r="121" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="93"/>
+      <c r="A121" s="98"/>
       <c r="B121" s="80" t="s">
         <v>347</v>
       </c>
@@ -11233,8 +11201,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="93"/>
+    <row r="122" spans="1:19" ht="142.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="98"/>
       <c r="B122" s="80" t="s">
         <v>347</v>
       </c>
@@ -11285,8 +11253,8 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="93"/>
+    <row r="123" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A123" s="98"/>
       <c r="B123" s="80" t="s">
         <v>347</v>
       </c>
@@ -11389,7 +11357,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A125" s="75"/>
       <c r="B125" s="80" t="s">
         <v>356</v>
@@ -11441,7 +11409,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A126" s="75"/>
       <c r="B126" s="80" t="s">
         <v>356</v>
@@ -11544,7 +11512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="77"/>
       <c r="B128" s="80" t="s">
         <v>366</v>
@@ -11650,7 +11618,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="77"/>
       <c r="B130" s="80" t="s">
         <v>371</v>
@@ -11755,7 +11723,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="92">
+      <c r="A132" s="93">
         <v>35</v>
       </c>
       <c r="B132" s="80" t="s">
@@ -11811,7 +11779,7 @@
       </c>
     </row>
     <row r="133" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="92"/>
+      <c r="A133" s="93"/>
       <c r="B133" s="80" t="s">
         <v>371</v>
       </c>
@@ -11863,7 +11831,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="92"/>
+      <c r="A134" s="93"/>
       <c r="B134" s="80" t="s">
         <v>371</v>
       </c>
@@ -11920,8 +11888,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="92"/>
+    <row r="135" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A135" s="93"/>
       <c r="B135" s="80" t="s">
         <v>371</v>
       </c>
@@ -12030,7 +11998,7 @@
       <c r="S136" s="80"/>
     </row>
     <row r="137" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="92">
+      <c r="A137" s="93">
         <v>36</v>
       </c>
       <c r="B137" s="80" t="s">
@@ -12084,7 +12052,7 @@
       <c r="S137" s="80"/>
     </row>
     <row r="138" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="92"/>
+      <c r="A138" s="93"/>
       <c r="B138" s="80" t="s">
         <v>380</v>
       </c>
@@ -12136,7 +12104,7 @@
       <c r="S138" s="80"/>
     </row>
     <row r="139" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="92"/>
+      <c r="A139" s="93"/>
       <c r="B139" s="80" t="s">
         <v>380</v>
       </c>
@@ -12188,7 +12156,7 @@
       <c r="S139" s="80"/>
     </row>
     <row r="140" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="92"/>
+      <c r="A140" s="93"/>
       <c r="B140" s="80" t="s">
         <v>380</v>
       </c>
@@ -12239,7 +12207,7 @@
       <c r="S140" s="80"/>
     </row>
     <row r="141" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="92"/>
+      <c r="A141" s="93"/>
       <c r="B141" s="80" t="s">
         <v>380</v>
       </c>
@@ -12291,7 +12259,7 @@
       <c r="S141" s="80"/>
     </row>
     <row r="142" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="92"/>
+      <c r="A142" s="93"/>
       <c r="B142" s="80" t="s">
         <v>380</v>
       </c>
@@ -12342,8 +12310,8 @@
       </c>
       <c r="S142" s="75"/>
     </row>
-    <row r="143" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="92"/>
+    <row r="143" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A143" s="93"/>
       <c r="B143" s="80" t="s">
         <v>380</v>
       </c>
@@ -12395,7 +12363,7 @@
       <c r="S143" s="80"/>
     </row>
     <row r="144" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="92">
+      <c r="A144" s="93">
         <v>37</v>
       </c>
       <c r="B144" s="80" t="s">
@@ -12451,7 +12419,7 @@
       </c>
     </row>
     <row r="145" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="92"/>
+      <c r="A145" s="93"/>
       <c r="B145" s="80" t="s">
         <v>396</v>
       </c>
@@ -12501,7 +12469,7 @@
       </c>
     </row>
     <row r="146" spans="1:19" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="92"/>
+      <c r="A146" s="93"/>
       <c r="B146" s="80" t="s">
         <v>396</v>
       </c>
@@ -12605,7 +12573,7 @@
       </c>
     </row>
     <row r="148" spans="1:19" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="102"/>
+      <c r="A148" s="94"/>
       <c r="B148" s="80" t="s">
         <v>401</v>
       </c>
@@ -12656,7 +12624,7 @@
       </c>
     </row>
     <row r="149" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="98"/>
+      <c r="A149" s="95"/>
       <c r="B149" s="80" t="s">
         <v>401</v>
       </c>
@@ -12708,7 +12676,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="77"/>
       <c r="B150" s="80" t="s">
         <v>406</v>
@@ -12817,7 +12785,7 @@
       </c>
     </row>
     <row r="152" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="97">
+      <c r="A152" s="99">
         <v>40</v>
       </c>
       <c r="B152" s="80" t="s">
@@ -12873,7 +12841,7 @@
       </c>
     </row>
     <row r="153" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="102"/>
+      <c r="A153" s="94"/>
       <c r="B153" s="80" t="s">
         <v>412</v>
       </c>
@@ -12922,7 +12890,7 @@
       </c>
     </row>
     <row r="154" spans="1:19" ht="183.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="102"/>
+      <c r="A154" s="94"/>
       <c r="B154" s="80" t="s">
         <v>412</v>
       </c>
@@ -12969,7 +12937,7 @@
       </c>
     </row>
     <row r="155" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="102"/>
+      <c r="A155" s="94"/>
       <c r="B155" s="80" t="s">
         <v>412</v>
       </c>
@@ -13018,7 +12986,7 @@
       </c>
     </row>
     <row r="156" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="102"/>
+      <c r="A156" s="94"/>
       <c r="B156" s="80" t="s">
         <v>412</v>
       </c>
@@ -13072,7 +13040,7 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="102"/>
+      <c r="A157" s="94"/>
       <c r="B157" s="80" t="s">
         <v>412</v>
       </c>
@@ -13126,7 +13094,7 @@
       </c>
     </row>
     <row r="158" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="102"/>
+      <c r="A158" s="94"/>
       <c r="B158" s="80" t="s">
         <v>412</v>
       </c>
@@ -13180,7 +13148,7 @@
       </c>
     </row>
     <row r="159" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="102"/>
+      <c r="A159" s="94"/>
       <c r="B159" s="80" t="s">
         <v>426</v>
       </c>
@@ -13229,8 +13197,8 @@
       </c>
       <c r="S159" s="80"/>
     </row>
-    <row r="160" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="102"/>
+    <row r="160" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A160" s="94"/>
       <c r="B160" s="80" t="s">
         <v>426</v>
       </c>
@@ -13283,7 +13251,7 @@
       <c r="S160" s="80"/>
     </row>
     <row r="161" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="102"/>
+      <c r="A161" s="94"/>
       <c r="B161" s="80" t="s">
         <v>426</v>
       </c>
@@ -13333,7 +13301,7 @@
       <c r="S161" s="80"/>
     </row>
     <row r="162" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="102"/>
+      <c r="A162" s="94"/>
       <c r="B162" s="80" t="s">
         <v>426</v>
       </c>
@@ -13387,7 +13355,7 @@
       </c>
     </row>
     <row r="163" spans="1:19" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="98"/>
+      <c r="A163" s="95"/>
       <c r="B163" s="80" t="s">
         <v>434</v>
       </c>
@@ -13438,7 +13406,7 @@
       </c>
     </row>
     <row r="164" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="102"/>
+      <c r="A164" s="94"/>
       <c r="B164" s="80" t="s">
         <v>434</v>
       </c>
@@ -13489,7 +13457,7 @@
       </c>
     </row>
     <row r="165" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="98"/>
+      <c r="A165" s="95"/>
       <c r="B165" s="80" t="s">
         <v>434</v>
       </c>
@@ -13658,7 +13626,7 @@
       </c>
     </row>
     <row r="168" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="103">
+      <c r="A168" s="100">
         <v>44</v>
       </c>
       <c r="B168" s="80" t="s">
@@ -13716,7 +13684,7 @@
       </c>
     </row>
     <row r="169" spans="1:19" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="104"/>
+      <c r="A169" s="101"/>
       <c r="B169" s="80" t="s">
         <v>448</v>
       </c>
@@ -13765,7 +13733,7 @@
       </c>
     </row>
     <row r="170" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="104"/>
+      <c r="A170" s="101"/>
       <c r="B170" s="80" t="s">
         <v>448</v>
       </c>
@@ -13821,7 +13789,7 @@
       </c>
     </row>
     <row r="171" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="104"/>
+      <c r="A171" s="101"/>
       <c r="B171" s="80" t="s">
         <v>448</v>
       </c>
@@ -13875,7 +13843,7 @@
       </c>
     </row>
     <row r="172" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="105"/>
+      <c r="A172" s="102"/>
       <c r="B172" s="80" t="s">
         <v>455</v>
       </c>
@@ -13929,7 +13897,7 @@
       </c>
     </row>
     <row r="173" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="92">
+      <c r="A173" s="93">
         <v>45</v>
       </c>
       <c r="B173" s="80" t="s">
@@ -13984,7 +13952,7 @@
       </c>
     </row>
     <row r="174" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="92"/>
+      <c r="A174" s="93"/>
       <c r="B174" s="80" t="s">
         <v>457</v>
       </c>
@@ -14037,8 +14005,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="92"/>
+    <row r="175" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A175" s="93"/>
       <c r="B175" s="80" t="s">
         <v>457</v>
       </c>
@@ -14090,7 +14058,7 @@
       <c r="S175" s="80"/>
     </row>
     <row r="176" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="92"/>
+      <c r="A176" s="93"/>
       <c r="B176" s="80" t="s">
         <v>457</v>
       </c>
@@ -14144,7 +14112,7 @@
       </c>
     </row>
     <row r="177" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="92"/>
+      <c r="A177" s="93"/>
       <c r="B177" s="80" t="s">
         <v>457</v>
       </c>
@@ -14196,7 +14164,7 @@
       <c r="S177" s="80"/>
     </row>
     <row r="178" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="92"/>
+      <c r="A178" s="93"/>
       <c r="B178" s="80" t="s">
         <v>465</v>
       </c>
@@ -14250,7 +14218,7 @@
       </c>
     </row>
     <row r="179" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="92"/>
+      <c r="A179" s="93"/>
       <c r="B179" s="80" t="s">
         <v>467</v>
       </c>
@@ -14405,7 +14373,7 @@
       <c r="S181" s="75"/>
     </row>
     <row r="182" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="106">
+      <c r="A182" s="103">
         <v>46</v>
       </c>
       <c r="B182" s="80" t="s">
@@ -14456,8 +14424,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="106"/>
+    <row r="183" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="103"/>
       <c r="B183" s="80" t="s">
         <v>470</v>
       </c>
@@ -14467,7 +14435,9 @@
       <c r="D183" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E183" s="90"/>
+      <c r="E183" s="90">
+        <v>2025003050052</v>
+      </c>
       <c r="F183" s="80" t="s">
         <v>478</v>
       </c>
@@ -14507,7 +14477,7 @@
       </c>
     </row>
     <row r="184" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="106"/>
+      <c r="A184" s="103"/>
       <c r="B184" s="80" t="s">
         <v>470</v>
       </c>
@@ -14617,7 +14587,7 @@
       </c>
     </row>
     <row r="186" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="104"/>
+      <c r="A186" s="101"/>
       <c r="B186" s="80" t="s">
         <v>482</v>
       </c>
@@ -14664,16 +14634,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="104"/>
+    <row r="187" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A187" s="101"/>
       <c r="B187" s="80" t="s">
         <v>482</v>
       </c>
       <c r="C187" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="D187" s="75"/>
-      <c r="E187" s="90"/>
+      <c r="D187" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="E187" s="90">
+        <v>2026003050009</v>
+      </c>
       <c r="F187" s="80" t="s">
         <v>75</v>
       </c>
@@ -14711,7 +14685,7 @@
       <c r="S187" s="80"/>
     </row>
     <row r="188" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="105"/>
+      <c r="A188" s="102"/>
       <c r="B188" s="80" t="s">
         <v>482</v>
       </c>
@@ -14760,7 +14734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:19" ht="81" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="75"/>
       <c r="B189" s="80" t="s">
         <v>489</v>
@@ -14813,7 +14787,7 @@
       </c>
     </row>
     <row r="190" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="92">
+      <c r="A190" s="93">
         <v>48</v>
       </c>
       <c r="B190" s="80" t="s">
@@ -14866,7 +14840,7 @@
       </c>
     </row>
     <row r="191" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="92"/>
+      <c r="A191" s="93"/>
       <c r="B191" s="80" t="s">
         <v>489</v>
       </c>
@@ -14916,8 +14890,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="92"/>
+    <row r="192" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A192" s="93"/>
       <c r="B192" s="80" t="s">
         <v>489</v>
       </c>
@@ -14998,7 +14972,7 @@
       <c r="S193" s="75"/>
     </row>
     <row r="194" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="102"/>
+      <c r="A194" s="94"/>
       <c r="B194" s="80" t="s">
         <v>500</v>
       </c>
@@ -15050,7 +15024,7 @@
       </c>
     </row>
     <row r="195" spans="1:19" ht="24.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="98"/>
+      <c r="A195" s="95"/>
       <c r="B195" s="80" t="s">
         <v>500</v>
       </c>
@@ -15102,7 +15076,7 @@
       </c>
     </row>
     <row r="196" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="92">
+      <c r="A196" s="93">
         <v>51</v>
       </c>
       <c r="B196" s="80" t="s">
@@ -15155,7 +15129,7 @@
       </c>
     </row>
     <row r="197" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="92"/>
+      <c r="A197" s="93"/>
       <c r="B197" s="80" t="s">
         <v>504</v>
       </c>
@@ -15209,7 +15183,7 @@
       </c>
     </row>
     <row r="198" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="92"/>
+      <c r="A198" s="93"/>
       <c r="B198" s="80" t="s">
         <v>504</v>
       </c>
@@ -15263,7 +15237,7 @@
       </c>
     </row>
     <row r="199" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="92"/>
+      <c r="A199" s="93"/>
       <c r="B199" s="80" t="s">
         <v>504</v>
       </c>
@@ -15413,7 +15387,7 @@
       <c r="R201" s="79"/>
       <c r="S201" s="75"/>
     </row>
-    <row r="202" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A202" s="75">
         <v>52</v>
       </c>
@@ -15470,7 +15444,7 @@
       </c>
     </row>
     <row r="203" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="92">
+      <c r="A203" s="93">
         <v>53</v>
       </c>
       <c r="B203" s="80" t="s">
@@ -15524,8 +15498,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="92"/>
+    <row r="204" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A204" s="93"/>
       <c r="B204" s="80" t="s">
         <v>516</v>
       </c>
@@ -15579,7 +15553,7 @@
       </c>
     </row>
     <row r="205" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="92"/>
+      <c r="A205" s="93"/>
       <c r="B205" s="75" t="s">
         <v>520</v>
       </c>
@@ -15633,7 +15607,7 @@
       </c>
     </row>
     <row r="206" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="92">
+      <c r="A206" s="93">
         <v>54</v>
       </c>
       <c r="B206" s="80" t="s">
@@ -15686,8 +15660,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="92"/>
+    <row r="207" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A207" s="93"/>
       <c r="B207" s="80" t="s">
         <v>523</v>
       </c>
@@ -15743,7 +15717,7 @@
       </c>
     </row>
     <row r="208" spans="1:19" ht="32.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="92">
+      <c r="A208" s="93">
         <v>55</v>
       </c>
       <c r="B208" s="80" t="s">
@@ -15797,8 +15771,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="209" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="92"/>
+    <row r="209" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A209" s="93"/>
       <c r="B209" s="80" t="s">
         <v>526</v>
       </c>
@@ -15850,7 +15824,7 @@
       <c r="S209" s="80"/>
     </row>
     <row r="210" spans="1:19" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="92"/>
+      <c r="A210" s="93"/>
       <c r="B210" s="80" t="s">
         <v>526</v>
       </c>
@@ -15902,7 +15876,7 @@
       <c r="S210" s="75"/>
     </row>
     <row r="211" spans="1:19" ht="80.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="92">
+      <c r="A211" s="93">
         <v>56</v>
       </c>
       <c r="B211" s="80" t="s">
@@ -15954,8 +15928,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="92"/>
+    <row r="212" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A212" s="93"/>
       <c r="B212" s="80" t="s">
         <v>535</v>
       </c>
@@ -16011,7 +15985,7 @@
       </c>
     </row>
     <row r="213" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="103">
+      <c r="A213" s="100">
         <v>57</v>
       </c>
       <c r="B213" s="80" t="s">
@@ -16064,7 +16038,7 @@
       </c>
     </row>
     <row r="214" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="104"/>
+      <c r="A214" s="101"/>
       <c r="B214" s="80" t="s">
         <v>537</v>
       </c>
@@ -16118,7 +16092,7 @@
       </c>
     </row>
     <row r="215" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="104"/>
+      <c r="A215" s="101"/>
       <c r="B215" s="80" t="s">
         <v>537</v>
       </c>
@@ -16172,7 +16146,7 @@
       </c>
     </row>
     <row r="216" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="102"/>
+      <c r="A216" s="94"/>
       <c r="B216" s="80" t="s">
         <v>537</v>
       </c>
@@ -16225,7 +16199,7 @@
       </c>
     </row>
     <row r="217" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="105"/>
+      <c r="A217" s="102"/>
       <c r="B217" s="80" t="s">
         <v>537</v>
       </c>
@@ -16386,7 +16360,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A220" s="83"/>
       <c r="B220" s="80" t="s">
         <v>548</v>
@@ -16397,7 +16371,9 @@
       <c r="D220" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E220" s="90"/>
+      <c r="E220" s="90">
+        <v>2023003050099</v>
+      </c>
       <c r="F220" s="80" t="s">
         <v>553</v>
       </c>
@@ -16421,19 +16397,21 @@
       <c r="N220" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="O220" s="75"/>
+      <c r="O220" s="75" t="s">
+        <v>134</v>
+      </c>
       <c r="P220" s="75">
         <v>2023</v>
       </c>
       <c r="Q220" s="75"/>
       <c r="R220" s="79">
-        <v>0.86980000000000002</v>
+        <v>0.96</v>
       </c>
       <c r="S220" s="75" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="75">
         <v>58</v>
       </c>
@@ -16490,7 +16468,7 @@
       </c>
     </row>
     <row r="222" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="92">
+      <c r="A222" s="93">
         <v>59</v>
       </c>
       <c r="B222" s="80" t="s">
@@ -16542,8 +16520,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="92"/>
+    <row r="223" spans="1:19" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="93"/>
       <c r="B223" s="80" t="s">
         <v>558</v>
       </c>
@@ -16597,7 +16575,7 @@
       </c>
     </row>
     <row r="224" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="92"/>
+      <c r="A224" s="93"/>
       <c r="B224" s="80" t="s">
         <v>558</v>
       </c>
@@ -16646,7 +16624,7 @@
       <c r="S224" s="80"/>
     </row>
     <row r="225" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="92"/>
+      <c r="A225" s="93"/>
       <c r="B225" s="80" t="s">
         <v>558</v>
       </c>
@@ -16699,8 +16677,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="226" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="92"/>
+    <row r="226" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A226" s="93"/>
       <c r="B226" s="80" t="s">
         <v>558</v>
       </c>
@@ -16710,7 +16688,9 @@
       <c r="D226" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E226" s="90"/>
+      <c r="E226" s="90">
+        <v>2025003050050</v>
+      </c>
       <c r="F226" s="80" t="s">
         <v>568</v>
       </c>
@@ -16748,7 +16728,7 @@
       <c r="S226" s="75"/>
     </row>
     <row r="227" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="92"/>
+      <c r="A227" s="93"/>
       <c r="B227" s="80" t="s">
         <v>558</v>
       </c>
@@ -16801,7 +16781,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="228" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="75"/>
       <c r="B228" s="80" t="s">
         <v>570</v>
@@ -16905,7 +16885,7 @@
       </c>
       <c r="S229" s="75"/>
     </row>
-    <row r="230" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="75"/>
       <c r="B230" s="80" t="s">
         <v>570</v>
@@ -17037,7 +17017,7 @@
       <c r="R232" s="75"/>
       <c r="S232" s="75"/>
     </row>
-    <row r="233" spans="1:19" ht="224.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" ht="224.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="75">
         <v>62</v>
       </c>
@@ -17091,8 +17071,8 @@
         <v>578</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="97">
+    <row r="234" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="99">
         <v>63</v>
       </c>
       <c r="B234" s="80" t="s">
@@ -17104,7 +17084,9 @@
       <c r="D234" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E234" s="90"/>
+      <c r="E234" s="90" t="s">
+        <v>1065</v>
+      </c>
       <c r="F234" s="80" t="s">
         <v>580</v>
       </c>
@@ -17141,8 +17123,8 @@
         <v>582</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="102"/>
+    <row r="235" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="94"/>
       <c r="B235" s="80" t="s">
         <v>579</v>
       </c>
@@ -17193,8 +17175,8 @@
         <v>585</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="102"/>
+    <row r="236" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="94"/>
       <c r="B236" s="80" t="s">
         <v>579</v>
       </c>
@@ -17245,8 +17227,8 @@
         <v>588</v>
       </c>
     </row>
-    <row r="237" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="102"/>
+    <row r="237" spans="1:19" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="94"/>
       <c r="B237" s="80" t="s">
         <v>579</v>
       </c>
@@ -17256,7 +17238,9 @@
       <c r="D237" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="E237" s="90"/>
+      <c r="E237" s="64">
+        <v>2022053640012</v>
+      </c>
       <c r="F237" s="80" t="s">
         <v>589</v>
       </c>
@@ -17286,16 +17270,18 @@
       <c r="P237" s="75">
         <v>2022</v>
       </c>
-      <c r="Q237" s="75"/>
+      <c r="Q237" s="75" t="s">
+        <v>73</v>
+      </c>
       <c r="R237" s="49">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="S237" s="80" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="238" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="102"/>
+      <c r="A238" s="94"/>
       <c r="B238" s="80" t="s">
         <v>579</v>
       </c>
@@ -17348,7 +17334,7 @@
       </c>
     </row>
     <row r="239" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="98"/>
+      <c r="A239" s="95"/>
       <c r="B239" s="80" t="s">
         <v>592</v>
       </c>
@@ -17398,7 +17384,7 @@
       </c>
     </row>
     <row r="240" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="92">
+      <c r="A240" s="93">
         <v>64</v>
       </c>
       <c r="B240" s="80" t="s">
@@ -17450,8 +17436,8 @@
       </c>
       <c r="S240" s="80"/>
     </row>
-    <row r="241" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="92"/>
+    <row r="241" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="93"/>
       <c r="B241" s="80" t="s">
         <v>595</v>
       </c>
@@ -17461,7 +17447,9 @@
       <c r="D241" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E241" s="90"/>
+      <c r="E241" s="90">
+        <v>2022053680001</v>
+      </c>
       <c r="F241" s="80" t="s">
         <v>598</v>
       </c>
@@ -17501,7 +17489,7 @@
       </c>
     </row>
     <row r="242" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="92"/>
+      <c r="A242" s="93"/>
       <c r="B242" s="80" t="s">
         <v>595</v>
       </c>
@@ -17559,7 +17547,7 @@
       </c>
     </row>
     <row r="243" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="92"/>
+      <c r="A243" s="93"/>
       <c r="B243" s="80" t="s">
         <v>595</v>
       </c>
@@ -17609,7 +17597,7 @@
       </c>
     </row>
     <row r="244" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="92"/>
+      <c r="A244" s="93"/>
       <c r="B244" s="80" t="s">
         <v>595</v>
       </c>
@@ -17642,7 +17630,7 @@
       <c r="S244" s="80"/>
     </row>
     <row r="245" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="92"/>
+      <c r="A245" s="93"/>
       <c r="B245" s="80" t="s">
         <v>595</v>
       </c>
@@ -17692,7 +17680,7 @@
       </c>
     </row>
     <row r="246" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="92"/>
+      <c r="A246" s="93"/>
       <c r="B246" s="80" t="s">
         <v>595</v>
       </c>
@@ -17797,7 +17785,7 @@
       <c r="S247" s="80"/>
     </row>
     <row r="248" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="92">
+      <c r="A248" s="93">
         <v>65</v>
       </c>
       <c r="B248" s="80" t="s">
@@ -17849,8 +17837,8 @@
         <v>609</v>
       </c>
     </row>
-    <row r="249" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="92"/>
+    <row r="249" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="93"/>
       <c r="B249" s="80" t="s">
         <v>603</v>
       </c>
@@ -17860,7 +17848,9 @@
       <c r="D249" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="E249" s="90"/>
+      <c r="E249" s="90">
+        <v>4600015692</v>
+      </c>
       <c r="F249" s="80" t="s">
         <v>228</v>
       </c>
@@ -17900,7 +17890,7 @@
       </c>
     </row>
     <row r="250" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="92"/>
+      <c r="A250" s="93"/>
       <c r="B250" s="80" t="s">
         <v>603</v>
       </c>
@@ -18081,8 +18071,8 @@
       </c>
       <c r="S253" s="75"/>
     </row>
-    <row r="254" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="97">
+    <row r="254" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A254" s="99">
         <v>68</v>
       </c>
       <c r="B254" s="80" t="s">
@@ -18094,7 +18084,9 @@
       <c r="D254" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E254" s="90"/>
+      <c r="E254" s="90">
+        <v>2026003050001</v>
+      </c>
       <c r="F254" s="80" t="s">
         <v>617</v>
       </c>
@@ -18131,8 +18123,8 @@
         <v>618</v>
       </c>
     </row>
-    <row r="255" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="102"/>
+    <row r="255" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A255" s="94"/>
       <c r="B255" s="80" t="s">
         <v>616</v>
       </c>
@@ -18185,7 +18177,7 @@
       </c>
     </row>
     <row r="256" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.7">
-      <c r="A256" s="102"/>
+      <c r="A256" s="94"/>
       <c r="B256" s="80" t="s">
         <v>616</v>
       </c>
@@ -18239,7 +18231,7 @@
       </c>
     </row>
     <row r="257" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="102"/>
+      <c r="A257" s="94"/>
       <c r="B257" s="80" t="s">
         <v>616</v>
       </c>
@@ -18293,7 +18285,7 @@
       </c>
     </row>
     <row r="258" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="102"/>
+      <c r="A258" s="94"/>
       <c r="B258" s="80" t="s">
         <v>616</v>
       </c>
@@ -18345,7 +18337,7 @@
       </c>
     </row>
     <row r="259" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="98"/>
+      <c r="A259" s="95"/>
       <c r="B259" s="80" t="s">
         <v>616</v>
       </c>
@@ -18398,8 +18390,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="260" spans="1:19" ht="154.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="97">
+    <row r="260" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A260" s="99">
         <v>69</v>
       </c>
       <c r="B260" s="80" t="s">
@@ -18411,11 +18403,15 @@
       <c r="D260" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E260" s="90"/>
+      <c r="E260" s="90" t="s">
+        <v>1068</v>
+      </c>
       <c r="F260" s="85" t="s">
         <v>1061</v>
       </c>
-      <c r="G260" s="80"/>
+      <c r="G260" s="80" t="s">
+        <v>1067</v>
+      </c>
       <c r="H260" s="80"/>
       <c r="I260" s="80"/>
       <c r="J260" s="80"/>
@@ -18447,8 +18443,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="261" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="102"/>
+    <row r="261" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="94"/>
       <c r="B261" s="80" t="s">
         <v>626</v>
       </c>
@@ -18458,7 +18454,9 @@
       <c r="D261" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E261" s="90"/>
+      <c r="E261" s="90" t="s">
+        <v>1066</v>
+      </c>
       <c r="F261" s="80" t="s">
         <v>627</v>
       </c>
@@ -18496,7 +18494,7 @@
       </c>
     </row>
     <row r="262" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="102"/>
+      <c r="A262" s="94"/>
       <c r="B262" s="80" t="s">
         <v>630</v>
       </c>
@@ -18542,7 +18540,7 @@
       </c>
     </row>
     <row r="263" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="102"/>
+      <c r="A263" s="94"/>
       <c r="B263" s="80" t="s">
         <v>630</v>
       </c>
@@ -18590,7 +18588,7 @@
       </c>
     </row>
     <row r="264" spans="1:19" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="102"/>
+      <c r="A264" s="94"/>
       <c r="B264" s="80" t="s">
         <v>626</v>
       </c>
@@ -18641,7 +18639,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="265" spans="1:19" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="76"/>
       <c r="B265" s="80" t="s">
         <v>636</v>
@@ -18697,7 +18695,7 @@
       <c r="S265" s="80"/>
     </row>
     <row r="266" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="92">
+      <c r="A266" s="93">
         <v>70</v>
       </c>
       <c r="B266" s="80" t="s">
@@ -18753,7 +18751,7 @@
       <c r="S266" s="80"/>
     </row>
     <row r="267" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="92"/>
+      <c r="A267" s="93"/>
       <c r="B267" s="80" t="s">
         <v>636</v>
       </c>
@@ -18807,7 +18805,7 @@
       <c r="S267" s="80"/>
     </row>
     <row r="268" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="92"/>
+      <c r="A268" s="93"/>
       <c r="B268" s="80" t="s">
         <v>636</v>
       </c>
@@ -18860,8 +18858,8 @@
       </c>
       <c r="S268" s="80"/>
     </row>
-    <row r="269" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="92"/>
+    <row r="269" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="93"/>
       <c r="B269" s="80" t="s">
         <v>636</v>
       </c>
@@ -18925,7 +18923,9 @@
       <c r="D270" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="E270" s="54"/>
+      <c r="E270" s="54">
+        <v>2020054400058</v>
+      </c>
       <c r="F270" s="80" t="s">
         <v>228</v>
       </c>
@@ -18967,7 +18967,7 @@
       </c>
     </row>
     <row r="271" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="92">
+      <c r="A271" s="93">
         <v>71</v>
       </c>
       <c r="B271" s="80" t="s">
@@ -19020,8 +19020,8 @@
       </c>
       <c r="S271" s="80"/>
     </row>
-    <row r="272" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="92"/>
+    <row r="272" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="93"/>
       <c r="B272" s="80" t="s">
         <v>646</v>
       </c>
@@ -19070,10 +19070,12 @@
       <c r="R272" s="79">
         <v>1</v>
       </c>
-      <c r="S272" s="80"/>
-    </row>
-    <row r="273" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A273" s="92"/>
+      <c r="S272" s="80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="93"/>
       <c r="B273" s="80" t="s">
         <v>646</v>
       </c>
@@ -19126,8 +19128,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="274" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A274" s="92"/>
+    <row r="274" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="93"/>
       <c r="B274" s="80" t="s">
         <v>646</v>
       </c>
@@ -19176,10 +19178,12 @@
       <c r="R274" s="89">
         <v>1</v>
       </c>
-      <c r="S274" s="80"/>
-    </row>
-    <row r="275" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A275" s="92"/>
+      <c r="S274" s="80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="93"/>
       <c r="B275" s="75" t="s">
         <v>653</v>
       </c>
@@ -19340,7 +19344,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A278" s="75"/>
       <c r="B278" s="80" t="s">
         <v>658</v>
@@ -19348,8 +19352,12 @@
       <c r="C278" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="D278" s="75"/>
-      <c r="E278" s="90"/>
+      <c r="D278" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="E278" s="90">
+        <v>2026003050017</v>
+      </c>
       <c r="F278" s="80" t="s">
         <v>660</v>
       </c>
@@ -19441,7 +19449,7 @@
       <c r="S279" s="75"/>
     </row>
     <row r="280" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="92">
+      <c r="A280" s="93">
         <v>74</v>
       </c>
       <c r="B280" s="80" t="s">
@@ -19493,7 +19501,7 @@
       </c>
     </row>
     <row r="281" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="92"/>
+      <c r="A281" s="93"/>
       <c r="B281" s="80" t="s">
         <v>662</v>
       </c>
@@ -19540,7 +19548,7 @@
       <c r="S281" s="75"/>
     </row>
     <row r="282" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="92">
+      <c r="A282" s="93">
         <v>75</v>
       </c>
       <c r="B282" s="80" t="s">
@@ -19593,7 +19601,7 @@
       </c>
     </row>
     <row r="283" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="92"/>
+      <c r="A283" s="93"/>
       <c r="B283" s="80" t="s">
         <v>665</v>
       </c>
@@ -19645,7 +19653,7 @@
       <c r="S283" s="80"/>
     </row>
     <row r="284" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="98">
+      <c r="A284" s="95">
         <v>76</v>
       </c>
       <c r="B284" s="80" t="s">
@@ -19701,7 +19709,7 @@
       </c>
     </row>
     <row r="285" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="98"/>
+      <c r="A285" s="95"/>
       <c r="B285" s="80" t="s">
         <v>669</v>
       </c>
@@ -19755,7 +19763,7 @@
       </c>
     </row>
     <row r="286" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="98"/>
+      <c r="A286" s="95"/>
       <c r="B286" s="80" t="s">
         <v>669</v>
       </c>
@@ -19809,7 +19817,7 @@
       </c>
     </row>
     <row r="287" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="98"/>
+      <c r="A287" s="95"/>
       <c r="B287" s="80" t="s">
         <v>669</v>
       </c>
@@ -19863,7 +19871,7 @@
       </c>
     </row>
     <row r="288" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="92"/>
+      <c r="A288" s="93"/>
       <c r="B288" s="80" t="s">
         <v>669</v>
       </c>
@@ -19914,7 +19922,7 @@
       </c>
     </row>
     <row r="289" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="92"/>
+      <c r="A289" s="93"/>
       <c r="B289" s="80" t="s">
         <v>669</v>
       </c>
@@ -19966,7 +19974,7 @@
       </c>
     </row>
     <row r="290" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="92"/>
+      <c r="A290" s="93"/>
       <c r="B290" s="80" t="s">
         <v>669</v>
       </c>
@@ -20019,8 +20027,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="291" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="92"/>
+    <row r="291" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A291" s="93"/>
       <c r="B291" s="80" t="s">
         <v>669</v>
       </c>
@@ -20028,7 +20036,9 @@
         <v>20</v>
       </c>
       <c r="D291" s="75"/>
-      <c r="E291" s="90"/>
+      <c r="E291" s="90">
+        <v>2025003050045</v>
+      </c>
       <c r="F291" s="80" t="s">
         <v>75</v>
       </c>
@@ -20067,8 +20077,8 @@
       </c>
       <c r="S291" s="80"/>
     </row>
-    <row r="292" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="92"/>
+    <row r="292" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A292" s="93"/>
       <c r="B292" s="80" t="s">
         <v>669</v>
       </c>
@@ -20178,7 +20188,7 @@
       </c>
     </row>
     <row r="294" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="92">
+      <c r="A294" s="93">
         <v>77</v>
       </c>
       <c r="B294" s="80" t="s">
@@ -20238,7 +20248,7 @@
       </c>
     </row>
     <row r="295" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="92"/>
+      <c r="A295" s="93"/>
       <c r="B295" s="80" t="s">
         <v>684</v>
       </c>
@@ -20296,7 +20306,7 @@
       </c>
     </row>
     <row r="296" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="92"/>
+      <c r="A296" s="93"/>
       <c r="B296" s="80" t="s">
         <v>684</v>
       </c>
@@ -20354,7 +20364,7 @@
       </c>
     </row>
     <row r="297" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="92">
+      <c r="A297" s="93">
         <v>78</v>
       </c>
       <c r="B297" s="80" t="s">
@@ -20407,7 +20417,7 @@
       </c>
     </row>
     <row r="298" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="92"/>
+      <c r="A298" s="93"/>
       <c r="B298" s="80" t="s">
         <v>695</v>
       </c>
@@ -20459,7 +20469,7 @@
       <c r="S298" s="80"/>
     </row>
     <row r="299" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="92"/>
+      <c r="A299" s="93"/>
       <c r="B299" s="80" t="s">
         <v>695</v>
       </c>
@@ -20513,7 +20523,7 @@
       </c>
     </row>
     <row r="300" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="102"/>
+      <c r="A300" s="94"/>
       <c r="B300" s="80" t="s">
         <v>630</v>
       </c>
@@ -20565,7 +20575,7 @@
       <c r="S300" s="80"/>
     </row>
     <row r="301" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="98"/>
+      <c r="A301" s="95"/>
       <c r="B301" s="80" t="s">
         <v>630</v>
       </c>
@@ -20618,8 +20628,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="302" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="97">
+    <row r="302" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A302" s="99">
         <v>80</v>
       </c>
       <c r="B302" s="80" t="s">
@@ -20631,7 +20641,9 @@
       <c r="D302" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E302" s="90"/>
+      <c r="E302" s="90" t="s">
+        <v>1039</v>
+      </c>
       <c r="F302" s="80" t="s">
         <v>706</v>
       </c>
@@ -20670,7 +20682,7 @@
       </c>
     </row>
     <row r="303" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="102"/>
+      <c r="A303" s="94"/>
       <c r="B303" s="80" t="s">
         <v>708</v>
       </c>
@@ -20722,7 +20734,7 @@
       <c r="S303" s="80"/>
     </row>
     <row r="304" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="97">
+      <c r="A304" s="99">
         <v>81</v>
       </c>
       <c r="B304" s="80" t="s">
@@ -20774,7 +20786,7 @@
       </c>
     </row>
     <row r="305" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="102"/>
+      <c r="A305" s="94"/>
       <c r="B305" s="80" t="s">
         <v>710</v>
       </c>
@@ -20826,7 +20838,7 @@
       </c>
     </row>
     <row r="306" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="102"/>
+      <c r="A306" s="94"/>
       <c r="B306" s="80" t="s">
         <v>710</v>
       </c>
@@ -20877,7 +20889,7 @@
       </c>
     </row>
     <row r="307" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="98"/>
+      <c r="A307" s="95"/>
       <c r="B307" s="80" t="s">
         <v>710</v>
       </c>
@@ -20999,22 +21011,22 @@
       <c r="D309" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E309" s="99">
+      <c r="E309" s="105">
         <v>4600018191</v>
       </c>
-      <c r="F309" s="108" t="s">
+      <c r="F309" s="104" t="s">
         <v>1064</v>
       </c>
-      <c r="G309" s="92" t="s">
+      <c r="G309" s="93" t="s">
         <v>721</v>
       </c>
-      <c r="H309" s="92">
+      <c r="H309" s="93">
         <v>13.3</v>
       </c>
-      <c r="I309" s="97" t="s">
+      <c r="I309" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="J309" s="97" t="s">
+      <c r="J309" s="99" t="s">
         <v>538</v>
       </c>
       <c r="K309" s="96">
@@ -21028,25 +21040,25 @@
         <f>+K309</f>
         <v>988077089</v>
       </c>
-      <c r="N309" s="93" t="s">
+      <c r="N309" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="O309" s="93" t="s">
+      <c r="O309" s="98" t="s">
         <v>722</v>
       </c>
-      <c r="P309" s="92">
+      <c r="P309" s="93">
         <v>2025</v>
       </c>
-      <c r="Q309" s="93" t="s">
+      <c r="Q309" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="R309" s="92"/>
-      <c r="S309" s="92" t="s">
+      <c r="R309" s="93"/>
+      <c r="S309" s="93" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="92">
+      <c r="A310" s="93">
         <v>84</v>
       </c>
       <c r="B310" s="80" t="s">
@@ -21058,24 +21070,24 @@
       <c r="D310" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E310" s="100"/>
-      <c r="F310" s="93"/>
-      <c r="G310" s="92"/>
-      <c r="H310" s="92"/>
-      <c r="I310" s="98"/>
-      <c r="J310" s="98"/>
+      <c r="E310" s="106"/>
+      <c r="F310" s="98"/>
+      <c r="G310" s="93"/>
+      <c r="H310" s="93"/>
+      <c r="I310" s="95"/>
+      <c r="J310" s="95"/>
       <c r="K310" s="96"/>
       <c r="L310" s="96"/>
       <c r="M310" s="96"/>
-      <c r="N310" s="93"/>
-      <c r="O310" s="93"/>
-      <c r="P310" s="92"/>
-      <c r="Q310" s="93"/>
-      <c r="R310" s="92"/>
-      <c r="S310" s="92"/>
+      <c r="N310" s="98"/>
+      <c r="O310" s="98"/>
+      <c r="P310" s="93"/>
+      <c r="Q310" s="98"/>
+      <c r="R310" s="93"/>
+      <c r="S310" s="93"/>
     </row>
     <row r="311" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="92"/>
+      <c r="A311" s="93"/>
       <c r="B311" s="80" t="s">
         <v>720</v>
       </c>
@@ -21085,22 +21097,22 @@
       <c r="D311" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E311" s="99">
+      <c r="E311" s="105">
         <v>4600009793</v>
       </c>
-      <c r="F311" s="93" t="s">
+      <c r="F311" s="98" t="s">
         <v>724</v>
       </c>
-      <c r="G311" s="92" t="s">
+      <c r="G311" s="93" t="s">
         <v>725</v>
       </c>
-      <c r="H311" s="92">
+      <c r="H311" s="93">
         <v>31.12</v>
       </c>
-      <c r="I311" s="97" t="s">
+      <c r="I311" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="J311" s="97" t="s">
+      <c r="J311" s="99" t="s">
         <v>53</v>
       </c>
       <c r="K311" s="96">
@@ -21113,27 +21125,27 @@
       <c r="M311" s="96">
         <v>73907566008</v>
       </c>
-      <c r="N311" s="93" t="s">
+      <c r="N311" s="98" t="s">
         <v>726</v>
       </c>
-      <c r="O311" s="93" t="s">
+      <c r="O311" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="P311" s="92">
+      <c r="P311" s="93">
         <v>2019</v>
       </c>
-      <c r="Q311" s="93" t="s">
+      <c r="Q311" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="R311" s="109">
+      <c r="R311" s="97">
         <v>1</v>
       </c>
-      <c r="S311" s="92" t="s">
+      <c r="S311" s="93" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="92"/>
+      <c r="A312" s="93"/>
       <c r="B312" s="80" t="s">
         <v>723</v>
       </c>
@@ -21143,24 +21155,24 @@
       <c r="D312" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E312" s="100"/>
-      <c r="F312" s="93"/>
-      <c r="G312" s="92"/>
-      <c r="H312" s="92"/>
-      <c r="I312" s="98"/>
-      <c r="J312" s="98"/>
+      <c r="E312" s="106"/>
+      <c r="F312" s="98"/>
+      <c r="G312" s="93"/>
+      <c r="H312" s="93"/>
+      <c r="I312" s="95"/>
+      <c r="J312" s="95"/>
       <c r="K312" s="96"/>
       <c r="L312" s="96"/>
       <c r="M312" s="96"/>
-      <c r="N312" s="93"/>
-      <c r="O312" s="93"/>
-      <c r="P312" s="92"/>
-      <c r="Q312" s="93"/>
-      <c r="R312" s="109"/>
-      <c r="S312" s="92"/>
+      <c r="N312" s="98"/>
+      <c r="O312" s="98"/>
+      <c r="P312" s="93"/>
+      <c r="Q312" s="98"/>
+      <c r="R312" s="97"/>
+      <c r="S312" s="93"/>
     </row>
     <row r="313" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="92"/>
+      <c r="A313" s="93"/>
       <c r="B313" s="80" t="s">
         <v>723</v>
       </c>
@@ -21216,7 +21228,7 @@
       </c>
     </row>
     <row r="314" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="92"/>
+      <c r="A314" s="93"/>
       <c r="B314" s="80" t="s">
         <v>723</v>
       </c>
@@ -21269,8 +21281,8 @@
       </c>
       <c r="S314" s="80"/>
     </row>
-    <row r="315" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="92"/>
+    <row r="315" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="93"/>
       <c r="B315" s="80" t="s">
         <v>723</v>
       </c>
@@ -21324,7 +21336,7 @@
       </c>
       <c r="S315" s="80"/>
     </row>
-    <row r="316" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="81"/>
       <c r="B316" s="80" t="s">
         <v>729</v>
@@ -21335,7 +21347,9 @@
       <c r="D316" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E316" s="90"/>
+      <c r="E316" s="90">
+        <v>2023000040003</v>
+      </c>
       <c r="F316" s="80" t="s">
         <v>91</v>
       </c>
@@ -21415,8 +21429,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="318" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="97">
+    <row r="318" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="99">
         <v>85</v>
       </c>
       <c r="B318" s="80" t="s">
@@ -21463,7 +21477,7 @@
       <c r="S318" s="80"/>
     </row>
     <row r="319" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="98"/>
+      <c r="A319" s="95"/>
       <c r="B319" s="80" t="s">
         <v>729</v>
       </c>
@@ -21514,7 +21528,7 @@
       </c>
     </row>
     <row r="320" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="103">
+      <c r="A320" s="100">
         <v>86</v>
       </c>
       <c r="B320" s="80" t="s">
@@ -21566,7 +21580,7 @@
       </c>
     </row>
     <row r="321" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="104"/>
+      <c r="A321" s="101"/>
       <c r="B321" s="75" t="s">
         <v>735</v>
       </c>
@@ -21613,8 +21627,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="322" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="104"/>
+    <row r="322" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="101"/>
       <c r="B322" s="75" t="s">
         <v>735</v>
       </c>
@@ -21665,8 +21679,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="323" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="104"/>
+    <row r="323" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="101"/>
       <c r="B323" s="75" t="s">
         <v>735</v>
       </c>
@@ -21676,7 +21690,9 @@
       <c r="D323" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="E323" s="90"/>
+      <c r="E323" s="90">
+        <v>2023003050019</v>
+      </c>
       <c r="F323" s="80" t="s">
         <v>742</v>
       </c>
@@ -21716,7 +21732,7 @@
       </c>
     </row>
     <row r="324" spans="1:19" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="102"/>
+      <c r="A324" s="94"/>
       <c r="B324" s="75" t="s">
         <v>735</v>
       </c>
@@ -21766,7 +21782,7 @@
       </c>
     </row>
     <row r="325" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="102"/>
+      <c r="A325" s="94"/>
       <c r="B325" s="75" t="s">
         <v>735</v>
       </c>
@@ -21815,8 +21831,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="326" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="104"/>
+    <row r="326" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="101"/>
       <c r="B326" s="75" t="s">
         <v>735</v>
       </c>
@@ -21870,7 +21886,7 @@
       </c>
     </row>
     <row r="327" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="104"/>
+      <c r="A327" s="101"/>
       <c r="B327" s="80" t="s">
         <v>735</v>
       </c>
@@ -21919,8 +21935,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="328" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="104"/>
+    <row r="328" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="101"/>
       <c r="B328" s="80" t="s">
         <v>735</v>
       </c>
@@ -21972,7 +21988,7 @@
       <c r="S328" s="80"/>
     </row>
     <row r="329" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="105"/>
+      <c r="A329" s="102"/>
       <c r="B329" s="80" t="s">
         <v>735</v>
       </c>
@@ -22023,7 +22039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="330" spans="1:19" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="77"/>
       <c r="B330" s="80" t="s">
         <v>753</v>
@@ -22034,7 +22050,9 @@
       <c r="D330" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E330" s="90"/>
+      <c r="E330" s="90" t="s">
+        <v>1066</v>
+      </c>
       <c r="F330" s="80" t="s">
         <v>627</v>
       </c>
@@ -22098,7 +22116,7 @@
       <c r="R331" s="75"/>
       <c r="S331" s="75"/>
     </row>
-    <row r="332" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="81"/>
       <c r="B332" s="80" t="s">
         <v>756</v>
@@ -22192,7 +22210,7 @@
       </c>
     </row>
     <row r="334" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="97">
+      <c r="A334" s="99">
         <v>89</v>
       </c>
       <c r="B334" s="80" t="s">
@@ -22252,7 +22270,7 @@
       </c>
     </row>
     <row r="335" spans="1:19" ht="44.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="102"/>
+      <c r="A335" s="94"/>
       <c r="B335" s="80" t="s">
         <v>756</v>
       </c>
@@ -22303,7 +22321,7 @@
       </c>
     </row>
     <row r="336" spans="1:19" ht="155.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="102"/>
+      <c r="A336" s="94"/>
       <c r="B336" s="80" t="s">
         <v>756</v>
       </c>
@@ -22354,7 +22372,7 @@
       </c>
     </row>
     <row r="337" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="98"/>
+      <c r="A337" s="95"/>
       <c r="B337" s="80" t="s">
         <v>756</v>
       </c>
@@ -22407,7 +22425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A338" s="77"/>
       <c r="B338" s="80" t="s">
         <v>764</v>
@@ -22418,7 +22436,9 @@
       <c r="D338" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E338" s="90"/>
+      <c r="E338" s="90">
+        <v>2022003050012</v>
+      </c>
       <c r="F338" s="80" t="s">
         <v>765</v>
       </c>
@@ -22450,7 +22470,7 @@
       </c>
     </row>
     <row r="339" spans="1:20" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="92">
+      <c r="A339" s="93">
         <v>90</v>
       </c>
       <c r="B339" s="80" t="s">
@@ -22506,7 +22526,7 @@
       <c r="T339" s="36"/>
     </row>
     <row r="340" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="92"/>
+      <c r="A340" s="93"/>
       <c r="B340" s="80" t="s">
         <v>764</v>
       </c>
@@ -22559,7 +22579,7 @@
       <c r="T340" s="36"/>
     </row>
     <row r="341" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="92">
+      <c r="A341" s="93">
         <v>91</v>
       </c>
       <c r="B341" s="80" t="s">
@@ -22615,7 +22635,7 @@
       </c>
     </row>
     <row r="342" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="92"/>
+      <c r="A342" s="93"/>
       <c r="B342" s="80" t="s">
         <v>767</v>
       </c>
@@ -22668,8 +22688,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A343" s="92"/>
+    <row r="343" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A343" s="93"/>
       <c r="B343" s="80" t="s">
         <v>767</v>
       </c>
@@ -22679,7 +22699,9 @@
       <c r="D343" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E343" s="90"/>
+      <c r="E343" s="90" t="s">
+        <v>61</v>
+      </c>
       <c r="F343" s="80" t="s">
         <v>770</v>
       </c>
@@ -22717,7 +22739,7 @@
       </c>
     </row>
     <row r="344" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="92"/>
+      <c r="A344" s="93"/>
       <c r="B344" s="80" t="s">
         <v>767</v>
       </c>
@@ -22771,7 +22793,7 @@
       </c>
     </row>
     <row r="345" spans="1:20" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="92"/>
+      <c r="A345" s="93"/>
       <c r="B345" s="80" t="s">
         <v>767</v>
       </c>
@@ -22822,7 +22844,7 @@
       </c>
     </row>
     <row r="346" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="92"/>
+      <c r="A346" s="93"/>
       <c r="B346" s="80" t="s">
         <v>767</v>
       </c>
@@ -22865,8 +22887,8 @@
         <v>778</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="92"/>
+    <row r="347" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A347" s="93"/>
       <c r="B347" s="80" t="s">
         <v>767</v>
       </c>
@@ -22919,8 +22941,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="92">
+    <row r="348" spans="1:20" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A348" s="93">
         <v>92</v>
       </c>
       <c r="B348" s="80" t="s">
@@ -22975,7 +22997,7 @@
       <c r="S348" s="80"/>
     </row>
     <row r="349" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="92"/>
+      <c r="A349" s="93"/>
       <c r="B349" s="80" t="s">
         <v>779</v>
       </c>
@@ -23027,7 +23049,7 @@
       </c>
     </row>
     <row r="350" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="92"/>
+      <c r="A350" s="93"/>
       <c r="B350" s="80" t="s">
         <v>779</v>
       </c>
@@ -23080,8 +23102,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="92">
+    <row r="351" spans="1:20" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A351" s="93">
         <v>93</v>
       </c>
       <c r="B351" s="80" t="s">
@@ -23093,7 +23115,9 @@
       <c r="D351" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E351" s="90"/>
+      <c r="E351" s="90" t="s">
+        <v>1063</v>
+      </c>
       <c r="F351" s="80" t="s">
         <v>490</v>
       </c>
@@ -23124,16 +23148,18 @@
       <c r="P351" s="75">
         <v>2023</v>
       </c>
-      <c r="Q351" s="75"/>
+      <c r="Q351" s="75" t="s">
+        <v>73</v>
+      </c>
       <c r="R351" s="79">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="S351" s="75" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="352" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="92"/>
+      <c r="A352" s="93"/>
       <c r="B352" s="80" t="s">
         <v>784</v>
       </c>
@@ -23184,7 +23210,7 @@
       </c>
     </row>
     <row r="353" spans="1:19" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="92"/>
+      <c r="A353" s="93"/>
       <c r="B353" s="80" t="s">
         <v>784</v>
       </c>
@@ -23238,7 +23264,7 @@
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="92"/>
+      <c r="A354" s="93"/>
       <c r="B354" s="80" t="s">
         <v>784</v>
       </c>
@@ -23295,8 +23321,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="355" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="92"/>
+    <row r="355" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A355" s="93"/>
       <c r="B355" s="80" t="s">
         <v>784</v>
       </c>
@@ -23348,7 +23374,7 @@
       </c>
     </row>
     <row r="356" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="92"/>
+      <c r="A356" s="93"/>
       <c r="B356" s="80" t="s">
         <v>784</v>
       </c>
@@ -23401,7 +23427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="357" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="75"/>
       <c r="B357" s="80" t="s">
         <v>793</v>
@@ -23412,7 +23438,9 @@
       <c r="D357" s="75" t="s">
         <v>781</v>
       </c>
-      <c r="E357" s="90"/>
+      <c r="E357" s="91" t="s">
+        <v>1063</v>
+      </c>
       <c r="F357" s="85" t="s">
         <v>1062</v>
       </c>
@@ -23453,7 +23481,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="358" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="75"/>
       <c r="B358" s="80" t="s">
         <v>793</v>
@@ -23611,7 +23639,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="361" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A361" s="57"/>
       <c r="B361" s="80" t="s">
         <v>793</v>
@@ -23666,8 +23694,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="362" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="92"/>
+    <row r="362" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A362" s="93"/>
       <c r="B362" s="80" t="s">
         <v>803</v>
       </c>
@@ -23720,7 +23748,7 @@
       <c r="S362" s="80"/>
     </row>
     <row r="363" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="92"/>
+      <c r="A363" s="93"/>
       <c r="B363" s="80" t="s">
         <v>803</v>
       </c>
@@ -23879,7 +23907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="366" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A366" s="75">
         <v>96</v>
       </c>
@@ -23933,8 +23961,8 @@
       </c>
       <c r="S366" s="80"/>
     </row>
-    <row r="367" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="97">
+    <row r="367" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A367" s="99">
         <v>97</v>
       </c>
       <c r="B367" s="80" t="s">
@@ -23946,7 +23974,9 @@
       <c r="D367" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E367" s="90"/>
+      <c r="E367" s="91" t="s">
+        <v>1063</v>
+      </c>
       <c r="F367" s="80" t="s">
         <v>490</v>
       </c>
@@ -23981,7 +24011,7 @@
       </c>
     </row>
     <row r="368" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="102"/>
+      <c r="A368" s="94"/>
       <c r="B368" s="80" t="s">
         <v>810</v>
       </c>
@@ -24039,7 +24069,7 @@
       </c>
     </row>
     <row r="369" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="102"/>
+      <c r="A369" s="94"/>
       <c r="B369" s="80" t="s">
         <v>810</v>
       </c>
@@ -24090,7 +24120,7 @@
       </c>
     </row>
     <row r="370" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="102"/>
+      <c r="A370" s="94"/>
       <c r="B370" s="80" t="s">
         <v>810</v>
       </c>
@@ -24143,8 +24173,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="371" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="98"/>
+    <row r="371" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A371" s="95"/>
       <c r="B371" s="80" t="s">
         <v>810</v>
       </c>
@@ -24197,7 +24227,7 @@
       <c r="S371" s="80"/>
     </row>
     <row r="372" spans="1:19" ht="148.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="92">
+      <c r="A372" s="93">
         <v>98</v>
       </c>
       <c r="B372" s="80" t="s">
@@ -24250,7 +24280,7 @@
       </c>
     </row>
     <row r="373" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="92"/>
+      <c r="A373" s="93"/>
       <c r="B373" s="80" t="s">
         <v>816</v>
       </c>
@@ -24301,7 +24331,7 @@
       </c>
     </row>
     <row r="374" spans="1:19" ht="34.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="92"/>
+      <c r="A374" s="93"/>
       <c r="B374" s="80" t="s">
         <v>816</v>
       </c>
@@ -24352,7 +24382,7 @@
       </c>
     </row>
     <row r="375" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="92"/>
+      <c r="A375" s="93"/>
       <c r="B375" s="80" t="s">
         <v>816</v>
       </c>
@@ -24403,7 +24433,7 @@
       </c>
     </row>
     <row r="376" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="92"/>
+      <c r="A376" s="93"/>
       <c r="B376" s="80" t="s">
         <v>816</v>
       </c>
@@ -24443,8 +24473,8 @@
         <v>829</v>
       </c>
     </row>
-    <row r="377" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="92"/>
+    <row r="377" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="93"/>
       <c r="B377" s="80" t="s">
         <v>816</v>
       </c>
@@ -24493,8 +24523,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="378" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="92"/>
+    <row r="378" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="93"/>
       <c r="B378" s="80" t="s">
         <v>816</v>
       </c>
@@ -24544,7 +24574,7 @@
       </c>
     </row>
     <row r="379" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="92"/>
+      <c r="A379" s="93"/>
       <c r="B379" s="80" t="s">
         <v>816</v>
       </c>
@@ -24588,7 +24618,7 @@
       </c>
     </row>
     <row r="380" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="92"/>
+      <c r="A380" s="93"/>
       <c r="B380" s="80" t="s">
         <v>816</v>
       </c>
@@ -24635,7 +24665,7 @@
       <c r="S380" s="80"/>
     </row>
     <row r="381" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="92"/>
+      <c r="A381" s="93"/>
       <c r="B381" s="80" t="s">
         <v>816</v>
       </c>
@@ -24687,7 +24717,7 @@
       <c r="S381" s="80"/>
     </row>
     <row r="382" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="92"/>
+      <c r="A382" s="93"/>
       <c r="B382" s="80" t="s">
         <v>816</v>
       </c>
@@ -24737,7 +24767,7 @@
       </c>
     </row>
     <row r="383" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="92"/>
+      <c r="A383" s="93"/>
       <c r="B383" s="80" t="s">
         <v>816</v>
       </c>
@@ -24789,7 +24819,7 @@
       <c r="S383" s="80"/>
     </row>
     <row r="384" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="98">
+      <c r="A384" s="95">
         <v>99</v>
       </c>
       <c r="B384" s="80" t="s">
@@ -24842,7 +24872,7 @@
       </c>
     </row>
     <row r="385" spans="1:19" ht="163.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="92"/>
+      <c r="A385" s="93"/>
       <c r="B385" s="80" t="s">
         <v>844</v>
       </c>
@@ -24892,8 +24922,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="386" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="92"/>
+    <row r="386" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="93"/>
       <c r="B386" s="80" t="s">
         <v>844</v>
       </c>
@@ -24947,7 +24977,7 @@
       <c r="S386" s="80"/>
     </row>
     <row r="387" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="92"/>
+      <c r="A387" s="93"/>
       <c r="B387" s="80" t="s">
         <v>844</v>
       </c>
@@ -24999,7 +25029,7 @@
       </c>
     </row>
     <row r="388" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="92"/>
+      <c r="A388" s="93"/>
       <c r="B388" s="80" t="s">
         <v>843</v>
       </c>
@@ -25051,7 +25081,7 @@
       </c>
     </row>
     <row r="389" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="92"/>
+      <c r="A389" s="93"/>
       <c r="B389" s="80" t="s">
         <v>843</v>
       </c>
@@ -25105,7 +25135,7 @@
       </c>
     </row>
     <row r="390" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="92"/>
+      <c r="A390" s="93"/>
       <c r="B390" s="80" t="s">
         <v>843</v>
       </c>
@@ -25144,7 +25174,7 @@
       </c>
     </row>
     <row r="391" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="92"/>
+      <c r="A391" s="93"/>
       <c r="B391" s="75" t="s">
         <v>843</v>
       </c>
@@ -25247,7 +25277,7 @@
       </c>
     </row>
     <row r="393" spans="1:19" ht="58.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="92">
+      <c r="A393" s="93">
         <v>100</v>
       </c>
       <c r="B393" s="75" t="s">
@@ -25300,7 +25330,7 @@
       </c>
     </row>
     <row r="394" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="92"/>
+      <c r="A394" s="93"/>
       <c r="B394" s="75" t="s">
         <v>853</v>
       </c>
@@ -25351,7 +25381,7 @@
       </c>
     </row>
     <row r="395" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="92"/>
+      <c r="A395" s="93"/>
       <c r="B395" s="80" t="s">
         <v>853</v>
       </c>
@@ -25405,7 +25435,7 @@
       </c>
     </row>
     <row r="396" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="92"/>
+      <c r="A396" s="93"/>
       <c r="B396" s="80" t="s">
         <v>853</v>
       </c>
@@ -25453,7 +25483,7 @@
       </c>
     </row>
     <row r="397" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="92"/>
+      <c r="A397" s="93"/>
       <c r="B397" s="80" t="s">
         <v>853</v>
       </c>
@@ -25505,7 +25535,7 @@
       <c r="S397" s="80"/>
     </row>
     <row r="398" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="92"/>
+      <c r="A398" s="93"/>
       <c r="B398" s="80" t="s">
         <v>853</v>
       </c>
@@ -25557,7 +25587,7 @@
       <c r="S398" s="80"/>
     </row>
     <row r="399" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="106">
+      <c r="A399" s="103">
         <v>101</v>
       </c>
       <c r="B399" s="80" t="s">
@@ -25612,7 +25642,7 @@
       </c>
     </row>
     <row r="400" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="106"/>
+      <c r="A400" s="103"/>
       <c r="B400" s="80" t="s">
         <v>862</v>
       </c>
@@ -25651,7 +25681,7 @@
       <c r="S400" s="75"/>
     </row>
     <row r="401" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="106"/>
+      <c r="A401" s="103"/>
       <c r="B401" s="80" t="s">
         <v>862</v>
       </c>
@@ -25703,7 +25733,7 @@
       </c>
     </row>
     <row r="402" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="106"/>
+      <c r="A402" s="103"/>
       <c r="B402" s="80" t="s">
         <v>862</v>
       </c>
@@ -25756,16 +25786,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="403" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="106"/>
+    <row r="403" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="103"/>
       <c r="B403" s="80" t="s">
         <v>862</v>
       </c>
       <c r="C403" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="D403" s="75"/>
-      <c r="E403" s="90"/>
+      <c r="D403" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="E403" s="90">
+        <v>2025003050046</v>
+      </c>
       <c r="F403" s="80" t="s">
         <v>75</v>
       </c>
@@ -25805,7 +25839,7 @@
       <c r="S403" s="80"/>
     </row>
     <row r="404" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="106"/>
+      <c r="A404" s="103"/>
       <c r="B404" s="80" t="s">
         <v>862</v>
       </c>
@@ -25859,7 +25893,7 @@
       </c>
     </row>
     <row r="405" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="92">
+      <c r="A405" s="93">
         <v>102</v>
       </c>
       <c r="B405" s="75" t="s">
@@ -25912,7 +25946,7 @@
       </c>
     </row>
     <row r="406" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="92"/>
+      <c r="A406" s="93"/>
       <c r="B406" s="80" t="s">
         <v>869</v>
       </c>
@@ -25965,8 +25999,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="407" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="92">
+    <row r="407" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="93">
         <v>103</v>
       </c>
       <c r="B407" s="80" t="s">
@@ -26020,7 +26054,7 @@
       </c>
     </row>
     <row r="408" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="92"/>
+      <c r="A408" s="93"/>
       <c r="B408" s="80" t="s">
         <v>873</v>
       </c>
@@ -26074,7 +26108,7 @@
       </c>
     </row>
     <row r="409" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="92"/>
+      <c r="A409" s="93"/>
       <c r="B409" s="80" t="s">
         <v>873</v>
       </c>
@@ -26127,7 +26161,7 @@
       </c>
     </row>
     <row r="410" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="92"/>
+      <c r="A410" s="93"/>
       <c r="B410" s="80" t="s">
         <v>873</v>
       </c>
@@ -26181,7 +26215,7 @@
       </c>
     </row>
     <row r="411" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="92">
+      <c r="A411" s="93">
         <v>104</v>
       </c>
       <c r="B411" s="80" t="s">
@@ -26234,7 +26268,7 @@
       </c>
     </row>
     <row r="412" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="92"/>
+      <c r="A412" s="93"/>
       <c r="B412" s="80" t="s">
         <v>878</v>
       </c>
@@ -26292,7 +26326,7 @@
       </c>
     </row>
     <row r="413" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="92"/>
+      <c r="A413" s="93"/>
       <c r="B413" s="80"/>
       <c r="C413" s="75"/>
       <c r="D413" s="75"/>
@@ -26312,8 +26346,8 @@
       <c r="R413" s="89"/>
       <c r="S413" s="80"/>
     </row>
-    <row r="414" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="92"/>
+    <row r="414" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A414" s="93"/>
       <c r="B414" s="80" t="s">
         <v>878</v>
       </c>
@@ -26323,7 +26357,9 @@
       <c r="D414" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E414" s="90"/>
+      <c r="E414" s="90">
+        <v>2026003050013</v>
+      </c>
       <c r="F414" s="75" t="s">
         <v>882</v>
       </c>
@@ -26362,7 +26398,7 @@
       </c>
     </row>
     <row r="415" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="92"/>
+      <c r="A415" s="93"/>
       <c r="B415" s="80" t="s">
         <v>878</v>
       </c>
@@ -26415,7 +26451,7 @@
       </c>
     </row>
     <row r="416" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="92">
+      <c r="A416" s="93">
         <v>105</v>
       </c>
       <c r="B416" s="80" t="s">
@@ -26468,7 +26504,7 @@
       </c>
     </row>
     <row r="417" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="92"/>
+      <c r="A417" s="93"/>
       <c r="B417" s="80" t="s">
         <v>885</v>
       </c>
@@ -26513,7 +26549,7 @@
       </c>
     </row>
     <row r="418" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="92"/>
+      <c r="A418" s="93"/>
       <c r="B418" s="80" t="s">
         <v>885</v>
       </c>
@@ -26567,7 +26603,7 @@
       </c>
     </row>
     <row r="419" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="92"/>
+      <c r="A419" s="93"/>
       <c r="B419" s="80" t="s">
         <v>885</v>
       </c>
@@ -26621,7 +26657,7 @@
       </c>
     </row>
     <row r="420" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="92"/>
+      <c r="A420" s="93"/>
       <c r="B420" s="80" t="s">
         <v>885</v>
       </c>
@@ -26675,7 +26711,7 @@
       </c>
     </row>
     <row r="421" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="92"/>
+      <c r="A421" s="93"/>
       <c r="B421" s="80" t="s">
         <v>885</v>
       </c>
@@ -26715,8 +26751,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="422" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="92"/>
+    <row r="422" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A422" s="93"/>
       <c r="B422" s="80" t="s">
         <v>885</v>
       </c>
@@ -26764,7 +26800,7 @@
       </c>
     </row>
     <row r="423" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="92"/>
+      <c r="A423" s="93"/>
       <c r="B423" s="80" t="s">
         <v>885</v>
       </c>
@@ -26816,7 +26852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="424" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A424" s="75">
         <v>106</v>
       </c>
@@ -26863,7 +26899,7 @@
       <c r="R424" s="75"/>
       <c r="S424" s="80"/>
     </row>
-    <row r="425" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A425" s="75"/>
       <c r="B425" s="75" t="s">
         <v>901</v>
@@ -26874,7 +26910,9 @@
       <c r="D425" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="E425" s="90"/>
+      <c r="E425" s="90">
+        <v>2022003050018</v>
+      </c>
       <c r="F425" s="80" t="s">
         <v>33</v>
       </c>
@@ -26912,7 +26950,7 @@
       </c>
     </row>
     <row r="426" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="92">
+      <c r="A426" s="93">
         <v>107</v>
       </c>
       <c r="B426" s="80" t="s">
@@ -26967,7 +27005,7 @@
       </c>
     </row>
     <row r="427" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="92"/>
+      <c r="A427" s="93"/>
       <c r="B427" s="80" t="s">
         <v>902</v>
       </c>
@@ -27019,7 +27057,7 @@
       <c r="S427" s="80"/>
     </row>
     <row r="428" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="92"/>
+      <c r="A428" s="93"/>
       <c r="B428" s="80" t="s">
         <v>902</v>
       </c>
@@ -27068,8 +27106,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="429" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="92"/>
+    <row r="429" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="93"/>
       <c r="B429" s="80" t="s">
         <v>901</v>
       </c>
@@ -27079,7 +27117,9 @@
       <c r="D429" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E429" s="90"/>
+      <c r="E429" s="90" t="s">
+        <v>61</v>
+      </c>
       <c r="F429" s="80" t="s">
         <v>908</v>
       </c>
@@ -27116,8 +27156,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="430" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="92"/>
+    <row r="430" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="93"/>
       <c r="B430" s="80" t="s">
         <v>901</v>
       </c>
@@ -27164,8 +27204,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="431" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="92"/>
+    <row r="431" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A431" s="93"/>
       <c r="B431" s="80" t="s">
         <v>902</v>
       </c>
@@ -27217,7 +27257,7 @@
       <c r="S431" s="80"/>
     </row>
     <row r="432" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="92"/>
+      <c r="A432" s="93"/>
       <c r="B432" s="80" t="s">
         <v>901</v>
       </c>
@@ -27268,8 +27308,8 @@
       </c>
       <c r="S432" s="75"/>
     </row>
-    <row r="433" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="102"/>
+    <row r="433" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A433" s="94"/>
       <c r="B433" s="80" t="s">
         <v>913</v>
       </c>
@@ -27301,25 +27341,25 @@
         <f>+K433+L433</f>
         <v>13746524997</v>
       </c>
-      <c r="N433" s="93" t="s">
+      <c r="N433" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="O433" s="93" t="s">
+      <c r="O433" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="P433" s="92">
+      <c r="P433" s="93">
         <v>2025</v>
       </c>
       <c r="Q433" s="75"/>
-      <c r="R433" s="109">
+      <c r="R433" s="97">
         <v>0.65</v>
       </c>
-      <c r="S433" s="92" t="s">
+      <c r="S433" s="93" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="434" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="102"/>
+      <c r="A434" s="94"/>
       <c r="B434" s="80" t="s">
         <v>913</v>
       </c>
@@ -27344,15 +27384,15 @@
       <c r="K434" s="96"/>
       <c r="L434" s="96"/>
       <c r="M434" s="96"/>
-      <c r="N434" s="93"/>
-      <c r="O434" s="93"/>
-      <c r="P434" s="92"/>
+      <c r="N434" s="98"/>
+      <c r="O434" s="98"/>
+      <c r="P434" s="93"/>
       <c r="Q434" s="75"/>
-      <c r="R434" s="109"/>
-      <c r="S434" s="92"/>
+      <c r="R434" s="97"/>
+      <c r="S434" s="93"/>
     </row>
     <row r="435" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="102"/>
+      <c r="A435" s="94"/>
       <c r="B435" s="80" t="s">
         <v>913</v>
       </c>
@@ -27404,7 +27444,7 @@
       </c>
     </row>
     <row r="436" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="102"/>
+      <c r="A436" s="94"/>
       <c r="B436" s="80" t="s">
         <v>917</v>
       </c>
@@ -27456,7 +27496,7 @@
       </c>
     </row>
     <row r="437" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="102"/>
+      <c r="A437" s="94"/>
       <c r="B437" s="80" t="s">
         <v>913</v>
       </c>
@@ -27506,7 +27546,7 @@
       </c>
     </row>
     <row r="438" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="98"/>
+      <c r="A438" s="95"/>
       <c r="B438" s="80" t="s">
         <v>913</v>
       </c>
@@ -27557,7 +27597,7 @@
       </c>
     </row>
     <row r="439" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="97">
+      <c r="A439" s="99">
         <v>109</v>
       </c>
       <c r="B439" s="80" t="s">
@@ -27609,7 +27649,7 @@
       </c>
     </row>
     <row r="440" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="102"/>
+      <c r="A440" s="94"/>
       <c r="B440" s="80" t="s">
         <v>925</v>
       </c>
@@ -27658,7 +27698,7 @@
       </c>
     </row>
     <row r="441" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="102"/>
+      <c r="A441" s="94"/>
       <c r="B441" s="80" t="s">
         <v>925</v>
       </c>
@@ -27711,7 +27751,7 @@
       </c>
     </row>
     <row r="442" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="102"/>
+      <c r="A442" s="94"/>
       <c r="B442" s="80" t="s">
         <v>925</v>
       </c>
@@ -27762,8 +27802,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="443" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="102"/>
+    <row r="443" spans="1:19" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A443" s="94"/>
       <c r="B443" s="80" t="s">
         <v>925</v>
       </c>
@@ -27811,7 +27851,7 @@
       </c>
     </row>
     <row r="444" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="102"/>
+      <c r="A444" s="94"/>
       <c r="B444" s="80" t="s">
         <v>925</v>
       </c>
@@ -27859,7 +27899,7 @@
       </c>
     </row>
     <row r="445" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="102"/>
+      <c r="A445" s="94"/>
       <c r="B445" s="80" t="s">
         <v>925</v>
       </c>
@@ -27893,8 +27933,8 @@
       <c r="R445" s="89"/>
       <c r="S445" s="80"/>
     </row>
-    <row r="446" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="98"/>
+    <row r="446" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A446" s="95"/>
       <c r="B446" s="80" t="s">
         <v>925</v>
       </c>
@@ -27945,8 +27985,8 @@
       </c>
       <c r="S446" s="53"/>
     </row>
-    <row r="447" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="92"/>
+    <row r="447" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A447" s="93"/>
       <c r="B447" s="80" t="s">
         <v>935</v>
       </c>
@@ -28000,7 +28040,7 @@
       </c>
     </row>
     <row r="448" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="92"/>
+      <c r="A448" s="93"/>
       <c r="B448" s="60" t="s">
         <v>935</v>
       </c>
@@ -28057,8 +28097,8 @@
         <v>941</v>
       </c>
     </row>
-    <row r="449" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="97">
+    <row r="449" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A449" s="99">
         <v>111</v>
       </c>
       <c r="B449" s="80" t="s">
@@ -28110,7 +28150,7 @@
       </c>
     </row>
     <row r="450" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="102"/>
+      <c r="A450" s="94"/>
       <c r="B450" s="80" t="s">
         <v>942</v>
       </c>
@@ -28162,7 +28202,7 @@
       </c>
     </row>
     <row r="451" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="102"/>
+      <c r="A451" s="94"/>
       <c r="B451" s="80" t="s">
         <v>942</v>
       </c>
@@ -28218,7 +28258,7 @@
       </c>
     </row>
     <row r="452" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="98"/>
+      <c r="A452" s="95"/>
       <c r="B452" s="80" t="s">
         <v>942</v>
       </c>
@@ -28270,7 +28310,7 @@
       </c>
     </row>
     <row r="453" spans="1:19" ht="42.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="92">
+      <c r="A453" s="93">
         <v>112</v>
       </c>
       <c r="B453" s="80" t="s">
@@ -28329,7 +28369,7 @@
       </c>
     </row>
     <row r="454" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="92"/>
+      <c r="A454" s="93"/>
       <c r="B454" s="80" t="s">
         <v>949</v>
       </c>
@@ -28381,8 +28421,8 @@
       </c>
       <c r="S454" s="80"/>
     </row>
-    <row r="455" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="92"/>
+    <row r="455" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A455" s="93"/>
       <c r="B455" s="80" t="s">
         <v>949</v>
       </c>
@@ -28436,8 +28476,8 @@
       </c>
       <c r="S455" s="80"/>
     </row>
-    <row r="456" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="92">
+    <row r="456" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A456" s="93">
         <v>113</v>
       </c>
       <c r="B456" s="80" t="s">
@@ -28486,7 +28526,7 @@
       </c>
     </row>
     <row r="457" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="92"/>
+      <c r="A457" s="93"/>
       <c r="B457" s="80" t="s">
         <v>953</v>
       </c>
@@ -28537,7 +28577,7 @@
       </c>
     </row>
     <row r="458" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="92"/>
+      <c r="A458" s="93"/>
       <c r="B458" s="80" t="s">
         <v>953</v>
       </c>
@@ -28588,8 +28628,8 @@
       </c>
       <c r="S458" s="75"/>
     </row>
-    <row r="459" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="92"/>
+    <row r="459" spans="1:19" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A459" s="93"/>
       <c r="B459" s="80" t="s">
         <v>953</v>
       </c>
@@ -28635,7 +28675,7 @@
       <c r="S459" s="75"/>
     </row>
     <row r="460" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="92"/>
+      <c r="A460" s="93"/>
       <c r="B460" s="80" t="s">
         <v>953</v>
       </c>
@@ -28850,7 +28890,7 @@
       </c>
       <c r="S463" s="80"/>
     </row>
-    <row r="464" spans="1:19" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="75"/>
       <c r="B464" s="80" t="s">
         <v>960</v>
@@ -29005,8 +29045,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="467" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="102"/>
+    <row r="467" spans="1:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A467" s="94"/>
       <c r="B467" s="80" t="s">
         <v>971</v>
       </c>
@@ -29055,7 +29095,7 @@
       </c>
     </row>
     <row r="468" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="102"/>
+      <c r="A468" s="94"/>
       <c r="B468" s="80" t="s">
         <v>324</v>
       </c>
@@ -29107,7 +29147,7 @@
       <c r="S468" s="80"/>
     </row>
     <row r="469" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="102"/>
+      <c r="A469" s="94"/>
       <c r="B469" s="80" t="s">
         <v>324</v>
       </c>
@@ -29159,7 +29199,7 @@
       <c r="S469" s="80"/>
     </row>
     <row r="470" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="102"/>
+      <c r="A470" s="94"/>
       <c r="B470" s="80" t="s">
         <v>324</v>
       </c>
@@ -29211,7 +29251,7 @@
       <c r="S470" s="80"/>
     </row>
     <row r="471" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="102"/>
+      <c r="A471" s="94"/>
       <c r="B471" s="80" t="s">
         <v>324</v>
       </c>
@@ -29264,8 +29304,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="472" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="102"/>
+    <row r="472" spans="1:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A472" s="94"/>
       <c r="B472" s="80" t="s">
         <v>324</v>
       </c>
@@ -29315,7 +29355,7 @@
       </c>
     </row>
     <row r="473" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="98"/>
+      <c r="A473" s="95"/>
       <c r="B473" s="80" t="s">
         <v>971</v>
       </c>
@@ -29362,8 +29402,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="474" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="92">
+    <row r="474" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A474" s="93">
         <v>116</v>
       </c>
       <c r="B474" s="80" t="s">
@@ -29375,7 +29415,7 @@
       <c r="D474" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E474" s="95">
+      <c r="E474" s="111">
         <v>2025003050036</v>
       </c>
       <c r="F474" s="80" t="s">
@@ -29389,11 +29429,11 @@
       </c>
       <c r="I474" s="80"/>
       <c r="J474" s="80"/>
-      <c r="K474" s="91">
+      <c r="K474" s="109">
         <f>+M474</f>
         <v>14202451801</v>
       </c>
-      <c r="L474" s="91">
+      <c r="L474" s="109">
         <v>0</v>
       </c>
       <c r="M474" s="96">
@@ -29412,12 +29452,12 @@
         <v>563</v>
       </c>
       <c r="R474" s="80"/>
-      <c r="S474" s="93" t="s">
+      <c r="S474" s="98" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="475" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="92"/>
+    <row r="475" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A475" s="93"/>
       <c r="B475" s="80" t="s">
         <v>983</v>
       </c>
@@ -29427,7 +29467,7 @@
       <c r="D475" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E475" s="95"/>
+      <c r="E475" s="111"/>
       <c r="F475" s="80" t="s">
         <v>174</v>
       </c>
@@ -29439,8 +29479,8 @@
       </c>
       <c r="I475" s="80"/>
       <c r="J475" s="80"/>
-      <c r="K475" s="91"/>
-      <c r="L475" s="91"/>
+      <c r="K475" s="109"/>
+      <c r="L475" s="109"/>
       <c r="M475" s="96"/>
       <c r="N475" s="80" t="s">
         <v>35</v>
@@ -29455,10 +29495,10 @@
         <v>563</v>
       </c>
       <c r="R475" s="80"/>
-      <c r="S475" s="93"/>
+      <c r="S475" s="98"/>
     </row>
     <row r="476" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="92"/>
+      <c r="A476" s="93"/>
       <c r="B476" s="80" t="s">
         <v>983</v>
       </c>
@@ -29514,7 +29554,7 @@
       </c>
     </row>
     <row r="477" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="92"/>
+      <c r="A477" s="93"/>
       <c r="B477" s="80" t="s">
         <v>983</v>
       </c>
@@ -29619,7 +29659,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="479" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="75"/>
       <c r="B479" s="80" t="s">
         <v>989</v>
@@ -29775,7 +29815,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="482" spans="1:19" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:19" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="75"/>
       <c r="B482" s="80" t="s">
         <v>995</v>
@@ -29798,7 +29838,7 @@
       </c>
       <c r="I482" s="80"/>
       <c r="J482" s="80"/>
-      <c r="K482" s="111">
+      <c r="K482" s="92">
         <v>4263692901</v>
       </c>
       <c r="L482" s="78">
@@ -29825,7 +29865,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="483" spans="1:19" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:19" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="75"/>
       <c r="B483" s="80" t="s">
         <v>995</v>
@@ -29929,7 +29969,7 @@
       <c r="S484" s="75"/>
     </row>
     <row r="485" spans="1:19" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="92">
+      <c r="A485" s="93">
         <v>121</v>
       </c>
       <c r="B485" s="80" t="s">
@@ -29983,7 +30023,7 @@
       <c r="S485" s="80"/>
     </row>
     <row r="486" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="92"/>
+      <c r="A486" s="93"/>
       <c r="B486" s="80" t="s">
         <v>999</v>
       </c>
@@ -30033,7 +30073,7 @@
       </c>
     </row>
     <row r="487" spans="1:19" ht="163.19999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="92"/>
+      <c r="A487" s="93"/>
       <c r="B487" s="80" t="s">
         <v>999</v>
       </c>
@@ -30084,7 +30124,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="488" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="77"/>
       <c r="B488" s="80" t="s">
         <v>1007</v>
@@ -30189,7 +30229,7 @@
       <c r="S489" s="80"/>
     </row>
     <row r="490" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="102"/>
+      <c r="A490" s="94"/>
       <c r="B490" s="80" t="s">
         <v>1009</v>
       </c>
@@ -30241,7 +30281,7 @@
       <c r="S490" s="80"/>
     </row>
     <row r="491" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="102"/>
+      <c r="A491" s="94"/>
       <c r="B491" s="80" t="s">
         <v>1009</v>
       </c>
@@ -30292,8 +30332,8 @@
       </c>
       <c r="S491" s="80"/>
     </row>
-    <row r="492" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="102"/>
+    <row r="492" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A492" s="94"/>
       <c r="B492" s="80" t="s">
         <v>1009</v>
       </c>
@@ -30340,7 +30380,7 @@
       </c>
     </row>
     <row r="493" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="98"/>
+      <c r="A493" s="95"/>
       <c r="B493" s="80" t="s">
         <v>1009</v>
       </c>
@@ -30392,7 +30432,7 @@
       <c r="S493" s="80"/>
     </row>
     <row r="494" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="92">
+      <c r="A494" s="93">
         <v>124</v>
       </c>
       <c r="B494" s="80" t="s">
@@ -30447,8 +30487,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="495" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="92"/>
+    <row r="495" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A495" s="93"/>
       <c r="B495" s="80" t="s">
         <v>1016</v>
       </c>
@@ -30498,7 +30538,7 @@
       </c>
     </row>
     <row r="496" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="92"/>
+      <c r="A496" s="93"/>
       <c r="B496" s="80" t="s">
         <v>1016</v>
       </c>
@@ -30550,7 +30590,7 @@
       </c>
     </row>
     <row r="497" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="92"/>
+      <c r="A497" s="93"/>
       <c r="B497" s="80" t="s">
         <v>1022</v>
       </c>
@@ -30661,7 +30701,7 @@
       </c>
     </row>
     <row r="499" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="93">
+      <c r="A499" s="98">
         <v>126</v>
       </c>
       <c r="B499" s="80" t="s">
@@ -30720,7 +30760,7 @@
       </c>
     </row>
     <row r="500" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="93"/>
+      <c r="A500" s="98"/>
       <c r="B500" s="80" t="s">
         <v>1023</v>
       </c>
@@ -30769,7 +30809,7 @@
       <c r="S500" s="80"/>
     </row>
     <row r="501" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="93"/>
+      <c r="A501" s="98"/>
       <c r="B501" s="80" t="s">
         <v>1023</v>
       </c>
@@ -30823,7 +30863,7 @@
       </c>
     </row>
     <row r="502" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="92">
+      <c r="A502" s="93">
         <v>127</v>
       </c>
       <c r="B502" s="80" t="s">
@@ -30883,7 +30923,7 @@
       </c>
     </row>
     <row r="503" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="92"/>
+      <c r="A503" s="93"/>
       <c r="B503" s="80" t="s">
         <v>1031</v>
       </c>
@@ -30939,7 +30979,7 @@
       <c r="S503" s="80"/>
     </row>
     <row r="504" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="92"/>
+      <c r="A504" s="93"/>
       <c r="B504" s="60" t="s">
         <v>1031</v>
       </c>
@@ -31062,25 +31102,116 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:S506" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-    <filterColumn colId="1">
+    <filterColumn colId="13">
       <filters>
-        <filter val="Marinilla"/>
+        <filter val="Recursos propios + regalías"/>
+        <filter val="Regalías"/>
+        <filter val="Regalías + Recursos Propios"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A407:A410"/>
-    <mergeCell ref="A411:A415"/>
-    <mergeCell ref="A416:A423"/>
-    <mergeCell ref="A426:A432"/>
-    <mergeCell ref="A433:A438"/>
-    <mergeCell ref="K433:K434"/>
-    <mergeCell ref="R433:R434"/>
-    <mergeCell ref="L433:L434"/>
-    <mergeCell ref="M433:M434"/>
-    <mergeCell ref="N433:N434"/>
-    <mergeCell ref="O433:O434"/>
-    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="M91:M100"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="R91:R92"/>
+    <mergeCell ref="E474:E475"/>
+    <mergeCell ref="S91:S92"/>
+    <mergeCell ref="M474:M475"/>
+    <mergeCell ref="K474:K475"/>
+    <mergeCell ref="L474:L475"/>
+    <mergeCell ref="S474:S475"/>
+    <mergeCell ref="S433:S434"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="H311:H312"/>
+    <mergeCell ref="J309:J310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="I311:I312"/>
+    <mergeCell ref="J311:J312"/>
+    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="K91:K100"/>
+    <mergeCell ref="L91:L100"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A116"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A190:A192"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A152:A163"/>
+    <mergeCell ref="A213:A217"/>
+    <mergeCell ref="A222:A227"/>
+    <mergeCell ref="A234:A239"/>
+    <mergeCell ref="A240:A246"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A254:A259"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A294:A296"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A304:A307"/>
+    <mergeCell ref="F309:F310"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A275"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A284:A292"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A399:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="P309:P310"/>
+    <mergeCell ref="S309:S310"/>
+    <mergeCell ref="R309:R310"/>
+    <mergeCell ref="A310:A315"/>
+    <mergeCell ref="F311:F312"/>
+    <mergeCell ref="G311:G312"/>
+    <mergeCell ref="K311:K312"/>
+    <mergeCell ref="L311:L312"/>
+    <mergeCell ref="M311:M312"/>
+    <mergeCell ref="N311:N312"/>
+    <mergeCell ref="G309:G310"/>
+    <mergeCell ref="K309:K310"/>
+    <mergeCell ref="L309:L310"/>
+    <mergeCell ref="M309:M310"/>
+    <mergeCell ref="N309:N310"/>
+    <mergeCell ref="O309:O310"/>
+    <mergeCell ref="Q309:Q310"/>
+    <mergeCell ref="Q311:Q312"/>
+    <mergeCell ref="O311:O312"/>
+    <mergeCell ref="P311:P312"/>
+    <mergeCell ref="S311:S312"/>
+    <mergeCell ref="R311:R312"/>
     <mergeCell ref="A318:A319"/>
     <mergeCell ref="A320:A329"/>
     <mergeCell ref="A334:A337"/>
@@ -31105,107 +31236,18 @@
     <mergeCell ref="A372:A383"/>
     <mergeCell ref="A384:A391"/>
     <mergeCell ref="A393:A398"/>
-    <mergeCell ref="A399:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="P309:P310"/>
-    <mergeCell ref="S309:S310"/>
-    <mergeCell ref="R309:R310"/>
-    <mergeCell ref="A310:A315"/>
-    <mergeCell ref="F311:F312"/>
-    <mergeCell ref="G311:G312"/>
-    <mergeCell ref="K311:K312"/>
-    <mergeCell ref="L311:L312"/>
-    <mergeCell ref="M311:M312"/>
-    <mergeCell ref="N311:N312"/>
-    <mergeCell ref="G309:G310"/>
-    <mergeCell ref="K309:K310"/>
-    <mergeCell ref="L309:L310"/>
-    <mergeCell ref="M309:M310"/>
-    <mergeCell ref="N309:N310"/>
-    <mergeCell ref="O309:O310"/>
-    <mergeCell ref="Q309:Q310"/>
-    <mergeCell ref="Q311:Q312"/>
-    <mergeCell ref="O311:O312"/>
-    <mergeCell ref="P311:P312"/>
-    <mergeCell ref="S311:S312"/>
-    <mergeCell ref="R311:R312"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A304:A307"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A275"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A284:A292"/>
-    <mergeCell ref="E309:E310"/>
-    <mergeCell ref="A213:A217"/>
-    <mergeCell ref="A222:A227"/>
-    <mergeCell ref="A234:A239"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A254:A259"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A208:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A152:A163"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="R91:R92"/>
-    <mergeCell ref="E474:E475"/>
-    <mergeCell ref="S91:S92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="M474:M475"/>
-    <mergeCell ref="K474:K475"/>
-    <mergeCell ref="L474:L475"/>
-    <mergeCell ref="S474:S475"/>
-    <mergeCell ref="S433:S434"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="H311:H312"/>
-    <mergeCell ref="J309:J310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="I311:I312"/>
-    <mergeCell ref="J311:J312"/>
-    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="A407:A410"/>
+    <mergeCell ref="A411:A415"/>
+    <mergeCell ref="A416:A423"/>
+    <mergeCell ref="A426:A432"/>
+    <mergeCell ref="A433:A438"/>
+    <mergeCell ref="K433:K434"/>
+    <mergeCell ref="R433:R434"/>
+    <mergeCell ref="L433:L434"/>
+    <mergeCell ref="M433:M434"/>
+    <mergeCell ref="N433:N434"/>
+    <mergeCell ref="O433:O434"/>
+    <mergeCell ref="P433:P434"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -31236,10 +31278,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="40.799999999999997" x14ac:dyDescent="0.7">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>1040</v>
       </c>
-      <c r="C2" s="110"/>
+      <c r="C2" s="112"/>
       <c r="D2" s="24" t="s">
         <v>1041</v>
       </c>
@@ -31446,23 +31488,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -31618,25 +31643,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31652,4 +31676,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B7762D2-9A41-41B1-81EE-84F87E8850C5}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB81A53B-146C-45F4-90FC-69F97FE40998}"/>
   <bookViews>
-    <workbookView xWindow="4008" yWindow="4008" windowWidth="14184" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos SIF'!$A$2:$S$506</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Proyectos SIF'!$A$2:$T$506</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterate="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="1068">
   <si>
     <t>PROYECTOS SIF</t>
   </si>
@@ -3572,9 +3572,6 @@
   </si>
   <si>
     <t>Placa huella JAC Corregimiento El Dos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se firmó acta de inicio el  16 de abril </t>
   </si>
   <si>
     <t>25AS111B2819</t>
@@ -4239,7 +4236,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4509,25 +4506,52 @@
     <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4542,41 +4566,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4929,10 +4929,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="108"/>
+      <c r="C1" s="107"/>
       <c r="D1" s="87"/>
       <c r="E1" s="37"/>
       <c r="F1" s="87"/>
@@ -5008,8 +5008,8 @@
       </c>
       <c r="U2" s="14"/>
     </row>
-    <row r="3" spans="1:21" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="95">
+    <row r="3" spans="1:21" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="104">
         <v>1</v>
       </c>
       <c r="B3" s="77" t="s">
@@ -5069,8 +5069,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="95"/>
+    <row r="4" spans="1:21" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="104"/>
       <c r="B4" s="80" t="s">
         <v>19</v>
       </c>
@@ -5129,7 +5129,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="95"/>
+      <c r="A5" s="104"/>
       <c r="B5" s="81" t="s">
         <v>19</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="81"/>
       <c r="B6" s="80" t="s">
         <v>38</v>
@@ -5233,7 +5233,7 @@
       <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="99">
+      <c r="A7" s="103">
         <v>2</v>
       </c>
       <c r="B7" s="80" t="s">
@@ -5266,7 +5266,7 @@
       <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94"/>
+      <c r="A8" s="108"/>
       <c r="B8" s="80" t="s">
         <v>38</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="80" t="s">
         <v>38</v>
       </c>
@@ -5372,7 +5372,7 @@
       <c r="S9" s="75"/>
     </row>
     <row r="10" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="75" t="s">
         <v>38</v>
       </c>
@@ -5427,8 +5427,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="93">
+    <row r="11" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A11" s="97">
         <v>3</v>
       </c>
       <c r="B11" s="86" t="s">
@@ -5488,8 +5488,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="52.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
+    <row r="12" spans="1:21" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="97"/>
       <c r="B12" s="80" t="s">
         <v>56</v>
       </c>
@@ -5542,8 +5542,8 @@
       </c>
       <c r="S12" s="85"/>
     </row>
-    <row r="13" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="93"/>
+    <row r="13" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="97"/>
       <c r="B13" s="80" t="s">
         <v>56</v>
       </c>
@@ -5596,8 +5596,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="93"/>
+    <row r="14" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="97"/>
       <c r="B14" s="80" t="s">
         <v>56</v>
       </c>
@@ -5651,7 +5651,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="80" t="s">
         <v>56</v>
       </c>
@@ -5704,8 +5704,8 @@
       </c>
       <c r="S15" s="75"/>
     </row>
-    <row r="16" spans="1:21" ht="66.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
+    <row r="16" spans="1:21" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="97"/>
       <c r="B16" s="80" t="s">
         <v>56</v>
       </c>
@@ -5797,7 +5797,7 @@
       <c r="R17" s="89"/>
       <c r="S17" s="80"/>
     </row>
-    <row r="18" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="75">
         <v>4</v>
       </c>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="S18" s="80"/>
     </row>
-    <row r="19" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="75"/>
       <c r="B19" s="80" t="s">
         <v>89</v>
@@ -5914,7 +5914,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="97.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93">
+      <c r="A20" s="97">
         <v>5</v>
       </c>
       <c r="B20" s="80" t="s">
@@ -5974,7 +5974,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="80" t="s">
         <v>89</v>
       </c>
@@ -6030,7 +6030,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="80" t="s">
         <v>89</v>
       </c>
@@ -6086,8 +6086,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A23" s="93"/>
+    <row r="23" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="97"/>
       <c r="B23" s="80" t="s">
         <v>89</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="S23" s="80"/>
     </row>
     <row r="24" spans="1:19" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="93">
+      <c r="A24" s="97">
         <v>6</v>
       </c>
       <c r="B24" s="80" t="s">
@@ -6201,7 +6201,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="93"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="80" t="s">
         <v>106</v>
       </c>
@@ -6255,7 +6255,7 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="80" t="s">
         <v>106</v>
       </c>
@@ -6308,8 +6308,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="93"/>
+    <row r="27" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="97"/>
       <c r="B27" s="80" t="s">
         <v>106</v>
       </c>
@@ -6365,7 +6365,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="93"/>
+      <c r="A28" s="97"/>
       <c r="B28" s="80" t="s">
         <v>106</v>
       </c>
@@ -6417,7 +6417,7 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="93"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="80" t="s">
         <v>106</v>
       </c>
@@ -6471,7 +6471,7 @@
       </c>
     </row>
     <row r="30" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="93"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="80" t="s">
         <v>106</v>
       </c>
@@ -6521,7 +6521,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="93"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="80" t="s">
         <v>106</v>
       </c>
@@ -6577,7 +6577,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="93"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="80" t="s">
         <v>106</v>
       </c>
@@ -6635,7 +6635,7 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="80" t="s">
         <v>106</v>
       </c>
@@ -6688,8 +6688,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="93"/>
+    <row r="34" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="97"/>
       <c r="B34" s="80" t="s">
         <v>106</v>
       </c>
@@ -6747,7 +6747,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="94"/>
+      <c r="A35" s="108"/>
       <c r="B35" s="80" t="s">
         <v>144</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="S35" s="80"/>
     </row>
     <row r="36" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="95"/>
+      <c r="A36" s="104"/>
       <c r="B36" s="80" t="s">
         <v>144</v>
       </c>
@@ -6888,7 +6888,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="93">
+      <c r="A38" s="97">
         <v>8</v>
       </c>
       <c r="B38" s="80" t="s">
@@ -6946,8 +6946,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="93"/>
+    <row r="39" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="97"/>
       <c r="B39" s="80" t="s">
         <v>147</v>
       </c>
@@ -7005,7 +7005,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="93"/>
+      <c r="A40" s="97"/>
       <c r="B40" s="80" t="s">
         <v>147</v>
       </c>
@@ -7059,8 +7059,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="93">
+    <row r="41" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="97">
         <v>9</v>
       </c>
       <c r="B41" s="80" t="s">
@@ -7118,7 +7118,7 @@
       <c r="S41" s="80"/>
     </row>
     <row r="42" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="93"/>
+      <c r="A42" s="97"/>
       <c r="B42" s="80" t="s">
         <v>157</v>
       </c>
@@ -7165,7 +7165,7 @@
       </c>
     </row>
     <row r="43" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="93"/>
+      <c r="A43" s="97"/>
       <c r="B43" s="80" t="s">
         <v>157</v>
       </c>
@@ -7214,7 +7214,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="93"/>
+      <c r="A44" s="97"/>
       <c r="B44" s="80" t="s">
         <v>157</v>
       </c>
@@ -7260,7 +7260,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93"/>
+      <c r="A45" s="97"/>
       <c r="B45" s="80" t="s">
         <v>157</v>
       </c>
@@ -7313,8 +7313,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="93">
+    <row r="46" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="97">
         <v>10</v>
       </c>
       <c r="B46" s="80" t="s">
@@ -7368,7 +7368,7 @@
       </c>
     </row>
     <row r="47" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="99"/>
+      <c r="A47" s="103"/>
       <c r="B47" s="80" t="s">
         <v>172</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="S47" s="80"/>
     </row>
     <row r="48" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="93"/>
+      <c r="A48" s="97"/>
       <c r="B48" s="80" t="s">
         <v>179</v>
       </c>
@@ -7453,7 +7453,7 @@
       <c r="S48" s="80"/>
     </row>
     <row r="49" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="93"/>
+      <c r="A49" s="97"/>
       <c r="B49" s="80" t="s">
         <v>179</v>
       </c>
@@ -7489,8 +7489,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="93"/>
+    <row r="50" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="97"/>
       <c r="B50" s="80" t="s">
         <v>179</v>
       </c>
@@ -7541,8 +7541,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="102" x14ac:dyDescent="0.3">
-      <c r="A51" s="93"/>
+    <row r="51" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="97"/>
       <c r="B51" s="80" t="s">
         <v>179</v>
       </c>
@@ -7593,8 +7593,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="93"/>
+    <row r="52" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="97"/>
       <c r="B52" s="80" t="s">
         <v>179</v>
       </c>
@@ -7646,7 +7646,7 @@
       </c>
     </row>
     <row r="53" spans="1:19" ht="45.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="93"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="80" t="s">
         <v>179</v>
       </c>
@@ -7697,8 +7697,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="93"/>
+    <row r="54" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="97"/>
       <c r="B54" s="80" t="s">
         <v>194</v>
       </c>
@@ -7749,7 +7749,7 @@
       </c>
     </row>
     <row r="55" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="93"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="80" t="s">
         <v>194</v>
       </c>
@@ -7800,8 +7800,8 @@
       </c>
       <c r="S55" s="75"/>
     </row>
-    <row r="56" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="93"/>
+    <row r="56" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="97"/>
       <c r="B56" s="80" t="s">
         <v>194</v>
       </c>
@@ -7857,7 +7857,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="93"/>
+      <c r="A57" s="97"/>
       <c r="B57" s="80" t="s">
         <v>194</v>
       </c>
@@ -7911,7 +7911,7 @@
       <c r="S57" s="80"/>
     </row>
     <row r="58" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="93"/>
+      <c r="A58" s="97"/>
       <c r="B58" s="80" t="s">
         <v>194</v>
       </c>
@@ -7967,8 +7967,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="95"/>
+    <row r="59" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="104"/>
       <c r="B59" s="80" t="s">
         <v>206</v>
       </c>
@@ -8022,7 +8022,7 @@
       </c>
     </row>
     <row r="60" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="95"/>
+      <c r="A60" s="104"/>
       <c r="B60" s="80" t="s">
         <v>206</v>
       </c>
@@ -8075,7 +8075,7 @@
       </c>
     </row>
     <row r="61" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="93"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="70" t="s">
         <v>206</v>
       </c>
@@ -8126,7 +8126,7 @@
       </c>
     </row>
     <row r="62" spans="1:19" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="99">
+      <c r="A62" s="103">
         <v>14</v>
       </c>
       <c r="B62" s="80" t="s">
@@ -8180,8 +8180,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="94"/>
+    <row r="63" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="108"/>
       <c r="B63" s="80" t="s">
         <v>212</v>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
     </row>
     <row r="64" spans="1:19" ht="107.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="95"/>
+      <c r="A64" s="104"/>
       <c r="B64" s="80" t="s">
         <v>212</v>
       </c>
@@ -8391,7 +8391,7 @@
       </c>
     </row>
     <row r="67" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="99">
+      <c r="A67" s="103">
         <v>16</v>
       </c>
       <c r="B67" s="80" t="s">
@@ -8444,7 +8444,7 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="95"/>
+      <c r="A68" s="104"/>
       <c r="B68" s="80" t="s">
         <v>227</v>
       </c>
@@ -8494,7 +8494,7 @@
       </c>
     </row>
     <row r="69" spans="1:19" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="99">
+      <c r="A69" s="103">
         <v>17</v>
       </c>
       <c r="B69" s="80" t="s">
@@ -8547,7 +8547,7 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="94"/>
+      <c r="A70" s="108"/>
       <c r="B70" s="80" t="s">
         <v>233</v>
       </c>
@@ -8598,8 +8598,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
+    <row r="71" spans="1:19" ht="67.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="108"/>
       <c r="B71" s="80" t="s">
         <v>239</v>
       </c>
@@ -8651,7 +8651,7 @@
       </c>
     </row>
     <row r="72" spans="1:19" ht="174.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="94"/>
+      <c r="A72" s="108"/>
       <c r="B72" s="80" t="s">
         <v>242</v>
       </c>
@@ -8703,8 +8703,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="94"/>
+    <row r="73" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="108"/>
       <c r="B73" s="80" t="s">
         <v>242</v>
       </c>
@@ -8754,7 +8754,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="94"/>
+      <c r="A74" s="108"/>
       <c r="B74" s="80" t="s">
         <v>242</v>
       </c>
@@ -8806,7 +8806,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="94"/>
+      <c r="A75" s="108"/>
       <c r="B75" s="80" t="s">
         <v>242</v>
       </c>
@@ -8863,8 +8863,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="94"/>
+    <row r="76" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="108"/>
       <c r="B76" s="80" t="s">
         <v>242</v>
       </c>
@@ -8914,7 +8914,7 @@
       <c r="S76" s="80"/>
     </row>
     <row r="77" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="95"/>
+      <c r="A77" s="104"/>
       <c r="B77" s="80" t="s">
         <v>242</v>
       </c>
@@ -8968,7 +8968,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="94"/>
+      <c r="A78" s="108"/>
       <c r="B78" s="80" t="s">
         <v>253</v>
       </c>
@@ -9026,7 +9026,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="94"/>
+      <c r="A79" s="108"/>
       <c r="B79" s="80" t="s">
         <v>253</v>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="94"/>
+      <c r="A80" s="108"/>
       <c r="B80" s="80" t="s">
         <v>253</v>
       </c>
@@ -9130,7 +9130,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="1:20" ht="150.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="94"/>
+      <c r="A81" s="108"/>
       <c r="B81" s="80" t="s">
         <v>253</v>
       </c>
@@ -9183,7 +9183,7 @@
       </c>
     </row>
     <row r="82" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="94"/>
+      <c r="A82" s="108"/>
       <c r="B82" s="80" t="s">
         <v>262</v>
       </c>
@@ -9237,8 +9237,8 @@
       </c>
       <c r="T82" s="36"/>
     </row>
-    <row r="83" spans="1:20" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="94"/>
+    <row r="83" spans="1:20" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="108"/>
       <c r="B83" s="80" t="s">
         <v>262</v>
       </c>
@@ -9289,8 +9289,8 @@
       </c>
       <c r="T83" s="36"/>
     </row>
-    <row r="84" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A84" s="94"/>
+    <row r="84" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="108"/>
       <c r="B84" s="80" t="s">
         <v>262</v>
       </c>
@@ -9341,8 +9341,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A85" s="94"/>
+    <row r="85" spans="1:20" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="108"/>
       <c r="B85" s="80" t="s">
         <v>262</v>
       </c>
@@ -9393,7 +9393,7 @@
       <c r="T85" s="36"/>
     </row>
     <row r="86" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="94"/>
+      <c r="A86" s="108"/>
       <c r="B86" s="80" t="s">
         <v>262</v>
       </c>
@@ -9448,7 +9448,7 @@
       <c r="T86" s="36"/>
     </row>
     <row r="87" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="94"/>
+      <c r="A87" s="108"/>
       <c r="B87" s="80" t="s">
         <v>262</v>
       </c>
@@ -9502,8 +9502,8 @@
       </c>
       <c r="T87" s="36"/>
     </row>
-    <row r="88" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A88" s="94"/>
+    <row r="88" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="108"/>
       <c r="B88" s="80" t="s">
         <v>262</v>
       </c>
@@ -9557,8 +9557,8 @@
       </c>
       <c r="T88" s="36"/>
     </row>
-    <row r="89" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A89" s="94"/>
+    <row r="89" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="108"/>
       <c r="B89" s="80" t="s">
         <v>262</v>
       </c>
@@ -9611,7 +9611,7 @@
       <c r="T89" s="36"/>
     </row>
     <row r="90" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="94"/>
+      <c r="A90" s="108"/>
       <c r="B90" s="75" t="s">
         <v>262</v>
       </c>
@@ -9657,8 +9657,8 @@
       </c>
       <c r="T90" s="36"/>
     </row>
-    <row r="91" spans="1:20" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="94"/>
+    <row r="91" spans="1:20" ht="43.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="108"/>
       <c r="B91" s="80" t="s">
         <v>282</v>
       </c>
@@ -9682,29 +9682,29 @@
       </c>
       <c r="I91" s="80"/>
       <c r="J91" s="80"/>
-      <c r="K91" s="113">
+      <c r="K91" s="94">
         <v>12438994717</v>
       </c>
-      <c r="L91" s="113">
+      <c r="L91" s="94">
         <v>0</v>
       </c>
-      <c r="M91" s="113">
+      <c r="M91" s="94">
         <f>+K91</f>
         <v>12438994717</v>
       </c>
-      <c r="N91" s="93" t="s">
+      <c r="N91" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="93" t="s">
+      <c r="O91" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="P91" s="93">
+      <c r="P91" s="97">
         <v>2026</v>
       </c>
       <c r="Q91" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="R91" s="110">
+      <c r="R91" s="99">
         <v>0</v>
       </c>
       <c r="S91" s="98" t="s">
@@ -9713,7 +9713,7 @@
       <c r="T91" s="36"/>
     </row>
     <row r="92" spans="1:20" ht="40.799999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="94"/>
+      <c r="A92" s="108"/>
       <c r="B92" s="80" t="s">
         <v>282</v>
       </c>
@@ -9737,18 +9737,18 @@
       </c>
       <c r="I92" s="80"/>
       <c r="J92" s="80"/>
-      <c r="K92" s="114"/>
-      <c r="L92" s="114"/>
-      <c r="M92" s="114"/>
-      <c r="N92" s="93"/>
-      <c r="O92" s="93"/>
-      <c r="P92" s="93"/>
+      <c r="K92" s="95"/>
+      <c r="L92" s="95"/>
+      <c r="M92" s="95"/>
+      <c r="N92" s="97"/>
+      <c r="O92" s="97"/>
+      <c r="P92" s="97"/>
       <c r="Q92" s="98"/>
-      <c r="R92" s="110"/>
+      <c r="R92" s="99"/>
       <c r="S92" s="98"/>
     </row>
     <row r="93" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="94"/>
+      <c r="A93" s="108"/>
       <c r="B93" s="80" t="s">
         <v>282</v>
       </c>
@@ -9772,9 +9772,9 @@
       </c>
       <c r="I93" s="80"/>
       <c r="J93" s="80"/>
-      <c r="K93" s="114"/>
-      <c r="L93" s="114"/>
-      <c r="M93" s="114"/>
+      <c r="K93" s="95"/>
+      <c r="L93" s="95"/>
+      <c r="M93" s="95"/>
       <c r="N93" s="75" t="s">
         <v>26</v>
       </c>
@@ -9795,7 +9795,7 @@
       </c>
     </row>
     <row r="94" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="94"/>
+      <c r="A94" s="108"/>
       <c r="B94" s="80" t="s">
         <v>282</v>
       </c>
@@ -9817,9 +9817,9 @@
       </c>
       <c r="I94" s="80"/>
       <c r="J94" s="80"/>
-      <c r="K94" s="114"/>
-      <c r="L94" s="114"/>
-      <c r="M94" s="114"/>
+      <c r="K94" s="95"/>
+      <c r="L94" s="95"/>
+      <c r="M94" s="95"/>
       <c r="N94" s="75" t="s">
         <v>26</v>
       </c>
@@ -9840,7 +9840,7 @@
       </c>
     </row>
     <row r="95" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="94"/>
+      <c r="A95" s="108"/>
       <c r="B95" s="80" t="s">
         <v>282</v>
       </c>
@@ -9864,9 +9864,9 @@
       </c>
       <c r="I95" s="75"/>
       <c r="J95" s="75"/>
-      <c r="K95" s="114"/>
-      <c r="L95" s="114"/>
-      <c r="M95" s="114"/>
+      <c r="K95" s="95"/>
+      <c r="L95" s="95"/>
+      <c r="M95" s="95"/>
       <c r="N95" s="75" t="s">
         <v>146</v>
       </c>
@@ -9887,7 +9887,7 @@
       </c>
     </row>
     <row r="96" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="94"/>
+      <c r="A96" s="108"/>
       <c r="B96" s="80" t="s">
         <v>290</v>
       </c>
@@ -9915,9 +9915,9 @@
       <c r="J96" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="K96" s="114"/>
-      <c r="L96" s="114"/>
-      <c r="M96" s="114"/>
+      <c r="K96" s="95"/>
+      <c r="L96" s="95"/>
+      <c r="M96" s="95"/>
       <c r="N96" s="75" t="s">
         <v>26</v>
       </c>
@@ -9936,7 +9936,7 @@
       </c>
     </row>
     <row r="97" spans="1:19" ht="99.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="94"/>
+      <c r="A97" s="108"/>
       <c r="B97" s="80" t="s">
         <v>290</v>
       </c>
@@ -9964,9 +9964,9 @@
       <c r="J97" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="K97" s="114"/>
-      <c r="L97" s="114"/>
-      <c r="M97" s="114"/>
+      <c r="K97" s="95"/>
+      <c r="L97" s="95"/>
+      <c r="M97" s="95"/>
       <c r="N97" s="75" t="s">
         <v>98</v>
       </c>
@@ -9987,7 +9987,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="94"/>
+      <c r="A98" s="108"/>
       <c r="B98" s="80" t="s">
         <v>299</v>
       </c>
@@ -10011,9 +10011,9 @@
       </c>
       <c r="I98" s="75"/>
       <c r="J98" s="75"/>
-      <c r="K98" s="114"/>
-      <c r="L98" s="114"/>
-      <c r="M98" s="114"/>
+      <c r="K98" s="95"/>
+      <c r="L98" s="95"/>
+      <c r="M98" s="95"/>
       <c r="N98" s="75" t="s">
         <v>146</v>
       </c>
@@ -10034,7 +10034,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="94"/>
+      <c r="A99" s="108"/>
       <c r="B99" s="80" t="s">
         <v>299</v>
       </c>
@@ -10058,9 +10058,9 @@
       </c>
       <c r="I99" s="75"/>
       <c r="J99" s="75"/>
-      <c r="K99" s="114"/>
-      <c r="L99" s="114"/>
-      <c r="M99" s="114"/>
+      <c r="K99" s="95"/>
+      <c r="L99" s="95"/>
+      <c r="M99" s="95"/>
       <c r="N99" s="75" t="s">
         <v>72</v>
       </c>
@@ -10080,8 +10080,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="94"/>
+    <row r="100" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="108"/>
       <c r="B100" s="80" t="s">
         <v>299</v>
       </c>
@@ -10105,9 +10105,9 @@
       </c>
       <c r="I100" s="80"/>
       <c r="J100" s="80"/>
-      <c r="K100" s="115"/>
-      <c r="L100" s="115"/>
-      <c r="M100" s="115"/>
+      <c r="K100" s="96"/>
+      <c r="L100" s="96"/>
+      <c r="M100" s="96"/>
       <c r="N100" s="75" t="s">
         <v>35</v>
       </c>
@@ -10128,7 +10128,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="94"/>
+      <c r="A101" s="108"/>
       <c r="B101" s="80" t="s">
         <v>299</v>
       </c>
@@ -10182,7 +10182,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="94"/>
+      <c r="A102" s="108"/>
       <c r="B102" s="80" t="s">
         <v>299</v>
       </c>
@@ -10230,8 +10230,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="94"/>
+    <row r="103" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="108"/>
       <c r="B103" s="80" t="s">
         <v>299</v>
       </c>
@@ -10280,8 +10280,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="94"/>
+    <row r="104" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="108"/>
       <c r="B104" s="80" t="s">
         <v>299</v>
       </c>
@@ -10333,7 +10333,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="1:19" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="94"/>
+      <c r="A105" s="108"/>
       <c r="B105" s="80" t="s">
         <v>299</v>
       </c>
@@ -10384,8 +10384,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="142.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A106" s="94"/>
+    <row r="106" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="108"/>
       <c r="B106" s="80" t="s">
         <v>311</v>
       </c>
@@ -10434,7 +10434,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="94"/>
+      <c r="A107" s="108"/>
       <c r="B107" s="80" t="s">
         <v>317</v>
       </c>
@@ -10476,8 +10476,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A108" s="94"/>
+    <row r="108" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="108"/>
       <c r="B108" s="80" t="s">
         <v>317</v>
       </c>
@@ -10527,7 +10527,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="94"/>
+      <c r="A109" s="108"/>
       <c r="B109" s="80" t="s">
         <v>317</v>
       </c>
@@ -10578,8 +10578,8 @@
       </c>
       <c r="S109" s="80"/>
     </row>
-    <row r="110" spans="1:19" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="94"/>
+    <row r="110" spans="1:19" ht="60.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="108"/>
       <c r="B110" s="80" t="s">
         <v>322</v>
       </c>
@@ -10635,7 +10635,7 @@
       <c r="S110" s="80"/>
     </row>
     <row r="111" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="94"/>
+      <c r="A111" s="108"/>
       <c r="B111" s="80" t="s">
         <v>324</v>
       </c>
@@ -10685,7 +10685,7 @@
       </c>
     </row>
     <row r="112" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="94"/>
+      <c r="A112" s="108"/>
       <c r="B112" s="80" t="s">
         <v>324</v>
       </c>
@@ -10735,7 +10735,7 @@
       </c>
     </row>
     <row r="113" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="94"/>
+      <c r="A113" s="108"/>
       <c r="B113" s="80" t="s">
         <v>324</v>
       </c>
@@ -10774,7 +10774,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="22.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="94"/>
+      <c r="A114" s="108"/>
       <c r="B114" s="80" t="s">
         <v>324</v>
       </c>
@@ -10827,8 +10827,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="94"/>
+    <row r="115" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="108"/>
       <c r="B115" s="80" t="s">
         <v>334</v>
       </c>
@@ -10885,8 +10885,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A116" s="95"/>
+    <row r="116" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="104"/>
       <c r="B116" s="80" t="s">
         <v>339</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="81">
         <v>29</v>
       </c>
@@ -10994,7 +10994,7 @@
       <c r="S117" s="80"/>
     </row>
     <row r="118" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="93">
+      <c r="A118" s="97">
         <v>30</v>
       </c>
       <c r="B118" s="80" t="s">
@@ -11046,7 +11046,7 @@
       <c r="S118" s="80"/>
     </row>
     <row r="119" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="93"/>
+      <c r="A119" s="97"/>
       <c r="B119" s="80" t="s">
         <v>344</v>
       </c>
@@ -11098,7 +11098,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="107">
+      <c r="A120" s="113">
         <v>31</v>
       </c>
       <c r="B120" s="80" t="s">
@@ -11201,7 +11201,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="142.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="98"/>
       <c r="B122" s="80" t="s">
         <v>347</v>
@@ -11253,7 +11253,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="98"/>
       <c r="B123" s="80" t="s">
         <v>347</v>
@@ -11357,7 +11357,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="75"/>
       <c r="B125" s="80" t="s">
         <v>356</v>
@@ -11409,7 +11409,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="75"/>
       <c r="B126" s="80" t="s">
         <v>356</v>
@@ -11512,7 +11512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="77"/>
       <c r="B128" s="80" t="s">
         <v>366</v>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="S129" s="75"/>
     </row>
-    <row r="130" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="77"/>
       <c r="B130" s="80" t="s">
         <v>371</v>
@@ -11723,7 +11723,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="93">
+      <c r="A132" s="97">
         <v>35</v>
       </c>
       <c r="B132" s="80" t="s">
@@ -11779,7 +11779,7 @@
       </c>
     </row>
     <row r="133" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="93"/>
+      <c r="A133" s="97"/>
       <c r="B133" s="80" t="s">
         <v>371</v>
       </c>
@@ -11831,7 +11831,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="93"/>
+      <c r="A134" s="97"/>
       <c r="B134" s="80" t="s">
         <v>371</v>
       </c>
@@ -11888,8 +11888,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A135" s="93"/>
+    <row r="135" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="97"/>
       <c r="B135" s="80" t="s">
         <v>371</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="125.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="75"/>
       <c r="B136" s="80" t="s">
         <v>380</v>
@@ -11997,8 +11997,8 @@
       </c>
       <c r="S136" s="80"/>
     </row>
-    <row r="137" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="93">
+    <row r="137" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A137" s="97">
         <v>36</v>
       </c>
       <c r="B137" s="80" t="s">
@@ -12051,8 +12051,8 @@
       </c>
       <c r="S137" s="80"/>
     </row>
-    <row r="138" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="93"/>
+    <row r="138" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="97"/>
       <c r="B138" s="80" t="s">
         <v>380</v>
       </c>
@@ -12103,8 +12103,8 @@
       </c>
       <c r="S138" s="80"/>
     </row>
-    <row r="139" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="93"/>
+    <row r="139" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="97"/>
       <c r="B139" s="80" t="s">
         <v>380</v>
       </c>
@@ -12155,8 +12155,8 @@
       </c>
       <c r="S139" s="80"/>
     </row>
-    <row r="140" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="93"/>
+    <row r="140" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="97"/>
       <c r="B140" s="80" t="s">
         <v>380</v>
       </c>
@@ -12206,8 +12206,8 @@
       </c>
       <c r="S140" s="80"/>
     </row>
-    <row r="141" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="93"/>
+    <row r="141" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A141" s="97"/>
       <c r="B141" s="80" t="s">
         <v>380</v>
       </c>
@@ -12258,8 +12258,8 @@
       </c>
       <c r="S141" s="80"/>
     </row>
-    <row r="142" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="93"/>
+    <row r="142" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A142" s="97"/>
       <c r="B142" s="80" t="s">
         <v>380</v>
       </c>
@@ -12311,7 +12311,7 @@
       <c r="S142" s="75"/>
     </row>
     <row r="143" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A143" s="93"/>
+      <c r="A143" s="97"/>
       <c r="B143" s="80" t="s">
         <v>380</v>
       </c>
@@ -12362,8 +12362,8 @@
       </c>
       <c r="S143" s="80"/>
     </row>
-    <row r="144" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="93">
+    <row r="144" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A144" s="97">
         <v>37</v>
       </c>
       <c r="B144" s="80" t="s">
@@ -12418,8 +12418,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="93"/>
+    <row r="145" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="97"/>
       <c r="B145" s="80" t="s">
         <v>396</v>
       </c>
@@ -12468,8 +12468,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:19" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="93"/>
+    <row r="146" spans="1:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="97"/>
       <c r="B146" s="80" t="s">
         <v>396</v>
       </c>
@@ -12573,7 +12573,7 @@
       </c>
     </row>
     <row r="148" spans="1:19" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="94"/>
+      <c r="A148" s="108"/>
       <c r="B148" s="80" t="s">
         <v>401</v>
       </c>
@@ -12624,7 +12624,7 @@
       </c>
     </row>
     <row r="149" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="95"/>
+      <c r="A149" s="104"/>
       <c r="B149" s="80" t="s">
         <v>401</v>
       </c>
@@ -12676,7 +12676,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="77"/>
       <c r="B150" s="80" t="s">
         <v>406</v>
@@ -12785,7 +12785,7 @@
       </c>
     </row>
     <row r="152" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="99">
+      <c r="A152" s="103">
         <v>40</v>
       </c>
       <c r="B152" s="80" t="s">
@@ -12841,7 +12841,7 @@
       </c>
     </row>
     <row r="153" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="94"/>
+      <c r="A153" s="108"/>
       <c r="B153" s="80" t="s">
         <v>412</v>
       </c>
@@ -12890,7 +12890,7 @@
       </c>
     </row>
     <row r="154" spans="1:19" ht="183.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="94"/>
+      <c r="A154" s="108"/>
       <c r="B154" s="80" t="s">
         <v>412</v>
       </c>
@@ -12937,7 +12937,7 @@
       </c>
     </row>
     <row r="155" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="94"/>
+      <c r="A155" s="108"/>
       <c r="B155" s="80" t="s">
         <v>412</v>
       </c>
@@ -12986,7 +12986,7 @@
       </c>
     </row>
     <row r="156" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="94"/>
+      <c r="A156" s="108"/>
       <c r="B156" s="80" t="s">
         <v>412</v>
       </c>
@@ -13040,7 +13040,7 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="94"/>
+      <c r="A157" s="108"/>
       <c r="B157" s="80" t="s">
         <v>412</v>
       </c>
@@ -13094,7 +13094,7 @@
       </c>
     </row>
     <row r="158" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="94"/>
+      <c r="A158" s="108"/>
       <c r="B158" s="80" t="s">
         <v>412</v>
       </c>
@@ -13148,7 +13148,7 @@
       </c>
     </row>
     <row r="159" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="94"/>
+      <c r="A159" s="108"/>
       <c r="B159" s="80" t="s">
         <v>426</v>
       </c>
@@ -13197,8 +13197,8 @@
       </c>
       <c r="S159" s="80"/>
     </row>
-    <row r="160" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A160" s="94"/>
+    <row r="160" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="108"/>
       <c r="B160" s="80" t="s">
         <v>426</v>
       </c>
@@ -13251,7 +13251,7 @@
       <c r="S160" s="80"/>
     </row>
     <row r="161" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="94"/>
+      <c r="A161" s="108"/>
       <c r="B161" s="80" t="s">
         <v>426</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="S161" s="80"/>
     </row>
     <row r="162" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="94"/>
+      <c r="A162" s="108"/>
       <c r="B162" s="80" t="s">
         <v>426</v>
       </c>
@@ -13355,7 +13355,7 @@
       </c>
     </row>
     <row r="163" spans="1:19" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="95"/>
+      <c r="A163" s="104"/>
       <c r="B163" s="80" t="s">
         <v>434</v>
       </c>
@@ -13406,7 +13406,7 @@
       </c>
     </row>
     <row r="164" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="94"/>
+      <c r="A164" s="108"/>
       <c r="B164" s="80" t="s">
         <v>434</v>
       </c>
@@ -13457,7 +13457,7 @@
       </c>
     </row>
     <row r="165" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="95"/>
+      <c r="A165" s="104"/>
       <c r="B165" s="80" t="s">
         <v>434</v>
       </c>
@@ -13625,8 +13625,8 @@
         <v>447</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="100">
+    <row r="168" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A168" s="109">
         <v>44</v>
       </c>
       <c r="B168" s="80" t="s">
@@ -13683,8 +13683,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="169" spans="1:19" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="101"/>
+    <row r="169" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="110"/>
       <c r="B169" s="80" t="s">
         <v>448</v>
       </c>
@@ -13732,8 +13732,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="101"/>
+    <row r="170" spans="1:19" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="110"/>
       <c r="B170" s="80" t="s">
         <v>448</v>
       </c>
@@ -13788,8 +13788,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="171" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="101"/>
+    <row r="171" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A171" s="110"/>
       <c r="B171" s="80" t="s">
         <v>448</v>
       </c>
@@ -13842,8 +13842,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="102"/>
+    <row r="172" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A172" s="111"/>
       <c r="B172" s="80" t="s">
         <v>455</v>
       </c>
@@ -13896,8 +13896,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="173" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="93">
+    <row r="173" spans="1:19" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="97">
         <v>45</v>
       </c>
       <c r="B173" s="80" t="s">
@@ -13951,8 +13951,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="93"/>
+    <row r="174" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A174" s="97"/>
       <c r="B174" s="80" t="s">
         <v>457</v>
       </c>
@@ -14006,7 +14006,7 @@
       </c>
     </row>
     <row r="175" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A175" s="93"/>
+      <c r="A175" s="97"/>
       <c r="B175" s="80" t="s">
         <v>457</v>
       </c>
@@ -14057,8 +14057,8 @@
       </c>
       <c r="S175" s="80"/>
     </row>
-    <row r="176" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="93"/>
+    <row r="176" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A176" s="97"/>
       <c r="B176" s="80" t="s">
         <v>457</v>
       </c>
@@ -14111,8 +14111,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="177" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="93"/>
+    <row r="177" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A177" s="97"/>
       <c r="B177" s="80" t="s">
         <v>457</v>
       </c>
@@ -14163,8 +14163,8 @@
       </c>
       <c r="S177" s="80"/>
     </row>
-    <row r="178" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="93"/>
+    <row r="178" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A178" s="97"/>
       <c r="B178" s="80" t="s">
         <v>465</v>
       </c>
@@ -14217,8 +14217,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="93"/>
+    <row r="179" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A179" s="97"/>
       <c r="B179" s="80" t="s">
         <v>467</v>
       </c>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="S179" s="75"/>
     </row>
-    <row r="180" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A180" s="84"/>
       <c r="B180" s="80" t="s">
         <v>470</v>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="S180" s="75"/>
     </row>
-    <row r="181" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="84"/>
       <c r="B181" s="80" t="s">
         <v>470</v>
@@ -14372,8 +14372,8 @@
       </c>
       <c r="S181" s="75"/>
     </row>
-    <row r="182" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="103">
+    <row r="182" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="112">
         <v>46</v>
       </c>
       <c r="B182" s="80" t="s">
@@ -14425,7 +14425,7 @@
       </c>
     </row>
     <row r="183" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="103"/>
+      <c r="A183" s="112"/>
       <c r="B183" s="80" t="s">
         <v>470</v>
       </c>
@@ -14476,8 +14476,8 @@
         <v>480</v>
       </c>
     </row>
-    <row r="184" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="103"/>
+    <row r="184" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A184" s="112"/>
       <c r="B184" s="80" t="s">
         <v>470</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="185" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A185" s="81"/>
       <c r="B185" s="80" t="s">
         <v>482</v>
@@ -14586,8 +14586,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="186" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="101"/>
+    <row r="186" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A186" s="110"/>
       <c r="B186" s="80" t="s">
         <v>482</v>
       </c>
@@ -14635,7 +14635,7 @@
       </c>
     </row>
     <row r="187" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A187" s="101"/>
+      <c r="A187" s="110"/>
       <c r="B187" s="80" t="s">
         <v>482</v>
       </c>
@@ -14684,8 +14684,8 @@
       <c r="R187" s="89"/>
       <c r="S187" s="80"/>
     </row>
-    <row r="188" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="102"/>
+    <row r="188" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="111"/>
       <c r="B188" s="80" t="s">
         <v>482</v>
       </c>
@@ -14734,7 +14734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:19" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" ht="81" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="75"/>
       <c r="B189" s="80" t="s">
         <v>489</v>
@@ -14746,7 +14746,7 @@
         <v>21</v>
       </c>
       <c r="E189" s="90" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F189" s="80" t="s">
         <v>490</v>
@@ -14787,7 +14787,7 @@
       </c>
     </row>
     <row r="190" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="93">
+      <c r="A190" s="97">
         <v>48</v>
       </c>
       <c r="B190" s="80" t="s">
@@ -14840,7 +14840,7 @@
       </c>
     </row>
     <row r="191" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="93"/>
+      <c r="A191" s="97"/>
       <c r="B191" s="80" t="s">
         <v>489</v>
       </c>
@@ -14890,8 +14890,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A192" s="93"/>
+    <row r="192" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="97"/>
       <c r="B192" s="80" t="s">
         <v>489</v>
       </c>
@@ -14972,7 +14972,7 @@
       <c r="S193" s="75"/>
     </row>
     <row r="194" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="94"/>
+      <c r="A194" s="108"/>
       <c r="B194" s="80" t="s">
         <v>500</v>
       </c>
@@ -15024,7 +15024,7 @@
       </c>
     </row>
     <row r="195" spans="1:19" ht="24.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="95"/>
+      <c r="A195" s="104"/>
       <c r="B195" s="80" t="s">
         <v>500</v>
       </c>
@@ -15076,7 +15076,7 @@
       </c>
     </row>
     <row r="196" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="93">
+      <c r="A196" s="97">
         <v>51</v>
       </c>
       <c r="B196" s="80" t="s">
@@ -15129,7 +15129,7 @@
       </c>
     </row>
     <row r="197" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="93"/>
+      <c r="A197" s="97"/>
       <c r="B197" s="80" t="s">
         <v>504</v>
       </c>
@@ -15183,7 +15183,7 @@
       </c>
     </row>
     <row r="198" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="93"/>
+      <c r="A198" s="97"/>
       <c r="B198" s="80" t="s">
         <v>504</v>
       </c>
@@ -15237,7 +15237,7 @@
       </c>
     </row>
     <row r="199" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="93"/>
+      <c r="A199" s="97"/>
       <c r="B199" s="80" t="s">
         <v>504</v>
       </c>
@@ -15387,7 +15387,7 @@
       <c r="R201" s="79"/>
       <c r="S201" s="75"/>
     </row>
-    <row r="202" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="75">
         <v>52</v>
       </c>
@@ -15444,7 +15444,7 @@
       </c>
     </row>
     <row r="203" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="93">
+      <c r="A203" s="97">
         <v>53</v>
       </c>
       <c r="B203" s="80" t="s">
@@ -15498,8 +15498,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A204" s="93"/>
+    <row r="204" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="97"/>
       <c r="B204" s="80" t="s">
         <v>516</v>
       </c>
@@ -15553,7 +15553,7 @@
       </c>
     </row>
     <row r="205" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="93"/>
+      <c r="A205" s="97"/>
       <c r="B205" s="75" t="s">
         <v>520</v>
       </c>
@@ -15607,7 +15607,7 @@
       </c>
     </row>
     <row r="206" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="93">
+      <c r="A206" s="97">
         <v>54</v>
       </c>
       <c r="B206" s="80" t="s">
@@ -15660,8 +15660,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A207" s="93"/>
+    <row r="207" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="97"/>
       <c r="B207" s="80" t="s">
         <v>523</v>
       </c>
@@ -15716,8 +15716,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:19" ht="32.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="93">
+    <row r="208" spans="1:19" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="97">
         <v>55</v>
       </c>
       <c r="B208" s="80" t="s">
@@ -15772,7 +15772,7 @@
       </c>
     </row>
     <row r="209" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A209" s="93"/>
+      <c r="A209" s="97"/>
       <c r="B209" s="80" t="s">
         <v>526</v>
       </c>
@@ -15823,8 +15823,8 @@
       </c>
       <c r="S209" s="80"/>
     </row>
-    <row r="210" spans="1:19" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="93"/>
+    <row r="210" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="97"/>
       <c r="B210" s="80" t="s">
         <v>526</v>
       </c>
@@ -15876,7 +15876,7 @@
       <c r="S210" s="75"/>
     </row>
     <row r="211" spans="1:19" ht="80.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="93">
+      <c r="A211" s="97">
         <v>56</v>
       </c>
       <c r="B211" s="80" t="s">
@@ -15928,8 +15928,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A212" s="93"/>
+    <row r="212" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="97"/>
       <c r="B212" s="80" t="s">
         <v>535</v>
       </c>
@@ -15984,8 +15984,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="213" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="100">
+    <row r="213" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A213" s="109">
         <v>57</v>
       </c>
       <c r="B213" s="80" t="s">
@@ -16037,8 +16037,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="101"/>
+    <row r="214" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A214" s="110"/>
       <c r="B214" s="80" t="s">
         <v>537</v>
       </c>
@@ -16091,8 +16091,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="101"/>
+    <row r="215" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A215" s="110"/>
       <c r="B215" s="80" t="s">
         <v>537</v>
       </c>
@@ -16145,8 +16145,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="94"/>
+    <row r="216" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A216" s="108"/>
       <c r="B216" s="80" t="s">
         <v>537</v>
       </c>
@@ -16198,8 +16198,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="102"/>
+    <row r="217" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A217" s="111"/>
       <c r="B217" s="80" t="s">
         <v>537</v>
       </c>
@@ -16252,7 +16252,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A218" s="83"/>
       <c r="B218" s="80" t="s">
         <v>548</v>
@@ -16306,7 +16306,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A219" s="83"/>
       <c r="B219" s="80" t="s">
         <v>548</v>
@@ -16468,7 +16468,7 @@
       </c>
     </row>
     <row r="222" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="93">
+      <c r="A222" s="97">
         <v>59</v>
       </c>
       <c r="B222" s="80" t="s">
@@ -16520,8 +16520,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="93"/>
+    <row r="223" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="97"/>
       <c r="B223" s="80" t="s">
         <v>558</v>
       </c>
@@ -16575,7 +16575,7 @@
       </c>
     </row>
     <row r="224" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="93"/>
+      <c r="A224" s="97"/>
       <c r="B224" s="80" t="s">
         <v>558</v>
       </c>
@@ -16624,7 +16624,7 @@
       <c r="S224" s="80"/>
     </row>
     <row r="225" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="93"/>
+      <c r="A225" s="97"/>
       <c r="B225" s="80" t="s">
         <v>558</v>
       </c>
@@ -16677,8 +16677,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="226" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A226" s="93"/>
+    <row r="226" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="97"/>
       <c r="B226" s="80" t="s">
         <v>558</v>
       </c>
@@ -16728,7 +16728,7 @@
       <c r="S226" s="75"/>
     </row>
     <row r="227" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="93"/>
+      <c r="A227" s="97"/>
       <c r="B227" s="80" t="s">
         <v>558</v>
       </c>
@@ -16781,7 +16781,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="228" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="75"/>
       <c r="B228" s="80" t="s">
         <v>570</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="S229" s="75"/>
     </row>
-    <row r="230" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="75"/>
       <c r="B230" s="80" t="s">
         <v>570</v>
@@ -17017,7 +17017,7 @@
       <c r="R232" s="75"/>
       <c r="S232" s="75"/>
     </row>
-    <row r="233" spans="1:19" ht="224.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" ht="224.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="75">
         <v>62</v>
       </c>
@@ -17071,8 +17071,8 @@
         <v>578</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="99">
+    <row r="234" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="103">
         <v>63</v>
       </c>
       <c r="B234" s="80" t="s">
@@ -17085,7 +17085,7 @@
         <v>21</v>
       </c>
       <c r="E234" s="90" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F234" s="80" t="s">
         <v>580</v>
@@ -17123,8 +17123,8 @@
         <v>582</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="94"/>
+    <row r="235" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="108"/>
       <c r="B235" s="80" t="s">
         <v>579</v>
       </c>
@@ -17175,8 +17175,8 @@
         <v>585</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="94"/>
+    <row r="236" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="108"/>
       <c r="B236" s="80" t="s">
         <v>579</v>
       </c>
@@ -17227,8 +17227,8 @@
         <v>588</v>
       </c>
     </row>
-    <row r="237" spans="1:19" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="94"/>
+    <row r="237" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="108"/>
       <c r="B237" s="80" t="s">
         <v>579</v>
       </c>
@@ -17281,7 +17281,7 @@
       </c>
     </row>
     <row r="238" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="94"/>
+      <c r="A238" s="108"/>
       <c r="B238" s="80" t="s">
         <v>579</v>
       </c>
@@ -17334,7 +17334,7 @@
       </c>
     </row>
     <row r="239" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="95"/>
+      <c r="A239" s="104"/>
       <c r="B239" s="80" t="s">
         <v>592</v>
       </c>
@@ -17384,7 +17384,7 @@
       </c>
     </row>
     <row r="240" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="93">
+      <c r="A240" s="97">
         <v>64</v>
       </c>
       <c r="B240" s="80" t="s">
@@ -17436,8 +17436,8 @@
       </c>
       <c r="S240" s="80"/>
     </row>
-    <row r="241" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="93"/>
+    <row r="241" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="97"/>
       <c r="B241" s="80" t="s">
         <v>595</v>
       </c>
@@ -17489,7 +17489,7 @@
       </c>
     </row>
     <row r="242" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="93"/>
+      <c r="A242" s="97"/>
       <c r="B242" s="80" t="s">
         <v>595</v>
       </c>
@@ -17547,7 +17547,7 @@
       </c>
     </row>
     <row r="243" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="93"/>
+      <c r="A243" s="97"/>
       <c r="B243" s="80" t="s">
         <v>595</v>
       </c>
@@ -17597,7 +17597,7 @@
       </c>
     </row>
     <row r="244" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="93"/>
+      <c r="A244" s="97"/>
       <c r="B244" s="80" t="s">
         <v>595</v>
       </c>
@@ -17630,7 +17630,7 @@
       <c r="S244" s="80"/>
     </row>
     <row r="245" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="93"/>
+      <c r="A245" s="97"/>
       <c r="B245" s="80" t="s">
         <v>595</v>
       </c>
@@ -17680,7 +17680,7 @@
       </c>
     </row>
     <row r="246" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="93"/>
+      <c r="A246" s="97"/>
       <c r="B246" s="80" t="s">
         <v>595</v>
       </c>
@@ -17732,7 +17732,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="247" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="75"/>
       <c r="B247" s="80" t="s">
         <v>603</v>
@@ -17784,8 +17784,8 @@
       </c>
       <c r="S247" s="80"/>
     </row>
-    <row r="248" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="93">
+    <row r="248" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="97">
         <v>65</v>
       </c>
       <c r="B248" s="80" t="s">
@@ -17838,7 +17838,7 @@
       </c>
     </row>
     <row r="249" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="93"/>
+      <c r="A249" s="97"/>
       <c r="B249" s="80" t="s">
         <v>603</v>
       </c>
@@ -17889,8 +17889,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="250" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="93"/>
+    <row r="250" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="97"/>
       <c r="B250" s="80" t="s">
         <v>603</v>
       </c>
@@ -18072,7 +18072,7 @@
       <c r="S253" s="75"/>
     </row>
     <row r="254" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A254" s="99">
+      <c r="A254" s="103">
         <v>68</v>
       </c>
       <c r="B254" s="80" t="s">
@@ -18124,7 +18124,7 @@
       </c>
     </row>
     <row r="255" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A255" s="94"/>
+      <c r="A255" s="108"/>
       <c r="B255" s="80" t="s">
         <v>616</v>
       </c>
@@ -18176,8 +18176,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="256" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.7">
-      <c r="A256" s="94"/>
+    <row r="256" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A256" s="108"/>
       <c r="B256" s="80" t="s">
         <v>616</v>
       </c>
@@ -18230,8 +18230,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="257" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="94"/>
+    <row r="257" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A257" s="108"/>
       <c r="B257" s="80" t="s">
         <v>616</v>
       </c>
@@ -18284,8 +18284,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="258" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="94"/>
+    <row r="258" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A258" s="108"/>
       <c r="B258" s="80" t="s">
         <v>616</v>
       </c>
@@ -18336,8 +18336,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="259" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="95"/>
+    <row r="259" spans="1:19" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="104"/>
       <c r="B259" s="80" t="s">
         <v>616</v>
       </c>
@@ -18390,8 +18390,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="260" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A260" s="99">
+    <row r="260" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="103">
         <v>69</v>
       </c>
       <c r="B260" s="80" t="s">
@@ -18404,13 +18404,13 @@
         <v>21</v>
       </c>
       <c r="E260" s="90" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F260" s="85" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G260" s="80" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H260" s="80"/>
       <c r="I260" s="80"/>
@@ -18443,8 +18443,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="261" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="94"/>
+    <row r="261" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="108"/>
       <c r="B261" s="80" t="s">
         <v>626</v>
       </c>
@@ -18455,7 +18455,7 @@
         <v>21</v>
       </c>
       <c r="E261" s="90" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F261" s="80" t="s">
         <v>627</v>
@@ -18494,7 +18494,7 @@
       </c>
     </row>
     <row r="262" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="94"/>
+      <c r="A262" s="108"/>
       <c r="B262" s="80" t="s">
         <v>630</v>
       </c>
@@ -18540,7 +18540,7 @@
       </c>
     </row>
     <row r="263" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="94"/>
+      <c r="A263" s="108"/>
       <c r="B263" s="80" t="s">
         <v>630</v>
       </c>
@@ -18588,7 +18588,7 @@
       </c>
     </row>
     <row r="264" spans="1:19" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="94"/>
+      <c r="A264" s="108"/>
       <c r="B264" s="80" t="s">
         <v>626</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="265" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="76"/>
       <c r="B265" s="80" t="s">
         <v>636</v>
@@ -18695,7 +18695,7 @@
       <c r="S265" s="80"/>
     </row>
     <row r="266" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="93">
+      <c r="A266" s="97">
         <v>70</v>
       </c>
       <c r="B266" s="80" t="s">
@@ -18751,7 +18751,7 @@
       <c r="S266" s="80"/>
     </row>
     <row r="267" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="93"/>
+      <c r="A267" s="97"/>
       <c r="B267" s="80" t="s">
         <v>636</v>
       </c>
@@ -18805,7 +18805,7 @@
       <c r="S267" s="80"/>
     </row>
     <row r="268" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="93"/>
+      <c r="A268" s="97"/>
       <c r="B268" s="80" t="s">
         <v>636</v>
       </c>
@@ -18858,8 +18858,8 @@
       </c>
       <c r="S268" s="80"/>
     </row>
-    <row r="269" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="93"/>
+    <row r="269" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="97"/>
       <c r="B269" s="80" t="s">
         <v>636</v>
       </c>
@@ -18967,7 +18967,7 @@
       </c>
     </row>
     <row r="271" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="93">
+      <c r="A271" s="97">
         <v>71</v>
       </c>
       <c r="B271" s="80" t="s">
@@ -19020,8 +19020,8 @@
       </c>
       <c r="S271" s="80"/>
     </row>
-    <row r="272" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="93"/>
+    <row r="272" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="97"/>
       <c r="B272" s="80" t="s">
         <v>646</v>
       </c>
@@ -19074,8 +19074,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="273" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="93"/>
+    <row r="273" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A273" s="97"/>
       <c r="B273" s="80" t="s">
         <v>646</v>
       </c>
@@ -19128,8 +19128,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="274" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="93"/>
+    <row r="274" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A274" s="97"/>
       <c r="B274" s="80" t="s">
         <v>646</v>
       </c>
@@ -19182,8 +19182,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="275" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="93"/>
+    <row r="275" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A275" s="97"/>
       <c r="B275" s="75" t="s">
         <v>653</v>
       </c>
@@ -19344,7 +19344,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="75"/>
       <c r="B278" s="80" t="s">
         <v>658</v>
@@ -19449,7 +19449,7 @@
       <c r="S279" s="75"/>
     </row>
     <row r="280" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="93">
+      <c r="A280" s="97">
         <v>74</v>
       </c>
       <c r="B280" s="80" t="s">
@@ -19501,7 +19501,7 @@
       </c>
     </row>
     <row r="281" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="93"/>
+      <c r="A281" s="97"/>
       <c r="B281" s="80" t="s">
         <v>662</v>
       </c>
@@ -19548,7 +19548,7 @@
       <c r="S281" s="75"/>
     </row>
     <row r="282" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="93">
+      <c r="A282" s="97">
         <v>75</v>
       </c>
       <c r="B282" s="80" t="s">
@@ -19601,7 +19601,7 @@
       </c>
     </row>
     <row r="283" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="93"/>
+      <c r="A283" s="97"/>
       <c r="B283" s="80" t="s">
         <v>665</v>
       </c>
@@ -19652,8 +19652,8 @@
       </c>
       <c r="S283" s="80"/>
     </row>
-    <row r="284" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="95">
+    <row r="284" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A284" s="104">
         <v>76</v>
       </c>
       <c r="B284" s="80" t="s">
@@ -19708,8 +19708,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="285" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="95"/>
+    <row r="285" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A285" s="104"/>
       <c r="B285" s="80" t="s">
         <v>669</v>
       </c>
@@ -19762,8 +19762,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="286" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="95"/>
+    <row r="286" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A286" s="104"/>
       <c r="B286" s="80" t="s">
         <v>669</v>
       </c>
@@ -19816,8 +19816,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="287" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="95"/>
+    <row r="287" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A287" s="104"/>
       <c r="B287" s="80" t="s">
         <v>669</v>
       </c>
@@ -19870,8 +19870,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="288" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="93"/>
+    <row r="288" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A288" s="97"/>
       <c r="B288" s="80" t="s">
         <v>669</v>
       </c>
@@ -19921,8 +19921,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="289" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="93"/>
+    <row r="289" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A289" s="97"/>
       <c r="B289" s="80" t="s">
         <v>669</v>
       </c>
@@ -19973,8 +19973,8 @@
         <v>681</v>
       </c>
     </row>
-    <row r="290" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="93"/>
+    <row r="290" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A290" s="97"/>
       <c r="B290" s="80" t="s">
         <v>669</v>
       </c>
@@ -20028,7 +20028,7 @@
       </c>
     </row>
     <row r="291" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A291" s="93"/>
+      <c r="A291" s="97"/>
       <c r="B291" s="80" t="s">
         <v>669</v>
       </c>
@@ -20078,7 +20078,7 @@
       <c r="S291" s="80"/>
     </row>
     <row r="292" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A292" s="93"/>
+      <c r="A292" s="97"/>
       <c r="B292" s="80" t="s">
         <v>669</v>
       </c>
@@ -20188,7 +20188,7 @@
       </c>
     </row>
     <row r="294" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="93">
+      <c r="A294" s="97">
         <v>77</v>
       </c>
       <c r="B294" s="80" t="s">
@@ -20248,7 +20248,7 @@
       </c>
     </row>
     <row r="295" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="93"/>
+      <c r="A295" s="97"/>
       <c r="B295" s="80" t="s">
         <v>684</v>
       </c>
@@ -20306,7 +20306,7 @@
       </c>
     </row>
     <row r="296" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="93"/>
+      <c r="A296" s="97"/>
       <c r="B296" s="80" t="s">
         <v>684</v>
       </c>
@@ -20364,7 +20364,7 @@
       </c>
     </row>
     <row r="297" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="93">
+      <c r="A297" s="97">
         <v>78</v>
       </c>
       <c r="B297" s="80" t="s">
@@ -20417,7 +20417,7 @@
       </c>
     </row>
     <row r="298" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="93"/>
+      <c r="A298" s="97"/>
       <c r="B298" s="80" t="s">
         <v>695</v>
       </c>
@@ -20469,7 +20469,7 @@
       <c r="S298" s="80"/>
     </row>
     <row r="299" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="93"/>
+      <c r="A299" s="97"/>
       <c r="B299" s="80" t="s">
         <v>695</v>
       </c>
@@ -20523,7 +20523,7 @@
       </c>
     </row>
     <row r="300" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="94"/>
+      <c r="A300" s="108"/>
       <c r="B300" s="80" t="s">
         <v>630</v>
       </c>
@@ -20575,7 +20575,7 @@
       <c r="S300" s="80"/>
     </row>
     <row r="301" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="95"/>
+      <c r="A301" s="104"/>
       <c r="B301" s="80" t="s">
         <v>630</v>
       </c>
@@ -20628,8 +20628,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="302" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A302" s="99">
+    <row r="302" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="103">
         <v>80</v>
       </c>
       <c r="B302" s="80" t="s">
@@ -20642,7 +20642,7 @@
         <v>21</v>
       </c>
       <c r="E302" s="90" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F302" s="80" t="s">
         <v>706</v>
@@ -20682,7 +20682,7 @@
       </c>
     </row>
     <row r="303" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="94"/>
+      <c r="A303" s="108"/>
       <c r="B303" s="80" t="s">
         <v>708</v>
       </c>
@@ -20734,7 +20734,7 @@
       <c r="S303" s="80"/>
     </row>
     <row r="304" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="99">
+      <c r="A304" s="103">
         <v>81</v>
       </c>
       <c r="B304" s="80" t="s">
@@ -20786,7 +20786,7 @@
       </c>
     </row>
     <row r="305" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="94"/>
+      <c r="A305" s="108"/>
       <c r="B305" s="80" t="s">
         <v>710</v>
       </c>
@@ -20838,7 +20838,7 @@
       </c>
     </row>
     <row r="306" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="94"/>
+      <c r="A306" s="108"/>
       <c r="B306" s="80" t="s">
         <v>710</v>
       </c>
@@ -20889,7 +20889,7 @@
       </c>
     </row>
     <row r="307" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="95"/>
+      <c r="A307" s="104"/>
       <c r="B307" s="80" t="s">
         <v>710</v>
       </c>
@@ -21014,29 +21014,29 @@
       <c r="E309" s="105">
         <v>4600018191</v>
       </c>
-      <c r="F309" s="104" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G309" s="93" t="s">
+      <c r="F309" s="114" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G309" s="97" t="s">
         <v>721</v>
       </c>
-      <c r="H309" s="93">
+      <c r="H309" s="97">
         <v>13.3</v>
       </c>
-      <c r="I309" s="99" t="s">
+      <c r="I309" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="J309" s="99" t="s">
+      <c r="J309" s="103" t="s">
         <v>538</v>
       </c>
-      <c r="K309" s="96">
+      <c r="K309" s="101">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L309" s="96">
+      <c r="L309" s="101">
         <v>0</v>
       </c>
-      <c r="M309" s="96">
+      <c r="M309" s="101">
         <f>+K309</f>
         <v>988077089</v>
       </c>
@@ -21046,19 +21046,19 @@
       <c r="O309" s="98" t="s">
         <v>722</v>
       </c>
-      <c r="P309" s="93">
+      <c r="P309" s="97">
         <v>2025</v>
       </c>
       <c r="Q309" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="R309" s="93"/>
-      <c r="S309" s="93" t="s">
+      <c r="R309" s="97"/>
+      <c r="S309" s="97" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="93">
+      <c r="A310" s="97">
         <v>84</v>
       </c>
       <c r="B310" s="80" t="s">
@@ -21072,22 +21072,22 @@
       </c>
       <c r="E310" s="106"/>
       <c r="F310" s="98"/>
-      <c r="G310" s="93"/>
-      <c r="H310" s="93"/>
-      <c r="I310" s="95"/>
-      <c r="J310" s="95"/>
-      <c r="K310" s="96"/>
-      <c r="L310" s="96"/>
-      <c r="M310" s="96"/>
+      <c r="G310" s="97"/>
+      <c r="H310" s="97"/>
+      <c r="I310" s="104"/>
+      <c r="J310" s="104"/>
+      <c r="K310" s="101"/>
+      <c r="L310" s="101"/>
+      <c r="M310" s="101"/>
       <c r="N310" s="98"/>
       <c r="O310" s="98"/>
-      <c r="P310" s="93"/>
+      <c r="P310" s="97"/>
       <c r="Q310" s="98"/>
-      <c r="R310" s="93"/>
-      <c r="S310" s="93"/>
+      <c r="R310" s="97"/>
+      <c r="S310" s="97"/>
     </row>
     <row r="311" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="93"/>
+      <c r="A311" s="97"/>
       <c r="B311" s="80" t="s">
         <v>720</v>
       </c>
@@ -21103,26 +21103,26 @@
       <c r="F311" s="98" t="s">
         <v>724</v>
       </c>
-      <c r="G311" s="93" t="s">
+      <c r="G311" s="97" t="s">
         <v>725</v>
       </c>
-      <c r="H311" s="93">
+      <c r="H311" s="97">
         <v>31.12</v>
       </c>
-      <c r="I311" s="99" t="s">
+      <c r="I311" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="J311" s="99" t="s">
+      <c r="J311" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="K311" s="96">
+      <c r="K311" s="101">
         <f>+M311</f>
         <v>73907566008</v>
       </c>
-      <c r="L311" s="96">
+      <c r="L311" s="101">
         <v>0</v>
       </c>
-      <c r="M311" s="96">
+      <c r="M311" s="101">
         <v>73907566008</v>
       </c>
       <c r="N311" s="98" t="s">
@@ -21131,21 +21131,21 @@
       <c r="O311" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="P311" s="93">
+      <c r="P311" s="97">
         <v>2019</v>
       </c>
       <c r="Q311" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="R311" s="97">
+      <c r="R311" s="115">
         <v>1</v>
       </c>
-      <c r="S311" s="93" t="s">
+      <c r="S311" s="97" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="93"/>
+      <c r="A312" s="97"/>
       <c r="B312" s="80" t="s">
         <v>723</v>
       </c>
@@ -21157,22 +21157,22 @@
       </c>
       <c r="E312" s="106"/>
       <c r="F312" s="98"/>
-      <c r="G312" s="93"/>
-      <c r="H312" s="93"/>
-      <c r="I312" s="95"/>
-      <c r="J312" s="95"/>
-      <c r="K312" s="96"/>
-      <c r="L312" s="96"/>
-      <c r="M312" s="96"/>
+      <c r="G312" s="97"/>
+      <c r="H312" s="97"/>
+      <c r="I312" s="104"/>
+      <c r="J312" s="104"/>
+      <c r="K312" s="101"/>
+      <c r="L312" s="101"/>
+      <c r="M312" s="101"/>
       <c r="N312" s="98"/>
       <c r="O312" s="98"/>
-      <c r="P312" s="93"/>
+      <c r="P312" s="97"/>
       <c r="Q312" s="98"/>
-      <c r="R312" s="97"/>
-      <c r="S312" s="93"/>
+      <c r="R312" s="115"/>
+      <c r="S312" s="97"/>
     </row>
     <row r="313" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="93"/>
+      <c r="A313" s="97"/>
       <c r="B313" s="80" t="s">
         <v>723</v>
       </c>
@@ -21228,7 +21228,7 @@
       </c>
     </row>
     <row r="314" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="93"/>
+      <c r="A314" s="97"/>
       <c r="B314" s="80" t="s">
         <v>723</v>
       </c>
@@ -21281,8 +21281,8 @@
       </c>
       <c r="S314" s="80"/>
     </row>
-    <row r="315" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="93"/>
+    <row r="315" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="97"/>
       <c r="B315" s="80" t="s">
         <v>723</v>
       </c>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="S315" s="80"/>
     </row>
-    <row r="316" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="81"/>
       <c r="B316" s="80" t="s">
         <v>729</v>
@@ -21429,8 +21429,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="318" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="99">
+    <row r="318" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="103">
         <v>85</v>
       </c>
       <c r="B318" s="80" t="s">
@@ -21477,7 +21477,7 @@
       <c r="S318" s="80"/>
     </row>
     <row r="319" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="95"/>
+      <c r="A319" s="104"/>
       <c r="B319" s="80" t="s">
         <v>729</v>
       </c>
@@ -21527,8 +21527,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="320" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="100">
+    <row r="320" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="109">
         <v>86</v>
       </c>
       <c r="B320" s="80" t="s">
@@ -21579,8 +21579,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="321" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="101"/>
+    <row r="321" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="110"/>
       <c r="B321" s="75" t="s">
         <v>735</v>
       </c>
@@ -21628,7 +21628,7 @@
       </c>
     </row>
     <row r="322" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="101"/>
+      <c r="A322" s="110"/>
       <c r="B322" s="75" t="s">
         <v>735</v>
       </c>
@@ -21680,7 +21680,7 @@
       </c>
     </row>
     <row r="323" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="101"/>
+      <c r="A323" s="110"/>
       <c r="B323" s="75" t="s">
         <v>735</v>
       </c>
@@ -21731,8 +21731,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="324" spans="1:19" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="94"/>
+    <row r="324" spans="1:19" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="108"/>
       <c r="B324" s="75" t="s">
         <v>735</v>
       </c>
@@ -21781,8 +21781,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="325" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="94"/>
+    <row r="325" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="108"/>
       <c r="B325" s="75" t="s">
         <v>735</v>
       </c>
@@ -21832,7 +21832,7 @@
       </c>
     </row>
     <row r="326" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="101"/>
+      <c r="A326" s="110"/>
       <c r="B326" s="75" t="s">
         <v>735</v>
       </c>
@@ -21885,8 +21885,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="327" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="101"/>
+    <row r="327" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A327" s="110"/>
       <c r="B327" s="80" t="s">
         <v>735</v>
       </c>
@@ -21936,7 +21936,7 @@
       </c>
     </row>
     <row r="328" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="101"/>
+      <c r="A328" s="110"/>
       <c r="B328" s="80" t="s">
         <v>735</v>
       </c>
@@ -21987,8 +21987,8 @@
       </c>
       <c r="S328" s="80"/>
     </row>
-    <row r="329" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="102"/>
+    <row r="329" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A329" s="111"/>
       <c r="B329" s="80" t="s">
         <v>735</v>
       </c>
@@ -22039,7 +22039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="330" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:19" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="77"/>
       <c r="B330" s="80" t="s">
         <v>753</v>
@@ -22051,7 +22051,7 @@
         <v>21</v>
       </c>
       <c r="E330" s="90" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F330" s="80" t="s">
         <v>627</v>
@@ -22116,7 +22116,7 @@
       <c r="R331" s="75"/>
       <c r="S331" s="75"/>
     </row>
-    <row r="332" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="81"/>
       <c r="B332" s="80" t="s">
         <v>756</v>
@@ -22210,7 +22210,7 @@
       </c>
     </row>
     <row r="334" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="99">
+      <c r="A334" s="103">
         <v>89</v>
       </c>
       <c r="B334" s="80" t="s">
@@ -22270,7 +22270,7 @@
       </c>
     </row>
     <row r="335" spans="1:19" ht="44.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="94"/>
+      <c r="A335" s="108"/>
       <c r="B335" s="80" t="s">
         <v>756</v>
       </c>
@@ -22321,7 +22321,7 @@
       </c>
     </row>
     <row r="336" spans="1:19" ht="155.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="94"/>
+      <c r="A336" s="108"/>
       <c r="B336" s="80" t="s">
         <v>756</v>
       </c>
@@ -22372,7 +22372,7 @@
       </c>
     </row>
     <row r="337" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="95"/>
+      <c r="A337" s="104"/>
       <c r="B337" s="80" t="s">
         <v>756</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="77"/>
       <c r="B338" s="80" t="s">
         <v>764</v>
@@ -22470,7 +22470,7 @@
       </c>
     </row>
     <row r="339" spans="1:20" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="93">
+      <c r="A339" s="97">
         <v>90</v>
       </c>
       <c r="B339" s="80" t="s">
@@ -22526,7 +22526,7 @@
       <c r="T339" s="36"/>
     </row>
     <row r="340" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="93"/>
+      <c r="A340" s="97"/>
       <c r="B340" s="80" t="s">
         <v>764</v>
       </c>
@@ -22578,8 +22578,8 @@
       <c r="S340" s="75"/>
       <c r="T340" s="36"/>
     </row>
-    <row r="341" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="93">
+    <row r="341" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A341" s="97">
         <v>91</v>
       </c>
       <c r="B341" s="80" t="s">
@@ -22634,8 +22634,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="93"/>
+    <row r="342" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A342" s="97"/>
       <c r="B342" s="80" t="s">
         <v>767</v>
       </c>
@@ -22689,7 +22689,7 @@
       </c>
     </row>
     <row r="343" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A343" s="93"/>
+      <c r="A343" s="97"/>
       <c r="B343" s="80" t="s">
         <v>767</v>
       </c>
@@ -22738,8 +22738,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="93"/>
+    <row r="344" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A344" s="97"/>
       <c r="B344" s="80" t="s">
         <v>767</v>
       </c>
@@ -22792,8 +22792,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="345" spans="1:20" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="93"/>
+    <row r="345" spans="1:20" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A345" s="97"/>
       <c r="B345" s="80" t="s">
         <v>767</v>
       </c>
@@ -22844,7 +22844,7 @@
       </c>
     </row>
     <row r="346" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="93"/>
+      <c r="A346" s="97"/>
       <c r="B346" s="80" t="s">
         <v>767</v>
       </c>
@@ -22888,7 +22888,7 @@
       </c>
     </row>
     <row r="347" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A347" s="93"/>
+      <c r="A347" s="97"/>
       <c r="B347" s="80" t="s">
         <v>767</v>
       </c>
@@ -22942,7 +22942,7 @@
       </c>
     </row>
     <row r="348" spans="1:20" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="93">
+      <c r="A348" s="97">
         <v>92</v>
       </c>
       <c r="B348" s="80" t="s">
@@ -22996,8 +22996,8 @@
       </c>
       <c r="S348" s="80"/>
     </row>
-    <row r="349" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="93"/>
+    <row r="349" spans="1:20" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A349" s="97"/>
       <c r="B349" s="80" t="s">
         <v>779</v>
       </c>
@@ -23048,8 +23048,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="93"/>
+    <row r="350" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A350" s="97"/>
       <c r="B350" s="80" t="s">
         <v>779</v>
       </c>
@@ -23102,8 +23102,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="93">
+    <row r="351" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A351" s="97">
         <v>93</v>
       </c>
       <c r="B351" s="80" t="s">
@@ -23116,7 +23116,7 @@
         <v>21</v>
       </c>
       <c r="E351" s="90" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F351" s="80" t="s">
         <v>490</v>
@@ -23159,7 +23159,7 @@
       </c>
     </row>
     <row r="352" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="93"/>
+      <c r="A352" s="97"/>
       <c r="B352" s="80" t="s">
         <v>784</v>
       </c>
@@ -23210,7 +23210,7 @@
       </c>
     </row>
     <row r="353" spans="1:19" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="93"/>
+      <c r="A353" s="97"/>
       <c r="B353" s="80" t="s">
         <v>784</v>
       </c>
@@ -23264,7 +23264,7 @@
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="93"/>
+      <c r="A354" s="97"/>
       <c r="B354" s="80" t="s">
         <v>784</v>
       </c>
@@ -23321,8 +23321,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="355" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A355" s="93"/>
+    <row r="355" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A355" s="97"/>
       <c r="B355" s="80" t="s">
         <v>784</v>
       </c>
@@ -23374,7 +23374,7 @@
       </c>
     </row>
     <row r="356" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="93"/>
+      <c r="A356" s="97"/>
       <c r="B356" s="80" t="s">
         <v>784</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="357" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="75"/>
       <c r="B357" s="80" t="s">
         <v>793</v>
@@ -23439,10 +23439,10 @@
         <v>781</v>
       </c>
       <c r="E357" s="91" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F357" s="85" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G357" s="80" t="s">
         <v>491</v>
@@ -23481,7 +23481,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="358" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="75"/>
       <c r="B358" s="80" t="s">
         <v>793</v>
@@ -23639,7 +23639,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="361" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="57"/>
       <c r="B361" s="80" t="s">
         <v>793</v>
@@ -23694,8 +23694,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="362" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A362" s="93"/>
+    <row r="362" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A362" s="97"/>
       <c r="B362" s="80" t="s">
         <v>803</v>
       </c>
@@ -23748,7 +23748,7 @@
       <c r="S362" s="80"/>
     </row>
     <row r="363" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="93"/>
+      <c r="A363" s="97"/>
       <c r="B363" s="80" t="s">
         <v>803</v>
       </c>
@@ -23801,7 +23801,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="364" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A364" s="77">
         <v>96</v>
       </c>
@@ -23855,7 +23855,7 @@
       </c>
       <c r="S364" s="75"/>
     </row>
-    <row r="365" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A365" s="77"/>
       <c r="B365" s="80" t="s">
         <v>807</v>
@@ -23961,8 +23961,8 @@
       </c>
       <c r="S366" s="80"/>
     </row>
-    <row r="367" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A367" s="99">
+    <row r="367" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="103">
         <v>97</v>
       </c>
       <c r="B367" s="80" t="s">
@@ -23975,7 +23975,7 @@
         <v>21</v>
       </c>
       <c r="E367" s="91" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F367" s="80" t="s">
         <v>490</v>
@@ -24011,7 +24011,7 @@
       </c>
     </row>
     <row r="368" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="94"/>
+      <c r="A368" s="108"/>
       <c r="B368" s="80" t="s">
         <v>810</v>
       </c>
@@ -24069,7 +24069,7 @@
       </c>
     </row>
     <row r="369" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="94"/>
+      <c r="A369" s="108"/>
       <c r="B369" s="80" t="s">
         <v>810</v>
       </c>
@@ -24120,7 +24120,7 @@
       </c>
     </row>
     <row r="370" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="94"/>
+      <c r="A370" s="108"/>
       <c r="B370" s="80" t="s">
         <v>810</v>
       </c>
@@ -24173,8 +24173,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="371" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A371" s="95"/>
+    <row r="371" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A371" s="104"/>
       <c r="B371" s="80" t="s">
         <v>810</v>
       </c>
@@ -24227,7 +24227,7 @@
       <c r="S371" s="80"/>
     </row>
     <row r="372" spans="1:19" ht="148.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="93">
+      <c r="A372" s="97">
         <v>98</v>
       </c>
       <c r="B372" s="80" t="s">
@@ -24280,7 +24280,7 @@
       </c>
     </row>
     <row r="373" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="93"/>
+      <c r="A373" s="97"/>
       <c r="B373" s="80" t="s">
         <v>816</v>
       </c>
@@ -24331,7 +24331,7 @@
       </c>
     </row>
     <row r="374" spans="1:19" ht="34.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="93"/>
+      <c r="A374" s="97"/>
       <c r="B374" s="80" t="s">
         <v>816</v>
       </c>
@@ -24382,7 +24382,7 @@
       </c>
     </row>
     <row r="375" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="93"/>
+      <c r="A375" s="97"/>
       <c r="B375" s="80" t="s">
         <v>816</v>
       </c>
@@ -24433,7 +24433,7 @@
       </c>
     </row>
     <row r="376" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="93"/>
+      <c r="A376" s="97"/>
       <c r="B376" s="80" t="s">
         <v>816</v>
       </c>
@@ -24473,8 +24473,8 @@
         <v>829</v>
       </c>
     </row>
-    <row r="377" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="93"/>
+    <row r="377" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="97"/>
       <c r="B377" s="80" t="s">
         <v>816</v>
       </c>
@@ -24523,8 +24523,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="378" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="93"/>
+    <row r="378" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="97"/>
       <c r="B378" s="80" t="s">
         <v>816</v>
       </c>
@@ -24574,7 +24574,7 @@
       </c>
     </row>
     <row r="379" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="93"/>
+      <c r="A379" s="97"/>
       <c r="B379" s="80" t="s">
         <v>816</v>
       </c>
@@ -24618,7 +24618,7 @@
       </c>
     </row>
     <row r="380" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="93"/>
+      <c r="A380" s="97"/>
       <c r="B380" s="80" t="s">
         <v>816</v>
       </c>
@@ -24665,7 +24665,7 @@
       <c r="S380" s="80"/>
     </row>
     <row r="381" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="93"/>
+      <c r="A381" s="97"/>
       <c r="B381" s="80" t="s">
         <v>816</v>
       </c>
@@ -24717,7 +24717,7 @@
       <c r="S381" s="80"/>
     </row>
     <row r="382" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="93"/>
+      <c r="A382" s="97"/>
       <c r="B382" s="80" t="s">
         <v>816</v>
       </c>
@@ -24767,7 +24767,7 @@
       </c>
     </row>
     <row r="383" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="93"/>
+      <c r="A383" s="97"/>
       <c r="B383" s="80" t="s">
         <v>816</v>
       </c>
@@ -24818,8 +24818,8 @@
       </c>
       <c r="S383" s="80"/>
     </row>
-    <row r="384" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="95">
+    <row r="384" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A384" s="104">
         <v>99</v>
       </c>
       <c r="B384" s="80" t="s">
@@ -24871,8 +24871,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:19" ht="163.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="93"/>
+    <row r="385" spans="1:19" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="97"/>
       <c r="B385" s="80" t="s">
         <v>844</v>
       </c>
@@ -24923,7 +24923,7 @@
       </c>
     </row>
     <row r="386" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="93"/>
+      <c r="A386" s="97"/>
       <c r="B386" s="80" t="s">
         <v>844</v>
       </c>
@@ -24976,8 +24976,8 @@
       </c>
       <c r="S386" s="80"/>
     </row>
-    <row r="387" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="93"/>
+    <row r="387" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A387" s="97"/>
       <c r="B387" s="80" t="s">
         <v>844</v>
       </c>
@@ -25028,8 +25028,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="388" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="93"/>
+    <row r="388" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A388" s="97"/>
       <c r="B388" s="80" t="s">
         <v>843</v>
       </c>
@@ -25080,8 +25080,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="389" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="93"/>
+    <row r="389" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A389" s="97"/>
       <c r="B389" s="80" t="s">
         <v>843</v>
       </c>
@@ -25134,8 +25134,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="390" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="93"/>
+    <row r="390" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A390" s="97"/>
       <c r="B390" s="80" t="s">
         <v>843</v>
       </c>
@@ -25173,8 +25173,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="391" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="93"/>
+    <row r="391" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A391" s="97"/>
       <c r="B391" s="75" t="s">
         <v>843</v>
       </c>
@@ -25277,7 +25277,7 @@
       </c>
     </row>
     <row r="393" spans="1:19" ht="58.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="93">
+      <c r="A393" s="97">
         <v>100</v>
       </c>
       <c r="B393" s="75" t="s">
@@ -25330,7 +25330,7 @@
       </c>
     </row>
     <row r="394" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="93"/>
+      <c r="A394" s="97"/>
       <c r="B394" s="75" t="s">
         <v>853</v>
       </c>
@@ -25381,7 +25381,7 @@
       </c>
     </row>
     <row r="395" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="93"/>
+      <c r="A395" s="97"/>
       <c r="B395" s="80" t="s">
         <v>853</v>
       </c>
@@ -25435,7 +25435,7 @@
       </c>
     </row>
     <row r="396" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="93"/>
+      <c r="A396" s="97"/>
       <c r="B396" s="80" t="s">
         <v>853</v>
       </c>
@@ -25483,7 +25483,7 @@
       </c>
     </row>
     <row r="397" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="93"/>
+      <c r="A397" s="97"/>
       <c r="B397" s="80" t="s">
         <v>853</v>
       </c>
@@ -25535,7 +25535,7 @@
       <c r="S397" s="80"/>
     </row>
     <row r="398" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="93"/>
+      <c r="A398" s="97"/>
       <c r="B398" s="80" t="s">
         <v>853</v>
       </c>
@@ -25586,8 +25586,8 @@
       </c>
       <c r="S398" s="80"/>
     </row>
-    <row r="399" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="103">
+    <row r="399" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A399" s="112">
         <v>101</v>
       </c>
       <c r="B399" s="80" t="s">
@@ -25641,8 +25641,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="400" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="103"/>
+    <row r="400" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="112"/>
       <c r="B400" s="80" t="s">
         <v>862</v>
       </c>
@@ -25680,8 +25680,8 @@
       <c r="R400" s="89"/>
       <c r="S400" s="75"/>
     </row>
-    <row r="401" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="103"/>
+    <row r="401" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="112"/>
       <c r="B401" s="80" t="s">
         <v>862</v>
       </c>
@@ -25732,8 +25732,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="402" spans="1:19" ht="31.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="103"/>
+    <row r="402" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="112"/>
       <c r="B402" s="80" t="s">
         <v>862</v>
       </c>
@@ -25787,7 +25787,7 @@
       </c>
     </row>
     <row r="403" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="103"/>
+      <c r="A403" s="112"/>
       <c r="B403" s="80" t="s">
         <v>862</v>
       </c>
@@ -25838,8 +25838,8 @@
       </c>
       <c r="S403" s="80"/>
     </row>
-    <row r="404" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="103"/>
+    <row r="404" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A404" s="112"/>
       <c r="B404" s="80" t="s">
         <v>862</v>
       </c>
@@ -25893,7 +25893,7 @@
       </c>
     </row>
     <row r="405" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="93">
+      <c r="A405" s="97">
         <v>102</v>
       </c>
       <c r="B405" s="75" t="s">
@@ -25946,7 +25946,7 @@
       </c>
     </row>
     <row r="406" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="93"/>
+      <c r="A406" s="97"/>
       <c r="B406" s="80" t="s">
         <v>869</v>
       </c>
@@ -25999,8 +25999,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="407" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="93">
+    <row r="407" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="97">
         <v>103</v>
       </c>
       <c r="B407" s="80" t="s">
@@ -26054,7 +26054,7 @@
       </c>
     </row>
     <row r="408" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="93"/>
+      <c r="A408" s="97"/>
       <c r="B408" s="80" t="s">
         <v>873</v>
       </c>
@@ -26108,7 +26108,7 @@
       </c>
     </row>
     <row r="409" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="93"/>
+      <c r="A409" s="97"/>
       <c r="B409" s="80" t="s">
         <v>873</v>
       </c>
@@ -26161,7 +26161,7 @@
       </c>
     </row>
     <row r="410" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="93"/>
+      <c r="A410" s="97"/>
       <c r="B410" s="80" t="s">
         <v>873</v>
       </c>
@@ -26215,7 +26215,7 @@
       </c>
     </row>
     <row r="411" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="93">
+      <c r="A411" s="97">
         <v>104</v>
       </c>
       <c r="B411" s="80" t="s">
@@ -26268,7 +26268,7 @@
       </c>
     </row>
     <row r="412" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="93"/>
+      <c r="A412" s="97"/>
       <c r="B412" s="80" t="s">
         <v>878</v>
       </c>
@@ -26326,7 +26326,7 @@
       </c>
     </row>
     <row r="413" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="93"/>
+      <c r="A413" s="97"/>
       <c r="B413" s="80"/>
       <c r="C413" s="75"/>
       <c r="D413" s="75"/>
@@ -26346,8 +26346,8 @@
       <c r="R413" s="89"/>
       <c r="S413" s="80"/>
     </row>
-    <row r="414" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A414" s="93"/>
+    <row r="414" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="97"/>
       <c r="B414" s="80" t="s">
         <v>878</v>
       </c>
@@ -26398,7 +26398,7 @@
       </c>
     </row>
     <row r="415" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="93"/>
+      <c r="A415" s="97"/>
       <c r="B415" s="80" t="s">
         <v>878</v>
       </c>
@@ -26451,7 +26451,7 @@
       </c>
     </row>
     <row r="416" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="93">
+      <c r="A416" s="97">
         <v>105</v>
       </c>
       <c r="B416" s="80" t="s">
@@ -26504,7 +26504,7 @@
       </c>
     </row>
     <row r="417" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="93"/>
+      <c r="A417" s="97"/>
       <c r="B417" s="80" t="s">
         <v>885</v>
       </c>
@@ -26549,7 +26549,7 @@
       </c>
     </row>
     <row r="418" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="93"/>
+      <c r="A418" s="97"/>
       <c r="B418" s="80" t="s">
         <v>885</v>
       </c>
@@ -26603,7 +26603,7 @@
       </c>
     </row>
     <row r="419" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="93"/>
+      <c r="A419" s="97"/>
       <c r="B419" s="80" t="s">
         <v>885</v>
       </c>
@@ -26657,7 +26657,7 @@
       </c>
     </row>
     <row r="420" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="93"/>
+      <c r="A420" s="97"/>
       <c r="B420" s="80" t="s">
         <v>885</v>
       </c>
@@ -26711,7 +26711,7 @@
       </c>
     </row>
     <row r="421" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="93"/>
+      <c r="A421" s="97"/>
       <c r="B421" s="80" t="s">
         <v>885</v>
       </c>
@@ -26751,8 +26751,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="422" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A422" s="93"/>
+    <row r="422" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="97"/>
       <c r="B422" s="80" t="s">
         <v>885</v>
       </c>
@@ -26800,7 +26800,7 @@
       </c>
     </row>
     <row r="423" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="93"/>
+      <c r="A423" s="97"/>
       <c r="B423" s="80" t="s">
         <v>885</v>
       </c>
@@ -26852,7 +26852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="424" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="75">
         <v>106</v>
       </c>
@@ -26949,8 +26949,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="426" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="93">
+    <row r="426" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A426" s="97">
         <v>107</v>
       </c>
       <c r="B426" s="80" t="s">
@@ -27004,8 +27004,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="93"/>
+    <row r="427" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A427" s="97"/>
       <c r="B427" s="80" t="s">
         <v>902</v>
       </c>
@@ -27056,8 +27056,8 @@
       </c>
       <c r="S427" s="80"/>
     </row>
-    <row r="428" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="93"/>
+    <row r="428" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="97"/>
       <c r="B428" s="80" t="s">
         <v>902</v>
       </c>
@@ -27107,7 +27107,7 @@
       </c>
     </row>
     <row r="429" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="93"/>
+      <c r="A429" s="97"/>
       <c r="B429" s="80" t="s">
         <v>901</v>
       </c>
@@ -27157,7 +27157,7 @@
       </c>
     </row>
     <row r="430" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="93"/>
+      <c r="A430" s="97"/>
       <c r="B430" s="80" t="s">
         <v>901</v>
       </c>
@@ -27167,7 +27167,9 @@
       <c r="D430" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E430" s="90"/>
+      <c r="E430" s="90" t="s">
+        <v>61</v>
+      </c>
       <c r="F430" s="80" t="s">
         <v>910</v>
       </c>
@@ -27205,7 +27207,7 @@
       </c>
     </row>
     <row r="431" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A431" s="93"/>
+      <c r="A431" s="97"/>
       <c r="B431" s="80" t="s">
         <v>902</v>
       </c>
@@ -27256,8 +27258,8 @@
       </c>
       <c r="S431" s="80"/>
     </row>
-    <row r="432" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="93"/>
+    <row r="432" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A432" s="97"/>
       <c r="B432" s="80" t="s">
         <v>901</v>
       </c>
@@ -27308,8 +27310,8 @@
       </c>
       <c r="S432" s="75"/>
     </row>
-    <row r="433" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A433" s="94"/>
+    <row r="433" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="108"/>
       <c r="B433" s="80" t="s">
         <v>913</v>
       </c>
@@ -27331,13 +27333,13 @@
       </c>
       <c r="I433" s="80"/>
       <c r="J433" s="80"/>
-      <c r="K433" s="96">
+      <c r="K433" s="101">
         <v>12746524997</v>
       </c>
-      <c r="L433" s="96">
+      <c r="L433" s="101">
         <v>1000000000</v>
       </c>
-      <c r="M433" s="96">
+      <c r="M433" s="101">
         <f>+K433+L433</f>
         <v>13746524997</v>
       </c>
@@ -27347,19 +27349,19 @@
       <c r="O433" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="P433" s="93">
+      <c r="P433" s="97">
         <v>2025</v>
       </c>
       <c r="Q433" s="75"/>
-      <c r="R433" s="97">
+      <c r="R433" s="115">
         <v>0.65</v>
       </c>
-      <c r="S433" s="93" t="s">
+      <c r="S433" s="97" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="434" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="94"/>
+      <c r="A434" s="108"/>
       <c r="B434" s="80" t="s">
         <v>913</v>
       </c>
@@ -27381,18 +27383,18 @@
       </c>
       <c r="I434" s="80"/>
       <c r="J434" s="80"/>
-      <c r="K434" s="96"/>
-      <c r="L434" s="96"/>
-      <c r="M434" s="96"/>
+      <c r="K434" s="101"/>
+      <c r="L434" s="101"/>
+      <c r="M434" s="101"/>
       <c r="N434" s="98"/>
       <c r="O434" s="98"/>
-      <c r="P434" s="93"/>
+      <c r="P434" s="97"/>
       <c r="Q434" s="75"/>
-      <c r="R434" s="97"/>
-      <c r="S434" s="93"/>
+      <c r="R434" s="115"/>
+      <c r="S434" s="97"/>
     </row>
     <row r="435" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="94"/>
+      <c r="A435" s="108"/>
       <c r="B435" s="80" t="s">
         <v>913</v>
       </c>
@@ -27444,7 +27446,7 @@
       </c>
     </row>
     <row r="436" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="94"/>
+      <c r="A436" s="108"/>
       <c r="B436" s="80" t="s">
         <v>917</v>
       </c>
@@ -27496,7 +27498,7 @@
       </c>
     </row>
     <row r="437" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="94"/>
+      <c r="A437" s="108"/>
       <c r="B437" s="80" t="s">
         <v>913</v>
       </c>
@@ -27546,7 +27548,7 @@
       </c>
     </row>
     <row r="438" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="95"/>
+      <c r="A438" s="104"/>
       <c r="B438" s="80" t="s">
         <v>913</v>
       </c>
@@ -27597,7 +27599,7 @@
       </c>
     </row>
     <row r="439" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="99">
+      <c r="A439" s="103">
         <v>109</v>
       </c>
       <c r="B439" s="80" t="s">
@@ -27649,7 +27651,7 @@
       </c>
     </row>
     <row r="440" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="94"/>
+      <c r="A440" s="108"/>
       <c r="B440" s="80" t="s">
         <v>925</v>
       </c>
@@ -27698,7 +27700,7 @@
       </c>
     </row>
     <row r="441" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="94"/>
+      <c r="A441" s="108"/>
       <c r="B441" s="80" t="s">
         <v>925</v>
       </c>
@@ -27751,7 +27753,7 @@
       </c>
     </row>
     <row r="442" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="94"/>
+      <c r="A442" s="108"/>
       <c r="B442" s="80" t="s">
         <v>925</v>
       </c>
@@ -27802,8 +27804,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="443" spans="1:19" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="94"/>
+    <row r="443" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A443" s="108"/>
       <c r="B443" s="80" t="s">
         <v>925</v>
       </c>
@@ -27813,7 +27815,9 @@
       <c r="D443" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E443" s="90"/>
+      <c r="E443" s="90">
+        <v>4600016804</v>
+      </c>
       <c r="F443" s="80" t="s">
         <v>929</v>
       </c>
@@ -27851,7 +27855,7 @@
       </c>
     </row>
     <row r="444" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="94"/>
+      <c r="A444" s="108"/>
       <c r="B444" s="80" t="s">
         <v>925</v>
       </c>
@@ -27899,7 +27903,7 @@
       </c>
     </row>
     <row r="445" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="94"/>
+      <c r="A445" s="108"/>
       <c r="B445" s="80" t="s">
         <v>925</v>
       </c>
@@ -27933,8 +27937,8 @@
       <c r="R445" s="89"/>
       <c r="S445" s="80"/>
     </row>
-    <row r="446" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="95"/>
+    <row r="446" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A446" s="104"/>
       <c r="B446" s="80" t="s">
         <v>925</v>
       </c>
@@ -27985,8 +27989,8 @@
       </c>
       <c r="S446" s="53"/>
     </row>
-    <row r="447" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A447" s="93"/>
+    <row r="447" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A447" s="97"/>
       <c r="B447" s="80" t="s">
         <v>935</v>
       </c>
@@ -28040,7 +28044,7 @@
       </c>
     </row>
     <row r="448" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="93"/>
+      <c r="A448" s="97"/>
       <c r="B448" s="60" t="s">
         <v>935</v>
       </c>
@@ -28097,8 +28101,8 @@
         <v>941</v>
       </c>
     </row>
-    <row r="449" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A449" s="99">
+    <row r="449" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A449" s="103">
         <v>111</v>
       </c>
       <c r="B449" s="80" t="s">
@@ -28110,7 +28114,9 @@
       <c r="D449" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E449" s="90"/>
+      <c r="E449" s="90">
+        <v>2022003050024</v>
+      </c>
       <c r="F449" s="80" t="s">
         <v>943</v>
       </c>
@@ -28150,7 +28156,7 @@
       </c>
     </row>
     <row r="450" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="94"/>
+      <c r="A450" s="108"/>
       <c r="B450" s="80" t="s">
         <v>942</v>
       </c>
@@ -28202,7 +28208,7 @@
       </c>
     </row>
     <row r="451" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="94"/>
+      <c r="A451" s="108"/>
       <c r="B451" s="80" t="s">
         <v>942</v>
       </c>
@@ -28258,7 +28264,7 @@
       </c>
     </row>
     <row r="452" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="95"/>
+      <c r="A452" s="104"/>
       <c r="B452" s="80" t="s">
         <v>942</v>
       </c>
@@ -28310,7 +28316,7 @@
       </c>
     </row>
     <row r="453" spans="1:19" ht="42.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="93">
+      <c r="A453" s="97">
         <v>112</v>
       </c>
       <c r="B453" s="80" t="s">
@@ -28369,7 +28375,7 @@
       </c>
     </row>
     <row r="454" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="93"/>
+      <c r="A454" s="97"/>
       <c r="B454" s="80" t="s">
         <v>949</v>
       </c>
@@ -28421,8 +28427,8 @@
       </c>
       <c r="S454" s="80"/>
     </row>
-    <row r="455" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="93"/>
+    <row r="455" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A455" s="97"/>
       <c r="B455" s="80" t="s">
         <v>949</v>
       </c>
@@ -28476,8 +28482,8 @@
       </c>
       <c r="S455" s="80"/>
     </row>
-    <row r="456" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A456" s="93">
+    <row r="456" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A456" s="97">
         <v>113</v>
       </c>
       <c r="B456" s="80" t="s">
@@ -28489,7 +28495,9 @@
       <c r="D456" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E456" s="90"/>
+      <c r="E456" s="90">
+        <v>2026003050015</v>
+      </c>
       <c r="F456" s="80" t="s">
         <v>954</v>
       </c>
@@ -28526,7 +28534,7 @@
       </c>
     </row>
     <row r="457" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="93"/>
+      <c r="A457" s="97"/>
       <c r="B457" s="80" t="s">
         <v>953</v>
       </c>
@@ -28577,7 +28585,7 @@
       </c>
     </row>
     <row r="458" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="93"/>
+      <c r="A458" s="97"/>
       <c r="B458" s="80" t="s">
         <v>953</v>
       </c>
@@ -28628,8 +28636,8 @@
       </c>
       <c r="S458" s="75"/>
     </row>
-    <row r="459" spans="1:19" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="93"/>
+    <row r="459" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A459" s="97"/>
       <c r="B459" s="80" t="s">
         <v>953</v>
       </c>
@@ -28675,7 +28683,7 @@
       <c r="S459" s="75"/>
     </row>
     <row r="460" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="93"/>
+      <c r="A460" s="97"/>
       <c r="B460" s="80" t="s">
         <v>953</v>
       </c>
@@ -28728,7 +28736,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="461" spans="1:19" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="75"/>
       <c r="B461" s="80" t="s">
         <v>960</v>
@@ -28777,10 +28785,8 @@
       <c r="Q461" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="R461" s="79">
-        <v>0.87</v>
-      </c>
-      <c r="S461" s="80" t="s">
+      <c r="R461" s="79"/>
+      <c r="S461" s="93" t="s">
         <v>135</v>
       </c>
     </row>
@@ -28829,14 +28835,12 @@
         <v>2025</v>
       </c>
       <c r="Q462" s="75" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R462" s="89">
-        <v>0</v>
-      </c>
-      <c r="S462" s="80" t="s">
-        <v>964</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="S462" s="80"/>
     </row>
     <row r="463" spans="1:19" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="75"/>
@@ -28850,10 +28854,10 @@
         <v>40</v>
       </c>
       <c r="E463" s="90" t="s">
+        <v>964</v>
+      </c>
+      <c r="F463" s="80" t="s">
         <v>965</v>
-      </c>
-      <c r="F463" s="80" t="s">
-        <v>966</v>
       </c>
       <c r="G463" s="80" t="s">
         <v>203</v>
@@ -28886,11 +28890,11 @@
         <v>36</v>
       </c>
       <c r="R463" s="89">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="S463" s="80"/>
     </row>
-    <row r="464" spans="1:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:19" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="75"/>
       <c r="B464" s="80" t="s">
         <v>960</v>
@@ -28901,15 +28905,17 @@
       <c r="D464" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E464" s="90"/>
+      <c r="E464" s="90">
+        <v>2025003050039</v>
+      </c>
       <c r="F464" s="80" t="s">
+        <v>966</v>
+      </c>
+      <c r="G464" s="80" t="s">
         <v>967</v>
       </c>
-      <c r="G464" s="80" t="s">
-        <v>968</v>
-      </c>
       <c r="H464" s="80" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="I464" s="80"/>
       <c r="J464" s="80"/>
@@ -28933,12 +28939,10 @@
         <v>2026</v>
       </c>
       <c r="Q464" s="75" t="s">
-        <v>563</v>
+        <v>28</v>
       </c>
       <c r="R464" s="89"/>
-      <c r="S464" s="80" t="s">
-        <v>369</v>
-      </c>
+      <c r="S464" s="80"/>
     </row>
     <row r="465" spans="1:19" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="75"/>
@@ -28952,10 +28956,10 @@
         <v>40</v>
       </c>
       <c r="E465" s="90" t="s">
+        <v>968</v>
+      </c>
+      <c r="F465" s="80" t="s">
         <v>969</v>
-      </c>
-      <c r="F465" s="80" t="s">
-        <v>970</v>
       </c>
       <c r="G465" s="80" t="s">
         <v>203</v>
@@ -28988,7 +28992,7 @@
         <v>36</v>
       </c>
       <c r="R465" s="89">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="S465" s="80"/>
     </row>
@@ -29045,10 +29049,10 @@
         <v>153</v>
       </c>
     </row>
-    <row r="467" spans="1:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="94"/>
+    <row r="467" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A467" s="108"/>
       <c r="B467" s="80" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C467" s="75" t="s">
         <v>39</v>
@@ -29095,7 +29099,7 @@
       </c>
     </row>
     <row r="468" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="94"/>
+      <c r="A468" s="108"/>
       <c r="B468" s="80" t="s">
         <v>324</v>
       </c>
@@ -29106,10 +29110,10 @@
         <v>40</v>
       </c>
       <c r="E468" s="90" t="s">
+        <v>971</v>
+      </c>
+      <c r="F468" s="80" t="s">
         <v>972</v>
-      </c>
-      <c r="F468" s="80" t="s">
-        <v>973</v>
       </c>
       <c r="G468" s="75" t="s">
         <v>203</v>
@@ -29139,7 +29143,7 @@
         <v>2025</v>
       </c>
       <c r="Q468" s="75" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="R468" s="79">
         <v>0.25</v>
@@ -29147,7 +29151,7 @@
       <c r="S468" s="80"/>
     </row>
     <row r="469" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="94"/>
+      <c r="A469" s="108"/>
       <c r="B469" s="80" t="s">
         <v>324</v>
       </c>
@@ -29158,10 +29162,10 @@
         <v>40</v>
       </c>
       <c r="E469" s="90" t="s">
+        <v>974</v>
+      </c>
+      <c r="F469" s="80" t="s">
         <v>975</v>
-      </c>
-      <c r="F469" s="80" t="s">
-        <v>976</v>
       </c>
       <c r="G469" s="75" t="s">
         <v>203</v>
@@ -29199,7 +29203,7 @@
       <c r="S469" s="80"/>
     </row>
     <row r="470" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="94"/>
+      <c r="A470" s="108"/>
       <c r="B470" s="80" t="s">
         <v>324</v>
       </c>
@@ -29210,10 +29214,10 @@
         <v>40</v>
       </c>
       <c r="E470" s="90" t="s">
+        <v>976</v>
+      </c>
+      <c r="F470" s="80" t="s">
         <v>977</v>
-      </c>
-      <c r="F470" s="80" t="s">
-        <v>978</v>
       </c>
       <c r="G470" s="75" t="s">
         <v>203</v>
@@ -29251,7 +29255,7 @@
       <c r="S470" s="80"/>
     </row>
     <row r="471" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="94"/>
+      <c r="A471" s="108"/>
       <c r="B471" s="80" t="s">
         <v>324</v>
       </c>
@@ -29262,7 +29266,7 @@
         <v>40</v>
       </c>
       <c r="E471" s="90" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F471" s="80" t="s">
         <v>264</v>
@@ -29304,8 +29308,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="472" spans="1:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="94"/>
+    <row r="472" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A472" s="108"/>
       <c r="B472" s="80" t="s">
         <v>324</v>
       </c>
@@ -29315,10 +29319,10 @@
       <c r="D472" s="75"/>
       <c r="E472" s="90"/>
       <c r="F472" s="80" t="s">
+        <v>979</v>
+      </c>
+      <c r="G472" s="75" t="s">
         <v>980</v>
-      </c>
-      <c r="G472" s="75" t="s">
-        <v>981</v>
       </c>
       <c r="H472" s="75">
         <v>9.39</v>
@@ -29355,9 +29359,9 @@
       </c>
     </row>
     <row r="473" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="95"/>
+      <c r="A473" s="104"/>
       <c r="B473" s="80" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C473" s="75" t="s">
         <v>39</v>
@@ -29367,7 +29371,7 @@
       </c>
       <c r="E473" s="90"/>
       <c r="F473" s="80" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G473" s="75" t="s">
         <v>306</v>
@@ -29402,12 +29406,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="474" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="93">
+    <row r="474" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A474" s="97">
         <v>116</v>
       </c>
       <c r="B474" s="80" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C474" s="75" t="s">
         <v>83</v>
@@ -29415,28 +29419,28 @@
       <c r="D474" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E474" s="111">
+      <c r="E474" s="100">
         <v>2025003050036</v>
       </c>
       <c r="F474" s="80" t="s">
         <v>174</v>
       </c>
       <c r="G474" s="80" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H474" s="80" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="I474" s="80"/>
       <c r="J474" s="80"/>
-      <c r="K474" s="109">
+      <c r="K474" s="102">
         <f>+M474</f>
         <v>14202451801</v>
       </c>
-      <c r="L474" s="109">
+      <c r="L474" s="102">
         <v>0</v>
       </c>
-      <c r="M474" s="96">
+      <c r="M474" s="101">
         <v>14202451801</v>
       </c>
       <c r="N474" s="80" t="s">
@@ -29456,10 +29460,10 @@
         <v>369</v>
       </c>
     </row>
-    <row r="475" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="93"/>
+    <row r="475" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A475" s="97"/>
       <c r="B475" s="80" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C475" s="75" t="s">
         <v>83</v>
@@ -29467,21 +29471,21 @@
       <c r="D475" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E475" s="111"/>
+      <c r="E475" s="100"/>
       <c r="F475" s="80" t="s">
         <v>174</v>
       </c>
       <c r="G475" s="80" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H475" s="80" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I475" s="80"/>
       <c r="J475" s="80"/>
-      <c r="K475" s="109"/>
-      <c r="L475" s="109"/>
-      <c r="M475" s="96"/>
+      <c r="K475" s="102"/>
+      <c r="L475" s="102"/>
+      <c r="M475" s="101"/>
       <c r="N475" s="80" t="s">
         <v>35</v>
       </c>
@@ -29498,9 +29502,9 @@
       <c r="S475" s="98"/>
     </row>
     <row r="476" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="93"/>
+      <c r="A476" s="97"/>
       <c r="B476" s="80" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C476" s="75" t="s">
         <v>83</v>
@@ -29554,9 +29558,9 @@
       </c>
     </row>
     <row r="477" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="93"/>
+      <c r="A477" s="97"/>
       <c r="B477" s="80" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C477" s="75" t="s">
         <v>83</v>
@@ -29611,7 +29615,7 @@
         <v>118</v>
       </c>
       <c r="B478" s="80" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C478" s="75" t="s">
         <v>83</v>
@@ -29624,10 +29628,10 @@
         <v>100</v>
       </c>
       <c r="G478" s="75" t="s">
+        <v>986</v>
+      </c>
+      <c r="H478" s="75" t="s">
         <v>987</v>
-      </c>
-      <c r="H478" s="75" t="s">
-        <v>988</v>
       </c>
       <c r="I478" s="75"/>
       <c r="J478" s="75"/>
@@ -29659,10 +29663,10 @@
         <v>698</v>
       </c>
     </row>
-    <row r="479" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="75"/>
       <c r="B479" s="80" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C479" s="75" t="s">
         <v>90</v>
@@ -29670,7 +29674,9 @@
       <c r="D479" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E479" s="90"/>
+      <c r="E479" s="90">
+        <v>2023000040003</v>
+      </c>
       <c r="F479" s="80" t="s">
         <v>91</v>
       </c>
@@ -29712,7 +29718,7 @@
     <row r="480" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="75"/>
       <c r="B480" s="80" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C480" s="75" t="s">
         <v>90</v>
@@ -29722,10 +29728,10 @@
       </c>
       <c r="E480" s="90"/>
       <c r="F480" s="80" t="s">
+        <v>990</v>
+      </c>
+      <c r="G480" s="75" t="s">
         <v>991</v>
-      </c>
-      <c r="G480" s="75" t="s">
-        <v>992</v>
       </c>
       <c r="H480" s="75"/>
       <c r="I480" s="75"/>
@@ -29764,7 +29770,7 @@
         <v>119</v>
       </c>
       <c r="B481" s="80" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C481" s="75" t="s">
         <v>90</v>
@@ -29773,7 +29779,7 @@
         <v>40</v>
       </c>
       <c r="E481" s="90" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F481" s="80" t="s">
         <v>399</v>
@@ -29812,13 +29818,13 @@
         <v>1</v>
       </c>
       <c r="S481" s="75" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="482" spans="1:19" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="482" spans="1:19" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="75"/>
       <c r="B482" s="80" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C482" s="75" t="s">
         <v>83</v>
@@ -29826,15 +29832,17 @@
       <c r="D482" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E482" s="90"/>
+      <c r="E482" s="90">
+        <v>2026003050012</v>
+      </c>
       <c r="F482" s="80" t="s">
         <v>882</v>
       </c>
       <c r="G482" s="80" t="s">
+        <v>995</v>
+      </c>
+      <c r="H482" s="80" t="s">
         <v>996</v>
-      </c>
-      <c r="H482" s="80" t="s">
-        <v>997</v>
       </c>
       <c r="I482" s="80"/>
       <c r="J482" s="80"/>
@@ -29865,10 +29873,10 @@
         <v>588</v>
       </c>
     </row>
-    <row r="483" spans="1:19" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:19" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="75"/>
       <c r="B483" s="80" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C483" s="75" t="s">
         <v>83</v>
@@ -29881,10 +29889,10 @@
         <v>637</v>
       </c>
       <c r="G483" s="80" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H483" s="80" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="I483" s="80"/>
       <c r="J483" s="80"/>
@@ -29920,7 +29928,7 @@
         <v>120</v>
       </c>
       <c r="B484" s="80" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C484" s="75" t="s">
         <v>83</v>
@@ -29969,11 +29977,11 @@
       <c r="S484" s="75"/>
     </row>
     <row r="485" spans="1:19" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="93">
+      <c r="A485" s="97">
         <v>121</v>
       </c>
       <c r="B485" s="80" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C485" s="75" t="s">
         <v>180</v>
@@ -29982,13 +29990,13 @@
         <v>40</v>
       </c>
       <c r="E485" s="90" t="s">
+        <v>999</v>
+      </c>
+      <c r="F485" s="80" t="s">
         <v>1000</v>
       </c>
-      <c r="F485" s="80" t="s">
+      <c r="G485" s="75" t="s">
         <v>1001</v>
-      </c>
-      <c r="G485" s="75" t="s">
-        <v>1002</v>
       </c>
       <c r="H485" s="75">
         <v>0.14000000000000001</v>
@@ -30023,25 +30031,25 @@
       <c r="S485" s="80"/>
     </row>
     <row r="486" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="93"/>
+      <c r="A486" s="97"/>
       <c r="B486" s="80" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C486" s="75" t="s">
         <v>180</v>
       </c>
       <c r="D486" s="75" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E486" s="90"/>
       <c r="F486" s="80" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G486" s="75" t="s">
         <v>1004</v>
       </c>
-      <c r="G486" s="75" t="s">
-        <v>1005</v>
-      </c>
       <c r="H486" s="75" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I486" s="75"/>
       <c r="J486" s="75"/>
@@ -30073,9 +30081,9 @@
       </c>
     </row>
     <row r="487" spans="1:19" ht="163.19999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="93"/>
+      <c r="A487" s="97"/>
       <c r="B487" s="80" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C487" s="75" t="s">
         <v>180</v>
@@ -30085,7 +30093,7 @@
       </c>
       <c r="E487" s="90"/>
       <c r="F487" s="80" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G487" s="75" t="s">
         <v>76</v>
@@ -30115,19 +30123,19 @@
         <v>2024</v>
       </c>
       <c r="Q487" s="75" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="R487" s="89">
         <v>0.6</v>
       </c>
       <c r="S487" s="80" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="488" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="488" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="77"/>
       <c r="B488" s="80" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C488" s="75" t="s">
         <v>90</v>
@@ -30135,7 +30143,9 @@
       <c r="D488" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="E488" s="90"/>
+      <c r="E488" s="90">
+        <v>2023000040003</v>
+      </c>
       <c r="F488" s="80" t="s">
         <v>91</v>
       </c>
@@ -30179,7 +30189,7 @@
         <v>122</v>
       </c>
       <c r="B489" s="80" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C489" s="75" t="s">
         <v>90</v>
@@ -30188,7 +30198,7 @@
         <v>40</v>
       </c>
       <c r="E489" s="90" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F489" s="80" t="s">
         <v>80</v>
@@ -30229,9 +30239,9 @@
       <c r="S489" s="80"/>
     </row>
     <row r="490" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="94"/>
+      <c r="A490" s="108"/>
       <c r="B490" s="80" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C490" s="75" t="s">
         <v>90</v>
@@ -30240,7 +30250,7 @@
         <v>40</v>
       </c>
       <c r="E490" s="90" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F490" s="80" t="s">
         <v>75</v>
@@ -30281,9 +30291,9 @@
       <c r="S490" s="80"/>
     </row>
     <row r="491" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="94"/>
+      <c r="A491" s="108"/>
       <c r="B491" s="80" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C491" s="75" t="s">
         <v>90</v>
@@ -30292,10 +30302,10 @@
         <v>40</v>
       </c>
       <c r="E491" s="90" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F491" s="80" t="s">
         <v>1011</v>
-      </c>
-      <c r="F491" s="80" t="s">
-        <v>1012</v>
       </c>
       <c r="G491" s="75" t="s">
         <v>398</v>
@@ -30332,10 +30342,10 @@
       </c>
       <c r="S491" s="80"/>
     </row>
-    <row r="492" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A492" s="94"/>
+    <row r="492" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="108"/>
       <c r="B492" s="80" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C492" s="75" t="s">
         <v>90</v>
@@ -30343,12 +30353,14 @@
       <c r="D492" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E492" s="90"/>
+      <c r="E492" s="90">
+        <v>2026003050013</v>
+      </c>
       <c r="F492" s="75" t="s">
         <v>882</v>
       </c>
       <c r="G492" s="80" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H492" s="80"/>
       <c r="I492" s="80"/>
@@ -30380,9 +30392,9 @@
       </c>
     </row>
     <row r="493" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="95"/>
+      <c r="A493" s="104"/>
       <c r="B493" s="80" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C493" s="75" t="s">
         <v>90</v>
@@ -30391,13 +30403,13 @@
         <v>40</v>
       </c>
       <c r="E493" s="90" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F493" s="80" t="s">
         <v>80</v>
       </c>
       <c r="G493" s="75" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H493" s="75">
         <v>2</v>
@@ -30432,11 +30444,11 @@
       <c r="S493" s="80"/>
     </row>
     <row r="494" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="93">
+      <c r="A494" s="97">
         <v>124</v>
       </c>
       <c r="B494" s="80" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C494" s="75" t="s">
         <v>148</v>
@@ -30445,7 +30457,7 @@
         <v>40</v>
       </c>
       <c r="E494" s="90" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F494" s="80" t="s">
         <v>80</v>
@@ -30487,10 +30499,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="495" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A495" s="93"/>
+    <row r="495" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="97"/>
       <c r="B495" s="80" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C495" s="75" t="s">
         <v>148</v>
@@ -30502,13 +30514,13 @@
         <v>61</v>
       </c>
       <c r="F495" s="80" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G495" s="80" t="s">
         <v>1018</v>
       </c>
-      <c r="G495" s="80" t="s">
-        <v>1019</v>
-      </c>
       <c r="H495" s="80" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="I495" s="80"/>
       <c r="J495" s="80"/>
@@ -30538,9 +30550,9 @@
       </c>
     </row>
     <row r="496" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="93"/>
+      <c r="A496" s="97"/>
       <c r="B496" s="80" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C496" s="75" t="s">
         <v>148</v>
@@ -30550,13 +30562,13 @@
       </c>
       <c r="E496" s="90"/>
       <c r="F496" s="80" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G496" s="80" t="s">
         <v>1020</v>
       </c>
-      <c r="G496" s="80" t="s">
-        <v>1021</v>
-      </c>
       <c r="H496" s="80" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="I496" s="80"/>
       <c r="J496" s="80"/>
@@ -30590,9 +30602,9 @@
       </c>
     </row>
     <row r="497" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="93"/>
+      <c r="A497" s="97"/>
       <c r="B497" s="80" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C497" s="75" t="s">
         <v>148</v>
@@ -30645,7 +30657,7 @@
     <row r="498" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="75"/>
       <c r="B498" s="80" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C498" s="75" t="s">
         <v>335</v>
@@ -30705,7 +30717,7 @@
         <v>126</v>
       </c>
       <c r="B499" s="80" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C499" s="80" t="s">
         <v>335</v>
@@ -30720,7 +30732,7 @@
         <v>100</v>
       </c>
       <c r="G499" s="75" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H499" s="75">
         <v>30</v>
@@ -30756,13 +30768,13 @@
       </c>
       <c r="R499" s="89"/>
       <c r="S499" s="80" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="500" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="98"/>
       <c r="B500" s="80" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C500" s="80" t="s">
         <v>335</v>
@@ -30774,10 +30786,10 @@
         <v>61</v>
       </c>
       <c r="F500" s="80" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G500" s="75" t="s">
         <v>1026</v>
-      </c>
-      <c r="G500" s="75" t="s">
-        <v>1027</v>
       </c>
       <c r="H500" s="75">
         <v>9</v>
@@ -30811,7 +30823,7 @@
     <row r="501" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="98"/>
       <c r="B501" s="80" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C501" s="80" t="s">
         <v>335</v>
@@ -30823,10 +30835,10 @@
         <v>61</v>
       </c>
       <c r="F501" s="80" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G501" s="80" t="s">
         <v>1028</v>
-      </c>
-      <c r="G501" s="80" t="s">
-        <v>1029</v>
       </c>
       <c r="H501" s="80">
         <v>10</v>
@@ -30859,15 +30871,15 @@
       </c>
       <c r="R501" s="75"/>
       <c r="S501" s="80" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="502" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A502" s="97">
+        <v>127</v>
+      </c>
+      <c r="B502" s="80" t="s">
         <v>1030</v>
-      </c>
-    </row>
-    <row r="502" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="93">
-        <v>127</v>
-      </c>
-      <c r="B502" s="80" t="s">
-        <v>1031</v>
       </c>
       <c r="C502" s="75" t="s">
         <v>291</v>
@@ -30879,10 +30891,10 @@
         <v>20240214000273</v>
       </c>
       <c r="F502" s="80" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G502" s="80" t="s">
         <v>1032</v>
-      </c>
-      <c r="G502" s="80" t="s">
-        <v>1033</v>
       </c>
       <c r="H502" s="80">
         <v>2.8</v>
@@ -30919,13 +30931,13 @@
         <v>0</v>
       </c>
       <c r="S502" s="80" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="503" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="93"/>
+      <c r="A503" s="97"/>
       <c r="B503" s="80" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C503" s="75" t="s">
         <v>291</v>
@@ -30934,7 +30946,7 @@
         <v>40</v>
       </c>
       <c r="E503" s="90" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F503" s="80" t="s">
         <v>264</v>
@@ -30979,9 +30991,9 @@
       <c r="S503" s="80"/>
     </row>
     <row r="504" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="93"/>
+      <c r="A504" s="97"/>
       <c r="B504" s="60" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C504" s="61" t="s">
         <v>291</v>
@@ -30990,10 +31002,10 @@
         <v>40</v>
       </c>
       <c r="E504" s="62" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F504" s="60" t="s">
         <v>1036</v>
-      </c>
-      <c r="F504" s="60" t="s">
-        <v>1037</v>
       </c>
       <c r="G504" s="61">
         <v>0</v>
@@ -31031,7 +31043,7 @@
         <v>0</v>
       </c>
       <c r="S504" s="60" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="505" spans="1:19" ht="55.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -31041,7 +31053,7 @@
     </row>
     <row r="506" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="E506" s="64" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="K506" s="9"/>
       <c r="R506" s="32"/>
@@ -31102,92 +31114,49 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:S506" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-    <filterColumn colId="13">
+    <filterColumn colId="2">
       <filters>
-        <filter val="Recursos propios + regalías"/>
-        <filter val="Regalías"/>
-        <filter val="Regalías + Recursos Propios"/>
+        <filter val="Oriente"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="M91:M100"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="R91:R92"/>
-    <mergeCell ref="E474:E475"/>
-    <mergeCell ref="S91:S92"/>
-    <mergeCell ref="M474:M475"/>
-    <mergeCell ref="K474:K475"/>
-    <mergeCell ref="L474:L475"/>
-    <mergeCell ref="S474:S475"/>
-    <mergeCell ref="S433:S434"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="H311:H312"/>
-    <mergeCell ref="J309:J310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="I311:I312"/>
-    <mergeCell ref="J311:J312"/>
-    <mergeCell ref="E311:E312"/>
-    <mergeCell ref="K91:K100"/>
-    <mergeCell ref="L91:L100"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A152:A163"/>
-    <mergeCell ref="A213:A217"/>
-    <mergeCell ref="A222:A227"/>
-    <mergeCell ref="A234:A239"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A254:A259"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A208:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A304:A307"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A275"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A284:A292"/>
-    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A407:A410"/>
+    <mergeCell ref="A411:A415"/>
+    <mergeCell ref="A416:A423"/>
+    <mergeCell ref="A426:A432"/>
+    <mergeCell ref="A433:A438"/>
+    <mergeCell ref="K433:K434"/>
+    <mergeCell ref="R433:R434"/>
+    <mergeCell ref="L433:L434"/>
+    <mergeCell ref="M433:M434"/>
+    <mergeCell ref="N433:N434"/>
+    <mergeCell ref="O433:O434"/>
+    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="A320:A329"/>
+    <mergeCell ref="A334:A337"/>
+    <mergeCell ref="A339:A340"/>
+    <mergeCell ref="A341:A347"/>
+    <mergeCell ref="A502:A504"/>
+    <mergeCell ref="A467:A473"/>
+    <mergeCell ref="A474:A477"/>
+    <mergeCell ref="A485:A487"/>
+    <mergeCell ref="A490:A493"/>
+    <mergeCell ref="A494:A497"/>
+    <mergeCell ref="A499:A501"/>
+    <mergeCell ref="A439:A446"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="A449:A452"/>
+    <mergeCell ref="A453:A455"/>
+    <mergeCell ref="A456:A460"/>
+    <mergeCell ref="A348:A350"/>
+    <mergeCell ref="A351:A356"/>
+    <mergeCell ref="A362:A363"/>
+    <mergeCell ref="A367:A371"/>
+    <mergeCell ref="A372:A383"/>
+    <mergeCell ref="A384:A391"/>
+    <mergeCell ref="A393:A398"/>
     <mergeCell ref="A399:A404"/>
     <mergeCell ref="A405:A406"/>
     <mergeCell ref="P309:P310"/>
@@ -31212,42 +31181,83 @@
     <mergeCell ref="P311:P312"/>
     <mergeCell ref="S311:S312"/>
     <mergeCell ref="R311:R312"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="A320:A329"/>
-    <mergeCell ref="A334:A337"/>
-    <mergeCell ref="A339:A340"/>
-    <mergeCell ref="A341:A347"/>
-    <mergeCell ref="A502:A504"/>
-    <mergeCell ref="A467:A473"/>
-    <mergeCell ref="A474:A477"/>
-    <mergeCell ref="A485:A487"/>
-    <mergeCell ref="A490:A493"/>
-    <mergeCell ref="A494:A497"/>
-    <mergeCell ref="A499:A501"/>
-    <mergeCell ref="A439:A446"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="A449:A452"/>
-    <mergeCell ref="A453:A455"/>
-    <mergeCell ref="A456:A460"/>
-    <mergeCell ref="A348:A350"/>
-    <mergeCell ref="A351:A356"/>
-    <mergeCell ref="A362:A363"/>
-    <mergeCell ref="A367:A371"/>
-    <mergeCell ref="A372:A383"/>
-    <mergeCell ref="A384:A391"/>
-    <mergeCell ref="A393:A398"/>
-    <mergeCell ref="A407:A410"/>
-    <mergeCell ref="A411:A415"/>
-    <mergeCell ref="A416:A423"/>
-    <mergeCell ref="A426:A432"/>
-    <mergeCell ref="A433:A438"/>
-    <mergeCell ref="K433:K434"/>
-    <mergeCell ref="R433:R434"/>
-    <mergeCell ref="L433:L434"/>
-    <mergeCell ref="M433:M434"/>
-    <mergeCell ref="N433:N434"/>
-    <mergeCell ref="O433:O434"/>
-    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="A294:A296"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A304:A307"/>
+    <mergeCell ref="F309:F310"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A275"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A284:A292"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A213:A217"/>
+    <mergeCell ref="A222:A227"/>
+    <mergeCell ref="A234:A239"/>
+    <mergeCell ref="A240:A246"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A254:A259"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A190:A192"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A152:A163"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A116"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="M91:M100"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="R91:R92"/>
+    <mergeCell ref="E474:E475"/>
+    <mergeCell ref="S91:S92"/>
+    <mergeCell ref="M474:M475"/>
+    <mergeCell ref="K474:K475"/>
+    <mergeCell ref="L474:L475"/>
+    <mergeCell ref="S474:S475"/>
+    <mergeCell ref="S433:S434"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="H311:H312"/>
+    <mergeCell ref="J309:J310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="I311:I312"/>
+    <mergeCell ref="J311:J312"/>
+    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="K91:K100"/>
+    <mergeCell ref="L91:L100"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -31278,29 +31288,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="40.799999999999997" x14ac:dyDescent="0.7">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="116" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C2" s="116"/>
+      <c r="D2" s="24" t="s">
         <v>1040</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>1041</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="F2" s="25" t="s">
         <v>1042</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="26" t="s">
         <v>1043</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B3" s="15" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>1045</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>1046</v>
       </c>
       <c r="D3" s="18">
         <v>108554215084</v>
@@ -31322,10 +31332,10 @@
     </row>
     <row r="4" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B4" s="16" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>1047</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>1048</v>
       </c>
       <c r="D4" s="20">
         <v>104855613958</v>
@@ -31347,10 +31357,10 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.7">
       <c r="B5" s="16" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>1049</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>1050</v>
       </c>
       <c r="D5" s="20">
         <v>144973755369</v>
@@ -31368,10 +31378,10 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.7">
       <c r="B6" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>1051</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>1052</v>
       </c>
       <c r="D6" s="20">
         <v>54441800920</v>
@@ -31389,10 +31399,10 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.7">
       <c r="B7" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>1053</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>1054</v>
       </c>
       <c r="D7" s="20">
         <v>72870090400</v>
@@ -31411,10 +31421,10 @@
     </row>
     <row r="8" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B8" s="16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>1055</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>1056</v>
       </c>
       <c r="D8" s="20">
         <v>57385592096</v>
@@ -31432,10 +31442,10 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.7">
       <c r="B9" s="16" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>1057</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>1058</v>
       </c>
       <c r="D9" s="20">
         <v>26362070969</v>
@@ -31453,10 +31463,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.7">
       <c r="B10" s="16" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>1059</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>1060</v>
       </c>
       <c r="D10" s="20">
         <v>124487403196</v>
@@ -31488,6 +31498,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -31643,24 +31670,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31676,22 +31704,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB81A53B-146C-45F4-90FC-69F97FE40998}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D74BB8-CE1A-471A-BFDB-1C46CDB7D2AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4509,49 +4509,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4566,14 +4542,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4929,10 +4929,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="107"/>
+      <c r="C1" s="109"/>
       <c r="D1" s="87"/>
       <c r="E1" s="37"/>
       <c r="F1" s="87"/>
@@ -5009,7 +5009,7 @@
       <c r="U2" s="14"/>
     </row>
     <row r="3" spans="1:21" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="104">
+      <c r="A3" s="96">
         <v>1</v>
       </c>
       <c r="B3" s="77" t="s">
@@ -5070,7 +5070,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="104"/>
+      <c r="A4" s="96"/>
       <c r="B4" s="80" t="s">
         <v>19</v>
       </c>
@@ -5129,7 +5129,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="104"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="81" t="s">
         <v>19</v>
       </c>
@@ -5233,7 +5233,7 @@
       <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:21" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="103">
+      <c r="A7" s="100">
         <v>2</v>
       </c>
       <c r="B7" s="80" t="s">
@@ -5266,7 +5266,7 @@
       <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:21" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="108"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="80" t="s">
         <v>38</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="108"/>
+      <c r="A9" s="95"/>
       <c r="B9" s="80" t="s">
         <v>38</v>
       </c>
@@ -5372,7 +5372,7 @@
       <c r="S9" s="75"/>
     </row>
     <row r="10" spans="1:21" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="104"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="75" t="s">
         <v>38</v>
       </c>
@@ -5428,7 +5428,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A11" s="97">
+      <c r="A11" s="94">
         <v>3</v>
       </c>
       <c r="B11" s="86" t="s">
@@ -5489,7 +5489,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="80" t="s">
         <v>56</v>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="S12" s="85"/>
     </row>
     <row r="13" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="97"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="80" t="s">
         <v>56</v>
       </c>
@@ -5597,7 +5597,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="97"/>
+      <c r="A14" s="94"/>
       <c r="B14" s="80" t="s">
         <v>56</v>
       </c>
@@ -5651,7 +5651,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="97"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="80" t="s">
         <v>56</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="S15" s="75"/>
     </row>
     <row r="16" spans="1:21" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="97"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="80" t="s">
         <v>56</v>
       </c>
@@ -5914,7 +5914,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="97.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="97">
+      <c r="A20" s="94">
         <v>5</v>
       </c>
       <c r="B20" s="80" t="s">
@@ -5974,7 +5974,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="97"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="80" t="s">
         <v>89</v>
       </c>
@@ -6030,7 +6030,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="97"/>
+      <c r="A22" s="94"/>
       <c r="B22" s="80" t="s">
         <v>89</v>
       </c>
@@ -6087,7 +6087,7 @@
       </c>
     </row>
     <row r="23" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="97"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="80" t="s">
         <v>89</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="S23" s="80"/>
     </row>
     <row r="24" spans="1:19" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="97">
+      <c r="A24" s="94">
         <v>6</v>
       </c>
       <c r="B24" s="80" t="s">
@@ -6201,7 +6201,7 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="97"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="80" t="s">
         <v>106</v>
       </c>
@@ -6255,7 +6255,7 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
+      <c r="A26" s="94"/>
       <c r="B26" s="80" t="s">
         <v>106</v>
       </c>
@@ -6309,7 +6309,7 @@
       </c>
     </row>
     <row r="27" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="97"/>
+      <c r="A27" s="94"/>
       <c r="B27" s="80" t="s">
         <v>106</v>
       </c>
@@ -6365,7 +6365,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="97"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="80" t="s">
         <v>106</v>
       </c>
@@ -6417,7 +6417,7 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="97"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="80" t="s">
         <v>106</v>
       </c>
@@ -6471,7 +6471,7 @@
       </c>
     </row>
     <row r="30" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="97"/>
+      <c r="A30" s="94"/>
       <c r="B30" s="80" t="s">
         <v>106</v>
       </c>
@@ -6521,7 +6521,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="97"/>
+      <c r="A31" s="94"/>
       <c r="B31" s="80" t="s">
         <v>106</v>
       </c>
@@ -6577,7 +6577,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="97"/>
+      <c r="A32" s="94"/>
       <c r="B32" s="80" t="s">
         <v>106</v>
       </c>
@@ -6635,7 +6635,7 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="97"/>
+      <c r="A33" s="94"/>
       <c r="B33" s="80" t="s">
         <v>106</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="97"/>
+      <c r="A34" s="94"/>
       <c r="B34" s="80" t="s">
         <v>106</v>
       </c>
@@ -6747,7 +6747,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="108"/>
+      <c r="A35" s="95"/>
       <c r="B35" s="80" t="s">
         <v>144</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="S35" s="80"/>
     </row>
     <row r="36" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="104"/>
+      <c r="A36" s="96"/>
       <c r="B36" s="80" t="s">
         <v>144</v>
       </c>
@@ -6888,7 +6888,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="97">
+      <c r="A38" s="94">
         <v>8</v>
       </c>
       <c r="B38" s="80" t="s">
@@ -6947,7 +6947,7 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="97"/>
+      <c r="A39" s="94"/>
       <c r="B39" s="80" t="s">
         <v>147</v>
       </c>
@@ -7005,7 +7005,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="97"/>
+      <c r="A40" s="94"/>
       <c r="B40" s="80" t="s">
         <v>147</v>
       </c>
@@ -7060,7 +7060,7 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="97">
+      <c r="A41" s="94">
         <v>9</v>
       </c>
       <c r="B41" s="80" t="s">
@@ -7118,7 +7118,7 @@
       <c r="S41" s="80"/>
     </row>
     <row r="42" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="97"/>
+      <c r="A42" s="94"/>
       <c r="B42" s="80" t="s">
         <v>157</v>
       </c>
@@ -7165,7 +7165,7 @@
       </c>
     </row>
     <row r="43" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="97"/>
+      <c r="A43" s="94"/>
       <c r="B43" s="80" t="s">
         <v>157</v>
       </c>
@@ -7214,7 +7214,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="97"/>
+      <c r="A44" s="94"/>
       <c r="B44" s="80" t="s">
         <v>157</v>
       </c>
@@ -7260,7 +7260,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="97"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="80" t="s">
         <v>157</v>
       </c>
@@ -7314,7 +7314,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="97">
+      <c r="A46" s="94">
         <v>10</v>
       </c>
       <c r="B46" s="80" t="s">
@@ -7368,7 +7368,7 @@
       </c>
     </row>
     <row r="47" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="103"/>
+      <c r="A47" s="100"/>
       <c r="B47" s="80" t="s">
         <v>172</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="S47" s="80"/>
     </row>
     <row r="48" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="97"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="80" t="s">
         <v>179</v>
       </c>
@@ -7453,7 +7453,7 @@
       <c r="S48" s="80"/>
     </row>
     <row r="49" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="97"/>
+      <c r="A49" s="94"/>
       <c r="B49" s="80" t="s">
         <v>179</v>
       </c>
@@ -7490,7 +7490,7 @@
       </c>
     </row>
     <row r="50" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="97"/>
+      <c r="A50" s="94"/>
       <c r="B50" s="80" t="s">
         <v>179</v>
       </c>
@@ -7542,7 +7542,7 @@
       </c>
     </row>
     <row r="51" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="97"/>
+      <c r="A51" s="94"/>
       <c r="B51" s="80" t="s">
         <v>179</v>
       </c>
@@ -7594,7 +7594,7 @@
       </c>
     </row>
     <row r="52" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="97"/>
+      <c r="A52" s="94"/>
       <c r="B52" s="80" t="s">
         <v>179</v>
       </c>
@@ -7646,7 +7646,7 @@
       </c>
     </row>
     <row r="53" spans="1:19" ht="45.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="97"/>
+      <c r="A53" s="94"/>
       <c r="B53" s="80" t="s">
         <v>179</v>
       </c>
@@ -7698,7 +7698,7 @@
       </c>
     </row>
     <row r="54" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="97"/>
+      <c r="A54" s="94"/>
       <c r="B54" s="80" t="s">
         <v>194</v>
       </c>
@@ -7749,7 +7749,7 @@
       </c>
     </row>
     <row r="55" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="97"/>
+      <c r="A55" s="94"/>
       <c r="B55" s="80" t="s">
         <v>194</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="S55" s="75"/>
     </row>
     <row r="56" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="97"/>
+      <c r="A56" s="94"/>
       <c r="B56" s="80" t="s">
         <v>194</v>
       </c>
@@ -7857,7 +7857,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="97"/>
+      <c r="A57" s="94"/>
       <c r="B57" s="80" t="s">
         <v>194</v>
       </c>
@@ -7911,7 +7911,7 @@
       <c r="S57" s="80"/>
     </row>
     <row r="58" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="97"/>
+      <c r="A58" s="94"/>
       <c r="B58" s="80" t="s">
         <v>194</v>
       </c>
@@ -7968,7 +7968,7 @@
       </c>
     </row>
     <row r="59" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="104"/>
+      <c r="A59" s="96"/>
       <c r="B59" s="80" t="s">
         <v>206</v>
       </c>
@@ -8022,7 +8022,7 @@
       </c>
     </row>
     <row r="60" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="104"/>
+      <c r="A60" s="96"/>
       <c r="B60" s="80" t="s">
         <v>206</v>
       </c>
@@ -8075,7 +8075,7 @@
       </c>
     </row>
     <row r="61" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="97"/>
+      <c r="A61" s="94"/>
       <c r="B61" s="70" t="s">
         <v>206</v>
       </c>
@@ -8126,7 +8126,7 @@
       </c>
     </row>
     <row r="62" spans="1:19" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="103">
+      <c r="A62" s="100">
         <v>14</v>
       </c>
       <c r="B62" s="80" t="s">
@@ -8181,7 +8181,7 @@
       </c>
     </row>
     <row r="63" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="108"/>
+      <c r="A63" s="95"/>
       <c r="B63" s="80" t="s">
         <v>212</v>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
     </row>
     <row r="64" spans="1:19" ht="107.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="104"/>
+      <c r="A64" s="96"/>
       <c r="B64" s="80" t="s">
         <v>212</v>
       </c>
@@ -8391,7 +8391,7 @@
       </c>
     </row>
     <row r="67" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="103">
+      <c r="A67" s="100">
         <v>16</v>
       </c>
       <c r="B67" s="80" t="s">
@@ -8444,7 +8444,7 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="104"/>
+      <c r="A68" s="96"/>
       <c r="B68" s="80" t="s">
         <v>227</v>
       </c>
@@ -8494,7 +8494,7 @@
       </c>
     </row>
     <row r="69" spans="1:19" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="103">
+      <c r="A69" s="100">
         <v>17</v>
       </c>
       <c r="B69" s="80" t="s">
@@ -8547,7 +8547,7 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="108"/>
+      <c r="A70" s="95"/>
       <c r="B70" s="80" t="s">
         <v>233</v>
       </c>
@@ -8599,7 +8599,7 @@
       </c>
     </row>
     <row r="71" spans="1:19" ht="67.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="108"/>
+      <c r="A71" s="95"/>
       <c r="B71" s="80" t="s">
         <v>239</v>
       </c>
@@ -8651,7 +8651,7 @@
       </c>
     </row>
     <row r="72" spans="1:19" ht="174.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="108"/>
+      <c r="A72" s="95"/>
       <c r="B72" s="80" t="s">
         <v>242</v>
       </c>
@@ -8704,7 +8704,7 @@
       </c>
     </row>
     <row r="73" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="108"/>
+      <c r="A73" s="95"/>
       <c r="B73" s="80" t="s">
         <v>242</v>
       </c>
@@ -8754,7 +8754,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="108"/>
+      <c r="A74" s="95"/>
       <c r="B74" s="80" t="s">
         <v>242</v>
       </c>
@@ -8806,7 +8806,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="108"/>
+      <c r="A75" s="95"/>
       <c r="B75" s="80" t="s">
         <v>242</v>
       </c>
@@ -8864,7 +8864,7 @@
       </c>
     </row>
     <row r="76" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="108"/>
+      <c r="A76" s="95"/>
       <c r="B76" s="80" t="s">
         <v>242</v>
       </c>
@@ -8914,7 +8914,7 @@
       <c r="S76" s="80"/>
     </row>
     <row r="77" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="104"/>
+      <c r="A77" s="96"/>
       <c r="B77" s="80" t="s">
         <v>242</v>
       </c>
@@ -8968,7 +8968,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="108"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="80" t="s">
         <v>253</v>
       </c>
@@ -9026,7 +9026,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="108"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="80" t="s">
         <v>253</v>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="S79" s="75"/>
     </row>
     <row r="80" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="108"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="80" t="s">
         <v>253</v>
       </c>
@@ -9130,7 +9130,7 @@
       <c r="S80" s="75"/>
     </row>
     <row r="81" spans="1:20" ht="150.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="108"/>
+      <c r="A81" s="95"/>
       <c r="B81" s="80" t="s">
         <v>253</v>
       </c>
@@ -9183,7 +9183,7 @@
       </c>
     </row>
     <row r="82" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="108"/>
+      <c r="A82" s="95"/>
       <c r="B82" s="80" t="s">
         <v>262</v>
       </c>
@@ -9238,7 +9238,7 @@
       <c r="T82" s="36"/>
     </row>
     <row r="83" spans="1:20" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="108"/>
+      <c r="A83" s="95"/>
       <c r="B83" s="80" t="s">
         <v>262</v>
       </c>
@@ -9290,7 +9290,7 @@
       <c r="T83" s="36"/>
     </row>
     <row r="84" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="108"/>
+      <c r="A84" s="95"/>
       <c r="B84" s="80" t="s">
         <v>262</v>
       </c>
@@ -9342,7 +9342,7 @@
       </c>
     </row>
     <row r="85" spans="1:20" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="108"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="80" t="s">
         <v>262</v>
       </c>
@@ -9393,7 +9393,7 @@
       <c r="T85" s="36"/>
     </row>
     <row r="86" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="108"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="80" t="s">
         <v>262</v>
       </c>
@@ -9448,7 +9448,7 @@
       <c r="T86" s="36"/>
     </row>
     <row r="87" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="108"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="80" t="s">
         <v>262</v>
       </c>
@@ -9503,7 +9503,7 @@
       <c r="T87" s="36"/>
     </row>
     <row r="88" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="108"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="80" t="s">
         <v>262</v>
       </c>
@@ -9558,7 +9558,7 @@
       <c r="T88" s="36"/>
     </row>
     <row r="89" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="108"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="80" t="s">
         <v>262</v>
       </c>
@@ -9611,7 +9611,7 @@
       <c r="T89" s="36"/>
     </row>
     <row r="90" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="108"/>
+      <c r="A90" s="95"/>
       <c r="B90" s="75" t="s">
         <v>262</v>
       </c>
@@ -9658,7 +9658,7 @@
       <c r="T90" s="36"/>
     </row>
     <row r="91" spans="1:20" ht="43.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="108"/>
+      <c r="A91" s="95"/>
       <c r="B91" s="80" t="s">
         <v>282</v>
       </c>
@@ -9682,38 +9682,38 @@
       </c>
       <c r="I91" s="80"/>
       <c r="J91" s="80"/>
-      <c r="K91" s="94">
+      <c r="K91" s="110">
         <v>12438994717</v>
       </c>
-      <c r="L91" s="94">
+      <c r="L91" s="110">
         <v>0</v>
       </c>
-      <c r="M91" s="94">
+      <c r="M91" s="110">
         <f>+K91</f>
         <v>12438994717</v>
       </c>
-      <c r="N91" s="97" t="s">
+      <c r="N91" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="97" t="s">
+      <c r="O91" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="P91" s="97">
+      <c r="P91" s="94">
         <v>2026</v>
       </c>
-      <c r="Q91" s="98" t="s">
+      <c r="Q91" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="R91" s="99">
+      <c r="R91" s="113">
         <v>0</v>
       </c>
-      <c r="S91" s="98" t="s">
+      <c r="S91" s="99" t="s">
         <v>285</v>
       </c>
       <c r="T91" s="36"/>
     </row>
     <row r="92" spans="1:20" ht="40.799999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="108"/>
+      <c r="A92" s="95"/>
       <c r="B92" s="80" t="s">
         <v>282</v>
       </c>
@@ -9737,18 +9737,18 @@
       </c>
       <c r="I92" s="80"/>
       <c r="J92" s="80"/>
-      <c r="K92" s="95"/>
-      <c r="L92" s="95"/>
-      <c r="M92" s="95"/>
-      <c r="N92" s="97"/>
-      <c r="O92" s="97"/>
-      <c r="P92" s="97"/>
-      <c r="Q92" s="98"/>
-      <c r="R92" s="99"/>
-      <c r="S92" s="98"/>
+      <c r="K92" s="111"/>
+      <c r="L92" s="111"/>
+      <c r="M92" s="111"/>
+      <c r="N92" s="94"/>
+      <c r="O92" s="94"/>
+      <c r="P92" s="94"/>
+      <c r="Q92" s="99"/>
+      <c r="R92" s="113"/>
+      <c r="S92" s="99"/>
     </row>
     <row r="93" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="108"/>
+      <c r="A93" s="95"/>
       <c r="B93" s="80" t="s">
         <v>282</v>
       </c>
@@ -9772,9 +9772,9 @@
       </c>
       <c r="I93" s="80"/>
       <c r="J93" s="80"/>
-      <c r="K93" s="95"/>
-      <c r="L93" s="95"/>
-      <c r="M93" s="95"/>
+      <c r="K93" s="111"/>
+      <c r="L93" s="111"/>
+      <c r="M93" s="111"/>
       <c r="N93" s="75" t="s">
         <v>26</v>
       </c>
@@ -9795,7 +9795,7 @@
       </c>
     </row>
     <row r="94" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="108"/>
+      <c r="A94" s="95"/>
       <c r="B94" s="80" t="s">
         <v>282</v>
       </c>
@@ -9817,9 +9817,9 @@
       </c>
       <c r="I94" s="80"/>
       <c r="J94" s="80"/>
-      <c r="K94" s="95"/>
-      <c r="L94" s="95"/>
-      <c r="M94" s="95"/>
+      <c r="K94" s="111"/>
+      <c r="L94" s="111"/>
+      <c r="M94" s="111"/>
       <c r="N94" s="75" t="s">
         <v>26</v>
       </c>
@@ -9840,7 +9840,7 @@
       </c>
     </row>
     <row r="95" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="108"/>
+      <c r="A95" s="95"/>
       <c r="B95" s="80" t="s">
         <v>282</v>
       </c>
@@ -9864,9 +9864,9 @@
       </c>
       <c r="I95" s="75"/>
       <c r="J95" s="75"/>
-      <c r="K95" s="95"/>
-      <c r="L95" s="95"/>
-      <c r="M95" s="95"/>
+      <c r="K95" s="111"/>
+      <c r="L95" s="111"/>
+      <c r="M95" s="111"/>
       <c r="N95" s="75" t="s">
         <v>146</v>
       </c>
@@ -9887,7 +9887,7 @@
       </c>
     </row>
     <row r="96" spans="1:20" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="108"/>
+      <c r="A96" s="95"/>
       <c r="B96" s="80" t="s">
         <v>290</v>
       </c>
@@ -9915,9 +9915,9 @@
       <c r="J96" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="K96" s="95"/>
-      <c r="L96" s="95"/>
-      <c r="M96" s="95"/>
+      <c r="K96" s="111"/>
+      <c r="L96" s="111"/>
+      <c r="M96" s="111"/>
       <c r="N96" s="75" t="s">
         <v>26</v>
       </c>
@@ -9936,7 +9936,7 @@
       </c>
     </row>
     <row r="97" spans="1:19" ht="99.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="108"/>
+      <c r="A97" s="95"/>
       <c r="B97" s="80" t="s">
         <v>290</v>
       </c>
@@ -9964,9 +9964,9 @@
       <c r="J97" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="K97" s="95"/>
-      <c r="L97" s="95"/>
-      <c r="M97" s="95"/>
+      <c r="K97" s="111"/>
+      <c r="L97" s="111"/>
+      <c r="M97" s="111"/>
       <c r="N97" s="75" t="s">
         <v>98</v>
       </c>
@@ -9987,7 +9987,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="108"/>
+      <c r="A98" s="95"/>
       <c r="B98" s="80" t="s">
         <v>299</v>
       </c>
@@ -10011,9 +10011,9 @@
       </c>
       <c r="I98" s="75"/>
       <c r="J98" s="75"/>
-      <c r="K98" s="95"/>
-      <c r="L98" s="95"/>
-      <c r="M98" s="95"/>
+      <c r="K98" s="111"/>
+      <c r="L98" s="111"/>
+      <c r="M98" s="111"/>
       <c r="N98" s="75" t="s">
         <v>146</v>
       </c>
@@ -10034,7 +10034,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="108"/>
+      <c r="A99" s="95"/>
       <c r="B99" s="80" t="s">
         <v>299</v>
       </c>
@@ -10058,9 +10058,9 @@
       </c>
       <c r="I99" s="75"/>
       <c r="J99" s="75"/>
-      <c r="K99" s="95"/>
-      <c r="L99" s="95"/>
-      <c r="M99" s="95"/>
+      <c r="K99" s="111"/>
+      <c r="L99" s="111"/>
+      <c r="M99" s="111"/>
       <c r="N99" s="75" t="s">
         <v>72</v>
       </c>
@@ -10081,7 +10081,7 @@
       </c>
     </row>
     <row r="100" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="108"/>
+      <c r="A100" s="95"/>
       <c r="B100" s="80" t="s">
         <v>299</v>
       </c>
@@ -10105,9 +10105,9 @@
       </c>
       <c r="I100" s="80"/>
       <c r="J100" s="80"/>
-      <c r="K100" s="96"/>
-      <c r="L100" s="96"/>
-      <c r="M100" s="96"/>
+      <c r="K100" s="112"/>
+      <c r="L100" s="112"/>
+      <c r="M100" s="112"/>
       <c r="N100" s="75" t="s">
         <v>35</v>
       </c>
@@ -10128,7 +10128,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="108"/>
+      <c r="A101" s="95"/>
       <c r="B101" s="80" t="s">
         <v>299</v>
       </c>
@@ -10182,7 +10182,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="108"/>
+      <c r="A102" s="95"/>
       <c r="B102" s="80" t="s">
         <v>299</v>
       </c>
@@ -10231,7 +10231,7 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="108"/>
+      <c r="A103" s="95"/>
       <c r="B103" s="80" t="s">
         <v>299</v>
       </c>
@@ -10281,7 +10281,7 @@
       </c>
     </row>
     <row r="104" spans="1:19" ht="53.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="108"/>
+      <c r="A104" s="95"/>
       <c r="B104" s="80" t="s">
         <v>299</v>
       </c>
@@ -10333,7 +10333,7 @@
       <c r="S104" s="75"/>
     </row>
     <row r="105" spans="1:19" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="108"/>
+      <c r="A105" s="95"/>
       <c r="B105" s="80" t="s">
         <v>299</v>
       </c>
@@ -10385,7 +10385,7 @@
       </c>
     </row>
     <row r="106" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="108"/>
+      <c r="A106" s="95"/>
       <c r="B106" s="80" t="s">
         <v>311</v>
       </c>
@@ -10434,7 +10434,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="108"/>
+      <c r="A107" s="95"/>
       <c r="B107" s="80" t="s">
         <v>317</v>
       </c>
@@ -10477,7 +10477,7 @@
       </c>
     </row>
     <row r="108" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="108"/>
+      <c r="A108" s="95"/>
       <c r="B108" s="80" t="s">
         <v>317</v>
       </c>
@@ -10527,7 +10527,7 @@
       <c r="S108" s="75"/>
     </row>
     <row r="109" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="108"/>
+      <c r="A109" s="95"/>
       <c r="B109" s="80" t="s">
         <v>317</v>
       </c>
@@ -10579,7 +10579,7 @@
       <c r="S109" s="80"/>
     </row>
     <row r="110" spans="1:19" ht="60.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="108"/>
+      <c r="A110" s="95"/>
       <c r="B110" s="80" t="s">
         <v>322</v>
       </c>
@@ -10635,7 +10635,7 @@
       <c r="S110" s="80"/>
     </row>
     <row r="111" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="108"/>
+      <c r="A111" s="95"/>
       <c r="B111" s="80" t="s">
         <v>324</v>
       </c>
@@ -10685,7 +10685,7 @@
       </c>
     </row>
     <row r="112" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="108"/>
+      <c r="A112" s="95"/>
       <c r="B112" s="80" t="s">
         <v>324</v>
       </c>
@@ -10735,7 +10735,7 @@
       </c>
     </row>
     <row r="113" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="108"/>
+      <c r="A113" s="95"/>
       <c r="B113" s="80" t="s">
         <v>324</v>
       </c>
@@ -10774,7 +10774,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="22.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="108"/>
+      <c r="A114" s="95"/>
       <c r="B114" s="80" t="s">
         <v>324</v>
       </c>
@@ -10828,7 +10828,7 @@
       </c>
     </row>
     <row r="115" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="108"/>
+      <c r="A115" s="95"/>
       <c r="B115" s="80" t="s">
         <v>334</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
     </row>
     <row r="116" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="104"/>
+      <c r="A116" s="96"/>
       <c r="B116" s="80" t="s">
         <v>339</v>
       </c>
@@ -10994,7 +10994,7 @@
       <c r="S117" s="80"/>
     </row>
     <row r="118" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="97">
+      <c r="A118" s="94">
         <v>30</v>
       </c>
       <c r="B118" s="80" t="s">
@@ -11046,7 +11046,7 @@
       <c r="S118" s="80"/>
     </row>
     <row r="119" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="97"/>
+      <c r="A119" s="94"/>
       <c r="B119" s="80" t="s">
         <v>344</v>
       </c>
@@ -11098,7 +11098,7 @@
       <c r="S119" s="75"/>
     </row>
     <row r="120" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="113">
+      <c r="A120" s="108">
         <v>31</v>
       </c>
       <c r="B120" s="80" t="s">
@@ -11151,7 +11151,7 @@
       </c>
     </row>
     <row r="121" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="98"/>
+      <c r="A121" s="99"/>
       <c r="B121" s="80" t="s">
         <v>347</v>
       </c>
@@ -11202,7 +11202,7 @@
       </c>
     </row>
     <row r="122" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="98"/>
+      <c r="A122" s="99"/>
       <c r="B122" s="80" t="s">
         <v>347</v>
       </c>
@@ -11254,7 +11254,7 @@
       </c>
     </row>
     <row r="123" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="98"/>
+      <c r="A123" s="99"/>
       <c r="B123" s="80" t="s">
         <v>347</v>
       </c>
@@ -11723,7 +11723,7 @@
       <c r="S131" s="75"/>
     </row>
     <row r="132" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="97">
+      <c r="A132" s="94">
         <v>35</v>
       </c>
       <c r="B132" s="80" t="s">
@@ -11779,7 +11779,7 @@
       </c>
     </row>
     <row r="133" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="97"/>
+      <c r="A133" s="94"/>
       <c r="B133" s="80" t="s">
         <v>371</v>
       </c>
@@ -11831,7 +11831,7 @@
       <c r="S133" s="75"/>
     </row>
     <row r="134" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="97"/>
+      <c r="A134" s="94"/>
       <c r="B134" s="80" t="s">
         <v>371</v>
       </c>
@@ -11889,7 +11889,7 @@
       </c>
     </row>
     <row r="135" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="97"/>
+      <c r="A135" s="94"/>
       <c r="B135" s="80" t="s">
         <v>371</v>
       </c>
@@ -11998,7 +11998,7 @@
       <c r="S136" s="80"/>
     </row>
     <row r="137" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A137" s="97">
+      <c r="A137" s="94">
         <v>36</v>
       </c>
       <c r="B137" s="80" t="s">
@@ -12052,7 +12052,7 @@
       <c r="S137" s="80"/>
     </row>
     <row r="138" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="97"/>
+      <c r="A138" s="94"/>
       <c r="B138" s="80" t="s">
         <v>380</v>
       </c>
@@ -12104,7 +12104,7 @@
       <c r="S138" s="80"/>
     </row>
     <row r="139" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="97"/>
+      <c r="A139" s="94"/>
       <c r="B139" s="80" t="s">
         <v>380</v>
       </c>
@@ -12156,7 +12156,7 @@
       <c r="S139" s="80"/>
     </row>
     <row r="140" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="97"/>
+      <c r="A140" s="94"/>
       <c r="B140" s="80" t="s">
         <v>380</v>
       </c>
@@ -12207,7 +12207,7 @@
       <c r="S140" s="80"/>
     </row>
     <row r="141" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A141" s="97"/>
+      <c r="A141" s="94"/>
       <c r="B141" s="80" t="s">
         <v>380</v>
       </c>
@@ -12259,7 +12259,7 @@
       <c r="S141" s="80"/>
     </row>
     <row r="142" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A142" s="97"/>
+      <c r="A142" s="94"/>
       <c r="B142" s="80" t="s">
         <v>380</v>
       </c>
@@ -12311,7 +12311,7 @@
       <c r="S142" s="75"/>
     </row>
     <row r="143" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A143" s="97"/>
+      <c r="A143" s="94"/>
       <c r="B143" s="80" t="s">
         <v>380</v>
       </c>
@@ -12363,7 +12363,7 @@
       <c r="S143" s="80"/>
     </row>
     <row r="144" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A144" s="97">
+      <c r="A144" s="94">
         <v>37</v>
       </c>
       <c r="B144" s="80" t="s">
@@ -12419,7 +12419,7 @@
       </c>
     </row>
     <row r="145" spans="1:19" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="97"/>
+      <c r="A145" s="94"/>
       <c r="B145" s="80" t="s">
         <v>396</v>
       </c>
@@ -12469,7 +12469,7 @@
       </c>
     </row>
     <row r="146" spans="1:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="97"/>
+      <c r="A146" s="94"/>
       <c r="B146" s="80" t="s">
         <v>396</v>
       </c>
@@ -12573,7 +12573,7 @@
       </c>
     </row>
     <row r="148" spans="1:19" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="108"/>
+      <c r="A148" s="95"/>
       <c r="B148" s="80" t="s">
         <v>401</v>
       </c>
@@ -12624,7 +12624,7 @@
       </c>
     </row>
     <row r="149" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="104"/>
+      <c r="A149" s="96"/>
       <c r="B149" s="80" t="s">
         <v>401</v>
       </c>
@@ -12785,7 +12785,7 @@
       </c>
     </row>
     <row r="152" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="103">
+      <c r="A152" s="100">
         <v>40</v>
       </c>
       <c r="B152" s="80" t="s">
@@ -12841,7 +12841,7 @@
       </c>
     </row>
     <row r="153" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="108"/>
+      <c r="A153" s="95"/>
       <c r="B153" s="80" t="s">
         <v>412</v>
       </c>
@@ -12890,7 +12890,7 @@
       </c>
     </row>
     <row r="154" spans="1:19" ht="183.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="108"/>
+      <c r="A154" s="95"/>
       <c r="B154" s="80" t="s">
         <v>412</v>
       </c>
@@ -12937,7 +12937,7 @@
       </c>
     </row>
     <row r="155" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="108"/>
+      <c r="A155" s="95"/>
       <c r="B155" s="80" t="s">
         <v>412</v>
       </c>
@@ -12986,7 +12986,7 @@
       </c>
     </row>
     <row r="156" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="108"/>
+      <c r="A156" s="95"/>
       <c r="B156" s="80" t="s">
         <v>412</v>
       </c>
@@ -13040,7 +13040,7 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="108"/>
+      <c r="A157" s="95"/>
       <c r="B157" s="80" t="s">
         <v>412</v>
       </c>
@@ -13094,7 +13094,7 @@
       </c>
     </row>
     <row r="158" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="108"/>
+      <c r="A158" s="95"/>
       <c r="B158" s="80" t="s">
         <v>412</v>
       </c>
@@ -13148,7 +13148,7 @@
       </c>
     </row>
     <row r="159" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="108"/>
+      <c r="A159" s="95"/>
       <c r="B159" s="80" t="s">
         <v>426</v>
       </c>
@@ -13198,7 +13198,7 @@
       <c r="S159" s="80"/>
     </row>
     <row r="160" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="108"/>
+      <c r="A160" s="95"/>
       <c r="B160" s="80" t="s">
         <v>426</v>
       </c>
@@ -13251,7 +13251,7 @@
       <c r="S160" s="80"/>
     </row>
     <row r="161" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="108"/>
+      <c r="A161" s="95"/>
       <c r="B161" s="80" t="s">
         <v>426</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="S161" s="80"/>
     </row>
     <row r="162" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="108"/>
+      <c r="A162" s="95"/>
       <c r="B162" s="80" t="s">
         <v>426</v>
       </c>
@@ -13355,7 +13355,7 @@
       </c>
     </row>
     <row r="163" spans="1:19" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="104"/>
+      <c r="A163" s="96"/>
       <c r="B163" s="80" t="s">
         <v>434</v>
       </c>
@@ -13406,7 +13406,7 @@
       </c>
     </row>
     <row r="164" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="108"/>
+      <c r="A164" s="95"/>
       <c r="B164" s="80" t="s">
         <v>434</v>
       </c>
@@ -13457,7 +13457,7 @@
       </c>
     </row>
     <row r="165" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="104"/>
+      <c r="A165" s="96"/>
       <c r="B165" s="80" t="s">
         <v>434</v>
       </c>
@@ -13626,7 +13626,7 @@
       </c>
     </row>
     <row r="168" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A168" s="109">
+      <c r="A168" s="101">
         <v>44</v>
       </c>
       <c r="B168" s="80" t="s">
@@ -13684,7 +13684,7 @@
       </c>
     </row>
     <row r="169" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="110"/>
+      <c r="A169" s="102"/>
       <c r="B169" s="80" t="s">
         <v>448</v>
       </c>
@@ -13733,7 +13733,7 @@
       </c>
     </row>
     <row r="170" spans="1:19" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="110"/>
+      <c r="A170" s="102"/>
       <c r="B170" s="80" t="s">
         <v>448</v>
       </c>
@@ -13789,7 +13789,7 @@
       </c>
     </row>
     <row r="171" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A171" s="110"/>
+      <c r="A171" s="102"/>
       <c r="B171" s="80" t="s">
         <v>448</v>
       </c>
@@ -13843,7 +13843,7 @@
       </c>
     </row>
     <row r="172" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A172" s="111"/>
+      <c r="A172" s="103"/>
       <c r="B172" s="80" t="s">
         <v>455</v>
       </c>
@@ -13897,7 +13897,7 @@
       </c>
     </row>
     <row r="173" spans="1:19" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="97">
+      <c r="A173" s="94">
         <v>45</v>
       </c>
       <c r="B173" s="80" t="s">
@@ -13952,7 +13952,7 @@
       </c>
     </row>
     <row r="174" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A174" s="97"/>
+      <c r="A174" s="94"/>
       <c r="B174" s="80" t="s">
         <v>457</v>
       </c>
@@ -14006,7 +14006,7 @@
       </c>
     </row>
     <row r="175" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A175" s="97"/>
+      <c r="A175" s="94"/>
       <c r="B175" s="80" t="s">
         <v>457</v>
       </c>
@@ -14058,7 +14058,7 @@
       <c r="S175" s="80"/>
     </row>
     <row r="176" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A176" s="97"/>
+      <c r="A176" s="94"/>
       <c r="B176" s="80" t="s">
         <v>457</v>
       </c>
@@ -14112,7 +14112,7 @@
       </c>
     </row>
     <row r="177" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A177" s="97"/>
+      <c r="A177" s="94"/>
       <c r="B177" s="80" t="s">
         <v>457</v>
       </c>
@@ -14164,7 +14164,7 @@
       <c r="S177" s="80"/>
     </row>
     <row r="178" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A178" s="97"/>
+      <c r="A178" s="94"/>
       <c r="B178" s="80" t="s">
         <v>465</v>
       </c>
@@ -14218,7 +14218,7 @@
       </c>
     </row>
     <row r="179" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A179" s="97"/>
+      <c r="A179" s="94"/>
       <c r="B179" s="80" t="s">
         <v>467</v>
       </c>
@@ -14373,7 +14373,7 @@
       <c r="S181" s="75"/>
     </row>
     <row r="182" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="112">
+      <c r="A182" s="104">
         <v>46</v>
       </c>
       <c r="B182" s="80" t="s">
@@ -14425,7 +14425,7 @@
       </c>
     </row>
     <row r="183" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="112"/>
+      <c r="A183" s="104"/>
       <c r="B183" s="80" t="s">
         <v>470</v>
       </c>
@@ -14477,7 +14477,7 @@
       </c>
     </row>
     <row r="184" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A184" s="112"/>
+      <c r="A184" s="104"/>
       <c r="B184" s="80" t="s">
         <v>470</v>
       </c>
@@ -14587,7 +14587,7 @@
       </c>
     </row>
     <row r="186" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A186" s="110"/>
+      <c r="A186" s="102"/>
       <c r="B186" s="80" t="s">
         <v>482</v>
       </c>
@@ -14635,7 +14635,7 @@
       </c>
     </row>
     <row r="187" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A187" s="110"/>
+      <c r="A187" s="102"/>
       <c r="B187" s="80" t="s">
         <v>482</v>
       </c>
@@ -14685,7 +14685,7 @@
       <c r="S187" s="80"/>
     </row>
     <row r="188" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="111"/>
+      <c r="A188" s="103"/>
       <c r="B188" s="80" t="s">
         <v>482</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
     </row>
     <row r="190" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="97">
+      <c r="A190" s="94">
         <v>48</v>
       </c>
       <c r="B190" s="80" t="s">
@@ -14840,7 +14840,7 @@
       </c>
     </row>
     <row r="191" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="97"/>
+      <c r="A191" s="94"/>
       <c r="B191" s="80" t="s">
         <v>489</v>
       </c>
@@ -14891,7 +14891,7 @@
       </c>
     </row>
     <row r="192" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="97"/>
+      <c r="A192" s="94"/>
       <c r="B192" s="80" t="s">
         <v>489</v>
       </c>
@@ -14972,7 +14972,7 @@
       <c r="S193" s="75"/>
     </row>
     <row r="194" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="108"/>
+      <c r="A194" s="95"/>
       <c r="B194" s="80" t="s">
         <v>500</v>
       </c>
@@ -15024,7 +15024,7 @@
       </c>
     </row>
     <row r="195" spans="1:19" ht="24.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="104"/>
+      <c r="A195" s="96"/>
       <c r="B195" s="80" t="s">
         <v>500</v>
       </c>
@@ -15076,7 +15076,7 @@
       </c>
     </row>
     <row r="196" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="97">
+      <c r="A196" s="94">
         <v>51</v>
       </c>
       <c r="B196" s="80" t="s">
@@ -15129,7 +15129,7 @@
       </c>
     </row>
     <row r="197" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="97"/>
+      <c r="A197" s="94"/>
       <c r="B197" s="80" t="s">
         <v>504</v>
       </c>
@@ -15183,7 +15183,7 @@
       </c>
     </row>
     <row r="198" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="97"/>
+      <c r="A198" s="94"/>
       <c r="B198" s="80" t="s">
         <v>504</v>
       </c>
@@ -15237,7 +15237,7 @@
       </c>
     </row>
     <row r="199" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="97"/>
+      <c r="A199" s="94"/>
       <c r="B199" s="80" t="s">
         <v>504</v>
       </c>
@@ -15444,7 +15444,7 @@
       </c>
     </row>
     <row r="203" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="97">
+      <c r="A203" s="94">
         <v>53</v>
       </c>
       <c r="B203" s="80" t="s">
@@ -15499,7 +15499,7 @@
       </c>
     </row>
     <row r="204" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="97"/>
+      <c r="A204" s="94"/>
       <c r="B204" s="80" t="s">
         <v>516</v>
       </c>
@@ -15553,7 +15553,7 @@
       </c>
     </row>
     <row r="205" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="97"/>
+      <c r="A205" s="94"/>
       <c r="B205" s="75" t="s">
         <v>520</v>
       </c>
@@ -15607,7 +15607,7 @@
       </c>
     </row>
     <row r="206" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="97">
+      <c r="A206" s="94">
         <v>54</v>
       </c>
       <c r="B206" s="80" t="s">
@@ -15661,7 +15661,7 @@
       </c>
     </row>
     <row r="207" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="97"/>
+      <c r="A207" s="94"/>
       <c r="B207" s="80" t="s">
         <v>523</v>
       </c>
@@ -15717,7 +15717,7 @@
       </c>
     </row>
     <row r="208" spans="1:19" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="97">
+      <c r="A208" s="94">
         <v>55</v>
       </c>
       <c r="B208" s="80" t="s">
@@ -15772,7 +15772,7 @@
       </c>
     </row>
     <row r="209" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A209" s="97"/>
+      <c r="A209" s="94"/>
       <c r="B209" s="80" t="s">
         <v>526</v>
       </c>
@@ -15824,7 +15824,7 @@
       <c r="S209" s="80"/>
     </row>
     <row r="210" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="97"/>
+      <c r="A210" s="94"/>
       <c r="B210" s="80" t="s">
         <v>526</v>
       </c>
@@ -15876,7 +15876,7 @@
       <c r="S210" s="75"/>
     </row>
     <row r="211" spans="1:19" ht="80.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="97">
+      <c r="A211" s="94">
         <v>56</v>
       </c>
       <c r="B211" s="80" t="s">
@@ -15929,7 +15929,7 @@
       </c>
     </row>
     <row r="212" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="97"/>
+      <c r="A212" s="94"/>
       <c r="B212" s="80" t="s">
         <v>535</v>
       </c>
@@ -15985,7 +15985,7 @@
       </c>
     </row>
     <row r="213" spans="1:19" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A213" s="109">
+      <c r="A213" s="101">
         <v>57</v>
       </c>
       <c r="B213" s="80" t="s">
@@ -16038,7 +16038,7 @@
       </c>
     </row>
     <row r="214" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A214" s="110"/>
+      <c r="A214" s="102"/>
       <c r="B214" s="80" t="s">
         <v>537</v>
       </c>
@@ -16092,7 +16092,7 @@
       </c>
     </row>
     <row r="215" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A215" s="110"/>
+      <c r="A215" s="102"/>
       <c r="B215" s="80" t="s">
         <v>537</v>
       </c>
@@ -16146,7 +16146,7 @@
       </c>
     </row>
     <row r="216" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A216" s="108"/>
+      <c r="A216" s="95"/>
       <c r="B216" s="80" t="s">
         <v>537</v>
       </c>
@@ -16199,7 +16199,7 @@
       </c>
     </row>
     <row r="217" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A217" s="111"/>
+      <c r="A217" s="103"/>
       <c r="B217" s="80" t="s">
         <v>537</v>
       </c>
@@ -16468,7 +16468,7 @@
       </c>
     </row>
     <row r="222" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="97">
+      <c r="A222" s="94">
         <v>59</v>
       </c>
       <c r="B222" s="80" t="s">
@@ -16521,7 +16521,7 @@
       </c>
     </row>
     <row r="223" spans="1:19" ht="34.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="97"/>
+      <c r="A223" s="94"/>
       <c r="B223" s="80" t="s">
         <v>558</v>
       </c>
@@ -16575,7 +16575,7 @@
       </c>
     </row>
     <row r="224" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="97"/>
+      <c r="A224" s="94"/>
       <c r="B224" s="80" t="s">
         <v>558</v>
       </c>
@@ -16624,7 +16624,7 @@
       <c r="S224" s="80"/>
     </row>
     <row r="225" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="97"/>
+      <c r="A225" s="94"/>
       <c r="B225" s="80" t="s">
         <v>558</v>
       </c>
@@ -16678,7 +16678,7 @@
       </c>
     </row>
     <row r="226" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="97"/>
+      <c r="A226" s="94"/>
       <c r="B226" s="80" t="s">
         <v>558</v>
       </c>
@@ -16728,7 +16728,7 @@
       <c r="S226" s="75"/>
     </row>
     <row r="227" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="97"/>
+      <c r="A227" s="94"/>
       <c r="B227" s="80" t="s">
         <v>558</v>
       </c>
@@ -17072,7 +17072,7 @@
       </c>
     </row>
     <row r="234" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="103">
+      <c r="A234" s="100">
         <v>63</v>
       </c>
       <c r="B234" s="80" t="s">
@@ -17124,7 +17124,7 @@
       </c>
     </row>
     <row r="235" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="108"/>
+      <c r="A235" s="95"/>
       <c r="B235" s="80" t="s">
         <v>579</v>
       </c>
@@ -17176,7 +17176,7 @@
       </c>
     </row>
     <row r="236" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="108"/>
+      <c r="A236" s="95"/>
       <c r="B236" s="80" t="s">
         <v>579</v>
       </c>
@@ -17228,7 +17228,7 @@
       </c>
     </row>
     <row r="237" spans="1:19" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="108"/>
+      <c r="A237" s="95"/>
       <c r="B237" s="80" t="s">
         <v>579</v>
       </c>
@@ -17281,7 +17281,7 @@
       </c>
     </row>
     <row r="238" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="108"/>
+      <c r="A238" s="95"/>
       <c r="B238" s="80" t="s">
         <v>579</v>
       </c>
@@ -17334,7 +17334,7 @@
       </c>
     </row>
     <row r="239" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="104"/>
+      <c r="A239" s="96"/>
       <c r="B239" s="80" t="s">
         <v>592</v>
       </c>
@@ -17384,7 +17384,7 @@
       </c>
     </row>
     <row r="240" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="97">
+      <c r="A240" s="94">
         <v>64</v>
       </c>
       <c r="B240" s="80" t="s">
@@ -17437,7 +17437,7 @@
       <c r="S240" s="80"/>
     </row>
     <row r="241" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="97"/>
+      <c r="A241" s="94"/>
       <c r="B241" s="80" t="s">
         <v>595</v>
       </c>
@@ -17489,7 +17489,7 @@
       </c>
     </row>
     <row r="242" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="97"/>
+      <c r="A242" s="94"/>
       <c r="B242" s="80" t="s">
         <v>595</v>
       </c>
@@ -17547,7 +17547,7 @@
       </c>
     </row>
     <row r="243" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="97"/>
+      <c r="A243" s="94"/>
       <c r="B243" s="80" t="s">
         <v>595</v>
       </c>
@@ -17597,7 +17597,7 @@
       </c>
     </row>
     <row r="244" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="97"/>
+      <c r="A244" s="94"/>
       <c r="B244" s="80" t="s">
         <v>595</v>
       </c>
@@ -17630,7 +17630,7 @@
       <c r="S244" s="80"/>
     </row>
     <row r="245" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="97"/>
+      <c r="A245" s="94"/>
       <c r="B245" s="80" t="s">
         <v>595</v>
       </c>
@@ -17680,7 +17680,7 @@
       </c>
     </row>
     <row r="246" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="97"/>
+      <c r="A246" s="94"/>
       <c r="B246" s="80" t="s">
         <v>595</v>
       </c>
@@ -17785,7 +17785,7 @@
       <c r="S247" s="80"/>
     </row>
     <row r="248" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="97">
+      <c r="A248" s="94">
         <v>65</v>
       </c>
       <c r="B248" s="80" t="s">
@@ -17838,7 +17838,7 @@
       </c>
     </row>
     <row r="249" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="97"/>
+      <c r="A249" s="94"/>
       <c r="B249" s="80" t="s">
         <v>603</v>
       </c>
@@ -17890,7 +17890,7 @@
       </c>
     </row>
     <row r="250" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="97"/>
+      <c r="A250" s="94"/>
       <c r="B250" s="80" t="s">
         <v>603</v>
       </c>
@@ -18072,7 +18072,7 @@
       <c r="S253" s="75"/>
     </row>
     <row r="254" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A254" s="103">
+      <c r="A254" s="100">
         <v>68</v>
       </c>
       <c r="B254" s="80" t="s">
@@ -18124,7 +18124,7 @@
       </c>
     </row>
     <row r="255" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A255" s="108"/>
+      <c r="A255" s="95"/>
       <c r="B255" s="80" t="s">
         <v>616</v>
       </c>
@@ -18177,7 +18177,7 @@
       </c>
     </row>
     <row r="256" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A256" s="108"/>
+      <c r="A256" s="95"/>
       <c r="B256" s="80" t="s">
         <v>616</v>
       </c>
@@ -18231,7 +18231,7 @@
       </c>
     </row>
     <row r="257" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A257" s="108"/>
+      <c r="A257" s="95"/>
       <c r="B257" s="80" t="s">
         <v>616</v>
       </c>
@@ -18285,7 +18285,7 @@
       </c>
     </row>
     <row r="258" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A258" s="108"/>
+      <c r="A258" s="95"/>
       <c r="B258" s="80" t="s">
         <v>616</v>
       </c>
@@ -18337,7 +18337,7 @@
       </c>
     </row>
     <row r="259" spans="1:19" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="104"/>
+      <c r="A259" s="96"/>
       <c r="B259" s="80" t="s">
         <v>616</v>
       </c>
@@ -18391,7 +18391,7 @@
       </c>
     </row>
     <row r="260" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="103">
+      <c r="A260" s="100">
         <v>69</v>
       </c>
       <c r="B260" s="80" t="s">
@@ -18444,7 +18444,7 @@
       </c>
     </row>
     <row r="261" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="108"/>
+      <c r="A261" s="95"/>
       <c r="B261" s="80" t="s">
         <v>626</v>
       </c>
@@ -18494,7 +18494,7 @@
       </c>
     </row>
     <row r="262" spans="1:19" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="108"/>
+      <c r="A262" s="95"/>
       <c r="B262" s="80" t="s">
         <v>630</v>
       </c>
@@ -18540,7 +18540,7 @@
       </c>
     </row>
     <row r="263" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="108"/>
+      <c r="A263" s="95"/>
       <c r="B263" s="80" t="s">
         <v>630</v>
       </c>
@@ -18588,7 +18588,7 @@
       </c>
     </row>
     <row r="264" spans="1:19" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="108"/>
+      <c r="A264" s="95"/>
       <c r="B264" s="80" t="s">
         <v>626</v>
       </c>
@@ -18695,7 +18695,7 @@
       <c r="S265" s="80"/>
     </row>
     <row r="266" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="97">
+      <c r="A266" s="94">
         <v>70</v>
       </c>
       <c r="B266" s="80" t="s">
@@ -18751,7 +18751,7 @@
       <c r="S266" s="80"/>
     </row>
     <row r="267" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="97"/>
+      <c r="A267" s="94"/>
       <c r="B267" s="80" t="s">
         <v>636</v>
       </c>
@@ -18805,7 +18805,7 @@
       <c r="S267" s="80"/>
     </row>
     <row r="268" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="97"/>
+      <c r="A268" s="94"/>
       <c r="B268" s="80" t="s">
         <v>636</v>
       </c>
@@ -18859,7 +18859,7 @@
       <c r="S268" s="80"/>
     </row>
     <row r="269" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="97"/>
+      <c r="A269" s="94"/>
       <c r="B269" s="80" t="s">
         <v>636</v>
       </c>
@@ -18967,7 +18967,7 @@
       </c>
     </row>
     <row r="271" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="97">
+      <c r="A271" s="94">
         <v>71</v>
       </c>
       <c r="B271" s="80" t="s">
@@ -19021,7 +19021,7 @@
       <c r="S271" s="80"/>
     </row>
     <row r="272" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="97"/>
+      <c r="A272" s="94"/>
       <c r="B272" s="80" t="s">
         <v>646</v>
       </c>
@@ -19075,7 +19075,7 @@
       </c>
     </row>
     <row r="273" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A273" s="97"/>
+      <c r="A273" s="94"/>
       <c r="B273" s="80" t="s">
         <v>646</v>
       </c>
@@ -19129,7 +19129,7 @@
       </c>
     </row>
     <row r="274" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A274" s="97"/>
+      <c r="A274" s="94"/>
       <c r="B274" s="80" t="s">
         <v>646</v>
       </c>
@@ -19183,7 +19183,7 @@
       </c>
     </row>
     <row r="275" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A275" s="97"/>
+      <c r="A275" s="94"/>
       <c r="B275" s="75" t="s">
         <v>653</v>
       </c>
@@ -19449,7 +19449,7 @@
       <c r="S279" s="75"/>
     </row>
     <row r="280" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="97">
+      <c r="A280" s="94">
         <v>74</v>
       </c>
       <c r="B280" s="80" t="s">
@@ -19501,7 +19501,7 @@
       </c>
     </row>
     <row r="281" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="97"/>
+      <c r="A281" s="94"/>
       <c r="B281" s="80" t="s">
         <v>662</v>
       </c>
@@ -19548,7 +19548,7 @@
       <c r="S281" s="75"/>
     </row>
     <row r="282" spans="1:19" ht="37.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="97">
+      <c r="A282" s="94">
         <v>75</v>
       </c>
       <c r="B282" s="80" t="s">
@@ -19601,7 +19601,7 @@
       </c>
     </row>
     <row r="283" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="97"/>
+      <c r="A283" s="94"/>
       <c r="B283" s="80" t="s">
         <v>665</v>
       </c>
@@ -19653,7 +19653,7 @@
       <c r="S283" s="80"/>
     </row>
     <row r="284" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A284" s="104">
+      <c r="A284" s="96">
         <v>76</v>
       </c>
       <c r="B284" s="80" t="s">
@@ -19709,7 +19709,7 @@
       </c>
     </row>
     <row r="285" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A285" s="104"/>
+      <c r="A285" s="96"/>
       <c r="B285" s="80" t="s">
         <v>669</v>
       </c>
@@ -19763,7 +19763,7 @@
       </c>
     </row>
     <row r="286" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A286" s="104"/>
+      <c r="A286" s="96"/>
       <c r="B286" s="80" t="s">
         <v>669</v>
       </c>
@@ -19817,7 +19817,7 @@
       </c>
     </row>
     <row r="287" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A287" s="104"/>
+      <c r="A287" s="96"/>
       <c r="B287" s="80" t="s">
         <v>669</v>
       </c>
@@ -19871,7 +19871,7 @@
       </c>
     </row>
     <row r="288" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A288" s="97"/>
+      <c r="A288" s="94"/>
       <c r="B288" s="80" t="s">
         <v>669</v>
       </c>
@@ -19922,7 +19922,7 @@
       </c>
     </row>
     <row r="289" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A289" s="97"/>
+      <c r="A289" s="94"/>
       <c r="B289" s="80" t="s">
         <v>669</v>
       </c>
@@ -19974,7 +19974,7 @@
       </c>
     </row>
     <row r="290" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A290" s="97"/>
+      <c r="A290" s="94"/>
       <c r="B290" s="80" t="s">
         <v>669</v>
       </c>
@@ -20028,7 +20028,7 @@
       </c>
     </row>
     <row r="291" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A291" s="97"/>
+      <c r="A291" s="94"/>
       <c r="B291" s="80" t="s">
         <v>669</v>
       </c>
@@ -20078,7 +20078,7 @@
       <c r="S291" s="80"/>
     </row>
     <row r="292" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A292" s="97"/>
+      <c r="A292" s="94"/>
       <c r="B292" s="80" t="s">
         <v>669</v>
       </c>
@@ -20188,7 +20188,7 @@
       </c>
     </row>
     <row r="294" spans="1:19" ht="142.80000000000001" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="97">
+      <c r="A294" s="94">
         <v>77</v>
       </c>
       <c r="B294" s="80" t="s">
@@ -20248,7 +20248,7 @@
       </c>
     </row>
     <row r="295" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="97"/>
+      <c r="A295" s="94"/>
       <c r="B295" s="80" t="s">
         <v>684</v>
       </c>
@@ -20306,7 +20306,7 @@
       </c>
     </row>
     <row r="296" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="97"/>
+      <c r="A296" s="94"/>
       <c r="B296" s="80" t="s">
         <v>684</v>
       </c>
@@ -20364,7 +20364,7 @@
       </c>
     </row>
     <row r="297" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="97">
+      <c r="A297" s="94">
         <v>78</v>
       </c>
       <c r="B297" s="80" t="s">
@@ -20417,7 +20417,7 @@
       </c>
     </row>
     <row r="298" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="97"/>
+      <c r="A298" s="94"/>
       <c r="B298" s="80" t="s">
         <v>695</v>
       </c>
@@ -20469,7 +20469,7 @@
       <c r="S298" s="80"/>
     </row>
     <row r="299" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="97"/>
+      <c r="A299" s="94"/>
       <c r="B299" s="80" t="s">
         <v>695</v>
       </c>
@@ -20523,7 +20523,7 @@
       </c>
     </row>
     <row r="300" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="108"/>
+      <c r="A300" s="95"/>
       <c r="B300" s="80" t="s">
         <v>630</v>
       </c>
@@ -20575,7 +20575,7 @@
       <c r="S300" s="80"/>
     </row>
     <row r="301" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="104"/>
+      <c r="A301" s="96"/>
       <c r="B301" s="80" t="s">
         <v>630</v>
       </c>
@@ -20629,7 +20629,7 @@
       </c>
     </row>
     <row r="302" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="103">
+      <c r="A302" s="100">
         <v>80</v>
       </c>
       <c r="B302" s="80" t="s">
@@ -20682,7 +20682,7 @@
       </c>
     </row>
     <row r="303" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="108"/>
+      <c r="A303" s="95"/>
       <c r="B303" s="80" t="s">
         <v>708</v>
       </c>
@@ -20734,7 +20734,7 @@
       <c r="S303" s="80"/>
     </row>
     <row r="304" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="103">
+      <c r="A304" s="100">
         <v>81</v>
       </c>
       <c r="B304" s="80" t="s">
@@ -20786,7 +20786,7 @@
       </c>
     </row>
     <row r="305" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="108"/>
+      <c r="A305" s="95"/>
       <c r="B305" s="80" t="s">
         <v>710</v>
       </c>
@@ -20838,7 +20838,7 @@
       </c>
     </row>
     <row r="306" spans="1:19" ht="81.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="108"/>
+      <c r="A306" s="95"/>
       <c r="B306" s="80" t="s">
         <v>710</v>
       </c>
@@ -20889,7 +20889,7 @@
       </c>
     </row>
     <row r="307" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="104"/>
+      <c r="A307" s="96"/>
       <c r="B307" s="80" t="s">
         <v>710</v>
       </c>
@@ -21011,54 +21011,54 @@
       <c r="D309" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E309" s="105">
+      <c r="E309" s="106">
         <v>4600018191</v>
       </c>
-      <c r="F309" s="114" t="s">
+      <c r="F309" s="105" t="s">
         <v>1063</v>
       </c>
-      <c r="G309" s="97" t="s">
+      <c r="G309" s="94" t="s">
         <v>721</v>
       </c>
-      <c r="H309" s="97">
+      <c r="H309" s="94">
         <v>13.3</v>
       </c>
-      <c r="I309" s="103" t="s">
+      <c r="I309" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="J309" s="103" t="s">
+      <c r="J309" s="100" t="s">
         <v>538</v>
       </c>
-      <c r="K309" s="101">
+      <c r="K309" s="97">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L309" s="101">
+      <c r="L309" s="97">
         <v>0</v>
       </c>
-      <c r="M309" s="101">
+      <c r="M309" s="97">
         <f>+K309</f>
         <v>988077089</v>
       </c>
-      <c r="N309" s="98" t="s">
+      <c r="N309" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="O309" s="98" t="s">
+      <c r="O309" s="99" t="s">
         <v>722</v>
       </c>
-      <c r="P309" s="97">
+      <c r="P309" s="94">
         <v>2025</v>
       </c>
-      <c r="Q309" s="98" t="s">
+      <c r="Q309" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="R309" s="97"/>
-      <c r="S309" s="97" t="s">
+      <c r="R309" s="94"/>
+      <c r="S309" s="94" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="97">
+      <c r="A310" s="94">
         <v>84</v>
       </c>
       <c r="B310" s="80" t="s">
@@ -21070,24 +21070,24 @@
       <c r="D310" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E310" s="106"/>
-      <c r="F310" s="98"/>
-      <c r="G310" s="97"/>
-      <c r="H310" s="97"/>
-      <c r="I310" s="104"/>
-      <c r="J310" s="104"/>
-      <c r="K310" s="101"/>
-      <c r="L310" s="101"/>
-      <c r="M310" s="101"/>
-      <c r="N310" s="98"/>
-      <c r="O310" s="98"/>
-      <c r="P310" s="97"/>
-      <c r="Q310" s="98"/>
-      <c r="R310" s="97"/>
-      <c r="S310" s="97"/>
+      <c r="E310" s="107"/>
+      <c r="F310" s="99"/>
+      <c r="G310" s="94"/>
+      <c r="H310" s="94"/>
+      <c r="I310" s="96"/>
+      <c r="J310" s="96"/>
+      <c r="K310" s="97"/>
+      <c r="L310" s="97"/>
+      <c r="M310" s="97"/>
+      <c r="N310" s="99"/>
+      <c r="O310" s="99"/>
+      <c r="P310" s="94"/>
+      <c r="Q310" s="99"/>
+      <c r="R310" s="94"/>
+      <c r="S310" s="94"/>
     </row>
     <row r="311" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="97"/>
+      <c r="A311" s="94"/>
       <c r="B311" s="80" t="s">
         <v>720</v>
       </c>
@@ -21097,55 +21097,55 @@
       <c r="D311" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E311" s="105">
+      <c r="E311" s="106">
         <v>4600009793</v>
       </c>
-      <c r="F311" s="98" t="s">
+      <c r="F311" s="99" t="s">
         <v>724</v>
       </c>
-      <c r="G311" s="97" t="s">
+      <c r="G311" s="94" t="s">
         <v>725</v>
       </c>
-      <c r="H311" s="97">
+      <c r="H311" s="94">
         <v>31.12</v>
       </c>
-      <c r="I311" s="103" t="s">
+      <c r="I311" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="J311" s="103" t="s">
+      <c r="J311" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="K311" s="101">
+      <c r="K311" s="97">
         <f>+M311</f>
         <v>73907566008</v>
       </c>
-      <c r="L311" s="101">
+      <c r="L311" s="97">
         <v>0</v>
       </c>
-      <c r="M311" s="101">
+      <c r="M311" s="97">
         <v>73907566008</v>
       </c>
-      <c r="N311" s="98" t="s">
+      <c r="N311" s="99" t="s">
         <v>726</v>
       </c>
-      <c r="O311" s="98" t="s">
+      <c r="O311" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="P311" s="97">
+      <c r="P311" s="94">
         <v>2019</v>
       </c>
-      <c r="Q311" s="98" t="s">
+      <c r="Q311" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="R311" s="115">
+      <c r="R311" s="98">
         <v>1</v>
       </c>
-      <c r="S311" s="97" t="s">
+      <c r="S311" s="94" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="97"/>
+      <c r="A312" s="94"/>
       <c r="B312" s="80" t="s">
         <v>723</v>
       </c>
@@ -21155,24 +21155,24 @@
       <c r="D312" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="E312" s="106"/>
-      <c r="F312" s="98"/>
-      <c r="G312" s="97"/>
-      <c r="H312" s="97"/>
-      <c r="I312" s="104"/>
-      <c r="J312" s="104"/>
-      <c r="K312" s="101"/>
-      <c r="L312" s="101"/>
-      <c r="M312" s="101"/>
-      <c r="N312" s="98"/>
-      <c r="O312" s="98"/>
-      <c r="P312" s="97"/>
-      <c r="Q312" s="98"/>
-      <c r="R312" s="115"/>
-      <c r="S312" s="97"/>
+      <c r="E312" s="107"/>
+      <c r="F312" s="99"/>
+      <c r="G312" s="94"/>
+      <c r="H312" s="94"/>
+      <c r="I312" s="96"/>
+      <c r="J312" s="96"/>
+      <c r="K312" s="97"/>
+      <c r="L312" s="97"/>
+      <c r="M312" s="97"/>
+      <c r="N312" s="99"/>
+      <c r="O312" s="99"/>
+      <c r="P312" s="94"/>
+      <c r="Q312" s="99"/>
+      <c r="R312" s="98"/>
+      <c r="S312" s="94"/>
     </row>
     <row r="313" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="97"/>
+      <c r="A313" s="94"/>
       <c r="B313" s="80" t="s">
         <v>723</v>
       </c>
@@ -21228,7 +21228,7 @@
       </c>
     </row>
     <row r="314" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="97"/>
+      <c r="A314" s="94"/>
       <c r="B314" s="80" t="s">
         <v>723</v>
       </c>
@@ -21282,7 +21282,7 @@
       <c r="S314" s="80"/>
     </row>
     <row r="315" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="97"/>
+      <c r="A315" s="94"/>
       <c r="B315" s="80" t="s">
         <v>723</v>
       </c>
@@ -21430,7 +21430,7 @@
       </c>
     </row>
     <row r="318" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="103">
+      <c r="A318" s="100">
         <v>85</v>
       </c>
       <c r="B318" s="80" t="s">
@@ -21477,7 +21477,7 @@
       <c r="S318" s="80"/>
     </row>
     <row r="319" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="104"/>
+      <c r="A319" s="96"/>
       <c r="B319" s="80" t="s">
         <v>729</v>
       </c>
@@ -21528,7 +21528,7 @@
       </c>
     </row>
     <row r="320" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="109">
+      <c r="A320" s="101">
         <v>86</v>
       </c>
       <c r="B320" s="80" t="s">
@@ -21580,7 +21580,7 @@
       </c>
     </row>
     <row r="321" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="110"/>
+      <c r="A321" s="102"/>
       <c r="B321" s="75" t="s">
         <v>735</v>
       </c>
@@ -21628,7 +21628,7 @@
       </c>
     </row>
     <row r="322" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="110"/>
+      <c r="A322" s="102"/>
       <c r="B322" s="75" t="s">
         <v>735</v>
       </c>
@@ -21680,7 +21680,7 @@
       </c>
     </row>
     <row r="323" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="110"/>
+      <c r="A323" s="102"/>
       <c r="B323" s="75" t="s">
         <v>735</v>
       </c>
@@ -21732,7 +21732,7 @@
       </c>
     </row>
     <row r="324" spans="1:19" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="108"/>
+      <c r="A324" s="95"/>
       <c r="B324" s="75" t="s">
         <v>735</v>
       </c>
@@ -21782,7 +21782,7 @@
       </c>
     </row>
     <row r="325" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="108"/>
+      <c r="A325" s="95"/>
       <c r="B325" s="75" t="s">
         <v>735</v>
       </c>
@@ -21832,7 +21832,7 @@
       </c>
     </row>
     <row r="326" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="110"/>
+      <c r="A326" s="102"/>
       <c r="B326" s="75" t="s">
         <v>735</v>
       </c>
@@ -21886,7 +21886,7 @@
       </c>
     </row>
     <row r="327" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="110"/>
+      <c r="A327" s="102"/>
       <c r="B327" s="80" t="s">
         <v>735</v>
       </c>
@@ -21936,7 +21936,7 @@
       </c>
     </row>
     <row r="328" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="110"/>
+      <c r="A328" s="102"/>
       <c r="B328" s="80" t="s">
         <v>735</v>
       </c>
@@ -21988,7 +21988,7 @@
       <c r="S328" s="80"/>
     </row>
     <row r="329" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A329" s="111"/>
+      <c r="A329" s="103"/>
       <c r="B329" s="80" t="s">
         <v>735</v>
       </c>
@@ -22210,7 +22210,7 @@
       </c>
     </row>
     <row r="334" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="103">
+      <c r="A334" s="100">
         <v>89</v>
       </c>
       <c r="B334" s="80" t="s">
@@ -22270,7 +22270,7 @@
       </c>
     </row>
     <row r="335" spans="1:19" ht="44.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="108"/>
+      <c r="A335" s="95"/>
       <c r="B335" s="80" t="s">
         <v>756</v>
       </c>
@@ -22321,7 +22321,7 @@
       </c>
     </row>
     <row r="336" spans="1:19" ht="155.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="108"/>
+      <c r="A336" s="95"/>
       <c r="B336" s="80" t="s">
         <v>756</v>
       </c>
@@ -22372,7 +22372,7 @@
       </c>
     </row>
     <row r="337" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="104"/>
+      <c r="A337" s="96"/>
       <c r="B337" s="80" t="s">
         <v>756</v>
       </c>
@@ -22470,7 +22470,7 @@
       </c>
     </row>
     <row r="339" spans="1:20" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="97">
+      <c r="A339" s="94">
         <v>90</v>
       </c>
       <c r="B339" s="80" t="s">
@@ -22526,7 +22526,7 @@
       <c r="T339" s="36"/>
     </row>
     <row r="340" spans="1:20" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="97"/>
+      <c r="A340" s="94"/>
       <c r="B340" s="80" t="s">
         <v>764</v>
       </c>
@@ -22579,7 +22579,7 @@
       <c r="T340" s="36"/>
     </row>
     <row r="341" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A341" s="97">
+      <c r="A341" s="94">
         <v>91</v>
       </c>
       <c r="B341" s="80" t="s">
@@ -22635,7 +22635,7 @@
       </c>
     </row>
     <row r="342" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A342" s="97"/>
+      <c r="A342" s="94"/>
       <c r="B342" s="80" t="s">
         <v>767</v>
       </c>
@@ -22689,7 +22689,7 @@
       </c>
     </row>
     <row r="343" spans="1:20" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A343" s="97"/>
+      <c r="A343" s="94"/>
       <c r="B343" s="80" t="s">
         <v>767</v>
       </c>
@@ -22739,7 +22739,7 @@
       </c>
     </row>
     <row r="344" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A344" s="97"/>
+      <c r="A344" s="94"/>
       <c r="B344" s="80" t="s">
         <v>767</v>
       </c>
@@ -22793,7 +22793,7 @@
       </c>
     </row>
     <row r="345" spans="1:20" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A345" s="97"/>
+      <c r="A345" s="94"/>
       <c r="B345" s="80" t="s">
         <v>767</v>
       </c>
@@ -22844,7 +22844,7 @@
       </c>
     </row>
     <row r="346" spans="1:20" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="97"/>
+      <c r="A346" s="94"/>
       <c r="B346" s="80" t="s">
         <v>767</v>
       </c>
@@ -22888,7 +22888,7 @@
       </c>
     </row>
     <row r="347" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A347" s="97"/>
+      <c r="A347" s="94"/>
       <c r="B347" s="80" t="s">
         <v>767</v>
       </c>
@@ -22942,7 +22942,7 @@
       </c>
     </row>
     <row r="348" spans="1:20" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="97">
+      <c r="A348" s="94">
         <v>92</v>
       </c>
       <c r="B348" s="80" t="s">
@@ -22997,7 +22997,7 @@
       <c r="S348" s="80"/>
     </row>
     <row r="349" spans="1:20" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="97"/>
+      <c r="A349" s="94"/>
       <c r="B349" s="80" t="s">
         <v>779</v>
       </c>
@@ -23049,7 +23049,7 @@
       </c>
     </row>
     <row r="350" spans="1:20" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A350" s="97"/>
+      <c r="A350" s="94"/>
       <c r="B350" s="80" t="s">
         <v>779</v>
       </c>
@@ -23103,7 +23103,7 @@
       </c>
     </row>
     <row r="351" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="97">
+      <c r="A351" s="94">
         <v>93</v>
       </c>
       <c r="B351" s="80" t="s">
@@ -23159,7 +23159,7 @@
       </c>
     </row>
     <row r="352" spans="1:20" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="97"/>
+      <c r="A352" s="94"/>
       <c r="B352" s="80" t="s">
         <v>784</v>
       </c>
@@ -23210,7 +23210,7 @@
       </c>
     </row>
     <row r="353" spans="1:19" ht="94.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="97"/>
+      <c r="A353" s="94"/>
       <c r="B353" s="80" t="s">
         <v>784</v>
       </c>
@@ -23264,7 +23264,7 @@
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="97"/>
+      <c r="A354" s="94"/>
       <c r="B354" s="80" t="s">
         <v>784</v>
       </c>
@@ -23322,7 +23322,7 @@
       </c>
     </row>
     <row r="355" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="97"/>
+      <c r="A355" s="94"/>
       <c r="B355" s="80" t="s">
         <v>784</v>
       </c>
@@ -23374,7 +23374,7 @@
       </c>
     </row>
     <row r="356" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="97"/>
+      <c r="A356" s="94"/>
       <c r="B356" s="80" t="s">
         <v>784</v>
       </c>
@@ -23695,7 +23695,7 @@
       </c>
     </row>
     <row r="362" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="97"/>
+      <c r="A362" s="94"/>
       <c r="B362" s="80" t="s">
         <v>803</v>
       </c>
@@ -23748,7 +23748,7 @@
       <c r="S362" s="80"/>
     </row>
     <row r="363" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="97"/>
+      <c r="A363" s="94"/>
       <c r="B363" s="80" t="s">
         <v>803</v>
       </c>
@@ -23962,7 +23962,7 @@
       <c r="S366" s="80"/>
     </row>
     <row r="367" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="103">
+      <c r="A367" s="100">
         <v>97</v>
       </c>
       <c r="B367" s="80" t="s">
@@ -24011,7 +24011,7 @@
       </c>
     </row>
     <row r="368" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="108"/>
+      <c r="A368" s="95"/>
       <c r="B368" s="80" t="s">
         <v>810</v>
       </c>
@@ -24069,7 +24069,7 @@
       </c>
     </row>
     <row r="369" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="108"/>
+      <c r="A369" s="95"/>
       <c r="B369" s="80" t="s">
         <v>810</v>
       </c>
@@ -24120,7 +24120,7 @@
       </c>
     </row>
     <row r="370" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="108"/>
+      <c r="A370" s="95"/>
       <c r="B370" s="80" t="s">
         <v>810</v>
       </c>
@@ -24174,7 +24174,7 @@
       </c>
     </row>
     <row r="371" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="104"/>
+      <c r="A371" s="96"/>
       <c r="B371" s="80" t="s">
         <v>810</v>
       </c>
@@ -24227,7 +24227,7 @@
       <c r="S371" s="80"/>
     </row>
     <row r="372" spans="1:19" ht="148.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="97">
+      <c r="A372" s="94">
         <v>98</v>
       </c>
       <c r="B372" s="80" t="s">
@@ -24280,7 +24280,7 @@
       </c>
     </row>
     <row r="373" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="97"/>
+      <c r="A373" s="94"/>
       <c r="B373" s="80" t="s">
         <v>816</v>
       </c>
@@ -24331,7 +24331,7 @@
       </c>
     </row>
     <row r="374" spans="1:19" ht="34.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="97"/>
+      <c r="A374" s="94"/>
       <c r="B374" s="80" t="s">
         <v>816</v>
       </c>
@@ -24382,7 +24382,7 @@
       </c>
     </row>
     <row r="375" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="97"/>
+      <c r="A375" s="94"/>
       <c r="B375" s="80" t="s">
         <v>816</v>
       </c>
@@ -24433,7 +24433,7 @@
       </c>
     </row>
     <row r="376" spans="1:19" ht="122.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="97"/>
+      <c r="A376" s="94"/>
       <c r="B376" s="80" t="s">
         <v>816</v>
       </c>
@@ -24474,7 +24474,7 @@
       </c>
     </row>
     <row r="377" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="97"/>
+      <c r="A377" s="94"/>
       <c r="B377" s="80" t="s">
         <v>816</v>
       </c>
@@ -24524,7 +24524,7 @@
       </c>
     </row>
     <row r="378" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="97"/>
+      <c r="A378" s="94"/>
       <c r="B378" s="80" t="s">
         <v>816</v>
       </c>
@@ -24574,7 +24574,7 @@
       </c>
     </row>
     <row r="379" spans="1:19" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="97"/>
+      <c r="A379" s="94"/>
       <c r="B379" s="80" t="s">
         <v>816</v>
       </c>
@@ -24618,7 +24618,7 @@
       </c>
     </row>
     <row r="380" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="97"/>
+      <c r="A380" s="94"/>
       <c r="B380" s="80" t="s">
         <v>816</v>
       </c>
@@ -24665,7 +24665,7 @@
       <c r="S380" s="80"/>
     </row>
     <row r="381" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="97"/>
+      <c r="A381" s="94"/>
       <c r="B381" s="80" t="s">
         <v>816</v>
       </c>
@@ -24717,7 +24717,7 @@
       <c r="S381" s="80"/>
     </row>
     <row r="382" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="97"/>
+      <c r="A382" s="94"/>
       <c r="B382" s="80" t="s">
         <v>816</v>
       </c>
@@ -24767,7 +24767,7 @@
       </c>
     </row>
     <row r="383" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="97"/>
+      <c r="A383" s="94"/>
       <c r="B383" s="80" t="s">
         <v>816</v>
       </c>
@@ -24819,7 +24819,7 @@
       <c r="S383" s="80"/>
     </row>
     <row r="384" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A384" s="104">
+      <c r="A384" s="96">
         <v>99</v>
       </c>
       <c r="B384" s="80" t="s">
@@ -24872,7 +24872,7 @@
       </c>
     </row>
     <row r="385" spans="1:19" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="97"/>
+      <c r="A385" s="94"/>
       <c r="B385" s="80" t="s">
         <v>844</v>
       </c>
@@ -24923,7 +24923,7 @@
       </c>
     </row>
     <row r="386" spans="1:19" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="97"/>
+      <c r="A386" s="94"/>
       <c r="B386" s="80" t="s">
         <v>844</v>
       </c>
@@ -24977,7 +24977,7 @@
       <c r="S386" s="80"/>
     </row>
     <row r="387" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A387" s="97"/>
+      <c r="A387" s="94"/>
       <c r="B387" s="80" t="s">
         <v>844</v>
       </c>
@@ -25029,7 +25029,7 @@
       </c>
     </row>
     <row r="388" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A388" s="97"/>
+      <c r="A388" s="94"/>
       <c r="B388" s="80" t="s">
         <v>843</v>
       </c>
@@ -25081,7 +25081,7 @@
       </c>
     </row>
     <row r="389" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A389" s="97"/>
+      <c r="A389" s="94"/>
       <c r="B389" s="80" t="s">
         <v>843</v>
       </c>
@@ -25135,7 +25135,7 @@
       </c>
     </row>
     <row r="390" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A390" s="97"/>
+      <c r="A390" s="94"/>
       <c r="B390" s="80" t="s">
         <v>843</v>
       </c>
@@ -25174,7 +25174,7 @@
       </c>
     </row>
     <row r="391" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A391" s="97"/>
+      <c r="A391" s="94"/>
       <c r="B391" s="75" t="s">
         <v>843</v>
       </c>
@@ -25277,7 +25277,7 @@
       </c>
     </row>
     <row r="393" spans="1:19" ht="58.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="97">
+      <c r="A393" s="94">
         <v>100</v>
       </c>
       <c r="B393" s="75" t="s">
@@ -25330,7 +25330,7 @@
       </c>
     </row>
     <row r="394" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="97"/>
+      <c r="A394" s="94"/>
       <c r="B394" s="75" t="s">
         <v>853</v>
       </c>
@@ -25381,7 +25381,7 @@
       </c>
     </row>
     <row r="395" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="97"/>
+      <c r="A395" s="94"/>
       <c r="B395" s="80" t="s">
         <v>853</v>
       </c>
@@ -25435,7 +25435,7 @@
       </c>
     </row>
     <row r="396" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="97"/>
+      <c r="A396" s="94"/>
       <c r="B396" s="80" t="s">
         <v>853</v>
       </c>
@@ -25483,7 +25483,7 @@
       </c>
     </row>
     <row r="397" spans="1:19" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="97"/>
+      <c r="A397" s="94"/>
       <c r="B397" s="80" t="s">
         <v>853</v>
       </c>
@@ -25535,7 +25535,7 @@
       <c r="S397" s="80"/>
     </row>
     <row r="398" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="97"/>
+      <c r="A398" s="94"/>
       <c r="B398" s="80" t="s">
         <v>853</v>
       </c>
@@ -25587,7 +25587,7 @@
       <c r="S398" s="80"/>
     </row>
     <row r="399" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A399" s="112">
+      <c r="A399" s="104">
         <v>101</v>
       </c>
       <c r="B399" s="80" t="s">
@@ -25642,7 +25642,7 @@
       </c>
     </row>
     <row r="400" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="112"/>
+      <c r="A400" s="104"/>
       <c r="B400" s="80" t="s">
         <v>862</v>
       </c>
@@ -25681,7 +25681,7 @@
       <c r="S400" s="75"/>
     </row>
     <row r="401" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="112"/>
+      <c r="A401" s="104"/>
       <c r="B401" s="80" t="s">
         <v>862</v>
       </c>
@@ -25733,7 +25733,7 @@
       </c>
     </row>
     <row r="402" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="112"/>
+      <c r="A402" s="104"/>
       <c r="B402" s="80" t="s">
         <v>862</v>
       </c>
@@ -25787,7 +25787,7 @@
       </c>
     </row>
     <row r="403" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="112"/>
+      <c r="A403" s="104"/>
       <c r="B403" s="80" t="s">
         <v>862</v>
       </c>
@@ -25839,7 +25839,7 @@
       <c r="S403" s="80"/>
     </row>
     <row r="404" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A404" s="112"/>
+      <c r="A404" s="104"/>
       <c r="B404" s="80" t="s">
         <v>862</v>
       </c>
@@ -25893,7 +25893,7 @@
       </c>
     </row>
     <row r="405" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="97">
+      <c r="A405" s="94">
         <v>102</v>
       </c>
       <c r="B405" s="75" t="s">
@@ -25946,7 +25946,7 @@
       </c>
     </row>
     <row r="406" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="97"/>
+      <c r="A406" s="94"/>
       <c r="B406" s="80" t="s">
         <v>869</v>
       </c>
@@ -26000,7 +26000,7 @@
       </c>
     </row>
     <row r="407" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="97">
+      <c r="A407" s="94">
         <v>103</v>
       </c>
       <c r="B407" s="80" t="s">
@@ -26054,7 +26054,7 @@
       </c>
     </row>
     <row r="408" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="97"/>
+      <c r="A408" s="94"/>
       <c r="B408" s="80" t="s">
         <v>873</v>
       </c>
@@ -26108,7 +26108,7 @@
       </c>
     </row>
     <row r="409" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="97"/>
+      <c r="A409" s="94"/>
       <c r="B409" s="80" t="s">
         <v>873</v>
       </c>
@@ -26161,7 +26161,7 @@
       </c>
     </row>
     <row r="410" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="97"/>
+      <c r="A410" s="94"/>
       <c r="B410" s="80" t="s">
         <v>873</v>
       </c>
@@ -26215,7 +26215,7 @@
       </c>
     </row>
     <row r="411" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="97">
+      <c r="A411" s="94">
         <v>104</v>
       </c>
       <c r="B411" s="80" t="s">
@@ -26268,7 +26268,7 @@
       </c>
     </row>
     <row r="412" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="97"/>
+      <c r="A412" s="94"/>
       <c r="B412" s="80" t="s">
         <v>878</v>
       </c>
@@ -26326,7 +26326,7 @@
       </c>
     </row>
     <row r="413" spans="1:19" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="97"/>
+      <c r="A413" s="94"/>
       <c r="B413" s="80"/>
       <c r="C413" s="75"/>
       <c r="D413" s="75"/>
@@ -26347,7 +26347,7 @@
       <c r="S413" s="80"/>
     </row>
     <row r="414" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="97"/>
+      <c r="A414" s="94"/>
       <c r="B414" s="80" t="s">
         <v>878</v>
       </c>
@@ -26398,7 +26398,7 @@
       </c>
     </row>
     <row r="415" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="97"/>
+      <c r="A415" s="94"/>
       <c r="B415" s="80" t="s">
         <v>878</v>
       </c>
@@ -26451,7 +26451,7 @@
       </c>
     </row>
     <row r="416" spans="1:19" ht="61.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="97">
+      <c r="A416" s="94">
         <v>105</v>
       </c>
       <c r="B416" s="80" t="s">
@@ -26504,7 +26504,7 @@
       </c>
     </row>
     <row r="417" spans="1:19" ht="142.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="97"/>
+      <c r="A417" s="94"/>
       <c r="B417" s="80" t="s">
         <v>885</v>
       </c>
@@ -26549,7 +26549,7 @@
       </c>
     </row>
     <row r="418" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="97"/>
+      <c r="A418" s="94"/>
       <c r="B418" s="80" t="s">
         <v>885</v>
       </c>
@@ -26603,7 +26603,7 @@
       </c>
     </row>
     <row r="419" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="97"/>
+      <c r="A419" s="94"/>
       <c r="B419" s="80" t="s">
         <v>885</v>
       </c>
@@ -26657,7 +26657,7 @@
       </c>
     </row>
     <row r="420" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="97"/>
+      <c r="A420" s="94"/>
       <c r="B420" s="80" t="s">
         <v>885</v>
       </c>
@@ -26711,7 +26711,7 @@
       </c>
     </row>
     <row r="421" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="97"/>
+      <c r="A421" s="94"/>
       <c r="B421" s="80" t="s">
         <v>885</v>
       </c>
@@ -26752,7 +26752,7 @@
       </c>
     </row>
     <row r="422" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="97"/>
+      <c r="A422" s="94"/>
       <c r="B422" s="80" t="s">
         <v>885</v>
       </c>
@@ -26800,7 +26800,7 @@
       </c>
     </row>
     <row r="423" spans="1:19" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="97"/>
+      <c r="A423" s="94"/>
       <c r="B423" s="80" t="s">
         <v>885</v>
       </c>
@@ -26950,7 +26950,7 @@
       </c>
     </row>
     <row r="426" spans="1:19" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A426" s="97">
+      <c r="A426" s="94">
         <v>107</v>
       </c>
       <c r="B426" s="80" t="s">
@@ -27005,7 +27005,7 @@
       </c>
     </row>
     <row r="427" spans="1:19" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A427" s="97"/>
+      <c r="A427" s="94"/>
       <c r="B427" s="80" t="s">
         <v>902</v>
       </c>
@@ -27057,7 +27057,7 @@
       <c r="S427" s="80"/>
     </row>
     <row r="428" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="97"/>
+      <c r="A428" s="94"/>
       <c r="B428" s="80" t="s">
         <v>902</v>
       </c>
@@ -27107,7 +27107,7 @@
       </c>
     </row>
     <row r="429" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="97"/>
+      <c r="A429" s="94"/>
       <c r="B429" s="80" t="s">
         <v>901</v>
       </c>
@@ -27157,7 +27157,7 @@
       </c>
     </row>
     <row r="430" spans="1:19" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="97"/>
+      <c r="A430" s="94"/>
       <c r="B430" s="80" t="s">
         <v>901</v>
       </c>
@@ -27207,7 +27207,7 @@
       </c>
     </row>
     <row r="431" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A431" s="97"/>
+      <c r="A431" s="94"/>
       <c r="B431" s="80" t="s">
         <v>902</v>
       </c>
@@ -27259,7 +27259,7 @@
       <c r="S431" s="80"/>
     </row>
     <row r="432" spans="1:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A432" s="97"/>
+      <c r="A432" s="94"/>
       <c r="B432" s="80" t="s">
         <v>901</v>
       </c>
@@ -27311,7 +27311,7 @@
       <c r="S432" s="75"/>
     </row>
     <row r="433" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="108"/>
+      <c r="A433" s="95"/>
       <c r="B433" s="80" t="s">
         <v>913</v>
       </c>
@@ -27333,35 +27333,35 @@
       </c>
       <c r="I433" s="80"/>
       <c r="J433" s="80"/>
-      <c r="K433" s="101">
+      <c r="K433" s="97">
         <v>12746524997</v>
       </c>
-      <c r="L433" s="101">
+      <c r="L433" s="97">
         <v>1000000000</v>
       </c>
-      <c r="M433" s="101">
+      <c r="M433" s="97">
         <f>+K433+L433</f>
         <v>13746524997</v>
       </c>
-      <c r="N433" s="98" t="s">
+      <c r="N433" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="O433" s="98" t="s">
+      <c r="O433" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="P433" s="97">
+      <c r="P433" s="94">
         <v>2025</v>
       </c>
       <c r="Q433" s="75"/>
-      <c r="R433" s="115">
+      <c r="R433" s="98">
         <v>0.65</v>
       </c>
-      <c r="S433" s="97" t="s">
+      <c r="S433" s="94" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="434" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="108"/>
+      <c r="A434" s="95"/>
       <c r="B434" s="80" t="s">
         <v>913</v>
       </c>
@@ -27383,18 +27383,18 @@
       </c>
       <c r="I434" s="80"/>
       <c r="J434" s="80"/>
-      <c r="K434" s="101"/>
-      <c r="L434" s="101"/>
-      <c r="M434" s="101"/>
-      <c r="N434" s="98"/>
-      <c r="O434" s="98"/>
-      <c r="P434" s="97"/>
+      <c r="K434" s="97"/>
+      <c r="L434" s="97"/>
+      <c r="M434" s="97"/>
+      <c r="N434" s="99"/>
+      <c r="O434" s="99"/>
+      <c r="P434" s="94"/>
       <c r="Q434" s="75"/>
-      <c r="R434" s="115"/>
-      <c r="S434" s="97"/>
+      <c r="R434" s="98"/>
+      <c r="S434" s="94"/>
     </row>
     <row r="435" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="108"/>
+      <c r="A435" s="95"/>
       <c r="B435" s="80" t="s">
         <v>913</v>
       </c>
@@ -27446,7 +27446,7 @@
       </c>
     </row>
     <row r="436" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="108"/>
+      <c r="A436" s="95"/>
       <c r="B436" s="80" t="s">
         <v>917</v>
       </c>
@@ -27498,7 +27498,7 @@
       </c>
     </row>
     <row r="437" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="108"/>
+      <c r="A437" s="95"/>
       <c r="B437" s="80" t="s">
         <v>913</v>
       </c>
@@ -27548,7 +27548,7 @@
       </c>
     </row>
     <row r="438" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="104"/>
+      <c r="A438" s="96"/>
       <c r="B438" s="80" t="s">
         <v>913</v>
       </c>
@@ -27599,7 +27599,7 @@
       </c>
     </row>
     <row r="439" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="103">
+      <c r="A439" s="100">
         <v>109</v>
       </c>
       <c r="B439" s="80" t="s">
@@ -27651,7 +27651,7 @@
       </c>
     </row>
     <row r="440" spans="1:19" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="108"/>
+      <c r="A440" s="95"/>
       <c r="B440" s="80" t="s">
         <v>925</v>
       </c>
@@ -27700,7 +27700,7 @@
       </c>
     </row>
     <row r="441" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="108"/>
+      <c r="A441" s="95"/>
       <c r="B441" s="80" t="s">
         <v>925</v>
       </c>
@@ -27753,7 +27753,7 @@
       </c>
     </row>
     <row r="442" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="108"/>
+      <c r="A442" s="95"/>
       <c r="B442" s="80" t="s">
         <v>925</v>
       </c>
@@ -27805,7 +27805,7 @@
       </c>
     </row>
     <row r="443" spans="1:19" ht="64.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="108"/>
+      <c r="A443" s="95"/>
       <c r="B443" s="80" t="s">
         <v>925</v>
       </c>
@@ -27855,7 +27855,7 @@
       </c>
     </row>
     <row r="444" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="108"/>
+      <c r="A444" s="95"/>
       <c r="B444" s="80" t="s">
         <v>925</v>
       </c>
@@ -27903,7 +27903,7 @@
       </c>
     </row>
     <row r="445" spans="1:19" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="108"/>
+      <c r="A445" s="95"/>
       <c r="B445" s="80" t="s">
         <v>925</v>
       </c>
@@ -27938,7 +27938,7 @@
       <c r="S445" s="80"/>
     </row>
     <row r="446" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="104"/>
+      <c r="A446" s="96"/>
       <c r="B446" s="80" t="s">
         <v>925</v>
       </c>
@@ -27990,7 +27990,7 @@
       <c r="S446" s="53"/>
     </row>
     <row r="447" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="97"/>
+      <c r="A447" s="94"/>
       <c r="B447" s="80" t="s">
         <v>935</v>
       </c>
@@ -28044,7 +28044,7 @@
       </c>
     </row>
     <row r="448" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="97"/>
+      <c r="A448" s="94"/>
       <c r="B448" s="60" t="s">
         <v>935</v>
       </c>
@@ -28102,7 +28102,7 @@
       </c>
     </row>
     <row r="449" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="103">
+      <c r="A449" s="100">
         <v>111</v>
       </c>
       <c r="B449" s="80" t="s">
@@ -28156,7 +28156,7 @@
       </c>
     </row>
     <row r="450" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="108"/>
+      <c r="A450" s="95"/>
       <c r="B450" s="80" t="s">
         <v>942</v>
       </c>
@@ -28208,7 +28208,7 @@
       </c>
     </row>
     <row r="451" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="108"/>
+      <c r="A451" s="95"/>
       <c r="B451" s="80" t="s">
         <v>942</v>
       </c>
@@ -28264,7 +28264,7 @@
       </c>
     </row>
     <row r="452" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="104"/>
+      <c r="A452" s="96"/>
       <c r="B452" s="80" t="s">
         <v>942</v>
       </c>
@@ -28316,7 +28316,7 @@
       </c>
     </row>
     <row r="453" spans="1:19" ht="42.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="97">
+      <c r="A453" s="94">
         <v>112</v>
       </c>
       <c r="B453" s="80" t="s">
@@ -28375,7 +28375,7 @@
       </c>
     </row>
     <row r="454" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="97"/>
+      <c r="A454" s="94"/>
       <c r="B454" s="80" t="s">
         <v>949</v>
       </c>
@@ -28428,7 +28428,7 @@
       <c r="S454" s="80"/>
     </row>
     <row r="455" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="97"/>
+      <c r="A455" s="94"/>
       <c r="B455" s="80" t="s">
         <v>949</v>
       </c>
@@ -28483,7 +28483,7 @@
       <c r="S455" s="80"/>
     </row>
     <row r="456" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="97">
+      <c r="A456" s="94">
         <v>113</v>
       </c>
       <c r="B456" s="80" t="s">
@@ -28534,7 +28534,7 @@
       </c>
     </row>
     <row r="457" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="97"/>
+      <c r="A457" s="94"/>
       <c r="B457" s="80" t="s">
         <v>953</v>
       </c>
@@ -28585,7 +28585,7 @@
       </c>
     </row>
     <row r="458" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="97"/>
+      <c r="A458" s="94"/>
       <c r="B458" s="80" t="s">
         <v>953</v>
       </c>
@@ -28637,7 +28637,7 @@
       <c r="S458" s="75"/>
     </row>
     <row r="459" spans="1:19" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="97"/>
+      <c r="A459" s="94"/>
       <c r="B459" s="80" t="s">
         <v>953</v>
       </c>
@@ -28683,7 +28683,7 @@
       <c r="S459" s="75"/>
     </row>
     <row r="460" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="97"/>
+      <c r="A460" s="94"/>
       <c r="B460" s="80" t="s">
         <v>953</v>
       </c>
@@ -29050,7 +29050,7 @@
       </c>
     </row>
     <row r="467" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="108"/>
+      <c r="A467" s="95"/>
       <c r="B467" s="80" t="s">
         <v>970</v>
       </c>
@@ -29099,7 +29099,7 @@
       </c>
     </row>
     <row r="468" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="108"/>
+      <c r="A468" s="95"/>
       <c r="B468" s="80" t="s">
         <v>324</v>
       </c>
@@ -29151,7 +29151,7 @@
       <c r="S468" s="80"/>
     </row>
     <row r="469" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="108"/>
+      <c r="A469" s="95"/>
       <c r="B469" s="80" t="s">
         <v>324</v>
       </c>
@@ -29203,7 +29203,7 @@
       <c r="S469" s="80"/>
     </row>
     <row r="470" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="108"/>
+      <c r="A470" s="95"/>
       <c r="B470" s="80" t="s">
         <v>324</v>
       </c>
@@ -29255,7 +29255,7 @@
       <c r="S470" s="80"/>
     </row>
     <row r="471" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="108"/>
+      <c r="A471" s="95"/>
       <c r="B471" s="80" t="s">
         <v>324</v>
       </c>
@@ -29309,7 +29309,7 @@
       </c>
     </row>
     <row r="472" spans="1:19" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="108"/>
+      <c r="A472" s="95"/>
       <c r="B472" s="80" t="s">
         <v>324</v>
       </c>
@@ -29359,7 +29359,7 @@
       </c>
     </row>
     <row r="473" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="104"/>
+      <c r="A473" s="96"/>
       <c r="B473" s="80" t="s">
         <v>970</v>
       </c>
@@ -29407,7 +29407,7 @@
       </c>
     </row>
     <row r="474" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="97">
+      <c r="A474" s="94">
         <v>116</v>
       </c>
       <c r="B474" s="80" t="s">
@@ -29419,7 +29419,7 @@
       <c r="D474" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E474" s="100">
+      <c r="E474" s="114">
         <v>2025003050036</v>
       </c>
       <c r="F474" s="80" t="s">
@@ -29433,14 +29433,14 @@
       </c>
       <c r="I474" s="80"/>
       <c r="J474" s="80"/>
-      <c r="K474" s="102">
+      <c r="K474" s="115">
         <f>+M474</f>
         <v>14202451801</v>
       </c>
-      <c r="L474" s="102">
+      <c r="L474" s="115">
         <v>0</v>
       </c>
-      <c r="M474" s="101">
+      <c r="M474" s="97">
         <v>14202451801</v>
       </c>
       <c r="N474" s="80" t="s">
@@ -29456,12 +29456,12 @@
         <v>563</v>
       </c>
       <c r="R474" s="80"/>
-      <c r="S474" s="98" t="s">
+      <c r="S474" s="99" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="475" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="97"/>
+      <c r="A475" s="94"/>
       <c r="B475" s="80" t="s">
         <v>982</v>
       </c>
@@ -29471,7 +29471,7 @@
       <c r="D475" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="E475" s="100"/>
+      <c r="E475" s="114"/>
       <c r="F475" s="80" t="s">
         <v>174</v>
       </c>
@@ -29483,9 +29483,9 @@
       </c>
       <c r="I475" s="80"/>
       <c r="J475" s="80"/>
-      <c r="K475" s="102"/>
-      <c r="L475" s="102"/>
-      <c r="M475" s="101"/>
+      <c r="K475" s="115"/>
+      <c r="L475" s="115"/>
+      <c r="M475" s="97"/>
       <c r="N475" s="80" t="s">
         <v>35</v>
       </c>
@@ -29499,10 +29499,10 @@
         <v>563</v>
       </c>
       <c r="R475" s="80"/>
-      <c r="S475" s="98"/>
+      <c r="S475" s="99"/>
     </row>
     <row r="476" spans="1:19" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="97"/>
+      <c r="A476" s="94"/>
       <c r="B476" s="80" t="s">
         <v>982</v>
       </c>
@@ -29558,7 +29558,7 @@
       </c>
     </row>
     <row r="477" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="97"/>
+      <c r="A477" s="94"/>
       <c r="B477" s="80" t="s">
         <v>982</v>
       </c>
@@ -29977,7 +29977,7 @@
       <c r="S484" s="75"/>
     </row>
     <row r="485" spans="1:19" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="97">
+      <c r="A485" s="94">
         <v>121</v>
       </c>
       <c r="B485" s="80" t="s">
@@ -30031,7 +30031,7 @@
       <c r="S485" s="80"/>
     </row>
     <row r="486" spans="1:19" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="97"/>
+      <c r="A486" s="94"/>
       <c r="B486" s="80" t="s">
         <v>998</v>
       </c>
@@ -30081,7 +30081,7 @@
       </c>
     </row>
     <row r="487" spans="1:19" ht="163.19999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="97"/>
+      <c r="A487" s="94"/>
       <c r="B487" s="80" t="s">
         <v>998</v>
       </c>
@@ -30239,7 +30239,7 @@
       <c r="S489" s="80"/>
     </row>
     <row r="490" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="108"/>
+      <c r="A490" s="95"/>
       <c r="B490" s="80" t="s">
         <v>1008</v>
       </c>
@@ -30291,7 +30291,7 @@
       <c r="S490" s="80"/>
     </row>
     <row r="491" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="108"/>
+      <c r="A491" s="95"/>
       <c r="B491" s="80" t="s">
         <v>1008</v>
       </c>
@@ -30343,7 +30343,7 @@
       <c r="S491" s="80"/>
     </row>
     <row r="492" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="108"/>
+      <c r="A492" s="95"/>
       <c r="B492" s="80" t="s">
         <v>1008</v>
       </c>
@@ -30392,7 +30392,7 @@
       </c>
     </row>
     <row r="493" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="104"/>
+      <c r="A493" s="96"/>
       <c r="B493" s="80" t="s">
         <v>1008</v>
       </c>
@@ -30444,7 +30444,7 @@
       <c r="S493" s="80"/>
     </row>
     <row r="494" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="97">
+      <c r="A494" s="94">
         <v>124</v>
       </c>
       <c r="B494" s="80" t="s">
@@ -30500,7 +30500,7 @@
       </c>
     </row>
     <row r="495" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="97"/>
+      <c r="A495" s="94"/>
       <c r="B495" s="80" t="s">
         <v>1015</v>
       </c>
@@ -30550,7 +30550,7 @@
       </c>
     </row>
     <row r="496" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="97"/>
+      <c r="A496" s="94"/>
       <c r="B496" s="80" t="s">
         <v>1015</v>
       </c>
@@ -30602,7 +30602,7 @@
       </c>
     </row>
     <row r="497" spans="1:19" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="97"/>
+      <c r="A497" s="94"/>
       <c r="B497" s="80" t="s">
         <v>1021</v>
       </c>
@@ -30713,7 +30713,7 @@
       </c>
     </row>
     <row r="499" spans="1:19" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="98">
+      <c r="A499" s="99">
         <v>126</v>
       </c>
       <c r="B499" s="80" t="s">
@@ -30772,7 +30772,7 @@
       </c>
     </row>
     <row r="500" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="98"/>
+      <c r="A500" s="99"/>
       <c r="B500" s="80" t="s">
         <v>1022</v>
       </c>
@@ -30821,7 +30821,7 @@
       <c r="S500" s="80"/>
     </row>
     <row r="501" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="98"/>
+      <c r="A501" s="99"/>
       <c r="B501" s="80" t="s">
         <v>1022</v>
       </c>
@@ -30875,7 +30875,7 @@
       </c>
     </row>
     <row r="502" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="97">
+      <c r="A502" s="94">
         <v>127</v>
       </c>
       <c r="B502" s="80" t="s">
@@ -30935,7 +30935,7 @@
       </c>
     </row>
     <row r="503" spans="1:19" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="97"/>
+      <c r="A503" s="94"/>
       <c r="B503" s="80" t="s">
         <v>1030</v>
       </c>
@@ -30991,7 +30991,7 @@
       <c r="S503" s="80"/>
     </row>
     <row r="504" spans="1:19" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="97"/>
+      <c r="A504" s="94"/>
       <c r="B504" s="60" t="s">
         <v>1030</v>
       </c>
@@ -31121,18 +31121,107 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A407:A410"/>
-    <mergeCell ref="A411:A415"/>
-    <mergeCell ref="A416:A423"/>
-    <mergeCell ref="A426:A432"/>
-    <mergeCell ref="A433:A438"/>
-    <mergeCell ref="K433:K434"/>
-    <mergeCell ref="R433:R434"/>
-    <mergeCell ref="L433:L434"/>
-    <mergeCell ref="M433:M434"/>
-    <mergeCell ref="N433:N434"/>
-    <mergeCell ref="O433:O434"/>
-    <mergeCell ref="P433:P434"/>
+    <mergeCell ref="M91:M100"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="R91:R92"/>
+    <mergeCell ref="E474:E475"/>
+    <mergeCell ref="S91:S92"/>
+    <mergeCell ref="M474:M475"/>
+    <mergeCell ref="K474:K475"/>
+    <mergeCell ref="L474:L475"/>
+    <mergeCell ref="S474:S475"/>
+    <mergeCell ref="S433:S434"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="H311:H312"/>
+    <mergeCell ref="J309:J310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="I311:I312"/>
+    <mergeCell ref="J311:J312"/>
+    <mergeCell ref="E311:E312"/>
+    <mergeCell ref="K91:K100"/>
+    <mergeCell ref="L91:L100"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A116"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A190:A192"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A152:A163"/>
+    <mergeCell ref="A213:A217"/>
+    <mergeCell ref="A222:A227"/>
+    <mergeCell ref="A234:A239"/>
+    <mergeCell ref="A240:A246"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A254:A259"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A294:A296"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A304:A307"/>
+    <mergeCell ref="F309:F310"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A275"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A284:A292"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="A399:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="P309:P310"/>
+    <mergeCell ref="S309:S310"/>
+    <mergeCell ref="R309:R310"/>
+    <mergeCell ref="A310:A315"/>
+    <mergeCell ref="F311:F312"/>
+    <mergeCell ref="G311:G312"/>
+    <mergeCell ref="K311:K312"/>
+    <mergeCell ref="L311:L312"/>
+    <mergeCell ref="M311:M312"/>
+    <mergeCell ref="N311:N312"/>
+    <mergeCell ref="G309:G310"/>
+    <mergeCell ref="K309:K310"/>
+    <mergeCell ref="L309:L310"/>
+    <mergeCell ref="M309:M310"/>
+    <mergeCell ref="N309:N310"/>
+    <mergeCell ref="O309:O310"/>
+    <mergeCell ref="Q309:Q310"/>
+    <mergeCell ref="Q311:Q312"/>
+    <mergeCell ref="O311:O312"/>
+    <mergeCell ref="P311:P312"/>
+    <mergeCell ref="S311:S312"/>
+    <mergeCell ref="R311:R312"/>
     <mergeCell ref="A318:A319"/>
     <mergeCell ref="A320:A329"/>
     <mergeCell ref="A334:A337"/>
@@ -31157,107 +31246,18 @@
     <mergeCell ref="A372:A383"/>
     <mergeCell ref="A384:A391"/>
     <mergeCell ref="A393:A398"/>
-    <mergeCell ref="A399:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="P309:P310"/>
-    <mergeCell ref="S309:S310"/>
-    <mergeCell ref="R309:R310"/>
-    <mergeCell ref="A310:A315"/>
-    <mergeCell ref="F311:F312"/>
-    <mergeCell ref="G311:G312"/>
-    <mergeCell ref="K311:K312"/>
-    <mergeCell ref="L311:L312"/>
-    <mergeCell ref="M311:M312"/>
-    <mergeCell ref="N311:N312"/>
-    <mergeCell ref="G309:G310"/>
-    <mergeCell ref="K309:K310"/>
-    <mergeCell ref="L309:L310"/>
-    <mergeCell ref="M309:M310"/>
-    <mergeCell ref="N309:N310"/>
-    <mergeCell ref="O309:O310"/>
-    <mergeCell ref="Q309:Q310"/>
-    <mergeCell ref="Q311:Q312"/>
-    <mergeCell ref="O311:O312"/>
-    <mergeCell ref="P311:P312"/>
-    <mergeCell ref="S311:S312"/>
-    <mergeCell ref="R311:R312"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A304:A307"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A275"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A284:A292"/>
-    <mergeCell ref="E309:E310"/>
-    <mergeCell ref="A213:A217"/>
-    <mergeCell ref="A222:A227"/>
-    <mergeCell ref="A234:A239"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A254:A259"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A208:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A152:A163"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="M91:M100"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="R91:R92"/>
-    <mergeCell ref="E474:E475"/>
-    <mergeCell ref="S91:S92"/>
-    <mergeCell ref="M474:M475"/>
-    <mergeCell ref="K474:K475"/>
-    <mergeCell ref="L474:L475"/>
-    <mergeCell ref="S474:S475"/>
-    <mergeCell ref="S433:S434"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="H311:H312"/>
-    <mergeCell ref="J309:J310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="I311:I312"/>
-    <mergeCell ref="J311:J312"/>
-    <mergeCell ref="E311:E312"/>
-    <mergeCell ref="K91:K100"/>
-    <mergeCell ref="L91:L100"/>
+    <mergeCell ref="A407:A410"/>
+    <mergeCell ref="A411:A415"/>
+    <mergeCell ref="A416:A423"/>
+    <mergeCell ref="A426:A432"/>
+    <mergeCell ref="A433:A438"/>
+    <mergeCell ref="K433:K434"/>
+    <mergeCell ref="R433:R434"/>
+    <mergeCell ref="L433:L434"/>
+    <mergeCell ref="M433:M434"/>
+    <mergeCell ref="N433:N434"/>
+    <mergeCell ref="O433:O434"/>
+    <mergeCell ref="P433:P434"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -31498,23 +31498,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -31670,25 +31653,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31704,4 +31686,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9B4C750-E26A-4678-AC8A-B0F448B3B734}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB298789-C642-4CD5-856D-28E610491063}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4496,25 +4496,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4529,38 +4553,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4919,10 +4919,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="13.8" hidden="1">
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="99"/>
+      <c r="C1" s="97"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -5011,7 +5011,7 @@
       <c r="X2" s="13"/>
     </row>
     <row r="3" spans="1:24" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="86">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5075,7 +5075,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="86"/>
+      <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>22</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="41.4" hidden="1">
-      <c r="A5" s="86"/>
+      <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>22</v>
       </c>
@@ -5247,7 +5247,7 @@
       <c r="V6" s="66"/>
     </row>
     <row r="7" spans="1:24" ht="13.8" hidden="1">
-      <c r="A7" s="90">
+      <c r="A7" s="93">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5283,7 +5283,7 @@
       <c r="V7" s="66"/>
     </row>
     <row r="8" spans="1:24" ht="13.8" hidden="1">
-      <c r="A8" s="85"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="71" t="s">
         <v>41</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="V8" s="66"/>
     </row>
     <row r="9" spans="1:24" ht="41.4" hidden="1">
-      <c r="A9" s="85"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="71" t="s">
         <v>41</v>
       </c>
@@ -5395,7 +5395,7 @@
       <c r="V9" s="66"/>
     </row>
     <row r="10" spans="1:24" ht="41.4" hidden="1">
-      <c r="A10" s="86"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>41</v>
       </c>
@@ -5454,7 +5454,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" ht="27.6" hidden="1">
-      <c r="A11" s="84">
+      <c r="A11" s="87">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5518,7 +5518,7 @@
       </c>
     </row>
     <row r="12" spans="1:24" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="84"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="71" t="s">
         <v>59</v>
       </c>
@@ -5575,7 +5575,7 @@
       <c r="V12" s="76"/>
     </row>
     <row r="13" spans="1:24" ht="13.8" hidden="1">
-      <c r="A13" s="84"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
@@ -5632,7 +5632,7 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="13.8" hidden="1">
-      <c r="A14" s="84"/>
+      <c r="A14" s="87"/>
       <c r="B14" s="71" t="s">
         <v>59</v>
       </c>
@@ -5689,7 +5689,7 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="13.8" hidden="1">
-      <c r="A15" s="84"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="71" t="s">
         <v>59</v>
       </c>
@@ -5746,7 +5746,7 @@
       <c r="V15" s="66"/>
     </row>
     <row r="16" spans="1:24" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="84"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="71" t="s">
         <v>59</v>
       </c>
@@ -5967,7 +5967,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="84">
+      <c r="A20" s="87">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6030,7 +6030,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="84"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="71" t="s">
         <v>92</v>
       </c>
@@ -6089,7 +6089,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="27.6" hidden="1">
-      <c r="A22" s="84"/>
+      <c r="A22" s="87"/>
       <c r="B22" s="71" t="s">
         <v>92</v>
       </c>
@@ -6149,7 +6149,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="13.8" hidden="1">
-      <c r="A23" s="84"/>
+      <c r="A23" s="87"/>
       <c r="B23" s="71" t="s">
         <v>92</v>
       </c>
@@ -6207,7 +6207,7 @@
       <c r="V23" s="71"/>
     </row>
     <row r="24" spans="1:22" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="84">
+      <c r="A24" s="87">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6269,7 +6269,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" ht="13.8" hidden="1">
-      <c r="A25" s="84"/>
+      <c r="A25" s="87"/>
       <c r="B25" s="71" t="s">
         <v>109</v>
       </c>
@@ -6326,7 +6326,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="84"/>
+      <c r="A26" s="87"/>
       <c r="B26" s="71" t="s">
         <v>109</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="84"/>
+      <c r="A27" s="87"/>
       <c r="B27" s="71" t="s">
         <v>109</v>
       </c>
@@ -6442,7 +6442,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="13.8" hidden="1">
-      <c r="A28" s="84"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="71" t="s">
         <v>109</v>
       </c>
@@ -6497,7 +6497,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="84"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="71" t="s">
         <v>109</v>
       </c>
@@ -6554,7 +6554,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="84"/>
+      <c r="A30" s="87"/>
       <c r="B30" s="71" t="s">
         <v>109</v>
       </c>
@@ -6607,7 +6607,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="84"/>
+      <c r="A31" s="87"/>
       <c r="B31" s="71" t="s">
         <v>109</v>
       </c>
@@ -6666,7 +6666,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="84"/>
+      <c r="A32" s="87"/>
       <c r="B32" s="71" t="s">
         <v>109</v>
       </c>
@@ -6727,7 +6727,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="84"/>
+      <c r="A33" s="87"/>
       <c r="B33" s="71" t="s">
         <v>109</v>
       </c>
@@ -6784,7 +6784,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="84"/>
+      <c r="A34" s="87"/>
       <c r="B34" s="71" t="s">
         <v>109</v>
       </c>
@@ -6845,7 +6845,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="13.8" hidden="1">
-      <c r="A35" s="85"/>
+      <c r="A35" s="98"/>
       <c r="B35" s="71" t="s">
         <v>147</v>
       </c>
@@ -6881,7 +6881,7 @@
       <c r="V35" s="71"/>
     </row>
     <row r="36" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="86"/>
+      <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>147</v>
       </c>
@@ -6995,7 +6995,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="84">
+      <c r="A38" s="87">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7057,7 +7057,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="84"/>
+      <c r="A39" s="87"/>
       <c r="B39" s="71" t="s">
         <v>150</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="84"/>
+      <c r="A40" s="87"/>
       <c r="B40" s="71" t="s">
         <v>150</v>
       </c>
@@ -7176,7 +7176,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="84">
+      <c r="A41" s="87">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7237,7 +7237,7 @@
       <c r="V41" s="71"/>
     </row>
     <row r="42" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="84"/>
+      <c r="A42" s="87"/>
       <c r="B42" s="71" t="s">
         <v>160</v>
       </c>
@@ -7287,7 +7287,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="84"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="71" t="s">
         <v>160</v>
       </c>
@@ -7339,7 +7339,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="84"/>
+      <c r="A44" s="87"/>
       <c r="B44" s="71" t="s">
         <v>160</v>
       </c>
@@ -7388,7 +7388,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="27.6" hidden="1">
-      <c r="A45" s="84"/>
+      <c r="A45" s="87"/>
       <c r="B45" s="71" t="s">
         <v>160</v>
       </c>
@@ -7445,7 +7445,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="84">
+      <c r="A46" s="87">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7502,7 +7502,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="13.8" hidden="1">
-      <c r="A47" s="90"/>
+      <c r="A47" s="93"/>
       <c r="B47" s="71" t="s">
         <v>175</v>
       </c>
@@ -7557,7 +7557,7 @@
       <c r="V47" s="71"/>
     </row>
     <row r="48" spans="1:22" ht="13.8" hidden="1">
-      <c r="A48" s="84"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="71" t="s">
         <v>182</v>
       </c>
@@ -7593,7 +7593,7 @@
       <c r="V48" s="71"/>
     </row>
     <row r="49" spans="1:22" ht="13.8" hidden="1">
-      <c r="A49" s="84"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="71" t="s">
         <v>182</v>
       </c>
@@ -7633,7 +7633,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" ht="13.8" hidden="1">
-      <c r="A50" s="84"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="71" t="s">
         <v>182</v>
       </c>
@@ -7688,7 +7688,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" ht="55.2" hidden="1">
-      <c r="A51" s="84"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="71" t="s">
         <v>182</v>
       </c>
@@ -7743,7 +7743,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="41.4" hidden="1">
-      <c r="A52" s="84"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="71" t="s">
         <v>182</v>
       </c>
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="84"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="71" t="s">
         <v>182</v>
       </c>
@@ -7853,7 +7853,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="84"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="71" t="s">
         <v>197</v>
       </c>
@@ -7907,7 +7907,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="84"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="71" t="s">
         <v>197</v>
       </c>
@@ -7962,7 +7962,7 @@
       <c r="V55" s="66"/>
     </row>
     <row r="56" spans="1:22" ht="41.4" hidden="1">
-      <c r="A56" s="84"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="71" t="s">
         <v>197</v>
       </c>
@@ -8021,7 +8021,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="84"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="71" t="s">
         <v>197</v>
       </c>
@@ -8078,7 +8078,7 @@
       <c r="V57" s="71"/>
     </row>
     <row r="58" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="84"/>
+      <c r="A58" s="87"/>
       <c r="B58" s="71" t="s">
         <v>197</v>
       </c>
@@ -8138,7 +8138,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A59" s="86"/>
+      <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>209</v>
       </c>
@@ -8195,7 +8195,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A60" s="86"/>
+      <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>209</v>
       </c>
@@ -8251,7 +8251,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" ht="41.4" hidden="1">
-      <c r="A61" s="84"/>
+      <c r="A61" s="87"/>
       <c r="B61" s="61" t="s">
         <v>209</v>
       </c>
@@ -8305,7 +8305,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="90">
+      <c r="A62" s="93">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8363,7 +8363,7 @@
       </c>
     </row>
     <row r="63" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="85"/>
+      <c r="A63" s="98"/>
       <c r="B63" s="71" t="s">
         <v>215</v>
       </c>
@@ -8420,7 +8420,7 @@
       </c>
     </row>
     <row r="64" spans="1:22" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="86"/>
+      <c r="A64" s="94"/>
       <c r="B64" s="71" t="s">
         <v>215</v>
       </c>
@@ -8585,7 +8585,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="90">
+      <c r="A67" s="93">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8641,7 +8641,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" ht="13.8" hidden="1">
-      <c r="A68" s="86"/>
+      <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>230</v>
       </c>
@@ -8694,7 +8694,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="90">
+      <c r="A69" s="93">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8750,7 +8750,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" ht="41.4" hidden="1">
-      <c r="A70" s="85"/>
+      <c r="A70" s="98"/>
       <c r="B70" s="71" t="s">
         <v>236</v>
       </c>
@@ -8805,7 +8805,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" ht="67.95" hidden="1" customHeight="1">
-      <c r="A71" s="85"/>
+      <c r="A71" s="98"/>
       <c r="B71" s="71" t="s">
         <v>242</v>
       </c>
@@ -8860,7 +8860,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="85"/>
+      <c r="A72" s="98"/>
       <c r="B72" s="71" t="s">
         <v>245</v>
       </c>
@@ -8916,7 +8916,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="85"/>
+      <c r="A73" s="98"/>
       <c r="B73" s="71" t="s">
         <v>245</v>
       </c>
@@ -8969,7 +8969,7 @@
       </c>
     </row>
     <row r="74" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="85"/>
+      <c r="A74" s="98"/>
       <c r="B74" s="71" t="s">
         <v>245</v>
       </c>
@@ -9024,7 +9024,7 @@
       </c>
     </row>
     <row r="75" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="85"/>
+      <c r="A75" s="98"/>
       <c r="B75" s="71" t="s">
         <v>245</v>
       </c>
@@ -9085,7 +9085,7 @@
       </c>
     </row>
     <row r="76" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A76" s="85"/>
+      <c r="A76" s="98"/>
       <c r="B76" s="71" t="s">
         <v>245</v>
       </c>
@@ -9138,7 +9138,7 @@
       <c r="V76" s="71"/>
     </row>
     <row r="77" spans="1:22" ht="13.8" hidden="1">
-      <c r="A77" s="86"/>
+      <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>245</v>
       </c>
@@ -9195,7 +9195,7 @@
       </c>
     </row>
     <row r="78" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="85"/>
+      <c r="A78" s="98"/>
       <c r="B78" s="71" t="s">
         <v>256</v>
       </c>
@@ -9256,7 +9256,7 @@
       </c>
     </row>
     <row r="79" spans="1:22" ht="13.8" hidden="1">
-      <c r="A79" s="85"/>
+      <c r="A79" s="98"/>
       <c r="B79" s="71" t="s">
         <v>256</v>
       </c>
@@ -9311,7 +9311,7 @@
       <c r="V79" s="66"/>
     </row>
     <row r="80" spans="1:22" ht="13.8" hidden="1">
-      <c r="A80" s="85"/>
+      <c r="A80" s="98"/>
       <c r="B80" s="71" t="s">
         <v>256</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="V80" s="66"/>
     </row>
     <row r="81" spans="1:23" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="85"/>
+      <c r="A81" s="98"/>
       <c r="B81" s="71" t="s">
         <v>256</v>
       </c>
@@ -9422,7 +9422,7 @@
       </c>
     </row>
     <row r="82" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="85"/>
+      <c r="A82" s="98"/>
       <c r="B82" s="71" t="s">
         <v>265</v>
       </c>
@@ -9480,7 +9480,7 @@
       <c r="W82" s="33"/>
     </row>
     <row r="83" spans="1:23" ht="38.4" hidden="1" customHeight="1">
-      <c r="A83" s="85"/>
+      <c r="A83" s="98"/>
       <c r="B83" s="71" t="s">
         <v>265</v>
       </c>
@@ -9535,7 +9535,7 @@
       <c r="W83" s="33"/>
     </row>
     <row r="84" spans="1:23" ht="27.6" hidden="1">
-      <c r="A84" s="85"/>
+      <c r="A84" s="98"/>
       <c r="B84" s="71" t="s">
         <v>265</v>
       </c>
@@ -9590,7 +9590,7 @@
       </c>
     </row>
     <row r="85" spans="1:23" ht="55.2" hidden="1">
-      <c r="A85" s="85"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="71" t="s">
         <v>265</v>
       </c>
@@ -9644,7 +9644,7 @@
       <c r="W85" s="33"/>
     </row>
     <row r="86" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="85"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="71" t="s">
         <v>265</v>
       </c>
@@ -9702,7 +9702,7 @@
       <c r="W86" s="33"/>
     </row>
     <row r="87" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="85"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="71" t="s">
         <v>265</v>
       </c>
@@ -9760,7 +9760,7 @@
       <c r="W87" s="33"/>
     </row>
     <row r="88" spans="1:23" ht="13.8" hidden="1">
-      <c r="A88" s="85"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="71" t="s">
         <v>265</v>
       </c>
@@ -9818,7 +9818,7 @@
       <c r="W88" s="33"/>
     </row>
     <row r="89" spans="1:23" ht="13.8" hidden="1">
-      <c r="A89" s="85"/>
+      <c r="A89" s="98"/>
       <c r="B89" s="71" t="s">
         <v>265</v>
       </c>
@@ -9874,7 +9874,7 @@
       <c r="W89" s="33"/>
     </row>
     <row r="90" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="85"/>
+      <c r="A90" s="98"/>
       <c r="B90" s="66" t="s">
         <v>265</v>
       </c>
@@ -9924,7 +9924,7 @@
       <c r="W90" s="33"/>
     </row>
     <row r="91" spans="1:23" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="85"/>
+      <c r="A91" s="98"/>
       <c r="B91" s="71" t="s">
         <v>285</v>
       </c>
@@ -9948,36 +9948,36 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="100"/>
-      <c r="L91" s="100">
+      <c r="K91" s="84"/>
+      <c r="L91" s="84">
         <v>0</v>
       </c>
-      <c r="M91" s="100"/>
-      <c r="N91" s="84" t="s">
+      <c r="M91" s="84"/>
+      <c r="N91" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="O91" s="84" t="s">
+      <c r="O91" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="P91" s="84">
+      <c r="P91" s="87">
         <v>2026</v>
       </c>
-      <c r="Q91" s="89" t="s">
+      <c r="Q91" s="88" t="s">
         <v>131</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
       <c r="T91" s="71"/>
-      <c r="U91" s="103">
+      <c r="U91" s="89">
         <v>0</v>
       </c>
-      <c r="V91" s="89" t="s">
+      <c r="V91" s="88" t="s">
         <v>288</v>
       </c>
       <c r="W91" s="33"/>
     </row>
     <row r="92" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A92" s="85"/>
+      <c r="A92" s="98"/>
       <c r="B92" s="71" t="s">
         <v>285</v>
       </c>
@@ -10001,21 +10001,21 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="101"/>
-      <c r="L92" s="101"/>
-      <c r="M92" s="101"/>
-      <c r="N92" s="84"/>
-      <c r="O92" s="84"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="89"/>
+      <c r="K92" s="85"/>
+      <c r="L92" s="85"/>
+      <c r="M92" s="85"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="88"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
       <c r="T92" s="71"/>
-      <c r="U92" s="103"/>
-      <c r="V92" s="89"/>
+      <c r="U92" s="89"/>
+      <c r="V92" s="88"/>
     </row>
     <row r="93" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="85"/>
+      <c r="A93" s="98"/>
       <c r="B93" s="71" t="s">
         <v>285</v>
       </c>
@@ -10039,9 +10039,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="101"/>
-      <c r="L93" s="101"/>
-      <c r="M93" s="101"/>
+      <c r="K93" s="85"/>
+      <c r="L93" s="85"/>
+      <c r="M93" s="85"/>
       <c r="N93" s="66" t="s">
         <v>29</v>
       </c>
@@ -10065,7 +10065,7 @@
       </c>
     </row>
     <row r="94" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="85"/>
+      <c r="A94" s="98"/>
       <c r="B94" s="71" t="s">
         <v>285</v>
       </c>
@@ -10087,9 +10087,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="101"/>
-      <c r="L94" s="101"/>
-      <c r="M94" s="101"/>
+      <c r="K94" s="85"/>
+      <c r="L94" s="85"/>
+      <c r="M94" s="85"/>
       <c r="N94" s="66" t="s">
         <v>29</v>
       </c>
@@ -10113,7 +10113,7 @@
       </c>
     </row>
     <row r="95" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A95" s="85"/>
+      <c r="A95" s="98"/>
       <c r="B95" s="71" t="s">
         <v>285</v>
       </c>
@@ -10137,9 +10137,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="101"/>
-      <c r="L95" s="101"/>
-      <c r="M95" s="101"/>
+      <c r="K95" s="85"/>
+      <c r="L95" s="85"/>
+      <c r="M95" s="85"/>
       <c r="N95" s="66" t="s">
         <v>149</v>
       </c>
@@ -10163,7 +10163,7 @@
       </c>
     </row>
     <row r="96" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A96" s="85"/>
+      <c r="A96" s="98"/>
       <c r="B96" s="71" t="s">
         <v>293</v>
       </c>
@@ -10183,9 +10183,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="101"/>
-      <c r="L96" s="101"/>
-      <c r="M96" s="101"/>
+      <c r="K96" s="85"/>
+      <c r="L96" s="85"/>
+      <c r="M96" s="85"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10197,7 +10197,7 @@
       <c r="V96" s="66"/>
     </row>
     <row r="97" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A97" s="85"/>
+      <c r="A97" s="98"/>
       <c r="B97" s="71" t="s">
         <v>293</v>
       </c>
@@ -10225,9 +10225,9 @@
       <c r="J97" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="K97" s="101"/>
-      <c r="L97" s="101"/>
-      <c r="M97" s="101"/>
+      <c r="K97" s="85"/>
+      <c r="L97" s="85"/>
+      <c r="M97" s="85"/>
       <c r="N97" s="66" t="s">
         <v>29</v>
       </c>
@@ -10249,7 +10249,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="85"/>
+      <c r="A98" s="98"/>
       <c r="B98" s="71" t="s">
         <v>293</v>
       </c>
@@ -10277,9 +10277,9 @@
       <c r="J98" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="K98" s="101"/>
-      <c r="L98" s="101"/>
-      <c r="M98" s="101"/>
+      <c r="K98" s="85"/>
+      <c r="L98" s="85"/>
+      <c r="M98" s="85"/>
       <c r="N98" s="66" t="s">
         <v>101</v>
       </c>
@@ -10303,7 +10303,7 @@
       </c>
     </row>
     <row r="99" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="85"/>
+      <c r="A99" s="98"/>
       <c r="B99" s="71" t="s">
         <v>302</v>
       </c>
@@ -10327,9 +10327,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="101"/>
-      <c r="L99" s="101"/>
-      <c r="M99" s="101"/>
+      <c r="K99" s="85"/>
+      <c r="L99" s="85"/>
+      <c r="M99" s="85"/>
       <c r="N99" s="66" t="s">
         <v>149</v>
       </c>
@@ -10353,7 +10353,7 @@
       </c>
     </row>
     <row r="100" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A100" s="85"/>
+      <c r="A100" s="98"/>
       <c r="B100" s="71" t="s">
         <v>302</v>
       </c>
@@ -10377,9 +10377,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="101"/>
-      <c r="L100" s="101"/>
-      <c r="M100" s="101"/>
+      <c r="K100" s="85"/>
+      <c r="L100" s="85"/>
+      <c r="M100" s="85"/>
       <c r="N100" s="66" t="s">
         <v>75</v>
       </c>
@@ -10403,7 +10403,7 @@
       </c>
     </row>
     <row r="101" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="85"/>
+      <c r="A101" s="98"/>
       <c r="B101" s="71" t="s">
         <v>302</v>
       </c>
@@ -10427,9 +10427,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="102"/>
-      <c r="L101" s="102"/>
-      <c r="M101" s="102"/>
+      <c r="K101" s="86"/>
+      <c r="L101" s="86"/>
+      <c r="M101" s="86"/>
       <c r="N101" s="66" t="s">
         <v>38</v>
       </c>
@@ -10453,7 +10453,7 @@
       </c>
     </row>
     <row r="102" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="85"/>
+      <c r="A102" s="98"/>
       <c r="B102" s="71" t="s">
         <v>302</v>
       </c>
@@ -10510,7 +10510,7 @@
       </c>
     </row>
     <row r="103" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="85"/>
+      <c r="A103" s="98"/>
       <c r="B103" s="71" t="s">
         <v>302</v>
       </c>
@@ -10562,7 +10562,7 @@
       </c>
     </row>
     <row r="104" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A104" s="85"/>
+      <c r="A104" s="98"/>
       <c r="B104" s="71" t="s">
         <v>302</v>
       </c>
@@ -10615,7 +10615,7 @@
       </c>
     </row>
     <row r="105" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A105" s="85"/>
+      <c r="A105" s="98"/>
       <c r="B105" s="71" t="s">
         <v>302</v>
       </c>
@@ -10670,7 +10670,7 @@
       <c r="V105" s="66"/>
     </row>
     <row r="106" spans="1:22" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="85"/>
+      <c r="A106" s="98"/>
       <c r="B106" s="71" t="s">
         <v>302</v>
       </c>
@@ -10725,7 +10725,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" ht="96.6" hidden="1">
-      <c r="A107" s="85"/>
+      <c r="A107" s="98"/>
       <c r="B107" s="71" t="s">
         <v>314</v>
       </c>
@@ -10777,7 +10777,7 @@
       </c>
     </row>
     <row r="108" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A108" s="85"/>
+      <c r="A108" s="98"/>
       <c r="B108" s="71" t="s">
         <v>320</v>
       </c>
@@ -10823,7 +10823,7 @@
       </c>
     </row>
     <row r="109" spans="1:22" ht="13.8" hidden="1">
-      <c r="A109" s="85"/>
+      <c r="A109" s="98"/>
       <c r="B109" s="71" t="s">
         <v>320</v>
       </c>
@@ -10876,7 +10876,7 @@
       <c r="V109" s="66"/>
     </row>
     <row r="110" spans="1:22" ht="13.8" hidden="1">
-      <c r="A110" s="85"/>
+      <c r="A110" s="98"/>
       <c r="B110" s="71" t="s">
         <v>320</v>
       </c>
@@ -10931,7 +10931,7 @@
       <c r="V110" s="71"/>
     </row>
     <row r="111" spans="1:22" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="85"/>
+      <c r="A111" s="98"/>
       <c r="B111" s="71" t="s">
         <v>325</v>
       </c>
@@ -10990,7 +10990,7 @@
       <c r="V111" s="71"/>
     </row>
     <row r="112" spans="1:22" ht="13.8" hidden="1">
-      <c r="A112" s="85"/>
+      <c r="A112" s="98"/>
       <c r="B112" s="71" t="s">
         <v>327</v>
       </c>
@@ -11043,7 +11043,7 @@
       </c>
     </row>
     <row r="113" spans="1:22" ht="13.8" hidden="1">
-      <c r="A113" s="85"/>
+      <c r="A113" s="98"/>
       <c r="B113" s="71" t="s">
         <v>327</v>
       </c>
@@ -11096,7 +11096,7 @@
       </c>
     </row>
     <row r="114" spans="1:22" ht="41.4" hidden="1">
-      <c r="A114" s="85"/>
+      <c r="A114" s="98"/>
       <c r="B114" s="71" t="s">
         <v>327</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
     </row>
     <row r="115" spans="1:22" ht="22.95" hidden="1" customHeight="1">
-      <c r="A115" s="85"/>
+      <c r="A115" s="98"/>
       <c r="B115" s="71" t="s">
         <v>327</v>
       </c>
@@ -11195,7 +11195,7 @@
       </c>
     </row>
     <row r="116" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A116" s="85"/>
+      <c r="A116" s="98"/>
       <c r="B116" s="71" t="s">
         <v>337</v>
       </c>
@@ -11256,7 +11256,7 @@
       </c>
     </row>
     <row r="117" spans="1:22" ht="55.2" hidden="1">
-      <c r="A117" s="86"/>
+      <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>342</v>
       </c>
@@ -11370,7 +11370,7 @@
       <c r="V118" s="71"/>
     </row>
     <row r="119" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="84">
+      <c r="A119" s="87">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11425,7 +11425,7 @@
       <c r="V119" s="71"/>
     </row>
     <row r="120" spans="1:22" ht="13.8" hidden="1">
-      <c r="A120" s="84"/>
+      <c r="A120" s="87"/>
       <c r="B120" s="71" t="s">
         <v>347</v>
       </c>
@@ -11480,7 +11480,7 @@
       <c r="V120" s="66"/>
     </row>
     <row r="121" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="98">
+      <c r="A121" s="103">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11536,7 +11536,7 @@
       </c>
     </row>
     <row r="122" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A122" s="89"/>
+      <c r="A122" s="88"/>
       <c r="B122" s="71" t="s">
         <v>350</v>
       </c>
@@ -11590,7 +11590,7 @@
       </c>
     </row>
     <row r="123" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A123" s="89"/>
+      <c r="A123" s="88"/>
       <c r="B123" s="71" t="s">
         <v>350</v>
       </c>
@@ -11645,7 +11645,7 @@
       </c>
     </row>
     <row r="124" spans="1:22" ht="13.8" hidden="1">
-      <c r="A124" s="89"/>
+      <c r="A124" s="88"/>
       <c r="B124" s="71" t="s">
         <v>350</v>
       </c>
@@ -12141,7 +12141,7 @@
       <c r="V132" s="66"/>
     </row>
     <row r="133" spans="1:22" ht="13.8" hidden="1">
-      <c r="A133" s="84">
+      <c r="A133" s="87">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12200,7 +12200,7 @@
       </c>
     </row>
     <row r="134" spans="1:22" ht="13.8" hidden="1">
-      <c r="A134" s="84"/>
+      <c r="A134" s="87"/>
       <c r="B134" s="71" t="s">
         <v>374</v>
       </c>
@@ -12255,7 +12255,7 @@
       <c r="V134" s="66"/>
     </row>
     <row r="135" spans="1:22" ht="41.4" hidden="1">
-      <c r="A135" s="84"/>
+      <c r="A135" s="87"/>
       <c r="B135" s="71" t="s">
         <v>374</v>
       </c>
@@ -12316,7 +12316,7 @@
       </c>
     </row>
     <row r="136" spans="1:22" ht="13.8" hidden="1">
-      <c r="A136" s="84"/>
+      <c r="A136" s="87"/>
       <c r="B136" s="71" t="s">
         <v>374</v>
       </c>
@@ -12431,7 +12431,7 @@
       <c r="V137" s="71"/>
     </row>
     <row r="138" spans="1:22" ht="13.8" hidden="1">
-      <c r="A138" s="84">
+      <c r="A138" s="87">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12488,7 +12488,7 @@
       <c r="V138" s="71"/>
     </row>
     <row r="139" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A139" s="84"/>
+      <c r="A139" s="87"/>
       <c r="B139" s="71" t="s">
         <v>383</v>
       </c>
@@ -12543,7 +12543,7 @@
       <c r="V139" s="71"/>
     </row>
     <row r="140" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A140" s="84"/>
+      <c r="A140" s="87"/>
       <c r="B140" s="71" t="s">
         <v>383</v>
       </c>
@@ -12598,7 +12598,7 @@
       <c r="V140" s="71"/>
     </row>
     <row r="141" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="84"/>
+      <c r="A141" s="87"/>
       <c r="B141" s="71" t="s">
         <v>383</v>
       </c>
@@ -12652,7 +12652,7 @@
       <c r="V141" s="71"/>
     </row>
     <row r="142" spans="1:22" ht="13.8" hidden="1">
-      <c r="A142" s="84"/>
+      <c r="A142" s="87"/>
       <c r="B142" s="71" t="s">
         <v>383</v>
       </c>
@@ -12707,7 +12707,7 @@
       <c r="V142" s="71"/>
     </row>
     <row r="143" spans="1:22" ht="13.8" hidden="1">
-      <c r="A143" s="84"/>
+      <c r="A143" s="87"/>
       <c r="B143" s="71" t="s">
         <v>383</v>
       </c>
@@ -12762,7 +12762,7 @@
       <c r="V143" s="66"/>
     </row>
     <row r="144" spans="1:22" ht="13.8" hidden="1">
-      <c r="A144" s="84"/>
+      <c r="A144" s="87"/>
       <c r="B144" s="71" t="s">
         <v>383</v>
       </c>
@@ -12817,7 +12817,7 @@
       <c r="V144" s="71"/>
     </row>
     <row r="145" spans="1:22" ht="13.8" hidden="1">
-      <c r="A145" s="84">
+      <c r="A145" s="87">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12876,7 +12876,7 @@
       </c>
     </row>
     <row r="146" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="84"/>
+      <c r="A146" s="87"/>
       <c r="B146" s="71" t="s">
         <v>399</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="147" spans="1:22" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="84"/>
+      <c r="A147" s="87"/>
       <c r="B147" s="71" t="s">
         <v>399</v>
       </c>
@@ -13039,7 +13039,7 @@
       </c>
     </row>
     <row r="149" spans="1:22" ht="35.4" hidden="1" customHeight="1">
-      <c r="A149" s="85"/>
+      <c r="A149" s="98"/>
       <c r="B149" s="71" t="s">
         <v>404</v>
       </c>
@@ -13093,7 +13093,7 @@
       </c>
     </row>
     <row r="150" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A150" s="86"/>
+      <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>404</v>
       </c>
@@ -13263,7 +13263,7 @@
       </c>
     </row>
     <row r="153" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A153" s="90">
+      <c r="A153" s="93">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13322,7 +13322,7 @@
       </c>
     </row>
     <row r="154" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A154" s="85"/>
+      <c r="A154" s="98"/>
       <c r="B154" s="71" t="s">
         <v>415</v>
       </c>
@@ -13374,7 +13374,7 @@
       </c>
     </row>
     <row r="155" spans="1:22" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="85"/>
+      <c r="A155" s="98"/>
       <c r="B155" s="71" t="s">
         <v>415</v>
       </c>
@@ -13424,7 +13424,7 @@
       </c>
     </row>
     <row r="156" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="85"/>
+      <c r="A156" s="98"/>
       <c r="B156" s="71" t="s">
         <v>415</v>
       </c>
@@ -13476,7 +13476,7 @@
       </c>
     </row>
     <row r="157" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A157" s="85"/>
+      <c r="A157" s="98"/>
       <c r="B157" s="71" t="s">
         <v>415</v>
       </c>
@@ -13533,7 +13533,7 @@
       </c>
     </row>
     <row r="158" spans="1:22" ht="13.8" hidden="1">
-      <c r="A158" s="85"/>
+      <c r="A158" s="98"/>
       <c r="B158" s="71" t="s">
         <v>415</v>
       </c>
@@ -13590,7 +13590,7 @@
       </c>
     </row>
     <row r="159" spans="1:22" ht="13.8" hidden="1">
-      <c r="A159" s="85"/>
+      <c r="A159" s="98"/>
       <c r="B159" s="71" t="s">
         <v>415</v>
       </c>
@@ -13647,7 +13647,7 @@
       </c>
     </row>
     <row r="160" spans="1:22" ht="55.2" hidden="1">
-      <c r="A160" s="85"/>
+      <c r="A160" s="98"/>
       <c r="B160" s="71" t="s">
         <v>429</v>
       </c>
@@ -13700,7 +13700,7 @@
       <c r="V160" s="71"/>
     </row>
     <row r="161" spans="1:22" ht="27.6" hidden="1">
-      <c r="A161" s="85"/>
+      <c r="A161" s="98"/>
       <c r="B161" s="71" t="s">
         <v>429</v>
       </c>
@@ -13756,7 +13756,7 @@
       <c r="V161" s="71"/>
     </row>
     <row r="162" spans="1:22" ht="13.8" hidden="1">
-      <c r="A162" s="85"/>
+      <c r="A162" s="98"/>
       <c r="B162" s="71" t="s">
         <v>429</v>
       </c>
@@ -13809,7 +13809,7 @@
       <c r="V162" s="71"/>
     </row>
     <row r="163" spans="1:22" ht="13.8" hidden="1">
-      <c r="A163" s="85"/>
+      <c r="A163" s="98"/>
       <c r="B163" s="71" t="s">
         <v>429</v>
       </c>
@@ -13866,7 +13866,7 @@
       </c>
     </row>
     <row r="164" spans="1:22" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="86"/>
+      <c r="A164" s="94"/>
       <c r="B164" s="71" t="s">
         <v>437</v>
       </c>
@@ -13920,7 +13920,7 @@
       </c>
     </row>
     <row r="165" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A165" s="85"/>
+      <c r="A165" s="98"/>
       <c r="B165" s="71" t="s">
         <v>437</v>
       </c>
@@ -13974,7 +13974,7 @@
       </c>
     </row>
     <row r="166" spans="1:22" ht="13.8" hidden="1">
-      <c r="A166" s="86"/>
+      <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>437</v>
       </c>
@@ -14152,7 +14152,7 @@
       </c>
     </row>
     <row r="169" spans="1:22" ht="41.4" hidden="1">
-      <c r="A169" s="91">
+      <c r="A169" s="99">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14213,7 +14213,7 @@
       </c>
     </row>
     <row r="170" spans="1:22" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="92"/>
+      <c r="A170" s="100"/>
       <c r="B170" s="71" t="s">
         <v>451</v>
       </c>
@@ -14265,7 +14265,7 @@
       </c>
     </row>
     <row r="171" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A171" s="92"/>
+      <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>451</v>
       </c>
@@ -14324,7 +14324,7 @@
       </c>
     </row>
     <row r="172" spans="1:22" ht="13.8" hidden="1">
-      <c r="A172" s="92"/>
+      <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>451</v>
       </c>
@@ -14381,7 +14381,7 @@
       </c>
     </row>
     <row r="173" spans="1:22" ht="13.8" hidden="1">
-      <c r="A173" s="93"/>
+      <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>458</v>
       </c>
@@ -14438,7 +14438,7 @@
       </c>
     </row>
     <row r="174" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A174" s="84">
+      <c r="A174" s="87">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14496,7 +14496,7 @@
       </c>
     </row>
     <row r="175" spans="1:22" ht="13.8" hidden="1">
-      <c r="A175" s="84"/>
+      <c r="A175" s="87"/>
       <c r="B175" s="71" t="s">
         <v>460</v>
       </c>
@@ -14553,7 +14553,7 @@
       </c>
     </row>
     <row r="176" spans="1:22" ht="13.8" hidden="1">
-      <c r="A176" s="84"/>
+      <c r="A176" s="87"/>
       <c r="B176" s="71" t="s">
         <v>460</v>
       </c>
@@ -14608,7 +14608,7 @@
       <c r="V176" s="71"/>
     </row>
     <row r="177" spans="1:22" ht="13.8" hidden="1">
-      <c r="A177" s="84"/>
+      <c r="A177" s="87"/>
       <c r="B177" s="71" t="s">
         <v>460</v>
       </c>
@@ -14665,7 +14665,7 @@
       </c>
     </row>
     <row r="178" spans="1:22" ht="41.4" hidden="1">
-      <c r="A178" s="84"/>
+      <c r="A178" s="87"/>
       <c r="B178" s="71" t="s">
         <v>460</v>
       </c>
@@ -14720,7 +14720,7 @@
       <c r="V178" s="71"/>
     </row>
     <row r="179" spans="1:22" ht="13.8" hidden="1">
-      <c r="A179" s="84"/>
+      <c r="A179" s="87"/>
       <c r="B179" s="71" t="s">
         <v>468</v>
       </c>
@@ -14777,7 +14777,7 @@
       </c>
     </row>
     <row r="180" spans="1:22" ht="13.8" hidden="1">
-      <c r="A180" s="84"/>
+      <c r="A180" s="87"/>
       <c r="B180" s="71" t="s">
         <v>470</v>
       </c>
@@ -14941,7 +14941,7 @@
       <c r="V182" s="66"/>
     </row>
     <row r="183" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A183" s="94">
+      <c r="A183" s="102">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14996,7 +14996,7 @@
       </c>
     </row>
     <row r="184" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A184" s="94"/>
+      <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>473</v>
       </c>
@@ -15051,7 +15051,7 @@
       </c>
     </row>
     <row r="185" spans="1:22" ht="13.8" hidden="1">
-      <c r="A185" s="94"/>
+      <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>473</v>
       </c>
@@ -15167,7 +15167,7 @@
       </c>
     </row>
     <row r="187" spans="1:22" ht="13.8" hidden="1">
-      <c r="A187" s="92"/>
+      <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>485</v>
       </c>
@@ -15218,7 +15218,7 @@
       </c>
     </row>
     <row r="188" spans="1:22" ht="13.8" hidden="1">
-      <c r="A188" s="92"/>
+      <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>485</v>
       </c>
@@ -15271,7 +15271,7 @@
       <c r="V188" s="71"/>
     </row>
     <row r="189" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A189" s="93"/>
+      <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>485</v>
       </c>
@@ -15379,7 +15379,7 @@
       </c>
     </row>
     <row r="191" spans="1:22" ht="64.95" hidden="1" customHeight="1">
-      <c r="A191" s="84">
+      <c r="A191" s="87">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15435,7 +15435,7 @@
       </c>
     </row>
     <row r="192" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="84"/>
+      <c r="A192" s="87"/>
       <c r="B192" s="71" t="s">
         <v>492</v>
       </c>
@@ -15489,7 +15489,7 @@
       </c>
     </row>
     <row r="193" spans="1:22" ht="13.8" hidden="1">
-      <c r="A193" s="84"/>
+      <c r="A193" s="87"/>
       <c r="B193" s="71" t="s">
         <v>492</v>
       </c>
@@ -15576,7 +15576,7 @@
       <c r="V194" s="66"/>
     </row>
     <row r="195" spans="1:22" ht="13.8" hidden="1">
-      <c r="A195" s="85"/>
+      <c r="A195" s="98"/>
       <c r="B195" s="71" t="s">
         <v>504</v>
       </c>
@@ -15631,7 +15631,7 @@
       </c>
     </row>
     <row r="196" spans="1:22" ht="24.6" hidden="1" customHeight="1">
-      <c r="A196" s="86"/>
+      <c r="A196" s="94"/>
       <c r="B196" s="71" t="s">
         <v>504</v>
       </c>
@@ -15686,7 +15686,7 @@
       </c>
     </row>
     <row r="197" spans="1:22" ht="13.8" hidden="1">
-      <c r="A197" s="84">
+      <c r="A197" s="87">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15742,7 +15742,7 @@
       </c>
     </row>
     <row r="198" spans="1:22" ht="13.8" hidden="1">
-      <c r="A198" s="84"/>
+      <c r="A198" s="87"/>
       <c r="B198" s="71" t="s">
         <v>508</v>
       </c>
@@ -15799,7 +15799,7 @@
       </c>
     </row>
     <row r="199" spans="1:22" ht="13.8" hidden="1">
-      <c r="A199" s="84"/>
+      <c r="A199" s="87"/>
       <c r="B199" s="71" t="s">
         <v>508</v>
       </c>
@@ -15856,7 +15856,7 @@
       </c>
     </row>
     <row r="200" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A200" s="84"/>
+      <c r="A200" s="87"/>
       <c r="B200" s="71" t="s">
         <v>508</v>
       </c>
@@ -16075,7 +16075,7 @@
       </c>
     </row>
     <row r="204" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A204" s="84">
+      <c r="A204" s="87">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -16133,7 +16133,7 @@
       </c>
     </row>
     <row r="205" spans="1:22" ht="55.2" hidden="1">
-      <c r="A205" s="84"/>
+      <c r="A205" s="87"/>
       <c r="B205" s="71" t="s">
         <v>520</v>
       </c>
@@ -16190,7 +16190,7 @@
       </c>
     </row>
     <row r="206" spans="1:22" ht="13.8" hidden="1">
-      <c r="A206" s="84"/>
+      <c r="A206" s="87"/>
       <c r="B206" s="66" t="s">
         <v>524</v>
       </c>
@@ -16247,7 +16247,7 @@
       </c>
     </row>
     <row r="207" spans="1:22" ht="13.8" hidden="1">
-      <c r="A207" s="84">
+      <c r="A207" s="87">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16304,7 +16304,7 @@
       </c>
     </row>
     <row r="208" spans="1:22" ht="13.8" hidden="1">
-      <c r="A208" s="84"/>
+      <c r="A208" s="87"/>
       <c r="B208" s="71" t="s">
         <v>527</v>
       </c>
@@ -16363,7 +16363,7 @@
       </c>
     </row>
     <row r="209" spans="1:22" ht="32.4" hidden="1" customHeight="1">
-      <c r="A209" s="84">
+      <c r="A209" s="87">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16421,7 +16421,7 @@
       </c>
     </row>
     <row r="210" spans="1:22" ht="13.8" hidden="1">
-      <c r="A210" s="84"/>
+      <c r="A210" s="87"/>
       <c r="B210" s="71" t="s">
         <v>530</v>
       </c>
@@ -16476,7 +16476,7 @@
       <c r="V210" s="71"/>
     </row>
     <row r="211" spans="1:22" ht="16.2" hidden="1" customHeight="1">
-      <c r="A211" s="84"/>
+      <c r="A211" s="87"/>
       <c r="B211" s="71" t="s">
         <v>530</v>
       </c>
@@ -16531,7 +16531,7 @@
       <c r="V211" s="66"/>
     </row>
     <row r="212" spans="1:22" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A212" s="84">
+      <c r="A212" s="87">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16587,7 +16587,7 @@
       </c>
     </row>
     <row r="213" spans="1:22" ht="13.8" hidden="1">
-      <c r="A213" s="84"/>
+      <c r="A213" s="87"/>
       <c r="B213" s="71" t="s">
         <v>539</v>
       </c>
@@ -16646,7 +16646,7 @@
       </c>
     </row>
     <row r="214" spans="1:22" ht="41.4" hidden="1">
-      <c r="A214" s="91">
+      <c r="A214" s="99">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16702,7 +16702,7 @@
       </c>
     </row>
     <row r="215" spans="1:22" ht="13.8" hidden="1">
-      <c r="A215" s="92"/>
+      <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>541</v>
       </c>
@@ -16759,7 +16759,7 @@
       </c>
     </row>
     <row r="216" spans="1:22" ht="13.8" hidden="1">
-      <c r="A216" s="92"/>
+      <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>541</v>
       </c>
@@ -16816,7 +16816,7 @@
       </c>
     </row>
     <row r="217" spans="1:22" ht="27.6" hidden="1">
-      <c r="A217" s="85"/>
+      <c r="A217" s="98"/>
       <c r="B217" s="71" t="s">
         <v>541</v>
       </c>
@@ -16872,7 +16872,7 @@
       </c>
     </row>
     <row r="218" spans="1:22" ht="13.8" hidden="1">
-      <c r="A218" s="93"/>
+      <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>541</v>
       </c>
@@ -17156,7 +17156,7 @@
       </c>
     </row>
     <row r="223" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A223" s="84">
+      <c r="A223" s="87">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17212,7 +17212,7 @@
       </c>
     </row>
     <row r="224" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A224" s="84"/>
+      <c r="A224" s="87"/>
       <c r="B224" s="71" t="s">
         <v>562</v>
       </c>
@@ -17269,7 +17269,7 @@
       </c>
     </row>
     <row r="225" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A225" s="84"/>
+      <c r="A225" s="87"/>
       <c r="B225" s="71" t="s">
         <v>562</v>
       </c>
@@ -17321,7 +17321,7 @@
       <c r="V225" s="71"/>
     </row>
     <row r="226" spans="1:22" ht="13.8" hidden="1">
-      <c r="A226" s="84"/>
+      <c r="A226" s="87"/>
       <c r="B226" s="71" t="s">
         <v>562</v>
       </c>
@@ -17378,7 +17378,7 @@
       </c>
     </row>
     <row r="227" spans="1:22" ht="27.6" hidden="1">
-      <c r="A227" s="84"/>
+      <c r="A227" s="87"/>
       <c r="B227" s="71" t="s">
         <v>562</v>
       </c>
@@ -17431,7 +17431,7 @@
       <c r="V227" s="66"/>
     </row>
     <row r="228" spans="1:22" ht="13.8" hidden="1">
-      <c r="A228" s="84"/>
+      <c r="A228" s="87"/>
       <c r="B228" s="71" t="s">
         <v>562</v>
       </c>
@@ -17796,7 +17796,7 @@
       </c>
     </row>
     <row r="235" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="90">
+      <c r="A235" s="93">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17851,7 +17851,7 @@
       </c>
     </row>
     <row r="236" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="85"/>
+      <c r="A236" s="98"/>
       <c r="B236" s="71" t="s">
         <v>583</v>
       </c>
@@ -17906,7 +17906,7 @@
       </c>
     </row>
     <row r="237" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="85"/>
+      <c r="A237" s="98"/>
       <c r="B237" s="71" t="s">
         <v>583</v>
       </c>
@@ -17961,7 +17961,7 @@
       </c>
     </row>
     <row r="238" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="85"/>
+      <c r="A238" s="98"/>
       <c r="B238" s="71" t="s">
         <v>583</v>
       </c>
@@ -18017,7 +18017,7 @@
       </c>
     </row>
     <row r="239" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A239" s="85"/>
+      <c r="A239" s="98"/>
       <c r="B239" s="71" t="s">
         <v>583</v>
       </c>
@@ -18073,7 +18073,7 @@
       </c>
     </row>
     <row r="240" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="86"/>
+      <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>597</v>
       </c>
@@ -18126,7 +18126,7 @@
       </c>
     </row>
     <row r="241" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="84">
+      <c r="A241" s="87">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -18182,7 +18182,7 @@
       <c r="V241" s="71"/>
     </row>
     <row r="242" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="84"/>
+      <c r="A242" s="87"/>
       <c r="B242" s="71" t="s">
         <v>600</v>
       </c>
@@ -18237,7 +18237,7 @@
       </c>
     </row>
     <row r="243" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A243" s="84"/>
+      <c r="A243" s="87"/>
       <c r="B243" s="71" t="s">
         <v>600</v>
       </c>
@@ -18298,7 +18298,7 @@
       </c>
     </row>
     <row r="244" spans="1:22" ht="55.2" hidden="1">
-      <c r="A244" s="84"/>
+      <c r="A244" s="87"/>
       <c r="B244" s="71" t="s">
         <v>600</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="245" spans="1:22" ht="13.8" hidden="1">
-      <c r="A245" s="84"/>
+      <c r="A245" s="87"/>
       <c r="B245" s="71" t="s">
         <v>600</v>
       </c>
@@ -18387,7 +18387,7 @@
       <c r="V245" s="71"/>
     </row>
     <row r="246" spans="1:22" ht="13.8" hidden="1">
-      <c r="A246" s="84"/>
+      <c r="A246" s="87"/>
       <c r="B246" s="71" t="s">
         <v>600</v>
       </c>
@@ -18440,7 +18440,7 @@
       </c>
     </row>
     <row r="247" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A247" s="84"/>
+      <c r="A247" s="87"/>
       <c r="B247" s="71" t="s">
         <v>600</v>
       </c>
@@ -18551,7 +18551,7 @@
       <c r="V248" s="71"/>
     </row>
     <row r="249" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="84">
+      <c r="A249" s="87">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18607,7 +18607,7 @@
       </c>
     </row>
     <row r="250" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A250" s="84"/>
+      <c r="A250" s="87"/>
       <c r="B250" s="71" t="s">
         <v>608</v>
       </c>
@@ -18662,7 +18662,7 @@
       </c>
     </row>
     <row r="251" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A251" s="84"/>
+      <c r="A251" s="87"/>
       <c r="B251" s="71" t="s">
         <v>608</v>
       </c>
@@ -18856,7 +18856,7 @@
       <c r="V254" s="66"/>
     </row>
     <row r="255" spans="1:22" ht="27.6" hidden="1">
-      <c r="A255" s="90">
+      <c r="A255" s="93">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18911,7 +18911,7 @@
       </c>
     </row>
     <row r="256" spans="1:22" ht="27.6" hidden="1">
-      <c r="A256" s="85"/>
+      <c r="A256" s="98"/>
       <c r="B256" s="71" t="s">
         <v>621</v>
       </c>
@@ -18967,7 +18967,7 @@
       </c>
     </row>
     <row r="257" spans="1:22" ht="13.8" hidden="1">
-      <c r="A257" s="85"/>
+      <c r="A257" s="98"/>
       <c r="B257" s="71" t="s">
         <v>621</v>
       </c>
@@ -19024,7 +19024,7 @@
       </c>
     </row>
     <row r="258" spans="1:22" ht="13.8" hidden="1">
-      <c r="A258" s="85"/>
+      <c r="A258" s="98"/>
       <c r="B258" s="71" t="s">
         <v>621</v>
       </c>
@@ -19081,7 +19081,7 @@
       </c>
     </row>
     <row r="259" spans="1:22" ht="13.8" hidden="1">
-      <c r="A259" s="85"/>
+      <c r="A259" s="98"/>
       <c r="B259" s="71" t="s">
         <v>621</v>
       </c>
@@ -19136,7 +19136,7 @@
       </c>
     </row>
     <row r="260" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A260" s="86"/>
+      <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>621</v>
       </c>
@@ -19193,7 +19193,7 @@
       </c>
     </row>
     <row r="261" spans="1:22" ht="55.2" hidden="1">
-      <c r="A261" s="90">
+      <c r="A261" s="93">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19249,7 +19249,7 @@
       </c>
     </row>
     <row r="262" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="85"/>
+      <c r="A262" s="98"/>
       <c r="B262" s="71" t="s">
         <v>631</v>
       </c>
@@ -19302,7 +19302,7 @@
       </c>
     </row>
     <row r="263" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="85"/>
+      <c r="A263" s="98"/>
       <c r="B263" s="71" t="s">
         <v>639</v>
       </c>
@@ -19351,7 +19351,7 @@
       </c>
     </row>
     <row r="264" spans="1:22" ht="55.2" hidden="1">
-      <c r="A264" s="85"/>
+      <c r="A264" s="98"/>
       <c r="B264" s="71" t="s">
         <v>639</v>
       </c>
@@ -19402,7 +19402,7 @@
       </c>
     </row>
     <row r="265" spans="1:22" ht="46.2" hidden="1" customHeight="1">
-      <c r="A265" s="85"/>
+      <c r="A265" s="98"/>
       <c r="B265" s="71" t="s">
         <v>631</v>
       </c>
@@ -19515,7 +19515,7 @@
       <c r="V266" s="71"/>
     </row>
     <row r="267" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="84">
+      <c r="A267" s="87">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19574,7 +19574,7 @@
       <c r="V267" s="71"/>
     </row>
     <row r="268" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="84"/>
+      <c r="A268" s="87"/>
       <c r="B268" s="71" t="s">
         <v>645</v>
       </c>
@@ -19631,7 +19631,7 @@
       <c r="V268" s="71"/>
     </row>
     <row r="269" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A269" s="84"/>
+      <c r="A269" s="87"/>
       <c r="B269" s="71" t="s">
         <v>645</v>
       </c>
@@ -19688,7 +19688,7 @@
       <c r="V269" s="71"/>
     </row>
     <row r="270" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A270" s="84"/>
+      <c r="A270" s="87"/>
       <c r="B270" s="71" t="s">
         <v>645</v>
       </c>
@@ -19802,7 +19802,7 @@
       </c>
     </row>
     <row r="272" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="84">
+      <c r="A272" s="87">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19859,7 +19859,7 @@
       <c r="V272" s="71"/>
     </row>
     <row r="273" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A273" s="84"/>
+      <c r="A273" s="87"/>
       <c r="B273" s="71" t="s">
         <v>655</v>
       </c>
@@ -19916,7 +19916,7 @@
       </c>
     </row>
     <row r="274" spans="1:22" ht="13.8" hidden="1">
-      <c r="A274" s="84"/>
+      <c r="A274" s="87"/>
       <c r="B274" s="71" t="s">
         <v>655</v>
       </c>
@@ -19973,7 +19973,7 @@
       </c>
     </row>
     <row r="275" spans="1:22" ht="13.8" hidden="1">
-      <c r="A275" s="84"/>
+      <c r="A275" s="87"/>
       <c r="B275" s="71" t="s">
         <v>655</v>
       </c>
@@ -20030,7 +20030,7 @@
       </c>
     </row>
     <row r="276" spans="1:22" ht="13.8" hidden="1">
-      <c r="A276" s="84"/>
+      <c r="A276" s="87"/>
       <c r="B276" s="66" t="s">
         <v>662</v>
       </c>
@@ -20311,7 +20311,7 @@
       <c r="V280" s="66"/>
     </row>
     <row r="281" spans="1:22" ht="27.6" hidden="1">
-      <c r="A281" s="84">
+      <c r="A281" s="87">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20366,7 +20366,7 @@
       </c>
     </row>
     <row r="282" spans="1:22" ht="13.8" hidden="1">
-      <c r="A282" s="84"/>
+      <c r="A282" s="87"/>
       <c r="B282" s="71" t="s">
         <v>671</v>
       </c>
@@ -20416,7 +20416,7 @@
       <c r="V282" s="66"/>
     </row>
     <row r="283" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A283" s="84">
+      <c r="A283" s="87">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20472,7 +20472,7 @@
       </c>
     </row>
     <row r="284" spans="1:22" ht="13.8" hidden="1">
-      <c r="A284" s="84"/>
+      <c r="A284" s="87"/>
       <c r="B284" s="71" t="s">
         <v>674</v>
       </c>
@@ -20527,7 +20527,7 @@
       <c r="V284" s="71"/>
     </row>
     <row r="285" spans="1:22" ht="13.8" hidden="1">
-      <c r="A285" s="86">
+      <c r="A285" s="94">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20586,7 +20586,7 @@
       </c>
     </row>
     <row r="286" spans="1:22" ht="13.8" hidden="1">
-      <c r="A286" s="86"/>
+      <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>678</v>
       </c>
@@ -20643,7 +20643,7 @@
       </c>
     </row>
     <row r="287" spans="1:22" ht="13.8" hidden="1">
-      <c r="A287" s="86"/>
+      <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>678</v>
       </c>
@@ -20700,7 +20700,7 @@
       </c>
     </row>
     <row r="288" spans="1:22" ht="13.8" hidden="1">
-      <c r="A288" s="86"/>
+      <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>678</v>
       </c>
@@ -20757,7 +20757,7 @@
       </c>
     </row>
     <row r="289" spans="1:22" ht="13.8" hidden="1">
-      <c r="A289" s="84"/>
+      <c r="A289" s="87"/>
       <c r="B289" s="71" t="s">
         <v>678</v>
       </c>
@@ -20811,7 +20811,7 @@
       </c>
     </row>
     <row r="290" spans="1:22" ht="27.6" hidden="1">
-      <c r="A290" s="84"/>
+      <c r="A290" s="87"/>
       <c r="B290" s="71" t="s">
         <v>678</v>
       </c>
@@ -20866,7 +20866,7 @@
       </c>
     </row>
     <row r="291" spans="1:22" ht="13.8" hidden="1">
-      <c r="A291" s="84"/>
+      <c r="A291" s="87"/>
       <c r="B291" s="71" t="s">
         <v>678</v>
       </c>
@@ -20923,7 +20923,7 @@
       </c>
     </row>
     <row r="292" spans="1:22" ht="13.8" hidden="1">
-      <c r="A292" s="84"/>
+      <c r="A292" s="87"/>
       <c r="B292" s="71" t="s">
         <v>678</v>
       </c>
@@ -20976,7 +20976,7 @@
       <c r="V292" s="71"/>
     </row>
     <row r="293" spans="1:22" ht="13.8" hidden="1">
-      <c r="A293" s="84"/>
+      <c r="A293" s="87"/>
       <c r="B293" s="71" t="s">
         <v>678</v>
       </c>
@@ -21092,7 +21092,7 @@
       </c>
     </row>
     <row r="295" spans="1:22" ht="96.6" hidden="1">
-      <c r="A295" s="84">
+      <c r="A295" s="87">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -21155,7 +21155,7 @@
       </c>
     </row>
     <row r="296" spans="1:22" ht="27.6" hidden="1">
-      <c r="A296" s="84"/>
+      <c r="A296" s="87"/>
       <c r="B296" s="71" t="s">
         <v>693</v>
       </c>
@@ -21216,7 +21216,7 @@
       </c>
     </row>
     <row r="297" spans="1:22" ht="13.8" hidden="1">
-      <c r="A297" s="84"/>
+      <c r="A297" s="87"/>
       <c r="B297" s="71" t="s">
         <v>693</v>
       </c>
@@ -21277,7 +21277,7 @@
       </c>
     </row>
     <row r="298" spans="1:22" ht="27.6" hidden="1">
-      <c r="A298" s="84">
+      <c r="A298" s="87">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21333,7 +21333,7 @@
       </c>
     </row>
     <row r="299" spans="1:22" ht="13.8" hidden="1">
-      <c r="A299" s="84"/>
+      <c r="A299" s="87"/>
       <c r="B299" s="71" t="s">
         <v>704</v>
       </c>
@@ -21388,7 +21388,7 @@
       <c r="V299" s="71"/>
     </row>
     <row r="300" spans="1:22" ht="13.8" hidden="1">
-      <c r="A300" s="84"/>
+      <c r="A300" s="87"/>
       <c r="B300" s="71" t="s">
         <v>704</v>
       </c>
@@ -21445,7 +21445,7 @@
       </c>
     </row>
     <row r="301" spans="1:22" ht="13.8" hidden="1">
-      <c r="A301" s="85"/>
+      <c r="A301" s="98"/>
       <c r="B301" s="71" t="s">
         <v>639</v>
       </c>
@@ -21500,7 +21500,7 @@
       <c r="V301" s="71"/>
     </row>
     <row r="302" spans="1:22" ht="13.8" hidden="1">
-      <c r="A302" s="86"/>
+      <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>639</v>
       </c>
@@ -21557,7 +21557,7 @@
       </c>
     </row>
     <row r="303" spans="1:22" ht="27.6" hidden="1">
-      <c r="A303" s="90">
+      <c r="A303" s="93">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21613,7 +21613,7 @@
       </c>
     </row>
     <row r="304" spans="1:22" ht="13.8" hidden="1">
-      <c r="A304" s="85"/>
+      <c r="A304" s="98"/>
       <c r="B304" s="71" t="s">
         <v>718</v>
       </c>
@@ -21668,7 +21668,7 @@
       <c r="V304" s="71"/>
     </row>
     <row r="305" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="90">
+      <c r="A305" s="93">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21723,7 +21723,7 @@
       </c>
     </row>
     <row r="306" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="85"/>
+      <c r="A306" s="98"/>
       <c r="B306" s="71" t="s">
         <v>720</v>
       </c>
@@ -21778,7 +21778,7 @@
       </c>
     </row>
     <row r="307" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="85"/>
+      <c r="A307" s="98"/>
       <c r="B307" s="71" t="s">
         <v>720</v>
       </c>
@@ -21832,7 +21832,7 @@
       </c>
     </row>
     <row r="308" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A308" s="86"/>
+      <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>720</v>
       </c>
@@ -21960,57 +21960,57 @@
       <c r="D310" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E310" s="96">
+      <c r="E310" s="95">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="95" t="s">
+      <c r="F310" s="104" t="s">
         <v>731</v>
       </c>
-      <c r="G310" s="84" t="s">
+      <c r="G310" s="87" t="s">
         <v>732</v>
       </c>
-      <c r="H310" s="84">
+      <c r="H310" s="87">
         <v>13.3</v>
       </c>
-      <c r="I310" s="90" t="s">
+      <c r="I310" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="J310" s="90" t="s">
+      <c r="J310" s="93" t="s">
         <v>542</v>
       </c>
-      <c r="K310" s="87">
+      <c r="K310" s="91">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="87">
+      <c r="L310" s="91">
         <v>0</v>
       </c>
-      <c r="M310" s="87">
+      <c r="M310" s="91">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="89" t="s">
+      <c r="N310" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="O310" s="89" t="s">
+      <c r="O310" s="88" t="s">
         <v>733</v>
       </c>
-      <c r="P310" s="84">
+      <c r="P310" s="87">
         <v>2025</v>
       </c>
-      <c r="Q310" s="89" t="s">
+      <c r="Q310" s="88" t="s">
         <v>39</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
       <c r="T310" s="71"/>
-      <c r="U310" s="84"/>
-      <c r="V310" s="84" t="s">
+      <c r="U310" s="87"/>
+      <c r="V310" s="87" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="311" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="84">
+      <c r="A311" s="87">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -22022,27 +22022,27 @@
       <c r="D311" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E311" s="97"/>
-      <c r="F311" s="89"/>
-      <c r="G311" s="84"/>
-      <c r="H311" s="84"/>
-      <c r="I311" s="86"/>
-      <c r="J311" s="86"/>
-      <c r="K311" s="87"/>
-      <c r="L311" s="87"/>
-      <c r="M311" s="87"/>
-      <c r="N311" s="89"/>
-      <c r="O311" s="89"/>
-      <c r="P311" s="84"/>
-      <c r="Q311" s="89"/>
+      <c r="E311" s="96"/>
+      <c r="F311" s="88"/>
+      <c r="G311" s="87"/>
+      <c r="H311" s="87"/>
+      <c r="I311" s="94"/>
+      <c r="J311" s="94"/>
+      <c r="K311" s="91"/>
+      <c r="L311" s="91"/>
+      <c r="M311" s="91"/>
+      <c r="N311" s="88"/>
+      <c r="O311" s="88"/>
+      <c r="P311" s="87"/>
+      <c r="Q311" s="88"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
       <c r="T311" s="71"/>
-      <c r="U311" s="84"/>
-      <c r="V311" s="84"/>
+      <c r="U311" s="87"/>
+      <c r="V311" s="87"/>
     </row>
     <row r="312" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="84"/>
+      <c r="A312" s="87"/>
       <c r="B312" s="71" t="s">
         <v>730</v>
       </c>
@@ -22052,58 +22052,58 @@
       <c r="D312" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E312" s="96">
+      <c r="E312" s="95">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="89" t="s">
+      <c r="F312" s="88" t="s">
         <v>735</v>
       </c>
-      <c r="G312" s="84" t="s">
+      <c r="G312" s="87" t="s">
         <v>736</v>
       </c>
-      <c r="H312" s="84">
+      <c r="H312" s="87">
         <v>31.12</v>
       </c>
-      <c r="I312" s="90" t="s">
+      <c r="I312" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="J312" s="90" t="s">
+      <c r="J312" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="K312" s="87">
+      <c r="K312" s="91">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="87">
+      <c r="L312" s="91">
         <v>0</v>
       </c>
-      <c r="M312" s="87">
+      <c r="M312" s="91">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="89" t="s">
+      <c r="N312" s="88" t="s">
         <v>737</v>
       </c>
-      <c r="O312" s="89" t="s">
+      <c r="O312" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="P312" s="84">
+      <c r="P312" s="87">
         <v>2019</v>
       </c>
-      <c r="Q312" s="89" t="s">
+      <c r="Q312" s="88" t="s">
         <v>53</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
       <c r="T312" s="71"/>
-      <c r="U312" s="88">
+      <c r="U312" s="105">
         <v>1</v>
       </c>
-      <c r="V312" s="84" t="s">
+      <c r="V312" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="313" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="84"/>
+      <c r="A313" s="87"/>
       <c r="B313" s="71" t="s">
         <v>734</v>
       </c>
@@ -22113,27 +22113,27 @@
       <c r="D313" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E313" s="97"/>
-      <c r="F313" s="89"/>
-      <c r="G313" s="84"/>
-      <c r="H313" s="84"/>
-      <c r="I313" s="86"/>
-      <c r="J313" s="86"/>
-      <c r="K313" s="87"/>
-      <c r="L313" s="87"/>
-      <c r="M313" s="87"/>
-      <c r="N313" s="89"/>
-      <c r="O313" s="89"/>
-      <c r="P313" s="84"/>
-      <c r="Q313" s="89"/>
+      <c r="E313" s="96"/>
+      <c r="F313" s="88"/>
+      <c r="G313" s="87"/>
+      <c r="H313" s="87"/>
+      <c r="I313" s="94"/>
+      <c r="J313" s="94"/>
+      <c r="K313" s="91"/>
+      <c r="L313" s="91"/>
+      <c r="M313" s="91"/>
+      <c r="N313" s="88"/>
+      <c r="O313" s="88"/>
+      <c r="P313" s="87"/>
+      <c r="Q313" s="88"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
       <c r="T313" s="71"/>
-      <c r="U313" s="88"/>
-      <c r="V313" s="84"/>
+      <c r="U313" s="105"/>
+      <c r="V313" s="87"/>
     </row>
     <row r="314" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="84"/>
+      <c r="A314" s="87"/>
       <c r="B314" s="71" t="s">
         <v>734</v>
       </c>
@@ -22192,7 +22192,7 @@
       </c>
     </row>
     <row r="315" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A315" s="84"/>
+      <c r="A315" s="87"/>
       <c r="B315" s="71" t="s">
         <v>734</v>
       </c>
@@ -22249,7 +22249,7 @@
       <c r="V315" s="71"/>
     </row>
     <row r="316" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A316" s="84"/>
+      <c r="A316" s="87"/>
       <c r="B316" s="71" t="s">
         <v>734</v>
       </c>
@@ -22406,7 +22406,7 @@
       </c>
     </row>
     <row r="319" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A319" s="90">
+      <c r="A319" s="93">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22456,7 +22456,7 @@
       <c r="V319" s="71"/>
     </row>
     <row r="320" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A320" s="86"/>
+      <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>740</v>
       </c>
@@ -22510,7 +22510,7 @@
       </c>
     </row>
     <row r="321" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A321" s="91">
+      <c r="A321" s="99">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22565,7 +22565,7 @@
       </c>
     </row>
     <row r="322" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A322" s="92"/>
+      <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>746</v>
       </c>
@@ -22616,7 +22616,7 @@
       </c>
     </row>
     <row r="323" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A323" s="92"/>
+      <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>746</v>
       </c>
@@ -22671,7 +22671,7 @@
       </c>
     </row>
     <row r="324" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A324" s="92"/>
+      <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>746</v>
       </c>
@@ -22726,7 +22726,7 @@
       </c>
     </row>
     <row r="325" spans="1:22" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="85"/>
+      <c r="A325" s="98"/>
       <c r="B325" s="66" t="s">
         <v>746</v>
       </c>
@@ -22779,7 +22779,7 @@
       </c>
     </row>
     <row r="326" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A326" s="85"/>
+      <c r="A326" s="98"/>
       <c r="B326" s="66" t="s">
         <v>746</v>
       </c>
@@ -22832,7 +22832,7 @@
       </c>
     </row>
     <row r="327" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A327" s="92"/>
+      <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>746</v>
       </c>
@@ -22889,7 +22889,7 @@
       </c>
     </row>
     <row r="328" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A328" s="92"/>
+      <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>746</v>
       </c>
@@ -22942,7 +22942,7 @@
       </c>
     </row>
     <row r="329" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A329" s="92"/>
+      <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>746</v>
       </c>
@@ -22997,7 +22997,7 @@
       <c r="V329" s="71"/>
     </row>
     <row r="330" spans="1:22" ht="13.8" hidden="1">
-      <c r="A330" s="93"/>
+      <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>746</v>
       </c>
@@ -23134,7 +23134,7 @@
       <c r="U332" s="66"/>
       <c r="V332" s="66"/>
     </row>
-    <row r="333" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="333" spans="1:22" ht="41.4">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>767</v>
@@ -23187,7 +23187,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:22" ht="13.8" hidden="1">
+    <row r="334" spans="1:22" ht="13.8">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>767</v>
@@ -23233,8 +23233,8 @@
         <v>590</v>
       </c>
     </row>
-    <row r="335" spans="1:22" ht="41.4" hidden="1">
-      <c r="A335" s="90">
+    <row r="335" spans="1:22" ht="41.4">
+      <c r="A335" s="93">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -23296,8 +23296,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="336" spans="1:22" ht="44.4" hidden="1" customHeight="1">
-      <c r="A336" s="85"/>
+    <row r="336" spans="1:22" ht="44.4" customHeight="1">
+      <c r="A336" s="98"/>
       <c r="B336" s="71" t="s">
         <v>767</v>
       </c>
@@ -23350,8 +23350,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="155.4" hidden="1" customHeight="1">
-      <c r="A337" s="85"/>
+    <row r="337" spans="1:23" ht="155.4" customHeight="1">
+      <c r="A337" s="98"/>
       <c r="B337" s="71" t="s">
         <v>767</v>
       </c>
@@ -23404,8 +23404,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="13.8" hidden="1">
-      <c r="A338" s="86"/>
+    <row r="338" spans="1:23" ht="13.8">
+      <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>767</v>
       </c>
@@ -23509,7 +23509,7 @@
       </c>
     </row>
     <row r="340" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A340" s="84">
+      <c r="A340" s="87">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23568,7 +23568,7 @@
       <c r="W340" s="33"/>
     </row>
     <row r="341" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A341" s="84"/>
+      <c r="A341" s="87"/>
       <c r="B341" s="71" t="s">
         <v>775</v>
       </c>
@@ -23624,7 +23624,7 @@
       <c r="W341" s="33"/>
     </row>
     <row r="342" spans="1:23" ht="13.8" hidden="1">
-      <c r="A342" s="84">
+      <c r="A342" s="87">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23683,7 +23683,7 @@
       </c>
     </row>
     <row r="343" spans="1:23" ht="13.8" hidden="1">
-      <c r="A343" s="84"/>
+      <c r="A343" s="87"/>
       <c r="B343" s="71" t="s">
         <v>778</v>
       </c>
@@ -23740,7 +23740,7 @@
       </c>
     </row>
     <row r="344" spans="1:23" ht="27.6" hidden="1">
-      <c r="A344" s="84"/>
+      <c r="A344" s="87"/>
       <c r="B344" s="71" t="s">
         <v>778</v>
       </c>
@@ -23793,7 +23793,7 @@
       </c>
     </row>
     <row r="345" spans="1:23" ht="13.8" hidden="1">
-      <c r="A345" s="84"/>
+      <c r="A345" s="87"/>
       <c r="B345" s="71" t="s">
         <v>778</v>
       </c>
@@ -23850,7 +23850,7 @@
       </c>
     </row>
     <row r="346" spans="1:23" ht="27.6" hidden="1">
-      <c r="A346" s="84"/>
+      <c r="A346" s="87"/>
       <c r="B346" s="71" t="s">
         <v>778</v>
       </c>
@@ -23904,7 +23904,7 @@
       </c>
     </row>
     <row r="347" spans="1:23" ht="27.6" hidden="1">
-      <c r="A347" s="84"/>
+      <c r="A347" s="87"/>
       <c r="B347" s="71" t="s">
         <v>778</v>
       </c>
@@ -23951,7 +23951,7 @@
       </c>
     </row>
     <row r="348" spans="1:23" ht="13.8" hidden="1">
-      <c r="A348" s="84"/>
+      <c r="A348" s="87"/>
       <c r="B348" s="71" t="s">
         <v>778</v>
       </c>
@@ -24008,7 +24008,7 @@
       </c>
     </row>
     <row r="349" spans="1:23" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="84">
+      <c r="A349" s="87">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -24066,7 +24066,7 @@
       <c r="V349" s="71"/>
     </row>
     <row r="350" spans="1:23" ht="61.2" hidden="1" customHeight="1">
-      <c r="A350" s="84"/>
+      <c r="A350" s="87"/>
       <c r="B350" s="71" t="s">
         <v>790</v>
       </c>
@@ -24121,7 +24121,7 @@
       </c>
     </row>
     <row r="351" spans="1:23" ht="13.8" hidden="1">
-      <c r="A351" s="84"/>
+      <c r="A351" s="87"/>
       <c r="B351" s="71" t="s">
         <v>790</v>
       </c>
@@ -24178,7 +24178,7 @@
       </c>
     </row>
     <row r="352" spans="1:23" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="84">
+      <c r="A352" s="87">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -24237,7 +24237,7 @@
       </c>
     </row>
     <row r="353" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="84"/>
+      <c r="A353" s="87"/>
       <c r="B353" s="71" t="s">
         <v>795</v>
       </c>
@@ -24291,7 +24291,7 @@
       </c>
     </row>
     <row r="354" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A354" s="84"/>
+      <c r="A354" s="87"/>
       <c r="B354" s="71" t="s">
         <v>795</v>
       </c>
@@ -24348,7 +24348,7 @@
       </c>
     </row>
     <row r="355" spans="1:22" ht="46.95" hidden="1" customHeight="1">
-      <c r="A355" s="84"/>
+      <c r="A355" s="87"/>
       <c r="B355" s="71" t="s">
         <v>795</v>
       </c>
@@ -24409,7 +24409,7 @@
       </c>
     </row>
     <row r="356" spans="1:22" ht="27.6" hidden="1">
-      <c r="A356" s="84"/>
+      <c r="A356" s="87"/>
       <c r="B356" s="71" t="s">
         <v>795</v>
       </c>
@@ -24464,7 +24464,7 @@
       </c>
     </row>
     <row r="357" spans="1:22" ht="13.8" hidden="1">
-      <c r="A357" s="84"/>
+      <c r="A357" s="87"/>
       <c r="B357" s="71" t="s">
         <v>795</v>
       </c>
@@ -24803,7 +24803,7 @@
       </c>
     </row>
     <row r="363" spans="1:22" ht="13.8" hidden="1">
-      <c r="A363" s="84"/>
+      <c r="A363" s="87"/>
       <c r="B363" s="71" t="s">
         <v>815</v>
       </c>
@@ -24859,7 +24859,7 @@
       <c r="V363" s="71"/>
     </row>
     <row r="364" spans="1:22" ht="13.8" hidden="1">
-      <c r="A364" s="84"/>
+      <c r="A364" s="87"/>
       <c r="B364" s="71" t="s">
         <v>815</v>
       </c>
@@ -25085,7 +25085,7 @@
       <c r="V367" s="71"/>
     </row>
     <row r="368" spans="1:22" ht="41.4" hidden="1">
-      <c r="A368" s="90">
+      <c r="A368" s="93">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -25137,7 +25137,7 @@
       </c>
     </row>
     <row r="369" spans="1:22" ht="41.4" hidden="1">
-      <c r="A369" s="85"/>
+      <c r="A369" s="98"/>
       <c r="B369" s="71" t="s">
         <v>822</v>
       </c>
@@ -25198,7 +25198,7 @@
       </c>
     </row>
     <row r="370" spans="1:22" ht="41.4" hidden="1">
-      <c r="A370" s="85"/>
+      <c r="A370" s="98"/>
       <c r="B370" s="71" t="s">
         <v>822</v>
       </c>
@@ -25252,7 +25252,7 @@
       </c>
     </row>
     <row r="371" spans="1:22" ht="27.6" hidden="1">
-      <c r="A371" s="85"/>
+      <c r="A371" s="98"/>
       <c r="B371" s="71" t="s">
         <v>822</v>
       </c>
@@ -25309,7 +25309,7 @@
       </c>
     </row>
     <row r="372" spans="1:22" ht="27.6" hidden="1">
-      <c r="A372" s="86"/>
+      <c r="A372" s="94"/>
       <c r="B372" s="71" t="s">
         <v>822</v>
       </c>
@@ -25365,7 +25365,7 @@
       <c r="V372" s="71"/>
     </row>
     <row r="373" spans="1:22" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A373" s="84">
+      <c r="A373" s="87">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25421,7 +25421,7 @@
       </c>
     </row>
     <row r="374" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="84"/>
+      <c r="A374" s="87"/>
       <c r="B374" s="71" t="s">
         <v>828</v>
       </c>
@@ -25475,7 +25475,7 @@
       </c>
     </row>
     <row r="375" spans="1:22" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="84"/>
+      <c r="A375" s="87"/>
       <c r="B375" s="71" t="s">
         <v>828</v>
       </c>
@@ -25529,7 +25529,7 @@
       </c>
     </row>
     <row r="376" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A376" s="84"/>
+      <c r="A376" s="87"/>
       <c r="B376" s="71" t="s">
         <v>828</v>
       </c>
@@ -25583,7 +25583,7 @@
       </c>
     </row>
     <row r="377" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A377" s="84"/>
+      <c r="A377" s="87"/>
       <c r="B377" s="71" t="s">
         <v>828</v>
       </c>
@@ -25627,7 +25627,7 @@
       </c>
     </row>
     <row r="378" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A378" s="84"/>
+      <c r="A378" s="87"/>
       <c r="B378" s="71" t="s">
         <v>828</v>
       </c>
@@ -25680,7 +25680,7 @@
       </c>
     </row>
     <row r="379" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A379" s="84"/>
+      <c r="A379" s="87"/>
       <c r="B379" s="71" t="s">
         <v>828</v>
       </c>
@@ -25733,7 +25733,7 @@
       </c>
     </row>
     <row r="380" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A380" s="84"/>
+      <c r="A380" s="87"/>
       <c r="B380" s="71" t="s">
         <v>828</v>
       </c>
@@ -25780,7 +25780,7 @@
       </c>
     </row>
     <row r="381" spans="1:22" ht="13.8" hidden="1">
-      <c r="A381" s="84"/>
+      <c r="A381" s="87"/>
       <c r="B381" s="71" t="s">
         <v>828</v>
       </c>
@@ -25830,7 +25830,7 @@
       <c r="V381" s="71"/>
     </row>
     <row r="382" spans="1:22" ht="13.8" hidden="1">
-      <c r="A382" s="84"/>
+      <c r="A382" s="87"/>
       <c r="B382" s="71" t="s">
         <v>828</v>
       </c>
@@ -25885,7 +25885,7 @@
       <c r="V382" s="71"/>
     </row>
     <row r="383" spans="1:22" ht="13.8" hidden="1">
-      <c r="A383" s="84"/>
+      <c r="A383" s="87"/>
       <c r="B383" s="71" t="s">
         <v>828</v>
       </c>
@@ -25938,7 +25938,7 @@
       </c>
     </row>
     <row r="384" spans="1:22" ht="13.8" hidden="1">
-      <c r="A384" s="84"/>
+      <c r="A384" s="87"/>
       <c r="B384" s="71" t="s">
         <v>828</v>
       </c>
@@ -25993,7 +25993,7 @@
       <c r="V384" s="71"/>
     </row>
     <row r="385" spans="1:22" ht="27.6" hidden="1">
-      <c r="A385" s="86">
+      <c r="A385" s="94">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -26049,7 +26049,7 @@
       </c>
     </row>
     <row r="386" spans="1:22" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A386" s="84"/>
+      <c r="A386" s="87"/>
       <c r="B386" s="71" t="s">
         <v>856</v>
       </c>
@@ -26103,7 +26103,7 @@
       </c>
     </row>
     <row r="387" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A387" s="84"/>
+      <c r="A387" s="87"/>
       <c r="B387" s="71" t="s">
         <v>856</v>
       </c>
@@ -26160,7 +26160,7 @@
       <c r="V387" s="71"/>
     </row>
     <row r="388" spans="1:22" ht="13.8" hidden="1">
-      <c r="A388" s="84"/>
+      <c r="A388" s="87"/>
       <c r="B388" s="71" t="s">
         <v>856</v>
       </c>
@@ -26215,7 +26215,7 @@
       </c>
     </row>
     <row r="389" spans="1:22" ht="13.8" hidden="1">
-      <c r="A389" s="84"/>
+      <c r="A389" s="87"/>
       <c r="B389" s="71" t="s">
         <v>855</v>
       </c>
@@ -26270,7 +26270,7 @@
       </c>
     </row>
     <row r="390" spans="1:22" ht="13.8" hidden="1">
-      <c r="A390" s="84"/>
+      <c r="A390" s="87"/>
       <c r="B390" s="71" t="s">
         <v>855</v>
       </c>
@@ -26327,7 +26327,7 @@
       </c>
     </row>
     <row r="391" spans="1:22" ht="13.8" hidden="1">
-      <c r="A391" s="84"/>
+      <c r="A391" s="87"/>
       <c r="B391" s="71" t="s">
         <v>855</v>
       </c>
@@ -26369,7 +26369,7 @@
       </c>
     </row>
     <row r="392" spans="1:22" ht="13.8" hidden="1">
-      <c r="A392" s="84"/>
+      <c r="A392" s="87"/>
       <c r="B392" s="66" t="s">
         <v>855</v>
       </c>
@@ -26423,7 +26423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="393" spans="1:22" ht="148.19999999999999" customHeight="1">
+    <row r="393" spans="1:22" ht="148.19999999999999" hidden="1" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>865</v>
@@ -26477,8 +26477,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="394" spans="1:22" ht="58.2" customHeight="1">
-      <c r="A394" s="84">
+    <row r="394" spans="1:22" ht="58.2" hidden="1" customHeight="1">
+      <c r="A394" s="87">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26533,8 +26533,8 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="395" spans="1:22" ht="41.4">
-      <c r="A395" s="84"/>
+    <row r="395" spans="1:22" ht="41.4" hidden="1">
+      <c r="A395" s="87"/>
       <c r="B395" s="66" t="s">
         <v>865</v>
       </c>
@@ -26587,8 +26587,8 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="396" spans="1:22" ht="18" customHeight="1">
-      <c r="A396" s="84"/>
+    <row r="396" spans="1:22" ht="18" hidden="1" customHeight="1">
+      <c r="A396" s="87"/>
       <c r="B396" s="71" t="s">
         <v>865</v>
       </c>
@@ -26644,8 +26644,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="397" spans="1:22" ht="27.6">
-      <c r="A397" s="84"/>
+    <row r="397" spans="1:22" ht="27.6" hidden="1">
+      <c r="A397" s="87"/>
       <c r="B397" s="71" t="s">
         <v>865</v>
       </c>
@@ -26697,8 +26697,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="398" spans="1:22" ht="18" customHeight="1">
-      <c r="A398" s="84"/>
+    <row r="398" spans="1:22" ht="18" hidden="1" customHeight="1">
+      <c r="A398" s="87"/>
       <c r="B398" s="71" t="s">
         <v>865</v>
       </c>
@@ -26752,8 +26752,8 @@
       </c>
       <c r="V398" s="71"/>
     </row>
-    <row r="399" spans="1:22" ht="13.8">
-      <c r="A399" s="84"/>
+    <row r="399" spans="1:22" ht="13.8" hidden="1">
+      <c r="A399" s="87"/>
       <c r="B399" s="71" t="s">
         <v>865</v>
       </c>
@@ -26808,7 +26808,7 @@
       <c r="V399" s="71"/>
     </row>
     <row r="400" spans="1:22" ht="27.6" hidden="1">
-      <c r="A400" s="94">
+      <c r="A400" s="102">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26866,7 +26866,7 @@
       </c>
     </row>
     <row r="401" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A401" s="94"/>
+      <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
         <v>874</v>
       </c>
@@ -26908,7 +26908,7 @@
       <c r="V401" s="66"/>
     </row>
     <row r="402" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A402" s="94"/>
+      <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
         <v>874</v>
       </c>
@@ -26963,7 +26963,7 @@
       </c>
     </row>
     <row r="403" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A403" s="94"/>
+      <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
         <v>874</v>
       </c>
@@ -27020,7 +27020,7 @@
       </c>
     </row>
     <row r="404" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A404" s="94"/>
+      <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
         <v>874</v>
       </c>
@@ -27075,7 +27075,7 @@
       <c r="V404" s="71"/>
     </row>
     <row r="405" spans="1:22" ht="13.8" hidden="1">
-      <c r="A405" s="94"/>
+      <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
         <v>874</v>
       </c>
@@ -27132,7 +27132,7 @@
       </c>
     </row>
     <row r="406" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="84">
+      <c r="A406" s="87">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -27188,7 +27188,7 @@
       </c>
     </row>
     <row r="407" spans="1:22" ht="13.8" hidden="1">
-      <c r="A407" s="84"/>
+      <c r="A407" s="87"/>
       <c r="B407" s="71" t="s">
         <v>881</v>
       </c>
@@ -27245,7 +27245,7 @@
       </c>
     </row>
     <row r="408" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="84">
+      <c r="A408" s="87">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -27302,7 +27302,7 @@
       </c>
     </row>
     <row r="409" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="84"/>
+      <c r="A409" s="87"/>
       <c r="B409" s="71" t="s">
         <v>885</v>
       </c>
@@ -27359,7 +27359,7 @@
       </c>
     </row>
     <row r="410" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A410" s="84"/>
+      <c r="A410" s="87"/>
       <c r="B410" s="71" t="s">
         <v>885</v>
       </c>
@@ -27415,7 +27415,7 @@
       </c>
     </row>
     <row r="411" spans="1:22" ht="13.8" hidden="1">
-      <c r="A411" s="84"/>
+      <c r="A411" s="87"/>
       <c r="B411" s="71" t="s">
         <v>885</v>
       </c>
@@ -27472,7 +27472,7 @@
       </c>
     </row>
     <row r="412" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="84">
+      <c r="A412" s="87">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27528,7 +27528,7 @@
       </c>
     </row>
     <row r="413" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="84"/>
+      <c r="A413" s="87"/>
       <c r="B413" s="71" t="s">
         <v>890</v>
       </c>
@@ -27589,7 +27589,7 @@
       </c>
     </row>
     <row r="414" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="84"/>
+      <c r="A414" s="87"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27613,7 +27613,7 @@
       <c r="V414" s="71"/>
     </row>
     <row r="415" spans="1:22" ht="55.2" hidden="1">
-      <c r="A415" s="84"/>
+      <c r="A415" s="87"/>
       <c r="B415" s="71" t="s">
         <v>890</v>
       </c>
@@ -27667,7 +27667,7 @@
       </c>
     </row>
     <row r="416" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A416" s="84"/>
+      <c r="A416" s="87"/>
       <c r="B416" s="71" t="s">
         <v>890</v>
       </c>
@@ -27723,7 +27723,7 @@
       </c>
     </row>
     <row r="417" spans="1:22" ht="41.4" hidden="1">
-      <c r="A417" s="84">
+      <c r="A417" s="87">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27779,7 +27779,7 @@
       </c>
     </row>
     <row r="418" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A418" s="84"/>
+      <c r="A418" s="87"/>
       <c r="B418" s="71" t="s">
         <v>897</v>
       </c>
@@ -27827,7 +27827,7 @@
       </c>
     </row>
     <row r="419" spans="1:22" ht="13.8" hidden="1">
-      <c r="A419" s="84"/>
+      <c r="A419" s="87"/>
       <c r="B419" s="71" t="s">
         <v>897</v>
       </c>
@@ -27884,7 +27884,7 @@
       </c>
     </row>
     <row r="420" spans="1:22" ht="13.8" hidden="1">
-      <c r="A420" s="84"/>
+      <c r="A420" s="87"/>
       <c r="B420" s="71" t="s">
         <v>897</v>
       </c>
@@ -27941,7 +27941,7 @@
       </c>
     </row>
     <row r="421" spans="1:22" ht="13.8" hidden="1">
-      <c r="A421" s="84"/>
+      <c r="A421" s="87"/>
       <c r="B421" s="71" t="s">
         <v>897</v>
       </c>
@@ -27998,7 +27998,7 @@
       </c>
     </row>
     <row r="422" spans="1:22" ht="27.6" hidden="1">
-      <c r="A422" s="84"/>
+      <c r="A422" s="87"/>
       <c r="B422" s="71" t="s">
         <v>897</v>
       </c>
@@ -28042,7 +28042,7 @@
       </c>
     </row>
     <row r="423" spans="1:22" ht="13.8" hidden="1">
-      <c r="A423" s="84"/>
+      <c r="A423" s="87"/>
       <c r="B423" s="71" t="s">
         <v>897</v>
       </c>
@@ -28093,7 +28093,7 @@
       </c>
     </row>
     <row r="424" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A424" s="84"/>
+      <c r="A424" s="87"/>
       <c r="B424" s="71" t="s">
         <v>897</v>
       </c>
@@ -28252,7 +28252,7 @@
       </c>
     </row>
     <row r="427" spans="1:22" ht="41.4" hidden="1">
-      <c r="A427" s="84">
+      <c r="A427" s="87">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -28310,7 +28310,7 @@
       </c>
     </row>
     <row r="428" spans="1:22" ht="13.8" hidden="1">
-      <c r="A428" s="84"/>
+      <c r="A428" s="87"/>
       <c r="B428" s="71" t="s">
         <v>914</v>
       </c>
@@ -28365,7 +28365,7 @@
       <c r="V428" s="71"/>
     </row>
     <row r="429" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="84"/>
+      <c r="A429" s="87"/>
       <c r="B429" s="71" t="s">
         <v>914</v>
       </c>
@@ -28418,7 +28418,7 @@
       </c>
     </row>
     <row r="430" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="84"/>
+      <c r="A430" s="87"/>
       <c r="B430" s="71" t="s">
         <v>913</v>
       </c>
@@ -28471,7 +28471,7 @@
       </c>
     </row>
     <row r="431" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A431" s="84"/>
+      <c r="A431" s="87"/>
       <c r="B431" s="71" t="s">
         <v>913</v>
       </c>
@@ -28524,7 +28524,7 @@
       </c>
     </row>
     <row r="432" spans="1:22" ht="13.8" hidden="1">
-      <c r="A432" s="84"/>
+      <c r="A432" s="87"/>
       <c r="B432" s="71" t="s">
         <v>914</v>
       </c>
@@ -28579,7 +28579,7 @@
       <c r="V432" s="71"/>
     </row>
     <row r="433" spans="1:22" ht="13.8" hidden="1">
-      <c r="A433" s="84"/>
+      <c r="A433" s="87"/>
       <c r="B433" s="71" t="s">
         <v>913</v>
       </c>
@@ -28634,7 +28634,7 @@
       <c r="V433" s="66"/>
     </row>
     <row r="434" spans="1:22" ht="27.6" hidden="1">
-      <c r="A434" s="85"/>
+      <c r="A434" s="98"/>
       <c r="B434" s="71" t="s">
         <v>925</v>
       </c>
@@ -28656,38 +28656,38 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="87">
+      <c r="K434" s="91">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="87">
+      <c r="L434" s="91">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="87">
+      <c r="M434" s="91">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="89" t="s">
+      <c r="N434" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="O434" s="89" t="s">
+      <c r="O434" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="P434" s="84">
+      <c r="P434" s="87">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
       <c r="T434" s="66"/>
-      <c r="U434" s="88">
+      <c r="U434" s="105">
         <v>0.65</v>
       </c>
-      <c r="V434" s="84" t="s">
+      <c r="V434" s="87" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="435" spans="1:22" ht="27.6" hidden="1">
-      <c r="A435" s="85"/>
+      <c r="A435" s="98"/>
       <c r="B435" s="71" t="s">
         <v>925</v>
       </c>
@@ -28709,21 +28709,21 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="87"/>
-      <c r="L435" s="87"/>
-      <c r="M435" s="87"/>
-      <c r="N435" s="89"/>
-      <c r="O435" s="89"/>
-      <c r="P435" s="84"/>
+      <c r="K435" s="91"/>
+      <c r="L435" s="91"/>
+      <c r="M435" s="91"/>
+      <c r="N435" s="88"/>
+      <c r="O435" s="88"/>
+      <c r="P435" s="87"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
       <c r="T435" s="66"/>
-      <c r="U435" s="88"/>
-      <c r="V435" s="84"/>
+      <c r="U435" s="105"/>
+      <c r="V435" s="87"/>
     </row>
     <row r="436" spans="1:22" ht="13.8" hidden="1">
-      <c r="A436" s="85"/>
+      <c r="A436" s="98"/>
       <c r="B436" s="71" t="s">
         <v>925</v>
       </c>
@@ -28778,7 +28778,7 @@
       </c>
     </row>
     <row r="437" spans="1:22" ht="13.8" hidden="1">
-      <c r="A437" s="85"/>
+      <c r="A437" s="98"/>
       <c r="B437" s="71" t="s">
         <v>929</v>
       </c>
@@ -28833,7 +28833,7 @@
       </c>
     </row>
     <row r="438" spans="1:22" ht="13.8" hidden="1">
-      <c r="A438" s="85"/>
+      <c r="A438" s="98"/>
       <c r="B438" s="71" t="s">
         <v>925</v>
       </c>
@@ -28886,7 +28886,7 @@
       </c>
     </row>
     <row r="439" spans="1:22" ht="27.6" hidden="1">
-      <c r="A439" s="86"/>
+      <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
         <v>925</v>
       </c>
@@ -28940,7 +28940,7 @@
       </c>
     </row>
     <row r="440" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="90">
+      <c r="A440" s="93">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28995,7 +28995,7 @@
       </c>
     </row>
     <row r="441" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="85"/>
+      <c r="A441" s="98"/>
       <c r="B441" s="71" t="s">
         <v>937</v>
       </c>
@@ -29047,7 +29047,7 @@
       </c>
     </row>
     <row r="442" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="85"/>
+      <c r="A442" s="98"/>
       <c r="B442" s="71" t="s">
         <v>937</v>
       </c>
@@ -29103,7 +29103,7 @@
       </c>
     </row>
     <row r="443" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="85"/>
+      <c r="A443" s="98"/>
       <c r="B443" s="71" t="s">
         <v>937</v>
       </c>
@@ -29158,7 +29158,7 @@
       </c>
     </row>
     <row r="444" spans="1:22" ht="64.95" hidden="1" customHeight="1">
-      <c r="A444" s="85"/>
+      <c r="A444" s="98"/>
       <c r="B444" s="71" t="s">
         <v>937</v>
       </c>
@@ -29211,7 +29211,7 @@
       </c>
     </row>
     <row r="445" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="85"/>
+      <c r="A445" s="98"/>
       <c r="B445" s="71" t="s">
         <v>937</v>
       </c>
@@ -29262,7 +29262,7 @@
       </c>
     </row>
     <row r="446" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="85"/>
+      <c r="A446" s="98"/>
       <c r="B446" s="71" t="s">
         <v>937</v>
       </c>
@@ -29300,7 +29300,7 @@
       <c r="V446" s="71"/>
     </row>
     <row r="447" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="86"/>
+      <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
         <v>937</v>
       </c>
@@ -29355,7 +29355,7 @@
       <c r="V447" s="44"/>
     </row>
     <row r="448" spans="1:22" ht="27.6" hidden="1">
-      <c r="A448" s="84"/>
+      <c r="A448" s="87"/>
       <c r="B448" s="71" t="s">
         <v>947</v>
       </c>
@@ -29412,7 +29412,7 @@
       </c>
     </row>
     <row r="449" spans="1:22" ht="41.4" hidden="1">
-      <c r="A449" s="84"/>
+      <c r="A449" s="87"/>
       <c r="B449" s="51" t="s">
         <v>947</v>
       </c>
@@ -29473,7 +29473,7 @@
       </c>
     </row>
     <row r="450" spans="1:22" ht="27.6" hidden="1">
-      <c r="A450" s="90">
+      <c r="A450" s="93">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29530,7 +29530,7 @@
       </c>
     </row>
     <row r="451" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="85"/>
+      <c r="A451" s="98"/>
       <c r="B451" s="71" t="s">
         <v>954</v>
       </c>
@@ -29585,7 +29585,7 @@
       </c>
     </row>
     <row r="452" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="85"/>
+      <c r="A452" s="98"/>
       <c r="B452" s="71" t="s">
         <v>954</v>
       </c>
@@ -29644,7 +29644,7 @@
       </c>
     </row>
     <row r="453" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="86"/>
+      <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
         <v>954</v>
       </c>
@@ -29699,7 +29699,7 @@
       </c>
     </row>
     <row r="454" spans="1:22" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="84">
+      <c r="A454" s="87">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29761,7 +29761,7 @@
       </c>
     </row>
     <row r="455" spans="1:22" ht="13.8" hidden="1">
-      <c r="A455" s="84"/>
+      <c r="A455" s="87"/>
       <c r="B455" s="71" t="s">
         <v>961</v>
       </c>
@@ -29817,7 +29817,7 @@
       <c r="V455" s="71"/>
     </row>
     <row r="456" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="84"/>
+      <c r="A456" s="87"/>
       <c r="B456" s="71" t="s">
         <v>961</v>
       </c>
@@ -29875,7 +29875,7 @@
       <c r="V456" s="71"/>
     </row>
     <row r="457" spans="1:22" ht="27.6" hidden="1">
-      <c r="A457" s="84">
+      <c r="A457" s="87">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29929,7 +29929,7 @@
       </c>
     </row>
     <row r="458" spans="1:22" ht="13.8" hidden="1">
-      <c r="A458" s="84"/>
+      <c r="A458" s="87"/>
       <c r="B458" s="71" t="s">
         <v>965</v>
       </c>
@@ -29983,7 +29983,7 @@
       </c>
     </row>
     <row r="459" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A459" s="84"/>
+      <c r="A459" s="87"/>
       <c r="B459" s="71" t="s">
         <v>965</v>
       </c>
@@ -30038,7 +30038,7 @@
       <c r="V459" s="66"/>
     </row>
     <row r="460" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A460" s="84"/>
+      <c r="A460" s="87"/>
       <c r="B460" s="71" t="s">
         <v>965</v>
       </c>
@@ -30087,7 +30087,7 @@
       <c r="V460" s="66"/>
     </row>
     <row r="461" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="84"/>
+      <c r="A461" s="87"/>
       <c r="B461" s="71" t="s">
         <v>965</v>
       </c>
@@ -30475,7 +30475,7 @@
       </c>
     </row>
     <row r="468" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="85"/>
+      <c r="A468" s="98"/>
       <c r="B468" s="71" t="s">
         <v>982</v>
       </c>
@@ -30527,7 +30527,7 @@
       </c>
     </row>
     <row r="469" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="85"/>
+      <c r="A469" s="98"/>
       <c r="B469" s="71" t="s">
         <v>327</v>
       </c>
@@ -30582,7 +30582,7 @@
       <c r="V469" s="71"/>
     </row>
     <row r="470" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="85"/>
+      <c r="A470" s="98"/>
       <c r="B470" s="71" t="s">
         <v>327</v>
       </c>
@@ -30637,7 +30637,7 @@
       <c r="V470" s="71"/>
     </row>
     <row r="471" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="85"/>
+      <c r="A471" s="98"/>
       <c r="B471" s="71" t="s">
         <v>327</v>
       </c>
@@ -30692,7 +30692,7 @@
       <c r="V471" s="71"/>
     </row>
     <row r="472" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="85"/>
+      <c r="A472" s="98"/>
       <c r="B472" s="71" t="s">
         <v>327</v>
       </c>
@@ -30749,7 +30749,7 @@
       </c>
     </row>
     <row r="473" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="85"/>
+      <c r="A473" s="98"/>
       <c r="B473" s="71" t="s">
         <v>327</v>
       </c>
@@ -30802,7 +30802,7 @@
       </c>
     </row>
     <row r="474" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="86"/>
+      <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
         <v>982</v>
       </c>
@@ -30853,7 +30853,7 @@
       </c>
     </row>
     <row r="475" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="84">
+      <c r="A475" s="87">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30865,7 +30865,7 @@
       <c r="D475" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E475" s="104">
+      <c r="E475" s="90">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30879,14 +30879,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="105">
+      <c r="K475" s="92">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="105">
+      <c r="L475" s="92">
         <v>0</v>
       </c>
-      <c r="M475" s="87">
+      <c r="M475" s="91">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30905,12 +30905,12 @@
       <c r="S475" s="66"/>
       <c r="T475" s="66"/>
       <c r="U475" s="71"/>
-      <c r="V475" s="89" t="s">
+      <c r="V475" s="88" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="476" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="84"/>
+      <c r="A476" s="87"/>
       <c r="B476" s="71" t="s">
         <v>994</v>
       </c>
@@ -30920,7 +30920,7 @@
       <c r="D476" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E476" s="104"/>
+      <c r="E476" s="90"/>
       <c r="F476" s="71" t="s">
         <v>177</v>
       </c>
@@ -30932,9 +30932,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="105"/>
-      <c r="L476" s="105"/>
-      <c r="M476" s="87"/>
+      <c r="K476" s="92"/>
+      <c r="L476" s="92"/>
+      <c r="M476" s="91"/>
       <c r="N476" s="71" t="s">
         <v>38</v>
       </c>
@@ -30951,10 +30951,10 @@
       <c r="S476" s="66"/>
       <c r="T476" s="66"/>
       <c r="U476" s="71"/>
-      <c r="V476" s="89"/>
+      <c r="V476" s="88"/>
     </row>
     <row r="477" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="84"/>
+      <c r="A477" s="87"/>
       <c r="B477" s="71" t="s">
         <v>994</v>
       </c>
@@ -31013,7 +31013,7 @@
       </c>
     </row>
     <row r="478" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="84"/>
+      <c r="A478" s="87"/>
       <c r="B478" s="71" t="s">
         <v>994</v>
       </c>
@@ -31456,7 +31456,7 @@
       <c r="V485" s="66"/>
     </row>
     <row r="486" spans="1:22" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="84">
+      <c r="A486" s="87">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31513,7 +31513,7 @@
       <c r="V486" s="71"/>
     </row>
     <row r="487" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="84"/>
+      <c r="A487" s="87"/>
       <c r="B487" s="71" t="s">
         <v>1010</v>
       </c>
@@ -31566,7 +31566,7 @@
       </c>
     </row>
     <row r="488" spans="1:22" ht="96.6" hidden="1">
-      <c r="A488" s="84"/>
+      <c r="A488" s="87"/>
       <c r="B488" s="71" t="s">
         <v>1010</v>
       </c>
@@ -31733,7 +31733,7 @@
       <c r="V490" s="71"/>
     </row>
     <row r="491" spans="1:22" ht="13.8" hidden="1">
-      <c r="A491" s="85"/>
+      <c r="A491" s="98"/>
       <c r="B491" s="71" t="s">
         <v>1020</v>
       </c>
@@ -31788,7 +31788,7 @@
       <c r="V491" s="71"/>
     </row>
     <row r="492" spans="1:22" ht="13.8" hidden="1">
-      <c r="A492" s="85"/>
+      <c r="A492" s="98"/>
       <c r="B492" s="71" t="s">
         <v>1020</v>
       </c>
@@ -31843,7 +31843,7 @@
       <c r="V492" s="71"/>
     </row>
     <row r="493" spans="1:22" ht="55.2" hidden="1">
-      <c r="A493" s="85"/>
+      <c r="A493" s="98"/>
       <c r="B493" s="71" t="s">
         <v>1020</v>
       </c>
@@ -31895,7 +31895,7 @@
       </c>
     </row>
     <row r="494" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="86"/>
+      <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
         <v>1020</v>
       </c>
@@ -31950,7 +31950,7 @@
       <c r="V494" s="71"/>
     </row>
     <row r="495" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="84">
+      <c r="A495" s="87">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -32009,7 +32009,7 @@
       </c>
     </row>
     <row r="496" spans="1:22" ht="27.6" hidden="1">
-      <c r="A496" s="84"/>
+      <c r="A496" s="87"/>
       <c r="B496" s="71" t="s">
         <v>1027</v>
       </c>
@@ -32062,7 +32062,7 @@
       </c>
     </row>
     <row r="497" spans="1:22" ht="13.8" hidden="1">
-      <c r="A497" s="84"/>
+      <c r="A497" s="87"/>
       <c r="B497" s="71" t="s">
         <v>1027</v>
       </c>
@@ -32117,7 +32117,7 @@
       </c>
     </row>
     <row r="498" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A498" s="84"/>
+      <c r="A498" s="87"/>
       <c r="B498" s="71" t="s">
         <v>1033</v>
       </c>
@@ -32234,7 +32234,7 @@
       </c>
     </row>
     <row r="500" spans="1:22" ht="27.6" hidden="1">
-      <c r="A500" s="89">
+      <c r="A500" s="88">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -32296,7 +32296,7 @@
       </c>
     </row>
     <row r="501" spans="1:22" ht="13.8" hidden="1">
-      <c r="A501" s="89"/>
+      <c r="A501" s="88"/>
       <c r="B501" s="71" t="s">
         <v>1034</v>
       </c>
@@ -32348,7 +32348,7 @@
       <c r="V501" s="71"/>
     </row>
     <row r="502" spans="1:22" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="89"/>
+      <c r="A502" s="88"/>
       <c r="B502" s="71" t="s">
         <v>1034</v>
       </c>
@@ -32405,7 +32405,7 @@
       </c>
     </row>
     <row r="503" spans="1:22" ht="41.4" hidden="1">
-      <c r="A503" s="84">
+      <c r="A503" s="87">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -32468,7 +32468,7 @@
       </c>
     </row>
     <row r="504" spans="1:22" ht="13.8" hidden="1">
-      <c r="A504" s="84"/>
+      <c r="A504" s="87"/>
       <c r="B504" s="71" t="s">
         <v>1042</v>
       </c>
@@ -32527,7 +32527,7 @@
       <c r="V504" s="71"/>
     </row>
     <row r="505" spans="1:22" ht="55.2" hidden="1">
-      <c r="A505" s="84"/>
+      <c r="A505" s="87"/>
       <c r="B505" s="51" t="s">
         <v>1042</v>
       </c>
@@ -32600,11 +32600,11 @@
     <row r="508" spans="1:22" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>56.15</v>
+        <v>24.185000000000002</v>
       </c>
       <c r="K508" s="8">
         <f>SUBTOTAL(9,K96:K507)</f>
-        <v>70456905098.699997</v>
+        <v>54029783587.699997</v>
       </c>
       <c r="M508" s="58"/>
       <c r="U508" s="29"/>
@@ -32662,88 +32662,47 @@
   <autoFilter ref="A2:V507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="San Roque"/>
+        <filter val="Salgar"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="V91:V92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="V475:V476"/>
-    <mergeCell ref="V434:V435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="A319:A320"/>
+    <mergeCell ref="A321:A330"/>
+    <mergeCell ref="A335:A338"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="A342:A348"/>
+    <mergeCell ref="A503:A505"/>
+    <mergeCell ref="A468:A474"/>
+    <mergeCell ref="A475:A478"/>
+    <mergeCell ref="A486:A488"/>
+    <mergeCell ref="A491:A494"/>
+    <mergeCell ref="A495:A498"/>
+    <mergeCell ref="A500:A502"/>
+    <mergeCell ref="A440:A447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="A450:A453"/>
+    <mergeCell ref="A454:A456"/>
+    <mergeCell ref="A457:A461"/>
+    <mergeCell ref="A349:A351"/>
+    <mergeCell ref="A352:A357"/>
+    <mergeCell ref="A363:A364"/>
+    <mergeCell ref="A368:A372"/>
+    <mergeCell ref="A373:A384"/>
+    <mergeCell ref="A385:A392"/>
+    <mergeCell ref="A394:A399"/>
     <mergeCell ref="A400:A405"/>
     <mergeCell ref="A406:A407"/>
     <mergeCell ref="P310:P311"/>
@@ -32768,42 +32727,83 @@
     <mergeCell ref="P312:P313"/>
     <mergeCell ref="V312:V313"/>
     <mergeCell ref="U312:U313"/>
-    <mergeCell ref="A319:A320"/>
-    <mergeCell ref="A321:A330"/>
-    <mergeCell ref="A335:A338"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="A342:A348"/>
-    <mergeCell ref="A503:A505"/>
-    <mergeCell ref="A468:A474"/>
-    <mergeCell ref="A475:A478"/>
-    <mergeCell ref="A486:A488"/>
-    <mergeCell ref="A491:A494"/>
-    <mergeCell ref="A495:A498"/>
-    <mergeCell ref="A500:A502"/>
-    <mergeCell ref="A440:A447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="A450:A453"/>
-    <mergeCell ref="A454:A456"/>
-    <mergeCell ref="A457:A461"/>
-    <mergeCell ref="A349:A351"/>
-    <mergeCell ref="A352:A357"/>
-    <mergeCell ref="A363:A364"/>
-    <mergeCell ref="A368:A372"/>
-    <mergeCell ref="A373:A384"/>
-    <mergeCell ref="A385:A392"/>
-    <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="V91:V92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="V475:V476"/>
+    <mergeCell ref="V434:V435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -33200,20 +33200,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -33235,14 +33235,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -33250,4 +33242,12 @@
     <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB298789-C642-4CD5-856D-28E610491063}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9504531B-B8C7-4BD4-9A8C-BCB37249954E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3319,6 +3316,9 @@
 San Roque: L= 21,33 km</t>
   </si>
   <si>
+    <t xml:space="preserve">Actividades preliminares </t>
+  </si>
+  <si>
     <t>San Rafael - San Roque  
 Santo Domingo - 
 Alejandría: L=25,72 km</t>
@@ -4015,23 +4015,20 @@
   <si>
     <t>NORTE</t>
   </si>
-  <si>
-    <t xml:space="preserve">Actividades preliminares </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -4250,7 +4247,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="107">
@@ -4258,34 +4255,34 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4299,42 +4296,42 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4358,7 +4355,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4367,13 +4364,13 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4385,7 +4382,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4394,7 +4391,7 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4406,25 +4403,25 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4436,10 +4433,10 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4451,7 +4448,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4481,7 +4478,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4490,19 +4487,19 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4517,10 +4514,10 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4591,9 +4588,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4631,7 +4628,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4737,7 +4734,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4879,7 +4876,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4889,36 +4886,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X521"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="33" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" style="55" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="49.109375" style="33" customWidth="1"/>
-    <col min="7" max="7" width="48.33203125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" style="33" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="25.88671875" style="56" customWidth="1"/>
-    <col min="13" max="13" width="24.33203125" style="33" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="33" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="55" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="49.140625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="48.28515625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="33" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" style="33" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="25.85546875" style="56" customWidth="1"/>
+    <col min="13" max="13" width="24.28515625" style="33" customWidth="1"/>
     <col min="14" max="14" width="26" style="33" customWidth="1"/>
-    <col min="15" max="15" width="32.5546875" style="33" customWidth="1"/>
-    <col min="16" max="16" width="19.109375" style="33" customWidth="1"/>
-    <col min="17" max="17" width="20.5546875" style="33" customWidth="1"/>
-    <col min="18" max="18" width="20.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="29.33203125" style="33" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="29.109375" style="33" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="19.109375" style="59" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="39.5546875" style="33" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="24.33203125" style="33" customWidth="1"/>
-    <col min="25" max="16384" width="10.88671875" style="33"/>
+    <col min="15" max="15" width="32.5703125" style="33" customWidth="1"/>
+    <col min="16" max="16" width="19.140625" style="33" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" style="33" customWidth="1"/>
+    <col min="18" max="18" width="20.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="29.28515625" style="33" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="29.140625" style="33" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" style="59" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="39.5703125" style="33" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" style="29" customWidth="1"/>
+    <col min="24" max="24" width="24.28515625" style="33" customWidth="1"/>
+    <col min="25" max="16384" width="10.85546875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="13.8" hidden="1">
+    <row r="1" spans="1:24" ht="13.9" hidden="1">
       <c r="B1" s="97" t="s">
         <v>0</v>
       </c>
@@ -4943,7 +4940,7 @@
       <c r="U1" s="78"/>
       <c r="V1" s="73"/>
     </row>
-    <row r="2" spans="1:24" ht="13.8">
+    <row r="2" spans="1:24" ht="21.75">
       <c r="A2" s="75"/>
       <c r="B2" s="35" t="s">
         <v>1</v>
@@ -5010,7 +5007,7 @@
       </c>
       <c r="X2" s="13"/>
     </row>
-    <row r="3" spans="1:24" ht="62.4" hidden="1" customHeight="1">
+    <row r="3" spans="1:24" ht="62.45" hidden="1" customHeight="1">
       <c r="A3" s="94">
         <v>1</v>
       </c>
@@ -5074,7 +5071,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="62.4" hidden="1" customHeight="1">
+    <row r="4" spans="1:24" ht="62.45" hidden="1" customHeight="1">
       <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>22</v>
@@ -5136,7 +5133,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="41.4" hidden="1">
+    <row r="5" spans="1:24" ht="41.45" hidden="1">
       <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>22</v>
@@ -5246,7 +5243,7 @@
       </c>
       <c r="V6" s="66"/>
     </row>
-    <row r="7" spans="1:24" ht="13.8" hidden="1">
+    <row r="7" spans="1:24" ht="13.9" hidden="1">
       <c r="A7" s="93">
         <v>2</v>
       </c>
@@ -5282,7 +5279,7 @@
       <c r="U7" s="66"/>
       <c r="V7" s="66"/>
     </row>
-    <row r="8" spans="1:24" ht="13.8" hidden="1">
+    <row r="8" spans="1:24" ht="13.9" hidden="1">
       <c r="A8" s="98"/>
       <c r="B8" s="71" t="s">
         <v>41</v>
@@ -5335,7 +5332,7 @@
       </c>
       <c r="V8" s="66"/>
     </row>
-    <row r="9" spans="1:24" ht="41.4" hidden="1">
+    <row r="9" spans="1:24" ht="41.45" hidden="1">
       <c r="A9" s="98"/>
       <c r="B9" s="71" t="s">
         <v>41</v>
@@ -5394,7 +5391,7 @@
       </c>
       <c r="V9" s="66"/>
     </row>
-    <row r="10" spans="1:24" ht="41.4" hidden="1">
+    <row r="10" spans="1:24" ht="41.45" hidden="1">
       <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>41</v>
@@ -5517,7 +5514,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="52.95" hidden="1" customHeight="1">
+    <row r="12" spans="1:24" ht="52.9" hidden="1" customHeight="1">
       <c r="A12" s="87"/>
       <c r="B12" s="71" t="s">
         <v>59</v>
@@ -5574,7 +5571,7 @@
       </c>
       <c r="V12" s="76"/>
     </row>
-    <row r="13" spans="1:24" ht="13.8" hidden="1">
+    <row r="13" spans="1:24" ht="13.9" hidden="1">
       <c r="A13" s="87"/>
       <c r="B13" s="71" t="s">
         <v>59</v>
@@ -5631,7 +5628,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="13.8" hidden="1">
+    <row r="14" spans="1:24" ht="13.9" hidden="1">
       <c r="A14" s="87"/>
       <c r="B14" s="71" t="s">
         <v>59</v>
@@ -5688,7 +5685,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="13.8" hidden="1">
+    <row r="15" spans="1:24" ht="13.9" hidden="1">
       <c r="A15" s="87"/>
       <c r="B15" s="71" t="s">
         <v>59</v>
@@ -5802,7 +5799,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="13.8" hidden="1">
+    <row r="17" spans="1:22" ht="13.9" hidden="1">
       <c r="A17" s="66"/>
       <c r="B17" s="71" t="s">
         <v>85</v>
@@ -5844,7 +5841,7 @@
       <c r="U17" s="80"/>
       <c r="V17" s="71"/>
     </row>
-    <row r="18" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="18" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A18" s="66">
         <v>4</v>
       </c>
@@ -5905,7 +5902,7 @@
       </c>
       <c r="V18" s="71"/>
     </row>
-    <row r="19" spans="1:22" ht="41.4" hidden="1">
+    <row r="19" spans="1:22" ht="41.45" hidden="1">
       <c r="A19" s="66"/>
       <c r="B19" s="71" t="s">
         <v>92</v>
@@ -5966,7 +5963,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="97.95" hidden="1" customHeight="1">
+    <row r="20" spans="1:22" ht="97.9" hidden="1" customHeight="1">
       <c r="A20" s="87">
         <v>5</v>
       </c>
@@ -6029,7 +6026,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="21" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A21" s="87"/>
       <c r="B21" s="71" t="s">
         <v>92</v>
@@ -6148,7 +6145,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="13.8" hidden="1">
+    <row r="23" spans="1:22" ht="13.9" hidden="1">
       <c r="A23" s="87"/>
       <c r="B23" s="71" t="s">
         <v>92</v>
@@ -6268,7 +6265,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="13.8" hidden="1">
+    <row r="25" spans="1:22" ht="13.9" hidden="1">
       <c r="A25" s="87"/>
       <c r="B25" s="71" t="s">
         <v>109</v>
@@ -6325,7 +6322,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="70.2" hidden="1" customHeight="1">
+    <row r="26" spans="1:22" ht="70.150000000000006" hidden="1" customHeight="1">
       <c r="A26" s="87"/>
       <c r="B26" s="71" t="s">
         <v>109</v>
@@ -6382,7 +6379,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="27" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A27" s="87"/>
       <c r="B27" s="71" t="s">
         <v>109</v>
@@ -6441,7 +6438,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="13.8" hidden="1">
+    <row r="28" spans="1:22" ht="13.9" hidden="1">
       <c r="A28" s="87"/>
       <c r="B28" s="71" t="s">
         <v>109</v>
@@ -6553,7 +6550,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="30" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A30" s="87"/>
       <c r="B30" s="71" t="s">
         <v>109</v>
@@ -6606,7 +6603,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="31" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A31" s="87"/>
       <c r="B31" s="71" t="s">
         <v>109</v>
@@ -6665,7 +6662,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="32" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A32" s="87"/>
       <c r="B32" s="71" t="s">
         <v>109</v>
@@ -6726,7 +6723,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="33" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A33" s="87"/>
       <c r="B33" s="71" t="s">
         <v>109</v>
@@ -6783,7 +6780,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="34" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A34" s="87"/>
       <c r="B34" s="71" t="s">
         <v>109</v>
@@ -6844,7 +6841,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="13.8" hidden="1">
+    <row r="35" spans="1:22" ht="13.9" hidden="1">
       <c r="A35" s="98"/>
       <c r="B35" s="71" t="s">
         <v>147</v>
@@ -6880,7 +6877,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="71"/>
     </row>
-    <row r="36" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="36" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>147</v>
@@ -6994,7 +6991,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="38" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A38" s="87">
         <v>8</v>
       </c>
@@ -7056,7 +7053,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="39" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A39" s="87"/>
       <c r="B39" s="71" t="s">
         <v>150</v>
@@ -7117,7 +7114,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="40" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A40" s="87"/>
       <c r="B40" s="71" t="s">
         <v>150</v>
@@ -7175,7 +7172,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="41" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A41" s="87">
         <v>9</v>
       </c>
@@ -7236,7 +7233,7 @@
       </c>
       <c r="V41" s="71"/>
     </row>
-    <row r="42" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="42" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A42" s="87"/>
       <c r="B42" s="71" t="s">
         <v>160</v>
@@ -7444,7 +7441,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="46" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A46" s="87">
         <v>10</v>
       </c>
@@ -7501,7 +7498,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="13.8" hidden="1">
+    <row r="47" spans="1:22" ht="13.9" hidden="1">
       <c r="A47" s="93"/>
       <c r="B47" s="71" t="s">
         <v>175</v>
@@ -7556,7 +7553,7 @@
       </c>
       <c r="V47" s="71"/>
     </row>
-    <row r="48" spans="1:22" ht="13.8" hidden="1">
+    <row r="48" spans="1:22" ht="13.9" hidden="1">
       <c r="A48" s="87"/>
       <c r="B48" s="71" t="s">
         <v>182</v>
@@ -7592,7 +7589,7 @@
       <c r="U48" s="80"/>
       <c r="V48" s="71"/>
     </row>
-    <row r="49" spans="1:22" ht="13.8" hidden="1">
+    <row r="49" spans="1:22" ht="13.9" hidden="1">
       <c r="A49" s="87"/>
       <c r="B49" s="71" t="s">
         <v>182</v>
@@ -7632,7 +7629,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="13.8" hidden="1">
+    <row r="50" spans="1:22" ht="13.9" hidden="1">
       <c r="A50" s="87"/>
       <c r="B50" s="71" t="s">
         <v>182</v>
@@ -7687,7 +7684,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="55.2" hidden="1">
+    <row r="51" spans="1:22" ht="55.15" hidden="1">
       <c r="A51" s="87"/>
       <c r="B51" s="71" t="s">
         <v>182</v>
@@ -7742,7 +7739,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="41.4" hidden="1">
+    <row r="52" spans="1:22" ht="41.45" hidden="1">
       <c r="A52" s="87"/>
       <c r="B52" s="71" t="s">
         <v>182</v>
@@ -7852,7 +7849,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="54" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A54" s="87"/>
       <c r="B54" s="71" t="s">
         <v>197</v>
@@ -7906,7 +7903,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="55" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A55" s="87"/>
       <c r="B55" s="71" t="s">
         <v>197</v>
@@ -7961,7 +7958,7 @@
       </c>
       <c r="V55" s="66"/>
     </row>
-    <row r="56" spans="1:22" ht="41.4" hidden="1">
+    <row r="56" spans="1:22" ht="41.45" hidden="1">
       <c r="A56" s="87"/>
       <c r="B56" s="71" t="s">
         <v>197</v>
@@ -8020,7 +8017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="57" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A57" s="87"/>
       <c r="B57" s="71" t="s">
         <v>197</v>
@@ -8077,7 +8074,7 @@
       </c>
       <c r="V57" s="71"/>
     </row>
-    <row r="58" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+    <row r="58" spans="1:22" ht="34.15" hidden="1" customHeight="1">
       <c r="A58" s="87"/>
       <c r="B58" s="71" t="s">
         <v>197</v>
@@ -8137,7 +8134,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="59" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>209</v>
@@ -8194,7 +8191,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="60" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>209</v>
@@ -8250,7 +8247,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="41.4" hidden="1">
+    <row r="61" spans="1:22" ht="41.45" hidden="1">
       <c r="A61" s="87"/>
       <c r="B61" s="61" t="s">
         <v>209</v>
@@ -8640,7 +8637,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="68" spans="1:22" ht="13.8" hidden="1">
+    <row r="68" spans="1:22" ht="13.9" hidden="1">
       <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>230</v>
@@ -8749,7 +8746,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="41.4" hidden="1">
+    <row r="70" spans="1:22" ht="41.45" hidden="1">
       <c r="A70" s="98"/>
       <c r="B70" s="71" t="s">
         <v>236</v>
@@ -8804,7 +8801,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="67.95" hidden="1" customHeight="1">
+    <row r="71" spans="1:22" ht="67.900000000000006" hidden="1" customHeight="1">
       <c r="A71" s="98"/>
       <c r="B71" s="71" t="s">
         <v>242</v>
@@ -8915,7 +8912,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="73" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A73" s="98"/>
       <c r="B73" s="71" t="s">
         <v>245</v>
@@ -8968,7 +8965,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="74" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A74" s="98"/>
       <c r="B74" s="71" t="s">
         <v>245</v>
@@ -9023,7 +9020,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="75" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A75" s="98"/>
       <c r="B75" s="71" t="s">
         <v>245</v>
@@ -9084,7 +9081,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="76" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A76" s="98"/>
       <c r="B76" s="71" t="s">
         <v>245</v>
@@ -9137,7 +9134,7 @@
       <c r="U76" s="70"/>
       <c r="V76" s="71"/>
     </row>
-    <row r="77" spans="1:22" ht="13.8" hidden="1">
+    <row r="77" spans="1:22" ht="13.9" hidden="1">
       <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>245</v>
@@ -9194,7 +9191,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="78" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A78" s="98"/>
       <c r="B78" s="71" t="s">
         <v>256</v>
@@ -9255,7 +9252,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="13.8" hidden="1">
+    <row r="79" spans="1:22" ht="13.9" hidden="1">
       <c r="A79" s="98"/>
       <c r="B79" s="71" t="s">
         <v>256</v>
@@ -9310,7 +9307,7 @@
       </c>
       <c r="V79" s="66"/>
     </row>
-    <row r="80" spans="1:22" ht="13.8" hidden="1">
+    <row r="80" spans="1:22" ht="13.9" hidden="1">
       <c r="A80" s="98"/>
       <c r="B80" s="71" t="s">
         <v>256</v>
@@ -9421,7 +9418,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="82" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A82" s="98"/>
       <c r="B82" s="71" t="s">
         <v>265</v>
@@ -9479,7 +9476,7 @@
       </c>
       <c r="W82" s="33"/>
     </row>
-    <row r="83" spans="1:23" ht="38.4" hidden="1" customHeight="1">
+    <row r="83" spans="1:23" ht="38.450000000000003" hidden="1" customHeight="1">
       <c r="A83" s="98"/>
       <c r="B83" s="71" t="s">
         <v>265</v>
@@ -9589,7 +9586,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="55.2" hidden="1">
+    <row r="85" spans="1:23" ht="55.15" hidden="1">
       <c r="A85" s="98"/>
       <c r="B85" s="71" t="s">
         <v>265</v>
@@ -9643,7 +9640,7 @@
       </c>
       <c r="W85" s="33"/>
     </row>
-    <row r="86" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="86" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A86" s="98"/>
       <c r="B86" s="71" t="s">
         <v>265</v>
@@ -9701,7 +9698,7 @@
       </c>
       <c r="W86" s="33"/>
     </row>
-    <row r="87" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="87" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A87" s="98"/>
       <c r="B87" s="71" t="s">
         <v>265</v>
@@ -9759,7 +9756,7 @@
       </c>
       <c r="W87" s="33"/>
     </row>
-    <row r="88" spans="1:23" ht="13.8" hidden="1">
+    <row r="88" spans="1:23" ht="13.9" hidden="1">
       <c r="A88" s="98"/>
       <c r="B88" s="71" t="s">
         <v>265</v>
@@ -9817,7 +9814,7 @@
       </c>
       <c r="W88" s="33"/>
     </row>
-    <row r="89" spans="1:23" ht="13.8" hidden="1">
+    <row r="89" spans="1:23" ht="13.9" hidden="1">
       <c r="A89" s="98"/>
       <c r="B89" s="71" t="s">
         <v>265</v>
@@ -9923,7 +9920,7 @@
       </c>
       <c r="W90" s="33"/>
     </row>
-    <row r="91" spans="1:23" ht="43.95" hidden="1" customHeight="1">
+    <row r="91" spans="1:23" ht="43.9" hidden="1" customHeight="1">
       <c r="A91" s="98"/>
       <c r="B91" s="71" t="s">
         <v>285</v>
@@ -9976,7 +9973,7 @@
       </c>
       <c r="W91" s="33"/>
     </row>
-    <row r="92" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="92" spans="1:23" ht="40.9" hidden="1" customHeight="1">
       <c r="A92" s="98"/>
       <c r="B92" s="71" t="s">
         <v>285</v>
@@ -10112,7 +10109,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="95" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A95" s="98"/>
       <c r="B95" s="71" t="s">
         <v>285</v>
@@ -10162,7 +10159,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="96" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A96" s="98"/>
       <c r="B96" s="71" t="s">
         <v>293</v>
@@ -10196,7 +10193,7 @@
       <c r="U96" s="70"/>
       <c r="V96" s="66"/>
     </row>
-    <row r="97" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="97" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A97" s="98"/>
       <c r="B97" s="71" t="s">
         <v>293</v>
@@ -10302,7 +10299,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="99" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
+    <row r="99" spans="1:22" ht="17.45" hidden="1" customHeight="1">
       <c r="A99" s="98"/>
       <c r="B99" s="71" t="s">
         <v>302</v>
@@ -10352,7 +10349,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
+    <row r="100" spans="1:22" ht="17.45" hidden="1" customHeight="1">
       <c r="A100" s="98"/>
       <c r="B100" s="71" t="s">
         <v>302</v>
@@ -10402,7 +10399,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+    <row r="101" spans="1:22" ht="53.45" hidden="1" customHeight="1">
       <c r="A101" s="98"/>
       <c r="B101" s="71" t="s">
         <v>302</v>
@@ -10452,7 +10449,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+    <row r="102" spans="1:22" ht="53.45" hidden="1" customHeight="1">
       <c r="A102" s="98"/>
       <c r="B102" s="71" t="s">
         <v>302</v>
@@ -10509,7 +10506,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+    <row r="103" spans="1:22" ht="53.45" hidden="1" customHeight="1">
       <c r="A103" s="98"/>
       <c r="B103" s="71" t="s">
         <v>302</v>
@@ -10561,7 +10558,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+    <row r="104" spans="1:22" ht="53.45" hidden="1" customHeight="1">
       <c r="A104" s="98"/>
       <c r="B104" s="71" t="s">
         <v>302</v>
@@ -10614,7 +10611,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="105" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+    <row r="105" spans="1:22" ht="53.45" hidden="1" customHeight="1">
       <c r="A105" s="98"/>
       <c r="B105" s="71" t="s">
         <v>302</v>
@@ -10776,7 +10773,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="108" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A108" s="98"/>
       <c r="B108" s="71" t="s">
         <v>320</v>
@@ -10822,7 +10819,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="109" spans="1:22" ht="13.8" hidden="1">
+    <row r="109" spans="1:22" ht="13.9" hidden="1">
       <c r="A109" s="98"/>
       <c r="B109" s="71" t="s">
         <v>320</v>
@@ -10875,7 +10872,7 @@
       <c r="U109" s="66"/>
       <c r="V109" s="66"/>
     </row>
-    <row r="110" spans="1:22" ht="13.8" hidden="1">
+    <row r="110" spans="1:22" ht="13.9" hidden="1">
       <c r="A110" s="98"/>
       <c r="B110" s="71" t="s">
         <v>320</v>
@@ -10989,7 +10986,7 @@
       </c>
       <c r="V111" s="71"/>
     </row>
-    <row r="112" spans="1:22" ht="13.8" hidden="1">
+    <row r="112" spans="1:22" ht="13.9" hidden="1">
       <c r="A112" s="98"/>
       <c r="B112" s="71" t="s">
         <v>327</v>
@@ -11042,7 +11039,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:22" ht="13.8" hidden="1">
+    <row r="113" spans="1:22" ht="13.9" hidden="1">
       <c r="A113" s="98"/>
       <c r="B113" s="71" t="s">
         <v>327</v>
@@ -11095,7 +11092,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="114" spans="1:22" ht="41.4" hidden="1">
+    <row r="114" spans="1:22" ht="41.45" hidden="1">
       <c r="A114" s="98"/>
       <c r="B114" s="71" t="s">
         <v>327</v>
@@ -11137,7 +11134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:22" ht="22.95" hidden="1" customHeight="1">
+    <row r="115" spans="1:22" ht="22.9" hidden="1" customHeight="1">
       <c r="A115" s="98"/>
       <c r="B115" s="71" t="s">
         <v>327</v>
@@ -11194,7 +11191,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="116" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A116" s="98"/>
       <c r="B116" s="71" t="s">
         <v>337</v>
@@ -11255,7 +11252,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="55.2" hidden="1">
+    <row r="117" spans="1:22" ht="55.15" hidden="1">
       <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>342</v>
@@ -11312,7 +11309,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="13.8" hidden="1">
+    <row r="118" spans="1:22" ht="13.9" hidden="1">
       <c r="A118" s="72">
         <v>29</v>
       </c>
@@ -11424,7 +11421,7 @@
       </c>
       <c r="V119" s="71"/>
     </row>
-    <row r="120" spans="1:22" ht="13.8" hidden="1">
+    <row r="120" spans="1:22" ht="13.9" hidden="1">
       <c r="A120" s="87"/>
       <c r="B120" s="71" t="s">
         <v>347</v>
@@ -11479,7 +11476,7 @@
       </c>
       <c r="V120" s="66"/>
     </row>
-    <row r="121" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+    <row r="121" spans="1:22" ht="37.15" hidden="1" customHeight="1">
       <c r="A121" s="103">
         <v>31</v>
       </c>
@@ -11535,7 +11532,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="122" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+    <row r="122" spans="1:22" ht="37.15" hidden="1" customHeight="1">
       <c r="A122" s="88"/>
       <c r="B122" s="71" t="s">
         <v>350</v>
@@ -11589,7 +11586,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
+    <row r="123" spans="1:22" ht="142.9" hidden="1" customHeight="1">
       <c r="A123" s="88"/>
       <c r="B123" s="71" t="s">
         <v>350</v>
@@ -11644,7 +11641,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="13.8" hidden="1">
+    <row r="124" spans="1:22" ht="13.9" hidden="1">
       <c r="A124" s="88"/>
       <c r="B124" s="71" t="s">
         <v>350</v>
@@ -11861,7 +11858,7 @@
       <c r="U127" s="80"/>
       <c r="V127" s="71"/>
     </row>
-    <row r="128" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="128" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A128" s="66">
         <v>33</v>
       </c>
@@ -11918,7 +11915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="129" spans="1:22" ht="37.9" customHeight="1">
       <c r="A129" s="68"/>
       <c r="B129" s="71" t="s">
         <v>369</v>
@@ -11973,7 +11970,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="13.8" hidden="1">
+    <row r="130" spans="1:22" ht="13.9">
       <c r="A130" s="68">
         <v>34</v>
       </c>
@@ -12030,7 +12027,7 @@
       </c>
       <c r="V130" s="66"/>
     </row>
-    <row r="131" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="131" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A131" s="68"/>
       <c r="B131" s="71" t="s">
         <v>374</v>
@@ -12085,7 +12082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="132" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A132" s="68"/>
       <c r="B132" s="71" t="s">
         <v>374</v>
@@ -12140,7 +12137,7 @@
       </c>
       <c r="V132" s="66"/>
     </row>
-    <row r="133" spans="1:22" ht="13.8" hidden="1">
+    <row r="133" spans="1:22" ht="13.9" hidden="1">
       <c r="A133" s="87">
         <v>35</v>
       </c>
@@ -12199,7 +12196,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:22" ht="13.8" hidden="1">
+    <row r="134" spans="1:22" ht="13.9" hidden="1">
       <c r="A134" s="87"/>
       <c r="B134" s="71" t="s">
         <v>374</v>
@@ -12254,7 +12251,7 @@
       </c>
       <c r="V134" s="66"/>
     </row>
-    <row r="135" spans="1:22" ht="41.4" hidden="1">
+    <row r="135" spans="1:22" ht="41.45" hidden="1">
       <c r="A135" s="87"/>
       <c r="B135" s="71" t="s">
         <v>374</v>
@@ -12315,7 +12312,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="13.8" hidden="1">
+    <row r="136" spans="1:22" ht="13.9" hidden="1">
       <c r="A136" s="87"/>
       <c r="B136" s="71" t="s">
         <v>374</v>
@@ -12372,7 +12369,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="125.4" hidden="1" customHeight="1">
+    <row r="137" spans="1:22" ht="125.45" hidden="1" customHeight="1">
       <c r="A137" s="66"/>
       <c r="B137" s="71" t="s">
         <v>383</v>
@@ -12430,7 +12427,7 @@
       </c>
       <c r="V137" s="71"/>
     </row>
-    <row r="138" spans="1:22" ht="13.8" hidden="1">
+    <row r="138" spans="1:22" ht="13.9" hidden="1">
       <c r="A138" s="87">
         <v>36</v>
       </c>
@@ -12487,7 +12484,7 @@
       </c>
       <c r="V138" s="71"/>
     </row>
-    <row r="139" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="139" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A139" s="87"/>
       <c r="B139" s="71" t="s">
         <v>383</v>
@@ -12542,7 +12539,7 @@
       </c>
       <c r="V139" s="71"/>
     </row>
-    <row r="140" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="140" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A140" s="87"/>
       <c r="B140" s="71" t="s">
         <v>383</v>
@@ -12651,7 +12648,7 @@
       </c>
       <c r="V141" s="71"/>
     </row>
-    <row r="142" spans="1:22" ht="13.8" hidden="1">
+    <row r="142" spans="1:22" ht="13.9" hidden="1">
       <c r="A142" s="87"/>
       <c r="B142" s="71" t="s">
         <v>383</v>
@@ -12706,7 +12703,7 @@
       </c>
       <c r="V142" s="71"/>
     </row>
-    <row r="143" spans="1:22" ht="13.8" hidden="1">
+    <row r="143" spans="1:22" ht="13.9" hidden="1">
       <c r="A143" s="87"/>
       <c r="B143" s="71" t="s">
         <v>383</v>
@@ -12761,7 +12758,7 @@
       </c>
       <c r="V143" s="66"/>
     </row>
-    <row r="144" spans="1:22" ht="13.8" hidden="1">
+    <row r="144" spans="1:22" ht="13.9" hidden="1">
       <c r="A144" s="87"/>
       <c r="B144" s="71" t="s">
         <v>383</v>
@@ -12816,7 +12813,7 @@
       </c>
       <c r="V144" s="71"/>
     </row>
-    <row r="145" spans="1:22" ht="13.8" hidden="1">
+    <row r="145" spans="1:22" ht="13.9" hidden="1">
       <c r="A145" s="87">
         <v>37</v>
       </c>
@@ -13038,7 +13035,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="35.4" hidden="1" customHeight="1">
+    <row r="149" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
       <c r="A149" s="98"/>
       <c r="B149" s="71" t="s">
         <v>404</v>
@@ -13092,7 +13089,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="150" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>404</v>
@@ -13148,7 +13145,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="151" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A151" s="68"/>
       <c r="B151" s="71" t="s">
         <v>409</v>
@@ -13203,7 +13200,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="13.8" hidden="1">
+    <row r="152" spans="1:22" ht="13.9" hidden="1">
       <c r="A152" s="66">
         <v>39</v>
       </c>
@@ -13262,7 +13259,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="153" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A153" s="93">
         <v>40</v>
       </c>
@@ -13321,7 +13318,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="154" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A154" s="98"/>
       <c r="B154" s="71" t="s">
         <v>415</v>
@@ -13423,7 +13420,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="156" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A156" s="98"/>
       <c r="B156" s="71" t="s">
         <v>415</v>
@@ -13475,7 +13472,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="157" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A157" s="98"/>
       <c r="B157" s="71" t="s">
         <v>415</v>
@@ -13532,7 +13529,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="13.8" hidden="1">
+    <row r="158" spans="1:22" ht="13.9" hidden="1">
       <c r="A158" s="98"/>
       <c r="B158" s="71" t="s">
         <v>415</v>
@@ -13589,7 +13586,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="13.8" hidden="1">
+    <row r="159" spans="1:22" ht="13.9" hidden="1">
       <c r="A159" s="98"/>
       <c r="B159" s="71" t="s">
         <v>415</v>
@@ -13646,7 +13643,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="55.2" hidden="1">
+    <row r="160" spans="1:22" ht="55.15" hidden="1">
       <c r="A160" s="98"/>
       <c r="B160" s="71" t="s">
         <v>429</v>
@@ -13755,7 +13752,7 @@
       </c>
       <c r="V161" s="71"/>
     </row>
-    <row r="162" spans="1:22" ht="13.8" hidden="1">
+    <row r="162" spans="1:22" ht="13.9" hidden="1">
       <c r="A162" s="98"/>
       <c r="B162" s="71" t="s">
         <v>429</v>
@@ -13808,7 +13805,7 @@
       </c>
       <c r="V162" s="71"/>
     </row>
-    <row r="163" spans="1:22" ht="13.8" hidden="1">
+    <row r="163" spans="1:22" ht="13.9" hidden="1">
       <c r="A163" s="98"/>
       <c r="B163" s="71" t="s">
         <v>429</v>
@@ -13919,7 +13916,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="165" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A165" s="98"/>
       <c r="B165" s="71" t="s">
         <v>437</v>
@@ -13973,7 +13970,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="166" spans="1:22" ht="13.8" hidden="1">
+    <row r="166" spans="1:22" ht="13.9" hidden="1">
       <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>437</v>
@@ -14029,7 +14026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="167" spans="1:22" ht="13.8" hidden="1">
+    <row r="167" spans="1:22" ht="13.9" hidden="1">
       <c r="A167" s="68"/>
       <c r="B167" s="71" t="s">
         <v>444</v>
@@ -14151,7 +14148,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="169" spans="1:22" ht="41.4" hidden="1">
+    <row r="169" spans="1:22" ht="41.45" hidden="1">
       <c r="A169" s="99">
         <v>44</v>
       </c>
@@ -14264,7 +14261,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="171" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+    <row r="171" spans="1:22" ht="37.15" hidden="1" customHeight="1">
       <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>451</v>
@@ -14323,7 +14320,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="172" spans="1:22" ht="13.8" hidden="1">
+    <row r="172" spans="1:22" ht="13.9" hidden="1">
       <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>451</v>
@@ -14380,7 +14377,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="173" spans="1:22" ht="13.8" hidden="1">
+    <row r="173" spans="1:22" ht="13.9" hidden="1">
       <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>458</v>
@@ -14437,7 +14434,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="174" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="174" spans="1:22" ht="40.15" hidden="1" customHeight="1">
       <c r="A174" s="87">
         <v>45</v>
       </c>
@@ -14495,7 +14492,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="175" spans="1:22" ht="13.8" hidden="1">
+    <row r="175" spans="1:22" ht="13.9" hidden="1">
       <c r="A175" s="87"/>
       <c r="B175" s="71" t="s">
         <v>460</v>
@@ -14552,7 +14549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:22" ht="13.8" hidden="1">
+    <row r="176" spans="1:22" ht="13.9" hidden="1">
       <c r="A176" s="87"/>
       <c r="B176" s="71" t="s">
         <v>460</v>
@@ -14607,7 +14604,7 @@
       </c>
       <c r="V176" s="71"/>
     </row>
-    <row r="177" spans="1:22" ht="13.8" hidden="1">
+    <row r="177" spans="1:22" ht="13.9" hidden="1">
       <c r="A177" s="87"/>
       <c r="B177" s="71" t="s">
         <v>460</v>
@@ -14664,7 +14661,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="178" spans="1:22" ht="41.4" hidden="1">
+    <row r="178" spans="1:22" ht="41.45" hidden="1">
       <c r="A178" s="87"/>
       <c r="B178" s="71" t="s">
         <v>460</v>
@@ -14719,7 +14716,7 @@
       </c>
       <c r="V178" s="71"/>
     </row>
-    <row r="179" spans="1:22" ht="13.8" hidden="1">
+    <row r="179" spans="1:22" ht="13.9" hidden="1">
       <c r="A179" s="87"/>
       <c r="B179" s="71" t="s">
         <v>468</v>
@@ -14776,7 +14773,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="13.8" hidden="1">
+    <row r="180" spans="1:22" ht="13.9" hidden="1">
       <c r="A180" s="87"/>
       <c r="B180" s="71" t="s">
         <v>470</v>
@@ -14831,7 +14828,7 @@
       </c>
       <c r="V180" s="66"/>
     </row>
-    <row r="181" spans="1:22" ht="13.8" hidden="1">
+    <row r="181" spans="1:22" ht="13.9" hidden="1">
       <c r="A181" s="75"/>
       <c r="B181" s="71" t="s">
         <v>473</v>
@@ -14940,7 +14937,7 @@
       </c>
       <c r="V182" s="66"/>
     </row>
-    <row r="183" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="183" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A183" s="102">
         <v>46</v>
       </c>
@@ -14995,7 +14992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="184" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>473</v>
@@ -15050,7 +15047,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="185" spans="1:22" ht="13.8" hidden="1">
+    <row r="185" spans="1:22" ht="13.9" hidden="1">
       <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>473</v>
@@ -15107,7 +15104,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="13.8" hidden="1">
+    <row r="186" spans="1:22" ht="13.9" hidden="1">
       <c r="A186" s="72"/>
       <c r="B186" s="71" t="s">
         <v>485</v>
@@ -15166,7 +15163,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="13.8" hidden="1">
+    <row r="187" spans="1:22" ht="13.9" hidden="1">
       <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>485</v>
@@ -15217,7 +15214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:22" ht="13.8" hidden="1">
+    <row r="188" spans="1:22" ht="13.9" hidden="1">
       <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>485</v>
@@ -15270,7 +15267,7 @@
       <c r="U188" s="80"/>
       <c r="V188" s="71"/>
     </row>
-    <row r="189" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="189" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>485</v>
@@ -15378,7 +15375,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:22" ht="64.95" hidden="1" customHeight="1">
+    <row r="191" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
       <c r="A191" s="87">
         <v>48</v>
       </c>
@@ -15488,7 +15485,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="193" spans="1:22" ht="13.8" hidden="1">
+    <row r="193" spans="1:22" ht="13.9" hidden="1">
       <c r="A193" s="87"/>
       <c r="B193" s="71" t="s">
         <v>492</v>
@@ -15545,7 +15542,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="194" spans="1:22" ht="13.8" hidden="1">
+    <row r="194" spans="1:22" ht="13.9" hidden="1">
       <c r="A194" s="66">
         <v>49</v>
       </c>
@@ -15575,7 +15572,7 @@
       <c r="U194" s="66"/>
       <c r="V194" s="66"/>
     </row>
-    <row r="195" spans="1:22" ht="13.8" hidden="1">
+    <row r="195" spans="1:22" ht="13.9" hidden="1">
       <c r="A195" s="98"/>
       <c r="B195" s="71" t="s">
         <v>504</v>
@@ -15685,7 +15682,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="197" spans="1:22" ht="13.8" hidden="1">
+    <row r="197" spans="1:22" ht="13.9" hidden="1">
       <c r="A197" s="87">
         <v>51</v>
       </c>
@@ -15741,7 +15738,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="198" spans="1:22" ht="13.8" hidden="1">
+    <row r="198" spans="1:22" ht="13.9" hidden="1">
       <c r="A198" s="87"/>
       <c r="B198" s="71" t="s">
         <v>508</v>
@@ -15798,7 +15795,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="199" spans="1:22" ht="13.8" hidden="1">
+    <row r="199" spans="1:22" ht="13.9" hidden="1">
       <c r="A199" s="87"/>
       <c r="B199" s="71" t="s">
         <v>508</v>
@@ -15855,7 +15852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="200" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="200" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A200" s="87"/>
       <c r="B200" s="71" t="s">
         <v>508</v>
@@ -15911,7 +15908,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="201" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="71" t="s">
         <v>515</v>
@@ -15966,7 +15963,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="202" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="71" t="s">
         <v>515</v>
@@ -16015,7 +16012,7 @@
       <c r="U202" s="70"/>
       <c r="V202" s="66"/>
     </row>
-    <row r="203" spans="1:22" ht="13.8" hidden="1">
+    <row r="203" spans="1:22" ht="13.9" hidden="1">
       <c r="A203" s="66">
         <v>52</v>
       </c>
@@ -16074,7 +16071,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="204" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="204" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A204" s="87">
         <v>53</v>
       </c>
@@ -16132,7 +16129,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="205" spans="1:22" ht="55.2" hidden="1">
+    <row r="205" spans="1:22" ht="55.15" hidden="1">
       <c r="A205" s="87"/>
       <c r="B205" s="71" t="s">
         <v>520</v>
@@ -16189,7 +16186,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="206" spans="1:22" ht="13.8" hidden="1">
+    <row r="206" spans="1:22" ht="13.9" hidden="1">
       <c r="A206" s="87"/>
       <c r="B206" s="66" t="s">
         <v>524</v>
@@ -16246,7 +16243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="207" spans="1:22" ht="13.8" hidden="1">
+    <row r="207" spans="1:22" ht="13.9" hidden="1">
       <c r="A207" s="87">
         <v>54</v>
       </c>
@@ -16303,7 +16300,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208" spans="1:22" ht="13.8" hidden="1">
+    <row r="208" spans="1:22" ht="13.9" hidden="1">
       <c r="A208" s="87"/>
       <c r="B208" s="71" t="s">
         <v>527</v>
@@ -16362,7 +16359,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="209" spans="1:22" ht="32.4" hidden="1" customHeight="1">
+    <row r="209" spans="1:22" ht="32.450000000000003" hidden="1" customHeight="1">
       <c r="A209" s="87">
         <v>55</v>
       </c>
@@ -16420,7 +16417,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="210" spans="1:22" ht="13.8" hidden="1">
+    <row r="210" spans="1:22" ht="13.9" hidden="1">
       <c r="A210" s="87"/>
       <c r="B210" s="71" t="s">
         <v>530</v>
@@ -16475,7 +16472,7 @@
       </c>
       <c r="V210" s="71"/>
     </row>
-    <row r="211" spans="1:22" ht="16.2" hidden="1" customHeight="1">
+    <row r="211" spans="1:22" ht="16.149999999999999" hidden="1" customHeight="1">
       <c r="A211" s="87"/>
       <c r="B211" s="71" t="s">
         <v>530</v>
@@ -16530,7 +16527,7 @@
       </c>
       <c r="V211" s="66"/>
     </row>
-    <row r="212" spans="1:22" ht="80.400000000000006" hidden="1" customHeight="1">
+    <row r="212" spans="1:22" ht="80.45" hidden="1" customHeight="1">
       <c r="A212" s="87">
         <v>56</v>
       </c>
@@ -16586,7 +16583,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="213" spans="1:22" ht="13.8" hidden="1">
+    <row r="213" spans="1:22" ht="13.9" hidden="1">
       <c r="A213" s="87"/>
       <c r="B213" s="71" t="s">
         <v>539</v>
@@ -16645,7 +16642,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="214" spans="1:22" ht="41.4" hidden="1">
+    <row r="214" spans="1:22" ht="41.45" hidden="1">
       <c r="A214" s="99">
         <v>57</v>
       </c>
@@ -16701,7 +16698,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="215" spans="1:22" ht="13.8" hidden="1">
+    <row r="215" spans="1:22" ht="13.9" hidden="1">
       <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>541</v>
@@ -16758,7 +16755,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216" spans="1:22" ht="13.8" hidden="1">
+    <row r="216" spans="1:22" ht="13.9" hidden="1">
       <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>541</v>
@@ -16871,7 +16868,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="218" spans="1:22" ht="13.8" hidden="1">
+    <row r="218" spans="1:22" ht="13.9" hidden="1">
       <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>541</v>
@@ -16928,7 +16925,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:22" ht="13.8" hidden="1">
+    <row r="219" spans="1:22" ht="13.9" hidden="1">
       <c r="A219" s="74"/>
       <c r="B219" s="71" t="s">
         <v>552</v>
@@ -16985,7 +16982,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220" spans="1:22" ht="13.8" hidden="1">
+    <row r="220" spans="1:22" ht="13.9" hidden="1">
       <c r="A220" s="74"/>
       <c r="B220" s="71" t="s">
         <v>552</v>
@@ -17042,7 +17039,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221" spans="1:22" ht="13.8" hidden="1">
+    <row r="221" spans="1:22" ht="13.9" hidden="1">
       <c r="A221" s="74"/>
       <c r="B221" s="71" t="s">
         <v>552</v>
@@ -17096,7 +17093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="222" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A222" s="66">
         <v>58</v>
       </c>
@@ -17155,7 +17152,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="223" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+    <row r="223" spans="1:22" ht="34.15" hidden="1" customHeight="1">
       <c r="A223" s="87">
         <v>59</v>
       </c>
@@ -17211,7 +17208,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="224" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+    <row r="224" spans="1:22" ht="34.15" hidden="1" customHeight="1">
       <c r="A224" s="87"/>
       <c r="B224" s="71" t="s">
         <v>562</v>
@@ -17320,7 +17317,7 @@
       </c>
       <c r="V225" s="71"/>
     </row>
-    <row r="226" spans="1:22" ht="13.8" hidden="1">
+    <row r="226" spans="1:22" ht="13.9" hidden="1">
       <c r="A226" s="87"/>
       <c r="B226" s="71" t="s">
         <v>562</v>
@@ -17430,7 +17427,7 @@
       <c r="U227" s="70"/>
       <c r="V227" s="66"/>
     </row>
-    <row r="228" spans="1:22" ht="13.8" hidden="1">
+    <row r="228" spans="1:22" ht="13.9" hidden="1">
       <c r="A228" s="87"/>
       <c r="B228" s="71" t="s">
         <v>562</v>
@@ -17487,7 +17484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="229" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="229" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A229" s="66"/>
       <c r="B229" s="71" t="s">
         <v>574</v>
@@ -17542,7 +17539,7 @@
       </c>
       <c r="V229" s="66"/>
     </row>
-    <row r="230" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="230" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A230" s="66"/>
       <c r="B230" s="71" t="s">
         <v>574</v>
@@ -17597,7 +17594,7 @@
       </c>
       <c r="V230" s="66"/>
     </row>
-    <row r="231" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="231" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A231" s="66"/>
       <c r="B231" s="71" t="s">
         <v>574</v>
@@ -17652,7 +17649,7 @@
       </c>
       <c r="V231" s="66"/>
     </row>
-    <row r="232" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="232" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A232" s="66">
         <v>60</v>
       </c>
@@ -17708,7 +17705,7 @@
       </c>
       <c r="V232" s="66"/>
     </row>
-    <row r="233" spans="1:22" ht="13.8" hidden="1">
+    <row r="233" spans="1:22" ht="13.9" hidden="1">
       <c r="A233" s="66">
         <v>61</v>
       </c>
@@ -17738,7 +17735,7 @@
       <c r="U233" s="66"/>
       <c r="V233" s="66"/>
     </row>
-    <row r="234" spans="1:22" ht="224.4" hidden="1" customHeight="1">
+    <row r="234" spans="1:22" ht="224.45" hidden="1" customHeight="1">
       <c r="A234" s="66">
         <v>62</v>
       </c>
@@ -18016,7 +18013,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="239" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A239" s="98"/>
       <c r="B239" s="71" t="s">
         <v>583</v>
@@ -18072,7 +18069,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="240" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>597</v>
@@ -18125,7 +18122,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="241" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="241" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A241" s="87">
         <v>64</v>
       </c>
@@ -18181,7 +18178,7 @@
       </c>
       <c r="V241" s="71"/>
     </row>
-    <row r="242" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="242" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A242" s="87"/>
       <c r="B242" s="71" t="s">
         <v>600</v>
@@ -18236,7 +18233,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="243" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A243" s="87"/>
       <c r="B243" s="71" t="s">
         <v>600</v>
@@ -18297,7 +18294,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="55.2" hidden="1">
+    <row r="244" spans="1:22" ht="55.15" hidden="1">
       <c r="A244" s="87"/>
       <c r="B244" s="71" t="s">
         <v>600</v>
@@ -18350,7 +18347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="245" spans="1:22" ht="13.8" hidden="1">
+    <row r="245" spans="1:22" ht="13.9" hidden="1">
       <c r="A245" s="87"/>
       <c r="B245" s="71" t="s">
         <v>600</v>
@@ -18386,7 +18383,7 @@
       <c r="U245" s="80"/>
       <c r="V245" s="71"/>
     </row>
-    <row r="246" spans="1:22" ht="13.8" hidden="1">
+    <row r="246" spans="1:22" ht="13.9" hidden="1">
       <c r="A246" s="87"/>
       <c r="B246" s="71" t="s">
         <v>600</v>
@@ -18439,7 +18436,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="247" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="247" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A247" s="87"/>
       <c r="B247" s="71" t="s">
         <v>600</v>
@@ -18495,7 +18492,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="248" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="248" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A248" s="66"/>
       <c r="B248" s="71" t="s">
         <v>608</v>
@@ -18661,7 +18658,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="251" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A251" s="87"/>
       <c r="B251" s="71" t="s">
         <v>608</v>
@@ -18717,7 +18714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="13.8" hidden="1">
+    <row r="252" spans="1:22" ht="13.9" hidden="1">
       <c r="A252" s="66">
         <v>66</v>
       </c>
@@ -18747,7 +18744,7 @@
       <c r="U252" s="66"/>
       <c r="V252" s="66"/>
     </row>
-    <row r="253" spans="1:22" ht="13.8" hidden="1">
+    <row r="253" spans="1:22" ht="13.9" hidden="1">
       <c r="A253" s="66"/>
       <c r="B253" s="71" t="s">
         <v>617</v>
@@ -18798,7 +18795,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="1:22" ht="13.8" hidden="1">
+    <row r="254" spans="1:22" ht="13.9" hidden="1">
       <c r="A254" s="66">
         <v>67</v>
       </c>
@@ -18966,7 +18963,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="257" spans="1:22" ht="13.8" hidden="1">
+    <row r="257" spans="1:22" ht="13.9" hidden="1">
       <c r="A257" s="98"/>
       <c r="B257" s="71" t="s">
         <v>621</v>
@@ -19023,7 +19020,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="258" spans="1:22" ht="13.8" hidden="1">
+    <row r="258" spans="1:22" ht="13.9" hidden="1">
       <c r="A258" s="98"/>
       <c r="B258" s="71" t="s">
         <v>621</v>
@@ -19080,7 +19077,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="259" spans="1:22" ht="13.8" hidden="1">
+    <row r="259" spans="1:22" ht="13.9" hidden="1">
       <c r="A259" s="98"/>
       <c r="B259" s="71" t="s">
         <v>621</v>
@@ -19135,7 +19132,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="260" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+    <row r="260" spans="1:22" ht="34.15" hidden="1" customHeight="1">
       <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>621</v>
@@ -19192,7 +19189,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:22" ht="55.2" hidden="1">
+    <row r="261" spans="1:22" ht="55.15" hidden="1">
       <c r="A261" s="93">
         <v>69</v>
       </c>
@@ -19350,7 +19347,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="264" spans="1:22" ht="55.2" hidden="1">
+    <row r="264" spans="1:22" ht="55.15" hidden="1">
       <c r="A264" s="98"/>
       <c r="B264" s="71" t="s">
         <v>639</v>
@@ -19401,7 +19398,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="265" spans="1:22" ht="46.2" hidden="1" customHeight="1">
+    <row r="265" spans="1:22" ht="46.15" hidden="1" customHeight="1">
       <c r="A265" s="98"/>
       <c r="B265" s="71" t="s">
         <v>631</v>
@@ -19456,7 +19453,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:22" ht="46.2" hidden="1" customHeight="1">
+    <row r="266" spans="1:22" ht="46.15" hidden="1" customHeight="1">
       <c r="A266" s="67"/>
       <c r="B266" s="71" t="s">
         <v>645</v>
@@ -19514,7 +19511,7 @@
       </c>
       <c r="V266" s="71"/>
     </row>
-    <row r="267" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="267" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A267" s="87">
         <v>70</v>
       </c>
@@ -19573,7 +19570,7 @@
       </c>
       <c r="V267" s="71"/>
     </row>
-    <row r="268" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="268" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A268" s="87"/>
       <c r="B268" s="71" t="s">
         <v>645</v>
@@ -19630,7 +19627,7 @@
       </c>
       <c r="V268" s="71"/>
     </row>
-    <row r="269" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="269" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A269" s="87"/>
       <c r="B269" s="71" t="s">
         <v>645</v>
@@ -19687,7 +19684,7 @@
       </c>
       <c r="V269" s="71"/>
     </row>
-    <row r="270" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="270" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A270" s="87"/>
       <c r="B270" s="71" t="s">
         <v>645</v>
@@ -19744,7 +19741,7 @@
       </c>
       <c r="V270" s="66"/>
     </row>
-    <row r="271" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="271" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A271" s="66"/>
       <c r="B271" s="71" t="s">
         <v>655</v>
@@ -19801,7 +19798,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="272" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A272" s="87">
         <v>71</v>
       </c>
@@ -19858,7 +19855,7 @@
       </c>
       <c r="V272" s="71"/>
     </row>
-    <row r="273" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="273" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A273" s="87"/>
       <c r="B273" s="71" t="s">
         <v>655</v>
@@ -19915,7 +19912,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="274" spans="1:22" ht="13.8" hidden="1">
+    <row r="274" spans="1:22" ht="13.9" hidden="1">
       <c r="A274" s="87"/>
       <c r="B274" s="71" t="s">
         <v>655</v>
@@ -19972,7 +19969,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="275" spans="1:22" ht="13.8" hidden="1">
+    <row r="275" spans="1:22" ht="13.9" hidden="1">
       <c r="A275" s="87"/>
       <c r="B275" s="71" t="s">
         <v>655</v>
@@ -20029,7 +20026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="276" spans="1:22" ht="13.8" hidden="1">
+    <row r="276" spans="1:22" ht="13.9" hidden="1">
       <c r="A276" s="87"/>
       <c r="B276" s="66" t="s">
         <v>662</v>
@@ -20086,7 +20083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="277" spans="1:22" ht="13.8" hidden="1">
+    <row r="277" spans="1:22" ht="13.9" hidden="1">
       <c r="A277" s="66">
         <v>72</v>
       </c>
@@ -20143,7 +20140,7 @@
       </c>
       <c r="V277" s="66"/>
     </row>
-    <row r="278" spans="1:22" ht="13.8" hidden="1">
+    <row r="278" spans="1:22" ht="13.9" hidden="1">
       <c r="A278" s="66"/>
       <c r="B278" s="71" t="s">
         <v>667</v>
@@ -20200,7 +20197,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="279" spans="1:22" ht="13.8" hidden="1">
+    <row r="279" spans="1:22" ht="13.9" hidden="1">
       <c r="A279" s="66"/>
       <c r="B279" s="71" t="s">
         <v>667</v>
@@ -20253,7 +20250,7 @@
       <c r="U279" s="70"/>
       <c r="V279" s="66"/>
     </row>
-    <row r="280" spans="1:22" ht="13.8" hidden="1">
+    <row r="280" spans="1:22" ht="13.9" hidden="1">
       <c r="A280" s="66">
         <v>73</v>
       </c>
@@ -20365,7 +20362,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="282" spans="1:22" ht="13.8" hidden="1">
+    <row r="282" spans="1:22" ht="13.9" hidden="1">
       <c r="A282" s="87"/>
       <c r="B282" s="71" t="s">
         <v>671</v>
@@ -20415,7 +20412,7 @@
       </c>
       <c r="V282" s="66"/>
     </row>
-    <row r="283" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+    <row r="283" spans="1:22" ht="37.15" hidden="1" customHeight="1">
       <c r="A283" s="87">
         <v>75</v>
       </c>
@@ -20471,7 +20468,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="13.8" hidden="1">
+    <row r="284" spans="1:22" ht="13.9" hidden="1">
       <c r="A284" s="87"/>
       <c r="B284" s="71" t="s">
         <v>674</v>
@@ -20526,7 +20523,7 @@
       </c>
       <c r="V284" s="71"/>
     </row>
-    <row r="285" spans="1:22" ht="13.8" hidden="1">
+    <row r="285" spans="1:22" ht="13.9" hidden="1">
       <c r="A285" s="94">
         <v>76</v>
       </c>
@@ -20585,7 +20582,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="286" spans="1:22" ht="13.8" hidden="1">
+    <row r="286" spans="1:22" ht="13.9" hidden="1">
       <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>678</v>
@@ -20642,7 +20639,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="287" spans="1:22" ht="13.8" hidden="1">
+    <row r="287" spans="1:22" ht="13.9" hidden="1">
       <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>678</v>
@@ -20699,7 +20696,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="288" spans="1:22" ht="13.8" hidden="1">
+    <row r="288" spans="1:22" ht="13.9" hidden="1">
       <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>678</v>
@@ -20756,7 +20753,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="289" spans="1:22" ht="13.8" hidden="1">
+    <row r="289" spans="1:22" ht="13.9" hidden="1">
       <c r="A289" s="87"/>
       <c r="B289" s="71" t="s">
         <v>678</v>
@@ -20865,7 +20862,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="291" spans="1:22" ht="13.8" hidden="1">
+    <row r="291" spans="1:22" ht="13.9" hidden="1">
       <c r="A291" s="87"/>
       <c r="B291" s="71" t="s">
         <v>678</v>
@@ -20922,7 +20919,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="292" spans="1:22" ht="13.8" hidden="1">
+    <row r="292" spans="1:22" ht="13.9" hidden="1">
       <c r="A292" s="87"/>
       <c r="B292" s="71" t="s">
         <v>678</v>
@@ -20975,7 +20972,7 @@
       </c>
       <c r="V292" s="71"/>
     </row>
-    <row r="293" spans="1:22" ht="13.8" hidden="1">
+    <row r="293" spans="1:22" ht="13.9" hidden="1">
       <c r="A293" s="87"/>
       <c r="B293" s="71" t="s">
         <v>678</v>
@@ -21030,7 +21027,7 @@
       </c>
       <c r="V293" s="71"/>
     </row>
-    <row r="294" spans="1:22" ht="41.4" hidden="1">
+    <row r="294" spans="1:22" ht="41.45" hidden="1">
       <c r="A294" s="66"/>
       <c r="B294" s="71" t="s">
         <v>693</v>
@@ -21215,7 +21212,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="297" spans="1:22" ht="13.8" hidden="1">
+    <row r="297" spans="1:22" ht="13.9" hidden="1">
       <c r="A297" s="87"/>
       <c r="B297" s="71" t="s">
         <v>693</v>
@@ -21332,7 +21329,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="299" spans="1:22" ht="13.8" hidden="1">
+    <row r="299" spans="1:22" ht="13.9" hidden="1">
       <c r="A299" s="87"/>
       <c r="B299" s="71" t="s">
         <v>704</v>
@@ -21387,7 +21384,7 @@
       </c>
       <c r="V299" s="71"/>
     </row>
-    <row r="300" spans="1:22" ht="13.8" hidden="1">
+    <row r="300" spans="1:22" ht="13.9" hidden="1">
       <c r="A300" s="87"/>
       <c r="B300" s="71" t="s">
         <v>704</v>
@@ -21444,7 +21441,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="301" spans="1:22" ht="13.8" hidden="1">
+    <row r="301" spans="1:22" ht="13.9" hidden="1">
       <c r="A301" s="98"/>
       <c r="B301" s="71" t="s">
         <v>639</v>
@@ -21499,7 +21496,7 @@
       </c>
       <c r="V301" s="71"/>
     </row>
-    <row r="302" spans="1:22" ht="13.8" hidden="1">
+    <row r="302" spans="1:22" ht="13.9" hidden="1">
       <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>639</v>
@@ -21612,7 +21609,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="304" spans="1:22" ht="13.8" hidden="1">
+    <row r="304" spans="1:22" ht="13.9" hidden="1">
       <c r="A304" s="98"/>
       <c r="B304" s="71" t="s">
         <v>718</v>
@@ -21831,7 +21828,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="308" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="308" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>720</v>
@@ -21947,7 +21944,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="310" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="310" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A310" s="66">
         <v>83</v>
       </c>
@@ -22009,7 +22006,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="311" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="311" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A311" s="87">
         <v>84</v>
       </c>
@@ -22041,7 +22038,7 @@
       <c r="U311" s="87"/>
       <c r="V311" s="87"/>
     </row>
-    <row r="312" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="312" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A312" s="87"/>
       <c r="B312" s="71" t="s">
         <v>730</v>
@@ -22102,7 +22099,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="313" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="313" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A313" s="87"/>
       <c r="B313" s="71" t="s">
         <v>734</v>
@@ -22132,7 +22129,7 @@
       <c r="U313" s="105"/>
       <c r="V313" s="87"/>
     </row>
-    <row r="314" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="314" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A314" s="87"/>
       <c r="B314" s="71" t="s">
         <v>734</v>
@@ -22191,7 +22188,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="315" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="315" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A315" s="87"/>
       <c r="B315" s="71" t="s">
         <v>734</v>
@@ -22248,7 +22245,7 @@
       </c>
       <c r="V315" s="71"/>
     </row>
-    <row r="316" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="316" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A316" s="87"/>
       <c r="B316" s="71" t="s">
         <v>734</v>
@@ -22306,7 +22303,7 @@
       </c>
       <c r="V316" s="71"/>
     </row>
-    <row r="317" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="317" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A317" s="72"/>
       <c r="B317" s="71" t="s">
         <v>740</v>
@@ -22361,7 +22358,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="318" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="318" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A318" s="72"/>
       <c r="B318" s="71" t="s">
         <v>740</v>
@@ -22405,7 +22402,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="319" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="319" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A319" s="93">
         <v>85</v>
       </c>
@@ -22455,7 +22452,7 @@
       <c r="U319" s="80"/>
       <c r="V319" s="71"/>
     </row>
-    <row r="320" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="320" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>740</v>
@@ -22509,7 +22506,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="321" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="321" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A321" s="99">
         <v>86</v>
       </c>
@@ -22564,7 +22561,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="322" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="322" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>746</v>
@@ -22615,7 +22612,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="323" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="323" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>746</v>
@@ -22670,7 +22667,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="324" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="324" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>746</v>
@@ -22778,7 +22775,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="326" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="326" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A326" s="98"/>
       <c r="B326" s="66" t="s">
         <v>746</v>
@@ -22831,7 +22828,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="327" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="327" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>746</v>
@@ -22888,7 +22885,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="328" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="328" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>746</v>
@@ -22941,7 +22938,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="329" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="329" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>746</v>
@@ -22996,7 +22993,7 @@
       </c>
       <c r="V329" s="71"/>
     </row>
-    <row r="330" spans="1:22" ht="13.8" hidden="1">
+    <row r="330" spans="1:22" ht="13.9" hidden="1">
       <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>746</v>
@@ -23051,7 +23048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="331" spans="1:22" ht="41.4" hidden="1" customHeight="1">
+    <row r="331" spans="1:22" ht="41.45" hidden="1" customHeight="1">
       <c r="A331" s="68"/>
       <c r="B331" s="71" t="s">
         <v>764</v>
@@ -23104,7 +23101,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="332" spans="1:22" ht="13.8" hidden="1">
+    <row r="332" spans="1:22" ht="13.9" hidden="1">
       <c r="A332" s="66">
         <v>88</v>
       </c>
@@ -23134,7 +23131,7 @@
       <c r="U332" s="66"/>
       <c r="V332" s="66"/>
     </row>
-    <row r="333" spans="1:22" ht="41.4">
+    <row r="333" spans="1:22" ht="41.45" hidden="1">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>767</v>
@@ -23187,7 +23184,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:22" ht="13.8">
+    <row r="334" spans="1:22" ht="13.9" hidden="1">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>767</v>
@@ -23233,7 +23230,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="335" spans="1:22" ht="41.4">
+    <row r="335" spans="1:22" ht="41.45" hidden="1">
       <c r="A335" s="93">
         <v>89</v>
       </c>
@@ -23296,7 +23293,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="336" spans="1:22" ht="44.4" customHeight="1">
+    <row r="336" spans="1:22" ht="44.45" hidden="1" customHeight="1">
       <c r="A336" s="98"/>
       <c r="B336" s="71" t="s">
         <v>767</v>
@@ -23350,7 +23347,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="155.4" customHeight="1">
+    <row r="337" spans="1:23" ht="155.44999999999999" hidden="1" customHeight="1">
       <c r="A337" s="98"/>
       <c r="B337" s="71" t="s">
         <v>767</v>
@@ -23404,7 +23401,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="13.8">
+    <row r="338" spans="1:23" ht="13.9" hidden="1">
       <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>767</v>
@@ -23508,7 +23505,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="340" spans="1:23" ht="40.9" hidden="1" customHeight="1">
       <c r="A340" s="87">
         <v>90</v>
       </c>
@@ -23567,7 +23564,7 @@
       </c>
       <c r="W340" s="33"/>
     </row>
-    <row r="341" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="341" spans="1:23" ht="20.45" hidden="1" customHeight="1">
       <c r="A341" s="87"/>
       <c r="B341" s="71" t="s">
         <v>775</v>
@@ -23623,7 +23620,7 @@
       <c r="V341" s="66"/>
       <c r="W341" s="33"/>
     </row>
-    <row r="342" spans="1:23" ht="13.8" hidden="1">
+    <row r="342" spans="1:23" ht="13.9" hidden="1">
       <c r="A342" s="87">
         <v>91</v>
       </c>
@@ -23682,7 +23679,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="13.8" hidden="1">
+    <row r="343" spans="1:23" ht="13.9" hidden="1">
       <c r="A343" s="87"/>
       <c r="B343" s="71" t="s">
         <v>778</v>
@@ -23792,7 +23789,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="13.8" hidden="1">
+    <row r="345" spans="1:23" ht="13.9" hidden="1">
       <c r="A345" s="87"/>
       <c r="B345" s="71" t="s">
         <v>778</v>
@@ -23950,7 +23947,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="13.8" hidden="1">
+    <row r="348" spans="1:23" ht="13.9" hidden="1">
       <c r="A348" s="87"/>
       <c r="B348" s="71" t="s">
         <v>778</v>
@@ -24007,7 +24004,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="61.2" hidden="1" customHeight="1">
+    <row r="349" spans="1:23" ht="61.15" hidden="1" customHeight="1">
       <c r="A349" s="87">
         <v>92</v>
       </c>
@@ -24065,7 +24062,7 @@
       </c>
       <c r="V349" s="71"/>
     </row>
-    <row r="350" spans="1:23" ht="61.2" hidden="1" customHeight="1">
+    <row r="350" spans="1:23" ht="61.15" hidden="1" customHeight="1">
       <c r="A350" s="87"/>
       <c r="B350" s="71" t="s">
         <v>790</v>
@@ -24120,7 +24117,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="13.8" hidden="1">
+    <row r="351" spans="1:23" ht="13.9" hidden="1">
       <c r="A351" s="87"/>
       <c r="B351" s="71" t="s">
         <v>790</v>
@@ -24177,7 +24174,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="94.2" hidden="1" customHeight="1">
+    <row r="352" spans="1:23" ht="94.15" hidden="1" customHeight="1">
       <c r="A352" s="87">
         <v>93</v>
       </c>
@@ -24236,7 +24233,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="353" spans="1:22" ht="94.2" hidden="1" customHeight="1">
+    <row r="353" spans="1:22" ht="94.15" hidden="1" customHeight="1">
       <c r="A353" s="87"/>
       <c r="B353" s="71" t="s">
         <v>795</v>
@@ -24290,7 +24287,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="354" spans="1:22" ht="94.2" hidden="1" customHeight="1">
+    <row r="354" spans="1:22" ht="94.15" hidden="1" customHeight="1">
       <c r="A354" s="87"/>
       <c r="B354" s="71" t="s">
         <v>795</v>
@@ -24347,7 +24344,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="355" spans="1:22" ht="46.95" hidden="1" customHeight="1">
+    <row r="355" spans="1:22" ht="46.9" hidden="1" customHeight="1">
       <c r="A355" s="87"/>
       <c r="B355" s="71" t="s">
         <v>795</v>
@@ -24463,7 +24460,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="357" spans="1:22" ht="13.8" hidden="1">
+    <row r="357" spans="1:22" ht="13.9" hidden="1">
       <c r="A357" s="87"/>
       <c r="B357" s="71" t="s">
         <v>795</v>
@@ -24631,7 +24628,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="360" spans="1:22" ht="65.400000000000006" hidden="1" customHeight="1">
+    <row r="360" spans="1:22" ht="65.45" hidden="1" customHeight="1">
       <c r="A360" s="48">
         <v>94</v>
       </c>
@@ -24802,7 +24799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="363" spans="1:22" ht="13.8" hidden="1">
+    <row r="363" spans="1:22" ht="13.9" hidden="1">
       <c r="A363" s="87"/>
       <c r="B363" s="71" t="s">
         <v>815</v>
@@ -24858,7 +24855,7 @@
       </c>
       <c r="V363" s="71"/>
     </row>
-    <row r="364" spans="1:22" ht="13.8" hidden="1">
+    <row r="364" spans="1:22" ht="13.9" hidden="1">
       <c r="A364" s="87"/>
       <c r="B364" s="71" t="s">
         <v>815</v>
@@ -24915,7 +24912,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="365" spans="1:22" ht="13.8" hidden="1">
+    <row r="365" spans="1:22" ht="13.9" hidden="1">
       <c r="A365" s="68">
         <v>96</v>
       </c>
@@ -24972,7 +24969,7 @@
       </c>
       <c r="V365" s="66"/>
     </row>
-    <row r="366" spans="1:22" ht="13.8" hidden="1">
+    <row r="366" spans="1:22" ht="13.9" hidden="1">
       <c r="A366" s="68"/>
       <c r="B366" s="71" t="s">
         <v>819</v>
@@ -25027,7 +25024,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="367" spans="1:22" ht="13.8" hidden="1">
+    <row r="367" spans="1:22" ht="13.9" hidden="1">
       <c r="A367" s="66">
         <v>96</v>
       </c>
@@ -25084,7 +25081,7 @@
       </c>
       <c r="V367" s="71"/>
     </row>
-    <row r="368" spans="1:22" ht="41.4" hidden="1">
+    <row r="368" spans="1:22" ht="41.45" hidden="1">
       <c r="A368" s="93">
         <v>97</v>
       </c>
@@ -25136,7 +25133,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="369" spans="1:22" ht="41.4" hidden="1">
+    <row r="369" spans="1:22" ht="41.45" hidden="1">
       <c r="A369" s="98"/>
       <c r="B369" s="71" t="s">
         <v>822</v>
@@ -25197,7 +25194,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="370" spans="1:22" ht="41.4" hidden="1">
+    <row r="370" spans="1:22" ht="41.45" hidden="1">
       <c r="A370" s="98"/>
       <c r="B370" s="71" t="s">
         <v>822</v>
@@ -25364,7 +25361,7 @@
       </c>
       <c r="V372" s="71"/>
     </row>
-    <row r="373" spans="1:22" ht="148.94999999999999" hidden="1" customHeight="1">
+    <row r="373" spans="1:22" ht="148.9" hidden="1" customHeight="1">
       <c r="A373" s="87">
         <v>98</v>
       </c>
@@ -25420,7 +25417,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="374" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="374" spans="1:22" ht="40.15" hidden="1" customHeight="1">
       <c r="A374" s="87"/>
       <c r="B374" s="71" t="s">
         <v>828</v>
@@ -25474,7 +25471,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="375" spans="1:22" ht="34.950000000000003" hidden="1" customHeight="1">
+    <row r="375" spans="1:22" ht="34.9" hidden="1" customHeight="1">
       <c r="A375" s="87"/>
       <c r="B375" s="71" t="s">
         <v>828</v>
@@ -25528,7 +25525,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="376" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="376" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A376" s="87"/>
       <c r="B376" s="71" t="s">
         <v>828</v>
@@ -25582,7 +25579,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="377" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+    <row r="377" spans="1:22" ht="122.45" hidden="1" customHeight="1">
       <c r="A377" s="87"/>
       <c r="B377" s="71" t="s">
         <v>828</v>
@@ -25626,7 +25623,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="378" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="378" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A378" s="87"/>
       <c r="B378" s="71" t="s">
         <v>828</v>
@@ -25679,7 +25676,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="379" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A379" s="87"/>
       <c r="B379" s="71" t="s">
         <v>828</v>
@@ -25732,7 +25729,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="380" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="380" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A380" s="87"/>
       <c r="B380" s="71" t="s">
         <v>828</v>
@@ -25779,7 +25776,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="381" spans="1:22" ht="13.8" hidden="1">
+    <row r="381" spans="1:22" ht="13.9" hidden="1">
       <c r="A381" s="87"/>
       <c r="B381" s="71" t="s">
         <v>828</v>
@@ -25829,7 +25826,7 @@
       </c>
       <c r="V381" s="71"/>
     </row>
-    <row r="382" spans="1:22" ht="13.8" hidden="1">
+    <row r="382" spans="1:22" ht="13.9" hidden="1">
       <c r="A382" s="87"/>
       <c r="B382" s="71" t="s">
         <v>828</v>
@@ -25884,7 +25881,7 @@
       </c>
       <c r="V382" s="71"/>
     </row>
-    <row r="383" spans="1:22" ht="13.8" hidden="1">
+    <row r="383" spans="1:22" ht="13.9" hidden="1">
       <c r="A383" s="87"/>
       <c r="B383" s="71" t="s">
         <v>828</v>
@@ -25937,7 +25934,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="384" spans="1:22" ht="13.8" hidden="1">
+    <row r="384" spans="1:22" ht="13.9" hidden="1">
       <c r="A384" s="87"/>
       <c r="B384" s="71" t="s">
         <v>828</v>
@@ -26048,7 +26045,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="386" spans="1:22" ht="163.19999999999999" hidden="1" customHeight="1">
+    <row r="386" spans="1:22" ht="163.15" hidden="1" customHeight="1">
       <c r="A386" s="87"/>
       <c r="B386" s="71" t="s">
         <v>856</v>
@@ -26102,7 +26099,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="387" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="387" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A387" s="87"/>
       <c r="B387" s="71" t="s">
         <v>856</v>
@@ -26159,7 +26156,7 @@
       </c>
       <c r="V387" s="71"/>
     </row>
-    <row r="388" spans="1:22" ht="13.8" hidden="1">
+    <row r="388" spans="1:22" ht="13.9" hidden="1">
       <c r="A388" s="87"/>
       <c r="B388" s="71" t="s">
         <v>856</v>
@@ -26214,7 +26211,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:22" ht="13.8" hidden="1">
+    <row r="389" spans="1:22" ht="13.9" hidden="1">
       <c r="A389" s="87"/>
       <c r="B389" s="71" t="s">
         <v>855</v>
@@ -26269,7 +26266,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="390" spans="1:22" ht="13.8" hidden="1">
+    <row r="390" spans="1:22" ht="13.9" hidden="1">
       <c r="A390" s="87"/>
       <c r="B390" s="71" t="s">
         <v>855</v>
@@ -26326,7 +26323,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="391" spans="1:22" ht="13.8" hidden="1">
+    <row r="391" spans="1:22" ht="13.9" hidden="1">
       <c r="A391" s="87"/>
       <c r="B391" s="71" t="s">
         <v>855</v>
@@ -26368,7 +26365,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="392" spans="1:22" ht="13.8" hidden="1">
+    <row r="392" spans="1:22" ht="13.9" hidden="1">
       <c r="A392" s="87"/>
       <c r="B392" s="66" t="s">
         <v>855</v>
@@ -26423,7 +26420,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="393" spans="1:22" ht="148.19999999999999" hidden="1" customHeight="1">
+    <row r="393" spans="1:22" ht="148.15" hidden="1" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>865</v>
@@ -26477,7 +26474,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="394" spans="1:22" ht="58.2" hidden="1" customHeight="1">
+    <row r="394" spans="1:22" ht="58.15" hidden="1" customHeight="1">
       <c r="A394" s="87">
         <v>100</v>
       </c>
@@ -26530,10 +26527,10 @@
       <c r="T394" s="66"/>
       <c r="U394" s="80"/>
       <c r="V394" s="71" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="395" spans="1:22" ht="41.4" hidden="1">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="395" spans="1:22" ht="41.45" hidden="1">
       <c r="A395" s="87"/>
       <c r="B395" s="66" t="s">
         <v>865</v>
@@ -26549,7 +26546,7 @@
         <v>103</v>
       </c>
       <c r="G395" s="71" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H395" s="71">
         <v>25.72</v>
@@ -26584,7 +26581,7 @@
       <c r="T395" s="66"/>
       <c r="U395" s="80"/>
       <c r="V395" s="71" t="s">
-        <v>1071</v>
+        <v>868</v>
       </c>
     </row>
     <row r="396" spans="1:22" ht="18" hidden="1" customHeight="1">
@@ -26599,7 +26596,7 @@
         <v>43</v>
       </c>
       <c r="E396" s="81" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F396" s="71" t="s">
         <v>83</v>
@@ -26658,7 +26655,7 @@
         <v>162</v>
       </c>
       <c r="G397" s="66" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H397" s="66">
         <v>6</v>
@@ -26709,10 +26706,10 @@
         <v>43</v>
       </c>
       <c r="E398" s="81" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F398" s="71" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G398" s="66" t="s">
         <v>206</v>
@@ -26752,7 +26749,7 @@
       </c>
       <c r="V398" s="71"/>
     </row>
-    <row r="399" spans="1:22" ht="13.8" hidden="1">
+    <row r="399" spans="1:22" ht="13.9" hidden="1">
       <c r="A399" s="87"/>
       <c r="B399" s="71" t="s">
         <v>865</v>
@@ -26764,7 +26761,7 @@
         <v>43</v>
       </c>
       <c r="E399" s="81" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F399" s="71" t="s">
         <v>83</v>
@@ -26812,7 +26809,7 @@
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C400" s="66" t="s">
         <v>23</v>
@@ -26827,7 +26824,7 @@
         <v>103</v>
       </c>
       <c r="G400" s="71" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H400" s="71">
         <v>15.22</v>
@@ -26865,10 +26862,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="401" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+    <row r="401" spans="1:22" ht="31.9" hidden="1" customHeight="1">
       <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C401" s="66" t="s">
         <v>23</v>
@@ -26878,7 +26875,7 @@
       </c>
       <c r="E401" s="81"/>
       <c r="F401" s="71" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G401" s="71"/>
       <c r="H401" s="71"/>
@@ -26907,10 +26904,10 @@
       <c r="U401" s="80"/>
       <c r="V401" s="66"/>
     </row>
-    <row r="402" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+    <row r="402" spans="1:22" ht="31.9" hidden="1" customHeight="1">
       <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C402" s="66" t="s">
         <v>23</v>
@@ -26919,7 +26916,7 @@
         <v>43</v>
       </c>
       <c r="E402" s="81" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F402" s="71" t="s">
         <v>267</v>
@@ -26962,10 +26959,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="403" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+    <row r="403" spans="1:22" ht="31.9" hidden="1" customHeight="1">
       <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C403" s="66" t="s">
         <v>23</v>
@@ -26974,10 +26971,10 @@
         <v>43</v>
       </c>
       <c r="E403" s="81" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F403" s="71" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G403" s="71" t="s">
         <v>206</v>
@@ -27019,10 +27016,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="404" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+    <row r="404" spans="1:22" ht="31.9" hidden="1" customHeight="1">
       <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C404" s="66" t="s">
         <v>23</v>
@@ -27074,10 +27071,10 @@
       </c>
       <c r="V404" s="71"/>
     </row>
-    <row r="405" spans="1:22" ht="13.8" hidden="1">
+    <row r="405" spans="1:22" ht="13.9" hidden="1">
       <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C405" s="66" t="s">
         <v>23</v>
@@ -27086,7 +27083,7 @@
         <v>43</v>
       </c>
       <c r="E405" s="81" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F405" s="71" t="s">
         <v>83</v>
@@ -27136,7 +27133,7 @@
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C406" s="66" t="s">
         <v>86</v>
@@ -27149,10 +27146,10 @@
         <v>438</v>
       </c>
       <c r="G406" s="71" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H406" s="71" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="I406" s="71"/>
       <c r="J406" s="71"/>
@@ -27187,10 +27184,10 @@
         <v>156</v>
       </c>
     </row>
-    <row r="407" spans="1:22" ht="13.8" hidden="1">
+    <row r="407" spans="1:22" ht="13.9" hidden="1">
       <c r="A407" s="87"/>
       <c r="B407" s="71" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C407" s="66" t="s">
         <v>86</v>
@@ -27199,7 +27196,7 @@
         <v>43</v>
       </c>
       <c r="E407" s="81" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F407" s="71" t="s">
         <v>83</v>
@@ -27244,12 +27241,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="408" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="408" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A408" s="87">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C408" s="66" t="s">
         <v>42</v>
@@ -27261,13 +27258,13 @@
         <v>64</v>
       </c>
       <c r="F408" s="71" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G408" s="71" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H408" s="71" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I408" s="71"/>
       <c r="J408" s="71"/>
@@ -27301,10 +27298,10 @@
         <v>593</v>
       </c>
     </row>
-    <row r="409" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="409" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A409" s="87"/>
       <c r="B409" s="71" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C409" s="66" t="s">
         <v>42</v>
@@ -27313,7 +27310,7 @@
         <v>43</v>
       </c>
       <c r="E409" s="81" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F409" s="71" t="s">
         <v>267</v>
@@ -27358,10 +27355,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="410" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="410" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A410" s="87"/>
       <c r="B410" s="71" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C410" s="66" t="s">
         <v>42</v>
@@ -27414,10 +27411,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="411" spans="1:22" ht="13.8" hidden="1">
+    <row r="411" spans="1:22" ht="13.9" hidden="1">
       <c r="A411" s="87"/>
       <c r="B411" s="71" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C411" s="66" t="s">
         <v>42</v>
@@ -27426,7 +27423,7 @@
         <v>43</v>
       </c>
       <c r="E411" s="81" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F411" s="71" t="s">
         <v>83</v>
@@ -27476,7 +27473,7 @@
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C412" s="66" t="s">
         <v>151</v>
@@ -27489,10 +27486,10 @@
         <v>438</v>
       </c>
       <c r="G412" s="71" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H412" s="71" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="I412" s="71"/>
       <c r="J412" s="71"/>
@@ -27530,7 +27527,7 @@
     <row r="413" spans="1:22" ht="60" hidden="1" customHeight="1">
       <c r="A413" s="87"/>
       <c r="B413" s="71" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C413" s="66" t="s">
         <v>151</v>
@@ -27545,7 +27542,7 @@
         <v>455</v>
       </c>
       <c r="G413" s="71" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H413" s="71">
         <v>48.875</v>
@@ -27612,10 +27609,10 @@
       <c r="U414" s="80"/>
       <c r="V414" s="71"/>
     </row>
-    <row r="415" spans="1:22" ht="55.2" hidden="1">
+    <row r="415" spans="1:22" ht="55.15" hidden="1">
       <c r="A415" s="87"/>
       <c r="B415" s="71" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C415" s="66" t="s">
         <v>151</v>
@@ -27627,13 +27624,13 @@
         <v>2026003050013</v>
       </c>
       <c r="F415" s="66" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G415" s="71" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H415" s="71" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I415" s="71"/>
       <c r="J415" s="71"/>
@@ -27663,13 +27660,13 @@
       <c r="T415" s="66"/>
       <c r="U415" s="80"/>
       <c r="V415" s="71" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="416" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="416" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A416" s="87"/>
       <c r="B416" s="71" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C416" s="66" t="s">
         <v>151</v>
@@ -27722,12 +27719,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="417" spans="1:22" ht="41.4" hidden="1">
+    <row r="417" spans="1:22" ht="41.45" hidden="1">
       <c r="A417" s="87">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C417" s="66" t="s">
         <v>93</v>
@@ -27740,7 +27737,7 @@
         <v>103</v>
       </c>
       <c r="G417" s="71" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H417" s="71">
         <v>25.72</v>
@@ -27778,10 +27775,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="418" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
+    <row r="418" spans="1:22" ht="142.9" hidden="1" customHeight="1">
       <c r="A418" s="87"/>
       <c r="B418" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C418" s="66" t="s">
         <v>93</v>
@@ -27791,10 +27788,10 @@
       </c>
       <c r="E418" s="81"/>
       <c r="F418" s="71" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G418" s="66" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H418" s="66">
         <v>9.0500000000000007</v>
@@ -27826,10 +27823,10 @@
         <v>345</v>
       </c>
     </row>
-    <row r="419" spans="1:22" ht="13.8" hidden="1">
+    <row r="419" spans="1:22" ht="13.9" hidden="1">
       <c r="A419" s="87"/>
       <c r="B419" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C419" s="66" t="s">
         <v>93</v>
@@ -27838,10 +27835,10 @@
         <v>43</v>
       </c>
       <c r="E419" s="81" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F419" s="71" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G419" s="66" t="s">
         <v>206</v>
@@ -27883,10 +27880,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="420" spans="1:22" ht="13.8" hidden="1">
+    <row r="420" spans="1:22" ht="13.9" hidden="1">
       <c r="A420" s="87"/>
       <c r="B420" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C420" s="66" t="s">
         <v>93</v>
@@ -27895,10 +27892,10 @@
         <v>43</v>
       </c>
       <c r="E420" s="81" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F420" s="71" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G420" s="49" t="s">
         <v>206</v>
@@ -27940,22 +27937,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="421" spans="1:22" ht="13.8" hidden="1">
+    <row r="421" spans="1:22" ht="13.9" hidden="1">
       <c r="A421" s="87"/>
       <c r="B421" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C421" s="66" t="s">
         <v>93</v>
       </c>
       <c r="D421" s="66" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E421" s="81" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F421" s="71" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G421" s="66" t="s">
         <v>206</v>
@@ -28000,7 +27997,7 @@
     <row r="422" spans="1:22" ht="27.6" hidden="1">
       <c r="A422" s="87"/>
       <c r="B422" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C422" s="66" t="s">
         <v>93</v>
@@ -28011,7 +28008,7 @@
         <v>162</v>
       </c>
       <c r="G422" s="71" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H422" s="71">
         <v>10</v>
@@ -28041,10 +28038,10 @@
         <v>165</v>
       </c>
     </row>
-    <row r="423" spans="1:22" ht="13.8" hidden="1">
+    <row r="423" spans="1:22" ht="13.9" hidden="1">
       <c r="A423" s="87"/>
       <c r="B423" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C423" s="66" t="s">
         <v>93</v>
@@ -28056,10 +28053,10 @@
         <v>64</v>
       </c>
       <c r="F423" s="71" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G423" s="66" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H423" s="66"/>
       <c r="I423" s="66"/>
@@ -28092,10 +28089,10 @@
         <v>180</v>
       </c>
     </row>
-    <row r="424" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="424" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A424" s="87"/>
       <c r="B424" s="71" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C424" s="66" t="s">
         <v>93</v>
@@ -28110,7 +28107,7 @@
         <v>83</v>
       </c>
       <c r="G424" s="66" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H424" s="66">
         <v>0.8</v>
@@ -28153,7 +28150,7 @@
         <v>106</v>
       </c>
       <c r="B425" s="71" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C425" s="66" t="s">
         <v>93</v>
@@ -28168,7 +28165,7 @@
         <v>743</v>
       </c>
       <c r="G425" s="66" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H425" s="66">
         <v>5.59</v>
@@ -28201,7 +28198,7 @@
     <row r="426" spans="1:22" ht="27.6" hidden="1">
       <c r="A426" s="66"/>
       <c r="B426" s="66" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C426" s="66" t="s">
         <v>23</v>
@@ -28251,12 +28248,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="427" spans="1:22" ht="41.4" hidden="1">
+    <row r="427" spans="1:22" ht="41.45" hidden="1">
       <c r="A427" s="87">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C427" s="66" t="s">
         <v>23</v>
@@ -28271,10 +28268,10 @@
         <v>103</v>
       </c>
       <c r="G427" s="71" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H427" s="71" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I427" s="71"/>
       <c r="J427" s="71"/>
@@ -28309,10 +28306,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="428" spans="1:22" ht="13.8" hidden="1">
+    <row r="428" spans="1:22" ht="13.9" hidden="1">
       <c r="A428" s="87"/>
       <c r="B428" s="71" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C428" s="66" t="s">
         <v>23</v>
@@ -28321,10 +28318,10 @@
         <v>43</v>
       </c>
       <c r="E428" s="81" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F428" s="71" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G428" s="66" t="s">
         <v>507</v>
@@ -28364,10 +28361,10 @@
       </c>
       <c r="V428" s="71"/>
     </row>
-    <row r="429" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="429" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A429" s="87"/>
       <c r="B429" s="71" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C429" s="66" t="s">
         <v>23</v>
@@ -28377,7 +28374,7 @@
       </c>
       <c r="E429" s="81"/>
       <c r="F429" s="71" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G429" s="66" t="s">
         <v>392</v>
@@ -28417,10 +28414,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="430" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="430" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A430" s="87"/>
       <c r="B430" s="71" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C430" s="66" t="s">
         <v>23</v>
@@ -28432,13 +28429,13 @@
         <v>64</v>
       </c>
       <c r="F430" s="71" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="G430" s="66" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H430" s="66" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I430" s="66"/>
       <c r="J430" s="66"/>
@@ -28470,10 +28467,10 @@
         <v>250</v>
       </c>
     </row>
-    <row r="431" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="431" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A431" s="87"/>
       <c r="B431" s="71" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C431" s="66" t="s">
         <v>23</v>
@@ -28485,13 +28482,13 @@
         <v>64</v>
       </c>
       <c r="F431" s="71" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G431" s="66" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H431" s="66" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I431" s="66"/>
       <c r="J431" s="66"/>
@@ -28523,10 +28520,10 @@
         <v>250</v>
       </c>
     </row>
-    <row r="432" spans="1:22" ht="13.8" hidden="1">
+    <row r="432" spans="1:22" ht="13.9" hidden="1">
       <c r="A432" s="87"/>
       <c r="B432" s="71" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C432" s="66" t="s">
         <v>23</v>
@@ -28578,10 +28575,10 @@
       </c>
       <c r="V432" s="71"/>
     </row>
-    <row r="433" spans="1:22" ht="13.8" hidden="1">
+    <row r="433" spans="1:22" ht="13.9" hidden="1">
       <c r="A433" s="87"/>
       <c r="B433" s="71" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C433" s="66" t="s">
         <v>23</v>
@@ -28590,7 +28587,7 @@
         <v>43</v>
       </c>
       <c r="E433" s="81" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F433" s="71" t="s">
         <v>83</v>
@@ -28636,7 +28633,7 @@
     <row r="434" spans="1:22" ht="27.6" hidden="1">
       <c r="A434" s="98"/>
       <c r="B434" s="71" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C434" s="66" t="s">
         <v>42</v>
@@ -28649,10 +28646,10 @@
         <v>806</v>
       </c>
       <c r="G434" s="71" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H434" s="71" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
@@ -28689,7 +28686,7 @@
     <row r="435" spans="1:22" ht="27.6" hidden="1">
       <c r="A435" s="98"/>
       <c r="B435" s="71" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C435" s="66" t="s">
         <v>42</v>
@@ -28699,7 +28696,7 @@
       </c>
       <c r="E435" s="81"/>
       <c r="F435" s="71" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G435" s="71" t="s">
         <v>398</v>
@@ -28722,10 +28719,10 @@
       <c r="U435" s="105"/>
       <c r="V435" s="87"/>
     </row>
-    <row r="436" spans="1:22" ht="13.8" hidden="1">
+    <row r="436" spans="1:22" ht="13.9" hidden="1">
       <c r="A436" s="98"/>
       <c r="B436" s="71" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C436" s="66" t="s">
         <v>42</v>
@@ -28734,7 +28731,7 @@
         <v>43</v>
       </c>
       <c r="E436" s="81" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F436" s="71" t="s">
         <v>267</v>
@@ -28777,10 +28774,10 @@
         <v>345</v>
       </c>
     </row>
-    <row r="437" spans="1:22" ht="13.8" hidden="1">
+    <row r="437" spans="1:22" ht="13.9" hidden="1">
       <c r="A437" s="98"/>
       <c r="B437" s="71" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C437" s="66" t="s">
         <v>42</v>
@@ -28795,7 +28792,7 @@
         <v>210</v>
       </c>
       <c r="G437" s="71" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H437" s="71">
         <v>46.45</v>
@@ -28832,10 +28829,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="438" spans="1:22" ht="13.8" hidden="1">
+    <row r="438" spans="1:22" ht="13.9" hidden="1">
       <c r="A438" s="98"/>
       <c r="B438" s="71" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C438" s="66" t="s">
         <v>42</v>
@@ -28845,7 +28842,7 @@
       </c>
       <c r="E438" s="81"/>
       <c r="F438" s="71" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G438" s="71" t="s">
         <v>673</v>
@@ -28888,7 +28885,7 @@
     <row r="439" spans="1:22" ht="27.6" hidden="1">
       <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C439" s="66" t="s">
         <v>42</v>
@@ -28901,10 +28898,10 @@
         <v>103</v>
       </c>
       <c r="G439" s="71" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H439" s="71" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I439" s="71"/>
       <c r="J439" s="71"/>
@@ -28944,7 +28941,7 @@
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C440" s="66" t="s">
         <v>86</v>
@@ -28954,10 +28951,10 @@
       </c>
       <c r="E440" s="81"/>
       <c r="F440" s="71" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="G440" s="71" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H440" s="71">
         <v>6.29</v>
@@ -28997,7 +28994,7 @@
     <row r="441" spans="1:22" ht="57" hidden="1" customHeight="1">
       <c r="A441" s="98"/>
       <c r="B441" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C441" s="66" t="s">
         <v>86</v>
@@ -29010,13 +29007,13 @@
         <v>438</v>
       </c>
       <c r="G441" s="66" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H441" s="66"/>
       <c r="I441" s="66"/>
       <c r="J441" s="66"/>
       <c r="K441" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L441" s="2">
         <v>0</v>
@@ -29049,7 +29046,7 @@
     <row r="442" spans="1:22" ht="36.6" hidden="1" customHeight="1">
       <c r="A442" s="98"/>
       <c r="B442" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C442" s="66" t="s">
         <v>86</v>
@@ -29105,7 +29102,7 @@
     <row r="443" spans="1:22" ht="36.6" hidden="1" customHeight="1">
       <c r="A443" s="98"/>
       <c r="B443" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C443" s="66" t="s">
         <v>86</v>
@@ -29120,7 +29117,7 @@
         <v>210</v>
       </c>
       <c r="G443" s="66" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H443" s="66">
         <v>46.5</v>
@@ -29157,10 +29154,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="444" spans="1:22" ht="64.95" hidden="1" customHeight="1">
+    <row r="444" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
       <c r="A444" s="98"/>
       <c r="B444" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C444" s="66" t="s">
         <v>86</v>
@@ -29172,10 +29169,10 @@
         <v>4600016804</v>
       </c>
       <c r="F444" s="71" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G444" s="66" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H444" s="66">
         <v>6.87</v>
@@ -29207,13 +29204,13 @@
       <c r="T444" s="66"/>
       <c r="U444" s="16"/>
       <c r="V444" s="71" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="445" spans="1:22" ht="36.6" hidden="1" customHeight="1">
       <c r="A445" s="98"/>
       <c r="B445" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C445" s="66" t="s">
         <v>86</v>
@@ -29223,7 +29220,7 @@
       </c>
       <c r="E445" s="81"/>
       <c r="F445" s="71" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G445" s="66" t="s">
         <v>392</v>
@@ -29264,7 +29261,7 @@
     <row r="446" spans="1:22" ht="36.6" hidden="1" customHeight="1">
       <c r="A446" s="98"/>
       <c r="B446" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C446" s="66" t="s">
         <v>86</v>
@@ -29276,7 +29273,7 @@
         <v>2025003050044</v>
       </c>
       <c r="F446" s="71" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G446" s="66" t="s">
         <v>203</v>
@@ -29302,7 +29299,7 @@
     <row r="447" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C447" s="66" t="s">
         <v>86</v>
@@ -29314,7 +29311,7 @@
         <v>2024057890040</v>
       </c>
       <c r="F447" s="71" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G447" s="66" t="s">
         <v>475</v>
@@ -29357,7 +29354,7 @@
     <row r="448" spans="1:22" ht="27.6" hidden="1">
       <c r="A448" s="87"/>
       <c r="B448" s="71" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C448" s="66" t="s">
         <v>294</v>
@@ -29369,10 +29366,10 @@
         <v>2025003050040</v>
       </c>
       <c r="F448" s="71" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G448" s="71" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H448" s="71"/>
       <c r="I448" s="71" t="s">
@@ -29408,13 +29405,13 @@
       <c r="T448" s="66"/>
       <c r="U448" s="80"/>
       <c r="V448" s="71" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="449" spans="1:22" ht="41.4" hidden="1">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="449" spans="1:22" ht="41.45" hidden="1">
       <c r="A449" s="87"/>
       <c r="B449" s="51" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C449" s="52" t="s">
         <v>294</v>
@@ -29423,10 +29420,10 @@
         <v>43</v>
       </c>
       <c r="E449" s="53" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F449" s="51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G449" s="52" t="s">
         <v>79</v>
@@ -29469,7 +29466,7 @@
         <v>0.33</v>
       </c>
       <c r="V449" s="51" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="450" spans="1:22" ht="27.6" hidden="1">
@@ -29477,7 +29474,7 @@
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C450" s="66" t="s">
         <v>86</v>
@@ -29489,10 +29486,10 @@
         <v>2022003050024</v>
       </c>
       <c r="F450" s="71" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G450" s="66" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H450" s="66">
         <v>1.7</v>
@@ -29532,7 +29529,7 @@
     <row r="451" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A451" s="98"/>
       <c r="B451" s="71" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C451" s="66" t="s">
         <v>86</v>
@@ -29547,7 +29544,7 @@
         <v>210</v>
       </c>
       <c r="G451" s="66" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H451" s="66">
         <v>50.3</v>
@@ -29587,7 +29584,7 @@
     <row r="452" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A452" s="98"/>
       <c r="B452" s="71" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C452" s="66" t="s">
         <v>86</v>
@@ -29602,7 +29599,7 @@
         <v>455</v>
       </c>
       <c r="G452" s="66" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H452" s="66"/>
       <c r="I452" s="71" t="s">
@@ -29646,7 +29643,7 @@
     <row r="453" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C453" s="66" t="s">
         <v>86</v>
@@ -29655,13 +29652,13 @@
         <v>43</v>
       </c>
       <c r="E453" s="81" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F453" s="71" t="s">
         <v>83</v>
       </c>
       <c r="G453" s="66" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H453" s="66">
         <v>0.6</v>
@@ -29703,7 +29700,7 @@
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C454" s="66" t="s">
         <v>86</v>
@@ -29718,10 +29715,10 @@
         <v>103</v>
       </c>
       <c r="G454" s="66" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H454" s="66" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="I454" s="66" t="s">
         <v>27</v>
@@ -29760,16 +29757,16 @@
         <v>156</v>
       </c>
     </row>
-    <row r="455" spans="1:22" ht="13.8" hidden="1">
+    <row r="455" spans="1:22" ht="13.9" hidden="1">
       <c r="A455" s="87"/>
       <c r="B455" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C455" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D455" s="66" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E455" s="81" t="s">
         <v>148</v>
@@ -29819,7 +29816,7 @@
     <row r="456" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A456" s="87"/>
       <c r="B456" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C456" s="66" t="s">
         <v>86</v>
@@ -29834,7 +29831,7 @@
         <v>78</v>
       </c>
       <c r="G456" s="66" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H456" s="66">
         <v>1.2</v>
@@ -29879,7 +29876,7 @@
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C457" s="66" t="s">
         <v>151</v>
@@ -29891,10 +29888,10 @@
         <v>2026003050015</v>
       </c>
       <c r="F457" s="71" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G457" s="66" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H457" s="66"/>
       <c r="I457" s="66"/>
@@ -29928,10 +29925,10 @@
         <v>593</v>
       </c>
     </row>
-    <row r="458" spans="1:22" ht="13.8" hidden="1">
+    <row r="458" spans="1:22" ht="13.9" hidden="1">
       <c r="A458" s="87"/>
       <c r="B458" s="71" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C458" s="66" t="s">
         <v>151</v>
@@ -29944,7 +29941,7 @@
         <v>103</v>
       </c>
       <c r="G458" s="66" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H458" s="66">
         <v>10</v>
@@ -29982,10 +29979,10 @@
         <v>156</v>
       </c>
     </row>
-    <row r="459" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="459" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A459" s="87"/>
       <c r="B459" s="71" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C459" s="66" t="s">
         <v>151</v>
@@ -29994,7 +29991,7 @@
         <v>43</v>
       </c>
       <c r="E459" s="81" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F459" s="71" t="s">
         <v>267</v>
@@ -30037,10 +30034,10 @@
       </c>
       <c r="V459" s="66"/>
     </row>
-    <row r="460" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="460" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A460" s="87"/>
       <c r="B460" s="71" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C460" s="66" t="s">
         <v>151</v>
@@ -30052,7 +30049,7 @@
         <v>2025003050053</v>
       </c>
       <c r="F460" s="71" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G460" s="66" t="s">
         <v>79</v>
@@ -30089,7 +30086,7 @@
     <row r="461" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A461" s="87"/>
       <c r="B461" s="71" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C461" s="66" t="s">
         <v>151</v>
@@ -30098,7 +30095,7 @@
         <v>43</v>
       </c>
       <c r="E461" s="81" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F461" s="71" t="s">
         <v>83</v>
@@ -30143,10 +30140,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="462" spans="1:22" ht="55.2" hidden="1">
+    <row r="462" spans="1:22" ht="55.15" hidden="1">
       <c r="A462" s="66"/>
       <c r="B462" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C462" s="66" t="s">
         <v>183</v>
@@ -30161,7 +30158,7 @@
         <v>455</v>
       </c>
       <c r="G462" s="71" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H462" s="71"/>
       <c r="I462" s="71" t="s">
@@ -30200,10 +30197,10 @@
         <v>138</v>
       </c>
     </row>
-    <row r="463" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="463" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A463" s="66"/>
       <c r="B463" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C463" s="66" t="s">
         <v>183</v>
@@ -30212,10 +30209,10 @@
         <v>43</v>
       </c>
       <c r="E463" s="81" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F463" s="71" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G463" s="71" t="s">
         <v>206</v>
@@ -30255,10 +30252,10 @@
       </c>
       <c r="V463" s="71"/>
     </row>
-    <row r="464" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="464" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A464" s="66"/>
       <c r="B464" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C464" s="66" t="s">
         <v>183</v>
@@ -30267,10 +30264,10 @@
         <v>43</v>
       </c>
       <c r="E464" s="81" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F464" s="71" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G464" s="71" t="s">
         <v>206</v>
@@ -30310,10 +30307,10 @@
       </c>
       <c r="V464" s="71"/>
     </row>
-    <row r="465" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="465" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A465" s="66"/>
       <c r="B465" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C465" s="66" t="s">
         <v>183</v>
@@ -30325,13 +30322,13 @@
         <v>2025003050039</v>
       </c>
       <c r="F465" s="71" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G465" s="71" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H465" s="71" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="I465" s="71"/>
       <c r="J465" s="71"/>
@@ -30363,10 +30360,10 @@
       <c r="U465" s="80"/>
       <c r="V465" s="71"/>
     </row>
-    <row r="466" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="466" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A466" s="66"/>
       <c r="B466" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C466" s="66" t="s">
         <v>183</v>
@@ -30375,10 +30372,10 @@
         <v>43</v>
       </c>
       <c r="E466" s="81" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F466" s="71" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G466" s="71" t="s">
         <v>206</v>
@@ -30423,7 +30420,7 @@
         <v>114</v>
       </c>
       <c r="B467" s="71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C467" s="66" t="s">
         <v>183</v>
@@ -30477,7 +30474,7 @@
     <row r="468" spans="1:22" ht="33.6" hidden="1" customHeight="1">
       <c r="A468" s="98"/>
       <c r="B468" s="71" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C468" s="66" t="s">
         <v>42</v>
@@ -30538,10 +30535,10 @@
         <v>43</v>
       </c>
       <c r="E469" s="81" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F469" s="71" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G469" s="66" t="s">
         <v>206</v>
@@ -30571,7 +30568,7 @@
         <v>2025</v>
       </c>
       <c r="Q469" s="66" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="R469" s="66"/>
       <c r="S469" s="66"/>
@@ -30593,10 +30590,10 @@
         <v>43</v>
       </c>
       <c r="E470" s="81" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F470" s="71" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G470" s="66" t="s">
         <v>206</v>
@@ -30648,10 +30645,10 @@
         <v>43</v>
       </c>
       <c r="E471" s="81" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F471" s="71" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G471" s="66" t="s">
         <v>206</v>
@@ -30703,7 +30700,7 @@
         <v>43</v>
       </c>
       <c r="E472" s="81" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F472" s="71" t="s">
         <v>267</v>
@@ -30759,10 +30756,10 @@
       <c r="D473" s="66"/>
       <c r="E473" s="81"/>
       <c r="F473" s="71" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G473" s="66" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H473" s="66">
         <v>9.39</v>
@@ -30804,7 +30801,7 @@
     <row r="474" spans="1:22" ht="39" hidden="1" customHeight="1">
       <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C474" s="66" t="s">
         <v>42</v>
@@ -30814,7 +30811,7 @@
       </c>
       <c r="E474" s="81"/>
       <c r="F474" s="71" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G474" s="66" t="s">
         <v>309</v>
@@ -30857,7 +30854,7 @@
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C475" s="66" t="s">
         <v>86</v>
@@ -30872,10 +30869,10 @@
         <v>177</v>
       </c>
       <c r="G475" s="71" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H475" s="71" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
@@ -30912,7 +30909,7 @@
     <row r="476" spans="1:22" ht="39" hidden="1" customHeight="1">
       <c r="A476" s="87"/>
       <c r="B476" s="71" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C476" s="66" t="s">
         <v>86</v>
@@ -30925,10 +30922,10 @@
         <v>177</v>
       </c>
       <c r="G476" s="71" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H476" s="71" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
@@ -30956,7 +30953,7 @@
     <row r="477" spans="1:22" ht="39" hidden="1" customHeight="1">
       <c r="A477" s="87"/>
       <c r="B477" s="71" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C477" s="66" t="s">
         <v>86</v>
@@ -31015,7 +31012,7 @@
     <row r="478" spans="1:22" ht="36" hidden="1" customHeight="1">
       <c r="A478" s="87"/>
       <c r="B478" s="71" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C478" s="66" t="s">
         <v>86</v>
@@ -31073,7 +31070,7 @@
         <v>118</v>
       </c>
       <c r="B479" s="71" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C479" s="66" t="s">
         <v>86</v>
@@ -31086,10 +31083,10 @@
         <v>103</v>
       </c>
       <c r="G479" s="66" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H479" s="66" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="I479" s="66"/>
       <c r="J479" s="66"/>
@@ -31127,7 +31124,7 @@
     <row r="480" spans="1:22" ht="36" hidden="1" customHeight="1">
       <c r="A480" s="66"/>
       <c r="B480" s="71" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C480" s="66" t="s">
         <v>93</v>
@@ -31182,7 +31179,7 @@
     <row r="481" spans="1:22" ht="36" hidden="1" customHeight="1">
       <c r="A481" s="66"/>
       <c r="B481" s="71" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C481" s="66" t="s">
         <v>93</v>
@@ -31192,10 +31189,10 @@
       </c>
       <c r="E481" s="81"/>
       <c r="F481" s="71" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G481" s="66" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H481" s="66"/>
       <c r="I481" s="66"/>
@@ -31237,7 +31234,7 @@
         <v>119</v>
       </c>
       <c r="B482" s="71" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C482" s="66" t="s">
         <v>93</v>
@@ -31246,7 +31243,7 @@
         <v>43</v>
       </c>
       <c r="E482" s="81" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F482" s="71" t="s">
         <v>402</v>
@@ -31288,13 +31285,13 @@
         <v>1</v>
       </c>
       <c r="V482" s="66" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="483" spans="1:22" ht="35.4" hidden="1" customHeight="1">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="483" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
       <c r="A483" s="66"/>
       <c r="B483" s="71" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C483" s="66" t="s">
         <v>86</v>
@@ -31306,13 +31303,13 @@
         <v>2026003050012</v>
       </c>
       <c r="F483" s="71" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G483" s="71" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H483" s="71" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="I483" s="71"/>
       <c r="J483" s="71"/>
@@ -31346,10 +31343,10 @@
         <v>593</v>
       </c>
     </row>
-    <row r="484" spans="1:22" ht="38.4" hidden="1" customHeight="1">
+    <row r="484" spans="1:22" ht="38.450000000000003" hidden="1" customHeight="1">
       <c r="A484" s="66"/>
       <c r="B484" s="71" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C484" s="66" t="s">
         <v>86</v>
@@ -31362,10 +31359,10 @@
         <v>646</v>
       </c>
       <c r="G484" s="71" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H484" s="71" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="I484" s="71"/>
       <c r="J484" s="71"/>
@@ -31404,7 +31401,7 @@
         <v>120</v>
       </c>
       <c r="B485" s="71" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C485" s="66" t="s">
         <v>86</v>
@@ -31460,7 +31457,7 @@
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C486" s="66" t="s">
         <v>183</v>
@@ -31469,13 +31466,13 @@
         <v>43</v>
       </c>
       <c r="E486" s="81" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F486" s="71" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G486" s="66" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H486" s="66">
         <v>0.14000000000000001</v>
@@ -31515,23 +31512,23 @@
     <row r="487" spans="1:22" ht="36" hidden="1" customHeight="1">
       <c r="A487" s="87"/>
       <c r="B487" s="71" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C487" s="66" t="s">
         <v>183</v>
       </c>
       <c r="D487" s="66" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E487" s="81"/>
       <c r="F487" s="71" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G487" s="66" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H487" s="66" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I487" s="66"/>
       <c r="J487" s="66"/>
@@ -31568,7 +31565,7 @@
     <row r="488" spans="1:22" ht="96.6" hidden="1">
       <c r="A488" s="87"/>
       <c r="B488" s="71" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C488" s="66" t="s">
         <v>183</v>
@@ -31578,7 +31575,7 @@
       </c>
       <c r="E488" s="81"/>
       <c r="F488" s="71" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G488" s="66" t="s">
         <v>79</v>
@@ -31608,7 +31605,7 @@
         <v>2024</v>
       </c>
       <c r="Q488" s="66" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="R488" s="66"/>
       <c r="S488" s="66"/>
@@ -31617,13 +31614,13 @@
         <v>0.6</v>
       </c>
       <c r="V488" s="71" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="489" spans="1:22" ht="36" hidden="1" customHeight="1">
       <c r="A489" s="68"/>
       <c r="B489" s="71" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C489" s="66" t="s">
         <v>93</v>
@@ -31675,12 +31672,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="490" spans="1:22" ht="13.8" hidden="1">
+    <row r="490" spans="1:22" ht="13.9" hidden="1">
       <c r="A490" s="68">
         <v>122</v>
       </c>
       <c r="B490" s="71" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C490" s="66" t="s">
         <v>93</v>
@@ -31689,7 +31686,7 @@
         <v>43</v>
       </c>
       <c r="E490" s="81" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F490" s="71" t="s">
         <v>83</v>
@@ -31732,10 +31729,10 @@
       </c>
       <c r="V490" s="71"/>
     </row>
-    <row r="491" spans="1:22" ht="13.8" hidden="1">
+    <row r="491" spans="1:22" ht="13.9" hidden="1">
       <c r="A491" s="98"/>
       <c r="B491" s="71" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C491" s="66" t="s">
         <v>93</v>
@@ -31744,7 +31741,7 @@
         <v>43</v>
       </c>
       <c r="E491" s="81" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F491" s="71" t="s">
         <v>78</v>
@@ -31787,10 +31784,10 @@
       </c>
       <c r="V491" s="71"/>
     </row>
-    <row r="492" spans="1:22" ht="13.8" hidden="1">
+    <row r="492" spans="1:22" ht="13.9" hidden="1">
       <c r="A492" s="98"/>
       <c r="B492" s="71" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C492" s="66" t="s">
         <v>93</v>
@@ -31799,10 +31796,10 @@
         <v>43</v>
       </c>
       <c r="E492" s="81" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F492" s="71" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G492" s="66" t="s">
         <v>401</v>
@@ -31842,10 +31839,10 @@
       </c>
       <c r="V492" s="71"/>
     </row>
-    <row r="493" spans="1:22" ht="55.2" hidden="1">
+    <row r="493" spans="1:22" ht="55.15" hidden="1">
       <c r="A493" s="98"/>
       <c r="B493" s="71" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C493" s="66" t="s">
         <v>93</v>
@@ -31857,10 +31854,10 @@
         <v>2026003050013</v>
       </c>
       <c r="F493" s="66" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G493" s="71" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H493" s="71"/>
       <c r="I493" s="71"/>
@@ -31891,13 +31888,13 @@
       <c r="T493" s="66"/>
       <c r="U493" s="80"/>
       <c r="V493" s="71" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="494" spans="1:22" ht="15" hidden="1" customHeight="1">
       <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C494" s="66" t="s">
         <v>93</v>
@@ -31906,13 +31903,13 @@
         <v>43</v>
       </c>
       <c r="E494" s="81" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F494" s="71" t="s">
         <v>83</v>
       </c>
       <c r="G494" s="66" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H494" s="66">
         <v>2</v>
@@ -31954,7 +31951,7 @@
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C495" s="66" t="s">
         <v>151</v>
@@ -31963,7 +31960,7 @@
         <v>43</v>
       </c>
       <c r="E495" s="81" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F495" s="71" t="s">
         <v>83</v>
@@ -32011,7 +32008,7 @@
     <row r="496" spans="1:22" ht="27.6" hidden="1">
       <c r="A496" s="87"/>
       <c r="B496" s="71" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C496" s="66" t="s">
         <v>151</v>
@@ -32023,13 +32020,13 @@
         <v>64</v>
       </c>
       <c r="F496" s="71" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G496" s="71" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H496" s="71" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="I496" s="71"/>
       <c r="J496" s="71"/>
@@ -32061,10 +32058,10 @@
         <v>250</v>
       </c>
     </row>
-    <row r="497" spans="1:22" ht="13.8" hidden="1">
+    <row r="497" spans="1:22" ht="13.9" hidden="1">
       <c r="A497" s="87"/>
       <c r="B497" s="71" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C497" s="66" t="s">
         <v>151</v>
@@ -32074,13 +32071,13 @@
       </c>
       <c r="E497" s="81"/>
       <c r="F497" s="71" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G497" s="71" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H497" s="71" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I497" s="71"/>
       <c r="J497" s="71"/>
@@ -32116,10 +32113,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="498" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="498" spans="1:22" ht="40.15" hidden="1" customHeight="1">
       <c r="A498" s="87"/>
       <c r="B498" s="71" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C498" s="66" t="s">
         <v>151</v>
@@ -32172,10 +32169,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="499" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="499" spans="1:22" ht="40.15" hidden="1" customHeight="1">
       <c r="A499" s="66"/>
       <c r="B499" s="71" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C499" s="66" t="s">
         <v>338</v>
@@ -32238,7 +32235,7 @@
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C500" s="71" t="s">
         <v>338</v>
@@ -32253,7 +32250,7 @@
         <v>103</v>
       </c>
       <c r="G500" s="66" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H500" s="66">
         <v>30</v>
@@ -32292,13 +32289,13 @@
       <c r="T500" s="66"/>
       <c r="U500" s="80"/>
       <c r="V500" s="71" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="501" spans="1:22" ht="13.8" hidden="1">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="501" spans="1:22" ht="13.9" hidden="1">
       <c r="A501" s="88"/>
       <c r="B501" s="71" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C501" s="71" t="s">
         <v>338</v>
@@ -32310,10 +32307,10 @@
         <v>64</v>
       </c>
       <c r="F501" s="71" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G501" s="66" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H501" s="66">
         <v>9</v>
@@ -32350,7 +32347,7 @@
     <row r="502" spans="1:22" ht="78" hidden="1" customHeight="1">
       <c r="A502" s="88"/>
       <c r="B502" s="71" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C502" s="71" t="s">
         <v>338</v>
@@ -32362,10 +32359,10 @@
         <v>64</v>
       </c>
       <c r="F502" s="71" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G502" s="71" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H502" s="71">
         <v>10</v>
@@ -32401,15 +32398,15 @@
       <c r="T502" s="66"/>
       <c r="U502" s="66"/>
       <c r="V502" s="71" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="503" spans="1:22" ht="41.4" hidden="1">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="503" spans="1:22" ht="41.45" hidden="1">
       <c r="A503" s="87">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C503" s="66" t="s">
         <v>294</v>
@@ -32421,10 +32418,10 @@
         <v>20240214000273</v>
       </c>
       <c r="F503" s="71" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G503" s="71" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H503" s="71">
         <v>2.8</v>
@@ -32464,13 +32461,13 @@
         <v>0</v>
       </c>
       <c r="V503" s="71" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="504" spans="1:22" ht="13.8" hidden="1">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="504" spans="1:22" ht="13.9" hidden="1">
       <c r="A504" s="87"/>
       <c r="B504" s="71" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C504" s="66" t="s">
         <v>294</v>
@@ -32479,7 +32476,7 @@
         <v>43</v>
       </c>
       <c r="E504" s="81" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F504" s="71" t="s">
         <v>267</v>
@@ -32526,10 +32523,10 @@
       </c>
       <c r="V504" s="71"/>
     </row>
-    <row r="505" spans="1:22" ht="55.2" hidden="1">
+    <row r="505" spans="1:22" ht="55.15" hidden="1">
       <c r="A505" s="87"/>
       <c r="B505" s="51" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C505" s="52" t="s">
         <v>294</v>
@@ -32538,10 +32535,10 @@
         <v>43</v>
       </c>
       <c r="E505" s="53" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F505" s="51" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G505" s="52">
         <v>0</v>
@@ -32582,15 +32579,15 @@
         <v>0</v>
       </c>
       <c r="V505" s="51" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="506" spans="1:22" ht="55.95" hidden="1" customHeight="1">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="506" spans="1:22" ht="55.9" hidden="1" customHeight="1">
       <c r="K506" s="27"/>
       <c r="M506" s="56"/>
       <c r="U506" s="57"/>
     </row>
-    <row r="507" spans="1:22" ht="13.8" hidden="1">
+    <row r="507" spans="1:22" ht="13.9" hidden="1">
       <c r="E507" s="55" t="s">
         <v>715</v>
       </c>
@@ -32600,11 +32597,11 @@
     <row r="508" spans="1:22" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>24.185000000000002</v>
+        <v>1</v>
       </c>
       <c r="K508" s="8">
         <f>SUBTOTAL(9,K96:K507)</f>
-        <v>54029783587.699997</v>
+        <v>10119116844</v>
       </c>
       <c r="M508" s="58"/>
       <c r="U508" s="29"/>
@@ -32662,7 +32659,8 @@
   <autoFilter ref="A2:V507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Salgar"/>
+        <filter val="Cisneros"/>
+        <filter val="(No vacías)"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -32817,46 +32815,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE741C3-3798-4F4E-8B25-FDCA2ADDEF39}">
   <dimension ref="B2:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="12"/>
-    <col min="2" max="2" width="15.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
     <col min="5" max="5" width="19" style="20" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="12"/>
-    <col min="11" max="11" width="9.33203125" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="12"/>
+    <col min="6" max="6" width="9.5703125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="12"/>
+    <col min="11" max="11" width="9.28515625" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="27.6">
       <c r="B2" s="106" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C2" s="106"/>
       <c r="D2" s="23" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="48" customHeight="1">
       <c r="B3" s="14" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D3" s="17">
         <v>108554215084</v>
@@ -32878,10 +32876,10 @@
     </row>
     <row r="4" spans="2:9" ht="48" customHeight="1">
       <c r="B4" s="15" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D4" s="19">
         <v>104855613958</v>
@@ -32903,10 +32901,10 @@
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="15" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D5" s="19">
         <v>144973755369</v>
@@ -32924,10 +32922,10 @@
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="15" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D6" s="19">
         <v>54441800920</v>
@@ -32945,10 +32943,10 @@
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="15" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D7" s="19">
         <v>72870090400</v>
@@ -32967,10 +32965,10 @@
     </row>
     <row r="8" spans="2:9" ht="48" customHeight="1">
       <c r="B8" s="15" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D8" s="19">
         <v>57385592096</v>
@@ -32988,10 +32986,10 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="15" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D9" s="19">
         <v>26362070969</v>
@@ -33009,10 +33007,10 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="15" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D10" s="19">
         <v>124487403196</v>
@@ -33217,37 +33215,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}"/>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9504531B-B8C7-4BD4-9A8C-BCB37249954E}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B10DA5-E19F-4807-B1C6-272EAAAA8A0D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4021,14 +4024,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -4247,7 +4250,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="107">
@@ -4255,34 +4258,34 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4296,42 +4299,42 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4355,7 +4358,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4364,13 +4367,13 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4382,7 +4385,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4391,7 +4394,7 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4403,25 +4406,25 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4433,10 +4436,10 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4448,7 +4451,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4478,7 +4481,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4487,55 +4490,31 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4550,14 +4529,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4587,10 +4590,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4628,7 +4635,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4734,7 +4741,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4876,7 +4883,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4886,40 +4893,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X521"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="33" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="33" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" style="55" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="49.140625" style="33" customWidth="1"/>
-    <col min="7" max="7" width="48.28515625" style="33" customWidth="1"/>
-    <col min="8" max="8" width="35.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="33" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" style="33" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" style="7" customWidth="1"/>
-    <col min="12" max="12" width="25.85546875" style="56" customWidth="1"/>
-    <col min="13" max="13" width="24.28515625" style="33" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="33" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="33" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" style="33" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="55" customWidth="1"/>
+    <col min="6" max="6" width="49.109375" style="33" customWidth="1"/>
+    <col min="7" max="7" width="48.33203125" style="33" customWidth="1"/>
+    <col min="8" max="8" width="35.5546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="33" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" style="33" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="25.88671875" style="56" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" style="33" customWidth="1"/>
     <col min="14" max="14" width="26" style="33" customWidth="1"/>
-    <col min="15" max="15" width="32.5703125" style="33" customWidth="1"/>
-    <col min="16" max="16" width="19.140625" style="33" customWidth="1"/>
-    <col min="17" max="17" width="20.5703125" style="33" customWidth="1"/>
-    <col min="18" max="18" width="20.5703125" style="33" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="29.28515625" style="33" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="29.140625" style="33" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" style="59" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="39.5703125" style="33" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" style="29" customWidth="1"/>
-    <col min="24" max="24" width="24.28515625" style="33" customWidth="1"/>
-    <col min="25" max="16384" width="10.85546875" style="33"/>
+    <col min="15" max="15" width="32.5546875" style="33" customWidth="1"/>
+    <col min="16" max="16" width="19.109375" style="33" customWidth="1"/>
+    <col min="17" max="17" width="20.5546875" style="33" customWidth="1"/>
+    <col min="18" max="18" width="20.5546875" style="33" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="29.33203125" style="33" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="29.109375" style="33" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="19.109375" style="59" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="39.5546875" style="33" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" style="29" customWidth="1"/>
+    <col min="24" max="24" width="24.33203125" style="33" customWidth="1"/>
+    <col min="25" max="16384" width="10.88671875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="13.9" hidden="1">
-      <c r="B1" s="97" t="s">
+    <row r="1" spans="1:24" ht="13.8" hidden="1">
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="97"/>
+      <c r="C1" s="99"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -4940,7 +4947,7 @@
       <c r="U1" s="78"/>
       <c r="V1" s="73"/>
     </row>
-    <row r="2" spans="1:24" ht="21.75">
+    <row r="2" spans="1:24" ht="13.8">
       <c r="A2" s="75"/>
       <c r="B2" s="35" t="s">
         <v>1</v>
@@ -5007,8 +5014,8 @@
       </c>
       <c r="X2" s="13"/>
     </row>
-    <row r="3" spans="1:24" ht="62.45" hidden="1" customHeight="1">
-      <c r="A3" s="94">
+    <row r="3" spans="1:24" ht="62.4" hidden="1" customHeight="1">
+      <c r="A3" s="86">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5071,8 +5078,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="62.45" hidden="1" customHeight="1">
-      <c r="A4" s="94"/>
+    <row r="4" spans="1:24" ht="62.4" hidden="1" customHeight="1">
+      <c r="A4" s="86"/>
       <c r="B4" s="71" t="s">
         <v>22</v>
       </c>
@@ -5133,8 +5140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="41.45" hidden="1">
-      <c r="A5" s="94"/>
+    <row r="5" spans="1:24" ht="41.4" hidden="1">
+      <c r="A5" s="86"/>
       <c r="B5" s="66" t="s">
         <v>22</v>
       </c>
@@ -5243,8 +5250,8 @@
       </c>
       <c r="V6" s="66"/>
     </row>
-    <row r="7" spans="1:24" ht="13.9" hidden="1">
-      <c r="A7" s="93">
+    <row r="7" spans="1:24" ht="13.8" hidden="1">
+      <c r="A7" s="90">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5279,8 +5286,8 @@
       <c r="U7" s="66"/>
       <c r="V7" s="66"/>
     </row>
-    <row r="8" spans="1:24" ht="13.9" hidden="1">
-      <c r="A8" s="98"/>
+    <row r="8" spans="1:24" ht="13.8" hidden="1">
+      <c r="A8" s="85"/>
       <c r="B8" s="71" t="s">
         <v>41</v>
       </c>
@@ -5332,8 +5339,8 @@
       </c>
       <c r="V8" s="66"/>
     </row>
-    <row r="9" spans="1:24" ht="41.45" hidden="1">
-      <c r="A9" s="98"/>
+    <row r="9" spans="1:24" ht="41.4" hidden="1">
+      <c r="A9" s="85"/>
       <c r="B9" s="71" t="s">
         <v>41</v>
       </c>
@@ -5391,8 +5398,8 @@
       </c>
       <c r="V9" s="66"/>
     </row>
-    <row r="10" spans="1:24" ht="41.45" hidden="1">
-      <c r="A10" s="94"/>
+    <row r="10" spans="1:24" ht="41.4" hidden="1">
+      <c r="A10" s="86"/>
       <c r="B10" s="66" t="s">
         <v>41</v>
       </c>
@@ -5451,7 +5458,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" ht="27.6" hidden="1">
-      <c r="A11" s="87">
+      <c r="A11" s="84">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5514,8 +5521,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="52.9" hidden="1" customHeight="1">
-      <c r="A12" s="87"/>
+    <row r="12" spans="1:24" ht="52.95" hidden="1" customHeight="1">
+      <c r="A12" s="84"/>
       <c r="B12" s="71" t="s">
         <v>59</v>
       </c>
@@ -5571,8 +5578,8 @@
       </c>
       <c r="V12" s="76"/>
     </row>
-    <row r="13" spans="1:24" ht="13.9" hidden="1">
-      <c r="A13" s="87"/>
+    <row r="13" spans="1:24" ht="13.8" hidden="1">
+      <c r="A13" s="84"/>
       <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
@@ -5628,8 +5635,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="13.9" hidden="1">
-      <c r="A14" s="87"/>
+    <row r="14" spans="1:24" ht="13.8" hidden="1">
+      <c r="A14" s="84"/>
       <c r="B14" s="71" t="s">
         <v>59</v>
       </c>
@@ -5685,8 +5692,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="13.9" hidden="1">
-      <c r="A15" s="87"/>
+    <row r="15" spans="1:24" ht="13.8" hidden="1">
+      <c r="A15" s="84"/>
       <c r="B15" s="71" t="s">
         <v>59</v>
       </c>
@@ -5743,7 +5750,7 @@
       <c r="V15" s="66"/>
     </row>
     <row r="16" spans="1:24" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="87"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="71" t="s">
         <v>59</v>
       </c>
@@ -5799,7 +5806,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="13.9" hidden="1">
+    <row r="17" spans="1:22" ht="13.8" hidden="1">
       <c r="A17" s="66"/>
       <c r="B17" s="71" t="s">
         <v>85</v>
@@ -5841,7 +5848,7 @@
       <c r="U17" s="80"/>
       <c r="V17" s="71"/>
     </row>
-    <row r="18" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+    <row r="18" spans="1:22" ht="61.2" hidden="1" customHeight="1">
       <c r="A18" s="66">
         <v>4</v>
       </c>
@@ -5902,7 +5909,7 @@
       </c>
       <c r="V18" s="71"/>
     </row>
-    <row r="19" spans="1:22" ht="41.45" hidden="1">
+    <row r="19" spans="1:22" ht="41.4" hidden="1">
       <c r="A19" s="66"/>
       <c r="B19" s="71" t="s">
         <v>92</v>
@@ -5963,8 +5970,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="97.9" hidden="1" customHeight="1">
-      <c r="A20" s="87">
+    <row r="20" spans="1:22" ht="97.95" hidden="1" customHeight="1">
+      <c r="A20" s="84">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6026,8 +6033,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A21" s="84"/>
       <c r="B21" s="71" t="s">
         <v>92</v>
       </c>
@@ -6086,7 +6093,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="27.6" hidden="1">
-      <c r="A22" s="87"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="71" t="s">
         <v>92</v>
       </c>
@@ -6145,8 +6152,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="13.9" hidden="1">
-      <c r="A23" s="87"/>
+    <row r="23" spans="1:22" ht="13.8" hidden="1">
+      <c r="A23" s="84"/>
       <c r="B23" s="71" t="s">
         <v>92</v>
       </c>
@@ -6204,7 +6211,7 @@
       <c r="V23" s="71"/>
     </row>
     <row r="24" spans="1:22" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="87">
+      <c r="A24" s="84">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6265,8 +6272,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="13.9" hidden="1">
-      <c r="A25" s="87"/>
+    <row r="25" spans="1:22" ht="13.8" hidden="1">
+      <c r="A25" s="84"/>
       <c r="B25" s="71" t="s">
         <v>109</v>
       </c>
@@ -6322,8 +6329,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="70.150000000000006" hidden="1" customHeight="1">
-      <c r="A26" s="87"/>
+    <row r="26" spans="1:22" ht="70.2" hidden="1" customHeight="1">
+      <c r="A26" s="84"/>
       <c r="B26" s="71" t="s">
         <v>109</v>
       </c>
@@ -6379,8 +6386,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A27" s="87"/>
+    <row r="27" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A27" s="84"/>
       <c r="B27" s="71" t="s">
         <v>109</v>
       </c>
@@ -6438,8 +6445,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="13.9" hidden="1">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:22" ht="13.8" hidden="1">
+      <c r="A28" s="84"/>
       <c r="B28" s="71" t="s">
         <v>109</v>
       </c>
@@ -6494,7 +6501,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="87"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="71" t="s">
         <v>109</v>
       </c>
@@ -6550,8 +6557,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A30" s="87"/>
+    <row r="30" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A30" s="84"/>
       <c r="B30" s="71" t="s">
         <v>109</v>
       </c>
@@ -6603,8 +6610,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A31" s="87"/>
+    <row r="31" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A31" s="84"/>
       <c r="B31" s="71" t="s">
         <v>109</v>
       </c>
@@ -6662,8 +6669,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A32" s="87"/>
+    <row r="32" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A32" s="84"/>
       <c r="B32" s="71" t="s">
         <v>109</v>
       </c>
@@ -6723,8 +6730,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A33" s="87"/>
+    <row r="33" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A33" s="84"/>
       <c r="B33" s="71" t="s">
         <v>109</v>
       </c>
@@ -6780,8 +6787,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A34" s="87"/>
+    <row r="34" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A34" s="84"/>
       <c r="B34" s="71" t="s">
         <v>109</v>
       </c>
@@ -6841,8 +6848,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="13.9" hidden="1">
-      <c r="A35" s="98"/>
+    <row r="35" spans="1:22" ht="13.8" hidden="1">
+      <c r="A35" s="85"/>
       <c r="B35" s="71" t="s">
         <v>147</v>
       </c>
@@ -6877,8 +6884,8 @@
       <c r="U35" s="1"/>
       <c r="V35" s="71"/>
     </row>
-    <row r="36" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A36" s="94"/>
+    <row r="36" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A36" s="86"/>
       <c r="B36" s="71" t="s">
         <v>147</v>
       </c>
@@ -6991,8 +6998,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A38" s="87">
+    <row r="38" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A38" s="84">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7053,8 +7060,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A39" s="87"/>
+    <row r="39" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A39" s="84"/>
       <c r="B39" s="71" t="s">
         <v>150</v>
       </c>
@@ -7114,8 +7121,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A40" s="87"/>
+    <row r="40" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A40" s="84"/>
       <c r="B40" s="71" t="s">
         <v>150</v>
       </c>
@@ -7172,8 +7179,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A41" s="87">
+    <row r="41" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A41" s="84">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7233,8 +7240,8 @@
       </c>
       <c r="V41" s="71"/>
     </row>
-    <row r="42" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A42" s="87"/>
+    <row r="42" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A42" s="84"/>
       <c r="B42" s="71" t="s">
         <v>160</v>
       </c>
@@ -7284,7 +7291,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="87"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="71" t="s">
         <v>160</v>
       </c>
@@ -7336,7 +7343,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="87"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="71" t="s">
         <v>160</v>
       </c>
@@ -7385,7 +7392,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="27.6" hidden="1">
-      <c r="A45" s="87"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="71" t="s">
         <v>160</v>
       </c>
@@ -7441,8 +7448,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A46" s="87">
+    <row r="46" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A46" s="84">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7498,8 +7505,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="13.9" hidden="1">
-      <c r="A47" s="93"/>
+    <row r="47" spans="1:22" ht="13.8" hidden="1">
+      <c r="A47" s="90"/>
       <c r="B47" s="71" t="s">
         <v>175</v>
       </c>
@@ -7553,8 +7560,8 @@
       </c>
       <c r="V47" s="71"/>
     </row>
-    <row r="48" spans="1:22" ht="13.9" hidden="1">
-      <c r="A48" s="87"/>
+    <row r="48" spans="1:22" ht="13.8" hidden="1">
+      <c r="A48" s="84"/>
       <c r="B48" s="71" t="s">
         <v>182</v>
       </c>
@@ -7589,8 +7596,8 @@
       <c r="U48" s="80"/>
       <c r="V48" s="71"/>
     </row>
-    <row r="49" spans="1:22" ht="13.9" hidden="1">
-      <c r="A49" s="87"/>
+    <row r="49" spans="1:22" ht="13.8" hidden="1">
+      <c r="A49" s="84"/>
       <c r="B49" s="71" t="s">
         <v>182</v>
       </c>
@@ -7629,8 +7636,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="13.9" hidden="1">
-      <c r="A50" s="87"/>
+    <row r="50" spans="1:22" ht="13.8" hidden="1">
+      <c r="A50" s="84"/>
       <c r="B50" s="71" t="s">
         <v>182</v>
       </c>
@@ -7684,8 +7691,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="55.15" hidden="1">
-      <c r="A51" s="87"/>
+    <row r="51" spans="1:22" ht="55.2" hidden="1">
+      <c r="A51" s="84"/>
       <c r="B51" s="71" t="s">
         <v>182</v>
       </c>
@@ -7739,8 +7746,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="41.45" hidden="1">
-      <c r="A52" s="87"/>
+    <row r="52" spans="1:22" ht="41.4" hidden="1">
+      <c r="A52" s="84"/>
       <c r="B52" s="71" t="s">
         <v>182</v>
       </c>
@@ -7795,7 +7802,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="87"/>
+      <c r="A53" s="84"/>
       <c r="B53" s="71" t="s">
         <v>182</v>
       </c>
@@ -7849,8 +7856,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A54" s="87"/>
+    <row r="54" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A54" s="84"/>
       <c r="B54" s="71" t="s">
         <v>197</v>
       </c>
@@ -7903,8 +7910,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A55" s="87"/>
+    <row r="55" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A55" s="84"/>
       <c r="B55" s="71" t="s">
         <v>197</v>
       </c>
@@ -7958,8 +7965,8 @@
       </c>
       <c r="V55" s="66"/>
     </row>
-    <row r="56" spans="1:22" ht="41.45" hidden="1">
-      <c r="A56" s="87"/>
+    <row r="56" spans="1:22" ht="41.4" hidden="1">
+      <c r="A56" s="84"/>
       <c r="B56" s="71" t="s">
         <v>197</v>
       </c>
@@ -8017,8 +8024,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A57" s="87"/>
+    <row r="57" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A57" s="84"/>
       <c r="B57" s="71" t="s">
         <v>197</v>
       </c>
@@ -8074,8 +8081,8 @@
       </c>
       <c r="V57" s="71"/>
     </row>
-    <row r="58" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A58" s="87"/>
+    <row r="58" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+      <c r="A58" s="84"/>
       <c r="B58" s="71" t="s">
         <v>197</v>
       </c>
@@ -8134,8 +8141,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A59" s="94"/>
+    <row r="59" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A59" s="86"/>
       <c r="B59" s="71" t="s">
         <v>209</v>
       </c>
@@ -8191,8 +8198,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A60" s="94"/>
+    <row r="60" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A60" s="86"/>
       <c r="B60" s="71" t="s">
         <v>209</v>
       </c>
@@ -8247,8 +8254,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="41.45" hidden="1">
-      <c r="A61" s="87"/>
+    <row r="61" spans="1:22" ht="41.4" hidden="1">
+      <c r="A61" s="84"/>
       <c r="B61" s="61" t="s">
         <v>209</v>
       </c>
@@ -8302,7 +8309,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="93">
+      <c r="A62" s="90">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8360,7 +8367,7 @@
       </c>
     </row>
     <row r="63" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="98"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="71" t="s">
         <v>215</v>
       </c>
@@ -8417,7 +8424,7 @@
       </c>
     </row>
     <row r="64" spans="1:22" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="94"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="71" t="s">
         <v>215</v>
       </c>
@@ -8582,7 +8589,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="93">
+      <c r="A67" s="90">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8637,8 +8644,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="68" spans="1:22" ht="13.9" hidden="1">
-      <c r="A68" s="94"/>
+    <row r="68" spans="1:22" ht="13.8" hidden="1">
+      <c r="A68" s="86"/>
       <c r="B68" s="71" t="s">
         <v>230</v>
       </c>
@@ -8691,7 +8698,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="93">
+      <c r="A69" s="90">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8746,8 +8753,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="41.45" hidden="1">
-      <c r="A70" s="98"/>
+    <row r="70" spans="1:22" ht="41.4" hidden="1">
+      <c r="A70" s="85"/>
       <c r="B70" s="71" t="s">
         <v>236</v>
       </c>
@@ -8801,8 +8808,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="67.900000000000006" hidden="1" customHeight="1">
-      <c r="A71" s="98"/>
+    <row r="71" spans="1:22" ht="67.95" hidden="1" customHeight="1">
+      <c r="A71" s="85"/>
       <c r="B71" s="71" t="s">
         <v>242</v>
       </c>
@@ -8857,7 +8864,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="98"/>
+      <c r="A72" s="85"/>
       <c r="B72" s="71" t="s">
         <v>245</v>
       </c>
@@ -8912,8 +8919,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A73" s="98"/>
+    <row r="73" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A73" s="85"/>
       <c r="B73" s="71" t="s">
         <v>245</v>
       </c>
@@ -8965,8 +8972,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A74" s="98"/>
+    <row r="74" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A74" s="85"/>
       <c r="B74" s="71" t="s">
         <v>245</v>
       </c>
@@ -9020,8 +9027,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A75" s="98"/>
+    <row r="75" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A75" s="85"/>
       <c r="B75" s="71" t="s">
         <v>245</v>
       </c>
@@ -9081,8 +9088,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A76" s="98"/>
+    <row r="76" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A76" s="85"/>
       <c r="B76" s="71" t="s">
         <v>245</v>
       </c>
@@ -9134,8 +9141,8 @@
       <c r="U76" s="70"/>
       <c r="V76" s="71"/>
     </row>
-    <row r="77" spans="1:22" ht="13.9" hidden="1">
-      <c r="A77" s="94"/>
+    <row r="77" spans="1:22" ht="13.8" hidden="1">
+      <c r="A77" s="86"/>
       <c r="B77" s="71" t="s">
         <v>245</v>
       </c>
@@ -9191,8 +9198,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:22" ht="20.45" hidden="1" customHeight="1">
-      <c r="A78" s="98"/>
+    <row r="78" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A78" s="85"/>
       <c r="B78" s="71" t="s">
         <v>256</v>
       </c>
@@ -9252,8 +9259,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="13.9" hidden="1">
-      <c r="A79" s="98"/>
+    <row r="79" spans="1:22" ht="13.8" hidden="1">
+      <c r="A79" s="85"/>
       <c r="B79" s="71" t="s">
         <v>256</v>
       </c>
@@ -9307,8 +9314,8 @@
       </c>
       <c r="V79" s="66"/>
     </row>
-    <row r="80" spans="1:22" ht="13.9" hidden="1">
-      <c r="A80" s="98"/>
+    <row r="80" spans="1:22" ht="13.8" hidden="1">
+      <c r="A80" s="85"/>
       <c r="B80" s="71" t="s">
         <v>256</v>
       </c>
@@ -9363,7 +9370,7 @@
       <c r="V80" s="66"/>
     </row>
     <row r="81" spans="1:23" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="98"/>
+      <c r="A81" s="85"/>
       <c r="B81" s="71" t="s">
         <v>256</v>
       </c>
@@ -9418,8 +9425,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A82" s="98"/>
+    <row r="82" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A82" s="85"/>
       <c r="B82" s="71" t="s">
         <v>265</v>
       </c>
@@ -9476,8 +9483,8 @@
       </c>
       <c r="W82" s="33"/>
     </row>
-    <row r="83" spans="1:23" ht="38.450000000000003" hidden="1" customHeight="1">
-      <c r="A83" s="98"/>
+    <row r="83" spans="1:23" ht="38.4" hidden="1" customHeight="1">
+      <c r="A83" s="85"/>
       <c r="B83" s="71" t="s">
         <v>265</v>
       </c>
@@ -9532,7 +9539,7 @@
       <c r="W83" s="33"/>
     </row>
     <row r="84" spans="1:23" ht="27.6" hidden="1">
-      <c r="A84" s="98"/>
+      <c r="A84" s="85"/>
       <c r="B84" s="71" t="s">
         <v>265</v>
       </c>
@@ -9586,8 +9593,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="55.15" hidden="1">
-      <c r="A85" s="98"/>
+    <row r="85" spans="1:23" ht="55.2" hidden="1">
+      <c r="A85" s="85"/>
       <c r="B85" s="71" t="s">
         <v>265</v>
       </c>
@@ -9640,8 +9647,8 @@
       </c>
       <c r="W85" s="33"/>
     </row>
-    <row r="86" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A86" s="98"/>
+    <row r="86" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A86" s="85"/>
       <c r="B86" s="71" t="s">
         <v>265</v>
       </c>
@@ -9698,8 +9705,8 @@
       </c>
       <c r="W86" s="33"/>
     </row>
-    <row r="87" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A87" s="98"/>
+    <row r="87" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A87" s="85"/>
       <c r="B87" s="71" t="s">
         <v>265</v>
       </c>
@@ -9756,8 +9763,8 @@
       </c>
       <c r="W87" s="33"/>
     </row>
-    <row r="88" spans="1:23" ht="13.9" hidden="1">
-      <c r="A88" s="98"/>
+    <row r="88" spans="1:23" ht="13.8" hidden="1">
+      <c r="A88" s="85"/>
       <c r="B88" s="71" t="s">
         <v>265</v>
       </c>
@@ -9814,8 +9821,8 @@
       </c>
       <c r="W88" s="33"/>
     </row>
-    <row r="89" spans="1:23" ht="13.9" hidden="1">
-      <c r="A89" s="98"/>
+    <row r="89" spans="1:23" ht="13.8" hidden="1">
+      <c r="A89" s="85"/>
       <c r="B89" s="71" t="s">
         <v>265</v>
       </c>
@@ -9871,7 +9878,7 @@
       <c r="W89" s="33"/>
     </row>
     <row r="90" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="98"/>
+      <c r="A90" s="85"/>
       <c r="B90" s="66" t="s">
         <v>265</v>
       </c>
@@ -9920,8 +9927,8 @@
       </c>
       <c r="W90" s="33"/>
     </row>
-    <row r="91" spans="1:23" ht="43.9" hidden="1" customHeight="1">
-      <c r="A91" s="98"/>
+    <row r="91" spans="1:23" ht="43.95" hidden="1" customHeight="1">
+      <c r="A91" s="85"/>
       <c r="B91" s="71" t="s">
         <v>285</v>
       </c>
@@ -9945,36 +9952,36 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="84"/>
-      <c r="L91" s="84">
+      <c r="K91" s="100"/>
+      <c r="L91" s="100">
         <v>0</v>
       </c>
-      <c r="M91" s="84"/>
-      <c r="N91" s="87" t="s">
+      <c r="M91" s="100"/>
+      <c r="N91" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="O91" s="87" t="s">
+      <c r="O91" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="P91" s="87">
+      <c r="P91" s="84">
         <v>2026</v>
       </c>
-      <c r="Q91" s="88" t="s">
+      <c r="Q91" s="89" t="s">
         <v>131</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
       <c r="T91" s="71"/>
-      <c r="U91" s="89">
+      <c r="U91" s="103">
         <v>0</v>
       </c>
-      <c r="V91" s="88" t="s">
+      <c r="V91" s="89" t="s">
         <v>288</v>
       </c>
       <c r="W91" s="33"/>
     </row>
-    <row r="92" spans="1:23" ht="40.9" hidden="1" customHeight="1">
-      <c r="A92" s="98"/>
+    <row r="92" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A92" s="85"/>
       <c r="B92" s="71" t="s">
         <v>285</v>
       </c>
@@ -9998,21 +10005,21 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="85"/>
-      <c r="L92" s="85"/>
-      <c r="M92" s="85"/>
-      <c r="N92" s="87"/>
-      <c r="O92" s="87"/>
-      <c r="P92" s="87"/>
-      <c r="Q92" s="88"/>
+      <c r="K92" s="101"/>
+      <c r="L92" s="101"/>
+      <c r="M92" s="101"/>
+      <c r="N92" s="84"/>
+      <c r="O92" s="84"/>
+      <c r="P92" s="84"/>
+      <c r="Q92" s="89"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
       <c r="T92" s="71"/>
-      <c r="U92" s="89"/>
-      <c r="V92" s="88"/>
+      <c r="U92" s="103"/>
+      <c r="V92" s="89"/>
     </row>
     <row r="93" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="98"/>
+      <c r="A93" s="85"/>
       <c r="B93" s="71" t="s">
         <v>285</v>
       </c>
@@ -10036,9 +10043,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="85"/>
-      <c r="L93" s="85"/>
-      <c r="M93" s="85"/>
+      <c r="K93" s="101"/>
+      <c r="L93" s="101"/>
+      <c r="M93" s="101"/>
       <c r="N93" s="66" t="s">
         <v>29</v>
       </c>
@@ -10062,7 +10069,7 @@
       </c>
     </row>
     <row r="94" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="98"/>
+      <c r="A94" s="85"/>
       <c r="B94" s="71" t="s">
         <v>285</v>
       </c>
@@ -10084,9 +10091,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="85"/>
-      <c r="L94" s="85"/>
-      <c r="M94" s="85"/>
+      <c r="K94" s="101"/>
+      <c r="L94" s="101"/>
+      <c r="M94" s="101"/>
       <c r="N94" s="66" t="s">
         <v>29</v>
       </c>
@@ -10109,8 +10116,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A95" s="98"/>
+    <row r="95" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A95" s="85"/>
       <c r="B95" s="71" t="s">
         <v>285</v>
       </c>
@@ -10134,9 +10141,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="85"/>
-      <c r="L95" s="85"/>
-      <c r="M95" s="85"/>
+      <c r="K95" s="101"/>
+      <c r="L95" s="101"/>
+      <c r="M95" s="101"/>
       <c r="N95" s="66" t="s">
         <v>149</v>
       </c>
@@ -10159,8 +10166,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A96" s="98"/>
+    <row r="96" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A96" s="85"/>
       <c r="B96" s="71" t="s">
         <v>293</v>
       </c>
@@ -10180,9 +10187,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="85"/>
-      <c r="L96" s="85"/>
-      <c r="M96" s="85"/>
+      <c r="K96" s="101"/>
+      <c r="L96" s="101"/>
+      <c r="M96" s="101"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10193,8 +10200,8 @@
       <c r="U96" s="70"/>
       <c r="V96" s="66"/>
     </row>
-    <row r="97" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A97" s="98"/>
+    <row r="97" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A97" s="85"/>
       <c r="B97" s="71" t="s">
         <v>293</v>
       </c>
@@ -10222,9 +10229,9 @@
       <c r="J97" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="K97" s="85"/>
-      <c r="L97" s="85"/>
-      <c r="M97" s="85"/>
+      <c r="K97" s="101"/>
+      <c r="L97" s="101"/>
+      <c r="M97" s="101"/>
       <c r="N97" s="66" t="s">
         <v>29</v>
       </c>
@@ -10246,7 +10253,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="98"/>
+      <c r="A98" s="85"/>
       <c r="B98" s="71" t="s">
         <v>293</v>
       </c>
@@ -10274,9 +10281,9 @@
       <c r="J98" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="K98" s="85"/>
-      <c r="L98" s="85"/>
-      <c r="M98" s="85"/>
+      <c r="K98" s="101"/>
+      <c r="L98" s="101"/>
+      <c r="M98" s="101"/>
       <c r="N98" s="66" t="s">
         <v>101</v>
       </c>
@@ -10299,8 +10306,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="99" spans="1:22" ht="17.45" hidden="1" customHeight="1">
-      <c r="A99" s="98"/>
+    <row r="99" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
+      <c r="A99" s="85"/>
       <c r="B99" s="71" t="s">
         <v>302</v>
       </c>
@@ -10324,9 +10331,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="85"/>
-      <c r="L99" s="85"/>
-      <c r="M99" s="85"/>
+      <c r="K99" s="101"/>
+      <c r="L99" s="101"/>
+      <c r="M99" s="101"/>
       <c r="N99" s="66" t="s">
         <v>149</v>
       </c>
@@ -10349,8 +10356,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:22" ht="17.45" hidden="1" customHeight="1">
-      <c r="A100" s="98"/>
+    <row r="100" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
+      <c r="A100" s="85"/>
       <c r="B100" s="71" t="s">
         <v>302</v>
       </c>
@@ -10374,9 +10381,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="85"/>
-      <c r="L100" s="85"/>
-      <c r="M100" s="85"/>
+      <c r="K100" s="101"/>
+      <c r="L100" s="101"/>
+      <c r="M100" s="101"/>
       <c r="N100" s="66" t="s">
         <v>75</v>
       </c>
@@ -10399,8 +10406,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A101" s="98"/>
+    <row r="101" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+      <c r="A101" s="85"/>
       <c r="B101" s="71" t="s">
         <v>302</v>
       </c>
@@ -10424,9 +10431,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="86"/>
-      <c r="L101" s="86"/>
-      <c r="M101" s="86"/>
+      <c r="K101" s="102"/>
+      <c r="L101" s="102"/>
+      <c r="M101" s="102"/>
       <c r="N101" s="66" t="s">
         <v>38</v>
       </c>
@@ -10449,8 +10456,8 @@
         <v>306</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A102" s="98"/>
+    <row r="102" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+      <c r="A102" s="85"/>
       <c r="B102" s="71" t="s">
         <v>302</v>
       </c>
@@ -10506,8 +10513,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A103" s="98"/>
+    <row r="103" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+      <c r="A103" s="85"/>
       <c r="B103" s="71" t="s">
         <v>302</v>
       </c>
@@ -10558,8 +10565,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A104" s="98"/>
+    <row r="104" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+      <c r="A104" s="85"/>
       <c r="B104" s="71" t="s">
         <v>302</v>
       </c>
@@ -10611,8 +10618,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="105" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A105" s="98"/>
+    <row r="105" spans="1:22" ht="53.4" hidden="1" customHeight="1">
+      <c r="A105" s="85"/>
       <c r="B105" s="71" t="s">
         <v>302</v>
       </c>
@@ -10667,7 +10674,7 @@
       <c r="V105" s="66"/>
     </row>
     <row r="106" spans="1:22" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="98"/>
+      <c r="A106" s="85"/>
       <c r="B106" s="71" t="s">
         <v>302</v>
       </c>
@@ -10722,7 +10729,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" ht="96.6" hidden="1">
-      <c r="A107" s="98"/>
+      <c r="A107" s="85"/>
       <c r="B107" s="71" t="s">
         <v>314</v>
       </c>
@@ -10773,8 +10780,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A108" s="98"/>
+    <row r="108" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A108" s="85"/>
       <c r="B108" s="71" t="s">
         <v>320</v>
       </c>
@@ -10819,8 +10826,8 @@
         <v>322</v>
       </c>
     </row>
-    <row r="109" spans="1:22" ht="13.9" hidden="1">
-      <c r="A109" s="98"/>
+    <row r="109" spans="1:22" ht="13.8" hidden="1">
+      <c r="A109" s="85"/>
       <c r="B109" s="71" t="s">
         <v>320</v>
       </c>
@@ -10872,8 +10879,8 @@
       <c r="U109" s="66"/>
       <c r="V109" s="66"/>
     </row>
-    <row r="110" spans="1:22" ht="13.9" hidden="1">
-      <c r="A110" s="98"/>
+    <row r="110" spans="1:22" ht="13.8" hidden="1">
+      <c r="A110" s="85"/>
       <c r="B110" s="71" t="s">
         <v>320</v>
       </c>
@@ -10928,7 +10935,7 @@
       <c r="V110" s="71"/>
     </row>
     <row r="111" spans="1:22" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="98"/>
+      <c r="A111" s="85"/>
       <c r="B111" s="71" t="s">
         <v>325</v>
       </c>
@@ -10986,8 +10993,8 @@
       </c>
       <c r="V111" s="71"/>
     </row>
-    <row r="112" spans="1:22" ht="13.9" hidden="1">
-      <c r="A112" s="98"/>
+    <row r="112" spans="1:22" ht="13.8" hidden="1">
+      <c r="A112" s="85"/>
       <c r="B112" s="71" t="s">
         <v>327</v>
       </c>
@@ -11039,8 +11046,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:22" ht="13.9" hidden="1">
-      <c r="A113" s="98"/>
+    <row r="113" spans="1:22" ht="13.8" hidden="1">
+      <c r="A113" s="85"/>
       <c r="B113" s="71" t="s">
         <v>327</v>
       </c>
@@ -11092,8 +11099,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="114" spans="1:22" ht="41.45" hidden="1">
-      <c r="A114" s="98"/>
+    <row r="114" spans="1:22" ht="41.4" hidden="1">
+      <c r="A114" s="85"/>
       <c r="B114" s="71" t="s">
         <v>327</v>
       </c>
@@ -11134,8 +11141,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:22" ht="22.9" hidden="1" customHeight="1">
-      <c r="A115" s="98"/>
+    <row r="115" spans="1:22" ht="22.95" hidden="1" customHeight="1">
+      <c r="A115" s="85"/>
       <c r="B115" s="71" t="s">
         <v>327</v>
       </c>
@@ -11191,8 +11198,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A116" s="98"/>
+    <row r="116" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A116" s="85"/>
       <c r="B116" s="71" t="s">
         <v>337</v>
       </c>
@@ -11252,8 +11259,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="55.15" hidden="1">
-      <c r="A117" s="94"/>
+    <row r="117" spans="1:22" ht="55.2" hidden="1">
+      <c r="A117" s="86"/>
       <c r="B117" s="71" t="s">
         <v>342</v>
       </c>
@@ -11309,7 +11316,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="13.9" hidden="1">
+    <row r="118" spans="1:22" ht="13.8" hidden="1">
       <c r="A118" s="72">
         <v>29</v>
       </c>
@@ -11367,7 +11374,7 @@
       <c r="V118" s="71"/>
     </row>
     <row r="119" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="87">
+      <c r="A119" s="84">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11421,8 +11428,8 @@
       </c>
       <c r="V119" s="71"/>
     </row>
-    <row r="120" spans="1:22" ht="13.9" hidden="1">
-      <c r="A120" s="87"/>
+    <row r="120" spans="1:22" ht="13.8" hidden="1">
+      <c r="A120" s="84"/>
       <c r="B120" s="71" t="s">
         <v>347</v>
       </c>
@@ -11476,8 +11483,8 @@
       </c>
       <c r="V120" s="66"/>
     </row>
-    <row r="121" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A121" s="103">
+    <row r="121" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+      <c r="A121" s="98">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11532,8 +11539,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="122" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A122" s="88"/>
+    <row r="122" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+      <c r="A122" s="89"/>
       <c r="B122" s="71" t="s">
         <v>350</v>
       </c>
@@ -11586,8 +11593,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="142.9" hidden="1" customHeight="1">
-      <c r="A123" s="88"/>
+    <row r="123" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
+      <c r="A123" s="89"/>
       <c r="B123" s="71" t="s">
         <v>350</v>
       </c>
@@ -11641,8 +11648,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="13.9" hidden="1">
-      <c r="A124" s="88"/>
+    <row r="124" spans="1:22" ht="13.8" hidden="1">
+      <c r="A124" s="89"/>
       <c r="B124" s="71" t="s">
         <v>350</v>
       </c>
@@ -11858,7 +11865,7 @@
       <c r="U127" s="80"/>
       <c r="V127" s="71"/>
     </row>
-    <row r="128" spans="1:22" ht="37.9" hidden="1" customHeight="1">
+    <row r="128" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A128" s="66">
         <v>33</v>
       </c>
@@ -11915,7 +11922,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" spans="1:22" ht="37.9" customHeight="1">
+    <row r="129" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A129" s="68"/>
       <c r="B129" s="71" t="s">
         <v>369</v>
@@ -11970,7 +11977,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="13.9">
+    <row r="130" spans="1:22" ht="13.8" hidden="1">
       <c r="A130" s="68">
         <v>34</v>
       </c>
@@ -12027,7 +12034,7 @@
       </c>
       <c r="V130" s="66"/>
     </row>
-    <row r="131" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="131" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A131" s="68"/>
       <c r="B131" s="71" t="s">
         <v>374</v>
@@ -12082,7 +12089,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="132" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A132" s="68"/>
       <c r="B132" s="71" t="s">
         <v>374</v>
@@ -12137,8 +12144,8 @@
       </c>
       <c r="V132" s="66"/>
     </row>
-    <row r="133" spans="1:22" ht="13.9" hidden="1">
-      <c r="A133" s="87">
+    <row r="133" spans="1:22" ht="13.8" hidden="1">
+      <c r="A133" s="84">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12196,8 +12203,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:22" ht="13.9" hidden="1">
-      <c r="A134" s="87"/>
+    <row r="134" spans="1:22" ht="13.8" hidden="1">
+      <c r="A134" s="84"/>
       <c r="B134" s="71" t="s">
         <v>374</v>
       </c>
@@ -12251,8 +12258,8 @@
       </c>
       <c r="V134" s="66"/>
     </row>
-    <row r="135" spans="1:22" ht="41.45" hidden="1">
-      <c r="A135" s="87"/>
+    <row r="135" spans="1:22" ht="41.4" hidden="1">
+      <c r="A135" s="84"/>
       <c r="B135" s="71" t="s">
         <v>374</v>
       </c>
@@ -12312,8 +12319,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="13.9" hidden="1">
-      <c r="A136" s="87"/>
+    <row r="136" spans="1:22" ht="13.8" hidden="1">
+      <c r="A136" s="84"/>
       <c r="B136" s="71" t="s">
         <v>374</v>
       </c>
@@ -12369,7 +12376,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="125.45" hidden="1" customHeight="1">
+    <row r="137" spans="1:22" ht="125.4" hidden="1" customHeight="1">
       <c r="A137" s="66"/>
       <c r="B137" s="71" t="s">
         <v>383</v>
@@ -12427,8 +12434,8 @@
       </c>
       <c r="V137" s="71"/>
     </row>
-    <row r="138" spans="1:22" ht="13.9" hidden="1">
-      <c r="A138" s="87">
+    <row r="138" spans="1:22" ht="13.8" hidden="1">
+      <c r="A138" s="84">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12484,8 +12491,8 @@
       </c>
       <c r="V138" s="71"/>
     </row>
-    <row r="139" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A139" s="87"/>
+    <row r="139" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A139" s="84"/>
       <c r="B139" s="71" t="s">
         <v>383</v>
       </c>
@@ -12539,8 +12546,8 @@
       </c>
       <c r="V139" s="71"/>
     </row>
-    <row r="140" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A140" s="87"/>
+    <row r="140" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A140" s="84"/>
       <c r="B140" s="71" t="s">
         <v>383</v>
       </c>
@@ -12595,7 +12602,7 @@
       <c r="V140" s="71"/>
     </row>
     <row r="141" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="87"/>
+      <c r="A141" s="84"/>
       <c r="B141" s="71" t="s">
         <v>383</v>
       </c>
@@ -12648,8 +12655,8 @@
       </c>
       <c r="V141" s="71"/>
     </row>
-    <row r="142" spans="1:22" ht="13.9" hidden="1">
-      <c r="A142" s="87"/>
+    <row r="142" spans="1:22" ht="13.8" hidden="1">
+      <c r="A142" s="84"/>
       <c r="B142" s="71" t="s">
         <v>383</v>
       </c>
@@ -12703,8 +12710,8 @@
       </c>
       <c r="V142" s="71"/>
     </row>
-    <row r="143" spans="1:22" ht="13.9" hidden="1">
-      <c r="A143" s="87"/>
+    <row r="143" spans="1:22" ht="13.8" hidden="1">
+      <c r="A143" s="84"/>
       <c r="B143" s="71" t="s">
         <v>383</v>
       </c>
@@ -12758,8 +12765,8 @@
       </c>
       <c r="V143" s="66"/>
     </row>
-    <row r="144" spans="1:22" ht="13.9" hidden="1">
-      <c r="A144" s="87"/>
+    <row r="144" spans="1:22" ht="13.8" hidden="1">
+      <c r="A144" s="84"/>
       <c r="B144" s="71" t="s">
         <v>383</v>
       </c>
@@ -12813,8 +12820,8 @@
       </c>
       <c r="V144" s="71"/>
     </row>
-    <row r="145" spans="1:22" ht="13.9" hidden="1">
-      <c r="A145" s="87">
+    <row r="145" spans="1:22" ht="13.8" hidden="1">
+      <c r="A145" s="84">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12873,7 +12880,7 @@
       </c>
     </row>
     <row r="146" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="87"/>
+      <c r="A146" s="84"/>
       <c r="B146" s="71" t="s">
         <v>399</v>
       </c>
@@ -12926,7 +12933,7 @@
       </c>
     </row>
     <row r="147" spans="1:22" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="87"/>
+      <c r="A147" s="84"/>
       <c r="B147" s="71" t="s">
         <v>399</v>
       </c>
@@ -13035,8 +13042,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
-      <c r="A149" s="98"/>
+    <row r="149" spans="1:22" ht="35.4" hidden="1" customHeight="1">
+      <c r="A149" s="85"/>
       <c r="B149" s="71" t="s">
         <v>404</v>
       </c>
@@ -13089,8 +13096,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A150" s="94"/>
+    <row r="150" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A150" s="86"/>
       <c r="B150" s="71" t="s">
         <v>404</v>
       </c>
@@ -13145,7 +13152,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="151" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A151" s="68"/>
       <c r="B151" s="71" t="s">
         <v>409</v>
@@ -13200,7 +13207,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="13.9" hidden="1">
+    <row r="152" spans="1:22" ht="13.8" hidden="1">
       <c r="A152" s="66">
         <v>39</v>
       </c>
@@ -13259,8 +13266,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A153" s="93">
+    <row r="153" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A153" s="90">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13318,8 +13325,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A154" s="98"/>
+    <row r="154" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A154" s="85"/>
       <c r="B154" s="71" t="s">
         <v>415</v>
       </c>
@@ -13371,7 +13378,7 @@
       </c>
     </row>
     <row r="155" spans="1:22" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="98"/>
+      <c r="A155" s="85"/>
       <c r="B155" s="71" t="s">
         <v>415</v>
       </c>
@@ -13420,8 +13427,8 @@
         <v>424</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A156" s="98"/>
+    <row r="156" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A156" s="85"/>
       <c r="B156" s="71" t="s">
         <v>415</v>
       </c>
@@ -13472,8 +13479,8 @@
         <v>426</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A157" s="98"/>
+    <row r="157" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A157" s="85"/>
       <c r="B157" s="71" t="s">
         <v>415</v>
       </c>
@@ -13529,8 +13536,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="13.9" hidden="1">
-      <c r="A158" s="98"/>
+    <row r="158" spans="1:22" ht="13.8" hidden="1">
+      <c r="A158" s="85"/>
       <c r="B158" s="71" t="s">
         <v>415</v>
       </c>
@@ -13586,8 +13593,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="13.9" hidden="1">
-      <c r="A159" s="98"/>
+    <row r="159" spans="1:22" ht="13.8" hidden="1">
+      <c r="A159" s="85"/>
       <c r="B159" s="71" t="s">
         <v>415</v>
       </c>
@@ -13643,8 +13650,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="55.15" hidden="1">
-      <c r="A160" s="98"/>
+    <row r="160" spans="1:22" ht="55.2" hidden="1">
+      <c r="A160" s="85"/>
       <c r="B160" s="71" t="s">
         <v>429</v>
       </c>
@@ -13697,7 +13704,7 @@
       <c r="V160" s="71"/>
     </row>
     <row r="161" spans="1:22" ht="27.6" hidden="1">
-      <c r="A161" s="98"/>
+      <c r="A161" s="85"/>
       <c r="B161" s="71" t="s">
         <v>429</v>
       </c>
@@ -13752,8 +13759,8 @@
       </c>
       <c r="V161" s="71"/>
     </row>
-    <row r="162" spans="1:22" ht="13.9" hidden="1">
-      <c r="A162" s="98"/>
+    <row r="162" spans="1:22" ht="13.8" hidden="1">
+      <c r="A162" s="85"/>
       <c r="B162" s="71" t="s">
         <v>429</v>
       </c>
@@ -13805,8 +13812,8 @@
       </c>
       <c r="V162" s="71"/>
     </row>
-    <row r="163" spans="1:22" ht="13.9" hidden="1">
-      <c r="A163" s="98"/>
+    <row r="163" spans="1:22" ht="13.8" hidden="1">
+      <c r="A163" s="85"/>
       <c r="B163" s="71" t="s">
         <v>429</v>
       </c>
@@ -13863,7 +13870,7 @@
       </c>
     </row>
     <row r="164" spans="1:22" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="94"/>
+      <c r="A164" s="86"/>
       <c r="B164" s="71" t="s">
         <v>437</v>
       </c>
@@ -13916,8 +13923,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A165" s="98"/>
+    <row r="165" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A165" s="85"/>
       <c r="B165" s="71" t="s">
         <v>437</v>
       </c>
@@ -13970,8 +13977,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="166" spans="1:22" ht="13.9" hidden="1">
-      <c r="A166" s="94"/>
+    <row r="166" spans="1:22" ht="13.8" hidden="1">
+      <c r="A166" s="86"/>
       <c r="B166" s="71" t="s">
         <v>437</v>
       </c>
@@ -14026,7 +14033,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="167" spans="1:22" ht="13.9" hidden="1">
+    <row r="167" spans="1:22" ht="13.8" hidden="1">
       <c r="A167" s="68"/>
       <c r="B167" s="71" t="s">
         <v>444</v>
@@ -14148,8 +14155,8 @@
         <v>450</v>
       </c>
     </row>
-    <row r="169" spans="1:22" ht="41.45" hidden="1">
-      <c r="A169" s="99">
+    <row r="169" spans="1:22" ht="41.4" hidden="1">
+      <c r="A169" s="91">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14210,7 +14217,7 @@
       </c>
     </row>
     <row r="170" spans="1:22" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="100"/>
+      <c r="A170" s="92"/>
       <c r="B170" s="71" t="s">
         <v>451</v>
       </c>
@@ -14261,8 +14268,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="171" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A171" s="100"/>
+    <row r="171" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+      <c r="A171" s="92"/>
       <c r="B171" s="71" t="s">
         <v>451</v>
       </c>
@@ -14320,8 +14327,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="172" spans="1:22" ht="13.9" hidden="1">
-      <c r="A172" s="100"/>
+    <row r="172" spans="1:22" ht="13.8" hidden="1">
+      <c r="A172" s="92"/>
       <c r="B172" s="71" t="s">
         <v>451</v>
       </c>
@@ -14377,8 +14384,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="173" spans="1:22" ht="13.9" hidden="1">
-      <c r="A173" s="101"/>
+    <row r="173" spans="1:22" ht="13.8" hidden="1">
+      <c r="A173" s="93"/>
       <c r="B173" s="71" t="s">
         <v>458</v>
       </c>
@@ -14434,8 +14441,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="174" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A174" s="87">
+    <row r="174" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+      <c r="A174" s="84">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14492,8 +14499,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="175" spans="1:22" ht="13.9" hidden="1">
-      <c r="A175" s="87"/>
+    <row r="175" spans="1:22" ht="13.8" hidden="1">
+      <c r="A175" s="84"/>
       <c r="B175" s="71" t="s">
         <v>460</v>
       </c>
@@ -14549,8 +14556,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:22" ht="13.9" hidden="1">
-      <c r="A176" s="87"/>
+    <row r="176" spans="1:22" ht="13.8" hidden="1">
+      <c r="A176" s="84"/>
       <c r="B176" s="71" t="s">
         <v>460</v>
       </c>
@@ -14604,8 +14611,8 @@
       </c>
       <c r="V176" s="71"/>
     </row>
-    <row r="177" spans="1:22" ht="13.9" hidden="1">
-      <c r="A177" s="87"/>
+    <row r="177" spans="1:22" ht="13.8" hidden="1">
+      <c r="A177" s="84"/>
       <c r="B177" s="71" t="s">
         <v>460</v>
       </c>
@@ -14661,8 +14668,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="178" spans="1:22" ht="41.45" hidden="1">
-      <c r="A178" s="87"/>
+    <row r="178" spans="1:22" ht="27.6" hidden="1">
+      <c r="A178" s="84"/>
       <c r="B178" s="71" t="s">
         <v>460</v>
       </c>
@@ -14716,8 +14723,8 @@
       </c>
       <c r="V178" s="71"/>
     </row>
-    <row r="179" spans="1:22" ht="13.9" hidden="1">
-      <c r="A179" s="87"/>
+    <row r="179" spans="1:22" ht="13.8" hidden="1">
+      <c r="A179" s="84"/>
       <c r="B179" s="71" t="s">
         <v>468</v>
       </c>
@@ -14773,8 +14780,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="13.9" hidden="1">
-      <c r="A180" s="87"/>
+    <row r="180" spans="1:22" ht="13.8" hidden="1">
+      <c r="A180" s="84"/>
       <c r="B180" s="71" t="s">
         <v>470</v>
       </c>
@@ -14828,7 +14835,7 @@
       </c>
       <c r="V180" s="66"/>
     </row>
-    <row r="181" spans="1:22" ht="13.9" hidden="1">
+    <row r="181" spans="1:22" ht="13.8" hidden="1">
       <c r="A181" s="75"/>
       <c r="B181" s="71" t="s">
         <v>473</v>
@@ -14937,8 +14944,8 @@
       </c>
       <c r="V182" s="66"/>
     </row>
-    <row r="183" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A183" s="102">
+    <row r="183" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A183" s="94">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14992,8 +14999,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A184" s="102"/>
+    <row r="184" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A184" s="94"/>
       <c r="B184" s="71" t="s">
         <v>473</v>
       </c>
@@ -15047,8 +15054,8 @@
         <v>483</v>
       </c>
     </row>
-    <row r="185" spans="1:22" ht="13.9" hidden="1">
-      <c r="A185" s="102"/>
+    <row r="185" spans="1:22" ht="13.8" hidden="1">
+      <c r="A185" s="94"/>
       <c r="B185" s="71" t="s">
         <v>473</v>
       </c>
@@ -15104,7 +15111,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="13.9" hidden="1">
+    <row r="186" spans="1:22" ht="13.8" hidden="1">
       <c r="A186" s="72"/>
       <c r="B186" s="71" t="s">
         <v>485</v>
@@ -15163,8 +15170,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="13.9" hidden="1">
-      <c r="A187" s="100"/>
+    <row r="187" spans="1:22" ht="13.8" hidden="1">
+      <c r="A187" s="92"/>
       <c r="B187" s="71" t="s">
         <v>485</v>
       </c>
@@ -15214,8 +15221,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:22" ht="13.9" hidden="1">
-      <c r="A188" s="100"/>
+    <row r="188" spans="1:22" ht="13.8" hidden="1">
+      <c r="A188" s="92"/>
       <c r="B188" s="71" t="s">
         <v>485</v>
       </c>
@@ -15267,8 +15274,8 @@
       <c r="U188" s="80"/>
       <c r="V188" s="71"/>
     </row>
-    <row r="189" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A189" s="101"/>
+    <row r="189" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A189" s="93"/>
       <c r="B189" s="71" t="s">
         <v>485</v>
       </c>
@@ -15375,8 +15382,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
-      <c r="A191" s="87">
+    <row r="191" spans="1:22" ht="64.95" hidden="1" customHeight="1">
+      <c r="A191" s="84">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15432,7 +15439,7 @@
       </c>
     </row>
     <row r="192" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="87"/>
+      <c r="A192" s="84"/>
       <c r="B192" s="71" t="s">
         <v>492</v>
       </c>
@@ -15485,8 +15492,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="193" spans="1:22" ht="13.9" hidden="1">
-      <c r="A193" s="87"/>
+    <row r="193" spans="1:22" ht="13.8" hidden="1">
+      <c r="A193" s="84"/>
       <c r="B193" s="71" t="s">
         <v>492</v>
       </c>
@@ -15542,7 +15549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="194" spans="1:22" ht="13.9" hidden="1">
+    <row r="194" spans="1:22" ht="13.8" hidden="1">
       <c r="A194" s="66">
         <v>49</v>
       </c>
@@ -15572,8 +15579,8 @@
       <c r="U194" s="66"/>
       <c r="V194" s="66"/>
     </row>
-    <row r="195" spans="1:22" ht="13.9" hidden="1">
-      <c r="A195" s="98"/>
+    <row r="195" spans="1:22" ht="13.8" hidden="1">
+      <c r="A195" s="85"/>
       <c r="B195" s="71" t="s">
         <v>504</v>
       </c>
@@ -15628,7 +15635,7 @@
       </c>
     </row>
     <row r="196" spans="1:22" ht="24.6" hidden="1" customHeight="1">
-      <c r="A196" s="94"/>
+      <c r="A196" s="86"/>
       <c r="B196" s="71" t="s">
         <v>504</v>
       </c>
@@ -15682,8 +15689,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="197" spans="1:22" ht="13.9" hidden="1">
-      <c r="A197" s="87">
+    <row r="197" spans="1:22" ht="13.8" hidden="1">
+      <c r="A197" s="84">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15738,8 +15745,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="198" spans="1:22" ht="13.9" hidden="1">
-      <c r="A198" s="87"/>
+    <row r="198" spans="1:22" ht="13.8" hidden="1">
+      <c r="A198" s="84"/>
       <c r="B198" s="71" t="s">
         <v>508</v>
       </c>
@@ -15795,8 +15802,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="199" spans="1:22" ht="13.9" hidden="1">
-      <c r="A199" s="87"/>
+    <row r="199" spans="1:22" ht="13.8" hidden="1">
+      <c r="A199" s="84"/>
       <c r="B199" s="71" t="s">
         <v>508</v>
       </c>
@@ -15852,8 +15859,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="200" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A200" s="87"/>
+    <row r="200" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A200" s="84"/>
       <c r="B200" s="71" t="s">
         <v>508</v>
       </c>
@@ -15908,7 +15915,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="201" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="71" t="s">
         <v>515</v>
@@ -15963,7 +15970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="202" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="71" t="s">
         <v>515</v>
@@ -16012,7 +16019,7 @@
       <c r="U202" s="70"/>
       <c r="V202" s="66"/>
     </row>
-    <row r="203" spans="1:22" ht="13.9" hidden="1">
+    <row r="203" spans="1:22" ht="13.8" hidden="1">
       <c r="A203" s="66">
         <v>52</v>
       </c>
@@ -16071,8 +16078,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="204" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A204" s="87">
+    <row r="204" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A204" s="84">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -16129,8 +16136,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="205" spans="1:22" ht="55.15" hidden="1">
-      <c r="A205" s="87"/>
+    <row r="205" spans="1:22" ht="55.2" hidden="1">
+      <c r="A205" s="84"/>
       <c r="B205" s="71" t="s">
         <v>520</v>
       </c>
@@ -16186,8 +16193,8 @@
         <v>523</v>
       </c>
     </row>
-    <row r="206" spans="1:22" ht="13.9" hidden="1">
-      <c r="A206" s="87"/>
+    <row r="206" spans="1:22" ht="13.8" hidden="1">
+      <c r="A206" s="84"/>
       <c r="B206" s="66" t="s">
         <v>524</v>
       </c>
@@ -16243,8 +16250,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="207" spans="1:22" ht="13.9" hidden="1">
-      <c r="A207" s="87">
+    <row r="207" spans="1:22" ht="13.8" hidden="1">
+      <c r="A207" s="84">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16300,8 +16307,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208" spans="1:22" ht="13.9" hidden="1">
-      <c r="A208" s="87"/>
+    <row r="208" spans="1:22" ht="13.8" hidden="1">
+      <c r="A208" s="84"/>
       <c r="B208" s="71" t="s">
         <v>527</v>
       </c>
@@ -16359,8 +16366,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="209" spans="1:22" ht="32.450000000000003" hidden="1" customHeight="1">
-      <c r="A209" s="87">
+    <row r="209" spans="1:22" ht="32.4" hidden="1" customHeight="1">
+      <c r="A209" s="84">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16417,8 +16424,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="210" spans="1:22" ht="13.9" hidden="1">
-      <c r="A210" s="87"/>
+    <row r="210" spans="1:22" ht="13.8" hidden="1">
+      <c r="A210" s="84"/>
       <c r="B210" s="71" t="s">
         <v>530</v>
       </c>
@@ -16472,8 +16479,8 @@
       </c>
       <c r="V210" s="71"/>
     </row>
-    <row r="211" spans="1:22" ht="16.149999999999999" hidden="1" customHeight="1">
-      <c r="A211" s="87"/>
+    <row r="211" spans="1:22" ht="16.2" hidden="1" customHeight="1">
+      <c r="A211" s="84"/>
       <c r="B211" s="71" t="s">
         <v>530</v>
       </c>
@@ -16527,8 +16534,8 @@
       </c>
       <c r="V211" s="66"/>
     </row>
-    <row r="212" spans="1:22" ht="80.45" hidden="1" customHeight="1">
-      <c r="A212" s="87">
+    <row r="212" spans="1:22" ht="80.400000000000006" hidden="1" customHeight="1">
+      <c r="A212" s="84">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16583,8 +16590,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="213" spans="1:22" ht="13.9" hidden="1">
-      <c r="A213" s="87"/>
+    <row r="213" spans="1:22" ht="13.8" hidden="1">
+      <c r="A213" s="84"/>
       <c r="B213" s="71" t="s">
         <v>539</v>
       </c>
@@ -16642,8 +16649,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="214" spans="1:22" ht="41.45" hidden="1">
-      <c r="A214" s="99">
+    <row r="214" spans="1:22" ht="27.6" hidden="1">
+      <c r="A214" s="91">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16698,8 +16705,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="215" spans="1:22" ht="13.9" hidden="1">
-      <c r="A215" s="100"/>
+    <row r="215" spans="1:22" ht="13.8" hidden="1">
+      <c r="A215" s="92"/>
       <c r="B215" s="71" t="s">
         <v>541</v>
       </c>
@@ -16755,8 +16762,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216" spans="1:22" ht="13.9" hidden="1">
-      <c r="A216" s="100"/>
+    <row r="216" spans="1:22" ht="13.8" hidden="1">
+      <c r="A216" s="92"/>
       <c r="B216" s="71" t="s">
         <v>541</v>
       </c>
@@ -16813,7 +16820,7 @@
       </c>
     </row>
     <row r="217" spans="1:22" ht="27.6" hidden="1">
-      <c r="A217" s="98"/>
+      <c r="A217" s="85"/>
       <c r="B217" s="71" t="s">
         <v>541</v>
       </c>
@@ -16868,8 +16875,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="218" spans="1:22" ht="13.9" hidden="1">
-      <c r="A218" s="101"/>
+    <row r="218" spans="1:22" ht="13.8" hidden="1">
+      <c r="A218" s="93"/>
       <c r="B218" s="71" t="s">
         <v>541</v>
       </c>
@@ -16925,7 +16932,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:22" ht="13.9" hidden="1">
+    <row r="219" spans="1:22" ht="13.8" hidden="1">
       <c r="A219" s="74"/>
       <c r="B219" s="71" t="s">
         <v>552</v>
@@ -16982,7 +16989,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220" spans="1:22" ht="13.9" hidden="1">
+    <row r="220" spans="1:22" ht="13.8" hidden="1">
       <c r="A220" s="74"/>
       <c r="B220" s="71" t="s">
         <v>552</v>
@@ -17039,7 +17046,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221" spans="1:22" ht="13.9" hidden="1">
+    <row r="221" spans="1:22" ht="13.8" hidden="1">
       <c r="A221" s="74"/>
       <c r="B221" s="71" t="s">
         <v>552</v>
@@ -17093,7 +17100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="222" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A222" s="66">
         <v>58</v>
       </c>
@@ -17152,8 +17159,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="223" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A223" s="87">
+    <row r="223" spans="1:22" ht="34.200000000000003" customHeight="1">
+      <c r="A223" s="84">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17208,8 +17215,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="224" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A224" s="87"/>
+    <row r="224" spans="1:22" ht="34.200000000000003" customHeight="1">
+      <c r="A224" s="84"/>
       <c r="B224" s="71" t="s">
         <v>562</v>
       </c>
@@ -17265,8 +17272,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="225" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A225" s="87"/>
+    <row r="225" spans="1:22" ht="81.599999999999994" customHeight="1">
+      <c r="A225" s="84"/>
       <c r="B225" s="71" t="s">
         <v>562</v>
       </c>
@@ -17317,8 +17324,8 @@
       </c>
       <c r="V225" s="71"/>
     </row>
-    <row r="226" spans="1:22" ht="13.9" hidden="1">
-      <c r="A226" s="87"/>
+    <row r="226" spans="1:22" ht="13.8">
+      <c r="A226" s="84"/>
       <c r="B226" s="71" t="s">
         <v>562</v>
       </c>
@@ -17374,8 +17381,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="227" spans="1:22" ht="27.6" hidden="1">
-      <c r="A227" s="87"/>
+    <row r="227" spans="1:22" ht="27.6">
+      <c r="A227" s="84"/>
       <c r="B227" s="71" t="s">
         <v>562</v>
       </c>
@@ -17427,8 +17434,8 @@
       <c r="U227" s="70"/>
       <c r="V227" s="66"/>
     </row>
-    <row r="228" spans="1:22" ht="13.9" hidden="1">
-      <c r="A228" s="87"/>
+    <row r="228" spans="1:22" ht="13.8">
+      <c r="A228" s="84"/>
       <c r="B228" s="71" t="s">
         <v>562</v>
       </c>
@@ -17484,7 +17491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="229" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="229" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A229" s="66"/>
       <c r="B229" s="71" t="s">
         <v>574</v>
@@ -17539,7 +17546,7 @@
       </c>
       <c r="V229" s="66"/>
     </row>
-    <row r="230" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="230" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A230" s="66"/>
       <c r="B230" s="71" t="s">
         <v>574</v>
@@ -17594,7 +17601,7 @@
       </c>
       <c r="V230" s="66"/>
     </row>
-    <row r="231" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+    <row r="231" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A231" s="66"/>
       <c r="B231" s="71" t="s">
         <v>574</v>
@@ -17649,7 +17656,7 @@
       </c>
       <c r="V231" s="66"/>
     </row>
-    <row r="232" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="232" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A232" s="66">
         <v>60</v>
       </c>
@@ -17705,7 +17712,7 @@
       </c>
       <c r="V232" s="66"/>
     </row>
-    <row r="233" spans="1:22" ht="13.9" hidden="1">
+    <row r="233" spans="1:22" ht="13.8" hidden="1">
       <c r="A233" s="66">
         <v>61</v>
       </c>
@@ -17735,7 +17742,7 @@
       <c r="U233" s="66"/>
       <c r="V233" s="66"/>
     </row>
-    <row r="234" spans="1:22" ht="224.45" hidden="1" customHeight="1">
+    <row r="234" spans="1:22" ht="224.4" hidden="1" customHeight="1">
       <c r="A234" s="66">
         <v>62</v>
       </c>
@@ -17793,7 +17800,7 @@
       </c>
     </row>
     <row r="235" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="93">
+      <c r="A235" s="90">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17848,7 +17855,7 @@
       </c>
     </row>
     <row r="236" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="98"/>
+      <c r="A236" s="85"/>
       <c r="B236" s="71" t="s">
         <v>583</v>
       </c>
@@ -17903,7 +17910,7 @@
       </c>
     </row>
     <row r="237" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="98"/>
+      <c r="A237" s="85"/>
       <c r="B237" s="71" t="s">
         <v>583</v>
       </c>
@@ -17958,7 +17965,7 @@
       </c>
     </row>
     <row r="238" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="98"/>
+      <c r="A238" s="85"/>
       <c r="B238" s="71" t="s">
         <v>583</v>
       </c>
@@ -18013,8 +18020,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A239" s="98"/>
+    <row r="239" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A239" s="85"/>
       <c r="B239" s="71" t="s">
         <v>583</v>
       </c>
@@ -18069,8 +18076,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A240" s="94"/>
+    <row r="240" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A240" s="86"/>
       <c r="B240" s="71" t="s">
         <v>597</v>
       </c>
@@ -18122,8 +18129,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="241" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A241" s="87">
+    <row r="241" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A241" s="84">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -18178,8 +18185,8 @@
       </c>
       <c r="V241" s="71"/>
     </row>
-    <row r="242" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A242" s="87"/>
+    <row r="242" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A242" s="84"/>
       <c r="B242" s="71" t="s">
         <v>600</v>
       </c>
@@ -18233,8 +18240,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A243" s="87"/>
+    <row r="243" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A243" s="84"/>
       <c r="B243" s="71" t="s">
         <v>600</v>
       </c>
@@ -18294,8 +18301,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="55.15" hidden="1">
-      <c r="A244" s="87"/>
+    <row r="244" spans="1:22" ht="41.4" hidden="1">
+      <c r="A244" s="84"/>
       <c r="B244" s="71" t="s">
         <v>600</v>
       </c>
@@ -18347,8 +18354,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="245" spans="1:22" ht="13.9" hidden="1">
-      <c r="A245" s="87"/>
+    <row r="245" spans="1:22" ht="13.8" hidden="1">
+      <c r="A245" s="84"/>
       <c r="B245" s="71" t="s">
         <v>600</v>
       </c>
@@ -18383,8 +18390,8 @@
       <c r="U245" s="80"/>
       <c r="V245" s="71"/>
     </row>
-    <row r="246" spans="1:22" ht="13.9" hidden="1">
-      <c r="A246" s="87"/>
+    <row r="246" spans="1:22" ht="13.8" hidden="1">
+      <c r="A246" s="84"/>
       <c r="B246" s="71" t="s">
         <v>600</v>
       </c>
@@ -18436,8 +18443,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="247" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A247" s="87"/>
+    <row r="247" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A247" s="84"/>
       <c r="B247" s="71" t="s">
         <v>600</v>
       </c>
@@ -18492,7 +18499,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="248" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="248" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A248" s="66"/>
       <c r="B248" s="71" t="s">
         <v>608</v>
@@ -18548,7 +18555,7 @@
       <c r="V248" s="71"/>
     </row>
     <row r="249" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="87">
+      <c r="A249" s="84">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18604,7 +18611,7 @@
       </c>
     </row>
     <row r="250" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A250" s="87"/>
+      <c r="A250" s="84"/>
       <c r="B250" s="71" t="s">
         <v>608</v>
       </c>
@@ -18658,8 +18665,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A251" s="87"/>
+    <row r="251" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A251" s="84"/>
       <c r="B251" s="71" t="s">
         <v>608</v>
       </c>
@@ -18714,7 +18721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="13.9" hidden="1">
+    <row r="252" spans="1:22" ht="13.8" hidden="1">
       <c r="A252" s="66">
         <v>66</v>
       </c>
@@ -18744,7 +18751,7 @@
       <c r="U252" s="66"/>
       <c r="V252" s="66"/>
     </row>
-    <row r="253" spans="1:22" ht="13.9" hidden="1">
+    <row r="253" spans="1:22" ht="13.8" hidden="1">
       <c r="A253" s="66"/>
       <c r="B253" s="71" t="s">
         <v>617</v>
@@ -18795,7 +18802,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="1:22" ht="13.9" hidden="1">
+    <row r="254" spans="1:22" ht="13.8" hidden="1">
       <c r="A254" s="66">
         <v>67</v>
       </c>
@@ -18853,7 +18860,7 @@
       <c r="V254" s="66"/>
     </row>
     <row r="255" spans="1:22" ht="27.6" hidden="1">
-      <c r="A255" s="93">
+      <c r="A255" s="90">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18908,7 +18915,7 @@
       </c>
     </row>
     <row r="256" spans="1:22" ht="27.6" hidden="1">
-      <c r="A256" s="98"/>
+      <c r="A256" s="85"/>
       <c r="B256" s="71" t="s">
         <v>621</v>
       </c>
@@ -18963,8 +18970,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="257" spans="1:22" ht="13.9" hidden="1">
-      <c r="A257" s="98"/>
+    <row r="257" spans="1:22" ht="13.8" hidden="1">
+      <c r="A257" s="85"/>
       <c r="B257" s="71" t="s">
         <v>621</v>
       </c>
@@ -19020,8 +19027,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="258" spans="1:22" ht="13.9" hidden="1">
-      <c r="A258" s="98"/>
+    <row r="258" spans="1:22" ht="13.8" hidden="1">
+      <c r="A258" s="85"/>
       <c r="B258" s="71" t="s">
         <v>621</v>
       </c>
@@ -19077,8 +19084,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="259" spans="1:22" ht="13.9" hidden="1">
-      <c r="A259" s="98"/>
+    <row r="259" spans="1:22" ht="13.8" hidden="1">
+      <c r="A259" s="85"/>
       <c r="B259" s="71" t="s">
         <v>621</v>
       </c>
@@ -19132,8 +19139,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="260" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A260" s="94"/>
+    <row r="260" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
+      <c r="A260" s="86"/>
       <c r="B260" s="71" t="s">
         <v>621</v>
       </c>
@@ -19189,8 +19196,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:22" ht="55.15" hidden="1">
-      <c r="A261" s="93">
+    <row r="261" spans="1:22" ht="55.2" hidden="1">
+      <c r="A261" s="90">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19246,7 +19253,7 @@
       </c>
     </row>
     <row r="262" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="98"/>
+      <c r="A262" s="85"/>
       <c r="B262" s="71" t="s">
         <v>631</v>
       </c>
@@ -19299,7 +19306,7 @@
       </c>
     </row>
     <row r="263" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="98"/>
+      <c r="A263" s="85"/>
       <c r="B263" s="71" t="s">
         <v>639</v>
       </c>
@@ -19347,8 +19354,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="264" spans="1:22" ht="55.15" hidden="1">
-      <c r="A264" s="98"/>
+    <row r="264" spans="1:22" ht="55.2" hidden="1">
+      <c r="A264" s="85"/>
       <c r="B264" s="71" t="s">
         <v>639</v>
       </c>
@@ -19398,8 +19405,8 @@
         <v>643</v>
       </c>
     </row>
-    <row r="265" spans="1:22" ht="46.15" hidden="1" customHeight="1">
-      <c r="A265" s="98"/>
+    <row r="265" spans="1:22" ht="46.2" hidden="1" customHeight="1">
+      <c r="A265" s="85"/>
       <c r="B265" s="71" t="s">
         <v>631</v>
       </c>
@@ -19453,7 +19460,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:22" ht="46.15" hidden="1" customHeight="1">
+    <row r="266" spans="1:22" ht="46.2" hidden="1" customHeight="1">
       <c r="A266" s="67"/>
       <c r="B266" s="71" t="s">
         <v>645</v>
@@ -19511,8 +19518,8 @@
       </c>
       <c r="V266" s="71"/>
     </row>
-    <row r="267" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A267" s="87">
+    <row r="267" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A267" s="84">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19570,8 +19577,8 @@
       </c>
       <c r="V267" s="71"/>
     </row>
-    <row r="268" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A268" s="87"/>
+    <row r="268" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A268" s="84"/>
       <c r="B268" s="71" t="s">
         <v>645</v>
       </c>
@@ -19627,8 +19634,8 @@
       </c>
       <c r="V268" s="71"/>
     </row>
-    <row r="269" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A269" s="87"/>
+    <row r="269" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A269" s="84"/>
       <c r="B269" s="71" t="s">
         <v>645</v>
       </c>
@@ -19684,8 +19691,8 @@
       </c>
       <c r="V269" s="71"/>
     </row>
-    <row r="270" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A270" s="87"/>
+    <row r="270" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A270" s="84"/>
       <c r="B270" s="71" t="s">
         <v>645</v>
       </c>
@@ -19741,7 +19748,7 @@
       </c>
       <c r="V270" s="66"/>
     </row>
-    <row r="271" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="271" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A271" s="66"/>
       <c r="B271" s="71" t="s">
         <v>655</v>
@@ -19798,8 +19805,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A272" s="87">
+    <row r="272" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A272" s="84">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19855,8 +19862,8 @@
       </c>
       <c r="V272" s="71"/>
     </row>
-    <row r="273" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A273" s="87"/>
+    <row r="273" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A273" s="84"/>
       <c r="B273" s="71" t="s">
         <v>655</v>
       </c>
@@ -19912,8 +19919,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="274" spans="1:22" ht="13.9" hidden="1">
-      <c r="A274" s="87"/>
+    <row r="274" spans="1:22" ht="13.8" hidden="1">
+      <c r="A274" s="84"/>
       <c r="B274" s="71" t="s">
         <v>655</v>
       </c>
@@ -19969,8 +19976,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="275" spans="1:22" ht="13.9" hidden="1">
-      <c r="A275" s="87"/>
+    <row r="275" spans="1:22" ht="13.8" hidden="1">
+      <c r="A275" s="84"/>
       <c r="B275" s="71" t="s">
         <v>655</v>
       </c>
@@ -20026,8 +20033,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="276" spans="1:22" ht="13.9" hidden="1">
-      <c r="A276" s="87"/>
+    <row r="276" spans="1:22" ht="13.8" hidden="1">
+      <c r="A276" s="84"/>
       <c r="B276" s="66" t="s">
         <v>662</v>
       </c>
@@ -20083,7 +20090,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="277" spans="1:22" ht="13.9" hidden="1">
+    <row r="277" spans="1:22" ht="13.8" hidden="1">
       <c r="A277" s="66">
         <v>72</v>
       </c>
@@ -20140,7 +20147,7 @@
       </c>
       <c r="V277" s="66"/>
     </row>
-    <row r="278" spans="1:22" ht="13.9" hidden="1">
+    <row r="278" spans="1:22" ht="13.8" hidden="1">
       <c r="A278" s="66"/>
       <c r="B278" s="71" t="s">
         <v>667</v>
@@ -20197,7 +20204,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="279" spans="1:22" ht="13.9" hidden="1">
+    <row r="279" spans="1:22" ht="13.8" hidden="1">
       <c r="A279" s="66"/>
       <c r="B279" s="71" t="s">
         <v>667</v>
@@ -20250,7 +20257,7 @@
       <c r="U279" s="70"/>
       <c r="V279" s="66"/>
     </row>
-    <row r="280" spans="1:22" ht="13.9" hidden="1">
+    <row r="280" spans="1:22" ht="13.8" hidden="1">
       <c r="A280" s="66">
         <v>73</v>
       </c>
@@ -20308,7 +20315,7 @@
       <c r="V280" s="66"/>
     </row>
     <row r="281" spans="1:22" ht="27.6" hidden="1">
-      <c r="A281" s="87">
+      <c r="A281" s="84">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20362,8 +20369,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="282" spans="1:22" ht="13.9" hidden="1">
-      <c r="A282" s="87"/>
+    <row r="282" spans="1:22" ht="13.8" hidden="1">
+      <c r="A282" s="84"/>
       <c r="B282" s="71" t="s">
         <v>671</v>
       </c>
@@ -20412,8 +20419,8 @@
       </c>
       <c r="V282" s="66"/>
     </row>
-    <row r="283" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A283" s="87">
+    <row r="283" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
+      <c r="A283" s="84">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20468,8 +20475,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="13.9" hidden="1">
-      <c r="A284" s="87"/>
+    <row r="284" spans="1:22" ht="13.8" hidden="1">
+      <c r="A284" s="84"/>
       <c r="B284" s="71" t="s">
         <v>674</v>
       </c>
@@ -20523,8 +20530,8 @@
       </c>
       <c r="V284" s="71"/>
     </row>
-    <row r="285" spans="1:22" ht="13.9" hidden="1">
-      <c r="A285" s="94">
+    <row r="285" spans="1:22" ht="13.8" hidden="1">
+      <c r="A285" s="86">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20582,8 +20589,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="286" spans="1:22" ht="13.9" hidden="1">
-      <c r="A286" s="94"/>
+    <row r="286" spans="1:22" ht="13.8" hidden="1">
+      <c r="A286" s="86"/>
       <c r="B286" s="71" t="s">
         <v>678</v>
       </c>
@@ -20639,8 +20646,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="287" spans="1:22" ht="13.9" hidden="1">
-      <c r="A287" s="94"/>
+    <row r="287" spans="1:22" ht="13.8" hidden="1">
+      <c r="A287" s="86"/>
       <c r="B287" s="71" t="s">
         <v>678</v>
       </c>
@@ -20696,8 +20703,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="288" spans="1:22" ht="13.9" hidden="1">
-      <c r="A288" s="94"/>
+    <row r="288" spans="1:22" ht="13.8" hidden="1">
+      <c r="A288" s="86"/>
       <c r="B288" s="71" t="s">
         <v>678</v>
       </c>
@@ -20753,8 +20760,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="289" spans="1:22" ht="13.9" hidden="1">
-      <c r="A289" s="87"/>
+    <row r="289" spans="1:22" ht="13.8" hidden="1">
+      <c r="A289" s="84"/>
       <c r="B289" s="71" t="s">
         <v>678</v>
       </c>
@@ -20808,7 +20815,7 @@
       </c>
     </row>
     <row r="290" spans="1:22" ht="27.6" hidden="1">
-      <c r="A290" s="87"/>
+      <c r="A290" s="84"/>
       <c r="B290" s="71" t="s">
         <v>678</v>
       </c>
@@ -20862,8 +20869,8 @@
         <v>690</v>
       </c>
     </row>
-    <row r="291" spans="1:22" ht="13.9" hidden="1">
-      <c r="A291" s="87"/>
+    <row r="291" spans="1:22" ht="13.8" hidden="1">
+      <c r="A291" s="84"/>
       <c r="B291" s="71" t="s">
         <v>678</v>
       </c>
@@ -20919,8 +20926,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="292" spans="1:22" ht="13.9" hidden="1">
-      <c r="A292" s="87"/>
+    <row r="292" spans="1:22" ht="13.8" hidden="1">
+      <c r="A292" s="84"/>
       <c r="B292" s="71" t="s">
         <v>678</v>
       </c>
@@ -20972,8 +20979,8 @@
       </c>
       <c r="V292" s="71"/>
     </row>
-    <row r="293" spans="1:22" ht="13.9" hidden="1">
-      <c r="A293" s="87"/>
+    <row r="293" spans="1:22" ht="13.8" hidden="1">
+      <c r="A293" s="84"/>
       <c r="B293" s="71" t="s">
         <v>678</v>
       </c>
@@ -21027,7 +21034,7 @@
       </c>
       <c r="V293" s="71"/>
     </row>
-    <row r="294" spans="1:22" ht="41.45" hidden="1">
+    <row r="294" spans="1:22" ht="41.4" hidden="1">
       <c r="A294" s="66"/>
       <c r="B294" s="71" t="s">
         <v>693</v>
@@ -21089,7 +21096,7 @@
       </c>
     </row>
     <row r="295" spans="1:22" ht="96.6" hidden="1">
-      <c r="A295" s="87">
+      <c r="A295" s="84">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -21152,7 +21159,7 @@
       </c>
     </row>
     <row r="296" spans="1:22" ht="27.6" hidden="1">
-      <c r="A296" s="87"/>
+      <c r="A296" s="84"/>
       <c r="B296" s="71" t="s">
         <v>693</v>
       </c>
@@ -21212,8 +21219,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="297" spans="1:22" ht="13.9" hidden="1">
-      <c r="A297" s="87"/>
+    <row r="297" spans="1:22" ht="13.8" hidden="1">
+      <c r="A297" s="84"/>
       <c r="B297" s="71" t="s">
         <v>693</v>
       </c>
@@ -21274,7 +21281,7 @@
       </c>
     </row>
     <row r="298" spans="1:22" ht="27.6" hidden="1">
-      <c r="A298" s="87">
+      <c r="A298" s="84">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21329,8 +21336,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="299" spans="1:22" ht="13.9" hidden="1">
-      <c r="A299" s="87"/>
+    <row r="299" spans="1:22" ht="13.8" hidden="1">
+      <c r="A299" s="84"/>
       <c r="B299" s="71" t="s">
         <v>704</v>
       </c>
@@ -21384,8 +21391,8 @@
       </c>
       <c r="V299" s="71"/>
     </row>
-    <row r="300" spans="1:22" ht="13.9" hidden="1">
-      <c r="A300" s="87"/>
+    <row r="300" spans="1:22" ht="13.8" hidden="1">
+      <c r="A300" s="84"/>
       <c r="B300" s="71" t="s">
         <v>704</v>
       </c>
@@ -21441,8 +21448,8 @@
         <v>711</v>
       </c>
     </row>
-    <row r="301" spans="1:22" ht="13.9" hidden="1">
-      <c r="A301" s="98"/>
+    <row r="301" spans="1:22" ht="13.8" hidden="1">
+      <c r="A301" s="85"/>
       <c r="B301" s="71" t="s">
         <v>639</v>
       </c>
@@ -21496,8 +21503,8 @@
       </c>
       <c r="V301" s="71"/>
     </row>
-    <row r="302" spans="1:22" ht="13.9" hidden="1">
-      <c r="A302" s="94"/>
+    <row r="302" spans="1:22" ht="13.8" hidden="1">
+      <c r="A302" s="86"/>
       <c r="B302" s="71" t="s">
         <v>639</v>
       </c>
@@ -21554,7 +21561,7 @@
       </c>
     </row>
     <row r="303" spans="1:22" ht="27.6" hidden="1">
-      <c r="A303" s="93">
+      <c r="A303" s="90">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21609,8 +21616,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="304" spans="1:22" ht="13.9" hidden="1">
-      <c r="A304" s="98"/>
+    <row r="304" spans="1:22" ht="13.8" hidden="1">
+      <c r="A304" s="85"/>
       <c r="B304" s="71" t="s">
         <v>718</v>
       </c>
@@ -21665,7 +21672,7 @@
       <c r="V304" s="71"/>
     </row>
     <row r="305" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="93">
+      <c r="A305" s="90">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21720,7 +21727,7 @@
       </c>
     </row>
     <row r="306" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="98"/>
+      <c r="A306" s="85"/>
       <c r="B306" s="71" t="s">
         <v>720</v>
       </c>
@@ -21775,7 +21782,7 @@
       </c>
     </row>
     <row r="307" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="98"/>
+      <c r="A307" s="85"/>
       <c r="B307" s="71" t="s">
         <v>720</v>
       </c>
@@ -21828,8 +21835,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="308" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A308" s="94"/>
+    <row r="308" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A308" s="86"/>
       <c r="B308" s="71" t="s">
         <v>720</v>
       </c>
@@ -21944,7 +21951,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="310" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="310" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A310" s="66">
         <v>83</v>
       </c>
@@ -21957,57 +21964,57 @@
       <c r="D310" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E310" s="95">
+      <c r="E310" s="96">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="104" t="s">
+      <c r="F310" s="95" t="s">
         <v>731</v>
       </c>
-      <c r="G310" s="87" t="s">
+      <c r="G310" s="84" t="s">
         <v>732</v>
       </c>
-      <c r="H310" s="87">
+      <c r="H310" s="84">
         <v>13.3</v>
       </c>
-      <c r="I310" s="93" t="s">
+      <c r="I310" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="J310" s="93" t="s">
+      <c r="J310" s="90" t="s">
         <v>542</v>
       </c>
-      <c r="K310" s="91">
+      <c r="K310" s="87">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="91">
+      <c r="L310" s="87">
         <v>0</v>
       </c>
-      <c r="M310" s="91">
+      <c r="M310" s="87">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="88" t="s">
+      <c r="N310" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="O310" s="88" t="s">
+      <c r="O310" s="89" t="s">
         <v>733</v>
       </c>
-      <c r="P310" s="87">
+      <c r="P310" s="84">
         <v>2025</v>
       </c>
-      <c r="Q310" s="88" t="s">
+      <c r="Q310" s="89" t="s">
         <v>39</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
       <c r="T310" s="71"/>
-      <c r="U310" s="87"/>
-      <c r="V310" s="87" t="s">
+      <c r="U310" s="84"/>
+      <c r="V310" s="84" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="311" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A311" s="87">
+    <row r="311" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A311" s="84">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -22019,27 +22026,27 @@
       <c r="D311" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E311" s="96"/>
-      <c r="F311" s="88"/>
-      <c r="G311" s="87"/>
-      <c r="H311" s="87"/>
-      <c r="I311" s="94"/>
-      <c r="J311" s="94"/>
-      <c r="K311" s="91"/>
-      <c r="L311" s="91"/>
-      <c r="M311" s="91"/>
-      <c r="N311" s="88"/>
-      <c r="O311" s="88"/>
-      <c r="P311" s="87"/>
-      <c r="Q311" s="88"/>
+      <c r="E311" s="97"/>
+      <c r="F311" s="89"/>
+      <c r="G311" s="84"/>
+      <c r="H311" s="84"/>
+      <c r="I311" s="86"/>
+      <c r="J311" s="86"/>
+      <c r="K311" s="87"/>
+      <c r="L311" s="87"/>
+      <c r="M311" s="87"/>
+      <c r="N311" s="89"/>
+      <c r="O311" s="89"/>
+      <c r="P311" s="84"/>
+      <c r="Q311" s="89"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
       <c r="T311" s="71"/>
-      <c r="U311" s="87"/>
-      <c r="V311" s="87"/>
-    </row>
-    <row r="312" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A312" s="87"/>
+      <c r="U311" s="84"/>
+      <c r="V311" s="84"/>
+    </row>
+    <row r="312" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A312" s="84"/>
       <c r="B312" s="71" t="s">
         <v>730</v>
       </c>
@@ -22049,58 +22056,58 @@
       <c r="D312" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E312" s="95">
+      <c r="E312" s="96">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="88" t="s">
+      <c r="F312" s="89" t="s">
         <v>735</v>
       </c>
-      <c r="G312" s="87" t="s">
+      <c r="G312" s="84" t="s">
         <v>736</v>
       </c>
-      <c r="H312" s="87">
+      <c r="H312" s="84">
         <v>31.12</v>
       </c>
-      <c r="I312" s="93" t="s">
+      <c r="I312" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="J312" s="93" t="s">
+      <c r="J312" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="K312" s="91">
+      <c r="K312" s="87">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="91">
+      <c r="L312" s="87">
         <v>0</v>
       </c>
-      <c r="M312" s="91">
+      <c r="M312" s="87">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="88" t="s">
+      <c r="N312" s="89" t="s">
         <v>737</v>
       </c>
-      <c r="O312" s="88" t="s">
+      <c r="O312" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="P312" s="87">
+      <c r="P312" s="84">
         <v>2019</v>
       </c>
-      <c r="Q312" s="88" t="s">
+      <c r="Q312" s="89" t="s">
         <v>53</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
       <c r="T312" s="71"/>
-      <c r="U312" s="105">
+      <c r="U312" s="88">
         <v>1</v>
       </c>
-      <c r="V312" s="87" t="s">
+      <c r="V312" s="84" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="313" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A313" s="87"/>
+    <row r="313" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A313" s="84"/>
       <c r="B313" s="71" t="s">
         <v>734</v>
       </c>
@@ -22110,27 +22117,27 @@
       <c r="D313" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E313" s="96"/>
-      <c r="F313" s="88"/>
-      <c r="G313" s="87"/>
-      <c r="H313" s="87"/>
-      <c r="I313" s="94"/>
-      <c r="J313" s="94"/>
-      <c r="K313" s="91"/>
-      <c r="L313" s="91"/>
-      <c r="M313" s="91"/>
-      <c r="N313" s="88"/>
-      <c r="O313" s="88"/>
-      <c r="P313" s="87"/>
-      <c r="Q313" s="88"/>
+      <c r="E313" s="97"/>
+      <c r="F313" s="89"/>
+      <c r="G313" s="84"/>
+      <c r="H313" s="84"/>
+      <c r="I313" s="86"/>
+      <c r="J313" s="86"/>
+      <c r="K313" s="87"/>
+      <c r="L313" s="87"/>
+      <c r="M313" s="87"/>
+      <c r="N313" s="89"/>
+      <c r="O313" s="89"/>
+      <c r="P313" s="84"/>
+      <c r="Q313" s="89"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
       <c r="T313" s="71"/>
-      <c r="U313" s="105"/>
-      <c r="V313" s="87"/>
-    </row>
-    <row r="314" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A314" s="87"/>
+      <c r="U313" s="88"/>
+      <c r="V313" s="84"/>
+    </row>
+    <row r="314" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A314" s="84"/>
       <c r="B314" s="71" t="s">
         <v>734</v>
       </c>
@@ -22188,8 +22195,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="315" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A315" s="87"/>
+    <row r="315" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A315" s="84"/>
       <c r="B315" s="71" t="s">
         <v>734</v>
       </c>
@@ -22245,8 +22252,8 @@
       </c>
       <c r="V315" s="71"/>
     </row>
-    <row r="316" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A316" s="87"/>
+    <row r="316" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A316" s="84"/>
       <c r="B316" s="71" t="s">
         <v>734</v>
       </c>
@@ -22303,7 +22310,7 @@
       </c>
       <c r="V316" s="71"/>
     </row>
-    <row r="317" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="317" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A317" s="72"/>
       <c r="B317" s="71" t="s">
         <v>740</v>
@@ -22358,7 +22365,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="318" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+    <row r="318" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A318" s="72"/>
       <c r="B318" s="71" t="s">
         <v>740</v>
@@ -22402,8 +22409,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="319" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A319" s="93">
+    <row r="319" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A319" s="90">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22452,8 +22459,8 @@
       <c r="U319" s="80"/>
       <c r="V319" s="71"/>
     </row>
-    <row r="320" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A320" s="94"/>
+    <row r="320" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A320" s="86"/>
       <c r="B320" s="71" t="s">
         <v>740</v>
       </c>
@@ -22506,8 +22513,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="321" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A321" s="99">
+    <row r="321" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A321" s="91">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22561,8 +22568,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="322" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A322" s="100"/>
+    <row r="322" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A322" s="92"/>
       <c r="B322" s="66" t="s">
         <v>746</v>
       </c>
@@ -22612,8 +22619,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="323" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A323" s="100"/>
+    <row r="323" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A323" s="92"/>
       <c r="B323" s="66" t="s">
         <v>746</v>
       </c>
@@ -22667,8 +22674,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="324" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A324" s="100"/>
+    <row r="324" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A324" s="92"/>
       <c r="B324" s="66" t="s">
         <v>746</v>
       </c>
@@ -22723,7 +22730,7 @@
       </c>
     </row>
     <row r="325" spans="1:22" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="98"/>
+      <c r="A325" s="85"/>
       <c r="B325" s="66" t="s">
         <v>746</v>
       </c>
@@ -22775,8 +22782,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="326" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A326" s="98"/>
+    <row r="326" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A326" s="85"/>
       <c r="B326" s="66" t="s">
         <v>746</v>
       </c>
@@ -22828,8 +22835,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="327" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A327" s="100"/>
+    <row r="327" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A327" s="92"/>
       <c r="B327" s="66" t="s">
         <v>746</v>
       </c>
@@ -22885,8 +22892,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="328" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A328" s="100"/>
+    <row r="328" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A328" s="92"/>
       <c r="B328" s="71" t="s">
         <v>746</v>
       </c>
@@ -22938,8 +22945,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="329" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A329" s="100"/>
+    <row r="329" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A329" s="92"/>
       <c r="B329" s="71" t="s">
         <v>746</v>
       </c>
@@ -22993,8 +23000,8 @@
       </c>
       <c r="V329" s="71"/>
     </row>
-    <row r="330" spans="1:22" ht="13.9" hidden="1">
-      <c r="A330" s="101"/>
+    <row r="330" spans="1:22" ht="13.8" hidden="1">
+      <c r="A330" s="93"/>
       <c r="B330" s="71" t="s">
         <v>746</v>
       </c>
@@ -23048,7 +23055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="331" spans="1:22" ht="41.45" hidden="1" customHeight="1">
+    <row r="331" spans="1:22" ht="41.4" hidden="1" customHeight="1">
       <c r="A331" s="68"/>
       <c r="B331" s="71" t="s">
         <v>764</v>
@@ -23101,7 +23108,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="332" spans="1:22" ht="13.9" hidden="1">
+    <row r="332" spans="1:22" ht="13.8" hidden="1">
       <c r="A332" s="66">
         <v>88</v>
       </c>
@@ -23131,7 +23138,7 @@
       <c r="U332" s="66"/>
       <c r="V332" s="66"/>
     </row>
-    <row r="333" spans="1:22" ht="41.45" hidden="1">
+    <row r="333" spans="1:22" ht="41.4" hidden="1">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>767</v>
@@ -23184,7 +23191,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:22" ht="13.9" hidden="1">
+    <row r="334" spans="1:22" ht="13.8" hidden="1">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>767</v>
@@ -23230,8 +23237,8 @@
         <v>590</v>
       </c>
     </row>
-    <row r="335" spans="1:22" ht="41.45" hidden="1">
-      <c r="A335" s="93">
+    <row r="335" spans="1:22" ht="41.4" hidden="1">
+      <c r="A335" s="90">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -23293,8 +23300,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="336" spans="1:22" ht="44.45" hidden="1" customHeight="1">
-      <c r="A336" s="98"/>
+    <row r="336" spans="1:22" ht="44.4" hidden="1" customHeight="1">
+      <c r="A336" s="85"/>
       <c r="B336" s="71" t="s">
         <v>767</v>
       </c>
@@ -23347,8 +23354,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="155.44999999999999" hidden="1" customHeight="1">
-      <c r="A337" s="98"/>
+    <row r="337" spans="1:23" ht="155.4" hidden="1" customHeight="1">
+      <c r="A337" s="85"/>
       <c r="B337" s="71" t="s">
         <v>767</v>
       </c>
@@ -23401,8 +23408,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="13.9" hidden="1">
-      <c r="A338" s="94"/>
+    <row r="338" spans="1:23" ht="13.8" hidden="1">
+      <c r="A338" s="86"/>
       <c r="B338" s="71" t="s">
         <v>767</v>
       </c>
@@ -23505,8 +23512,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="40.9" hidden="1" customHeight="1">
-      <c r="A340" s="87">
+    <row r="340" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A340" s="84">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23564,8 +23571,8 @@
       </c>
       <c r="W340" s="33"/>
     </row>
-    <row r="341" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A341" s="87"/>
+    <row r="341" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
+      <c r="A341" s="84"/>
       <c r="B341" s="71" t="s">
         <v>775</v>
       </c>
@@ -23620,8 +23627,8 @@
       <c r="V341" s="66"/>
       <c r="W341" s="33"/>
     </row>
-    <row r="342" spans="1:23" ht="13.9" hidden="1">
-      <c r="A342" s="87">
+    <row r="342" spans="1:23" ht="13.8" hidden="1">
+      <c r="A342" s="84">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23679,8 +23686,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="13.9" hidden="1">
-      <c r="A343" s="87"/>
+    <row r="343" spans="1:23" ht="13.8" hidden="1">
+      <c r="A343" s="84"/>
       <c r="B343" s="71" t="s">
         <v>778</v>
       </c>
@@ -23737,7 +23744,7 @@
       </c>
     </row>
     <row r="344" spans="1:23" ht="27.6" hidden="1">
-      <c r="A344" s="87"/>
+      <c r="A344" s="84"/>
       <c r="B344" s="71" t="s">
         <v>778</v>
       </c>
@@ -23789,8 +23796,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="13.9" hidden="1">
-      <c r="A345" s="87"/>
+    <row r="345" spans="1:23" ht="13.8" hidden="1">
+      <c r="A345" s="84"/>
       <c r="B345" s="71" t="s">
         <v>778</v>
       </c>
@@ -23847,7 +23854,7 @@
       </c>
     </row>
     <row r="346" spans="1:23" ht="27.6" hidden="1">
-      <c r="A346" s="87"/>
+      <c r="A346" s="84"/>
       <c r="B346" s="71" t="s">
         <v>778</v>
       </c>
@@ -23901,7 +23908,7 @@
       </c>
     </row>
     <row r="347" spans="1:23" ht="27.6" hidden="1">
-      <c r="A347" s="87"/>
+      <c r="A347" s="84"/>
       <c r="B347" s="71" t="s">
         <v>778</v>
       </c>
@@ -23947,8 +23954,8 @@
         <v>789</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="13.9" hidden="1">
-      <c r="A348" s="87"/>
+    <row r="348" spans="1:23" ht="13.8" hidden="1">
+      <c r="A348" s="84"/>
       <c r="B348" s="71" t="s">
         <v>778</v>
       </c>
@@ -24004,8 +24011,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="61.15" hidden="1" customHeight="1">
-      <c r="A349" s="87">
+    <row r="349" spans="1:23" ht="61.2" hidden="1" customHeight="1">
+      <c r="A349" s="84">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -24062,8 +24069,8 @@
       </c>
       <c r="V349" s="71"/>
     </row>
-    <row r="350" spans="1:23" ht="61.15" hidden="1" customHeight="1">
-      <c r="A350" s="87"/>
+    <row r="350" spans="1:23" ht="61.2" hidden="1" customHeight="1">
+      <c r="A350" s="84"/>
       <c r="B350" s="71" t="s">
         <v>790</v>
       </c>
@@ -24117,8 +24124,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="13.9" hidden="1">
-      <c r="A351" s="87"/>
+    <row r="351" spans="1:23" ht="13.8" hidden="1">
+      <c r="A351" s="84"/>
       <c r="B351" s="71" t="s">
         <v>790</v>
       </c>
@@ -24174,8 +24181,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="94.15" hidden="1" customHeight="1">
-      <c r="A352" s="87">
+    <row r="352" spans="1:23" ht="94.2" hidden="1" customHeight="1">
+      <c r="A352" s="84">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -24233,8 +24240,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="353" spans="1:22" ht="94.15" hidden="1" customHeight="1">
-      <c r="A353" s="87"/>
+    <row r="353" spans="1:22" ht="94.2" hidden="1" customHeight="1">
+      <c r="A353" s="84"/>
       <c r="B353" s="71" t="s">
         <v>795</v>
       </c>
@@ -24287,8 +24294,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="354" spans="1:22" ht="94.15" hidden="1" customHeight="1">
-      <c r="A354" s="87"/>
+    <row r="354" spans="1:22" ht="94.2" hidden="1" customHeight="1">
+      <c r="A354" s="84"/>
       <c r="B354" s="71" t="s">
         <v>795</v>
       </c>
@@ -24344,8 +24351,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="355" spans="1:22" ht="46.9" hidden="1" customHeight="1">
-      <c r="A355" s="87"/>
+    <row r="355" spans="1:22" ht="46.95" hidden="1" customHeight="1">
+      <c r="A355" s="84"/>
       <c r="B355" s="71" t="s">
         <v>795</v>
       </c>
@@ -24405,8 +24412,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="356" spans="1:22" ht="27.6" hidden="1">
-      <c r="A356" s="87"/>
+    <row r="356" spans="1:22" ht="13.8" hidden="1">
+      <c r="A356" s="84"/>
       <c r="B356" s="71" t="s">
         <v>795</v>
       </c>
@@ -24460,8 +24467,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="357" spans="1:22" ht="13.9" hidden="1">
-      <c r="A357" s="87"/>
+    <row r="357" spans="1:22" ht="13.8" hidden="1">
+      <c r="A357" s="84"/>
       <c r="B357" s="71" t="s">
         <v>795</v>
       </c>
@@ -24628,7 +24635,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="360" spans="1:22" ht="65.45" hidden="1" customHeight="1">
+    <row r="360" spans="1:22" ht="65.400000000000006" hidden="1" customHeight="1">
       <c r="A360" s="48">
         <v>94</v>
       </c>
@@ -24799,8 +24806,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="363" spans="1:22" ht="13.9" hidden="1">
-      <c r="A363" s="87"/>
+    <row r="363" spans="1:22" ht="13.8" hidden="1">
+      <c r="A363" s="84"/>
       <c r="B363" s="71" t="s">
         <v>815</v>
       </c>
@@ -24855,8 +24862,8 @@
       </c>
       <c r="V363" s="71"/>
     </row>
-    <row r="364" spans="1:22" ht="13.9" hidden="1">
-      <c r="A364" s="87"/>
+    <row r="364" spans="1:22" ht="13.8" hidden="1">
+      <c r="A364" s="84"/>
       <c r="B364" s="71" t="s">
         <v>815</v>
       </c>
@@ -24912,7 +24919,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="365" spans="1:22" ht="13.9" hidden="1">
+    <row r="365" spans="1:22" ht="13.8" hidden="1">
       <c r="A365" s="68">
         <v>96</v>
       </c>
@@ -24969,7 +24976,7 @@
       </c>
       <c r="V365" s="66"/>
     </row>
-    <row r="366" spans="1:22" ht="13.9" hidden="1">
+    <row r="366" spans="1:22" ht="13.8" hidden="1">
       <c r="A366" s="68"/>
       <c r="B366" s="71" t="s">
         <v>819</v>
@@ -25024,7 +25031,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="367" spans="1:22" ht="13.9" hidden="1">
+    <row r="367" spans="1:22" ht="13.8" hidden="1">
       <c r="A367" s="66">
         <v>96</v>
       </c>
@@ -25081,8 +25088,8 @@
       </c>
       <c r="V367" s="71"/>
     </row>
-    <row r="368" spans="1:22" ht="41.45" hidden="1">
-      <c r="A368" s="93">
+    <row r="368" spans="1:22" ht="27.6" hidden="1">
+      <c r="A368" s="90">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -25133,8 +25140,8 @@
         <v>387</v>
       </c>
     </row>
-    <row r="369" spans="1:22" ht="41.45" hidden="1">
-      <c r="A369" s="98"/>
+    <row r="369" spans="1:22" ht="41.4" hidden="1">
+      <c r="A369" s="85"/>
       <c r="B369" s="71" t="s">
         <v>822</v>
       </c>
@@ -25194,8 +25201,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="370" spans="1:22" ht="41.45" hidden="1">
-      <c r="A370" s="98"/>
+    <row r="370" spans="1:22" ht="27.6" hidden="1">
+      <c r="A370" s="85"/>
       <c r="B370" s="71" t="s">
         <v>822</v>
       </c>
@@ -25249,7 +25256,7 @@
       </c>
     </row>
     <row r="371" spans="1:22" ht="27.6" hidden="1">
-      <c r="A371" s="98"/>
+      <c r="A371" s="85"/>
       <c r="B371" s="71" t="s">
         <v>822</v>
       </c>
@@ -25306,7 +25313,7 @@
       </c>
     </row>
     <row r="372" spans="1:22" ht="27.6" hidden="1">
-      <c r="A372" s="94"/>
+      <c r="A372" s="86"/>
       <c r="B372" s="71" t="s">
         <v>822</v>
       </c>
@@ -25361,8 +25368,8 @@
       </c>
       <c r="V372" s="71"/>
     </row>
-    <row r="373" spans="1:22" ht="148.9" hidden="1" customHeight="1">
-      <c r="A373" s="87">
+    <row r="373" spans="1:22" ht="148.94999999999999" hidden="1" customHeight="1">
+      <c r="A373" s="84">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25417,8 +25424,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="374" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A374" s="87"/>
+    <row r="374" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+      <c r="A374" s="84"/>
       <c r="B374" s="71" t="s">
         <v>828</v>
       </c>
@@ -25471,8 +25478,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="375" spans="1:22" ht="34.9" hidden="1" customHeight="1">
-      <c r="A375" s="87"/>
+    <row r="375" spans="1:22" ht="34.950000000000003" hidden="1" customHeight="1">
+      <c r="A375" s="84"/>
       <c r="B375" s="71" t="s">
         <v>828</v>
       </c>
@@ -25525,8 +25532,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="376" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A376" s="87"/>
+    <row r="376" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A376" s="84"/>
       <c r="B376" s="71" t="s">
         <v>828</v>
       </c>
@@ -25579,8 +25586,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="377" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A377" s="87"/>
+    <row r="377" spans="1:22" ht="122.4" hidden="1" customHeight="1">
+      <c r="A377" s="84"/>
       <c r="B377" s="71" t="s">
         <v>828</v>
       </c>
@@ -25623,8 +25630,8 @@
         <v>841</v>
       </c>
     </row>
-    <row r="378" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A378" s="87"/>
+    <row r="378" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A378" s="84"/>
       <c r="B378" s="71" t="s">
         <v>828</v>
       </c>
@@ -25676,8 +25683,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A379" s="87"/>
+    <row r="379" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A379" s="84"/>
       <c r="B379" s="71" t="s">
         <v>828</v>
       </c>
@@ -25729,8 +25736,8 @@
         <v>844</v>
       </c>
     </row>
-    <row r="380" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A380" s="87"/>
+    <row r="380" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A380" s="84"/>
       <c r="B380" s="71" t="s">
         <v>828</v>
       </c>
@@ -25776,8 +25783,8 @@
         <v>846</v>
       </c>
     </row>
-    <row r="381" spans="1:22" ht="13.9" hidden="1">
-      <c r="A381" s="87"/>
+    <row r="381" spans="1:22" ht="13.8" hidden="1">
+      <c r="A381" s="84"/>
       <c r="B381" s="71" t="s">
         <v>828</v>
       </c>
@@ -25826,8 +25833,8 @@
       </c>
       <c r="V381" s="71"/>
     </row>
-    <row r="382" spans="1:22" ht="13.9" hidden="1">
-      <c r="A382" s="87"/>
+    <row r="382" spans="1:22" ht="13.8" hidden="1">
+      <c r="A382" s="84"/>
       <c r="B382" s="71" t="s">
         <v>828</v>
       </c>
@@ -25881,8 +25888,8 @@
       </c>
       <c r="V382" s="71"/>
     </row>
-    <row r="383" spans="1:22" ht="13.9" hidden="1">
-      <c r="A383" s="87"/>
+    <row r="383" spans="1:22" ht="13.8" hidden="1">
+      <c r="A383" s="84"/>
       <c r="B383" s="71" t="s">
         <v>828</v>
       </c>
@@ -25934,8 +25941,8 @@
         <v>852</v>
       </c>
     </row>
-    <row r="384" spans="1:22" ht="13.9" hidden="1">
-      <c r="A384" s="87"/>
+    <row r="384" spans="1:22" ht="13.8" hidden="1">
+      <c r="A384" s="84"/>
       <c r="B384" s="71" t="s">
         <v>828</v>
       </c>
@@ -25990,7 +25997,7 @@
       <c r="V384" s="71"/>
     </row>
     <row r="385" spans="1:22" ht="27.6" hidden="1">
-      <c r="A385" s="94">
+      <c r="A385" s="86">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -26045,8 +26052,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="386" spans="1:22" ht="163.15" hidden="1" customHeight="1">
-      <c r="A386" s="87"/>
+    <row r="386" spans="1:22" ht="163.19999999999999" hidden="1" customHeight="1">
+      <c r="A386" s="84"/>
       <c r="B386" s="71" t="s">
         <v>856</v>
       </c>
@@ -26099,8 +26106,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="387" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A387" s="87"/>
+    <row r="387" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+      <c r="A387" s="84"/>
       <c r="B387" s="71" t="s">
         <v>856</v>
       </c>
@@ -26156,8 +26163,8 @@
       </c>
       <c r="V387" s="71"/>
     </row>
-    <row r="388" spans="1:22" ht="13.9" hidden="1">
-      <c r="A388" s="87"/>
+    <row r="388" spans="1:22" ht="13.8" hidden="1">
+      <c r="A388" s="84"/>
       <c r="B388" s="71" t="s">
         <v>856</v>
       </c>
@@ -26211,8 +26218,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:22" ht="13.9" hidden="1">
-      <c r="A389" s="87"/>
+    <row r="389" spans="1:22" ht="13.8" hidden="1">
+      <c r="A389" s="84"/>
       <c r="B389" s="71" t="s">
         <v>855</v>
       </c>
@@ -26266,8 +26273,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="390" spans="1:22" ht="13.9" hidden="1">
-      <c r="A390" s="87"/>
+    <row r="390" spans="1:22" ht="13.8" hidden="1">
+      <c r="A390" s="84"/>
       <c r="B390" s="71" t="s">
         <v>855</v>
       </c>
@@ -26323,8 +26330,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="391" spans="1:22" ht="13.9" hidden="1">
-      <c r="A391" s="87"/>
+    <row r="391" spans="1:22" ht="13.8" hidden="1">
+      <c r="A391" s="84"/>
       <c r="B391" s="71" t="s">
         <v>855</v>
       </c>
@@ -26365,8 +26372,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="392" spans="1:22" ht="13.9" hidden="1">
-      <c r="A392" s="87"/>
+    <row r="392" spans="1:22" ht="13.8" hidden="1">
+      <c r="A392" s="84"/>
       <c r="B392" s="66" t="s">
         <v>855</v>
       </c>
@@ -26420,7 +26427,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="393" spans="1:22" ht="148.15" hidden="1" customHeight="1">
+    <row r="393" spans="1:22" ht="148.19999999999999" hidden="1" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>865</v>
@@ -26474,8 +26481,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="394" spans="1:22" ht="58.15" hidden="1" customHeight="1">
-      <c r="A394" s="87">
+    <row r="394" spans="1:22" ht="58.2" hidden="1" customHeight="1">
+      <c r="A394" s="84">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26530,8 +26537,8 @@
         <v>868</v>
       </c>
     </row>
-    <row r="395" spans="1:22" ht="41.45" hidden="1">
-      <c r="A395" s="87"/>
+    <row r="395" spans="1:22" ht="41.4" hidden="1">
+      <c r="A395" s="84"/>
       <c r="B395" s="66" t="s">
         <v>865</v>
       </c>
@@ -26585,7 +26592,7 @@
       </c>
     </row>
     <row r="396" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="87"/>
+      <c r="A396" s="84"/>
       <c r="B396" s="71" t="s">
         <v>865</v>
       </c>
@@ -26642,7 +26649,7 @@
       </c>
     </row>
     <row r="397" spans="1:22" ht="27.6" hidden="1">
-      <c r="A397" s="87"/>
+      <c r="A397" s="84"/>
       <c r="B397" s="71" t="s">
         <v>865</v>
       </c>
@@ -26695,7 +26702,7 @@
       </c>
     </row>
     <row r="398" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A398" s="87"/>
+      <c r="A398" s="84"/>
       <c r="B398" s="71" t="s">
         <v>865</v>
       </c>
@@ -26749,8 +26756,8 @@
       </c>
       <c r="V398" s="71"/>
     </row>
-    <row r="399" spans="1:22" ht="13.9" hidden="1">
-      <c r="A399" s="87"/>
+    <row r="399" spans="1:22" ht="13.8" hidden="1">
+      <c r="A399" s="84"/>
       <c r="B399" s="71" t="s">
         <v>865</v>
       </c>
@@ -26805,7 +26812,7 @@
       <c r="V399" s="71"/>
     </row>
     <row r="400" spans="1:22" ht="27.6" hidden="1">
-      <c r="A400" s="102">
+      <c r="A400" s="94">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26862,8 +26869,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="401" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A401" s="102"/>
+    <row r="401" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+      <c r="A401" s="94"/>
       <c r="B401" s="71" t="s">
         <v>875</v>
       </c>
@@ -26904,8 +26911,8 @@
       <c r="U401" s="80"/>
       <c r="V401" s="66"/>
     </row>
-    <row r="402" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A402" s="102"/>
+    <row r="402" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+      <c r="A402" s="94"/>
       <c r="B402" s="71" t="s">
         <v>875</v>
       </c>
@@ -26959,8 +26966,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="403" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A403" s="102"/>
+    <row r="403" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+      <c r="A403" s="94"/>
       <c r="B403" s="71" t="s">
         <v>875</v>
       </c>
@@ -27016,8 +27023,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="404" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A404" s="102"/>
+    <row r="404" spans="1:22" ht="31.95" hidden="1" customHeight="1">
+      <c r="A404" s="94"/>
       <c r="B404" s="71" t="s">
         <v>875</v>
       </c>
@@ -27071,8 +27078,8 @@
       </c>
       <c r="V404" s="71"/>
     </row>
-    <row r="405" spans="1:22" ht="13.9" hidden="1">
-      <c r="A405" s="102"/>
+    <row r="405" spans="1:22" ht="13.8" hidden="1">
+      <c r="A405" s="94"/>
       <c r="B405" s="71" t="s">
         <v>875</v>
       </c>
@@ -27129,7 +27136,7 @@
       </c>
     </row>
     <row r="406" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="87">
+      <c r="A406" s="84">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -27184,8 +27191,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="407" spans="1:22" ht="13.9" hidden="1">
-      <c r="A407" s="87"/>
+    <row r="407" spans="1:22" ht="13.8" hidden="1">
+      <c r="A407" s="84"/>
       <c r="B407" s="71" t="s">
         <v>882</v>
       </c>
@@ -27241,8 +27248,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="408" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A408" s="87">
+    <row r="408" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A408" s="84">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -27298,8 +27305,8 @@
         <v>593</v>
       </c>
     </row>
-    <row r="409" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A409" s="87"/>
+    <row r="409" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A409" s="84"/>
       <c r="B409" s="71" t="s">
         <v>886</v>
       </c>
@@ -27355,8 +27362,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="410" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A410" s="87"/>
+    <row r="410" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A410" s="84"/>
       <c r="B410" s="71" t="s">
         <v>886</v>
       </c>
@@ -27411,8 +27418,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="411" spans="1:22" ht="13.9" hidden="1">
-      <c r="A411" s="87"/>
+    <row r="411" spans="1:22" ht="13.8" hidden="1">
+      <c r="A411" s="84"/>
       <c r="B411" s="71" t="s">
         <v>886</v>
       </c>
@@ -27469,7 +27476,7 @@
       </c>
     </row>
     <row r="412" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="87">
+      <c r="A412" s="84">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27525,7 +27532,7 @@
       </c>
     </row>
     <row r="413" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="87"/>
+      <c r="A413" s="84"/>
       <c r="B413" s="71" t="s">
         <v>891</v>
       </c>
@@ -27586,7 +27593,7 @@
       </c>
     </row>
     <row r="414" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="87"/>
+      <c r="A414" s="84"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27609,8 +27616,8 @@
       <c r="U414" s="80"/>
       <c r="V414" s="71"/>
     </row>
-    <row r="415" spans="1:22" ht="55.15" hidden="1">
-      <c r="A415" s="87"/>
+    <row r="415" spans="1:22" ht="55.2" hidden="1">
+      <c r="A415" s="84"/>
       <c r="B415" s="71" t="s">
         <v>891</v>
       </c>
@@ -27663,8 +27670,8 @@
         <v>897</v>
       </c>
     </row>
-    <row r="416" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A416" s="87"/>
+    <row r="416" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A416" s="84"/>
       <c r="B416" s="71" t="s">
         <v>891</v>
       </c>
@@ -27719,8 +27726,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="417" spans="1:22" ht="41.45" hidden="1">
-      <c r="A417" s="87">
+    <row r="417" spans="1:22" ht="41.4" hidden="1">
+      <c r="A417" s="84">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27775,8 +27782,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="418" spans="1:22" ht="142.9" hidden="1" customHeight="1">
-      <c r="A418" s="87"/>
+    <row r="418" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
+      <c r="A418" s="84"/>
       <c r="B418" s="71" t="s">
         <v>898</v>
       </c>
@@ -27823,8 +27830,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="419" spans="1:22" ht="13.9" hidden="1">
-      <c r="A419" s="87"/>
+    <row r="419" spans="1:22" ht="13.8" hidden="1">
+      <c r="A419" s="84"/>
       <c r="B419" s="71" t="s">
         <v>898</v>
       </c>
@@ -27880,8 +27887,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="420" spans="1:22" ht="13.9" hidden="1">
-      <c r="A420" s="87"/>
+    <row r="420" spans="1:22" ht="13.8" hidden="1">
+      <c r="A420" s="84"/>
       <c r="B420" s="71" t="s">
         <v>898</v>
       </c>
@@ -27937,8 +27944,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="421" spans="1:22" ht="13.9" hidden="1">
-      <c r="A421" s="87"/>
+    <row r="421" spans="1:22" ht="13.8" hidden="1">
+      <c r="A421" s="84"/>
       <c r="B421" s="71" t="s">
         <v>898</v>
       </c>
@@ -27995,7 +28002,7 @@
       </c>
     </row>
     <row r="422" spans="1:22" ht="27.6" hidden="1">
-      <c r="A422" s="87"/>
+      <c r="A422" s="84"/>
       <c r="B422" s="71" t="s">
         <v>898</v>
       </c>
@@ -28038,8 +28045,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="423" spans="1:22" ht="13.9" hidden="1">
-      <c r="A423" s="87"/>
+    <row r="423" spans="1:22" ht="13.8" hidden="1">
+      <c r="A423" s="84"/>
       <c r="B423" s="71" t="s">
         <v>898</v>
       </c>
@@ -28089,8 +28096,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="424" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A424" s="87"/>
+    <row r="424" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A424" s="84"/>
       <c r="B424" s="71" t="s">
         <v>898</v>
       </c>
@@ -28248,8 +28255,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="427" spans="1:22" ht="41.45" hidden="1">
-      <c r="A427" s="87">
+    <row r="427" spans="1:22" ht="27.6" hidden="1">
+      <c r="A427" s="84">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -28306,8 +28313,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="428" spans="1:22" ht="13.9" hidden="1">
-      <c r="A428" s="87"/>
+    <row r="428" spans="1:22" ht="13.8" hidden="1">
+      <c r="A428" s="84"/>
       <c r="B428" s="71" t="s">
         <v>915</v>
       </c>
@@ -28361,8 +28368,8 @@
       </c>
       <c r="V428" s="71"/>
     </row>
-    <row r="429" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A429" s="87"/>
+    <row r="429" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A429" s="84"/>
       <c r="B429" s="71" t="s">
         <v>915</v>
       </c>
@@ -28414,8 +28421,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="430" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A430" s="87"/>
+    <row r="430" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A430" s="84"/>
       <c r="B430" s="71" t="s">
         <v>914</v>
       </c>
@@ -28467,8 +28474,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="431" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A431" s="87"/>
+    <row r="431" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+      <c r="A431" s="84"/>
       <c r="B431" s="71" t="s">
         <v>914</v>
       </c>
@@ -28520,8 +28527,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="432" spans="1:22" ht="13.9" hidden="1">
-      <c r="A432" s="87"/>
+    <row r="432" spans="1:22" ht="13.8" hidden="1">
+      <c r="A432" s="84"/>
       <c r="B432" s="71" t="s">
         <v>915</v>
       </c>
@@ -28575,8 +28582,8 @@
       </c>
       <c r="V432" s="71"/>
     </row>
-    <row r="433" spans="1:22" ht="13.9" hidden="1">
-      <c r="A433" s="87"/>
+    <row r="433" spans="1:22" ht="13.8" hidden="1">
+      <c r="A433" s="84"/>
       <c r="B433" s="71" t="s">
         <v>914</v>
       </c>
@@ -28630,8 +28637,8 @@
       </c>
       <c r="V433" s="66"/>
     </row>
-    <row r="434" spans="1:22" ht="27.6" hidden="1">
-      <c r="A434" s="98"/>
+    <row r="434" spans="1:22" ht="13.8" hidden="1">
+      <c r="A434" s="85"/>
       <c r="B434" s="71" t="s">
         <v>926</v>
       </c>
@@ -28653,38 +28660,38 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="91">
+      <c r="K434" s="87">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="91">
+      <c r="L434" s="87">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="91">
+      <c r="M434" s="87">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="88" t="s">
+      <c r="N434" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="O434" s="88" t="s">
+      <c r="O434" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="P434" s="87">
+      <c r="P434" s="84">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
       <c r="T434" s="66"/>
-      <c r="U434" s="105">
+      <c r="U434" s="88">
         <v>0.65</v>
       </c>
-      <c r="V434" s="87" t="s">
+      <c r="V434" s="84" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="435" spans="1:22" ht="27.6" hidden="1">
-      <c r="A435" s="98"/>
+      <c r="A435" s="85"/>
       <c r="B435" s="71" t="s">
         <v>926</v>
       </c>
@@ -28706,21 +28713,21 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="91"/>
-      <c r="L435" s="91"/>
-      <c r="M435" s="91"/>
-      <c r="N435" s="88"/>
-      <c r="O435" s="88"/>
-      <c r="P435" s="87"/>
+      <c r="K435" s="87"/>
+      <c r="L435" s="87"/>
+      <c r="M435" s="87"/>
+      <c r="N435" s="89"/>
+      <c r="O435" s="89"/>
+      <c r="P435" s="84"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
       <c r="T435" s="66"/>
-      <c r="U435" s="105"/>
-      <c r="V435" s="87"/>
-    </row>
-    <row r="436" spans="1:22" ht="13.9" hidden="1">
-      <c r="A436" s="98"/>
+      <c r="U435" s="88"/>
+      <c r="V435" s="84"/>
+    </row>
+    <row r="436" spans="1:22" ht="13.8" hidden="1">
+      <c r="A436" s="85"/>
       <c r="B436" s="71" t="s">
         <v>926</v>
       </c>
@@ -28774,8 +28781,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="437" spans="1:22" ht="13.9" hidden="1">
-      <c r="A437" s="98"/>
+    <row r="437" spans="1:22" ht="13.8" hidden="1">
+      <c r="A437" s="85"/>
       <c r="B437" s="71" t="s">
         <v>930</v>
       </c>
@@ -28829,8 +28836,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="438" spans="1:22" ht="13.9" hidden="1">
-      <c r="A438" s="98"/>
+    <row r="438" spans="1:22" ht="13.8" hidden="1">
+      <c r="A438" s="85"/>
       <c r="B438" s="71" t="s">
         <v>926</v>
       </c>
@@ -28883,7 +28890,7 @@
       </c>
     </row>
     <row r="439" spans="1:22" ht="27.6" hidden="1">
-      <c r="A439" s="94"/>
+      <c r="A439" s="86"/>
       <c r="B439" s="71" t="s">
         <v>926</v>
       </c>
@@ -28937,7 +28944,7 @@
       </c>
     </row>
     <row r="440" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="93">
+      <c r="A440" s="90">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28992,7 +28999,7 @@
       </c>
     </row>
     <row r="441" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="98"/>
+      <c r="A441" s="85"/>
       <c r="B441" s="71" t="s">
         <v>938</v>
       </c>
@@ -29044,7 +29051,7 @@
       </c>
     </row>
     <row r="442" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="98"/>
+      <c r="A442" s="85"/>
       <c r="B442" s="71" t="s">
         <v>938</v>
       </c>
@@ -29100,7 +29107,7 @@
       </c>
     </row>
     <row r="443" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="98"/>
+      <c r="A443" s="85"/>
       <c r="B443" s="71" t="s">
         <v>938</v>
       </c>
@@ -29154,8 +29161,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="444" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
-      <c r="A444" s="98"/>
+    <row r="444" spans="1:22" ht="64.95" hidden="1" customHeight="1">
+      <c r="A444" s="85"/>
       <c r="B444" s="71" t="s">
         <v>938</v>
       </c>
@@ -29208,7 +29215,7 @@
       </c>
     </row>
     <row r="445" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="98"/>
+      <c r="A445" s="85"/>
       <c r="B445" s="71" t="s">
         <v>938</v>
       </c>
@@ -29259,7 +29266,7 @@
       </c>
     </row>
     <row r="446" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="98"/>
+      <c r="A446" s="85"/>
       <c r="B446" s="71" t="s">
         <v>938</v>
       </c>
@@ -29297,7 +29304,7 @@
       <c r="V446" s="71"/>
     </row>
     <row r="447" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="94"/>
+      <c r="A447" s="86"/>
       <c r="B447" s="71" t="s">
         <v>938</v>
       </c>
@@ -29352,7 +29359,7 @@
       <c r="V447" s="44"/>
     </row>
     <row r="448" spans="1:22" ht="27.6" hidden="1">
-      <c r="A448" s="87"/>
+      <c r="A448" s="84"/>
       <c r="B448" s="71" t="s">
         <v>948</v>
       </c>
@@ -29408,8 +29415,8 @@
         <v>951</v>
       </c>
     </row>
-    <row r="449" spans="1:22" ht="41.45" hidden="1">
-      <c r="A449" s="87"/>
+    <row r="449" spans="1:22" ht="41.4" hidden="1">
+      <c r="A449" s="84"/>
       <c r="B449" s="51" t="s">
         <v>948</v>
       </c>
@@ -29470,7 +29477,7 @@
       </c>
     </row>
     <row r="450" spans="1:22" ht="27.6" hidden="1">
-      <c r="A450" s="93">
+      <c r="A450" s="90">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29527,7 +29534,7 @@
       </c>
     </row>
     <row r="451" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="98"/>
+      <c r="A451" s="85"/>
       <c r="B451" s="71" t="s">
         <v>955</v>
       </c>
@@ -29582,7 +29589,7 @@
       </c>
     </row>
     <row r="452" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="98"/>
+      <c r="A452" s="85"/>
       <c r="B452" s="71" t="s">
         <v>955</v>
       </c>
@@ -29641,7 +29648,7 @@
       </c>
     </row>
     <row r="453" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="94"/>
+      <c r="A453" s="86"/>
       <c r="B453" s="71" t="s">
         <v>955</v>
       </c>
@@ -29696,7 +29703,7 @@
       </c>
     </row>
     <row r="454" spans="1:22" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="87">
+      <c r="A454" s="84">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29757,8 +29764,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="455" spans="1:22" ht="13.9" hidden="1">
-      <c r="A455" s="87"/>
+    <row r="455" spans="1:22" ht="13.8" hidden="1">
+      <c r="A455" s="84"/>
       <c r="B455" s="71" t="s">
         <v>962</v>
       </c>
@@ -29814,7 +29821,7 @@
       <c r="V455" s="71"/>
     </row>
     <row r="456" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="87"/>
+      <c r="A456" s="84"/>
       <c r="B456" s="71" t="s">
         <v>962</v>
       </c>
@@ -29872,7 +29879,7 @@
       <c r="V456" s="71"/>
     </row>
     <row r="457" spans="1:22" ht="27.6" hidden="1">
-      <c r="A457" s="87">
+      <c r="A457" s="84">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29925,8 +29932,8 @@
         <v>593</v>
       </c>
     </row>
-    <row r="458" spans="1:22" ht="13.9" hidden="1">
-      <c r="A458" s="87"/>
+    <row r="458" spans="1:22" ht="13.8" hidden="1">
+      <c r="A458" s="84"/>
       <c r="B458" s="71" t="s">
         <v>966</v>
       </c>
@@ -29979,8 +29986,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="459" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A459" s="87"/>
+    <row r="459" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A459" s="84"/>
       <c r="B459" s="71" t="s">
         <v>966</v>
       </c>
@@ -30034,8 +30041,8 @@
       </c>
       <c r="V459" s="66"/>
     </row>
-    <row r="460" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A460" s="87"/>
+    <row r="460" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+      <c r="A460" s="84"/>
       <c r="B460" s="71" t="s">
         <v>966</v>
       </c>
@@ -30084,7 +30091,7 @@
       <c r="V460" s="66"/>
     </row>
     <row r="461" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="87"/>
+      <c r="A461" s="84"/>
       <c r="B461" s="71" t="s">
         <v>966</v>
       </c>
@@ -30140,7 +30147,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="462" spans="1:22" ht="55.15" hidden="1">
+    <row r="462" spans="1:22" ht="55.2" hidden="1">
       <c r="A462" s="66"/>
       <c r="B462" s="71" t="s">
         <v>973</v>
@@ -30197,7 +30204,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="463" spans="1:22" ht="43.15" hidden="1" customHeight="1">
+    <row r="463" spans="1:22" ht="43.2" hidden="1" customHeight="1">
       <c r="A463" s="66"/>
       <c r="B463" s="71" t="s">
         <v>973</v>
@@ -30252,7 +30259,7 @@
       </c>
       <c r="V463" s="71"/>
     </row>
-    <row r="464" spans="1:22" ht="43.15" hidden="1" customHeight="1">
+    <row r="464" spans="1:22" ht="43.2" hidden="1" customHeight="1">
       <c r="A464" s="66"/>
       <c r="B464" s="71" t="s">
         <v>973</v>
@@ -30307,7 +30314,7 @@
       </c>
       <c r="V464" s="71"/>
     </row>
-    <row r="465" spans="1:22" ht="43.15" hidden="1" customHeight="1">
+    <row r="465" spans="1:22" ht="43.2" hidden="1" customHeight="1">
       <c r="A465" s="66"/>
       <c r="B465" s="71" t="s">
         <v>973</v>
@@ -30360,7 +30367,7 @@
       <c r="U465" s="80"/>
       <c r="V465" s="71"/>
     </row>
-    <row r="466" spans="1:22" ht="43.15" hidden="1" customHeight="1">
+    <row r="466" spans="1:22" ht="43.2" hidden="1" customHeight="1">
       <c r="A466" s="66"/>
       <c r="B466" s="71" t="s">
         <v>973</v>
@@ -30472,7 +30479,7 @@
       </c>
     </row>
     <row r="468" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="98"/>
+      <c r="A468" s="85"/>
       <c r="B468" s="71" t="s">
         <v>983</v>
       </c>
@@ -30524,7 +30531,7 @@
       </c>
     </row>
     <row r="469" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="98"/>
+      <c r="A469" s="85"/>
       <c r="B469" s="71" t="s">
         <v>327</v>
       </c>
@@ -30579,7 +30586,7 @@
       <c r="V469" s="71"/>
     </row>
     <row r="470" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="98"/>
+      <c r="A470" s="85"/>
       <c r="B470" s="71" t="s">
         <v>327</v>
       </c>
@@ -30634,7 +30641,7 @@
       <c r="V470" s="71"/>
     </row>
     <row r="471" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="98"/>
+      <c r="A471" s="85"/>
       <c r="B471" s="71" t="s">
         <v>327</v>
       </c>
@@ -30689,7 +30696,7 @@
       <c r="V471" s="71"/>
     </row>
     <row r="472" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="98"/>
+      <c r="A472" s="85"/>
       <c r="B472" s="71" t="s">
         <v>327</v>
       </c>
@@ -30746,7 +30753,7 @@
       </c>
     </row>
     <row r="473" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="98"/>
+      <c r="A473" s="85"/>
       <c r="B473" s="71" t="s">
         <v>327</v>
       </c>
@@ -30799,7 +30806,7 @@
       </c>
     </row>
     <row r="474" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="94"/>
+      <c r="A474" s="86"/>
       <c r="B474" s="71" t="s">
         <v>983</v>
       </c>
@@ -30850,7 +30857,7 @@
       </c>
     </row>
     <row r="475" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="87">
+      <c r="A475" s="84">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30862,7 +30869,7 @@
       <c r="D475" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E475" s="90">
+      <c r="E475" s="104">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30876,14 +30883,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="92">
+      <c r="K475" s="105">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="92">
+      <c r="L475" s="105">
         <v>0</v>
       </c>
-      <c r="M475" s="91">
+      <c r="M475" s="87">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30902,12 +30909,12 @@
       <c r="S475" s="66"/>
       <c r="T475" s="66"/>
       <c r="U475" s="71"/>
-      <c r="V475" s="88" t="s">
+      <c r="V475" s="89" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="476" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="87"/>
+      <c r="A476" s="84"/>
       <c r="B476" s="71" t="s">
         <v>995</v>
       </c>
@@ -30917,7 +30924,7 @@
       <c r="D476" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E476" s="90"/>
+      <c r="E476" s="104"/>
       <c r="F476" s="71" t="s">
         <v>177</v>
       </c>
@@ -30929,9 +30936,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="92"/>
-      <c r="L476" s="92"/>
-      <c r="M476" s="91"/>
+      <c r="K476" s="105"/>
+      <c r="L476" s="105"/>
+      <c r="M476" s="87"/>
       <c r="N476" s="71" t="s">
         <v>38</v>
       </c>
@@ -30948,10 +30955,10 @@
       <c r="S476" s="66"/>
       <c r="T476" s="66"/>
       <c r="U476" s="71"/>
-      <c r="V476" s="88"/>
+      <c r="V476" s="89"/>
     </row>
     <row r="477" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="87"/>
+      <c r="A477" s="84"/>
       <c r="B477" s="71" t="s">
         <v>995</v>
       </c>
@@ -31010,7 +31017,7 @@
       </c>
     </row>
     <row r="478" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="87"/>
+      <c r="A478" s="84"/>
       <c r="B478" s="71" t="s">
         <v>995</v>
       </c>
@@ -31288,7 +31295,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="483" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
+    <row r="483" spans="1:22" ht="35.4" hidden="1" customHeight="1">
       <c r="A483" s="66"/>
       <c r="B483" s="71" t="s">
         <v>1007</v>
@@ -31343,7 +31350,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="484" spans="1:22" ht="38.450000000000003" hidden="1" customHeight="1">
+    <row r="484" spans="1:22" ht="38.4" hidden="1" customHeight="1">
       <c r="A484" s="66"/>
       <c r="B484" s="71" t="s">
         <v>1007</v>
@@ -31453,7 +31460,7 @@
       <c r="V485" s="66"/>
     </row>
     <row r="486" spans="1:22" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="87">
+      <c r="A486" s="84">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31510,7 +31517,7 @@
       <c r="V486" s="71"/>
     </row>
     <row r="487" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="87"/>
+      <c r="A487" s="84"/>
       <c r="B487" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31563,7 +31570,7 @@
       </c>
     </row>
     <row r="488" spans="1:22" ht="96.6" hidden="1">
-      <c r="A488" s="87"/>
+      <c r="A488" s="84"/>
       <c r="B488" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31672,7 +31679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="490" spans="1:22" ht="13.9" hidden="1">
+    <row r="490" spans="1:22" ht="13.8" hidden="1">
       <c r="A490" s="68">
         <v>122</v>
       </c>
@@ -31729,8 +31736,8 @@
       </c>
       <c r="V490" s="71"/>
     </row>
-    <row r="491" spans="1:22" ht="13.9" hidden="1">
-      <c r="A491" s="98"/>
+    <row r="491" spans="1:22" ht="13.8" hidden="1">
+      <c r="A491" s="85"/>
       <c r="B491" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31784,8 +31791,8 @@
       </c>
       <c r="V491" s="71"/>
     </row>
-    <row r="492" spans="1:22" ht="13.9" hidden="1">
-      <c r="A492" s="98"/>
+    <row r="492" spans="1:22" ht="13.8" hidden="1">
+      <c r="A492" s="85"/>
       <c r="B492" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31839,8 +31846,8 @@
       </c>
       <c r="V492" s="71"/>
     </row>
-    <row r="493" spans="1:22" ht="55.15" hidden="1">
-      <c r="A493" s="98"/>
+    <row r="493" spans="1:22" ht="55.2" hidden="1">
+      <c r="A493" s="85"/>
       <c r="B493" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31892,7 +31899,7 @@
       </c>
     </row>
     <row r="494" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="94"/>
+      <c r="A494" s="86"/>
       <c r="B494" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31947,7 +31954,7 @@
       <c r="V494" s="71"/>
     </row>
     <row r="495" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="87">
+      <c r="A495" s="84">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -32006,7 +32013,7 @@
       </c>
     </row>
     <row r="496" spans="1:22" ht="27.6" hidden="1">
-      <c r="A496" s="87"/>
+      <c r="A496" s="84"/>
       <c r="B496" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32058,8 +32065,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="497" spans="1:22" ht="13.9" hidden="1">
-      <c r="A497" s="87"/>
+    <row r="497" spans="1:22" ht="13.8" hidden="1">
+      <c r="A497" s="84"/>
       <c r="B497" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32113,8 +32120,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="498" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A498" s="87"/>
+    <row r="498" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+      <c r="A498" s="84"/>
       <c r="B498" s="71" t="s">
         <v>1034</v>
       </c>
@@ -32169,7 +32176,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="499" spans="1:22" ht="40.15" hidden="1" customHeight="1">
+    <row r="499" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A499" s="66"/>
       <c r="B499" s="71" t="s">
         <v>1035</v>
@@ -32231,7 +32238,7 @@
       </c>
     </row>
     <row r="500" spans="1:22" ht="27.6" hidden="1">
-      <c r="A500" s="88">
+      <c r="A500" s="89">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -32292,8 +32299,8 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="501" spans="1:22" ht="13.9" hidden="1">
-      <c r="A501" s="88"/>
+    <row r="501" spans="1:22" ht="13.8" hidden="1">
+      <c r="A501" s="89"/>
       <c r="B501" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32345,7 +32352,7 @@
       <c r="V501" s="71"/>
     </row>
     <row r="502" spans="1:22" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="88"/>
+      <c r="A502" s="89"/>
       <c r="B502" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32401,8 +32408,8 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="503" spans="1:22" ht="41.45" hidden="1">
-      <c r="A503" s="87">
+    <row r="503" spans="1:22" ht="41.4" hidden="1">
+      <c r="A503" s="84">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -32464,8 +32471,8 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="504" spans="1:22" ht="13.9" hidden="1">
-      <c r="A504" s="87"/>
+    <row r="504" spans="1:22" ht="13.8" hidden="1">
+      <c r="A504" s="84"/>
       <c r="B504" s="71" t="s">
         <v>1043</v>
       </c>
@@ -32523,8 +32530,8 @@
       </c>
       <c r="V504" s="71"/>
     </row>
-    <row r="505" spans="1:22" ht="55.15" hidden="1">
-      <c r="A505" s="87"/>
+    <row r="505" spans="1:22" ht="55.2" hidden="1">
+      <c r="A505" s="84"/>
       <c r="B505" s="51" t="s">
         <v>1043</v>
       </c>
@@ -32582,12 +32589,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="506" spans="1:22" ht="55.9" hidden="1" customHeight="1">
+    <row r="506" spans="1:22" ht="55.95" hidden="1" customHeight="1">
       <c r="K506" s="27"/>
       <c r="M506" s="56"/>
       <c r="U506" s="57"/>
     </row>
-    <row r="507" spans="1:22" ht="13.9" hidden="1">
+    <row r="507" spans="1:22" ht="13.8" hidden="1">
       <c r="E507" s="55" t="s">
         <v>715</v>
       </c>
@@ -32597,11 +32604,11 @@
     <row r="508" spans="1:22" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>1</v>
+        <v>2.35</v>
       </c>
       <c r="K508" s="8">
         <f>SUBTOTAL(9,K96:K507)</f>
-        <v>10119116844</v>
+        <v>48324835349.090004</v>
       </c>
       <c r="M508" s="58"/>
       <c r="U508" s="29"/>
@@ -32659,24 +32666,112 @@
   <autoFilter ref="A2:V507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Cisneros"/>
-        <filter val="(No vacías)"/>
+        <filter val="Heliconia"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="V91:V92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="V475:V476"/>
+    <mergeCell ref="V434:V435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A400:A405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="P310:P311"/>
+    <mergeCell ref="V310:V311"/>
+    <mergeCell ref="U310:U311"/>
+    <mergeCell ref="A311:A316"/>
+    <mergeCell ref="F312:F313"/>
+    <mergeCell ref="G312:G313"/>
+    <mergeCell ref="K312:K313"/>
+    <mergeCell ref="L312:L313"/>
+    <mergeCell ref="M312:M313"/>
+    <mergeCell ref="N312:N313"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="L310:L311"/>
+    <mergeCell ref="M310:M311"/>
+    <mergeCell ref="N310:N311"/>
+    <mergeCell ref="O310:O311"/>
+    <mergeCell ref="Q310:Q311"/>
+    <mergeCell ref="Q312:Q313"/>
+    <mergeCell ref="O312:O313"/>
+    <mergeCell ref="P312:P313"/>
+    <mergeCell ref="V312:V313"/>
+    <mergeCell ref="U312:U313"/>
     <mergeCell ref="A319:A320"/>
     <mergeCell ref="A321:A330"/>
     <mergeCell ref="A335:A338"/>
@@ -32701,107 +32796,18 @@
     <mergeCell ref="A373:A384"/>
     <mergeCell ref="A385:A392"/>
     <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A400:A405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="P310:P311"/>
-    <mergeCell ref="V310:V311"/>
-    <mergeCell ref="U310:U311"/>
-    <mergeCell ref="A311:A316"/>
-    <mergeCell ref="F312:F313"/>
-    <mergeCell ref="G312:G313"/>
-    <mergeCell ref="K312:K313"/>
-    <mergeCell ref="L312:L313"/>
-    <mergeCell ref="M312:M313"/>
-    <mergeCell ref="N312:N313"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="L310:L311"/>
-    <mergeCell ref="M310:M311"/>
-    <mergeCell ref="N310:N311"/>
-    <mergeCell ref="O310:O311"/>
-    <mergeCell ref="Q310:Q311"/>
-    <mergeCell ref="Q312:Q313"/>
-    <mergeCell ref="O312:O313"/>
-    <mergeCell ref="P312:P313"/>
-    <mergeCell ref="V312:V313"/>
-    <mergeCell ref="U312:U313"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="V91:V92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="V475:V476"/>
-    <mergeCell ref="V434:V435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -32815,20 +32821,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE741C3-3798-4F4E-8B25-FDCA2ADDEF39}">
   <dimension ref="B2:I16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="12"/>
-    <col min="2" max="2" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="12"/>
+    <col min="2" max="2" width="15.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
     <col min="5" max="5" width="19" style="20" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="12"/>
-    <col min="11" max="11" width="9.28515625" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="12"/>
+    <col min="6" max="6" width="9.5546875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" style="12" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" style="12"/>
+    <col min="11" max="11" width="9.33203125" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="27.6">
@@ -33042,6 +33048,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -33197,31 +33220,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B10DA5-E19F-4807-B1C6-272EAAAA8A0D}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7EEC1C-A430-44AF-82CE-A6CCEA0E700D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4024,14 +4021,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -4250,7 +4247,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="107">
@@ -4258,34 +4255,34 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4299,42 +4296,42 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4358,7 +4355,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4367,13 +4364,13 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4385,7 +4382,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4394,7 +4391,7 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4406,25 +4403,25 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4436,10 +4433,10 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4451,7 +4448,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4481,7 +4478,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4490,31 +4487,55 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4529,38 +4550,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4590,14 +4587,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4635,7 +4628,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4741,7 +4734,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4883,7 +4876,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4893,40 +4886,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:X521"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="33" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="33" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" style="55" customWidth="1"/>
-    <col min="6" max="6" width="49.109375" style="33" customWidth="1"/>
-    <col min="7" max="7" width="48.33203125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="35.5546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="33" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" style="33" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="25.88671875" style="56" customWidth="1"/>
-    <col min="13" max="13" width="24.33203125" style="33" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="33" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="33" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="55" customWidth="1"/>
+    <col min="6" max="6" width="49.140625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="48.28515625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" style="33" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="25.85546875" style="56" customWidth="1"/>
+    <col min="13" max="13" width="24.28515625" style="33" customWidth="1"/>
     <col min="14" max="14" width="26" style="33" customWidth="1"/>
-    <col min="15" max="15" width="32.5546875" style="33" customWidth="1"/>
-    <col min="16" max="16" width="19.109375" style="33" customWidth="1"/>
-    <col min="17" max="17" width="20.5546875" style="33" customWidth="1"/>
-    <col min="18" max="18" width="20.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="29.33203125" style="33" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="29.109375" style="33" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="19.109375" style="59" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="39.5546875" style="33" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="24.33203125" style="33" customWidth="1"/>
-    <col min="25" max="16384" width="10.88671875" style="33"/>
+    <col min="15" max="15" width="32.5703125" style="33" customWidth="1"/>
+    <col min="16" max="16" width="19.140625" style="33" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" style="33" customWidth="1"/>
+    <col min="18" max="18" width="20.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="29.28515625" style="33" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="29.140625" style="33" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" style="59" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="39.5703125" style="33" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" style="29" customWidth="1"/>
+    <col min="24" max="24" width="24.28515625" style="33" customWidth="1"/>
+    <col min="25" max="16384" width="10.85546875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="13.8" hidden="1">
-      <c r="B1" s="99" t="s">
+    <row r="1" spans="1:24" ht="13.9" hidden="1">
+      <c r="B1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="99"/>
+      <c r="C1" s="97"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -4947,7 +4940,7 @@
       <c r="U1" s="78"/>
       <c r="V1" s="73"/>
     </row>
-    <row r="2" spans="1:24" ht="13.8">
+    <row r="2" spans="1:24" ht="13.9">
       <c r="A2" s="75"/>
       <c r="B2" s="35" t="s">
         <v>1</v>
@@ -5014,8 +5007,8 @@
       </c>
       <c r="X2" s="13"/>
     </row>
-    <row r="3" spans="1:24" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="86">
+    <row r="3" spans="1:24" ht="62.45" hidden="1" customHeight="1">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5078,8 +5071,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="86"/>
+    <row r="4" spans="1:24" ht="62.45" hidden="1" customHeight="1">
+      <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>22</v>
       </c>
@@ -5140,8 +5133,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="41.4" hidden="1">
-      <c r="A5" s="86"/>
+    <row r="5" spans="1:24" ht="41.45" hidden="1">
+      <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>22</v>
       </c>
@@ -5250,8 +5243,8 @@
       </c>
       <c r="V6" s="66"/>
     </row>
-    <row r="7" spans="1:24" ht="13.8" hidden="1">
-      <c r="A7" s="90">
+    <row r="7" spans="1:24" ht="13.9" hidden="1">
+      <c r="A7" s="93">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5286,8 +5279,8 @@
       <c r="U7" s="66"/>
       <c r="V7" s="66"/>
     </row>
-    <row r="8" spans="1:24" ht="13.8" hidden="1">
-      <c r="A8" s="85"/>
+    <row r="8" spans="1:24" ht="13.9" hidden="1">
+      <c r="A8" s="98"/>
       <c r="B8" s="71" t="s">
         <v>41</v>
       </c>
@@ -5339,8 +5332,8 @@
       </c>
       <c r="V8" s="66"/>
     </row>
-    <row r="9" spans="1:24" ht="41.4" hidden="1">
-      <c r="A9" s="85"/>
+    <row r="9" spans="1:24" ht="41.45" hidden="1">
+      <c r="A9" s="98"/>
       <c r="B9" s="71" t="s">
         <v>41</v>
       </c>
@@ -5398,8 +5391,8 @@
       </c>
       <c r="V9" s="66"/>
     </row>
-    <row r="10" spans="1:24" ht="41.4" hidden="1">
-      <c r="A10" s="86"/>
+    <row r="10" spans="1:24" ht="41.45" hidden="1">
+      <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>41</v>
       </c>
@@ -5458,7 +5451,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" ht="27.6" hidden="1">
-      <c r="A11" s="84">
+      <c r="A11" s="87">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5521,8 +5514,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="84"/>
+    <row r="12" spans="1:24" ht="52.9" hidden="1" customHeight="1">
+      <c r="A12" s="87"/>
       <c r="B12" s="71" t="s">
         <v>59</v>
       </c>
@@ -5578,8 +5571,8 @@
       </c>
       <c r="V12" s="76"/>
     </row>
-    <row r="13" spans="1:24" ht="13.8" hidden="1">
-      <c r="A13" s="84"/>
+    <row r="13" spans="1:24" ht="13.9" hidden="1">
+      <c r="A13" s="87"/>
       <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
@@ -5635,8 +5628,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="13.8" hidden="1">
-      <c r="A14" s="84"/>
+    <row r="14" spans="1:24" ht="13.9" hidden="1">
+      <c r="A14" s="87"/>
       <c r="B14" s="71" t="s">
         <v>59</v>
       </c>
@@ -5692,8 +5685,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="13.8" hidden="1">
-      <c r="A15" s="84"/>
+    <row r="15" spans="1:24" ht="13.9" hidden="1">
+      <c r="A15" s="87"/>
       <c r="B15" s="71" t="s">
         <v>59</v>
       </c>
@@ -5750,7 +5743,7 @@
       <c r="V15" s="66"/>
     </row>
     <row r="16" spans="1:24" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="84"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="71" t="s">
         <v>59</v>
       </c>
@@ -5806,7 +5799,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="13.8" hidden="1">
+    <row r="17" spans="1:22" ht="13.9" hidden="1">
       <c r="A17" s="66"/>
       <c r="B17" s="71" t="s">
         <v>85</v>
@@ -5848,7 +5841,7 @@
       <c r="U17" s="80"/>
       <c r="V17" s="71"/>
     </row>
-    <row r="18" spans="1:22" ht="61.2" hidden="1" customHeight="1">
+    <row r="18" spans="1:22" ht="61.15" hidden="1" customHeight="1">
       <c r="A18" s="66">
         <v>4</v>
       </c>
@@ -5909,7 +5902,7 @@
       </c>
       <c r="V18" s="71"/>
     </row>
-    <row r="19" spans="1:22" ht="41.4" hidden="1">
+    <row r="19" spans="1:22" ht="41.45" hidden="1">
       <c r="A19" s="66"/>
       <c r="B19" s="71" t="s">
         <v>92</v>
@@ -5970,8 +5963,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="84">
+    <row r="20" spans="1:22" ht="97.9" hidden="1" customHeight="1">
+      <c r="A20" s="87">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6033,8 +6026,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="84"/>
+    <row r="21" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A21" s="87"/>
       <c r="B21" s="71" t="s">
         <v>92</v>
       </c>
@@ -6093,7 +6086,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="27.6" hidden="1">
-      <c r="A22" s="84"/>
+      <c r="A22" s="87"/>
       <c r="B22" s="71" t="s">
         <v>92</v>
       </c>
@@ -6152,8 +6145,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="13.8" hidden="1">
-      <c r="A23" s="84"/>
+    <row r="23" spans="1:22" ht="13.9" hidden="1">
+      <c r="A23" s="87"/>
       <c r="B23" s="71" t="s">
         <v>92</v>
       </c>
@@ -6211,7 +6204,7 @@
       <c r="V23" s="71"/>
     </row>
     <row r="24" spans="1:22" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="84">
+      <c r="A24" s="87">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6272,8 +6265,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="13.8" hidden="1">
-      <c r="A25" s="84"/>
+    <row r="25" spans="1:22" ht="13.9" hidden="1">
+      <c r="A25" s="87"/>
       <c r="B25" s="71" t="s">
         <v>109</v>
       </c>
@@ -6329,8 +6322,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="84"/>
+    <row r="26" spans="1:22" ht="70.150000000000006" hidden="1" customHeight="1">
+      <c r="A26" s="87"/>
       <c r="B26" s="71" t="s">
         <v>109</v>
       </c>
@@ -6386,8 +6379,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="84"/>
+    <row r="27" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A27" s="87"/>
       <c r="B27" s="71" t="s">
         <v>109</v>
       </c>
@@ -6445,8 +6438,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="13.8" hidden="1">
-      <c r="A28" s="84"/>
+    <row r="28" spans="1:22" ht="13.9" hidden="1">
+      <c r="A28" s="87"/>
       <c r="B28" s="71" t="s">
         <v>109</v>
       </c>
@@ -6501,7 +6494,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="84"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="71" t="s">
         <v>109</v>
       </c>
@@ -6557,8 +6550,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="84"/>
+    <row r="30" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A30" s="87"/>
       <c r="B30" s="71" t="s">
         <v>109</v>
       </c>
@@ -6610,8 +6603,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="84"/>
+    <row r="31" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A31" s="87"/>
       <c r="B31" s="71" t="s">
         <v>109</v>
       </c>
@@ -6669,8 +6662,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="84"/>
+    <row r="32" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A32" s="87"/>
       <c r="B32" s="71" t="s">
         <v>109</v>
       </c>
@@ -6730,8 +6723,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="84"/>
+    <row r="33" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A33" s="87"/>
       <c r="B33" s="71" t="s">
         <v>109</v>
       </c>
@@ -6787,8 +6780,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="84"/>
+    <row r="34" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A34" s="87"/>
       <c r="B34" s="71" t="s">
         <v>109</v>
       </c>
@@ -6848,8 +6841,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="13.8" hidden="1">
-      <c r="A35" s="85"/>
+    <row r="35" spans="1:22" ht="13.9" hidden="1">
+      <c r="A35" s="98"/>
       <c r="B35" s="71" t="s">
         <v>147</v>
       </c>
@@ -6884,8 +6877,8 @@
       <c r="U35" s="1"/>
       <c r="V35" s="71"/>
     </row>
-    <row r="36" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="86"/>
+    <row r="36" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>147</v>
       </c>
@@ -6998,8 +6991,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="84">
+    <row r="38" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A38" s="87">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7060,8 +7053,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="84"/>
+    <row r="39" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A39" s="87"/>
       <c r="B39" s="71" t="s">
         <v>150</v>
       </c>
@@ -7121,8 +7114,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="84"/>
+    <row r="40" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A40" s="87"/>
       <c r="B40" s="71" t="s">
         <v>150</v>
       </c>
@@ -7179,8 +7172,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="84">
+    <row r="41" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A41" s="87">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7240,8 +7233,8 @@
       </c>
       <c r="V41" s="71"/>
     </row>
-    <row r="42" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="84"/>
+    <row r="42" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A42" s="87"/>
       <c r="B42" s="71" t="s">
         <v>160</v>
       </c>
@@ -7291,7 +7284,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="84"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="71" t="s">
         <v>160</v>
       </c>
@@ -7343,7 +7336,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="84"/>
+      <c r="A44" s="87"/>
       <c r="B44" s="71" t="s">
         <v>160</v>
       </c>
@@ -7392,7 +7385,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="27.6" hidden="1">
-      <c r="A45" s="84"/>
+      <c r="A45" s="87"/>
       <c r="B45" s="71" t="s">
         <v>160</v>
       </c>
@@ -7448,8 +7441,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="84">
+    <row r="46" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A46" s="87">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7505,8 +7498,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="13.8" hidden="1">
-      <c r="A47" s="90"/>
+    <row r="47" spans="1:22" ht="13.9" hidden="1">
+      <c r="A47" s="93"/>
       <c r="B47" s="71" t="s">
         <v>175</v>
       </c>
@@ -7560,8 +7553,8 @@
       </c>
       <c r="V47" s="71"/>
     </row>
-    <row r="48" spans="1:22" ht="13.8" hidden="1">
-      <c r="A48" s="84"/>
+    <row r="48" spans="1:22" ht="13.9" hidden="1">
+      <c r="A48" s="87"/>
       <c r="B48" s="71" t="s">
         <v>182</v>
       </c>
@@ -7596,8 +7589,8 @@
       <c r="U48" s="80"/>
       <c r="V48" s="71"/>
     </row>
-    <row r="49" spans="1:22" ht="13.8" hidden="1">
-      <c r="A49" s="84"/>
+    <row r="49" spans="1:22" ht="13.9" hidden="1">
+      <c r="A49" s="87"/>
       <c r="B49" s="71" t="s">
         <v>182</v>
       </c>
@@ -7636,8 +7629,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="13.8" hidden="1">
-      <c r="A50" s="84"/>
+    <row r="50" spans="1:22" ht="13.9" hidden="1">
+      <c r="A50" s="87"/>
       <c r="B50" s="71" t="s">
         <v>182</v>
       </c>
@@ -7691,8 +7684,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="55.2" hidden="1">
-      <c r="A51" s="84"/>
+    <row r="51" spans="1:22" ht="55.15" hidden="1">
+      <c r="A51" s="87"/>
       <c r="B51" s="71" t="s">
         <v>182</v>
       </c>
@@ -7746,8 +7739,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="41.4" hidden="1">
-      <c r="A52" s="84"/>
+    <row r="52" spans="1:22" ht="41.45" hidden="1">
+      <c r="A52" s="87"/>
       <c r="B52" s="71" t="s">
         <v>182</v>
       </c>
@@ -7802,7 +7795,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="84"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="71" t="s">
         <v>182</v>
       </c>
@@ -7856,8 +7849,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="84"/>
+    <row r="54" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A54" s="87"/>
       <c r="B54" s="71" t="s">
         <v>197</v>
       </c>
@@ -7910,8 +7903,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="84"/>
+    <row r="55" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A55" s="87"/>
       <c r="B55" s="71" t="s">
         <v>197</v>
       </c>
@@ -7965,8 +7958,8 @@
       </c>
       <c r="V55" s="66"/>
     </row>
-    <row r="56" spans="1:22" ht="41.4" hidden="1">
-      <c r="A56" s="84"/>
+    <row r="56" spans="1:22" ht="41.45" hidden="1">
+      <c r="A56" s="87"/>
       <c r="B56" s="71" t="s">
         <v>197</v>
       </c>
@@ -8024,8 +8017,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="84"/>
+    <row r="57" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A57" s="87"/>
       <c r="B57" s="71" t="s">
         <v>197</v>
       </c>
@@ -8081,8 +8074,8 @@
       </c>
       <c r="V57" s="71"/>
     </row>
-    <row r="58" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="84"/>
+    <row r="58" spans="1:22" ht="34.15" hidden="1" customHeight="1">
+      <c r="A58" s="87"/>
       <c r="B58" s="71" t="s">
         <v>197</v>
       </c>
@@ -8141,8 +8134,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A59" s="86"/>
+    <row r="59" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>209</v>
       </c>
@@ -8198,8 +8191,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A60" s="86"/>
+    <row r="60" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>209</v>
       </c>
@@ -8254,8 +8247,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="41.4" hidden="1">
-      <c r="A61" s="84"/>
+    <row r="61" spans="1:22" ht="41.45" hidden="1">
+      <c r="A61" s="87"/>
       <c r="B61" s="61" t="s">
         <v>209</v>
       </c>
@@ -8309,7 +8302,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="90">
+      <c r="A62" s="93">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8367,7 +8360,7 @@
       </c>
     </row>
     <row r="63" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="85"/>
+      <c r="A63" s="98"/>
       <c r="B63" s="71" t="s">
         <v>215</v>
       </c>
@@ -8424,7 +8417,7 @@
       </c>
     </row>
     <row r="64" spans="1:22" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="86"/>
+      <c r="A64" s="94"/>
       <c r="B64" s="71" t="s">
         <v>215</v>
       </c>
@@ -8589,7 +8582,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="90">
+      <c r="A67" s="93">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8644,8 +8637,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="68" spans="1:22" ht="13.8" hidden="1">
-      <c r="A68" s="86"/>
+    <row r="68" spans="1:22" ht="13.9" hidden="1">
+      <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>230</v>
       </c>
@@ -8698,7 +8691,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="90">
+      <c r="A69" s="93">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8753,8 +8746,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="41.4" hidden="1">
-      <c r="A70" s="85"/>
+    <row r="70" spans="1:22" ht="41.45" hidden="1">
+      <c r="A70" s="98"/>
       <c r="B70" s="71" t="s">
         <v>236</v>
       </c>
@@ -8808,8 +8801,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="67.95" hidden="1" customHeight="1">
-      <c r="A71" s="85"/>
+    <row r="71" spans="1:22" ht="67.900000000000006" hidden="1" customHeight="1">
+      <c r="A71" s="98"/>
       <c r="B71" s="71" t="s">
         <v>242</v>
       </c>
@@ -8864,7 +8857,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="85"/>
+      <c r="A72" s="98"/>
       <c r="B72" s="71" t="s">
         <v>245</v>
       </c>
@@ -8919,8 +8912,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="85"/>
+    <row r="73" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A73" s="98"/>
       <c r="B73" s="71" t="s">
         <v>245</v>
       </c>
@@ -8972,8 +8965,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="85"/>
+    <row r="74" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A74" s="98"/>
       <c r="B74" s="71" t="s">
         <v>245</v>
       </c>
@@ -9027,8 +9020,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="85"/>
+    <row r="75" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A75" s="98"/>
       <c r="B75" s="71" t="s">
         <v>245</v>
       </c>
@@ -9088,8 +9081,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A76" s="85"/>
+    <row r="76" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A76" s="98"/>
       <c r="B76" s="71" t="s">
         <v>245</v>
       </c>
@@ -9141,8 +9134,8 @@
       <c r="U76" s="70"/>
       <c r="V76" s="71"/>
     </row>
-    <row r="77" spans="1:22" ht="13.8" hidden="1">
-      <c r="A77" s="86"/>
+    <row r="77" spans="1:22" ht="13.9" hidden="1">
+      <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>245</v>
       </c>
@@ -9198,8 +9191,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="85"/>
+    <row r="78" spans="1:22" ht="20.45" hidden="1" customHeight="1">
+      <c r="A78" s="98"/>
       <c r="B78" s="71" t="s">
         <v>256</v>
       </c>
@@ -9259,8 +9252,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="13.8" hidden="1">
-      <c r="A79" s="85"/>
+    <row r="79" spans="1:22" ht="13.9" hidden="1">
+      <c r="A79" s="98"/>
       <c r="B79" s="71" t="s">
         <v>256</v>
       </c>
@@ -9314,8 +9307,8 @@
       </c>
       <c r="V79" s="66"/>
     </row>
-    <row r="80" spans="1:22" ht="13.8" hidden="1">
-      <c r="A80" s="85"/>
+    <row r="80" spans="1:22" ht="13.9" hidden="1">
+      <c r="A80" s="98"/>
       <c r="B80" s="71" t="s">
         <v>256</v>
       </c>
@@ -9370,7 +9363,7 @@
       <c r="V80" s="66"/>
     </row>
     <row r="81" spans="1:23" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="85"/>
+      <c r="A81" s="98"/>
       <c r="B81" s="71" t="s">
         <v>256</v>
       </c>
@@ -9425,8 +9418,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="85"/>
+    <row r="82" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A82" s="98"/>
       <c r="B82" s="71" t="s">
         <v>265</v>
       </c>
@@ -9483,8 +9476,8 @@
       </c>
       <c r="W82" s="33"/>
     </row>
-    <row r="83" spans="1:23" ht="38.4" hidden="1" customHeight="1">
-      <c r="A83" s="85"/>
+    <row r="83" spans="1:23" ht="38.450000000000003" hidden="1" customHeight="1">
+      <c r="A83" s="98"/>
       <c r="B83" s="71" t="s">
         <v>265</v>
       </c>
@@ -9539,7 +9532,7 @@
       <c r="W83" s="33"/>
     </row>
     <row r="84" spans="1:23" ht="27.6" hidden="1">
-      <c r="A84" s="85"/>
+      <c r="A84" s="98"/>
       <c r="B84" s="71" t="s">
         <v>265</v>
       </c>
@@ -9593,8 +9586,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="55.2" hidden="1">
-      <c r="A85" s="85"/>
+    <row r="85" spans="1:23" ht="55.15" hidden="1">
+      <c r="A85" s="98"/>
       <c r="B85" s="71" t="s">
         <v>265</v>
       </c>
@@ -9647,8 +9640,8 @@
       </c>
       <c r="W85" s="33"/>
     </row>
-    <row r="86" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="85"/>
+    <row r="86" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A86" s="98"/>
       <c r="B86" s="71" t="s">
         <v>265</v>
       </c>
@@ -9705,8 +9698,8 @@
       </c>
       <c r="W86" s="33"/>
     </row>
-    <row r="87" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="85"/>
+    <row r="87" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A87" s="98"/>
       <c r="B87" s="71" t="s">
         <v>265</v>
       </c>
@@ -9763,8 +9756,8 @@
       </c>
       <c r="W87" s="33"/>
     </row>
-    <row r="88" spans="1:23" ht="13.8" hidden="1">
-      <c r="A88" s="85"/>
+    <row r="88" spans="1:23" ht="13.9" hidden="1">
+      <c r="A88" s="98"/>
       <c r="B88" s="71" t="s">
         <v>265</v>
       </c>
@@ -9821,8 +9814,8 @@
       </c>
       <c r="W88" s="33"/>
     </row>
-    <row r="89" spans="1:23" ht="13.8" hidden="1">
-      <c r="A89" s="85"/>
+    <row r="89" spans="1:23" ht="13.9" hidden="1">
+      <c r="A89" s="98"/>
       <c r="B89" s="71" t="s">
         <v>265</v>
       </c>
@@ -9878,7 +9871,7 @@
       <c r="W89" s="33"/>
     </row>
     <row r="90" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="85"/>
+      <c r="A90" s="98"/>
       <c r="B90" s="66" t="s">
         <v>265</v>
       </c>
@@ -9927,8 +9920,8 @@
       </c>
       <c r="W90" s="33"/>
     </row>
-    <row r="91" spans="1:23" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="85"/>
+    <row r="91" spans="1:23" ht="43.9" hidden="1" customHeight="1">
+      <c r="A91" s="98"/>
       <c r="B91" s="71" t="s">
         <v>285</v>
       </c>
@@ -9952,36 +9945,36 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="100"/>
-      <c r="L91" s="100">
+      <c r="K91" s="84"/>
+      <c r="L91" s="84">
         <v>0</v>
       </c>
-      <c r="M91" s="100"/>
-      <c r="N91" s="84" t="s">
+      <c r="M91" s="84"/>
+      <c r="N91" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="O91" s="84" t="s">
+      <c r="O91" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="P91" s="84">
+      <c r="P91" s="87">
         <v>2026</v>
       </c>
-      <c r="Q91" s="89" t="s">
+      <c r="Q91" s="88" t="s">
         <v>131</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
       <c r="T91" s="71"/>
-      <c r="U91" s="103">
+      <c r="U91" s="89">
         <v>0</v>
       </c>
-      <c r="V91" s="89" t="s">
+      <c r="V91" s="88" t="s">
         <v>288</v>
       </c>
       <c r="W91" s="33"/>
     </row>
-    <row r="92" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A92" s="85"/>
+    <row r="92" spans="1:23" ht="40.9" hidden="1" customHeight="1">
+      <c r="A92" s="98"/>
       <c r="B92" s="71" t="s">
         <v>285</v>
       </c>
@@ -10005,21 +9998,21 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="101"/>
-      <c r="L92" s="101"/>
-      <c r="M92" s="101"/>
-      <c r="N92" s="84"/>
-      <c r="O92" s="84"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="89"/>
+      <c r="K92" s="85"/>
+      <c r="L92" s="85"/>
+      <c r="M92" s="85"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="88"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
       <c r="T92" s="71"/>
-      <c r="U92" s="103"/>
-      <c r="V92" s="89"/>
+      <c r="U92" s="89"/>
+      <c r="V92" s="88"/>
     </row>
     <row r="93" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="85"/>
+      <c r="A93" s="98"/>
       <c r="B93" s="71" t="s">
         <v>285</v>
       </c>
@@ -10043,9 +10036,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="101"/>
-      <c r="L93" s="101"/>
-      <c r="M93" s="101"/>
+      <c r="K93" s="85"/>
+      <c r="L93" s="85"/>
+      <c r="M93" s="85"/>
       <c r="N93" s="66" t="s">
         <v>29</v>
       </c>
@@ -10069,7 +10062,7 @@
       </c>
     </row>
     <row r="94" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="85"/>
+      <c r="A94" s="98"/>
       <c r="B94" s="71" t="s">
         <v>285</v>
       </c>
@@ -10091,9 +10084,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="101"/>
-      <c r="L94" s="101"/>
-      <c r="M94" s="101"/>
+      <c r="K94" s="85"/>
+      <c r="L94" s="85"/>
+      <c r="M94" s="85"/>
       <c r="N94" s="66" t="s">
         <v>29</v>
       </c>
@@ -10116,8 +10109,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A95" s="85"/>
+    <row r="95" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A95" s="98"/>
       <c r="B95" s="71" t="s">
         <v>285</v>
       </c>
@@ -10141,9 +10134,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="101"/>
-      <c r="L95" s="101"/>
-      <c r="M95" s="101"/>
+      <c r="K95" s="85"/>
+      <c r="L95" s="85"/>
+      <c r="M95" s="85"/>
       <c r="N95" s="66" t="s">
         <v>149</v>
       </c>
@@ -10166,8 +10159,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A96" s="85"/>
+    <row r="96" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A96" s="98"/>
       <c r="B96" s="71" t="s">
         <v>293</v>
       </c>
@@ -10187,9 +10180,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="101"/>
-      <c r="L96" s="101"/>
-      <c r="M96" s="101"/>
+      <c r="K96" s="85"/>
+      <c r="L96" s="85"/>
+      <c r="M96" s="85"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10200,8 +10193,8 @@
       <c r="U96" s="70"/>
       <c r="V96" s="66"/>
     </row>
-    <row r="97" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A97" s="85"/>
+    <row r="97" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A97" s="98"/>
       <c r="B97" s="71" t="s">
         <v>293</v>
       </c>
@@ -10229,9 +10222,9 @@
       <c r="J97" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="K97" s="101"/>
-      <c r="L97" s="101"/>
-      <c r="M97" s="101"/>
+      <c r="K97" s="85"/>
+      <c r="L97" s="85"/>
+      <c r="M97" s="85"/>
       <c r="N97" s="66" t="s">
         <v>29</v>
       </c>
@@ -10253,7 +10246,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="85"/>
+      <c r="A98" s="98"/>
       <c r="B98" s="71" t="s">
         <v>293</v>
       </c>
@@ -10281,9 +10274,9 @@
       <c r="J98" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="K98" s="101"/>
-      <c r="L98" s="101"/>
-      <c r="M98" s="101"/>
+      <c r="K98" s="85"/>
+      <c r="L98" s="85"/>
+      <c r="M98" s="85"/>
       <c r="N98" s="66" t="s">
         <v>101</v>
       </c>
@@ -10306,8 +10299,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="99" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="85"/>
+    <row r="99" spans="1:22" ht="17.45" hidden="1" customHeight="1">
+      <c r="A99" s="98"/>
       <c r="B99" s="71" t="s">
         <v>302</v>
       </c>
@@ -10331,9 +10324,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="101"/>
-      <c r="L99" s="101"/>
-      <c r="M99" s="101"/>
+      <c r="K99" s="85"/>
+      <c r="L99" s="85"/>
+      <c r="M99" s="85"/>
       <c r="N99" s="66" t="s">
         <v>149</v>
       </c>
@@ -10356,8 +10349,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:22" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A100" s="85"/>
+    <row r="100" spans="1:22" ht="17.45" hidden="1" customHeight="1">
+      <c r="A100" s="98"/>
       <c r="B100" s="71" t="s">
         <v>302</v>
       </c>
@@ -10381,9 +10374,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="101"/>
-      <c r="L100" s="101"/>
-      <c r="M100" s="101"/>
+      <c r="K100" s="85"/>
+      <c r="L100" s="85"/>
+      <c r="M100" s="85"/>
       <c r="N100" s="66" t="s">
         <v>75</v>
       </c>
@@ -10406,8 +10399,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="85"/>
+    <row r="101" spans="1:22" ht="53.45" hidden="1" customHeight="1">
+      <c r="A101" s="98"/>
       <c r="B101" s="71" t="s">
         <v>302</v>
       </c>
@@ -10431,9 +10424,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="102"/>
-      <c r="L101" s="102"/>
-      <c r="M101" s="102"/>
+      <c r="K101" s="86"/>
+      <c r="L101" s="86"/>
+      <c r="M101" s="86"/>
       <c r="N101" s="66" t="s">
         <v>38</v>
       </c>
@@ -10456,8 +10449,8 @@
         <v>306</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="85"/>
+    <row r="102" spans="1:22" ht="53.45" hidden="1" customHeight="1">
+      <c r="A102" s="98"/>
       <c r="B102" s="71" t="s">
         <v>302</v>
       </c>
@@ -10513,8 +10506,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="85"/>
+    <row r="103" spans="1:22" ht="53.45" hidden="1" customHeight="1">
+      <c r="A103" s="98"/>
       <c r="B103" s="71" t="s">
         <v>302</v>
       </c>
@@ -10565,8 +10558,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A104" s="85"/>
+    <row r="104" spans="1:22" ht="53.45" hidden="1" customHeight="1">
+      <c r="A104" s="98"/>
       <c r="B104" s="71" t="s">
         <v>302</v>
       </c>
@@ -10618,8 +10611,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="105" spans="1:22" ht="53.4" hidden="1" customHeight="1">
-      <c r="A105" s="85"/>
+    <row r="105" spans="1:22" ht="53.45" hidden="1" customHeight="1">
+      <c r="A105" s="98"/>
       <c r="B105" s="71" t="s">
         <v>302</v>
       </c>
@@ -10674,7 +10667,7 @@
       <c r="V105" s="66"/>
     </row>
     <row r="106" spans="1:22" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="85"/>
+      <c r="A106" s="98"/>
       <c r="B106" s="71" t="s">
         <v>302</v>
       </c>
@@ -10729,7 +10722,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" ht="96.6" hidden="1">
-      <c r="A107" s="85"/>
+      <c r="A107" s="98"/>
       <c r="B107" s="71" t="s">
         <v>314</v>
       </c>
@@ -10780,8 +10773,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A108" s="85"/>
+    <row r="108" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A108" s="98"/>
       <c r="B108" s="71" t="s">
         <v>320</v>
       </c>
@@ -10826,8 +10819,8 @@
         <v>322</v>
       </c>
     </row>
-    <row r="109" spans="1:22" ht="13.8" hidden="1">
-      <c r="A109" s="85"/>
+    <row r="109" spans="1:22" ht="13.9" hidden="1">
+      <c r="A109" s="98"/>
       <c r="B109" s="71" t="s">
         <v>320</v>
       </c>
@@ -10879,8 +10872,8 @@
       <c r="U109" s="66"/>
       <c r="V109" s="66"/>
     </row>
-    <row r="110" spans="1:22" ht="13.8" hidden="1">
-      <c r="A110" s="85"/>
+    <row r="110" spans="1:22" ht="13.9" hidden="1">
+      <c r="A110" s="98"/>
       <c r="B110" s="71" t="s">
         <v>320</v>
       </c>
@@ -10935,7 +10928,7 @@
       <c r="V110" s="71"/>
     </row>
     <row r="111" spans="1:22" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="85"/>
+      <c r="A111" s="98"/>
       <c r="B111" s="71" t="s">
         <v>325</v>
       </c>
@@ -10993,8 +10986,8 @@
       </c>
       <c r="V111" s="71"/>
     </row>
-    <row r="112" spans="1:22" ht="13.8" hidden="1">
-      <c r="A112" s="85"/>
+    <row r="112" spans="1:22" ht="13.9" hidden="1">
+      <c r="A112" s="98"/>
       <c r="B112" s="71" t="s">
         <v>327</v>
       </c>
@@ -11046,8 +11039,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:22" ht="13.8" hidden="1">
-      <c r="A113" s="85"/>
+    <row r="113" spans="1:22" ht="13.9" hidden="1">
+      <c r="A113" s="98"/>
       <c r="B113" s="71" t="s">
         <v>327</v>
       </c>
@@ -11099,8 +11092,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="114" spans="1:22" ht="41.4" hidden="1">
-      <c r="A114" s="85"/>
+    <row r="114" spans="1:22" ht="41.45" hidden="1">
+      <c r="A114" s="98"/>
       <c r="B114" s="71" t="s">
         <v>327</v>
       </c>
@@ -11141,8 +11134,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:22" ht="22.95" hidden="1" customHeight="1">
-      <c r="A115" s="85"/>
+    <row r="115" spans="1:22" ht="22.9" hidden="1" customHeight="1">
+      <c r="A115" s="98"/>
       <c r="B115" s="71" t="s">
         <v>327</v>
       </c>
@@ -11198,8 +11191,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A116" s="85"/>
+    <row r="116" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A116" s="98"/>
       <c r="B116" s="71" t="s">
         <v>337</v>
       </c>
@@ -11259,8 +11252,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="55.2" hidden="1">
-      <c r="A117" s="86"/>
+    <row r="117" spans="1:22" ht="55.15" hidden="1">
+      <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>342</v>
       </c>
@@ -11316,7 +11309,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="13.8" hidden="1">
+    <row r="118" spans="1:22" ht="13.9" hidden="1">
       <c r="A118" s="72">
         <v>29</v>
       </c>
@@ -11374,7 +11367,7 @@
       <c r="V118" s="71"/>
     </row>
     <row r="119" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="84">
+      <c r="A119" s="87">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11428,8 +11421,8 @@
       </c>
       <c r="V119" s="71"/>
     </row>
-    <row r="120" spans="1:22" ht="13.8" hidden="1">
-      <c r="A120" s="84"/>
+    <row r="120" spans="1:22" ht="13.9" hidden="1">
+      <c r="A120" s="87"/>
       <c r="B120" s="71" t="s">
         <v>347</v>
       </c>
@@ -11483,8 +11476,8 @@
       </c>
       <c r="V120" s="66"/>
     </row>
-    <row r="121" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="98">
+    <row r="121" spans="1:22" ht="37.15" hidden="1" customHeight="1">
+      <c r="A121" s="103">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11539,8 +11532,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="122" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A122" s="89"/>
+    <row r="122" spans="1:22" ht="37.15" hidden="1" customHeight="1">
+      <c r="A122" s="88"/>
       <c r="B122" s="71" t="s">
         <v>350</v>
       </c>
@@ -11593,8 +11586,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A123" s="89"/>
+    <row r="123" spans="1:22" ht="142.9" hidden="1" customHeight="1">
+      <c r="A123" s="88"/>
       <c r="B123" s="71" t="s">
         <v>350</v>
       </c>
@@ -11648,8 +11641,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="13.8" hidden="1">
-      <c r="A124" s="89"/>
+    <row r="124" spans="1:22" ht="13.9" hidden="1">
+      <c r="A124" s="88"/>
       <c r="B124" s="71" t="s">
         <v>350</v>
       </c>
@@ -11865,7 +11858,7 @@
       <c r="U127" s="80"/>
       <c r="V127" s="71"/>
     </row>
-    <row r="128" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="128" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A128" s="66">
         <v>33</v>
       </c>
@@ -11922,7 +11915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="129" spans="1:22" ht="37.9" hidden="1" customHeight="1">
       <c r="A129" s="68"/>
       <c r="B129" s="71" t="s">
         <v>369</v>
@@ -11977,7 +11970,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="13.8" hidden="1">
+    <row r="130" spans="1:22" ht="13.9" hidden="1">
       <c r="A130" s="68">
         <v>34</v>
       </c>
@@ -12034,7 +12027,7 @@
       </c>
       <c r="V130" s="66"/>
     </row>
-    <row r="131" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="131" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A131" s="68"/>
       <c r="B131" s="71" t="s">
         <v>374</v>
@@ -12089,7 +12082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="132" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A132" s="68"/>
       <c r="B132" s="71" t="s">
         <v>374</v>
@@ -12144,8 +12137,8 @@
       </c>
       <c r="V132" s="66"/>
     </row>
-    <row r="133" spans="1:22" ht="13.8" hidden="1">
-      <c r="A133" s="84">
+    <row r="133" spans="1:22" ht="13.9" hidden="1">
+      <c r="A133" s="87">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12203,8 +12196,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:22" ht="13.8" hidden="1">
-      <c r="A134" s="84"/>
+    <row r="134" spans="1:22" ht="13.9" hidden="1">
+      <c r="A134" s="87"/>
       <c r="B134" s="71" t="s">
         <v>374</v>
       </c>
@@ -12258,8 +12251,8 @@
       </c>
       <c r="V134" s="66"/>
     </row>
-    <row r="135" spans="1:22" ht="41.4" hidden="1">
-      <c r="A135" s="84"/>
+    <row r="135" spans="1:22" ht="41.45" hidden="1">
+      <c r="A135" s="87"/>
       <c r="B135" s="71" t="s">
         <v>374</v>
       </c>
@@ -12319,8 +12312,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="13.8" hidden="1">
-      <c r="A136" s="84"/>
+    <row r="136" spans="1:22" ht="13.9" hidden="1">
+      <c r="A136" s="87"/>
       <c r="B136" s="71" t="s">
         <v>374</v>
       </c>
@@ -12376,7 +12369,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="125.4" hidden="1" customHeight="1">
+    <row r="137" spans="1:22" ht="125.45" hidden="1" customHeight="1">
       <c r="A137" s="66"/>
       <c r="B137" s="71" t="s">
         <v>383</v>
@@ -12434,8 +12427,8 @@
       </c>
       <c r="V137" s="71"/>
     </row>
-    <row r="138" spans="1:22" ht="13.8" hidden="1">
-      <c r="A138" s="84">
+    <row r="138" spans="1:22" ht="13.9" hidden="1">
+      <c r="A138" s="87">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12491,8 +12484,8 @@
       </c>
       <c r="V138" s="71"/>
     </row>
-    <row r="139" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A139" s="84"/>
+    <row r="139" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A139" s="87"/>
       <c r="B139" s="71" t="s">
         <v>383</v>
       </c>
@@ -12546,8 +12539,8 @@
       </c>
       <c r="V139" s="71"/>
     </row>
-    <row r="140" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A140" s="84"/>
+    <row r="140" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A140" s="87"/>
       <c r="B140" s="71" t="s">
         <v>383</v>
       </c>
@@ -12602,7 +12595,7 @@
       <c r="V140" s="71"/>
     </row>
     <row r="141" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="84"/>
+      <c r="A141" s="87"/>
       <c r="B141" s="71" t="s">
         <v>383</v>
       </c>
@@ -12655,8 +12648,8 @@
       </c>
       <c r="V141" s="71"/>
     </row>
-    <row r="142" spans="1:22" ht="13.8" hidden="1">
-      <c r="A142" s="84"/>
+    <row r="142" spans="1:22" ht="13.9" hidden="1">
+      <c r="A142" s="87"/>
       <c r="B142" s="71" t="s">
         <v>383</v>
       </c>
@@ -12710,8 +12703,8 @@
       </c>
       <c r="V142" s="71"/>
     </row>
-    <row r="143" spans="1:22" ht="13.8" hidden="1">
-      <c r="A143" s="84"/>
+    <row r="143" spans="1:22" ht="13.9" hidden="1">
+      <c r="A143" s="87"/>
       <c r="B143" s="71" t="s">
         <v>383</v>
       </c>
@@ -12765,8 +12758,8 @@
       </c>
       <c r="V143" s="66"/>
     </row>
-    <row r="144" spans="1:22" ht="13.8" hidden="1">
-      <c r="A144" s="84"/>
+    <row r="144" spans="1:22" ht="13.9" hidden="1">
+      <c r="A144" s="87"/>
       <c r="B144" s="71" t="s">
         <v>383</v>
       </c>
@@ -12820,8 +12813,8 @@
       </c>
       <c r="V144" s="71"/>
     </row>
-    <row r="145" spans="1:22" ht="13.8" hidden="1">
-      <c r="A145" s="84">
+    <row r="145" spans="1:22" ht="13.9" hidden="1">
+      <c r="A145" s="87">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12880,7 +12873,7 @@
       </c>
     </row>
     <row r="146" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="84"/>
+      <c r="A146" s="87"/>
       <c r="B146" s="71" t="s">
         <v>399</v>
       </c>
@@ -12933,7 +12926,7 @@
       </c>
     </row>
     <row r="147" spans="1:22" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="84"/>
+      <c r="A147" s="87"/>
       <c r="B147" s="71" t="s">
         <v>399</v>
       </c>
@@ -13042,8 +13035,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="35.4" hidden="1" customHeight="1">
-      <c r="A149" s="85"/>
+    <row r="149" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
+      <c r="A149" s="98"/>
       <c r="B149" s="71" t="s">
         <v>404</v>
       </c>
@@ -13096,8 +13089,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A150" s="86"/>
+    <row r="150" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>404</v>
       </c>
@@ -13152,7 +13145,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="151" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A151" s="68"/>
       <c r="B151" s="71" t="s">
         <v>409</v>
@@ -13207,7 +13200,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="13.8" hidden="1">
+    <row r="152" spans="1:22" ht="13.9" hidden="1">
       <c r="A152" s="66">
         <v>39</v>
       </c>
@@ -13266,8 +13259,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A153" s="90">
+    <row r="153" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A153" s="93">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13325,8 +13318,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A154" s="85"/>
+    <row r="154" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A154" s="98"/>
       <c r="B154" s="71" t="s">
         <v>415</v>
       </c>
@@ -13378,7 +13371,7 @@
       </c>
     </row>
     <row r="155" spans="1:22" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="85"/>
+      <c r="A155" s="98"/>
       <c r="B155" s="71" t="s">
         <v>415</v>
       </c>
@@ -13427,8 +13420,8 @@
         <v>424</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="85"/>
+    <row r="156" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A156" s="98"/>
       <c r="B156" s="71" t="s">
         <v>415</v>
       </c>
@@ -13479,8 +13472,8 @@
         <v>426</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A157" s="85"/>
+    <row r="157" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A157" s="98"/>
       <c r="B157" s="71" t="s">
         <v>415</v>
       </c>
@@ -13536,8 +13529,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="13.8" hidden="1">
-      <c r="A158" s="85"/>
+    <row r="158" spans="1:22" ht="13.9" hidden="1">
+      <c r="A158" s="98"/>
       <c r="B158" s="71" t="s">
         <v>415</v>
       </c>
@@ -13593,8 +13586,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="13.8" hidden="1">
-      <c r="A159" s="85"/>
+    <row r="159" spans="1:22" ht="13.9" hidden="1">
+      <c r="A159" s="98"/>
       <c r="B159" s="71" t="s">
         <v>415</v>
       </c>
@@ -13650,8 +13643,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="55.2" hidden="1">
-      <c r="A160" s="85"/>
+    <row r="160" spans="1:22" ht="55.15">
+      <c r="A160" s="98"/>
       <c r="B160" s="71" t="s">
         <v>429</v>
       </c>
@@ -13703,8 +13696,8 @@
       </c>
       <c r="V160" s="71"/>
     </row>
-    <row r="161" spans="1:22" ht="27.6" hidden="1">
-      <c r="A161" s="85"/>
+    <row r="161" spans="1:22" ht="37.5">
+      <c r="A161" s="98"/>
       <c r="B161" s="71" t="s">
         <v>429</v>
       </c>
@@ -13759,8 +13752,8 @@
       </c>
       <c r="V161" s="71"/>
     </row>
-    <row r="162" spans="1:22" ht="13.8" hidden="1">
-      <c r="A162" s="85"/>
+    <row r="162" spans="1:22" ht="13.9">
+      <c r="A162" s="98"/>
       <c r="B162" s="71" t="s">
         <v>429</v>
       </c>
@@ -13812,8 +13805,8 @@
       </c>
       <c r="V162" s="71"/>
     </row>
-    <row r="163" spans="1:22" ht="13.8" hidden="1">
-      <c r="A163" s="85"/>
+    <row r="163" spans="1:22" ht="13.9">
+      <c r="A163" s="98"/>
       <c r="B163" s="71" t="s">
         <v>429</v>
       </c>
@@ -13870,7 +13863,7 @@
       </c>
     </row>
     <row r="164" spans="1:22" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="86"/>
+      <c r="A164" s="94"/>
       <c r="B164" s="71" t="s">
         <v>437</v>
       </c>
@@ -13923,8 +13916,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A165" s="85"/>
+    <row r="165" spans="1:22" ht="37.9" hidden="1" customHeight="1">
+      <c r="A165" s="98"/>
       <c r="B165" s="71" t="s">
         <v>437</v>
       </c>
@@ -13977,8 +13970,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="166" spans="1:22" ht="13.8" hidden="1">
-      <c r="A166" s="86"/>
+    <row r="166" spans="1:22" ht="13.9" hidden="1">
+      <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>437</v>
       </c>
@@ -14033,7 +14026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="167" spans="1:22" ht="13.8" hidden="1">
+    <row r="167" spans="1:22" ht="13.9" hidden="1">
       <c r="A167" s="68"/>
       <c r="B167" s="71" t="s">
         <v>444</v>
@@ -14155,8 +14148,8 @@
         <v>450</v>
       </c>
     </row>
-    <row r="169" spans="1:22" ht="41.4" hidden="1">
-      <c r="A169" s="91">
+    <row r="169" spans="1:22" ht="41.45" hidden="1">
+      <c r="A169" s="99">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14217,7 +14210,7 @@
       </c>
     </row>
     <row r="170" spans="1:22" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="92"/>
+      <c r="A170" s="100"/>
       <c r="B170" s="71" t="s">
         <v>451</v>
       </c>
@@ -14268,8 +14261,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="171" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A171" s="92"/>
+    <row r="171" spans="1:22" ht="37.15" hidden="1" customHeight="1">
+      <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>451</v>
       </c>
@@ -14327,8 +14320,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="172" spans="1:22" ht="13.8" hidden="1">
-      <c r="A172" s="92"/>
+    <row r="172" spans="1:22" ht="13.9" hidden="1">
+      <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>451</v>
       </c>
@@ -14384,8 +14377,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="173" spans="1:22" ht="13.8" hidden="1">
-      <c r="A173" s="93"/>
+    <row r="173" spans="1:22" ht="13.9" hidden="1">
+      <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>458</v>
       </c>
@@ -14441,8 +14434,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="174" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A174" s="84">
+    <row r="174" spans="1:22" ht="40.15" hidden="1" customHeight="1">
+      <c r="A174" s="87">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14499,8 +14492,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="175" spans="1:22" ht="13.8" hidden="1">
-      <c r="A175" s="84"/>
+    <row r="175" spans="1:22" ht="13.9" hidden="1">
+      <c r="A175" s="87"/>
       <c r="B175" s="71" t="s">
         <v>460</v>
       </c>
@@ -14556,8 +14549,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:22" ht="13.8" hidden="1">
-      <c r="A176" s="84"/>
+    <row r="176" spans="1:22" ht="13.9" hidden="1">
+      <c r="A176" s="87"/>
       <c r="B176" s="71" t="s">
         <v>460</v>
       </c>
@@ -14611,8 +14604,8 @@
       </c>
       <c r="V176" s="71"/>
     </row>
-    <row r="177" spans="1:22" ht="13.8" hidden="1">
-      <c r="A177" s="84"/>
+    <row r="177" spans="1:22" ht="13.9" hidden="1">
+      <c r="A177" s="87"/>
       <c r="B177" s="71" t="s">
         <v>460</v>
       </c>
@@ -14669,7 +14662,7 @@
       </c>
     </row>
     <row r="178" spans="1:22" ht="27.6" hidden="1">
-      <c r="A178" s="84"/>
+      <c r="A178" s="87"/>
       <c r="B178" s="71" t="s">
         <v>460</v>
       </c>
@@ -14723,8 +14716,8 @@
       </c>
       <c r="V178" s="71"/>
     </row>
-    <row r="179" spans="1:22" ht="13.8" hidden="1">
-      <c r="A179" s="84"/>
+    <row r="179" spans="1:22" ht="13.9" hidden="1">
+      <c r="A179" s="87"/>
       <c r="B179" s="71" t="s">
         <v>468</v>
       </c>
@@ -14780,8 +14773,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="13.8" hidden="1">
-      <c r="A180" s="84"/>
+    <row r="180" spans="1:22" ht="13.9" hidden="1">
+      <c r="A180" s="87"/>
       <c r="B180" s="71" t="s">
         <v>470</v>
       </c>
@@ -14835,7 +14828,7 @@
       </c>
       <c r="V180" s="66"/>
     </row>
-    <row r="181" spans="1:22" ht="13.8" hidden="1">
+    <row r="181" spans="1:22" ht="13.9" hidden="1">
       <c r="A181" s="75"/>
       <c r="B181" s="71" t="s">
         <v>473</v>
@@ -14944,8 +14937,8 @@
       </c>
       <c r="V182" s="66"/>
     </row>
-    <row r="183" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A183" s="94">
+    <row r="183" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A183" s="102">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14999,8 +14992,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A184" s="94"/>
+    <row r="184" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>473</v>
       </c>
@@ -15054,8 +15047,8 @@
         <v>483</v>
       </c>
     </row>
-    <row r="185" spans="1:22" ht="13.8" hidden="1">
-      <c r="A185" s="94"/>
+    <row r="185" spans="1:22" ht="13.9" hidden="1">
+      <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>473</v>
       </c>
@@ -15111,7 +15104,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="13.8" hidden="1">
+    <row r="186" spans="1:22" ht="13.9" hidden="1">
       <c r="A186" s="72"/>
       <c r="B186" s="71" t="s">
         <v>485</v>
@@ -15170,8 +15163,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="13.8" hidden="1">
-      <c r="A187" s="92"/>
+    <row r="187" spans="1:22" ht="13.9" hidden="1">
+      <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>485</v>
       </c>
@@ -15221,8 +15214,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:22" ht="13.8" hidden="1">
-      <c r="A188" s="92"/>
+    <row r="188" spans="1:22" ht="13.9" hidden="1">
+      <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>485</v>
       </c>
@@ -15274,8 +15267,8 @@
       <c r="U188" s="80"/>
       <c r="V188" s="71"/>
     </row>
-    <row r="189" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A189" s="93"/>
+    <row r="189" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>485</v>
       </c>
@@ -15382,8 +15375,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:22" ht="64.95" hidden="1" customHeight="1">
-      <c r="A191" s="84">
+    <row r="191" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
+      <c r="A191" s="87">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15439,7 +15432,7 @@
       </c>
     </row>
     <row r="192" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="84"/>
+      <c r="A192" s="87"/>
       <c r="B192" s="71" t="s">
         <v>492</v>
       </c>
@@ -15492,8 +15485,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="193" spans="1:22" ht="13.8" hidden="1">
-      <c r="A193" s="84"/>
+    <row r="193" spans="1:22" ht="13.9" hidden="1">
+      <c r="A193" s="87"/>
       <c r="B193" s="71" t="s">
         <v>492</v>
       </c>
@@ -15549,7 +15542,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="194" spans="1:22" ht="13.8" hidden="1">
+    <row r="194" spans="1:22" ht="13.9" hidden="1">
       <c r="A194" s="66">
         <v>49</v>
       </c>
@@ -15579,8 +15572,8 @@
       <c r="U194" s="66"/>
       <c r="V194" s="66"/>
     </row>
-    <row r="195" spans="1:22" ht="13.8" hidden="1">
-      <c r="A195" s="85"/>
+    <row r="195" spans="1:22" ht="13.9">
+      <c r="A195" s="98"/>
       <c r="B195" s="71" t="s">
         <v>504</v>
       </c>
@@ -15634,8 +15627,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="196" spans="1:22" ht="24.6" hidden="1" customHeight="1">
-      <c r="A196" s="86"/>
+    <row r="196" spans="1:22" ht="24.6" customHeight="1">
+      <c r="A196" s="94"/>
       <c r="B196" s="71" t="s">
         <v>504</v>
       </c>
@@ -15689,8 +15682,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="197" spans="1:22" ht="13.8" hidden="1">
-      <c r="A197" s="84">
+    <row r="197" spans="1:22" ht="13.9" hidden="1">
+      <c r="A197" s="87">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15745,8 +15738,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="198" spans="1:22" ht="13.8" hidden="1">
-      <c r="A198" s="84"/>
+    <row r="198" spans="1:22" ht="13.9" hidden="1">
+      <c r="A198" s="87"/>
       <c r="B198" s="71" t="s">
         <v>508</v>
       </c>
@@ -15802,8 +15795,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="199" spans="1:22" ht="13.8" hidden="1">
-      <c r="A199" s="84"/>
+    <row r="199" spans="1:22" ht="13.9" hidden="1">
+      <c r="A199" s="87"/>
       <c r="B199" s="71" t="s">
         <v>508</v>
       </c>
@@ -15859,8 +15852,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="200" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A200" s="84"/>
+    <row r="200" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A200" s="87"/>
       <c r="B200" s="71" t="s">
         <v>508</v>
       </c>
@@ -15915,7 +15908,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="201" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="71" t="s">
         <v>515</v>
@@ -15970,7 +15963,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="202" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="71" t="s">
         <v>515</v>
@@ -16019,7 +16012,7 @@
       <c r="U202" s="70"/>
       <c r="V202" s="66"/>
     </row>
-    <row r="203" spans="1:22" ht="13.8" hidden="1">
+    <row r="203" spans="1:22" ht="13.9" hidden="1">
       <c r="A203" s="66">
         <v>52</v>
       </c>
@@ -16078,8 +16071,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="204" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A204" s="84">
+    <row r="204" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A204" s="87">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -16136,8 +16129,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="205" spans="1:22" ht="55.2" hidden="1">
-      <c r="A205" s="84"/>
+    <row r="205" spans="1:22" ht="55.15" hidden="1">
+      <c r="A205" s="87"/>
       <c r="B205" s="71" t="s">
         <v>520</v>
       </c>
@@ -16193,8 +16186,8 @@
         <v>523</v>
       </c>
     </row>
-    <row r="206" spans="1:22" ht="13.8" hidden="1">
-      <c r="A206" s="84"/>
+    <row r="206" spans="1:22" ht="13.9" hidden="1">
+      <c r="A206" s="87"/>
       <c r="B206" s="66" t="s">
         <v>524</v>
       </c>
@@ -16250,8 +16243,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="207" spans="1:22" ht="13.8" hidden="1">
-      <c r="A207" s="84">
+    <row r="207" spans="1:22" ht="13.9" hidden="1">
+      <c r="A207" s="87">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16307,8 +16300,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208" spans="1:22" ht="13.8" hidden="1">
-      <c r="A208" s="84"/>
+    <row r="208" spans="1:22" ht="13.9" hidden="1">
+      <c r="A208" s="87"/>
       <c r="B208" s="71" t="s">
         <v>527</v>
       </c>
@@ -16366,8 +16359,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="209" spans="1:22" ht="32.4" hidden="1" customHeight="1">
-      <c r="A209" s="84">
+    <row r="209" spans="1:22" ht="32.450000000000003" hidden="1" customHeight="1">
+      <c r="A209" s="87">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16424,8 +16417,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="210" spans="1:22" ht="13.8" hidden="1">
-      <c r="A210" s="84"/>
+    <row r="210" spans="1:22" ht="13.9" hidden="1">
+      <c r="A210" s="87"/>
       <c r="B210" s="71" t="s">
         <v>530</v>
       </c>
@@ -16479,8 +16472,8 @@
       </c>
       <c r="V210" s="71"/>
     </row>
-    <row r="211" spans="1:22" ht="16.2" hidden="1" customHeight="1">
-      <c r="A211" s="84"/>
+    <row r="211" spans="1:22" ht="16.149999999999999" hidden="1" customHeight="1">
+      <c r="A211" s="87"/>
       <c r="B211" s="71" t="s">
         <v>530</v>
       </c>
@@ -16534,8 +16527,8 @@
       </c>
       <c r="V211" s="66"/>
     </row>
-    <row r="212" spans="1:22" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A212" s="84">
+    <row r="212" spans="1:22" ht="80.45" hidden="1" customHeight="1">
+      <c r="A212" s="87">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16590,8 +16583,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="213" spans="1:22" ht="13.8" hidden="1">
-      <c r="A213" s="84"/>
+    <row r="213" spans="1:22" ht="13.9" hidden="1">
+      <c r="A213" s="87"/>
       <c r="B213" s="71" t="s">
         <v>539</v>
       </c>
@@ -16650,7 +16643,7 @@
       </c>
     </row>
     <row r="214" spans="1:22" ht="27.6" hidden="1">
-      <c r="A214" s="91">
+      <c r="A214" s="99">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16705,8 +16698,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="215" spans="1:22" ht="13.8" hidden="1">
-      <c r="A215" s="92"/>
+    <row r="215" spans="1:22" ht="13.9" hidden="1">
+      <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>541</v>
       </c>
@@ -16762,8 +16755,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216" spans="1:22" ht="13.8" hidden="1">
-      <c r="A216" s="92"/>
+    <row r="216" spans="1:22" ht="13.9" hidden="1">
+      <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>541</v>
       </c>
@@ -16820,7 +16813,7 @@
       </c>
     </row>
     <row r="217" spans="1:22" ht="27.6" hidden="1">
-      <c r="A217" s="85"/>
+      <c r="A217" s="98"/>
       <c r="B217" s="71" t="s">
         <v>541</v>
       </c>
@@ -16875,8 +16868,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="218" spans="1:22" ht="13.8" hidden="1">
-      <c r="A218" s="93"/>
+    <row r="218" spans="1:22" ht="13.9" hidden="1">
+      <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>541</v>
       </c>
@@ -16932,7 +16925,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:22" ht="13.8" hidden="1">
+    <row r="219" spans="1:22" ht="13.9" hidden="1">
       <c r="A219" s="74"/>
       <c r="B219" s="71" t="s">
         <v>552</v>
@@ -16989,7 +16982,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220" spans="1:22" ht="13.8" hidden="1">
+    <row r="220" spans="1:22" ht="13.9" hidden="1">
       <c r="A220" s="74"/>
       <c r="B220" s="71" t="s">
         <v>552</v>
@@ -17046,7 +17039,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221" spans="1:22" ht="13.8" hidden="1">
+    <row r="221" spans="1:22" ht="13.9" hidden="1">
       <c r="A221" s="74"/>
       <c r="B221" s="71" t="s">
         <v>552</v>
@@ -17100,7 +17093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="222" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A222" s="66">
         <v>58</v>
       </c>
@@ -17159,8 +17152,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="223" spans="1:22" ht="34.200000000000003" customHeight="1">
-      <c r="A223" s="84">
+    <row r="223" spans="1:22" ht="34.15" hidden="1" customHeight="1">
+      <c r="A223" s="87">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17215,8 +17208,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="224" spans="1:22" ht="34.200000000000003" customHeight="1">
-      <c r="A224" s="84"/>
+    <row r="224" spans="1:22" ht="34.15" hidden="1" customHeight="1">
+      <c r="A224" s="87"/>
       <c r="B224" s="71" t="s">
         <v>562</v>
       </c>
@@ -17272,8 +17265,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="225" spans="1:22" ht="81.599999999999994" customHeight="1">
-      <c r="A225" s="84"/>
+    <row r="225" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
+      <c r="A225" s="87"/>
       <c r="B225" s="71" t="s">
         <v>562</v>
       </c>
@@ -17324,8 +17317,8 @@
       </c>
       <c r="V225" s="71"/>
     </row>
-    <row r="226" spans="1:22" ht="13.8">
-      <c r="A226" s="84"/>
+    <row r="226" spans="1:22" ht="13.9" hidden="1">
+      <c r="A226" s="87"/>
       <c r="B226" s="71" t="s">
         <v>562</v>
       </c>
@@ -17381,8 +17374,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="227" spans="1:22" ht="27.6">
-      <c r="A227" s="84"/>
+    <row r="227" spans="1:22" ht="27.6" hidden="1">
+      <c r="A227" s="87"/>
       <c r="B227" s="71" t="s">
         <v>562</v>
       </c>
@@ -17434,8 +17427,8 @@
       <c r="U227" s="70"/>
       <c r="V227" s="66"/>
     </row>
-    <row r="228" spans="1:22" ht="13.8">
-      <c r="A228" s="84"/>
+    <row r="228" spans="1:22" ht="13.9" hidden="1">
+      <c r="A228" s="87"/>
       <c r="B228" s="71" t="s">
         <v>562</v>
       </c>
@@ -17491,7 +17484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="229" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="229" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A229" s="66"/>
       <c r="B229" s="71" t="s">
         <v>574</v>
@@ -17546,7 +17539,7 @@
       </c>
       <c r="V229" s="66"/>
     </row>
-    <row r="230" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="230" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A230" s="66"/>
       <c r="B230" s="71" t="s">
         <v>574</v>
@@ -17601,7 +17594,7 @@
       </c>
       <c r="V230" s="66"/>
     </row>
-    <row r="231" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="231" spans="1:22" ht="20.45" hidden="1" customHeight="1">
       <c r="A231" s="66"/>
       <c r="B231" s="71" t="s">
         <v>574</v>
@@ -17656,7 +17649,7 @@
       </c>
       <c r="V231" s="66"/>
     </row>
-    <row r="232" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="232" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A232" s="66">
         <v>60</v>
       </c>
@@ -17712,7 +17705,7 @@
       </c>
       <c r="V232" s="66"/>
     </row>
-    <row r="233" spans="1:22" ht="13.8" hidden="1">
+    <row r="233" spans="1:22" ht="13.9" hidden="1">
       <c r="A233" s="66">
         <v>61</v>
       </c>
@@ -17742,7 +17735,7 @@
       <c r="U233" s="66"/>
       <c r="V233" s="66"/>
     </row>
-    <row r="234" spans="1:22" ht="224.4" hidden="1" customHeight="1">
+    <row r="234" spans="1:22" ht="224.45" hidden="1" customHeight="1">
       <c r="A234" s="66">
         <v>62</v>
       </c>
@@ -17800,7 +17793,7 @@
       </c>
     </row>
     <row r="235" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="90">
+      <c r="A235" s="93">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17855,7 +17848,7 @@
       </c>
     </row>
     <row r="236" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="85"/>
+      <c r="A236" s="98"/>
       <c r="B236" s="71" t="s">
         <v>583</v>
       </c>
@@ -17910,7 +17903,7 @@
       </c>
     </row>
     <row r="237" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="85"/>
+      <c r="A237" s="98"/>
       <c r="B237" s="71" t="s">
         <v>583</v>
       </c>
@@ -17965,7 +17958,7 @@
       </c>
     </row>
     <row r="238" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="85"/>
+      <c r="A238" s="98"/>
       <c r="B238" s="71" t="s">
         <v>583</v>
       </c>
@@ -18020,8 +18013,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A239" s="85"/>
+    <row r="239" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A239" s="98"/>
       <c r="B239" s="71" t="s">
         <v>583</v>
       </c>
@@ -18076,8 +18069,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="86"/>
+    <row r="240" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>597</v>
       </c>
@@ -18129,8 +18122,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="241" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="84">
+    <row r="241" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A241" s="87">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -18185,8 +18178,8 @@
       </c>
       <c r="V241" s="71"/>
     </row>
-    <row r="242" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="84"/>
+    <row r="242" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A242" s="87"/>
       <c r="B242" s="71" t="s">
         <v>600</v>
       </c>
@@ -18240,8 +18233,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A243" s="84"/>
+    <row r="243" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A243" s="87"/>
       <c r="B243" s="71" t="s">
         <v>600</v>
       </c>
@@ -18301,8 +18294,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="41.4" hidden="1">
-      <c r="A244" s="84"/>
+    <row r="244" spans="1:22" ht="41.45" hidden="1">
+      <c r="A244" s="87"/>
       <c r="B244" s="71" t="s">
         <v>600</v>
       </c>
@@ -18354,8 +18347,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="245" spans="1:22" ht="13.8" hidden="1">
-      <c r="A245" s="84"/>
+    <row r="245" spans="1:22" ht="13.9" hidden="1">
+      <c r="A245" s="87"/>
       <c r="B245" s="71" t="s">
         <v>600</v>
       </c>
@@ -18390,8 +18383,8 @@
       <c r="U245" s="80"/>
       <c r="V245" s="71"/>
     </row>
-    <row r="246" spans="1:22" ht="13.8" hidden="1">
-      <c r="A246" s="84"/>
+    <row r="246" spans="1:22" ht="13.9" hidden="1">
+      <c r="A246" s="87"/>
       <c r="B246" s="71" t="s">
         <v>600</v>
       </c>
@@ -18443,8 +18436,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="247" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A247" s="84"/>
+    <row r="247" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A247" s="87"/>
       <c r="B247" s="71" t="s">
         <v>600</v>
       </c>
@@ -18499,7 +18492,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="248" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="248" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A248" s="66"/>
       <c r="B248" s="71" t="s">
         <v>608</v>
@@ -18555,7 +18548,7 @@
       <c r="V248" s="71"/>
     </row>
     <row r="249" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="84">
+      <c r="A249" s="87">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18611,7 +18604,7 @@
       </c>
     </row>
     <row r="250" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A250" s="84"/>
+      <c r="A250" s="87"/>
       <c r="B250" s="71" t="s">
         <v>608</v>
       </c>
@@ -18665,8 +18658,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A251" s="84"/>
+    <row r="251" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A251" s="87"/>
       <c r="B251" s="71" t="s">
         <v>608</v>
       </c>
@@ -18721,7 +18714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="13.8" hidden="1">
+    <row r="252" spans="1:22" ht="13.9" hidden="1">
       <c r="A252" s="66">
         <v>66</v>
       </c>
@@ -18751,7 +18744,7 @@
       <c r="U252" s="66"/>
       <c r="V252" s="66"/>
     </row>
-    <row r="253" spans="1:22" ht="13.8" hidden="1">
+    <row r="253" spans="1:22" ht="13.9" hidden="1">
       <c r="A253" s="66"/>
       <c r="B253" s="71" t="s">
         <v>617</v>
@@ -18802,7 +18795,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="1:22" ht="13.8" hidden="1">
+    <row r="254" spans="1:22" ht="13.9" hidden="1">
       <c r="A254" s="66">
         <v>67</v>
       </c>
@@ -18860,7 +18853,7 @@
       <c r="V254" s="66"/>
     </row>
     <row r="255" spans="1:22" ht="27.6" hidden="1">
-      <c r="A255" s="90">
+      <c r="A255" s="93">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18915,7 +18908,7 @@
       </c>
     </row>
     <row r="256" spans="1:22" ht="27.6" hidden="1">
-      <c r="A256" s="85"/>
+      <c r="A256" s="98"/>
       <c r="B256" s="71" t="s">
         <v>621</v>
       </c>
@@ -18970,8 +18963,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="257" spans="1:22" ht="13.8" hidden="1">
-      <c r="A257" s="85"/>
+    <row r="257" spans="1:22" ht="13.9" hidden="1">
+      <c r="A257" s="98"/>
       <c r="B257" s="71" t="s">
         <v>621</v>
       </c>
@@ -19027,8 +19020,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="258" spans="1:22" ht="13.8" hidden="1">
-      <c r="A258" s="85"/>
+    <row r="258" spans="1:22" ht="13.9" hidden="1">
+      <c r="A258" s="98"/>
       <c r="B258" s="71" t="s">
         <v>621</v>
       </c>
@@ -19084,8 +19077,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="259" spans="1:22" ht="13.8" hidden="1">
-      <c r="A259" s="85"/>
+    <row r="259" spans="1:22" ht="13.9" hidden="1">
+      <c r="A259" s="98"/>
       <c r="B259" s="71" t="s">
         <v>621</v>
       </c>
@@ -19139,8 +19132,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="260" spans="1:22" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A260" s="86"/>
+    <row r="260" spans="1:22" ht="34.15" hidden="1" customHeight="1">
+      <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>621</v>
       </c>
@@ -19196,8 +19189,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:22" ht="55.2" hidden="1">
-      <c r="A261" s="90">
+    <row r="261" spans="1:22" ht="55.15" hidden="1">
+      <c r="A261" s="93">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19253,7 +19246,7 @@
       </c>
     </row>
     <row r="262" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="85"/>
+      <c r="A262" s="98"/>
       <c r="B262" s="71" t="s">
         <v>631</v>
       </c>
@@ -19306,7 +19299,7 @@
       </c>
     </row>
     <row r="263" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="85"/>
+      <c r="A263" s="98"/>
       <c r="B263" s="71" t="s">
         <v>639</v>
       </c>
@@ -19354,8 +19347,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="264" spans="1:22" ht="55.2" hidden="1">
-      <c r="A264" s="85"/>
+    <row r="264" spans="1:22" ht="55.15" hidden="1">
+      <c r="A264" s="98"/>
       <c r="B264" s="71" t="s">
         <v>639</v>
       </c>
@@ -19405,8 +19398,8 @@
         <v>643</v>
       </c>
     </row>
-    <row r="265" spans="1:22" ht="46.2" hidden="1" customHeight="1">
-      <c r="A265" s="85"/>
+    <row r="265" spans="1:22" ht="46.15" hidden="1" customHeight="1">
+      <c r="A265" s="98"/>
       <c r="B265" s="71" t="s">
         <v>631</v>
       </c>
@@ -19460,7 +19453,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:22" ht="46.2" hidden="1" customHeight="1">
+    <row r="266" spans="1:22" ht="46.15" hidden="1" customHeight="1">
       <c r="A266" s="67"/>
       <c r="B266" s="71" t="s">
         <v>645</v>
@@ -19518,8 +19511,8 @@
       </c>
       <c r="V266" s="71"/>
     </row>
-    <row r="267" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="84">
+    <row r="267" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A267" s="87">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19577,8 +19570,8 @@
       </c>
       <c r="V267" s="71"/>
     </row>
-    <row r="268" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="84"/>
+    <row r="268" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A268" s="87"/>
       <c r="B268" s="71" t="s">
         <v>645</v>
       </c>
@@ -19634,8 +19627,8 @@
       </c>
       <c r="V268" s="71"/>
     </row>
-    <row r="269" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A269" s="84"/>
+    <row r="269" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A269" s="87"/>
       <c r="B269" s="71" t="s">
         <v>645</v>
       </c>
@@ -19691,8 +19684,8 @@
       </c>
       <c r="V269" s="71"/>
     </row>
-    <row r="270" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A270" s="84"/>
+    <row r="270" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A270" s="87"/>
       <c r="B270" s="71" t="s">
         <v>645</v>
       </c>
@@ -19748,7 +19741,7 @@
       </c>
       <c r="V270" s="66"/>
     </row>
-    <row r="271" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="271" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A271" s="66"/>
       <c r="B271" s="71" t="s">
         <v>655</v>
@@ -19805,8 +19798,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="84">
+    <row r="272" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A272" s="87">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19862,8 +19855,8 @@
       </c>
       <c r="V272" s="71"/>
     </row>
-    <row r="273" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A273" s="84"/>
+    <row r="273" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A273" s="87"/>
       <c r="B273" s="71" t="s">
         <v>655</v>
       </c>
@@ -19919,8 +19912,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="274" spans="1:22" ht="13.8" hidden="1">
-      <c r="A274" s="84"/>
+    <row r="274" spans="1:22" ht="13.9" hidden="1">
+      <c r="A274" s="87"/>
       <c r="B274" s="71" t="s">
         <v>655</v>
       </c>
@@ -19976,8 +19969,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="275" spans="1:22" ht="13.8" hidden="1">
-      <c r="A275" s="84"/>
+    <row r="275" spans="1:22" ht="13.9" hidden="1">
+      <c r="A275" s="87"/>
       <c r="B275" s="71" t="s">
         <v>655</v>
       </c>
@@ -20033,8 +20026,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="276" spans="1:22" ht="13.8" hidden="1">
-      <c r="A276" s="84"/>
+    <row r="276" spans="1:22" ht="13.9" hidden="1">
+      <c r="A276" s="87"/>
       <c r="B276" s="66" t="s">
         <v>662</v>
       </c>
@@ -20090,7 +20083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="277" spans="1:22" ht="13.8" hidden="1">
+    <row r="277" spans="1:22" ht="13.9" hidden="1">
       <c r="A277" s="66">
         <v>72</v>
       </c>
@@ -20147,7 +20140,7 @@
       </c>
       <c r="V277" s="66"/>
     </row>
-    <row r="278" spans="1:22" ht="13.8" hidden="1">
+    <row r="278" spans="1:22" ht="13.9" hidden="1">
       <c r="A278" s="66"/>
       <c r="B278" s="71" t="s">
         <v>667</v>
@@ -20204,7 +20197,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="279" spans="1:22" ht="13.8" hidden="1">
+    <row r="279" spans="1:22" ht="13.9" hidden="1">
       <c r="A279" s="66"/>
       <c r="B279" s="71" t="s">
         <v>667</v>
@@ -20257,7 +20250,7 @@
       <c r="U279" s="70"/>
       <c r="V279" s="66"/>
     </row>
-    <row r="280" spans="1:22" ht="13.8" hidden="1">
+    <row r="280" spans="1:22" ht="13.9" hidden="1">
       <c r="A280" s="66">
         <v>73</v>
       </c>
@@ -20315,7 +20308,7 @@
       <c r="V280" s="66"/>
     </row>
     <row r="281" spans="1:22" ht="27.6" hidden="1">
-      <c r="A281" s="84">
+      <c r="A281" s="87">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20369,8 +20362,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="282" spans="1:22" ht="13.8" hidden="1">
-      <c r="A282" s="84"/>
+    <row r="282" spans="1:22" ht="13.9" hidden="1">
+      <c r="A282" s="87"/>
       <c r="B282" s="71" t="s">
         <v>671</v>
       </c>
@@ -20419,8 +20412,8 @@
       </c>
       <c r="V282" s="66"/>
     </row>
-    <row r="283" spans="1:22" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A283" s="84">
+    <row r="283" spans="1:22" ht="37.15" hidden="1" customHeight="1">
+      <c r="A283" s="87">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20475,8 +20468,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="13.8" hidden="1">
-      <c r="A284" s="84"/>
+    <row r="284" spans="1:22" ht="13.9" hidden="1">
+      <c r="A284" s="87"/>
       <c r="B284" s="71" t="s">
         <v>674</v>
       </c>
@@ -20530,8 +20523,8 @@
       </c>
       <c r="V284" s="71"/>
     </row>
-    <row r="285" spans="1:22" ht="13.8" hidden="1">
-      <c r="A285" s="86">
+    <row r="285" spans="1:22" ht="13.9" hidden="1">
+      <c r="A285" s="94">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20589,8 +20582,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="286" spans="1:22" ht="13.8" hidden="1">
-      <c r="A286" s="86"/>
+    <row r="286" spans="1:22" ht="13.9" hidden="1">
+      <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>678</v>
       </c>
@@ -20646,8 +20639,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="287" spans="1:22" ht="13.8" hidden="1">
-      <c r="A287" s="86"/>
+    <row r="287" spans="1:22" ht="13.9" hidden="1">
+      <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>678</v>
       </c>
@@ -20703,8 +20696,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="288" spans="1:22" ht="13.8" hidden="1">
-      <c r="A288" s="86"/>
+    <row r="288" spans="1:22" ht="13.9" hidden="1">
+      <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>678</v>
       </c>
@@ -20760,8 +20753,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="289" spans="1:22" ht="13.8" hidden="1">
-      <c r="A289" s="84"/>
+    <row r="289" spans="1:22" ht="13.9" hidden="1">
+      <c r="A289" s="87"/>
       <c r="B289" s="71" t="s">
         <v>678</v>
       </c>
@@ -20815,7 +20808,7 @@
       </c>
     </row>
     <row r="290" spans="1:22" ht="27.6" hidden="1">
-      <c r="A290" s="84"/>
+      <c r="A290" s="87"/>
       <c r="B290" s="71" t="s">
         <v>678</v>
       </c>
@@ -20869,8 +20862,8 @@
         <v>690</v>
       </c>
     </row>
-    <row r="291" spans="1:22" ht="13.8" hidden="1">
-      <c r="A291" s="84"/>
+    <row r="291" spans="1:22" ht="13.9" hidden="1">
+      <c r="A291" s="87"/>
       <c r="B291" s="71" t="s">
         <v>678</v>
       </c>
@@ -20926,8 +20919,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="292" spans="1:22" ht="13.8" hidden="1">
-      <c r="A292" s="84"/>
+    <row r="292" spans="1:22" ht="13.9" hidden="1">
+      <c r="A292" s="87"/>
       <c r="B292" s="71" t="s">
         <v>678</v>
       </c>
@@ -20979,8 +20972,8 @@
       </c>
       <c r="V292" s="71"/>
     </row>
-    <row r="293" spans="1:22" ht="13.8" hidden="1">
-      <c r="A293" s="84"/>
+    <row r="293" spans="1:22" ht="13.9" hidden="1">
+      <c r="A293" s="87"/>
       <c r="B293" s="71" t="s">
         <v>678</v>
       </c>
@@ -21034,7 +21027,7 @@
       </c>
       <c r="V293" s="71"/>
     </row>
-    <row r="294" spans="1:22" ht="41.4" hidden="1">
+    <row r="294" spans="1:22" ht="41.45" hidden="1">
       <c r="A294" s="66"/>
       <c r="B294" s="71" t="s">
         <v>693</v>
@@ -21096,7 +21089,7 @@
       </c>
     </row>
     <row r="295" spans="1:22" ht="96.6" hidden="1">
-      <c r="A295" s="84">
+      <c r="A295" s="87">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -21159,7 +21152,7 @@
       </c>
     </row>
     <row r="296" spans="1:22" ht="27.6" hidden="1">
-      <c r="A296" s="84"/>
+      <c r="A296" s="87"/>
       <c r="B296" s="71" t="s">
         <v>693</v>
       </c>
@@ -21219,8 +21212,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="297" spans="1:22" ht="13.8" hidden="1">
-      <c r="A297" s="84"/>
+    <row r="297" spans="1:22" ht="13.9" hidden="1">
+      <c r="A297" s="87"/>
       <c r="B297" s="71" t="s">
         <v>693</v>
       </c>
@@ -21281,7 +21274,7 @@
       </c>
     </row>
     <row r="298" spans="1:22" ht="27.6" hidden="1">
-      <c r="A298" s="84">
+      <c r="A298" s="87">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21336,8 +21329,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="299" spans="1:22" ht="13.8" hidden="1">
-      <c r="A299" s="84"/>
+    <row r="299" spans="1:22" ht="13.9" hidden="1">
+      <c r="A299" s="87"/>
       <c r="B299" s="71" t="s">
         <v>704</v>
       </c>
@@ -21391,8 +21384,8 @@
       </c>
       <c r="V299" s="71"/>
     </row>
-    <row r="300" spans="1:22" ht="13.8" hidden="1">
-      <c r="A300" s="84"/>
+    <row r="300" spans="1:22" ht="13.9" hidden="1">
+      <c r="A300" s="87"/>
       <c r="B300" s="71" t="s">
         <v>704</v>
       </c>
@@ -21448,8 +21441,8 @@
         <v>711</v>
       </c>
     </row>
-    <row r="301" spans="1:22" ht="13.8" hidden="1">
-      <c r="A301" s="85"/>
+    <row r="301" spans="1:22" ht="13.9" hidden="1">
+      <c r="A301" s="98"/>
       <c r="B301" s="71" t="s">
         <v>639</v>
       </c>
@@ -21503,8 +21496,8 @@
       </c>
       <c r="V301" s="71"/>
     </row>
-    <row r="302" spans="1:22" ht="13.8" hidden="1">
-      <c r="A302" s="86"/>
+    <row r="302" spans="1:22" ht="13.9" hidden="1">
+      <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>639</v>
       </c>
@@ -21561,7 +21554,7 @@
       </c>
     </row>
     <row r="303" spans="1:22" ht="27.6" hidden="1">
-      <c r="A303" s="90">
+      <c r="A303" s="93">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21616,8 +21609,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="304" spans="1:22" ht="13.8" hidden="1">
-      <c r="A304" s="85"/>
+    <row r="304" spans="1:22" ht="13.9" hidden="1">
+      <c r="A304" s="98"/>
       <c r="B304" s="71" t="s">
         <v>718</v>
       </c>
@@ -21672,7 +21665,7 @@
       <c r="V304" s="71"/>
     </row>
     <row r="305" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="90">
+      <c r="A305" s="93">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21727,7 +21720,7 @@
       </c>
     </row>
     <row r="306" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="85"/>
+      <c r="A306" s="98"/>
       <c r="B306" s="71" t="s">
         <v>720</v>
       </c>
@@ -21782,7 +21775,7 @@
       </c>
     </row>
     <row r="307" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="85"/>
+      <c r="A307" s="98"/>
       <c r="B307" s="71" t="s">
         <v>720</v>
       </c>
@@ -21835,8 +21828,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="308" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A308" s="86"/>
+    <row r="308" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>720</v>
       </c>
@@ -21951,7 +21944,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="310" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="310" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A310" s="66">
         <v>83</v>
       </c>
@@ -21964,57 +21957,57 @@
       <c r="D310" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E310" s="96">
+      <c r="E310" s="95">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="95" t="s">
+      <c r="F310" s="104" t="s">
         <v>731</v>
       </c>
-      <c r="G310" s="84" t="s">
+      <c r="G310" s="87" t="s">
         <v>732</v>
       </c>
-      <c r="H310" s="84">
+      <c r="H310" s="87">
         <v>13.3</v>
       </c>
-      <c r="I310" s="90" t="s">
+      <c r="I310" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="J310" s="90" t="s">
+      <c r="J310" s="93" t="s">
         <v>542</v>
       </c>
-      <c r="K310" s="87">
+      <c r="K310" s="91">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="87">
+      <c r="L310" s="91">
         <v>0</v>
       </c>
-      <c r="M310" s="87">
+      <c r="M310" s="91">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="89" t="s">
+      <c r="N310" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="O310" s="89" t="s">
+      <c r="O310" s="88" t="s">
         <v>733</v>
       </c>
-      <c r="P310" s="84">
+      <c r="P310" s="87">
         <v>2025</v>
       </c>
-      <c r="Q310" s="89" t="s">
+      <c r="Q310" s="88" t="s">
         <v>39</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
       <c r="T310" s="71"/>
-      <c r="U310" s="84"/>
-      <c r="V310" s="84" t="s">
+      <c r="U310" s="87"/>
+      <c r="V310" s="87" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="311" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="84">
+    <row r="311" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A311" s="87">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -22026,27 +22019,27 @@
       <c r="D311" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E311" s="97"/>
-      <c r="F311" s="89"/>
-      <c r="G311" s="84"/>
-      <c r="H311" s="84"/>
-      <c r="I311" s="86"/>
-      <c r="J311" s="86"/>
-      <c r="K311" s="87"/>
-      <c r="L311" s="87"/>
-      <c r="M311" s="87"/>
-      <c r="N311" s="89"/>
-      <c r="O311" s="89"/>
-      <c r="P311" s="84"/>
-      <c r="Q311" s="89"/>
+      <c r="E311" s="96"/>
+      <c r="F311" s="88"/>
+      <c r="G311" s="87"/>
+      <c r="H311" s="87"/>
+      <c r="I311" s="94"/>
+      <c r="J311" s="94"/>
+      <c r="K311" s="91"/>
+      <c r="L311" s="91"/>
+      <c r="M311" s="91"/>
+      <c r="N311" s="88"/>
+      <c r="O311" s="88"/>
+      <c r="P311" s="87"/>
+      <c r="Q311" s="88"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
       <c r="T311" s="71"/>
-      <c r="U311" s="84"/>
-      <c r="V311" s="84"/>
-    </row>
-    <row r="312" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="84"/>
+      <c r="U311" s="87"/>
+      <c r="V311" s="87"/>
+    </row>
+    <row r="312" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A312" s="87"/>
       <c r="B312" s="71" t="s">
         <v>730</v>
       </c>
@@ -22056,58 +22049,58 @@
       <c r="D312" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E312" s="96">
+      <c r="E312" s="95">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="89" t="s">
+      <c r="F312" s="88" t="s">
         <v>735</v>
       </c>
-      <c r="G312" s="84" t="s">
+      <c r="G312" s="87" t="s">
         <v>736</v>
       </c>
-      <c r="H312" s="84">
+      <c r="H312" s="87">
         <v>31.12</v>
       </c>
-      <c r="I312" s="90" t="s">
+      <c r="I312" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="J312" s="90" t="s">
+      <c r="J312" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="K312" s="87">
+      <c r="K312" s="91">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="87">
+      <c r="L312" s="91">
         <v>0</v>
       </c>
-      <c r="M312" s="87">
+      <c r="M312" s="91">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="89" t="s">
+      <c r="N312" s="88" t="s">
         <v>737</v>
       </c>
-      <c r="O312" s="89" t="s">
+      <c r="O312" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="P312" s="84">
+      <c r="P312" s="87">
         <v>2019</v>
       </c>
-      <c r="Q312" s="89" t="s">
+      <c r="Q312" s="88" t="s">
         <v>53</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
       <c r="T312" s="71"/>
-      <c r="U312" s="88">
+      <c r="U312" s="105">
         <v>1</v>
       </c>
-      <c r="V312" s="84" t="s">
+      <c r="V312" s="87" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="313" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="84"/>
+    <row r="313" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A313" s="87"/>
       <c r="B313" s="71" t="s">
         <v>734</v>
       </c>
@@ -22117,27 +22110,27 @@
       <c r="D313" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E313" s="97"/>
-      <c r="F313" s="89"/>
-      <c r="G313" s="84"/>
-      <c r="H313" s="84"/>
-      <c r="I313" s="86"/>
-      <c r="J313" s="86"/>
-      <c r="K313" s="87"/>
-      <c r="L313" s="87"/>
-      <c r="M313" s="87"/>
-      <c r="N313" s="89"/>
-      <c r="O313" s="89"/>
-      <c r="P313" s="84"/>
-      <c r="Q313" s="89"/>
+      <c r="E313" s="96"/>
+      <c r="F313" s="88"/>
+      <c r="G313" s="87"/>
+      <c r="H313" s="87"/>
+      <c r="I313" s="94"/>
+      <c r="J313" s="94"/>
+      <c r="K313" s="91"/>
+      <c r="L313" s="91"/>
+      <c r="M313" s="91"/>
+      <c r="N313" s="88"/>
+      <c r="O313" s="88"/>
+      <c r="P313" s="87"/>
+      <c r="Q313" s="88"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
       <c r="T313" s="71"/>
-      <c r="U313" s="88"/>
-      <c r="V313" s="84"/>
-    </row>
-    <row r="314" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="84"/>
+      <c r="U313" s="105"/>
+      <c r="V313" s="87"/>
+    </row>
+    <row r="314" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A314" s="87"/>
       <c r="B314" s="71" t="s">
         <v>734</v>
       </c>
@@ -22195,8 +22188,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="315" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A315" s="84"/>
+    <row r="315" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A315" s="87"/>
       <c r="B315" s="71" t="s">
         <v>734</v>
       </c>
@@ -22252,8 +22245,8 @@
       </c>
       <c r="V315" s="71"/>
     </row>
-    <row r="316" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A316" s="84"/>
+    <row r="316" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A316" s="87"/>
       <c r="B316" s="71" t="s">
         <v>734</v>
       </c>
@@ -22310,7 +22303,7 @@
       </c>
       <c r="V316" s="71"/>
     </row>
-    <row r="317" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="317" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A317" s="72"/>
       <c r="B317" s="71" t="s">
         <v>740</v>
@@ -22365,7 +22358,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="318" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="318" spans="1:22" ht="40.9" hidden="1" customHeight="1">
       <c r="A318" s="72"/>
       <c r="B318" s="71" t="s">
         <v>740</v>
@@ -22409,8 +22402,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="319" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A319" s="90">
+    <row r="319" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A319" s="93">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22459,8 +22452,8 @@
       <c r="U319" s="80"/>
       <c r="V319" s="71"/>
     </row>
-    <row r="320" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A320" s="86"/>
+    <row r="320" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>740</v>
       </c>
@@ -22513,8 +22506,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="321" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A321" s="91">
+    <row r="321" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A321" s="99">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22568,8 +22561,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="322" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A322" s="92"/>
+    <row r="322" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>746</v>
       </c>
@@ -22619,8 +22612,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="323" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A323" s="92"/>
+    <row r="323" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>746</v>
       </c>
@@ -22674,8 +22667,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="324" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A324" s="92"/>
+    <row r="324" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>746</v>
       </c>
@@ -22730,7 +22723,7 @@
       </c>
     </row>
     <row r="325" spans="1:22" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="85"/>
+      <c r="A325" s="98"/>
       <c r="B325" s="66" t="s">
         <v>746</v>
       </c>
@@ -22782,8 +22775,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="326" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A326" s="85"/>
+    <row r="326" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A326" s="98"/>
       <c r="B326" s="66" t="s">
         <v>746</v>
       </c>
@@ -22835,8 +22828,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="327" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A327" s="92"/>
+    <row r="327" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>746</v>
       </c>
@@ -22892,8 +22885,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="328" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A328" s="92"/>
+    <row r="328" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>746</v>
       </c>
@@ -22945,8 +22938,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="329" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A329" s="92"/>
+    <row r="329" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>746</v>
       </c>
@@ -23000,8 +22993,8 @@
       </c>
       <c r="V329" s="71"/>
     </row>
-    <row r="330" spans="1:22" ht="13.8" hidden="1">
-      <c r="A330" s="93"/>
+    <row r="330" spans="1:22" ht="13.9" hidden="1">
+      <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>746</v>
       </c>
@@ -23055,7 +23048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="331" spans="1:22" ht="41.4" hidden="1" customHeight="1">
+    <row r="331" spans="1:22" ht="41.45" hidden="1" customHeight="1">
       <c r="A331" s="68"/>
       <c r="B331" s="71" t="s">
         <v>764</v>
@@ -23108,7 +23101,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="332" spans="1:22" ht="13.8" hidden="1">
+    <row r="332" spans="1:22" ht="13.9" hidden="1">
       <c r="A332" s="66">
         <v>88</v>
       </c>
@@ -23138,7 +23131,7 @@
       <c r="U332" s="66"/>
       <c r="V332" s="66"/>
     </row>
-    <row r="333" spans="1:22" ht="41.4" hidden="1">
+    <row r="333" spans="1:22" ht="41.45" hidden="1">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>767</v>
@@ -23191,7 +23184,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:22" ht="13.8" hidden="1">
+    <row r="334" spans="1:22" ht="13.9" hidden="1">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>767</v>
@@ -23237,8 +23230,8 @@
         <v>590</v>
       </c>
     </row>
-    <row r="335" spans="1:22" ht="41.4" hidden="1">
-      <c r="A335" s="90">
+    <row r="335" spans="1:22" ht="41.45" hidden="1">
+      <c r="A335" s="93">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -23300,8 +23293,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="336" spans="1:22" ht="44.4" hidden="1" customHeight="1">
-      <c r="A336" s="85"/>
+    <row r="336" spans="1:22" ht="44.45" hidden="1" customHeight="1">
+      <c r="A336" s="98"/>
       <c r="B336" s="71" t="s">
         <v>767</v>
       </c>
@@ -23354,8 +23347,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="155.4" hidden="1" customHeight="1">
-      <c r="A337" s="85"/>
+    <row r="337" spans="1:23" ht="155.44999999999999" hidden="1" customHeight="1">
+      <c r="A337" s="98"/>
       <c r="B337" s="71" t="s">
         <v>767</v>
       </c>
@@ -23408,8 +23401,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="13.8" hidden="1">
-      <c r="A338" s="86"/>
+    <row r="338" spans="1:23" ht="13.9" hidden="1">
+      <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>767</v>
       </c>
@@ -23512,8 +23505,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A340" s="84">
+    <row r="340" spans="1:23" ht="40.9" hidden="1" customHeight="1">
+      <c r="A340" s="87">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23571,8 +23564,8 @@
       </c>
       <c r="W340" s="33"/>
     </row>
-    <row r="341" spans="1:23" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A341" s="84"/>
+    <row r="341" spans="1:23" ht="20.45" hidden="1" customHeight="1">
+      <c r="A341" s="87"/>
       <c r="B341" s="71" t="s">
         <v>775</v>
       </c>
@@ -23627,8 +23620,8 @@
       <c r="V341" s="66"/>
       <c r="W341" s="33"/>
     </row>
-    <row r="342" spans="1:23" ht="13.8" hidden="1">
-      <c r="A342" s="84">
+    <row r="342" spans="1:23" ht="13.9" hidden="1">
+      <c r="A342" s="87">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23686,8 +23679,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="13.8" hidden="1">
-      <c r="A343" s="84"/>
+    <row r="343" spans="1:23" ht="13.9" hidden="1">
+      <c r="A343" s="87"/>
       <c r="B343" s="71" t="s">
         <v>778</v>
       </c>
@@ -23744,7 +23737,7 @@
       </c>
     </row>
     <row r="344" spans="1:23" ht="27.6" hidden="1">
-      <c r="A344" s="84"/>
+      <c r="A344" s="87"/>
       <c r="B344" s="71" t="s">
         <v>778</v>
       </c>
@@ -23796,8 +23789,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="13.8" hidden="1">
-      <c r="A345" s="84"/>
+    <row r="345" spans="1:23" ht="13.9" hidden="1">
+      <c r="A345" s="87"/>
       <c r="B345" s="71" t="s">
         <v>778</v>
       </c>
@@ -23854,7 +23847,7 @@
       </c>
     </row>
     <row r="346" spans="1:23" ht="27.6" hidden="1">
-      <c r="A346" s="84"/>
+      <c r="A346" s="87"/>
       <c r="B346" s="71" t="s">
         <v>778</v>
       </c>
@@ -23908,7 +23901,7 @@
       </c>
     </row>
     <row r="347" spans="1:23" ht="27.6" hidden="1">
-      <c r="A347" s="84"/>
+      <c r="A347" s="87"/>
       <c r="B347" s="71" t="s">
         <v>778</v>
       </c>
@@ -23954,8 +23947,8 @@
         <v>789</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="13.8" hidden="1">
-      <c r="A348" s="84"/>
+    <row r="348" spans="1:23" ht="13.9" hidden="1">
+      <c r="A348" s="87"/>
       <c r="B348" s="71" t="s">
         <v>778</v>
       </c>
@@ -24011,8 +24004,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="84">
+    <row r="349" spans="1:23" ht="61.15" hidden="1" customHeight="1">
+      <c r="A349" s="87">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -24069,8 +24062,8 @@
       </c>
       <c r="V349" s="71"/>
     </row>
-    <row r="350" spans="1:23" ht="61.2" hidden="1" customHeight="1">
-      <c r="A350" s="84"/>
+    <row r="350" spans="1:23" ht="61.15" hidden="1" customHeight="1">
+      <c r="A350" s="87"/>
       <c r="B350" s="71" t="s">
         <v>790</v>
       </c>
@@ -24124,8 +24117,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="13.8" hidden="1">
-      <c r="A351" s="84"/>
+    <row r="351" spans="1:23" ht="13.9" hidden="1">
+      <c r="A351" s="87"/>
       <c r="B351" s="71" t="s">
         <v>790</v>
       </c>
@@ -24181,8 +24174,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="84">
+    <row r="352" spans="1:23" ht="94.15" hidden="1" customHeight="1">
+      <c r="A352" s="87">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -24240,8 +24233,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="353" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="84"/>
+    <row r="353" spans="1:22" ht="94.15" hidden="1" customHeight="1">
+      <c r="A353" s="87"/>
       <c r="B353" s="71" t="s">
         <v>795</v>
       </c>
@@ -24294,8 +24287,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="354" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A354" s="84"/>
+    <row r="354" spans="1:22" ht="94.15" hidden="1" customHeight="1">
+      <c r="A354" s="87"/>
       <c r="B354" s="71" t="s">
         <v>795</v>
       </c>
@@ -24351,8 +24344,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="355" spans="1:22" ht="46.95" hidden="1" customHeight="1">
-      <c r="A355" s="84"/>
+    <row r="355" spans="1:22" ht="46.9" hidden="1" customHeight="1">
+      <c r="A355" s="87"/>
       <c r="B355" s="71" t="s">
         <v>795</v>
       </c>
@@ -24412,8 +24405,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="356" spans="1:22" ht="13.8" hidden="1">
-      <c r="A356" s="84"/>
+    <row r="356" spans="1:22" ht="13.9" hidden="1">
+      <c r="A356" s="87"/>
       <c r="B356" s="71" t="s">
         <v>795</v>
       </c>
@@ -24467,8 +24460,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="357" spans="1:22" ht="13.8" hidden="1">
-      <c r="A357" s="84"/>
+    <row r="357" spans="1:22" ht="13.9" hidden="1">
+      <c r="A357" s="87"/>
       <c r="B357" s="71" t="s">
         <v>795</v>
       </c>
@@ -24635,7 +24628,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="360" spans="1:22" ht="65.400000000000006" hidden="1" customHeight="1">
+    <row r="360" spans="1:22" ht="65.45" hidden="1" customHeight="1">
       <c r="A360" s="48">
         <v>94</v>
       </c>
@@ -24806,8 +24799,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="363" spans="1:22" ht="13.8" hidden="1">
-      <c r="A363" s="84"/>
+    <row r="363" spans="1:22" ht="13.9" hidden="1">
+      <c r="A363" s="87"/>
       <c r="B363" s="71" t="s">
         <v>815</v>
       </c>
@@ -24862,8 +24855,8 @@
       </c>
       <c r="V363" s="71"/>
     </row>
-    <row r="364" spans="1:22" ht="13.8" hidden="1">
-      <c r="A364" s="84"/>
+    <row r="364" spans="1:22" ht="13.9" hidden="1">
+      <c r="A364" s="87"/>
       <c r="B364" s="71" t="s">
         <v>815</v>
       </c>
@@ -24919,7 +24912,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="365" spans="1:22" ht="13.8" hidden="1">
+    <row r="365" spans="1:22" ht="13.9" hidden="1">
       <c r="A365" s="68">
         <v>96</v>
       </c>
@@ -24976,7 +24969,7 @@
       </c>
       <c r="V365" s="66"/>
     </row>
-    <row r="366" spans="1:22" ht="13.8" hidden="1">
+    <row r="366" spans="1:22" ht="13.9" hidden="1">
       <c r="A366" s="68"/>
       <c r="B366" s="71" t="s">
         <v>819</v>
@@ -25031,7 +25024,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="367" spans="1:22" ht="13.8" hidden="1">
+    <row r="367" spans="1:22" ht="13.9" hidden="1">
       <c r="A367" s="66">
         <v>96</v>
       </c>
@@ -25089,7 +25082,7 @@
       <c r="V367" s="71"/>
     </row>
     <row r="368" spans="1:22" ht="27.6" hidden="1">
-      <c r="A368" s="90">
+      <c r="A368" s="93">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -25140,8 +25133,8 @@
         <v>387</v>
       </c>
     </row>
-    <row r="369" spans="1:22" ht="41.4" hidden="1">
-      <c r="A369" s="85"/>
+    <row r="369" spans="1:22" ht="41.45" hidden="1">
+      <c r="A369" s="98"/>
       <c r="B369" s="71" t="s">
         <v>822</v>
       </c>
@@ -25202,7 +25195,7 @@
       </c>
     </row>
     <row r="370" spans="1:22" ht="27.6" hidden="1">
-      <c r="A370" s="85"/>
+      <c r="A370" s="98"/>
       <c r="B370" s="71" t="s">
         <v>822</v>
       </c>
@@ -25256,7 +25249,7 @@
       </c>
     </row>
     <row r="371" spans="1:22" ht="27.6" hidden="1">
-      <c r="A371" s="85"/>
+      <c r="A371" s="98"/>
       <c r="B371" s="71" t="s">
         <v>822</v>
       </c>
@@ -25313,7 +25306,7 @@
       </c>
     </row>
     <row r="372" spans="1:22" ht="27.6" hidden="1">
-      <c r="A372" s="86"/>
+      <c r="A372" s="94"/>
       <c r="B372" s="71" t="s">
         <v>822</v>
       </c>
@@ -25368,8 +25361,8 @@
       </c>
       <c r="V372" s="71"/>
     </row>
-    <row r="373" spans="1:22" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A373" s="84">
+    <row r="373" spans="1:22" ht="148.9" hidden="1" customHeight="1">
+      <c r="A373" s="87">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25424,8 +25417,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="374" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="84"/>
+    <row r="374" spans="1:22" ht="40.15" hidden="1" customHeight="1">
+      <c r="A374" s="87"/>
       <c r="B374" s="71" t="s">
         <v>828</v>
       </c>
@@ -25478,8 +25471,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="375" spans="1:22" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="84"/>
+    <row r="375" spans="1:22" ht="34.9" hidden="1" customHeight="1">
+      <c r="A375" s="87"/>
       <c r="B375" s="71" t="s">
         <v>828</v>
       </c>
@@ -25532,8 +25525,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="376" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A376" s="84"/>
+    <row r="376" spans="1:22" ht="37.9" hidden="1" customHeight="1">
+      <c r="A376" s="87"/>
       <c r="B376" s="71" t="s">
         <v>828</v>
       </c>
@@ -25586,8 +25579,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="377" spans="1:22" ht="122.4" hidden="1" customHeight="1">
-      <c r="A377" s="84"/>
+    <row r="377" spans="1:22" ht="122.45" hidden="1" customHeight="1">
+      <c r="A377" s="87"/>
       <c r="B377" s="71" t="s">
         <v>828</v>
       </c>
@@ -25630,8 +25623,8 @@
         <v>841</v>
       </c>
     </row>
-    <row r="378" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A378" s="84"/>
+    <row r="378" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A378" s="87"/>
       <c r="B378" s="71" t="s">
         <v>828</v>
       </c>
@@ -25683,8 +25676,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A379" s="84"/>
+    <row r="379" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A379" s="87"/>
       <c r="B379" s="71" t="s">
         <v>828</v>
       </c>
@@ -25736,8 +25729,8 @@
         <v>844</v>
       </c>
     </row>
-    <row r="380" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A380" s="84"/>
+    <row r="380" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A380" s="87"/>
       <c r="B380" s="71" t="s">
         <v>828</v>
       </c>
@@ -25783,8 +25776,8 @@
         <v>846</v>
       </c>
     </row>
-    <row r="381" spans="1:22" ht="13.8" hidden="1">
-      <c r="A381" s="84"/>
+    <row r="381" spans="1:22" ht="13.9" hidden="1">
+      <c r="A381" s="87"/>
       <c r="B381" s="71" t="s">
         <v>828</v>
       </c>
@@ -25833,8 +25826,8 @@
       </c>
       <c r="V381" s="71"/>
     </row>
-    <row r="382" spans="1:22" ht="13.8" hidden="1">
-      <c r="A382" s="84"/>
+    <row r="382" spans="1:22" ht="13.9" hidden="1">
+      <c r="A382" s="87"/>
       <c r="B382" s="71" t="s">
         <v>828</v>
       </c>
@@ -25888,8 +25881,8 @@
       </c>
       <c r="V382" s="71"/>
     </row>
-    <row r="383" spans="1:22" ht="13.8" hidden="1">
-      <c r="A383" s="84"/>
+    <row r="383" spans="1:22" ht="13.9" hidden="1">
+      <c r="A383" s="87"/>
       <c r="B383" s="71" t="s">
         <v>828</v>
       </c>
@@ -25941,8 +25934,8 @@
         <v>852</v>
       </c>
     </row>
-    <row r="384" spans="1:22" ht="13.8" hidden="1">
-      <c r="A384" s="84"/>
+    <row r="384" spans="1:22" ht="13.9" hidden="1">
+      <c r="A384" s="87"/>
       <c r="B384" s="71" t="s">
         <v>828</v>
       </c>
@@ -25997,7 +25990,7 @@
       <c r="V384" s="71"/>
     </row>
     <row r="385" spans="1:22" ht="27.6" hidden="1">
-      <c r="A385" s="86">
+      <c r="A385" s="94">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -26052,8 +26045,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="386" spans="1:22" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A386" s="84"/>
+    <row r="386" spans="1:22" ht="163.15" hidden="1" customHeight="1">
+      <c r="A386" s="87"/>
       <c r="B386" s="71" t="s">
         <v>856</v>
       </c>
@@ -26106,8 +26099,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="387" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A387" s="84"/>
+    <row r="387" spans="1:22" ht="61.15" hidden="1" customHeight="1">
+      <c r="A387" s="87"/>
       <c r="B387" s="71" t="s">
         <v>856</v>
       </c>
@@ -26163,8 +26156,8 @@
       </c>
       <c r="V387" s="71"/>
     </row>
-    <row r="388" spans="1:22" ht="13.8" hidden="1">
-      <c r="A388" s="84"/>
+    <row r="388" spans="1:22" ht="13.9" hidden="1">
+      <c r="A388" s="87"/>
       <c r="B388" s="71" t="s">
         <v>856</v>
       </c>
@@ -26218,8 +26211,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:22" ht="13.8" hidden="1">
-      <c r="A389" s="84"/>
+    <row r="389" spans="1:22" ht="13.9" hidden="1">
+      <c r="A389" s="87"/>
       <c r="B389" s="71" t="s">
         <v>855</v>
       </c>
@@ -26273,8 +26266,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="390" spans="1:22" ht="13.8" hidden="1">
-      <c r="A390" s="84"/>
+    <row r="390" spans="1:22" ht="13.9" hidden="1">
+      <c r="A390" s="87"/>
       <c r="B390" s="71" t="s">
         <v>855</v>
       </c>
@@ -26330,8 +26323,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="391" spans="1:22" ht="13.8" hidden="1">
-      <c r="A391" s="84"/>
+    <row r="391" spans="1:22" ht="13.9" hidden="1">
+      <c r="A391" s="87"/>
       <c r="B391" s="71" t="s">
         <v>855</v>
       </c>
@@ -26372,8 +26365,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="392" spans="1:22" ht="13.8" hidden="1">
-      <c r="A392" s="84"/>
+    <row r="392" spans="1:22" ht="13.9" hidden="1">
+      <c r="A392" s="87"/>
       <c r="B392" s="66" t="s">
         <v>855</v>
       </c>
@@ -26427,7 +26420,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="393" spans="1:22" ht="148.19999999999999" hidden="1" customHeight="1">
+    <row r="393" spans="1:22" ht="148.15" hidden="1" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>865</v>
@@ -26481,8 +26474,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="394" spans="1:22" ht="58.2" hidden="1" customHeight="1">
-      <c r="A394" s="84">
+    <row r="394" spans="1:22" ht="58.15" hidden="1" customHeight="1">
+      <c r="A394" s="87">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26537,8 +26530,8 @@
         <v>868</v>
       </c>
     </row>
-    <row r="395" spans="1:22" ht="41.4" hidden="1">
-      <c r="A395" s="84"/>
+    <row r="395" spans="1:22" ht="41.45" hidden="1">
+      <c r="A395" s="87"/>
       <c r="B395" s="66" t="s">
         <v>865</v>
       </c>
@@ -26592,7 +26585,7 @@
       </c>
     </row>
     <row r="396" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="84"/>
+      <c r="A396" s="87"/>
       <c r="B396" s="71" t="s">
         <v>865</v>
       </c>
@@ -26649,7 +26642,7 @@
       </c>
     </row>
     <row r="397" spans="1:22" ht="27.6" hidden="1">
-      <c r="A397" s="84"/>
+      <c r="A397" s="87"/>
       <c r="B397" s="71" t="s">
         <v>865</v>
       </c>
@@ -26702,7 +26695,7 @@
       </c>
     </row>
     <row r="398" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A398" s="84"/>
+      <c r="A398" s="87"/>
       <c r="B398" s="71" t="s">
         <v>865</v>
       </c>
@@ -26756,8 +26749,8 @@
       </c>
       <c r="V398" s="71"/>
     </row>
-    <row r="399" spans="1:22" ht="13.8" hidden="1">
-      <c r="A399" s="84"/>
+    <row r="399" spans="1:22" ht="13.9" hidden="1">
+      <c r="A399" s="87"/>
       <c r="B399" s="71" t="s">
         <v>865</v>
       </c>
@@ -26812,7 +26805,7 @@
       <c r="V399" s="71"/>
     </row>
     <row r="400" spans="1:22" ht="27.6" hidden="1">
-      <c r="A400" s="94">
+      <c r="A400" s="102">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26869,8 +26862,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="401" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A401" s="94"/>
+    <row r="401" spans="1:22" ht="31.9" hidden="1" customHeight="1">
+      <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
         <v>875</v>
       </c>
@@ -26911,8 +26904,8 @@
       <c r="U401" s="80"/>
       <c r="V401" s="66"/>
     </row>
-    <row r="402" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A402" s="94"/>
+    <row r="402" spans="1:22" ht="31.9" hidden="1" customHeight="1">
+      <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
         <v>875</v>
       </c>
@@ -26966,8 +26959,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="403" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A403" s="94"/>
+    <row r="403" spans="1:22" ht="31.9" hidden="1" customHeight="1">
+      <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
         <v>875</v>
       </c>
@@ -27023,8 +27016,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="404" spans="1:22" ht="31.95" hidden="1" customHeight="1">
-      <c r="A404" s="94"/>
+    <row r="404" spans="1:22" ht="31.9" hidden="1" customHeight="1">
+      <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
         <v>875</v>
       </c>
@@ -27078,8 +27071,8 @@
       </c>
       <c r="V404" s="71"/>
     </row>
-    <row r="405" spans="1:22" ht="13.8" hidden="1">
-      <c r="A405" s="94"/>
+    <row r="405" spans="1:22" ht="13.9" hidden="1">
+      <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
         <v>875</v>
       </c>
@@ -27136,7 +27129,7 @@
       </c>
     </row>
     <row r="406" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="84">
+      <c r="A406" s="87">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -27191,8 +27184,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="407" spans="1:22" ht="13.8" hidden="1">
-      <c r="A407" s="84"/>
+    <row r="407" spans="1:22" ht="13.9" hidden="1">
+      <c r="A407" s="87"/>
       <c r="B407" s="71" t="s">
         <v>882</v>
       </c>
@@ -27248,8 +27241,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="408" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="84">
+    <row r="408" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A408" s="87">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -27305,8 +27298,8 @@
         <v>593</v>
       </c>
     </row>
-    <row r="409" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="84"/>
+    <row r="409" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A409" s="87"/>
       <c r="B409" s="71" t="s">
         <v>886</v>
       </c>
@@ -27362,8 +27355,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="410" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A410" s="84"/>
+    <row r="410" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A410" s="87"/>
       <c r="B410" s="71" t="s">
         <v>886</v>
       </c>
@@ -27418,8 +27411,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="411" spans="1:22" ht="13.8" hidden="1">
-      <c r="A411" s="84"/>
+    <row r="411" spans="1:22" ht="13.9" hidden="1">
+      <c r="A411" s="87"/>
       <c r="B411" s="71" t="s">
         <v>886</v>
       </c>
@@ -27476,7 +27469,7 @@
       </c>
     </row>
     <row r="412" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="84">
+      <c r="A412" s="87">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27532,7 +27525,7 @@
       </c>
     </row>
     <row r="413" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="84"/>
+      <c r="A413" s="87"/>
       <c r="B413" s="71" t="s">
         <v>891</v>
       </c>
@@ -27593,7 +27586,7 @@
       </c>
     </row>
     <row r="414" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="84"/>
+      <c r="A414" s="87"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27616,8 +27609,8 @@
       <c r="U414" s="80"/>
       <c r="V414" s="71"/>
     </row>
-    <row r="415" spans="1:22" ht="55.2" hidden="1">
-      <c r="A415" s="84"/>
+    <row r="415" spans="1:22" ht="55.15" hidden="1">
+      <c r="A415" s="87"/>
       <c r="B415" s="71" t="s">
         <v>891</v>
       </c>
@@ -27670,8 +27663,8 @@
         <v>897</v>
       </c>
     </row>
-    <row r="416" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A416" s="84"/>
+    <row r="416" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A416" s="87"/>
       <c r="B416" s="71" t="s">
         <v>891</v>
       </c>
@@ -27726,8 +27719,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="417" spans="1:22" ht="41.4" hidden="1">
-      <c r="A417" s="84">
+    <row r="417" spans="1:22" ht="41.45" hidden="1">
+      <c r="A417" s="87">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27782,8 +27775,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="418" spans="1:22" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A418" s="84"/>
+    <row r="418" spans="1:22" ht="142.9" hidden="1" customHeight="1">
+      <c r="A418" s="87"/>
       <c r="B418" s="71" t="s">
         <v>898</v>
       </c>
@@ -27830,8 +27823,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="419" spans="1:22" ht="13.8" hidden="1">
-      <c r="A419" s="84"/>
+    <row r="419" spans="1:22" ht="13.9" hidden="1">
+      <c r="A419" s="87"/>
       <c r="B419" s="71" t="s">
         <v>898</v>
       </c>
@@ -27887,8 +27880,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="420" spans="1:22" ht="13.8" hidden="1">
-      <c r="A420" s="84"/>
+    <row r="420" spans="1:22" ht="13.9" hidden="1">
+      <c r="A420" s="87"/>
       <c r="B420" s="71" t="s">
         <v>898</v>
       </c>
@@ -27944,8 +27937,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="421" spans="1:22" ht="13.8" hidden="1">
-      <c r="A421" s="84"/>
+    <row r="421" spans="1:22" ht="13.9" hidden="1">
+      <c r="A421" s="87"/>
       <c r="B421" s="71" t="s">
         <v>898</v>
       </c>
@@ -28002,7 +27995,7 @@
       </c>
     </row>
     <row r="422" spans="1:22" ht="27.6" hidden="1">
-      <c r="A422" s="84"/>
+      <c r="A422" s="87"/>
       <c r="B422" s="71" t="s">
         <v>898</v>
       </c>
@@ -28045,8 +28038,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="423" spans="1:22" ht="13.8" hidden="1">
-      <c r="A423" s="84"/>
+    <row r="423" spans="1:22" ht="13.9" hidden="1">
+      <c r="A423" s="87"/>
       <c r="B423" s="71" t="s">
         <v>898</v>
       </c>
@@ -28096,8 +28089,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="424" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A424" s="84"/>
+    <row r="424" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A424" s="87"/>
       <c r="B424" s="71" t="s">
         <v>898</v>
       </c>
@@ -28256,7 +28249,7 @@
       </c>
     </row>
     <row r="427" spans="1:22" ht="27.6" hidden="1">
-      <c r="A427" s="84">
+      <c r="A427" s="87">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -28313,8 +28306,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="428" spans="1:22" ht="13.8" hidden="1">
-      <c r="A428" s="84"/>
+    <row r="428" spans="1:22" ht="13.9" hidden="1">
+      <c r="A428" s="87"/>
       <c r="B428" s="71" t="s">
         <v>915</v>
       </c>
@@ -28368,8 +28361,8 @@
       </c>
       <c r="V428" s="71"/>
     </row>
-    <row r="429" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="84"/>
+    <row r="429" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A429" s="87"/>
       <c r="B429" s="71" t="s">
         <v>915</v>
       </c>
@@ -28421,8 +28414,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="430" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="84"/>
+    <row r="430" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A430" s="87"/>
       <c r="B430" s="71" t="s">
         <v>914</v>
       </c>
@@ -28474,8 +28467,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="431" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A431" s="84"/>
+    <row r="431" spans="1:22" ht="40.9" hidden="1" customHeight="1">
+      <c r="A431" s="87"/>
       <c r="B431" s="71" t="s">
         <v>914</v>
       </c>
@@ -28527,8 +28520,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="432" spans="1:22" ht="13.8" hidden="1">
-      <c r="A432" s="84"/>
+    <row r="432" spans="1:22" ht="13.9" hidden="1">
+      <c r="A432" s="87"/>
       <c r="B432" s="71" t="s">
         <v>915</v>
       </c>
@@ -28582,8 +28575,8 @@
       </c>
       <c r="V432" s="71"/>
     </row>
-    <row r="433" spans="1:22" ht="13.8" hidden="1">
-      <c r="A433" s="84"/>
+    <row r="433" spans="1:22" ht="13.9" hidden="1">
+      <c r="A433" s="87"/>
       <c r="B433" s="71" t="s">
         <v>914</v>
       </c>
@@ -28637,8 +28630,8 @@
       </c>
       <c r="V433" s="66"/>
     </row>
-    <row r="434" spans="1:22" ht="13.8" hidden="1">
-      <c r="A434" s="85"/>
+    <row r="434" spans="1:22" ht="13.9" hidden="1">
+      <c r="A434" s="98"/>
       <c r="B434" s="71" t="s">
         <v>926</v>
       </c>
@@ -28660,38 +28653,38 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="87">
+      <c r="K434" s="91">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="87">
+      <c r="L434" s="91">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="87">
+      <c r="M434" s="91">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="89" t="s">
+      <c r="N434" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="O434" s="89" t="s">
+      <c r="O434" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="P434" s="84">
+      <c r="P434" s="87">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
       <c r="T434" s="66"/>
-      <c r="U434" s="88">
+      <c r="U434" s="105">
         <v>0.65</v>
       </c>
-      <c r="V434" s="84" t="s">
+      <c r="V434" s="87" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="435" spans="1:22" ht="27.6" hidden="1">
-      <c r="A435" s="85"/>
+      <c r="A435" s="98"/>
       <c r="B435" s="71" t="s">
         <v>926</v>
       </c>
@@ -28713,21 +28706,21 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="87"/>
-      <c r="L435" s="87"/>
-      <c r="M435" s="87"/>
-      <c r="N435" s="89"/>
-      <c r="O435" s="89"/>
-      <c r="P435" s="84"/>
+      <c r="K435" s="91"/>
+      <c r="L435" s="91"/>
+      <c r="M435" s="91"/>
+      <c r="N435" s="88"/>
+      <c r="O435" s="88"/>
+      <c r="P435" s="87"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
       <c r="T435" s="66"/>
-      <c r="U435" s="88"/>
-      <c r="V435" s="84"/>
-    </row>
-    <row r="436" spans="1:22" ht="13.8" hidden="1">
-      <c r="A436" s="85"/>
+      <c r="U435" s="105"/>
+      <c r="V435" s="87"/>
+    </row>
+    <row r="436" spans="1:22" ht="13.9" hidden="1">
+      <c r="A436" s="98"/>
       <c r="B436" s="71" t="s">
         <v>926</v>
       </c>
@@ -28781,8 +28774,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="437" spans="1:22" ht="13.8" hidden="1">
-      <c r="A437" s="85"/>
+    <row r="437" spans="1:22" ht="13.9" hidden="1">
+      <c r="A437" s="98"/>
       <c r="B437" s="71" t="s">
         <v>930</v>
       </c>
@@ -28836,8 +28829,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="438" spans="1:22" ht="13.8" hidden="1">
-      <c r="A438" s="85"/>
+    <row r="438" spans="1:22" ht="13.9" hidden="1">
+      <c r="A438" s="98"/>
       <c r="B438" s="71" t="s">
         <v>926</v>
       </c>
@@ -28890,7 +28883,7 @@
       </c>
     </row>
     <row r="439" spans="1:22" ht="27.6" hidden="1">
-      <c r="A439" s="86"/>
+      <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
         <v>926</v>
       </c>
@@ -28944,7 +28937,7 @@
       </c>
     </row>
     <row r="440" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="90">
+      <c r="A440" s="93">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28999,7 +28992,7 @@
       </c>
     </row>
     <row r="441" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="85"/>
+      <c r="A441" s="98"/>
       <c r="B441" s="71" t="s">
         <v>938</v>
       </c>
@@ -29051,7 +29044,7 @@
       </c>
     </row>
     <row r="442" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="85"/>
+      <c r="A442" s="98"/>
       <c r="B442" s="71" t="s">
         <v>938</v>
       </c>
@@ -29107,7 +29100,7 @@
       </c>
     </row>
     <row r="443" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="85"/>
+      <c r="A443" s="98"/>
       <c r="B443" s="71" t="s">
         <v>938</v>
       </c>
@@ -29161,8 +29154,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="444" spans="1:22" ht="64.95" hidden="1" customHeight="1">
-      <c r="A444" s="85"/>
+    <row r="444" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
+      <c r="A444" s="98"/>
       <c r="B444" s="71" t="s">
         <v>938</v>
       </c>
@@ -29215,7 +29208,7 @@
       </c>
     </row>
     <row r="445" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="85"/>
+      <c r="A445" s="98"/>
       <c r="B445" s="71" t="s">
         <v>938</v>
       </c>
@@ -29266,7 +29259,7 @@
       </c>
     </row>
     <row r="446" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="85"/>
+      <c r="A446" s="98"/>
       <c r="B446" s="71" t="s">
         <v>938</v>
       </c>
@@ -29304,7 +29297,7 @@
       <c r="V446" s="71"/>
     </row>
     <row r="447" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="86"/>
+      <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
         <v>938</v>
       </c>
@@ -29359,7 +29352,7 @@
       <c r="V447" s="44"/>
     </row>
     <row r="448" spans="1:22" ht="27.6" hidden="1">
-      <c r="A448" s="84"/>
+      <c r="A448" s="87"/>
       <c r="B448" s="71" t="s">
         <v>948</v>
       </c>
@@ -29415,8 +29408,8 @@
         <v>951</v>
       </c>
     </row>
-    <row r="449" spans="1:22" ht="41.4" hidden="1">
-      <c r="A449" s="84"/>
+    <row r="449" spans="1:22" ht="41.45" hidden="1">
+      <c r="A449" s="87"/>
       <c r="B449" s="51" t="s">
         <v>948</v>
       </c>
@@ -29477,7 +29470,7 @@
       </c>
     </row>
     <row r="450" spans="1:22" ht="27.6" hidden="1">
-      <c r="A450" s="90">
+      <c r="A450" s="93">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29534,7 +29527,7 @@
       </c>
     </row>
     <row r="451" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="85"/>
+      <c r="A451" s="98"/>
       <c r="B451" s="71" t="s">
         <v>955</v>
       </c>
@@ -29589,7 +29582,7 @@
       </c>
     </row>
     <row r="452" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="85"/>
+      <c r="A452" s="98"/>
       <c r="B452" s="71" t="s">
         <v>955</v>
       </c>
@@ -29648,7 +29641,7 @@
       </c>
     </row>
     <row r="453" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="86"/>
+      <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
         <v>955</v>
       </c>
@@ -29703,7 +29696,7 @@
       </c>
     </row>
     <row r="454" spans="1:22" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="84">
+      <c r="A454" s="87">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29764,8 +29757,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="455" spans="1:22" ht="13.8" hidden="1">
-      <c r="A455" s="84"/>
+    <row r="455" spans="1:22" ht="13.9" hidden="1">
+      <c r="A455" s="87"/>
       <c r="B455" s="71" t="s">
         <v>962</v>
       </c>
@@ -29821,7 +29814,7 @@
       <c r="V455" s="71"/>
     </row>
     <row r="456" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="84"/>
+      <c r="A456" s="87"/>
       <c r="B456" s="71" t="s">
         <v>962</v>
       </c>
@@ -29879,7 +29872,7 @@
       <c r="V456" s="71"/>
     </row>
     <row r="457" spans="1:22" ht="27.6" hidden="1">
-      <c r="A457" s="84">
+      <c r="A457" s="87">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29932,8 +29925,8 @@
         <v>593</v>
       </c>
     </row>
-    <row r="458" spans="1:22" ht="13.8" hidden="1">
-      <c r="A458" s="84"/>
+    <row r="458" spans="1:22" ht="13.9" hidden="1">
+      <c r="A458" s="87"/>
       <c r="B458" s="71" t="s">
         <v>966</v>
       </c>
@@ -29986,8 +29979,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="459" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A459" s="84"/>
+    <row r="459" spans="1:22" ht="37.9" hidden="1" customHeight="1">
+      <c r="A459" s="87"/>
       <c r="B459" s="71" t="s">
         <v>966</v>
       </c>
@@ -30041,8 +30034,8 @@
       </c>
       <c r="V459" s="66"/>
     </row>
-    <row r="460" spans="1:22" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A460" s="84"/>
+    <row r="460" spans="1:22" ht="37.9" hidden="1" customHeight="1">
+      <c r="A460" s="87"/>
       <c r="B460" s="71" t="s">
         <v>966</v>
       </c>
@@ -30091,7 +30084,7 @@
       <c r="V460" s="66"/>
     </row>
     <row r="461" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="84"/>
+      <c r="A461" s="87"/>
       <c r="B461" s="71" t="s">
         <v>966</v>
       </c>
@@ -30147,7 +30140,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="462" spans="1:22" ht="55.2" hidden="1">
+    <row r="462" spans="1:22" ht="55.15" hidden="1">
       <c r="A462" s="66"/>
       <c r="B462" s="71" t="s">
         <v>973</v>
@@ -30204,7 +30197,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="463" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="463" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A463" s="66"/>
       <c r="B463" s="71" t="s">
         <v>973</v>
@@ -30259,7 +30252,7 @@
       </c>
       <c r="V463" s="71"/>
     </row>
-    <row r="464" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="464" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A464" s="66"/>
       <c r="B464" s="71" t="s">
         <v>973</v>
@@ -30314,7 +30307,7 @@
       </c>
       <c r="V464" s="71"/>
     </row>
-    <row r="465" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="465" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A465" s="66"/>
       <c r="B465" s="71" t="s">
         <v>973</v>
@@ -30367,7 +30360,7 @@
       <c r="U465" s="80"/>
       <c r="V465" s="71"/>
     </row>
-    <row r="466" spans="1:22" ht="43.2" hidden="1" customHeight="1">
+    <row r="466" spans="1:22" ht="43.15" hidden="1" customHeight="1">
       <c r="A466" s="66"/>
       <c r="B466" s="71" t="s">
         <v>973</v>
@@ -30479,7 +30472,7 @@
       </c>
     </row>
     <row r="468" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="85"/>
+      <c r="A468" s="98"/>
       <c r="B468" s="71" t="s">
         <v>983</v>
       </c>
@@ -30531,7 +30524,7 @@
       </c>
     </row>
     <row r="469" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="85"/>
+      <c r="A469" s="98"/>
       <c r="B469" s="71" t="s">
         <v>327</v>
       </c>
@@ -30586,7 +30579,7 @@
       <c r="V469" s="71"/>
     </row>
     <row r="470" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="85"/>
+      <c r="A470" s="98"/>
       <c r="B470" s="71" t="s">
         <v>327</v>
       </c>
@@ -30641,7 +30634,7 @@
       <c r="V470" s="71"/>
     </row>
     <row r="471" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="85"/>
+      <c r="A471" s="98"/>
       <c r="B471" s="71" t="s">
         <v>327</v>
       </c>
@@ -30696,7 +30689,7 @@
       <c r="V471" s="71"/>
     </row>
     <row r="472" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="85"/>
+      <c r="A472" s="98"/>
       <c r="B472" s="71" t="s">
         <v>327</v>
       </c>
@@ -30753,7 +30746,7 @@
       </c>
     </row>
     <row r="473" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="85"/>
+      <c r="A473" s="98"/>
       <c r="B473" s="71" t="s">
         <v>327</v>
       </c>
@@ -30806,7 +30799,7 @@
       </c>
     </row>
     <row r="474" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="86"/>
+      <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
         <v>983</v>
       </c>
@@ -30857,7 +30850,7 @@
       </c>
     </row>
     <row r="475" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="84">
+      <c r="A475" s="87">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30869,7 +30862,7 @@
       <c r="D475" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E475" s="104">
+      <c r="E475" s="90">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30883,14 +30876,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="105">
+      <c r="K475" s="92">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="105">
+      <c r="L475" s="92">
         <v>0</v>
       </c>
-      <c r="M475" s="87">
+      <c r="M475" s="91">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30909,12 +30902,12 @@
       <c r="S475" s="66"/>
       <c r="T475" s="66"/>
       <c r="U475" s="71"/>
-      <c r="V475" s="89" t="s">
+      <c r="V475" s="88" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="476" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="84"/>
+      <c r="A476" s="87"/>
       <c r="B476" s="71" t="s">
         <v>995</v>
       </c>
@@ -30924,7 +30917,7 @@
       <c r="D476" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E476" s="104"/>
+      <c r="E476" s="90"/>
       <c r="F476" s="71" t="s">
         <v>177</v>
       </c>
@@ -30936,9 +30929,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="105"/>
-      <c r="L476" s="105"/>
-      <c r="M476" s="87"/>
+      <c r="K476" s="92"/>
+      <c r="L476" s="92"/>
+      <c r="M476" s="91"/>
       <c r="N476" s="71" t="s">
         <v>38</v>
       </c>
@@ -30955,10 +30948,10 @@
       <c r="S476" s="66"/>
       <c r="T476" s="66"/>
       <c r="U476" s="71"/>
-      <c r="V476" s="89"/>
+      <c r="V476" s="88"/>
     </row>
     <row r="477" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="84"/>
+      <c r="A477" s="87"/>
       <c r="B477" s="71" t="s">
         <v>995</v>
       </c>
@@ -31017,7 +31010,7 @@
       </c>
     </row>
     <row r="478" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="84"/>
+      <c r="A478" s="87"/>
       <c r="B478" s="71" t="s">
         <v>995</v>
       </c>
@@ -31295,7 +31288,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="483" spans="1:22" ht="35.4" hidden="1" customHeight="1">
+    <row r="483" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
       <c r="A483" s="66"/>
       <c r="B483" s="71" t="s">
         <v>1007</v>
@@ -31350,7 +31343,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="484" spans="1:22" ht="38.4" hidden="1" customHeight="1">
+    <row r="484" spans="1:22" ht="38.450000000000003" hidden="1" customHeight="1">
       <c r="A484" s="66"/>
       <c r="B484" s="71" t="s">
         <v>1007</v>
@@ -31460,7 +31453,7 @@
       <c r="V485" s="66"/>
     </row>
     <row r="486" spans="1:22" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="84">
+      <c r="A486" s="87">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31517,7 +31510,7 @@
       <c r="V486" s="71"/>
     </row>
     <row r="487" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="84"/>
+      <c r="A487" s="87"/>
       <c r="B487" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31570,7 +31563,7 @@
       </c>
     </row>
     <row r="488" spans="1:22" ht="96.6" hidden="1">
-      <c r="A488" s="84"/>
+      <c r="A488" s="87"/>
       <c r="B488" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31679,7 +31672,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="490" spans="1:22" ht="13.8" hidden="1">
+    <row r="490" spans="1:22" ht="13.9" hidden="1">
       <c r="A490" s="68">
         <v>122</v>
       </c>
@@ -31736,8 +31729,8 @@
       </c>
       <c r="V490" s="71"/>
     </row>
-    <row r="491" spans="1:22" ht="13.8" hidden="1">
-      <c r="A491" s="85"/>
+    <row r="491" spans="1:22" ht="13.9" hidden="1">
+      <c r="A491" s="98"/>
       <c r="B491" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31791,8 +31784,8 @@
       </c>
       <c r="V491" s="71"/>
     </row>
-    <row r="492" spans="1:22" ht="13.8" hidden="1">
-      <c r="A492" s="85"/>
+    <row r="492" spans="1:22" ht="13.9" hidden="1">
+      <c r="A492" s="98"/>
       <c r="B492" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31846,8 +31839,8 @@
       </c>
       <c r="V492" s="71"/>
     </row>
-    <row r="493" spans="1:22" ht="55.2" hidden="1">
-      <c r="A493" s="85"/>
+    <row r="493" spans="1:22" ht="55.15" hidden="1">
+      <c r="A493" s="98"/>
       <c r="B493" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31899,7 +31892,7 @@
       </c>
     </row>
     <row r="494" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="86"/>
+      <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31954,7 +31947,7 @@
       <c r="V494" s="71"/>
     </row>
     <row r="495" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="84">
+      <c r="A495" s="87">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -32013,7 +32006,7 @@
       </c>
     </row>
     <row r="496" spans="1:22" ht="27.6" hidden="1">
-      <c r="A496" s="84"/>
+      <c r="A496" s="87"/>
       <c r="B496" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32065,8 +32058,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="497" spans="1:22" ht="13.8" hidden="1">
-      <c r="A497" s="84"/>
+    <row r="497" spans="1:22" ht="13.9" hidden="1">
+      <c r="A497" s="87"/>
       <c r="B497" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32120,8 +32113,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="498" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A498" s="84"/>
+    <row r="498" spans="1:22" ht="40.15" hidden="1" customHeight="1">
+      <c r="A498" s="87"/>
       <c r="B498" s="71" t="s">
         <v>1034</v>
       </c>
@@ -32176,7 +32169,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="499" spans="1:22" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="499" spans="1:22" ht="40.15" hidden="1" customHeight="1">
       <c r="A499" s="66"/>
       <c r="B499" s="71" t="s">
         <v>1035</v>
@@ -32238,7 +32231,7 @@
       </c>
     </row>
     <row r="500" spans="1:22" ht="27.6" hidden="1">
-      <c r="A500" s="89">
+      <c r="A500" s="88">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -32299,8 +32292,8 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="501" spans="1:22" ht="13.8" hidden="1">
-      <c r="A501" s="89"/>
+    <row r="501" spans="1:22" ht="13.9" hidden="1">
+      <c r="A501" s="88"/>
       <c r="B501" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32352,7 +32345,7 @@
       <c r="V501" s="71"/>
     </row>
     <row r="502" spans="1:22" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="89"/>
+      <c r="A502" s="88"/>
       <c r="B502" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32408,8 +32401,8 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="503" spans="1:22" ht="41.4" hidden="1">
-      <c r="A503" s="84">
+    <row r="503" spans="1:22" ht="41.45" hidden="1">
+      <c r="A503" s="87">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -32471,8 +32464,8 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="504" spans="1:22" ht="13.8" hidden="1">
-      <c r="A504" s="84"/>
+    <row r="504" spans="1:22" ht="13.9" hidden="1">
+      <c r="A504" s="87"/>
       <c r="B504" s="71" t="s">
         <v>1043</v>
       </c>
@@ -32530,8 +32523,8 @@
       </c>
       <c r="V504" s="71"/>
     </row>
-    <row r="505" spans="1:22" ht="55.2" hidden="1">
-      <c r="A505" s="84"/>
+    <row r="505" spans="1:22" ht="55.15" hidden="1">
+      <c r="A505" s="87"/>
       <c r="B505" s="51" t="s">
         <v>1043</v>
       </c>
@@ -32589,12 +32582,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="506" spans="1:22" ht="55.95" hidden="1" customHeight="1">
+    <row r="506" spans="1:22" ht="55.9" hidden="1" customHeight="1">
       <c r="K506" s="27"/>
       <c r="M506" s="56"/>
       <c r="U506" s="57"/>
     </row>
-    <row r="507" spans="1:22" ht="13.8" hidden="1">
+    <row r="507" spans="1:22" ht="13.9" hidden="1">
       <c r="E507" s="55" t="s">
         <v>715</v>
       </c>
@@ -32604,11 +32597,11 @@
     <row r="508" spans="1:22" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>2.35</v>
+        <v>85.550000000000011</v>
       </c>
       <c r="K508" s="8">
         <f>SUBTOTAL(9,K96:K507)</f>
-        <v>48324835349.090004</v>
+        <v>23837759611</v>
       </c>
       <c r="M508" s="58"/>
       <c r="U508" s="29"/>
@@ -32666,88 +32659,48 @@
   <autoFilter ref="A2:V507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Heliconia"/>
+        <filter val="Donmatías"/>
+        <filter val="Fredonia"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="V91:V92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="V475:V476"/>
-    <mergeCell ref="V434:V435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="A319:A320"/>
+    <mergeCell ref="A321:A330"/>
+    <mergeCell ref="A335:A338"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="A342:A348"/>
+    <mergeCell ref="A503:A505"/>
+    <mergeCell ref="A468:A474"/>
+    <mergeCell ref="A475:A478"/>
+    <mergeCell ref="A486:A488"/>
+    <mergeCell ref="A491:A494"/>
+    <mergeCell ref="A495:A498"/>
+    <mergeCell ref="A500:A502"/>
+    <mergeCell ref="A440:A447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="A450:A453"/>
+    <mergeCell ref="A454:A456"/>
+    <mergeCell ref="A457:A461"/>
+    <mergeCell ref="A349:A351"/>
+    <mergeCell ref="A352:A357"/>
+    <mergeCell ref="A363:A364"/>
+    <mergeCell ref="A368:A372"/>
+    <mergeCell ref="A373:A384"/>
+    <mergeCell ref="A385:A392"/>
+    <mergeCell ref="A394:A399"/>
     <mergeCell ref="A400:A405"/>
     <mergeCell ref="A406:A407"/>
     <mergeCell ref="P310:P311"/>
@@ -32772,42 +32725,83 @@
     <mergeCell ref="P312:P313"/>
     <mergeCell ref="V312:V313"/>
     <mergeCell ref="U312:U313"/>
-    <mergeCell ref="A319:A320"/>
-    <mergeCell ref="A321:A330"/>
-    <mergeCell ref="A335:A338"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="A342:A348"/>
-    <mergeCell ref="A503:A505"/>
-    <mergeCell ref="A468:A474"/>
-    <mergeCell ref="A475:A478"/>
-    <mergeCell ref="A486:A488"/>
-    <mergeCell ref="A491:A494"/>
-    <mergeCell ref="A495:A498"/>
-    <mergeCell ref="A500:A502"/>
-    <mergeCell ref="A440:A447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="A450:A453"/>
-    <mergeCell ref="A454:A456"/>
-    <mergeCell ref="A457:A461"/>
-    <mergeCell ref="A349:A351"/>
-    <mergeCell ref="A352:A357"/>
-    <mergeCell ref="A363:A364"/>
-    <mergeCell ref="A368:A372"/>
-    <mergeCell ref="A373:A384"/>
-    <mergeCell ref="A385:A392"/>
-    <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="V91:V92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="V475:V476"/>
+    <mergeCell ref="V434:V435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -32821,20 +32815,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE741C3-3798-4F4E-8B25-FDCA2ADDEF39}">
   <dimension ref="B2:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="12"/>
-    <col min="2" max="2" width="15.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
     <col min="5" max="5" width="19" style="20" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="12"/>
-    <col min="11" max="11" width="9.33203125" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="12"/>
+    <col min="6" max="6" width="9.5703125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="12"/>
+    <col min="11" max="11" width="9.28515625" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="27.6">
@@ -33048,20 +33042,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -33221,37 +33215,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}"/>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7EEC1C-A430-44AF-82CE-A6CCEA0E700D}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E09D708E-6A9C-4F01-ADCA-22234588999B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4493,49 +4493,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4550,14 +4526,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4916,10 +4916,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="13.9" hidden="1">
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="97"/>
+      <c r="C1" s="99"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -5008,7 +5008,7 @@
       <c r="X2" s="13"/>
     </row>
     <row r="3" spans="1:24" ht="62.45" hidden="1" customHeight="1">
-      <c r="A3" s="94">
+      <c r="A3" s="86">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5072,7 +5072,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="62.45" hidden="1" customHeight="1">
-      <c r="A4" s="94"/>
+      <c r="A4" s="86"/>
       <c r="B4" s="71" t="s">
         <v>22</v>
       </c>
@@ -5134,7 +5134,7 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="41.45" hidden="1">
-      <c r="A5" s="94"/>
+      <c r="A5" s="86"/>
       <c r="B5" s="66" t="s">
         <v>22</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="V6" s="66"/>
     </row>
     <row r="7" spans="1:24" ht="13.9" hidden="1">
-      <c r="A7" s="93">
+      <c r="A7" s="90">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5280,7 +5280,7 @@
       <c r="V7" s="66"/>
     </row>
     <row r="8" spans="1:24" ht="13.9" hidden="1">
-      <c r="A8" s="98"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="71" t="s">
         <v>41</v>
       </c>
@@ -5333,7 +5333,7 @@
       <c r="V8" s="66"/>
     </row>
     <row r="9" spans="1:24" ht="41.45" hidden="1">
-      <c r="A9" s="98"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="71" t="s">
         <v>41</v>
       </c>
@@ -5392,7 +5392,7 @@
       <c r="V9" s="66"/>
     </row>
     <row r="10" spans="1:24" ht="41.45" hidden="1">
-      <c r="A10" s="94"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="66" t="s">
         <v>41</v>
       </c>
@@ -5451,7 +5451,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" ht="27.6" hidden="1">
-      <c r="A11" s="87">
+      <c r="A11" s="84">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5515,7 +5515,7 @@
       </c>
     </row>
     <row r="12" spans="1:24" ht="52.9" hidden="1" customHeight="1">
-      <c r="A12" s="87"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="71" t="s">
         <v>59</v>
       </c>
@@ -5572,7 +5572,7 @@
       <c r="V12" s="76"/>
     </row>
     <row r="13" spans="1:24" ht="13.9" hidden="1">
-      <c r="A13" s="87"/>
+      <c r="A13" s="84"/>
       <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
@@ -5629,7 +5629,7 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="13.9" hidden="1">
-      <c r="A14" s="87"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="71" t="s">
         <v>59</v>
       </c>
@@ -5686,7 +5686,7 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="13.9" hidden="1">
-      <c r="A15" s="87"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="71" t="s">
         <v>59</v>
       </c>
@@ -5743,7 +5743,7 @@
       <c r="V15" s="66"/>
     </row>
     <row r="16" spans="1:24" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="87"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="71" t="s">
         <v>59</v>
       </c>
@@ -5964,7 +5964,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="97.9" hidden="1" customHeight="1">
-      <c r="A20" s="87">
+      <c r="A20" s="84">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6027,7 +6027,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A21" s="87"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="71" t="s">
         <v>92</v>
       </c>
@@ -6086,7 +6086,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="27.6" hidden="1">
-      <c r="A22" s="87"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="71" t="s">
         <v>92</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="13.9" hidden="1">
-      <c r="A23" s="87"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="71" t="s">
         <v>92</v>
       </c>
@@ -6204,7 +6204,7 @@
       <c r="V23" s="71"/>
     </row>
     <row r="24" spans="1:22" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="87">
+      <c r="A24" s="84">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6266,7 +6266,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" ht="13.9" hidden="1">
-      <c r="A25" s="87"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="71" t="s">
         <v>109</v>
       </c>
@@ -6323,7 +6323,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="70.150000000000006" hidden="1" customHeight="1">
-      <c r="A26" s="87"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="71" t="s">
         <v>109</v>
       </c>
@@ -6380,7 +6380,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A27" s="87"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="71" t="s">
         <v>109</v>
       </c>
@@ -6439,7 +6439,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="13.9" hidden="1">
-      <c r="A28" s="87"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="71" t="s">
         <v>109</v>
       </c>
@@ -6494,7 +6494,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="87"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="71" t="s">
         <v>109</v>
       </c>
@@ -6551,7 +6551,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A30" s="87"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="71" t="s">
         <v>109</v>
       </c>
@@ -6604,7 +6604,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A31" s="87"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="71" t="s">
         <v>109</v>
       </c>
@@ -6663,7 +6663,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A32" s="87"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="71" t="s">
         <v>109</v>
       </c>
@@ -6724,7 +6724,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A33" s="87"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="71" t="s">
         <v>109</v>
       </c>
@@ -6781,7 +6781,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A34" s="87"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="71" t="s">
         <v>109</v>
       </c>
@@ -6842,7 +6842,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="13.9" hidden="1">
-      <c r="A35" s="98"/>
+      <c r="A35" s="85"/>
       <c r="B35" s="71" t="s">
         <v>147</v>
       </c>
@@ -6878,7 +6878,7 @@
       <c r="V35" s="71"/>
     </row>
     <row r="36" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A36" s="94"/>
+      <c r="A36" s="86"/>
       <c r="B36" s="71" t="s">
         <v>147</v>
       </c>
@@ -6992,7 +6992,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A38" s="87">
+      <c r="A38" s="84">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7054,7 +7054,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A39" s="87"/>
+      <c r="A39" s="84"/>
       <c r="B39" s="71" t="s">
         <v>150</v>
       </c>
@@ -7115,7 +7115,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A40" s="87"/>
+      <c r="A40" s="84"/>
       <c r="B40" s="71" t="s">
         <v>150</v>
       </c>
@@ -7173,7 +7173,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A41" s="87">
+      <c r="A41" s="84">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7234,7 +7234,7 @@
       <c r="V41" s="71"/>
     </row>
     <row r="42" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A42" s="87"/>
+      <c r="A42" s="84"/>
       <c r="B42" s="71" t="s">
         <v>160</v>
       </c>
@@ -7284,7 +7284,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="87"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="71" t="s">
         <v>160</v>
       </c>
@@ -7336,7 +7336,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="87"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="71" t="s">
         <v>160</v>
       </c>
@@ -7385,7 +7385,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="27.6" hidden="1">
-      <c r="A45" s="87"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="71" t="s">
         <v>160</v>
       </c>
@@ -7442,7 +7442,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A46" s="87">
+      <c r="A46" s="84">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7499,7 +7499,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="13.9" hidden="1">
-      <c r="A47" s="93"/>
+      <c r="A47" s="90"/>
       <c r="B47" s="71" t="s">
         <v>175</v>
       </c>
@@ -7554,7 +7554,7 @@
       <c r="V47" s="71"/>
     </row>
     <row r="48" spans="1:22" ht="13.9" hidden="1">
-      <c r="A48" s="87"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="71" t="s">
         <v>182</v>
       </c>
@@ -7590,7 +7590,7 @@
       <c r="V48" s="71"/>
     </row>
     <row r="49" spans="1:22" ht="13.9" hidden="1">
-      <c r="A49" s="87"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="71" t="s">
         <v>182</v>
       </c>
@@ -7630,7 +7630,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" ht="13.9" hidden="1">
-      <c r="A50" s="87"/>
+      <c r="A50" s="84"/>
       <c r="B50" s="71" t="s">
         <v>182</v>
       </c>
@@ -7685,7 +7685,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" ht="55.15" hidden="1">
-      <c r="A51" s="87"/>
+      <c r="A51" s="84"/>
       <c r="B51" s="71" t="s">
         <v>182</v>
       </c>
@@ -7740,7 +7740,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="41.45" hidden="1">
-      <c r="A52" s="87"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="71" t="s">
         <v>182</v>
       </c>
@@ -7795,7 +7795,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="87"/>
+      <c r="A53" s="84"/>
       <c r="B53" s="71" t="s">
         <v>182</v>
       </c>
@@ -7850,7 +7850,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A54" s="87"/>
+      <c r="A54" s="84"/>
       <c r="B54" s="71" t="s">
         <v>197</v>
       </c>
@@ -7904,7 +7904,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A55" s="87"/>
+      <c r="A55" s="84"/>
       <c r="B55" s="71" t="s">
         <v>197</v>
       </c>
@@ -7959,7 +7959,7 @@
       <c r="V55" s="66"/>
     </row>
     <row r="56" spans="1:22" ht="41.45" hidden="1">
-      <c r="A56" s="87"/>
+      <c r="A56" s="84"/>
       <c r="B56" s="71" t="s">
         <v>197</v>
       </c>
@@ -8018,7 +8018,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A57" s="87"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="71" t="s">
         <v>197</v>
       </c>
@@ -8075,7 +8075,7 @@
       <c r="V57" s="71"/>
     </row>
     <row r="58" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A58" s="87"/>
+      <c r="A58" s="84"/>
       <c r="B58" s="71" t="s">
         <v>197</v>
       </c>
@@ -8135,7 +8135,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A59" s="94"/>
+      <c r="A59" s="86"/>
       <c r="B59" s="71" t="s">
         <v>209</v>
       </c>
@@ -8192,7 +8192,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A60" s="94"/>
+      <c r="A60" s="86"/>
       <c r="B60" s="71" t="s">
         <v>209</v>
       </c>
@@ -8248,7 +8248,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" ht="41.45" hidden="1">
-      <c r="A61" s="87"/>
+      <c r="A61" s="84"/>
       <c r="B61" s="61" t="s">
         <v>209</v>
       </c>
@@ -8302,7 +8302,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="93">
+      <c r="A62" s="90">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8360,7 +8360,7 @@
       </c>
     </row>
     <row r="63" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="98"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="71" t="s">
         <v>215</v>
       </c>
@@ -8417,7 +8417,7 @@
       </c>
     </row>
     <row r="64" spans="1:22" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="94"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="71" t="s">
         <v>215</v>
       </c>
@@ -8582,7 +8582,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="93">
+      <c r="A67" s="90">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8638,7 +8638,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" ht="13.9" hidden="1">
-      <c r="A68" s="94"/>
+      <c r="A68" s="86"/>
       <c r="B68" s="71" t="s">
         <v>230</v>
       </c>
@@ -8691,7 +8691,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="93">
+      <c r="A69" s="90">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8747,7 +8747,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" ht="41.45" hidden="1">
-      <c r="A70" s="98"/>
+      <c r="A70" s="85"/>
       <c r="B70" s="71" t="s">
         <v>236</v>
       </c>
@@ -8802,7 +8802,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" ht="67.900000000000006" hidden="1" customHeight="1">
-      <c r="A71" s="98"/>
+      <c r="A71" s="85"/>
       <c r="B71" s="71" t="s">
         <v>242</v>
       </c>
@@ -8857,7 +8857,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="98"/>
+      <c r="A72" s="85"/>
       <c r="B72" s="71" t="s">
         <v>245</v>
       </c>
@@ -8913,7 +8913,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A73" s="98"/>
+      <c r="A73" s="85"/>
       <c r="B73" s="71" t="s">
         <v>245</v>
       </c>
@@ -8966,7 +8966,7 @@
       </c>
     </row>
     <row r="74" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A74" s="98"/>
+      <c r="A74" s="85"/>
       <c r="B74" s="71" t="s">
         <v>245</v>
       </c>
@@ -9021,7 +9021,7 @@
       </c>
     </row>
     <row r="75" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A75" s="98"/>
+      <c r="A75" s="85"/>
       <c r="B75" s="71" t="s">
         <v>245</v>
       </c>
@@ -9082,7 +9082,7 @@
       </c>
     </row>
     <row r="76" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A76" s="98"/>
+      <c r="A76" s="85"/>
       <c r="B76" s="71" t="s">
         <v>245</v>
       </c>
@@ -9135,7 +9135,7 @@
       <c r="V76" s="71"/>
     </row>
     <row r="77" spans="1:22" ht="13.9" hidden="1">
-      <c r="A77" s="94"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="71" t="s">
         <v>245</v>
       </c>
@@ -9192,7 +9192,7 @@
       </c>
     </row>
     <row r="78" spans="1:22" ht="20.45" hidden="1" customHeight="1">
-      <c r="A78" s="98"/>
+      <c r="A78" s="85"/>
       <c r="B78" s="71" t="s">
         <v>256</v>
       </c>
@@ -9253,7 +9253,7 @@
       </c>
     </row>
     <row r="79" spans="1:22" ht="13.9" hidden="1">
-      <c r="A79" s="98"/>
+      <c r="A79" s="85"/>
       <c r="B79" s="71" t="s">
         <v>256</v>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="V79" s="66"/>
     </row>
     <row r="80" spans="1:22" ht="13.9" hidden="1">
-      <c r="A80" s="98"/>
+      <c r="A80" s="85"/>
       <c r="B80" s="71" t="s">
         <v>256</v>
       </c>
@@ -9363,7 +9363,7 @@
       <c r="V80" s="66"/>
     </row>
     <row r="81" spans="1:23" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="98"/>
+      <c r="A81" s="85"/>
       <c r="B81" s="71" t="s">
         <v>256</v>
       </c>
@@ -9419,7 +9419,7 @@
       </c>
     </row>
     <row r="82" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A82" s="98"/>
+      <c r="A82" s="85"/>
       <c r="B82" s="71" t="s">
         <v>265</v>
       </c>
@@ -9477,7 +9477,7 @@
       <c r="W82" s="33"/>
     </row>
     <row r="83" spans="1:23" ht="38.450000000000003" hidden="1" customHeight="1">
-      <c r="A83" s="98"/>
+      <c r="A83" s="85"/>
       <c r="B83" s="71" t="s">
         <v>265</v>
       </c>
@@ -9532,7 +9532,7 @@
       <c r="W83" s="33"/>
     </row>
     <row r="84" spans="1:23" ht="27.6" hidden="1">
-      <c r="A84" s="98"/>
+      <c r="A84" s="85"/>
       <c r="B84" s="71" t="s">
         <v>265</v>
       </c>
@@ -9587,7 +9587,7 @@
       </c>
     </row>
     <row r="85" spans="1:23" ht="55.15" hidden="1">
-      <c r="A85" s="98"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="71" t="s">
         <v>265</v>
       </c>
@@ -9641,7 +9641,7 @@
       <c r="W85" s="33"/>
     </row>
     <row r="86" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A86" s="98"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="71" t="s">
         <v>265</v>
       </c>
@@ -9699,7 +9699,7 @@
       <c r="W86" s="33"/>
     </row>
     <row r="87" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A87" s="98"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="71" t="s">
         <v>265</v>
       </c>
@@ -9757,7 +9757,7 @@
       <c r="W87" s="33"/>
     </row>
     <row r="88" spans="1:23" ht="13.9" hidden="1">
-      <c r="A88" s="98"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="71" t="s">
         <v>265</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="W88" s="33"/>
     </row>
     <row r="89" spans="1:23" ht="13.9" hidden="1">
-      <c r="A89" s="98"/>
+      <c r="A89" s="85"/>
       <c r="B89" s="71" t="s">
         <v>265</v>
       </c>
@@ -9871,7 +9871,7 @@
       <c r="W89" s="33"/>
     </row>
     <row r="90" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="98"/>
+      <c r="A90" s="85"/>
       <c r="B90" s="66" t="s">
         <v>265</v>
       </c>
@@ -9921,7 +9921,7 @@
       <c r="W90" s="33"/>
     </row>
     <row r="91" spans="1:23" ht="43.9" hidden="1" customHeight="1">
-      <c r="A91" s="98"/>
+      <c r="A91" s="85"/>
       <c r="B91" s="71" t="s">
         <v>285</v>
       </c>
@@ -9945,36 +9945,36 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="84"/>
-      <c r="L91" s="84">
+      <c r="K91" s="100"/>
+      <c r="L91" s="100">
         <v>0</v>
       </c>
-      <c r="M91" s="84"/>
-      <c r="N91" s="87" t="s">
+      <c r="M91" s="100"/>
+      <c r="N91" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="O91" s="87" t="s">
+      <c r="O91" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="P91" s="87">
+      <c r="P91" s="84">
         <v>2026</v>
       </c>
-      <c r="Q91" s="88" t="s">
+      <c r="Q91" s="89" t="s">
         <v>131</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
       <c r="T91" s="71"/>
-      <c r="U91" s="89">
+      <c r="U91" s="103">
         <v>0</v>
       </c>
-      <c r="V91" s="88" t="s">
+      <c r="V91" s="89" t="s">
         <v>288</v>
       </c>
       <c r="W91" s="33"/>
     </row>
     <row r="92" spans="1:23" ht="40.9" hidden="1" customHeight="1">
-      <c r="A92" s="98"/>
+      <c r="A92" s="85"/>
       <c r="B92" s="71" t="s">
         <v>285</v>
       </c>
@@ -9998,21 +9998,21 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="85"/>
-      <c r="L92" s="85"/>
-      <c r="M92" s="85"/>
-      <c r="N92" s="87"/>
-      <c r="O92" s="87"/>
-      <c r="P92" s="87"/>
-      <c r="Q92" s="88"/>
+      <c r="K92" s="101"/>
+      <c r="L92" s="101"/>
+      <c r="M92" s="101"/>
+      <c r="N92" s="84"/>
+      <c r="O92" s="84"/>
+      <c r="P92" s="84"/>
+      <c r="Q92" s="89"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
       <c r="T92" s="71"/>
-      <c r="U92" s="89"/>
-      <c r="V92" s="88"/>
+      <c r="U92" s="103"/>
+      <c r="V92" s="89"/>
     </row>
     <row r="93" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="98"/>
+      <c r="A93" s="85"/>
       <c r="B93" s="71" t="s">
         <v>285</v>
       </c>
@@ -10036,9 +10036,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="85"/>
-      <c r="L93" s="85"/>
-      <c r="M93" s="85"/>
+      <c r="K93" s="101"/>
+      <c r="L93" s="101"/>
+      <c r="M93" s="101"/>
       <c r="N93" s="66" t="s">
         <v>29</v>
       </c>
@@ -10062,7 +10062,7 @@
       </c>
     </row>
     <row r="94" spans="1:23" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="98"/>
+      <c r="A94" s="85"/>
       <c r="B94" s="71" t="s">
         <v>285</v>
       </c>
@@ -10084,9 +10084,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="85"/>
-      <c r="L94" s="85"/>
-      <c r="M94" s="85"/>
+      <c r="K94" s="101"/>
+      <c r="L94" s="101"/>
+      <c r="M94" s="101"/>
       <c r="N94" s="66" t="s">
         <v>29</v>
       </c>
@@ -10110,7 +10110,7 @@
       </c>
     </row>
     <row r="95" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A95" s="98"/>
+      <c r="A95" s="85"/>
       <c r="B95" s="71" t="s">
         <v>285</v>
       </c>
@@ -10134,9 +10134,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="85"/>
-      <c r="L95" s="85"/>
-      <c r="M95" s="85"/>
+      <c r="K95" s="101"/>
+      <c r="L95" s="101"/>
+      <c r="M95" s="101"/>
       <c r="N95" s="66" t="s">
         <v>149</v>
       </c>
@@ -10160,7 +10160,7 @@
       </c>
     </row>
     <row r="96" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A96" s="98"/>
+      <c r="A96" s="85"/>
       <c r="B96" s="71" t="s">
         <v>293</v>
       </c>
@@ -10180,9 +10180,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="85"/>
-      <c r="L96" s="85"/>
-      <c r="M96" s="85"/>
+      <c r="K96" s="101"/>
+      <c r="L96" s="101"/>
+      <c r="M96" s="101"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10194,7 +10194,7 @@
       <c r="V96" s="66"/>
     </row>
     <row r="97" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A97" s="98"/>
+      <c r="A97" s="85"/>
       <c r="B97" s="71" t="s">
         <v>293</v>
       </c>
@@ -10222,9 +10222,9 @@
       <c r="J97" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="K97" s="85"/>
-      <c r="L97" s="85"/>
-      <c r="M97" s="85"/>
+      <c r="K97" s="101"/>
+      <c r="L97" s="101"/>
+      <c r="M97" s="101"/>
       <c r="N97" s="66" t="s">
         <v>29</v>
       </c>
@@ -10246,7 +10246,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="98"/>
+      <c r="A98" s="85"/>
       <c r="B98" s="71" t="s">
         <v>293</v>
       </c>
@@ -10274,9 +10274,9 @@
       <c r="J98" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="K98" s="85"/>
-      <c r="L98" s="85"/>
-      <c r="M98" s="85"/>
+      <c r="K98" s="101"/>
+      <c r="L98" s="101"/>
+      <c r="M98" s="101"/>
       <c r="N98" s="66" t="s">
         <v>101</v>
       </c>
@@ -10300,7 +10300,7 @@
       </c>
     </row>
     <row r="99" spans="1:22" ht="17.45" hidden="1" customHeight="1">
-      <c r="A99" s="98"/>
+      <c r="A99" s="85"/>
       <c r="B99" s="71" t="s">
         <v>302</v>
       </c>
@@ -10324,9 +10324,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="85"/>
-      <c r="L99" s="85"/>
-      <c r="M99" s="85"/>
+      <c r="K99" s="101"/>
+      <c r="L99" s="101"/>
+      <c r="M99" s="101"/>
       <c r="N99" s="66" t="s">
         <v>149</v>
       </c>
@@ -10350,7 +10350,7 @@
       </c>
     </row>
     <row r="100" spans="1:22" ht="17.45" hidden="1" customHeight="1">
-      <c r="A100" s="98"/>
+      <c r="A100" s="85"/>
       <c r="B100" s="71" t="s">
         <v>302</v>
       </c>
@@ -10374,9 +10374,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="85"/>
-      <c r="L100" s="85"/>
-      <c r="M100" s="85"/>
+      <c r="K100" s="101"/>
+      <c r="L100" s="101"/>
+      <c r="M100" s="101"/>
       <c r="N100" s="66" t="s">
         <v>75</v>
       </c>
@@ -10400,7 +10400,7 @@
       </c>
     </row>
     <row r="101" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A101" s="98"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="71" t="s">
         <v>302</v>
       </c>
@@ -10424,9 +10424,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="86"/>
-      <c r="L101" s="86"/>
-      <c r="M101" s="86"/>
+      <c r="K101" s="102"/>
+      <c r="L101" s="102"/>
+      <c r="M101" s="102"/>
       <c r="N101" s="66" t="s">
         <v>38</v>
       </c>
@@ -10450,7 +10450,7 @@
       </c>
     </row>
     <row r="102" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A102" s="98"/>
+      <c r="A102" s="85"/>
       <c r="B102" s="71" t="s">
         <v>302</v>
       </c>
@@ -10507,7 +10507,7 @@
       </c>
     </row>
     <row r="103" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A103" s="98"/>
+      <c r="A103" s="85"/>
       <c r="B103" s="71" t="s">
         <v>302</v>
       </c>
@@ -10559,7 +10559,7 @@
       </c>
     </row>
     <row r="104" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A104" s="98"/>
+      <c r="A104" s="85"/>
       <c r="B104" s="71" t="s">
         <v>302</v>
       </c>
@@ -10612,7 +10612,7 @@
       </c>
     </row>
     <row r="105" spans="1:22" ht="53.45" hidden="1" customHeight="1">
-      <c r="A105" s="98"/>
+      <c r="A105" s="85"/>
       <c r="B105" s="71" t="s">
         <v>302</v>
       </c>
@@ -10667,7 +10667,7 @@
       <c r="V105" s="66"/>
     </row>
     <row r="106" spans="1:22" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="98"/>
+      <c r="A106" s="85"/>
       <c r="B106" s="71" t="s">
         <v>302</v>
       </c>
@@ -10722,7 +10722,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" ht="96.6" hidden="1">
-      <c r="A107" s="98"/>
+      <c r="A107" s="85"/>
       <c r="B107" s="71" t="s">
         <v>314</v>
       </c>
@@ -10774,7 +10774,7 @@
       </c>
     </row>
     <row r="108" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A108" s="98"/>
+      <c r="A108" s="85"/>
       <c r="B108" s="71" t="s">
         <v>320</v>
       </c>
@@ -10820,7 +10820,7 @@
       </c>
     </row>
     <row r="109" spans="1:22" ht="13.9" hidden="1">
-      <c r="A109" s="98"/>
+      <c r="A109" s="85"/>
       <c r="B109" s="71" t="s">
         <v>320</v>
       </c>
@@ -10873,7 +10873,7 @@
       <c r="V109" s="66"/>
     </row>
     <row r="110" spans="1:22" ht="13.9" hidden="1">
-      <c r="A110" s="98"/>
+      <c r="A110" s="85"/>
       <c r="B110" s="71" t="s">
         <v>320</v>
       </c>
@@ -10928,7 +10928,7 @@
       <c r="V110" s="71"/>
     </row>
     <row r="111" spans="1:22" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="98"/>
+      <c r="A111" s="85"/>
       <c r="B111" s="71" t="s">
         <v>325</v>
       </c>
@@ -10987,7 +10987,7 @@
       <c r="V111" s="71"/>
     </row>
     <row r="112" spans="1:22" ht="13.9" hidden="1">
-      <c r="A112" s="98"/>
+      <c r="A112" s="85"/>
       <c r="B112" s="71" t="s">
         <v>327</v>
       </c>
@@ -11040,7 +11040,7 @@
       </c>
     </row>
     <row r="113" spans="1:22" ht="13.9" hidden="1">
-      <c r="A113" s="98"/>
+      <c r="A113" s="85"/>
       <c r="B113" s="71" t="s">
         <v>327</v>
       </c>
@@ -11093,7 +11093,7 @@
       </c>
     </row>
     <row r="114" spans="1:22" ht="41.45" hidden="1">
-      <c r="A114" s="98"/>
+      <c r="A114" s="85"/>
       <c r="B114" s="71" t="s">
         <v>327</v>
       </c>
@@ -11135,7 +11135,7 @@
       </c>
     </row>
     <row r="115" spans="1:22" ht="22.9" hidden="1" customHeight="1">
-      <c r="A115" s="98"/>
+      <c r="A115" s="85"/>
       <c r="B115" s="71" t="s">
         <v>327</v>
       </c>
@@ -11192,7 +11192,7 @@
       </c>
     </row>
     <row r="116" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A116" s="98"/>
+      <c r="A116" s="85"/>
       <c r="B116" s="71" t="s">
         <v>337</v>
       </c>
@@ -11253,7 +11253,7 @@
       </c>
     </row>
     <row r="117" spans="1:22" ht="55.15" hidden="1">
-      <c r="A117" s="94"/>
+      <c r="A117" s="86"/>
       <c r="B117" s="71" t="s">
         <v>342</v>
       </c>
@@ -11367,7 +11367,7 @@
       <c r="V118" s="71"/>
     </row>
     <row r="119" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="87">
+      <c r="A119" s="84">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11422,7 +11422,7 @@
       <c r="V119" s="71"/>
     </row>
     <row r="120" spans="1:22" ht="13.9" hidden="1">
-      <c r="A120" s="87"/>
+      <c r="A120" s="84"/>
       <c r="B120" s="71" t="s">
         <v>347</v>
       </c>
@@ -11477,7 +11477,7 @@
       <c r="V120" s="66"/>
     </row>
     <row r="121" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A121" s="103">
+      <c r="A121" s="98">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11533,7 +11533,7 @@
       </c>
     </row>
     <row r="122" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A122" s="88"/>
+      <c r="A122" s="89"/>
       <c r="B122" s="71" t="s">
         <v>350</v>
       </c>
@@ -11587,7 +11587,7 @@
       </c>
     </row>
     <row r="123" spans="1:22" ht="142.9" hidden="1" customHeight="1">
-      <c r="A123" s="88"/>
+      <c r="A123" s="89"/>
       <c r="B123" s="71" t="s">
         <v>350</v>
       </c>
@@ -11642,7 +11642,7 @@
       </c>
     </row>
     <row r="124" spans="1:22" ht="13.9" hidden="1">
-      <c r="A124" s="88"/>
+      <c r="A124" s="89"/>
       <c r="B124" s="71" t="s">
         <v>350</v>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="V132" s="66"/>
     </row>
     <row r="133" spans="1:22" ht="13.9" hidden="1">
-      <c r="A133" s="87">
+      <c r="A133" s="84">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12197,7 +12197,7 @@
       </c>
     </row>
     <row r="134" spans="1:22" ht="13.9" hidden="1">
-      <c r="A134" s="87"/>
+      <c r="A134" s="84"/>
       <c r="B134" s="71" t="s">
         <v>374</v>
       </c>
@@ -12252,7 +12252,7 @@
       <c r="V134" s="66"/>
     </row>
     <row r="135" spans="1:22" ht="41.45" hidden="1">
-      <c r="A135" s="87"/>
+      <c r="A135" s="84"/>
       <c r="B135" s="71" t="s">
         <v>374</v>
       </c>
@@ -12313,7 +12313,7 @@
       </c>
     </row>
     <row r="136" spans="1:22" ht="13.9" hidden="1">
-      <c r="A136" s="87"/>
+      <c r="A136" s="84"/>
       <c r="B136" s="71" t="s">
         <v>374</v>
       </c>
@@ -12428,7 +12428,7 @@
       <c r="V137" s="71"/>
     </row>
     <row r="138" spans="1:22" ht="13.9" hidden="1">
-      <c r="A138" s="87">
+      <c r="A138" s="84">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12485,7 +12485,7 @@
       <c r="V138" s="71"/>
     </row>
     <row r="139" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A139" s="87"/>
+      <c r="A139" s="84"/>
       <c r="B139" s="71" t="s">
         <v>383</v>
       </c>
@@ -12540,7 +12540,7 @@
       <c r="V139" s="71"/>
     </row>
     <row r="140" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A140" s="87"/>
+      <c r="A140" s="84"/>
       <c r="B140" s="71" t="s">
         <v>383</v>
       </c>
@@ -12595,7 +12595,7 @@
       <c r="V140" s="71"/>
     </row>
     <row r="141" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="87"/>
+      <c r="A141" s="84"/>
       <c r="B141" s="71" t="s">
         <v>383</v>
       </c>
@@ -12649,7 +12649,7 @@
       <c r="V141" s="71"/>
     </row>
     <row r="142" spans="1:22" ht="13.9" hidden="1">
-      <c r="A142" s="87"/>
+      <c r="A142" s="84"/>
       <c r="B142" s="71" t="s">
         <v>383</v>
       </c>
@@ -12704,7 +12704,7 @@
       <c r="V142" s="71"/>
     </row>
     <row r="143" spans="1:22" ht="13.9" hidden="1">
-      <c r="A143" s="87"/>
+      <c r="A143" s="84"/>
       <c r="B143" s="71" t="s">
         <v>383</v>
       </c>
@@ -12759,7 +12759,7 @@
       <c r="V143" s="66"/>
     </row>
     <row r="144" spans="1:22" ht="13.9" hidden="1">
-      <c r="A144" s="87"/>
+      <c r="A144" s="84"/>
       <c r="B144" s="71" t="s">
         <v>383</v>
       </c>
@@ -12814,7 +12814,7 @@
       <c r="V144" s="71"/>
     </row>
     <row r="145" spans="1:22" ht="13.9" hidden="1">
-      <c r="A145" s="87">
+      <c r="A145" s="84">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12873,7 +12873,7 @@
       </c>
     </row>
     <row r="146" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="87"/>
+      <c r="A146" s="84"/>
       <c r="B146" s="71" t="s">
         <v>399</v>
       </c>
@@ -12926,7 +12926,7 @@
       </c>
     </row>
     <row r="147" spans="1:22" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="87"/>
+      <c r="A147" s="84"/>
       <c r="B147" s="71" t="s">
         <v>399</v>
       </c>
@@ -13036,7 +13036,7 @@
       </c>
     </row>
     <row r="149" spans="1:22" ht="35.450000000000003" hidden="1" customHeight="1">
-      <c r="A149" s="98"/>
+      <c r="A149" s="85"/>
       <c r="B149" s="71" t="s">
         <v>404</v>
       </c>
@@ -13090,7 +13090,7 @@
       </c>
     </row>
     <row r="150" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A150" s="94"/>
+      <c r="A150" s="86"/>
       <c r="B150" s="71" t="s">
         <v>404</v>
       </c>
@@ -13260,7 +13260,7 @@
       </c>
     </row>
     <row r="153" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A153" s="93">
+      <c r="A153" s="90">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13319,7 +13319,7 @@
       </c>
     </row>
     <row r="154" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A154" s="98"/>
+      <c r="A154" s="85"/>
       <c r="B154" s="71" t="s">
         <v>415</v>
       </c>
@@ -13371,7 +13371,7 @@
       </c>
     </row>
     <row r="155" spans="1:22" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="98"/>
+      <c r="A155" s="85"/>
       <c r="B155" s="71" t="s">
         <v>415</v>
       </c>
@@ -13421,7 +13421,7 @@
       </c>
     </row>
     <row r="156" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A156" s="98"/>
+      <c r="A156" s="85"/>
       <c r="B156" s="71" t="s">
         <v>415</v>
       </c>
@@ -13473,7 +13473,7 @@
       </c>
     </row>
     <row r="157" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A157" s="98"/>
+      <c r="A157" s="85"/>
       <c r="B157" s="71" t="s">
         <v>415</v>
       </c>
@@ -13530,7 +13530,7 @@
       </c>
     </row>
     <row r="158" spans="1:22" ht="13.9" hidden="1">
-      <c r="A158" s="98"/>
+      <c r="A158" s="85"/>
       <c r="B158" s="71" t="s">
         <v>415</v>
       </c>
@@ -13587,7 +13587,7 @@
       </c>
     </row>
     <row r="159" spans="1:22" ht="13.9" hidden="1">
-      <c r="A159" s="98"/>
+      <c r="A159" s="85"/>
       <c r="B159" s="71" t="s">
         <v>415</v>
       </c>
@@ -13643,8 +13643,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="55.15">
-      <c r="A160" s="98"/>
+    <row r="160" spans="1:22" ht="55.15" hidden="1">
+      <c r="A160" s="85"/>
       <c r="B160" s="71" t="s">
         <v>429</v>
       </c>
@@ -13696,8 +13696,8 @@
       </c>
       <c r="V160" s="71"/>
     </row>
-    <row r="161" spans="1:22" ht="37.5">
-      <c r="A161" s="98"/>
+    <row r="161" spans="1:22" ht="37.5" hidden="1">
+      <c r="A161" s="85"/>
       <c r="B161" s="71" t="s">
         <v>429</v>
       </c>
@@ -13752,8 +13752,8 @@
       </c>
       <c r="V161" s="71"/>
     </row>
-    <row r="162" spans="1:22" ht="13.9">
-      <c r="A162" s="98"/>
+    <row r="162" spans="1:22" ht="13.9" hidden="1">
+      <c r="A162" s="85"/>
       <c r="B162" s="71" t="s">
         <v>429</v>
       </c>
@@ -13805,8 +13805,8 @@
       </c>
       <c r="V162" s="71"/>
     </row>
-    <row r="163" spans="1:22" ht="13.9">
-      <c r="A163" s="98"/>
+    <row r="163" spans="1:22" ht="13.9" hidden="1">
+      <c r="A163" s="85"/>
       <c r="B163" s="71" t="s">
         <v>429</v>
       </c>
@@ -13863,7 +13863,7 @@
       </c>
     </row>
     <row r="164" spans="1:22" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="94"/>
+      <c r="A164" s="86"/>
       <c r="B164" s="71" t="s">
         <v>437</v>
       </c>
@@ -13917,7 +13917,7 @@
       </c>
     </row>
     <row r="165" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A165" s="98"/>
+      <c r="A165" s="85"/>
       <c r="B165" s="71" t="s">
         <v>437</v>
       </c>
@@ -13971,7 +13971,7 @@
       </c>
     </row>
     <row r="166" spans="1:22" ht="13.9" hidden="1">
-      <c r="A166" s="94"/>
+      <c r="A166" s="86"/>
       <c r="B166" s="71" t="s">
         <v>437</v>
       </c>
@@ -14149,7 +14149,7 @@
       </c>
     </row>
     <row r="169" spans="1:22" ht="41.45" hidden="1">
-      <c r="A169" s="99">
+      <c r="A169" s="91">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14210,7 +14210,7 @@
       </c>
     </row>
     <row r="170" spans="1:22" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="100"/>
+      <c r="A170" s="92"/>
       <c r="B170" s="71" t="s">
         <v>451</v>
       </c>
@@ -14262,7 +14262,7 @@
       </c>
     </row>
     <row r="171" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A171" s="100"/>
+      <c r="A171" s="92"/>
       <c r="B171" s="71" t="s">
         <v>451</v>
       </c>
@@ -14321,7 +14321,7 @@
       </c>
     </row>
     <row r="172" spans="1:22" ht="13.9" hidden="1">
-      <c r="A172" s="100"/>
+      <c r="A172" s="92"/>
       <c r="B172" s="71" t="s">
         <v>451</v>
       </c>
@@ -14378,7 +14378,7 @@
       </c>
     </row>
     <row r="173" spans="1:22" ht="13.9" hidden="1">
-      <c r="A173" s="101"/>
+      <c r="A173" s="93"/>
       <c r="B173" s="71" t="s">
         <v>458</v>
       </c>
@@ -14435,7 +14435,7 @@
       </c>
     </row>
     <row r="174" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A174" s="87">
+      <c r="A174" s="84">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14493,7 +14493,7 @@
       </c>
     </row>
     <row r="175" spans="1:22" ht="13.9" hidden="1">
-      <c r="A175" s="87"/>
+      <c r="A175" s="84"/>
       <c r="B175" s="71" t="s">
         <v>460</v>
       </c>
@@ -14550,7 +14550,7 @@
       </c>
     </row>
     <row r="176" spans="1:22" ht="13.9" hidden="1">
-      <c r="A176" s="87"/>
+      <c r="A176" s="84"/>
       <c r="B176" s="71" t="s">
         <v>460</v>
       </c>
@@ -14605,7 +14605,7 @@
       <c r="V176" s="71"/>
     </row>
     <row r="177" spans="1:22" ht="13.9" hidden="1">
-      <c r="A177" s="87"/>
+      <c r="A177" s="84"/>
       <c r="B177" s="71" t="s">
         <v>460</v>
       </c>
@@ -14662,7 +14662,7 @@
       </c>
     </row>
     <row r="178" spans="1:22" ht="27.6" hidden="1">
-      <c r="A178" s="87"/>
+      <c r="A178" s="84"/>
       <c r="B178" s="71" t="s">
         <v>460</v>
       </c>
@@ -14717,7 +14717,7 @@
       <c r="V178" s="71"/>
     </row>
     <row r="179" spans="1:22" ht="13.9" hidden="1">
-      <c r="A179" s="87"/>
+      <c r="A179" s="84"/>
       <c r="B179" s="71" t="s">
         <v>468</v>
       </c>
@@ -14774,7 +14774,7 @@
       </c>
     </row>
     <row r="180" spans="1:22" ht="13.9" hidden="1">
-      <c r="A180" s="87"/>
+      <c r="A180" s="84"/>
       <c r="B180" s="71" t="s">
         <v>470</v>
       </c>
@@ -14938,7 +14938,7 @@
       <c r="V182" s="66"/>
     </row>
     <row r="183" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A183" s="102">
+      <c r="A183" s="94">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14993,7 +14993,7 @@
       </c>
     </row>
     <row r="184" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A184" s="102"/>
+      <c r="A184" s="94"/>
       <c r="B184" s="71" t="s">
         <v>473</v>
       </c>
@@ -15048,7 +15048,7 @@
       </c>
     </row>
     <row r="185" spans="1:22" ht="13.9" hidden="1">
-      <c r="A185" s="102"/>
+      <c r="A185" s="94"/>
       <c r="B185" s="71" t="s">
         <v>473</v>
       </c>
@@ -15164,7 +15164,7 @@
       </c>
     </row>
     <row r="187" spans="1:22" ht="13.9" hidden="1">
-      <c r="A187" s="100"/>
+      <c r="A187" s="92"/>
       <c r="B187" s="71" t="s">
         <v>485</v>
       </c>
@@ -15215,7 +15215,7 @@
       </c>
     </row>
     <row r="188" spans="1:22" ht="13.9" hidden="1">
-      <c r="A188" s="100"/>
+      <c r="A188" s="92"/>
       <c r="B188" s="71" t="s">
         <v>485</v>
       </c>
@@ -15268,7 +15268,7 @@
       <c r="V188" s="71"/>
     </row>
     <row r="189" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A189" s="101"/>
+      <c r="A189" s="93"/>
       <c r="B189" s="71" t="s">
         <v>485</v>
       </c>
@@ -15376,7 +15376,7 @@
       </c>
     </row>
     <row r="191" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
-      <c r="A191" s="87">
+      <c r="A191" s="84">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15432,7 +15432,7 @@
       </c>
     </row>
     <row r="192" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="87"/>
+      <c r="A192" s="84"/>
       <c r="B192" s="71" t="s">
         <v>492</v>
       </c>
@@ -15486,7 +15486,7 @@
       </c>
     </row>
     <row r="193" spans="1:22" ht="13.9" hidden="1">
-      <c r="A193" s="87"/>
+      <c r="A193" s="84"/>
       <c r="B193" s="71" t="s">
         <v>492</v>
       </c>
@@ -15572,8 +15572,8 @@
       <c r="U194" s="66"/>
       <c r="V194" s="66"/>
     </row>
-    <row r="195" spans="1:22" ht="13.9">
-      <c r="A195" s="98"/>
+    <row r="195" spans="1:22" ht="13.9" hidden="1">
+      <c r="A195" s="85"/>
       <c r="B195" s="71" t="s">
         <v>504</v>
       </c>
@@ -15627,8 +15627,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="196" spans="1:22" ht="24.6" customHeight="1">
-      <c r="A196" s="94"/>
+    <row r="196" spans="1:22" ht="24.6" hidden="1" customHeight="1">
+      <c r="A196" s="86"/>
       <c r="B196" s="71" t="s">
         <v>504</v>
       </c>
@@ -15683,7 +15683,7 @@
       </c>
     </row>
     <row r="197" spans="1:22" ht="13.9" hidden="1">
-      <c r="A197" s="87">
+      <c r="A197" s="84">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15739,7 +15739,7 @@
       </c>
     </row>
     <row r="198" spans="1:22" ht="13.9" hidden="1">
-      <c r="A198" s="87"/>
+      <c r="A198" s="84"/>
       <c r="B198" s="71" t="s">
         <v>508</v>
       </c>
@@ -15796,7 +15796,7 @@
       </c>
     </row>
     <row r="199" spans="1:22" ht="13.9" hidden="1">
-      <c r="A199" s="87"/>
+      <c r="A199" s="84"/>
       <c r="B199" s="71" t="s">
         <v>508</v>
       </c>
@@ -15853,7 +15853,7 @@
       </c>
     </row>
     <row r="200" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A200" s="87"/>
+      <c r="A200" s="84"/>
       <c r="B200" s="71" t="s">
         <v>508</v>
       </c>
@@ -16072,7 +16072,7 @@
       </c>
     </row>
     <row r="204" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A204" s="87">
+      <c r="A204" s="84">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -16130,7 +16130,7 @@
       </c>
     </row>
     <row r="205" spans="1:22" ht="55.15" hidden="1">
-      <c r="A205" s="87"/>
+      <c r="A205" s="84"/>
       <c r="B205" s="71" t="s">
         <v>520</v>
       </c>
@@ -16187,7 +16187,7 @@
       </c>
     </row>
     <row r="206" spans="1:22" ht="13.9" hidden="1">
-      <c r="A206" s="87"/>
+      <c r="A206" s="84"/>
       <c r="B206" s="66" t="s">
         <v>524</v>
       </c>
@@ -16244,7 +16244,7 @@
       </c>
     </row>
     <row r="207" spans="1:22" ht="13.9" hidden="1">
-      <c r="A207" s="87">
+      <c r="A207" s="84">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16301,7 +16301,7 @@
       </c>
     </row>
     <row r="208" spans="1:22" ht="13.9" hidden="1">
-      <c r="A208" s="87"/>
+      <c r="A208" s="84"/>
       <c r="B208" s="71" t="s">
         <v>527</v>
       </c>
@@ -16360,7 +16360,7 @@
       </c>
     </row>
     <row r="209" spans="1:22" ht="32.450000000000003" hidden="1" customHeight="1">
-      <c r="A209" s="87">
+      <c r="A209" s="84">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16418,7 +16418,7 @@
       </c>
     </row>
     <row r="210" spans="1:22" ht="13.9" hidden="1">
-      <c r="A210" s="87"/>
+      <c r="A210" s="84"/>
       <c r="B210" s="71" t="s">
         <v>530</v>
       </c>
@@ -16473,7 +16473,7 @@
       <c r="V210" s="71"/>
     </row>
     <row r="211" spans="1:22" ht="16.149999999999999" hidden="1" customHeight="1">
-      <c r="A211" s="87"/>
+      <c r="A211" s="84"/>
       <c r="B211" s="71" t="s">
         <v>530</v>
       </c>
@@ -16528,7 +16528,7 @@
       <c r="V211" s="66"/>
     </row>
     <row r="212" spans="1:22" ht="80.45" hidden="1" customHeight="1">
-      <c r="A212" s="87">
+      <c r="A212" s="84">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16584,7 +16584,7 @@
       </c>
     </row>
     <row r="213" spans="1:22" ht="13.9" hidden="1">
-      <c r="A213" s="87"/>
+      <c r="A213" s="84"/>
       <c r="B213" s="71" t="s">
         <v>539</v>
       </c>
@@ -16643,7 +16643,7 @@
       </c>
     </row>
     <row r="214" spans="1:22" ht="27.6" hidden="1">
-      <c r="A214" s="99">
+      <c r="A214" s="91">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16699,7 +16699,7 @@
       </c>
     </row>
     <row r="215" spans="1:22" ht="13.9" hidden="1">
-      <c r="A215" s="100"/>
+      <c r="A215" s="92"/>
       <c r="B215" s="71" t="s">
         <v>541</v>
       </c>
@@ -16756,7 +16756,7 @@
       </c>
     </row>
     <row r="216" spans="1:22" ht="13.9" hidden="1">
-      <c r="A216" s="100"/>
+      <c r="A216" s="92"/>
       <c r="B216" s="71" t="s">
         <v>541</v>
       </c>
@@ -16813,7 +16813,7 @@
       </c>
     </row>
     <row r="217" spans="1:22" ht="27.6" hidden="1">
-      <c r="A217" s="98"/>
+      <c r="A217" s="85"/>
       <c r="B217" s="71" t="s">
         <v>541</v>
       </c>
@@ -16869,7 +16869,7 @@
       </c>
     </row>
     <row r="218" spans="1:22" ht="13.9" hidden="1">
-      <c r="A218" s="101"/>
+      <c r="A218" s="93"/>
       <c r="B218" s="71" t="s">
         <v>541</v>
       </c>
@@ -17153,7 +17153,7 @@
       </c>
     </row>
     <row r="223" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A223" s="87">
+      <c r="A223" s="84">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17209,7 +17209,7 @@
       </c>
     </row>
     <row r="224" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A224" s="87"/>
+      <c r="A224" s="84"/>
       <c r="B224" s="71" t="s">
         <v>562</v>
       </c>
@@ -17266,7 +17266,7 @@
       </c>
     </row>
     <row r="225" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A225" s="87"/>
+      <c r="A225" s="84"/>
       <c r="B225" s="71" t="s">
         <v>562</v>
       </c>
@@ -17318,7 +17318,7 @@
       <c r="V225" s="71"/>
     </row>
     <row r="226" spans="1:22" ht="13.9" hidden="1">
-      <c r="A226" s="87"/>
+      <c r="A226" s="84"/>
       <c r="B226" s="71" t="s">
         <v>562</v>
       </c>
@@ -17375,7 +17375,7 @@
       </c>
     </row>
     <row r="227" spans="1:22" ht="27.6" hidden="1">
-      <c r="A227" s="87"/>
+      <c r="A227" s="84"/>
       <c r="B227" s="71" t="s">
         <v>562</v>
       </c>
@@ -17428,7 +17428,7 @@
       <c r="V227" s="66"/>
     </row>
     <row r="228" spans="1:22" ht="13.9" hidden="1">
-      <c r="A228" s="87"/>
+      <c r="A228" s="84"/>
       <c r="B228" s="71" t="s">
         <v>562</v>
       </c>
@@ -17793,7 +17793,7 @@
       </c>
     </row>
     <row r="235" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="93">
+      <c r="A235" s="90">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17848,7 +17848,7 @@
       </c>
     </row>
     <row r="236" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="98"/>
+      <c r="A236" s="85"/>
       <c r="B236" s="71" t="s">
         <v>583</v>
       </c>
@@ -17903,7 +17903,7 @@
       </c>
     </row>
     <row r="237" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="98"/>
+      <c r="A237" s="85"/>
       <c r="B237" s="71" t="s">
         <v>583</v>
       </c>
@@ -17958,7 +17958,7 @@
       </c>
     </row>
     <row r="238" spans="1:22" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="98"/>
+      <c r="A238" s="85"/>
       <c r="B238" s="71" t="s">
         <v>583</v>
       </c>
@@ -18014,7 +18014,7 @@
       </c>
     </row>
     <row r="239" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A239" s="98"/>
+      <c r="A239" s="85"/>
       <c r="B239" s="71" t="s">
         <v>583</v>
       </c>
@@ -18070,7 +18070,7 @@
       </c>
     </row>
     <row r="240" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A240" s="94"/>
+      <c r="A240" s="86"/>
       <c r="B240" s="71" t="s">
         <v>597</v>
       </c>
@@ -18123,7 +18123,7 @@
       </c>
     </row>
     <row r="241" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A241" s="87">
+      <c r="A241" s="84">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -18179,7 +18179,7 @@
       <c r="V241" s="71"/>
     </row>
     <row r="242" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A242" s="87"/>
+      <c r="A242" s="84"/>
       <c r="B242" s="71" t="s">
         <v>600</v>
       </c>
@@ -18234,7 +18234,7 @@
       </c>
     </row>
     <row r="243" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A243" s="87"/>
+      <c r="A243" s="84"/>
       <c r="B243" s="71" t="s">
         <v>600</v>
       </c>
@@ -18295,7 +18295,7 @@
       </c>
     </row>
     <row r="244" spans="1:22" ht="41.45" hidden="1">
-      <c r="A244" s="87"/>
+      <c r="A244" s="84"/>
       <c r="B244" s="71" t="s">
         <v>600</v>
       </c>
@@ -18348,7 +18348,7 @@
       </c>
     </row>
     <row r="245" spans="1:22" ht="13.9" hidden="1">
-      <c r="A245" s="87"/>
+      <c r="A245" s="84"/>
       <c r="B245" s="71" t="s">
         <v>600</v>
       </c>
@@ -18384,7 +18384,7 @@
       <c r="V245" s="71"/>
     </row>
     <row r="246" spans="1:22" ht="13.9" hidden="1">
-      <c r="A246" s="87"/>
+      <c r="A246" s="84"/>
       <c r="B246" s="71" t="s">
         <v>600</v>
       </c>
@@ -18437,7 +18437,7 @@
       </c>
     </row>
     <row r="247" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A247" s="87"/>
+      <c r="A247" s="84"/>
       <c r="B247" s="71" t="s">
         <v>600</v>
       </c>
@@ -18548,7 +18548,7 @@
       <c r="V248" s="71"/>
     </row>
     <row r="249" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="87">
+      <c r="A249" s="84">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18604,7 +18604,7 @@
       </c>
     </row>
     <row r="250" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A250" s="87"/>
+      <c r="A250" s="84"/>
       <c r="B250" s="71" t="s">
         <v>608</v>
       </c>
@@ -18659,7 +18659,7 @@
       </c>
     </row>
     <row r="251" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A251" s="87"/>
+      <c r="A251" s="84"/>
       <c r="B251" s="71" t="s">
         <v>608</v>
       </c>
@@ -18853,7 +18853,7 @@
       <c r="V254" s="66"/>
     </row>
     <row r="255" spans="1:22" ht="27.6" hidden="1">
-      <c r="A255" s="93">
+      <c r="A255" s="90">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18908,7 +18908,7 @@
       </c>
     </row>
     <row r="256" spans="1:22" ht="27.6" hidden="1">
-      <c r="A256" s="98"/>
+      <c r="A256" s="85"/>
       <c r="B256" s="71" t="s">
         <v>621</v>
       </c>
@@ -18964,7 +18964,7 @@
       </c>
     </row>
     <row r="257" spans="1:22" ht="13.9" hidden="1">
-      <c r="A257" s="98"/>
+      <c r="A257" s="85"/>
       <c r="B257" s="71" t="s">
         <v>621</v>
       </c>
@@ -19021,7 +19021,7 @@
       </c>
     </row>
     <row r="258" spans="1:22" ht="13.9" hidden="1">
-      <c r="A258" s="98"/>
+      <c r="A258" s="85"/>
       <c r="B258" s="71" t="s">
         <v>621</v>
       </c>
@@ -19078,7 +19078,7 @@
       </c>
     </row>
     <row r="259" spans="1:22" ht="13.9" hidden="1">
-      <c r="A259" s="98"/>
+      <c r="A259" s="85"/>
       <c r="B259" s="71" t="s">
         <v>621</v>
       </c>
@@ -19133,7 +19133,7 @@
       </c>
     </row>
     <row r="260" spans="1:22" ht="34.15" hidden="1" customHeight="1">
-      <c r="A260" s="94"/>
+      <c r="A260" s="86"/>
       <c r="B260" s="71" t="s">
         <v>621</v>
       </c>
@@ -19190,7 +19190,7 @@
       </c>
     </row>
     <row r="261" spans="1:22" ht="55.15" hidden="1">
-      <c r="A261" s="93">
+      <c r="A261" s="90">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19246,7 +19246,7 @@
       </c>
     </row>
     <row r="262" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="98"/>
+      <c r="A262" s="85"/>
       <c r="B262" s="71" t="s">
         <v>631</v>
       </c>
@@ -19299,7 +19299,7 @@
       </c>
     </row>
     <row r="263" spans="1:22" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="98"/>
+      <c r="A263" s="85"/>
       <c r="B263" s="71" t="s">
         <v>639</v>
       </c>
@@ -19348,7 +19348,7 @@
       </c>
     </row>
     <row r="264" spans="1:22" ht="55.15" hidden="1">
-      <c r="A264" s="98"/>
+      <c r="A264" s="85"/>
       <c r="B264" s="71" t="s">
         <v>639</v>
       </c>
@@ -19399,7 +19399,7 @@
       </c>
     </row>
     <row r="265" spans="1:22" ht="46.15" hidden="1" customHeight="1">
-      <c r="A265" s="98"/>
+      <c r="A265" s="85"/>
       <c r="B265" s="71" t="s">
         <v>631</v>
       </c>
@@ -19512,7 +19512,7 @@
       <c r="V266" s="71"/>
     </row>
     <row r="267" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A267" s="87">
+      <c r="A267" s="84">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19571,7 +19571,7 @@
       <c r="V267" s="71"/>
     </row>
     <row r="268" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A268" s="87"/>
+      <c r="A268" s="84"/>
       <c r="B268" s="71" t="s">
         <v>645</v>
       </c>
@@ -19628,7 +19628,7 @@
       <c r="V268" s="71"/>
     </row>
     <row r="269" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A269" s="87"/>
+      <c r="A269" s="84"/>
       <c r="B269" s="71" t="s">
         <v>645</v>
       </c>
@@ -19685,7 +19685,7 @@
       <c r="V269" s="71"/>
     </row>
     <row r="270" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A270" s="87"/>
+      <c r="A270" s="84"/>
       <c r="B270" s="71" t="s">
         <v>645</v>
       </c>
@@ -19799,7 +19799,7 @@
       </c>
     </row>
     <row r="272" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A272" s="87">
+      <c r="A272" s="84">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19856,7 +19856,7 @@
       <c r="V272" s="71"/>
     </row>
     <row r="273" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A273" s="87"/>
+      <c r="A273" s="84"/>
       <c r="B273" s="71" t="s">
         <v>655</v>
       </c>
@@ -19913,7 +19913,7 @@
       </c>
     </row>
     <row r="274" spans="1:22" ht="13.9" hidden="1">
-      <c r="A274" s="87"/>
+      <c r="A274" s="84"/>
       <c r="B274" s="71" t="s">
         <v>655</v>
       </c>
@@ -19970,7 +19970,7 @@
       </c>
     </row>
     <row r="275" spans="1:22" ht="13.9" hidden="1">
-      <c r="A275" s="87"/>
+      <c r="A275" s="84"/>
       <c r="B275" s="71" t="s">
         <v>655</v>
       </c>
@@ -20027,7 +20027,7 @@
       </c>
     </row>
     <row r="276" spans="1:22" ht="13.9" hidden="1">
-      <c r="A276" s="87"/>
+      <c r="A276" s="84"/>
       <c r="B276" s="66" t="s">
         <v>662</v>
       </c>
@@ -20308,7 +20308,7 @@
       <c r="V280" s="66"/>
     </row>
     <row r="281" spans="1:22" ht="27.6" hidden="1">
-      <c r="A281" s="87">
+      <c r="A281" s="84">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20363,7 +20363,7 @@
       </c>
     </row>
     <row r="282" spans="1:22" ht="13.9" hidden="1">
-      <c r="A282" s="87"/>
+      <c r="A282" s="84"/>
       <c r="B282" s="71" t="s">
         <v>671</v>
       </c>
@@ -20413,7 +20413,7 @@
       <c r="V282" s="66"/>
     </row>
     <row r="283" spans="1:22" ht="37.15" hidden="1" customHeight="1">
-      <c r="A283" s="87">
+      <c r="A283" s="84">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20469,7 +20469,7 @@
       </c>
     </row>
     <row r="284" spans="1:22" ht="13.9" hidden="1">
-      <c r="A284" s="87"/>
+      <c r="A284" s="84"/>
       <c r="B284" s="71" t="s">
         <v>674</v>
       </c>
@@ -20524,7 +20524,7 @@
       <c r="V284" s="71"/>
     </row>
     <row r="285" spans="1:22" ht="13.9" hidden="1">
-      <c r="A285" s="94">
+      <c r="A285" s="86">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20583,7 +20583,7 @@
       </c>
     </row>
     <row r="286" spans="1:22" ht="13.9" hidden="1">
-      <c r="A286" s="94"/>
+      <c r="A286" s="86"/>
       <c r="B286" s="71" t="s">
         <v>678</v>
       </c>
@@ -20640,7 +20640,7 @@
       </c>
     </row>
     <row r="287" spans="1:22" ht="13.9" hidden="1">
-      <c r="A287" s="94"/>
+      <c r="A287" s="86"/>
       <c r="B287" s="71" t="s">
         <v>678</v>
       </c>
@@ -20697,7 +20697,7 @@
       </c>
     </row>
     <row r="288" spans="1:22" ht="13.9" hidden="1">
-      <c r="A288" s="94"/>
+      <c r="A288" s="86"/>
       <c r="B288" s="71" t="s">
         <v>678</v>
       </c>
@@ -20754,7 +20754,7 @@
       </c>
     </row>
     <row r="289" spans="1:22" ht="13.9" hidden="1">
-      <c r="A289" s="87"/>
+      <c r="A289" s="84"/>
       <c r="B289" s="71" t="s">
         <v>678</v>
       </c>
@@ -20808,7 +20808,7 @@
       </c>
     </row>
     <row r="290" spans="1:22" ht="27.6" hidden="1">
-      <c r="A290" s="87"/>
+      <c r="A290" s="84"/>
       <c r="B290" s="71" t="s">
         <v>678</v>
       </c>
@@ -20863,7 +20863,7 @@
       </c>
     </row>
     <row r="291" spans="1:22" ht="13.9" hidden="1">
-      <c r="A291" s="87"/>
+      <c r="A291" s="84"/>
       <c r="B291" s="71" t="s">
         <v>678</v>
       </c>
@@ -20920,7 +20920,7 @@
       </c>
     </row>
     <row r="292" spans="1:22" ht="13.9" hidden="1">
-      <c r="A292" s="87"/>
+      <c r="A292" s="84"/>
       <c r="B292" s="71" t="s">
         <v>678</v>
       </c>
@@ -20973,7 +20973,7 @@
       <c r="V292" s="71"/>
     </row>
     <row r="293" spans="1:22" ht="13.9" hidden="1">
-      <c r="A293" s="87"/>
+      <c r="A293" s="84"/>
       <c r="B293" s="71" t="s">
         <v>678</v>
       </c>
@@ -21089,7 +21089,7 @@
       </c>
     </row>
     <row r="295" spans="1:22" ht="96.6" hidden="1">
-      <c r="A295" s="87">
+      <c r="A295" s="84">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -21152,7 +21152,7 @@
       </c>
     </row>
     <row r="296" spans="1:22" ht="27.6" hidden="1">
-      <c r="A296" s="87"/>
+      <c r="A296" s="84"/>
       <c r="B296" s="71" t="s">
         <v>693</v>
       </c>
@@ -21213,7 +21213,7 @@
       </c>
     </row>
     <row r="297" spans="1:22" ht="13.9" hidden="1">
-      <c r="A297" s="87"/>
+      <c r="A297" s="84"/>
       <c r="B297" s="71" t="s">
         <v>693</v>
       </c>
@@ -21274,7 +21274,7 @@
       </c>
     </row>
     <row r="298" spans="1:22" ht="27.6" hidden="1">
-      <c r="A298" s="87">
+      <c r="A298" s="84">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21330,7 +21330,7 @@
       </c>
     </row>
     <row r="299" spans="1:22" ht="13.9" hidden="1">
-      <c r="A299" s="87"/>
+      <c r="A299" s="84"/>
       <c r="B299" s="71" t="s">
         <v>704</v>
       </c>
@@ -21385,7 +21385,7 @@
       <c r="V299" s="71"/>
     </row>
     <row r="300" spans="1:22" ht="13.9" hidden="1">
-      <c r="A300" s="87"/>
+      <c r="A300" s="84"/>
       <c r="B300" s="71" t="s">
         <v>704</v>
       </c>
@@ -21442,7 +21442,7 @@
       </c>
     </row>
     <row r="301" spans="1:22" ht="13.9" hidden="1">
-      <c r="A301" s="98"/>
+      <c r="A301" s="85"/>
       <c r="B301" s="71" t="s">
         <v>639</v>
       </c>
@@ -21497,7 +21497,7 @@
       <c r="V301" s="71"/>
     </row>
     <row r="302" spans="1:22" ht="13.9" hidden="1">
-      <c r="A302" s="94"/>
+      <c r="A302" s="86"/>
       <c r="B302" s="71" t="s">
         <v>639</v>
       </c>
@@ -21554,7 +21554,7 @@
       </c>
     </row>
     <row r="303" spans="1:22" ht="27.6" hidden="1">
-      <c r="A303" s="93">
+      <c r="A303" s="90">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21610,7 +21610,7 @@
       </c>
     </row>
     <row r="304" spans="1:22" ht="13.9" hidden="1">
-      <c r="A304" s="98"/>
+      <c r="A304" s="85"/>
       <c r="B304" s="71" t="s">
         <v>718</v>
       </c>
@@ -21665,7 +21665,7 @@
       <c r="V304" s="71"/>
     </row>
     <row r="305" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="93">
+      <c r="A305" s="90">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21720,7 +21720,7 @@
       </c>
     </row>
     <row r="306" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="98"/>
+      <c r="A306" s="85"/>
       <c r="B306" s="71" t="s">
         <v>720</v>
       </c>
@@ -21775,7 +21775,7 @@
       </c>
     </row>
     <row r="307" spans="1:22" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="98"/>
+      <c r="A307" s="85"/>
       <c r="B307" s="71" t="s">
         <v>720</v>
       </c>
@@ -21829,7 +21829,7 @@
       </c>
     </row>
     <row r="308" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A308" s="94"/>
+      <c r="A308" s="86"/>
       <c r="B308" s="71" t="s">
         <v>720</v>
       </c>
@@ -21957,57 +21957,57 @@
       <c r="D310" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E310" s="95">
+      <c r="E310" s="96">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="104" t="s">
+      <c r="F310" s="95" t="s">
         <v>731</v>
       </c>
-      <c r="G310" s="87" t="s">
+      <c r="G310" s="84" t="s">
         <v>732</v>
       </c>
-      <c r="H310" s="87">
+      <c r="H310" s="84">
         <v>13.3</v>
       </c>
-      <c r="I310" s="93" t="s">
+      <c r="I310" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="J310" s="93" t="s">
+      <c r="J310" s="90" t="s">
         <v>542</v>
       </c>
-      <c r="K310" s="91">
+      <c r="K310" s="87">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="91">
+      <c r="L310" s="87">
         <v>0</v>
       </c>
-      <c r="M310" s="91">
+      <c r="M310" s="87">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="88" t="s">
+      <c r="N310" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="O310" s="88" t="s">
+      <c r="O310" s="89" t="s">
         <v>733</v>
       </c>
-      <c r="P310" s="87">
+      <c r="P310" s="84">
         <v>2025</v>
       </c>
-      <c r="Q310" s="88" t="s">
+      <c r="Q310" s="89" t="s">
         <v>39</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
       <c r="T310" s="71"/>
-      <c r="U310" s="87"/>
-      <c r="V310" s="87" t="s">
+      <c r="U310" s="84"/>
+      <c r="V310" s="84" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="311" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A311" s="87">
+      <c r="A311" s="84">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -22019,27 +22019,27 @@
       <c r="D311" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E311" s="96"/>
-      <c r="F311" s="88"/>
-      <c r="G311" s="87"/>
-      <c r="H311" s="87"/>
-      <c r="I311" s="94"/>
-      <c r="J311" s="94"/>
-      <c r="K311" s="91"/>
-      <c r="L311" s="91"/>
-      <c r="M311" s="91"/>
-      <c r="N311" s="88"/>
-      <c r="O311" s="88"/>
-      <c r="P311" s="87"/>
-      <c r="Q311" s="88"/>
+      <c r="E311" s="97"/>
+      <c r="F311" s="89"/>
+      <c r="G311" s="84"/>
+      <c r="H311" s="84"/>
+      <c r="I311" s="86"/>
+      <c r="J311" s="86"/>
+      <c r="K311" s="87"/>
+      <c r="L311" s="87"/>
+      <c r="M311" s="87"/>
+      <c r="N311" s="89"/>
+      <c r="O311" s="89"/>
+      <c r="P311" s="84"/>
+      <c r="Q311" s="89"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
       <c r="T311" s="71"/>
-      <c r="U311" s="87"/>
-      <c r="V311" s="87"/>
+      <c r="U311" s="84"/>
+      <c r="V311" s="84"/>
     </row>
     <row r="312" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A312" s="87"/>
+      <c r="A312" s="84"/>
       <c r="B312" s="71" t="s">
         <v>730</v>
       </c>
@@ -22049,58 +22049,58 @@
       <c r="D312" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E312" s="95">
+      <c r="E312" s="96">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="88" t="s">
+      <c r="F312" s="89" t="s">
         <v>735</v>
       </c>
-      <c r="G312" s="87" t="s">
+      <c r="G312" s="84" t="s">
         <v>736</v>
       </c>
-      <c r="H312" s="87">
+      <c r="H312" s="84">
         <v>31.12</v>
       </c>
-      <c r="I312" s="93" t="s">
+      <c r="I312" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="J312" s="93" t="s">
+      <c r="J312" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="K312" s="91">
+      <c r="K312" s="87">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="91">
+      <c r="L312" s="87">
         <v>0</v>
       </c>
-      <c r="M312" s="91">
+      <c r="M312" s="87">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="88" t="s">
+      <c r="N312" s="89" t="s">
         <v>737</v>
       </c>
-      <c r="O312" s="88" t="s">
+      <c r="O312" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="P312" s="87">
+      <c r="P312" s="84">
         <v>2019</v>
       </c>
-      <c r="Q312" s="88" t="s">
+      <c r="Q312" s="89" t="s">
         <v>53</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
       <c r="T312" s="71"/>
-      <c r="U312" s="105">
+      <c r="U312" s="88">
         <v>1</v>
       </c>
-      <c r="V312" s="87" t="s">
+      <c r="V312" s="84" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="313" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A313" s="87"/>
+      <c r="A313" s="84"/>
       <c r="B313" s="71" t="s">
         <v>734</v>
       </c>
@@ -22110,27 +22110,27 @@
       <c r="D313" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E313" s="96"/>
-      <c r="F313" s="88"/>
-      <c r="G313" s="87"/>
-      <c r="H313" s="87"/>
-      <c r="I313" s="94"/>
-      <c r="J313" s="94"/>
-      <c r="K313" s="91"/>
-      <c r="L313" s="91"/>
-      <c r="M313" s="91"/>
-      <c r="N313" s="88"/>
-      <c r="O313" s="88"/>
-      <c r="P313" s="87"/>
-      <c r="Q313" s="88"/>
+      <c r="E313" s="97"/>
+      <c r="F313" s="89"/>
+      <c r="G313" s="84"/>
+      <c r="H313" s="84"/>
+      <c r="I313" s="86"/>
+      <c r="J313" s="86"/>
+      <c r="K313" s="87"/>
+      <c r="L313" s="87"/>
+      <c r="M313" s="87"/>
+      <c r="N313" s="89"/>
+      <c r="O313" s="89"/>
+      <c r="P313" s="84"/>
+      <c r="Q313" s="89"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
       <c r="T313" s="71"/>
-      <c r="U313" s="105"/>
-      <c r="V313" s="87"/>
+      <c r="U313" s="88"/>
+      <c r="V313" s="84"/>
     </row>
     <row r="314" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A314" s="87"/>
+      <c r="A314" s="84"/>
       <c r="B314" s="71" t="s">
         <v>734</v>
       </c>
@@ -22189,7 +22189,7 @@
       </c>
     </row>
     <row r="315" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A315" s="87"/>
+      <c r="A315" s="84"/>
       <c r="B315" s="71" t="s">
         <v>734</v>
       </c>
@@ -22246,7 +22246,7 @@
       <c r="V315" s="71"/>
     </row>
     <row r="316" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A316" s="87"/>
+      <c r="A316" s="84"/>
       <c r="B316" s="71" t="s">
         <v>734</v>
       </c>
@@ -22403,7 +22403,7 @@
       </c>
     </row>
     <row r="319" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A319" s="93">
+      <c r="A319" s="90">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22453,7 +22453,7 @@
       <c r="V319" s="71"/>
     </row>
     <row r="320" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A320" s="94"/>
+      <c r="A320" s="86"/>
       <c r="B320" s="71" t="s">
         <v>740</v>
       </c>
@@ -22507,7 +22507,7 @@
       </c>
     </row>
     <row r="321" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A321" s="99">
+      <c r="A321" s="91">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22562,7 +22562,7 @@
       </c>
     </row>
     <row r="322" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A322" s="100"/>
+      <c r="A322" s="92"/>
       <c r="B322" s="66" t="s">
         <v>746</v>
       </c>
@@ -22613,7 +22613,7 @@
       </c>
     </row>
     <row r="323" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A323" s="100"/>
+      <c r="A323" s="92"/>
       <c r="B323" s="66" t="s">
         <v>746</v>
       </c>
@@ -22668,7 +22668,7 @@
       </c>
     </row>
     <row r="324" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A324" s="100"/>
+      <c r="A324" s="92"/>
       <c r="B324" s="66" t="s">
         <v>746</v>
       </c>
@@ -22723,7 +22723,7 @@
       </c>
     </row>
     <row r="325" spans="1:22" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="98"/>
+      <c r="A325" s="85"/>
       <c r="B325" s="66" t="s">
         <v>746</v>
       </c>
@@ -22776,7 +22776,7 @@
       </c>
     </row>
     <row r="326" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A326" s="98"/>
+      <c r="A326" s="85"/>
       <c r="B326" s="66" t="s">
         <v>746</v>
       </c>
@@ -22829,7 +22829,7 @@
       </c>
     </row>
     <row r="327" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A327" s="100"/>
+      <c r="A327" s="92"/>
       <c r="B327" s="66" t="s">
         <v>746</v>
       </c>
@@ -22886,7 +22886,7 @@
       </c>
     </row>
     <row r="328" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A328" s="100"/>
+      <c r="A328" s="92"/>
       <c r="B328" s="71" t="s">
         <v>746</v>
       </c>
@@ -22939,7 +22939,7 @@
       </c>
     </row>
     <row r="329" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A329" s="100"/>
+      <c r="A329" s="92"/>
       <c r="B329" s="71" t="s">
         <v>746</v>
       </c>
@@ -22994,7 +22994,7 @@
       <c r="V329" s="71"/>
     </row>
     <row r="330" spans="1:22" ht="13.9" hidden="1">
-      <c r="A330" s="101"/>
+      <c r="A330" s="93"/>
       <c r="B330" s="71" t="s">
         <v>746</v>
       </c>
@@ -23231,7 +23231,7 @@
       </c>
     </row>
     <row r="335" spans="1:22" ht="41.45" hidden="1">
-      <c r="A335" s="93">
+      <c r="A335" s="90">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -23294,7 +23294,7 @@
       </c>
     </row>
     <row r="336" spans="1:22" ht="44.45" hidden="1" customHeight="1">
-      <c r="A336" s="98"/>
+      <c r="A336" s="85"/>
       <c r="B336" s="71" t="s">
         <v>767</v>
       </c>
@@ -23348,7 +23348,7 @@
       </c>
     </row>
     <row r="337" spans="1:23" ht="155.44999999999999" hidden="1" customHeight="1">
-      <c r="A337" s="98"/>
+      <c r="A337" s="85"/>
       <c r="B337" s="71" t="s">
         <v>767</v>
       </c>
@@ -23402,7 +23402,7 @@
       </c>
     </row>
     <row r="338" spans="1:23" ht="13.9" hidden="1">
-      <c r="A338" s="94"/>
+      <c r="A338" s="86"/>
       <c r="B338" s="71" t="s">
         <v>767</v>
       </c>
@@ -23506,7 +23506,7 @@
       </c>
     </row>
     <row r="340" spans="1:23" ht="40.9" hidden="1" customHeight="1">
-      <c r="A340" s="87">
+      <c r="A340" s="84">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23565,7 +23565,7 @@
       <c r="W340" s="33"/>
     </row>
     <row r="341" spans="1:23" ht="20.45" hidden="1" customHeight="1">
-      <c r="A341" s="87"/>
+      <c r="A341" s="84"/>
       <c r="B341" s="71" t="s">
         <v>775</v>
       </c>
@@ -23621,7 +23621,7 @@
       <c r="W341" s="33"/>
     </row>
     <row r="342" spans="1:23" ht="13.9" hidden="1">
-      <c r="A342" s="87">
+      <c r="A342" s="84">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23680,7 +23680,7 @@
       </c>
     </row>
     <row r="343" spans="1:23" ht="13.9" hidden="1">
-      <c r="A343" s="87"/>
+      <c r="A343" s="84"/>
       <c r="B343" s="71" t="s">
         <v>778</v>
       </c>
@@ -23737,7 +23737,7 @@
       </c>
     </row>
     <row r="344" spans="1:23" ht="27.6" hidden="1">
-      <c r="A344" s="87"/>
+      <c r="A344" s="84"/>
       <c r="B344" s="71" t="s">
         <v>778</v>
       </c>
@@ -23790,7 +23790,7 @@
       </c>
     </row>
     <row r="345" spans="1:23" ht="13.9" hidden="1">
-      <c r="A345" s="87"/>
+      <c r="A345" s="84"/>
       <c r="B345" s="71" t="s">
         <v>778</v>
       </c>
@@ -23847,7 +23847,7 @@
       </c>
     </row>
     <row r="346" spans="1:23" ht="27.6" hidden="1">
-      <c r="A346" s="87"/>
+      <c r="A346" s="84"/>
       <c r="B346" s="71" t="s">
         <v>778</v>
       </c>
@@ -23901,7 +23901,7 @@
       </c>
     </row>
     <row r="347" spans="1:23" ht="27.6" hidden="1">
-      <c r="A347" s="87"/>
+      <c r="A347" s="84"/>
       <c r="B347" s="71" t="s">
         <v>778</v>
       </c>
@@ -23948,7 +23948,7 @@
       </c>
     </row>
     <row r="348" spans="1:23" ht="13.9" hidden="1">
-      <c r="A348" s="87"/>
+      <c r="A348" s="84"/>
       <c r="B348" s="71" t="s">
         <v>778</v>
       </c>
@@ -24005,7 +24005,7 @@
       </c>
     </row>
     <row r="349" spans="1:23" ht="61.15" hidden="1" customHeight="1">
-      <c r="A349" s="87">
+      <c r="A349" s="84">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -24063,7 +24063,7 @@
       <c r="V349" s="71"/>
     </row>
     <row r="350" spans="1:23" ht="61.15" hidden="1" customHeight="1">
-      <c r="A350" s="87"/>
+      <c r="A350" s="84"/>
       <c r="B350" s="71" t="s">
         <v>790</v>
       </c>
@@ -24118,7 +24118,7 @@
       </c>
     </row>
     <row r="351" spans="1:23" ht="13.9" hidden="1">
-      <c r="A351" s="87"/>
+      <c r="A351" s="84"/>
       <c r="B351" s="71" t="s">
         <v>790</v>
       </c>
@@ -24175,7 +24175,7 @@
       </c>
     </row>
     <row r="352" spans="1:23" ht="94.15" hidden="1" customHeight="1">
-      <c r="A352" s="87">
+      <c r="A352" s="84">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -24234,7 +24234,7 @@
       </c>
     </row>
     <row r="353" spans="1:22" ht="94.15" hidden="1" customHeight="1">
-      <c r="A353" s="87"/>
+      <c r="A353" s="84"/>
       <c r="B353" s="71" t="s">
         <v>795</v>
       </c>
@@ -24288,7 +24288,7 @@
       </c>
     </row>
     <row r="354" spans="1:22" ht="94.15" hidden="1" customHeight="1">
-      <c r="A354" s="87"/>
+      <c r="A354" s="84"/>
       <c r="B354" s="71" t="s">
         <v>795</v>
       </c>
@@ -24345,7 +24345,7 @@
       </c>
     </row>
     <row r="355" spans="1:22" ht="46.9" hidden="1" customHeight="1">
-      <c r="A355" s="87"/>
+      <c r="A355" s="84"/>
       <c r="B355" s="71" t="s">
         <v>795</v>
       </c>
@@ -24406,7 +24406,7 @@
       </c>
     </row>
     <row r="356" spans="1:22" ht="13.9" hidden="1">
-      <c r="A356" s="87"/>
+      <c r="A356" s="84"/>
       <c r="B356" s="71" t="s">
         <v>795</v>
       </c>
@@ -24461,7 +24461,7 @@
       </c>
     </row>
     <row r="357" spans="1:22" ht="13.9" hidden="1">
-      <c r="A357" s="87"/>
+      <c r="A357" s="84"/>
       <c r="B357" s="71" t="s">
         <v>795</v>
       </c>
@@ -24800,7 +24800,7 @@
       </c>
     </row>
     <row r="363" spans="1:22" ht="13.9" hidden="1">
-      <c r="A363" s="87"/>
+      <c r="A363" s="84"/>
       <c r="B363" s="71" t="s">
         <v>815</v>
       </c>
@@ -24856,7 +24856,7 @@
       <c r="V363" s="71"/>
     </row>
     <row r="364" spans="1:22" ht="13.9" hidden="1">
-      <c r="A364" s="87"/>
+      <c r="A364" s="84"/>
       <c r="B364" s="71" t="s">
         <v>815</v>
       </c>
@@ -25082,7 +25082,7 @@
       <c r="V367" s="71"/>
     </row>
     <row r="368" spans="1:22" ht="27.6" hidden="1">
-      <c r="A368" s="93">
+      <c r="A368" s="90">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -25134,7 +25134,7 @@
       </c>
     </row>
     <row r="369" spans="1:22" ht="41.45" hidden="1">
-      <c r="A369" s="98"/>
+      <c r="A369" s="85"/>
       <c r="B369" s="71" t="s">
         <v>822</v>
       </c>
@@ -25195,7 +25195,7 @@
       </c>
     </row>
     <row r="370" spans="1:22" ht="27.6" hidden="1">
-      <c r="A370" s="98"/>
+      <c r="A370" s="85"/>
       <c r="B370" s="71" t="s">
         <v>822</v>
       </c>
@@ -25249,7 +25249,7 @@
       </c>
     </row>
     <row r="371" spans="1:22" ht="27.6" hidden="1">
-      <c r="A371" s="98"/>
+      <c r="A371" s="85"/>
       <c r="B371" s="71" t="s">
         <v>822</v>
       </c>
@@ -25306,7 +25306,7 @@
       </c>
     </row>
     <row r="372" spans="1:22" ht="27.6" hidden="1">
-      <c r="A372" s="94"/>
+      <c r="A372" s="86"/>
       <c r="B372" s="71" t="s">
         <v>822</v>
       </c>
@@ -25361,8 +25361,8 @@
       </c>
       <c r="V372" s="71"/>
     </row>
-    <row r="373" spans="1:22" ht="148.9" hidden="1" customHeight="1">
-      <c r="A373" s="87">
+    <row r="373" spans="1:22" ht="148.9" customHeight="1">
+      <c r="A373" s="84">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25417,8 +25417,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="374" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A374" s="87"/>
+    <row r="374" spans="1:22" ht="40.15" customHeight="1">
+      <c r="A374" s="84"/>
       <c r="B374" s="71" t="s">
         <v>828</v>
       </c>
@@ -25471,8 +25471,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="375" spans="1:22" ht="34.9" hidden="1" customHeight="1">
-      <c r="A375" s="87"/>
+    <row r="375" spans="1:22" ht="34.9" customHeight="1">
+      <c r="A375" s="84"/>
       <c r="B375" s="71" t="s">
         <v>828</v>
       </c>
@@ -25525,8 +25525,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="376" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A376" s="87"/>
+    <row r="376" spans="1:22" ht="37.9" customHeight="1">
+      <c r="A376" s="84"/>
       <c r="B376" s="71" t="s">
         <v>828</v>
       </c>
@@ -25579,8 +25579,8 @@
         <v>707</v>
       </c>
     </row>
-    <row r="377" spans="1:22" ht="122.45" hidden="1" customHeight="1">
-      <c r="A377" s="87"/>
+    <row r="377" spans="1:22" ht="122.45" customHeight="1">
+      <c r="A377" s="84"/>
       <c r="B377" s="71" t="s">
         <v>828</v>
       </c>
@@ -25623,8 +25623,8 @@
         <v>841</v>
       </c>
     </row>
-    <row r="378" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A378" s="87"/>
+    <row r="378" spans="1:22" ht="61.15" customHeight="1">
+      <c r="A378" s="84"/>
       <c r="B378" s="71" t="s">
         <v>828</v>
       </c>
@@ -25676,8 +25676,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A379" s="87"/>
+    <row r="379" spans="1:22" ht="40.9" customHeight="1">
+      <c r="A379" s="84"/>
       <c r="B379" s="71" t="s">
         <v>828</v>
       </c>
@@ -25729,8 +25729,8 @@
         <v>844</v>
       </c>
     </row>
-    <row r="380" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A380" s="87"/>
+    <row r="380" spans="1:22" ht="61.15" customHeight="1">
+      <c r="A380" s="84"/>
       <c r="B380" s="71" t="s">
         <v>828</v>
       </c>
@@ -25776,8 +25776,8 @@
         <v>846</v>
       </c>
     </row>
-    <row r="381" spans="1:22" ht="13.9" hidden="1">
-      <c r="A381" s="87"/>
+    <row r="381" spans="1:22" ht="13.9">
+      <c r="A381" s="84"/>
       <c r="B381" s="71" t="s">
         <v>828</v>
       </c>
@@ -25826,8 +25826,8 @@
       </c>
       <c r="V381" s="71"/>
     </row>
-    <row r="382" spans="1:22" ht="13.9" hidden="1">
-      <c r="A382" s="87"/>
+    <row r="382" spans="1:22" ht="13.9">
+      <c r="A382" s="84"/>
       <c r="B382" s="71" t="s">
         <v>828</v>
       </c>
@@ -25881,8 +25881,8 @@
       </c>
       <c r="V382" s="71"/>
     </row>
-    <row r="383" spans="1:22" ht="13.9" hidden="1">
-      <c r="A383" s="87"/>
+    <row r="383" spans="1:22" ht="13.9">
+      <c r="A383" s="84"/>
       <c r="B383" s="71" t="s">
         <v>828</v>
       </c>
@@ -25934,8 +25934,8 @@
         <v>852</v>
       </c>
     </row>
-    <row r="384" spans="1:22" ht="13.9" hidden="1">
-      <c r="A384" s="87"/>
+    <row r="384" spans="1:22" ht="13.9">
+      <c r="A384" s="84"/>
       <c r="B384" s="71" t="s">
         <v>828</v>
       </c>
@@ -25990,7 +25990,7 @@
       <c r="V384" s="71"/>
     </row>
     <row r="385" spans="1:22" ht="27.6" hidden="1">
-      <c r="A385" s="94">
+      <c r="A385" s="86">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -26046,7 +26046,7 @@
       </c>
     </row>
     <row r="386" spans="1:22" ht="163.15" hidden="1" customHeight="1">
-      <c r="A386" s="87"/>
+      <c r="A386" s="84"/>
       <c r="B386" s="71" t="s">
         <v>856</v>
       </c>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="387" spans="1:22" ht="61.15" hidden="1" customHeight="1">
-      <c r="A387" s="87"/>
+      <c r="A387" s="84"/>
       <c r="B387" s="71" t="s">
         <v>856</v>
       </c>
@@ -26157,7 +26157,7 @@
       <c r="V387" s="71"/>
     </row>
     <row r="388" spans="1:22" ht="13.9" hidden="1">
-      <c r="A388" s="87"/>
+      <c r="A388" s="84"/>
       <c r="B388" s="71" t="s">
         <v>856</v>
       </c>
@@ -26212,7 +26212,7 @@
       </c>
     </row>
     <row r="389" spans="1:22" ht="13.9" hidden="1">
-      <c r="A389" s="87"/>
+      <c r="A389" s="84"/>
       <c r="B389" s="71" t="s">
         <v>855</v>
       </c>
@@ -26267,7 +26267,7 @@
       </c>
     </row>
     <row r="390" spans="1:22" ht="13.9" hidden="1">
-      <c r="A390" s="87"/>
+      <c r="A390" s="84"/>
       <c r="B390" s="71" t="s">
         <v>855</v>
       </c>
@@ -26324,7 +26324,7 @@
       </c>
     </row>
     <row r="391" spans="1:22" ht="13.9" hidden="1">
-      <c r="A391" s="87"/>
+      <c r="A391" s="84"/>
       <c r="B391" s="71" t="s">
         <v>855</v>
       </c>
@@ -26366,7 +26366,7 @@
       </c>
     </row>
     <row r="392" spans="1:22" ht="13.9" hidden="1">
-      <c r="A392" s="87"/>
+      <c r="A392" s="84"/>
       <c r="B392" s="66" t="s">
         <v>855</v>
       </c>
@@ -26475,7 +26475,7 @@
       </c>
     </row>
     <row r="394" spans="1:22" ht="58.15" hidden="1" customHeight="1">
-      <c r="A394" s="87">
+      <c r="A394" s="84">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26531,7 +26531,7 @@
       </c>
     </row>
     <row r="395" spans="1:22" ht="41.45" hidden="1">
-      <c r="A395" s="87"/>
+      <c r="A395" s="84"/>
       <c r="B395" s="66" t="s">
         <v>865</v>
       </c>
@@ -26585,7 +26585,7 @@
       </c>
     </row>
     <row r="396" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="87"/>
+      <c r="A396" s="84"/>
       <c r="B396" s="71" t="s">
         <v>865</v>
       </c>
@@ -26642,7 +26642,7 @@
       </c>
     </row>
     <row r="397" spans="1:22" ht="27.6" hidden="1">
-      <c r="A397" s="87"/>
+      <c r="A397" s="84"/>
       <c r="B397" s="71" t="s">
         <v>865</v>
       </c>
@@ -26695,7 +26695,7 @@
       </c>
     </row>
     <row r="398" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A398" s="87"/>
+      <c r="A398" s="84"/>
       <c r="B398" s="71" t="s">
         <v>865</v>
       </c>
@@ -26750,7 +26750,7 @@
       <c r="V398" s="71"/>
     </row>
     <row r="399" spans="1:22" ht="13.9" hidden="1">
-      <c r="A399" s="87"/>
+      <c r="A399" s="84"/>
       <c r="B399" s="71" t="s">
         <v>865</v>
       </c>
@@ -26805,7 +26805,7 @@
       <c r="V399" s="71"/>
     </row>
     <row r="400" spans="1:22" ht="27.6" hidden="1">
-      <c r="A400" s="102">
+      <c r="A400" s="94">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26863,7 +26863,7 @@
       </c>
     </row>
     <row r="401" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A401" s="102"/>
+      <c r="A401" s="94"/>
       <c r="B401" s="71" t="s">
         <v>875</v>
       </c>
@@ -26905,7 +26905,7 @@
       <c r="V401" s="66"/>
     </row>
     <row r="402" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A402" s="102"/>
+      <c r="A402" s="94"/>
       <c r="B402" s="71" t="s">
         <v>875</v>
       </c>
@@ -26960,7 +26960,7 @@
       </c>
     </row>
     <row r="403" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A403" s="102"/>
+      <c r="A403" s="94"/>
       <c r="B403" s="71" t="s">
         <v>875</v>
       </c>
@@ -27017,7 +27017,7 @@
       </c>
     </row>
     <row r="404" spans="1:22" ht="31.9" hidden="1" customHeight="1">
-      <c r="A404" s="102"/>
+      <c r="A404" s="94"/>
       <c r="B404" s="71" t="s">
         <v>875</v>
       </c>
@@ -27072,7 +27072,7 @@
       <c r="V404" s="71"/>
     </row>
     <row r="405" spans="1:22" ht="13.9" hidden="1">
-      <c r="A405" s="102"/>
+      <c r="A405" s="94"/>
       <c r="B405" s="71" t="s">
         <v>875</v>
       </c>
@@ -27129,7 +27129,7 @@
       </c>
     </row>
     <row r="406" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="87">
+      <c r="A406" s="84">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -27185,7 +27185,7 @@
       </c>
     </row>
     <row r="407" spans="1:22" ht="13.9" hidden="1">
-      <c r="A407" s="87"/>
+      <c r="A407" s="84"/>
       <c r="B407" s="71" t="s">
         <v>882</v>
       </c>
@@ -27242,7 +27242,7 @@
       </c>
     </row>
     <row r="408" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A408" s="87">
+      <c r="A408" s="84">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -27299,7 +27299,7 @@
       </c>
     </row>
     <row r="409" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A409" s="87"/>
+      <c r="A409" s="84"/>
       <c r="B409" s="71" t="s">
         <v>886</v>
       </c>
@@ -27356,7 +27356,7 @@
       </c>
     </row>
     <row r="410" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A410" s="87"/>
+      <c r="A410" s="84"/>
       <c r="B410" s="71" t="s">
         <v>886</v>
       </c>
@@ -27412,7 +27412,7 @@
       </c>
     </row>
     <row r="411" spans="1:22" ht="13.9" hidden="1">
-      <c r="A411" s="87"/>
+      <c r="A411" s="84"/>
       <c r="B411" s="71" t="s">
         <v>886</v>
       </c>
@@ -27469,7 +27469,7 @@
       </c>
     </row>
     <row r="412" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="87">
+      <c r="A412" s="84">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27525,7 +27525,7 @@
       </c>
     </row>
     <row r="413" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="87"/>
+      <c r="A413" s="84"/>
       <c r="B413" s="71" t="s">
         <v>891</v>
       </c>
@@ -27586,7 +27586,7 @@
       </c>
     </row>
     <row r="414" spans="1:22" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="87"/>
+      <c r="A414" s="84"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27610,7 +27610,7 @@
       <c r="V414" s="71"/>
     </row>
     <row r="415" spans="1:22" ht="55.15" hidden="1">
-      <c r="A415" s="87"/>
+      <c r="A415" s="84"/>
       <c r="B415" s="71" t="s">
         <v>891</v>
       </c>
@@ -27664,7 +27664,7 @@
       </c>
     </row>
     <row r="416" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A416" s="87"/>
+      <c r="A416" s="84"/>
       <c r="B416" s="71" t="s">
         <v>891</v>
       </c>
@@ -27720,7 +27720,7 @@
       </c>
     </row>
     <row r="417" spans="1:22" ht="41.45" hidden="1">
-      <c r="A417" s="87">
+      <c r="A417" s="84">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27776,7 +27776,7 @@
       </c>
     </row>
     <row r="418" spans="1:22" ht="142.9" hidden="1" customHeight="1">
-      <c r="A418" s="87"/>
+      <c r="A418" s="84"/>
       <c r="B418" s="71" t="s">
         <v>898</v>
       </c>
@@ -27824,7 +27824,7 @@
       </c>
     </row>
     <row r="419" spans="1:22" ht="13.9" hidden="1">
-      <c r="A419" s="87"/>
+      <c r="A419" s="84"/>
       <c r="B419" s="71" t="s">
         <v>898</v>
       </c>
@@ -27881,7 +27881,7 @@
       </c>
     </row>
     <row r="420" spans="1:22" ht="13.9" hidden="1">
-      <c r="A420" s="87"/>
+      <c r="A420" s="84"/>
       <c r="B420" s="71" t="s">
         <v>898</v>
       </c>
@@ -27938,7 +27938,7 @@
       </c>
     </row>
     <row r="421" spans="1:22" ht="13.9" hidden="1">
-      <c r="A421" s="87"/>
+      <c r="A421" s="84"/>
       <c r="B421" s="71" t="s">
         <v>898</v>
       </c>
@@ -27995,7 +27995,7 @@
       </c>
     </row>
     <row r="422" spans="1:22" ht="27.6" hidden="1">
-      <c r="A422" s="87"/>
+      <c r="A422" s="84"/>
       <c r="B422" s="71" t="s">
         <v>898</v>
       </c>
@@ -28039,7 +28039,7 @@
       </c>
     </row>
     <row r="423" spans="1:22" ht="13.9" hidden="1">
-      <c r="A423" s="87"/>
+      <c r="A423" s="84"/>
       <c r="B423" s="71" t="s">
         <v>898</v>
       </c>
@@ -28090,7 +28090,7 @@
       </c>
     </row>
     <row r="424" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A424" s="87"/>
+      <c r="A424" s="84"/>
       <c r="B424" s="71" t="s">
         <v>898</v>
       </c>
@@ -28249,7 +28249,7 @@
       </c>
     </row>
     <row r="427" spans="1:22" ht="27.6" hidden="1">
-      <c r="A427" s="87">
+      <c r="A427" s="84">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -28307,7 +28307,7 @@
       </c>
     </row>
     <row r="428" spans="1:22" ht="13.9" hidden="1">
-      <c r="A428" s="87"/>
+      <c r="A428" s="84"/>
       <c r="B428" s="71" t="s">
         <v>915</v>
       </c>
@@ -28362,7 +28362,7 @@
       <c r="V428" s="71"/>
     </row>
     <row r="429" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A429" s="87"/>
+      <c r="A429" s="84"/>
       <c r="B429" s="71" t="s">
         <v>915</v>
       </c>
@@ -28415,7 +28415,7 @@
       </c>
     </row>
     <row r="430" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A430" s="87"/>
+      <c r="A430" s="84"/>
       <c r="B430" s="71" t="s">
         <v>914</v>
       </c>
@@ -28468,7 +28468,7 @@
       </c>
     </row>
     <row r="431" spans="1:22" ht="40.9" hidden="1" customHeight="1">
-      <c r="A431" s="87"/>
+      <c r="A431" s="84"/>
       <c r="B431" s="71" t="s">
         <v>914</v>
       </c>
@@ -28521,7 +28521,7 @@
       </c>
     </row>
     <row r="432" spans="1:22" ht="13.9" hidden="1">
-      <c r="A432" s="87"/>
+      <c r="A432" s="84"/>
       <c r="B432" s="71" t="s">
         <v>915</v>
       </c>
@@ -28576,7 +28576,7 @@
       <c r="V432" s="71"/>
     </row>
     <row r="433" spans="1:22" ht="13.9" hidden="1">
-      <c r="A433" s="87"/>
+      <c r="A433" s="84"/>
       <c r="B433" s="71" t="s">
         <v>914</v>
       </c>
@@ -28631,7 +28631,7 @@
       <c r="V433" s="66"/>
     </row>
     <row r="434" spans="1:22" ht="13.9" hidden="1">
-      <c r="A434" s="98"/>
+      <c r="A434" s="85"/>
       <c r="B434" s="71" t="s">
         <v>926</v>
       </c>
@@ -28653,38 +28653,38 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="91">
+      <c r="K434" s="87">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="91">
+      <c r="L434" s="87">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="91">
+      <c r="M434" s="87">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="88" t="s">
+      <c r="N434" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="O434" s="88" t="s">
+      <c r="O434" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="P434" s="87">
+      <c r="P434" s="84">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
       <c r="T434" s="66"/>
-      <c r="U434" s="105">
+      <c r="U434" s="88">
         <v>0.65</v>
       </c>
-      <c r="V434" s="87" t="s">
+      <c r="V434" s="84" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="435" spans="1:22" ht="27.6" hidden="1">
-      <c r="A435" s="98"/>
+      <c r="A435" s="85"/>
       <c r="B435" s="71" t="s">
         <v>926</v>
       </c>
@@ -28706,21 +28706,21 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="91"/>
-      <c r="L435" s="91"/>
-      <c r="M435" s="91"/>
-      <c r="N435" s="88"/>
-      <c r="O435" s="88"/>
-      <c r="P435" s="87"/>
+      <c r="K435" s="87"/>
+      <c r="L435" s="87"/>
+      <c r="M435" s="87"/>
+      <c r="N435" s="89"/>
+      <c r="O435" s="89"/>
+      <c r="P435" s="84"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
       <c r="T435" s="66"/>
-      <c r="U435" s="105"/>
-      <c r="V435" s="87"/>
+      <c r="U435" s="88"/>
+      <c r="V435" s="84"/>
     </row>
     <row r="436" spans="1:22" ht="13.9" hidden="1">
-      <c r="A436" s="98"/>
+      <c r="A436" s="85"/>
       <c r="B436" s="71" t="s">
         <v>926</v>
       </c>
@@ -28775,7 +28775,7 @@
       </c>
     </row>
     <row r="437" spans="1:22" ht="13.9" hidden="1">
-      <c r="A437" s="98"/>
+      <c r="A437" s="85"/>
       <c r="B437" s="71" t="s">
         <v>930</v>
       </c>
@@ -28830,7 +28830,7 @@
       </c>
     </row>
     <row r="438" spans="1:22" ht="13.9" hidden="1">
-      <c r="A438" s="98"/>
+      <c r="A438" s="85"/>
       <c r="B438" s="71" t="s">
         <v>926</v>
       </c>
@@ -28883,7 +28883,7 @@
       </c>
     </row>
     <row r="439" spans="1:22" ht="27.6" hidden="1">
-      <c r="A439" s="94"/>
+      <c r="A439" s="86"/>
       <c r="B439" s="71" t="s">
         <v>926</v>
       </c>
@@ -28937,7 +28937,7 @@
       </c>
     </row>
     <row r="440" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="93">
+      <c r="A440" s="90">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28992,7 +28992,7 @@
       </c>
     </row>
     <row r="441" spans="1:22" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="98"/>
+      <c r="A441" s="85"/>
       <c r="B441" s="71" t="s">
         <v>938</v>
       </c>
@@ -29044,7 +29044,7 @@
       </c>
     </row>
     <row r="442" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="98"/>
+      <c r="A442" s="85"/>
       <c r="B442" s="71" t="s">
         <v>938</v>
       </c>
@@ -29100,7 +29100,7 @@
       </c>
     </row>
     <row r="443" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="98"/>
+      <c r="A443" s="85"/>
       <c r="B443" s="71" t="s">
         <v>938</v>
       </c>
@@ -29155,7 +29155,7 @@
       </c>
     </row>
     <row r="444" spans="1:22" ht="64.900000000000006" hidden="1" customHeight="1">
-      <c r="A444" s="98"/>
+      <c r="A444" s="85"/>
       <c r="B444" s="71" t="s">
         <v>938</v>
       </c>
@@ -29208,7 +29208,7 @@
       </c>
     </row>
     <row r="445" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="98"/>
+      <c r="A445" s="85"/>
       <c r="B445" s="71" t="s">
         <v>938</v>
       </c>
@@ -29259,7 +29259,7 @@
       </c>
     </row>
     <row r="446" spans="1:22" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="98"/>
+      <c r="A446" s="85"/>
       <c r="B446" s="71" t="s">
         <v>938</v>
       </c>
@@ -29297,7 +29297,7 @@
       <c r="V446" s="71"/>
     </row>
     <row r="447" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="94"/>
+      <c r="A447" s="86"/>
       <c r="B447" s="71" t="s">
         <v>938</v>
       </c>
@@ -29352,7 +29352,7 @@
       <c r="V447" s="44"/>
     </row>
     <row r="448" spans="1:22" ht="27.6" hidden="1">
-      <c r="A448" s="87"/>
+      <c r="A448" s="84"/>
       <c r="B448" s="71" t="s">
         <v>948</v>
       </c>
@@ -29409,7 +29409,7 @@
       </c>
     </row>
     <row r="449" spans="1:22" ht="41.45" hidden="1">
-      <c r="A449" s="87"/>
+      <c r="A449" s="84"/>
       <c r="B449" s="51" t="s">
         <v>948</v>
       </c>
@@ -29470,7 +29470,7 @@
       </c>
     </row>
     <row r="450" spans="1:22" ht="27.6" hidden="1">
-      <c r="A450" s="93">
+      <c r="A450" s="90">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29527,7 +29527,7 @@
       </c>
     </row>
     <row r="451" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="98"/>
+      <c r="A451" s="85"/>
       <c r="B451" s="71" t="s">
         <v>955</v>
       </c>
@@ -29582,7 +29582,7 @@
       </c>
     </row>
     <row r="452" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="98"/>
+      <c r="A452" s="85"/>
       <c r="B452" s="71" t="s">
         <v>955</v>
       </c>
@@ -29641,7 +29641,7 @@
       </c>
     </row>
     <row r="453" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="94"/>
+      <c r="A453" s="86"/>
       <c r="B453" s="71" t="s">
         <v>955</v>
       </c>
@@ -29696,7 +29696,7 @@
       </c>
     </row>
     <row r="454" spans="1:22" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="87">
+      <c r="A454" s="84">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29758,7 +29758,7 @@
       </c>
     </row>
     <row r="455" spans="1:22" ht="13.9" hidden="1">
-      <c r="A455" s="87"/>
+      <c r="A455" s="84"/>
       <c r="B455" s="71" t="s">
         <v>962</v>
       </c>
@@ -29814,7 +29814,7 @@
       <c r="V455" s="71"/>
     </row>
     <row r="456" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="87"/>
+      <c r="A456" s="84"/>
       <c r="B456" s="71" t="s">
         <v>962</v>
       </c>
@@ -29872,7 +29872,7 @@
       <c r="V456" s="71"/>
     </row>
     <row r="457" spans="1:22" ht="27.6" hidden="1">
-      <c r="A457" s="87">
+      <c r="A457" s="84">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29926,7 +29926,7 @@
       </c>
     </row>
     <row r="458" spans="1:22" ht="13.9" hidden="1">
-      <c r="A458" s="87"/>
+      <c r="A458" s="84"/>
       <c r="B458" s="71" t="s">
         <v>966</v>
       </c>
@@ -29980,7 +29980,7 @@
       </c>
     </row>
     <row r="459" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A459" s="87"/>
+      <c r="A459" s="84"/>
       <c r="B459" s="71" t="s">
         <v>966</v>
       </c>
@@ -30035,7 +30035,7 @@
       <c r="V459" s="66"/>
     </row>
     <row r="460" spans="1:22" ht="37.9" hidden="1" customHeight="1">
-      <c r="A460" s="87"/>
+      <c r="A460" s="84"/>
       <c r="B460" s="71" t="s">
         <v>966</v>
       </c>
@@ -30084,7 +30084,7 @@
       <c r="V460" s="66"/>
     </row>
     <row r="461" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="87"/>
+      <c r="A461" s="84"/>
       <c r="B461" s="71" t="s">
         <v>966</v>
       </c>
@@ -30472,7 +30472,7 @@
       </c>
     </row>
     <row r="468" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="98"/>
+      <c r="A468" s="85"/>
       <c r="B468" s="71" t="s">
         <v>983</v>
       </c>
@@ -30524,7 +30524,7 @@
       </c>
     </row>
     <row r="469" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="98"/>
+      <c r="A469" s="85"/>
       <c r="B469" s="71" t="s">
         <v>327</v>
       </c>
@@ -30579,7 +30579,7 @@
       <c r="V469" s="71"/>
     </row>
     <row r="470" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="98"/>
+      <c r="A470" s="85"/>
       <c r="B470" s="71" t="s">
         <v>327</v>
       </c>
@@ -30634,7 +30634,7 @@
       <c r="V470" s="71"/>
     </row>
     <row r="471" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="98"/>
+      <c r="A471" s="85"/>
       <c r="B471" s="71" t="s">
         <v>327</v>
       </c>
@@ -30689,7 +30689,7 @@
       <c r="V471" s="71"/>
     </row>
     <row r="472" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="98"/>
+      <c r="A472" s="85"/>
       <c r="B472" s="71" t="s">
         <v>327</v>
       </c>
@@ -30746,7 +30746,7 @@
       </c>
     </row>
     <row r="473" spans="1:22" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="98"/>
+      <c r="A473" s="85"/>
       <c r="B473" s="71" t="s">
         <v>327</v>
       </c>
@@ -30799,7 +30799,7 @@
       </c>
     </row>
     <row r="474" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="94"/>
+      <c r="A474" s="86"/>
       <c r="B474" s="71" t="s">
         <v>983</v>
       </c>
@@ -30850,7 +30850,7 @@
       </c>
     </row>
     <row r="475" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="87">
+      <c r="A475" s="84">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30862,7 +30862,7 @@
       <c r="D475" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E475" s="90">
+      <c r="E475" s="104">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30876,14 +30876,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="92">
+      <c r="K475" s="105">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="92">
+      <c r="L475" s="105">
         <v>0</v>
       </c>
-      <c r="M475" s="91">
+      <c r="M475" s="87">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30902,12 +30902,12 @@
       <c r="S475" s="66"/>
       <c r="T475" s="66"/>
       <c r="U475" s="71"/>
-      <c r="V475" s="88" t="s">
+      <c r="V475" s="89" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="476" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="87"/>
+      <c r="A476" s="84"/>
       <c r="B476" s="71" t="s">
         <v>995</v>
       </c>
@@ -30917,7 +30917,7 @@
       <c r="D476" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="E476" s="90"/>
+      <c r="E476" s="104"/>
       <c r="F476" s="71" t="s">
         <v>177</v>
       </c>
@@ -30929,9 +30929,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="92"/>
-      <c r="L476" s="92"/>
-      <c r="M476" s="91"/>
+      <c r="K476" s="105"/>
+      <c r="L476" s="105"/>
+      <c r="M476" s="87"/>
       <c r="N476" s="71" t="s">
         <v>38</v>
       </c>
@@ -30948,10 +30948,10 @@
       <c r="S476" s="66"/>
       <c r="T476" s="66"/>
       <c r="U476" s="71"/>
-      <c r="V476" s="88"/>
+      <c r="V476" s="89"/>
     </row>
     <row r="477" spans="1:22" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="87"/>
+      <c r="A477" s="84"/>
       <c r="B477" s="71" t="s">
         <v>995</v>
       </c>
@@ -31010,7 +31010,7 @@
       </c>
     </row>
     <row r="478" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="87"/>
+      <c r="A478" s="84"/>
       <c r="B478" s="71" t="s">
         <v>995</v>
       </c>
@@ -31453,7 +31453,7 @@
       <c r="V485" s="66"/>
     </row>
     <row r="486" spans="1:22" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="87">
+      <c r="A486" s="84">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31510,7 +31510,7 @@
       <c r="V486" s="71"/>
     </row>
     <row r="487" spans="1:22" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="87"/>
+      <c r="A487" s="84"/>
       <c r="B487" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31563,7 +31563,7 @@
       </c>
     </row>
     <row r="488" spans="1:22" ht="96.6" hidden="1">
-      <c r="A488" s="87"/>
+      <c r="A488" s="84"/>
       <c r="B488" s="71" t="s">
         <v>1011</v>
       </c>
@@ -31730,7 +31730,7 @@
       <c r="V490" s="71"/>
     </row>
     <row r="491" spans="1:22" ht="13.9" hidden="1">
-      <c r="A491" s="98"/>
+      <c r="A491" s="85"/>
       <c r="B491" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31785,7 +31785,7 @@
       <c r="V491" s="71"/>
     </row>
     <row r="492" spans="1:22" ht="13.9" hidden="1">
-      <c r="A492" s="98"/>
+      <c r="A492" s="85"/>
       <c r="B492" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31840,7 +31840,7 @@
       <c r="V492" s="71"/>
     </row>
     <row r="493" spans="1:22" ht="55.15" hidden="1">
-      <c r="A493" s="98"/>
+      <c r="A493" s="85"/>
       <c r="B493" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31892,7 +31892,7 @@
       </c>
     </row>
     <row r="494" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="94"/>
+      <c r="A494" s="86"/>
       <c r="B494" s="71" t="s">
         <v>1021</v>
       </c>
@@ -31947,7 +31947,7 @@
       <c r="V494" s="71"/>
     </row>
     <row r="495" spans="1:22" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="87">
+      <c r="A495" s="84">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -32006,7 +32006,7 @@
       </c>
     </row>
     <row r="496" spans="1:22" ht="27.6" hidden="1">
-      <c r="A496" s="87"/>
+      <c r="A496" s="84"/>
       <c r="B496" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32059,7 +32059,7 @@
       </c>
     </row>
     <row r="497" spans="1:22" ht="13.9" hidden="1">
-      <c r="A497" s="87"/>
+      <c r="A497" s="84"/>
       <c r="B497" s="71" t="s">
         <v>1028</v>
       </c>
@@ -32114,7 +32114,7 @@
       </c>
     </row>
     <row r="498" spans="1:22" ht="40.15" hidden="1" customHeight="1">
-      <c r="A498" s="87"/>
+      <c r="A498" s="84"/>
       <c r="B498" s="71" t="s">
         <v>1034</v>
       </c>
@@ -32231,7 +32231,7 @@
       </c>
     </row>
     <row r="500" spans="1:22" ht="27.6" hidden="1">
-      <c r="A500" s="88">
+      <c r="A500" s="89">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -32293,7 +32293,7 @@
       </c>
     </row>
     <row r="501" spans="1:22" ht="13.9" hidden="1">
-      <c r="A501" s="88"/>
+      <c r="A501" s="89"/>
       <c r="B501" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32345,7 +32345,7 @@
       <c r="V501" s="71"/>
     </row>
     <row r="502" spans="1:22" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="88"/>
+      <c r="A502" s="89"/>
       <c r="B502" s="71" t="s">
         <v>1035</v>
       </c>
@@ -32402,7 +32402,7 @@
       </c>
     </row>
     <row r="503" spans="1:22" ht="41.45" hidden="1">
-      <c r="A503" s="87">
+      <c r="A503" s="84">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -32465,7 +32465,7 @@
       </c>
     </row>
     <row r="504" spans="1:22" ht="13.9" hidden="1">
-      <c r="A504" s="87"/>
+      <c r="A504" s="84"/>
       <c r="B504" s="71" t="s">
         <v>1043</v>
       </c>
@@ -32524,7 +32524,7 @@
       <c r="V504" s="71"/>
     </row>
     <row r="505" spans="1:22" ht="55.15" hidden="1">
-      <c r="A505" s="87"/>
+      <c r="A505" s="84"/>
       <c r="B505" s="51" t="s">
         <v>1043</v>
       </c>
@@ -32597,11 +32597,11 @@
     <row r="508" spans="1:22" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>85.550000000000011</v>
+        <v>35</v>
       </c>
       <c r="K508" s="8">
         <f>SUBTOTAL(9,K96:K507)</f>
-        <v>23837759611</v>
+        <v>186871355377.09998</v>
       </c>
       <c r="M508" s="58"/>
       <c r="U508" s="29"/>
@@ -32659,24 +32659,113 @@
   <autoFilter ref="A2:V507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Donmatías"/>
-        <filter val="Fredonia"/>
+        <filter val="San Pedro de Urabá"/>
+        <filter val="(No vacías)"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="V91:V92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="V475:V476"/>
+    <mergeCell ref="V434:V435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A400:A405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="P310:P311"/>
+    <mergeCell ref="V310:V311"/>
+    <mergeCell ref="U310:U311"/>
+    <mergeCell ref="A311:A316"/>
+    <mergeCell ref="F312:F313"/>
+    <mergeCell ref="G312:G313"/>
+    <mergeCell ref="K312:K313"/>
+    <mergeCell ref="L312:L313"/>
+    <mergeCell ref="M312:M313"/>
+    <mergeCell ref="N312:N313"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="L310:L311"/>
+    <mergeCell ref="M310:M311"/>
+    <mergeCell ref="N310:N311"/>
+    <mergeCell ref="O310:O311"/>
+    <mergeCell ref="Q310:Q311"/>
+    <mergeCell ref="Q312:Q313"/>
+    <mergeCell ref="O312:O313"/>
+    <mergeCell ref="P312:P313"/>
+    <mergeCell ref="V312:V313"/>
+    <mergeCell ref="U312:U313"/>
     <mergeCell ref="A319:A320"/>
     <mergeCell ref="A321:A330"/>
     <mergeCell ref="A335:A338"/>
@@ -32701,107 +32790,18 @@
     <mergeCell ref="A373:A384"/>
     <mergeCell ref="A385:A392"/>
     <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A400:A405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="P310:P311"/>
-    <mergeCell ref="V310:V311"/>
-    <mergeCell ref="U310:U311"/>
-    <mergeCell ref="A311:A316"/>
-    <mergeCell ref="F312:F313"/>
-    <mergeCell ref="G312:G313"/>
-    <mergeCell ref="K312:K313"/>
-    <mergeCell ref="L312:L313"/>
-    <mergeCell ref="M312:M313"/>
-    <mergeCell ref="N312:N313"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="L310:L311"/>
-    <mergeCell ref="M310:M311"/>
-    <mergeCell ref="N310:N311"/>
-    <mergeCell ref="O310:O311"/>
-    <mergeCell ref="Q310:Q311"/>
-    <mergeCell ref="Q312:Q313"/>
-    <mergeCell ref="O312:O313"/>
-    <mergeCell ref="P312:P313"/>
-    <mergeCell ref="V312:V313"/>
-    <mergeCell ref="U312:U313"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="V91:V92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="V475:V476"/>
-    <mergeCell ref="V434:V435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -33042,23 +33042,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -33214,8 +33197,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -33223,5 +33223,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}"/>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E1B8477-B464-4900-9F24-3DA983D0C859}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D27003-46A8-42AB-B7EE-81282E7FF8E8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos SIF" sheetId="22" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="26" r:id="rId2"/>
-    <sheet name="Estabilización datos " sheetId="25" r:id="rId3"/>
+    <sheet name="Estabilización datos " sheetId="25" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos SIF'!$A$2:$U$507</definedName>
@@ -146,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="1072">
   <si>
     <t>PROYECTOS SIF</t>
   </si>
@@ -4020,37 +4019,6 @@
     <t xml:space="preserve">Actividades preliminares 
 Topografía, Exploración geotécnica,y Limpieza de obras transversales </t>
   </si>
-  <si>
-    <t>Frente</t>
-  </si>
-  <si>
-    <t>Maquinaria</t>
-  </si>
-  <si>
-    <t>Jardín- Alto Ventanas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Metida-Concordia </t>
-  </si>
-  <si>
-    <t>Concordia-Betulia 
-(Magajual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MINICARGADOR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RETRO </t>
-  </si>
-  <si>
-    <t>RETRO Y VQ DT</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor </t>
-  </si>
 </sst>
 </file>
 
@@ -4065,9 +4033,9 @@
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4133,14 +4101,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Poppins"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4295,7 +4255,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4544,49 +4504,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4601,53 +4555,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4971,7 +4913,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W521"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4992,8 +4933,8 @@
     <col min="15" max="15" width="32.5546875" style="33" customWidth="1"/>
     <col min="16" max="16" width="19.109375" style="33" customWidth="1"/>
     <col min="17" max="17" width="20.5546875" style="33" customWidth="1"/>
-    <col min="18" max="18" width="23.5546875" style="111" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="25.109375" style="114" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" style="88" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="25.109375" style="91" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="19.109375" style="59" customWidth="1"/>
     <col min="21" max="21" width="39.5546875" style="33" customWidth="1"/>
     <col min="22" max="22" width="16.6640625" style="29" customWidth="1"/>
@@ -5002,10 +4943,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.8" hidden="1">
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="99"/>
+      <c r="C1" s="107"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -5075,10 +5016,10 @@
       <c r="Q2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="109" t="s">
+      <c r="R2" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="113" t="s">
+      <c r="S2" s="90" t="s">
         <v>18</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -5089,8 +5030,8 @@
       </c>
       <c r="W2" s="13"/>
     </row>
-    <row r="3" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="96">
+    <row r="3" spans="1:23" ht="62.4" customHeight="1">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5142,10 +5083,10 @@
       <c r="Q3" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="112">
+      <c r="R3" s="89">
         <v>46174</v>
       </c>
-      <c r="S3" s="112">
+      <c r="S3" s="89">
         <v>46497</v>
       </c>
       <c r="T3" s="80">
@@ -5155,8 +5096,8 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="96"/>
+    <row r="4" spans="1:23" ht="62.4" customHeight="1">
+      <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>21</v>
       </c>
@@ -5206,10 +5147,10 @@
       <c r="Q4" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="112">
+      <c r="R4" s="89">
         <v>46174</v>
       </c>
-      <c r="S4" s="112">
+      <c r="S4" s="89">
         <v>46497</v>
       </c>
       <c r="T4" s="80">
@@ -5219,8 +5160,8 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="41.4" hidden="1">
-      <c r="A5" s="96"/>
+    <row r="5" spans="1:23" ht="41.4">
+      <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>21</v>
       </c>
@@ -5275,7 +5216,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="27.6" hidden="1">
+    <row r="6" spans="1:23" ht="27.6">
       <c r="A6" s="72"/>
       <c r="B6" s="71" t="s">
         <v>39</v>
@@ -5327,8 +5268,8 @@
       </c>
       <c r="U6" s="66"/>
     </row>
-    <row r="7" spans="1:23" ht="13.8" hidden="1">
-      <c r="A7" s="95">
+    <row r="7" spans="1:23" ht="13.8">
+      <c r="A7" s="98">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5362,8 +5303,8 @@
       <c r="T7" s="66"/>
       <c r="U7" s="66"/>
     </row>
-    <row r="8" spans="1:23" ht="13.8" hidden="1">
-      <c r="A8" s="100"/>
+    <row r="8" spans="1:23" ht="13.8">
+      <c r="A8" s="93"/>
       <c r="B8" s="71" t="s">
         <v>39</v>
       </c>
@@ -5414,8 +5355,8 @@
       </c>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:23" ht="41.4" hidden="1">
-      <c r="A9" s="100"/>
+    <row r="9" spans="1:23" ht="41.4">
+      <c r="A9" s="93"/>
       <c r="B9" s="71" t="s">
         <v>39</v>
       </c>
@@ -5472,8 +5413,8 @@
       </c>
       <c r="U9" s="66"/>
     </row>
-    <row r="10" spans="1:23" ht="41.4" hidden="1">
-      <c r="A10" s="96"/>
+    <row r="10" spans="1:23" ht="41.4">
+      <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>39</v>
       </c>
@@ -5530,8 +5471,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="27.6" hidden="1">
-      <c r="A11" s="89">
+    <row r="11" spans="1:23" ht="27.6">
+      <c r="A11" s="92">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5584,8 +5525,8 @@
       <c r="Q11" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R11" s="110"/>
-      <c r="S11" s="112"/>
+      <c r="R11" s="87"/>
+      <c r="S11" s="89"/>
       <c r="T11" s="80">
         <v>0</v>
       </c>
@@ -5593,8 +5534,8 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="89"/>
+    <row r="12" spans="1:23" ht="52.95" customHeight="1">
+      <c r="A12" s="92"/>
       <c r="B12" s="71" t="s">
         <v>57</v>
       </c>
@@ -5649,8 +5590,8 @@
       </c>
       <c r="U12" s="76"/>
     </row>
-    <row r="13" spans="1:23" ht="13.8" hidden="1">
-      <c r="A13" s="89"/>
+    <row r="13" spans="1:23" ht="13.8">
+      <c r="A13" s="92"/>
       <c r="B13" s="71" t="s">
         <v>57</v>
       </c>
@@ -5705,8 +5646,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="13.8" hidden="1">
-      <c r="A14" s="89"/>
+    <row r="14" spans="1:23" ht="13.8">
+      <c r="A14" s="92"/>
       <c r="B14" s="71" t="s">
         <v>57</v>
       </c>
@@ -5761,8 +5702,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="13.8" hidden="1">
-      <c r="A15" s="89"/>
+    <row r="15" spans="1:23" ht="13.8">
+      <c r="A15" s="92"/>
       <c r="B15" s="71" t="s">
         <v>57</v>
       </c>
@@ -5817,8 +5758,8 @@
       </c>
       <c r="U15" s="66"/>
     </row>
-    <row r="16" spans="1:23" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="89"/>
+    <row r="16" spans="1:23" ht="66.599999999999994" customHeight="1">
+      <c r="A16" s="92"/>
       <c r="B16" s="71" t="s">
         <v>57</v>
       </c>
@@ -5873,7 +5814,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.8" hidden="1">
+    <row r="17" spans="1:21" ht="13.8">
       <c r="A17" s="66"/>
       <c r="B17" s="71" t="s">
         <v>83</v>
@@ -5914,7 +5855,7 @@
       <c r="T17" s="80"/>
       <c r="U17" s="71"/>
     </row>
-    <row r="18" spans="1:21" ht="61.2" hidden="1" customHeight="1">
+    <row r="18" spans="1:21" ht="61.2" customHeight="1">
       <c r="A18" s="66">
         <v>4</v>
       </c>
@@ -5974,7 +5915,7 @@
       </c>
       <c r="U18" s="71"/>
     </row>
-    <row r="19" spans="1:21" ht="41.4" hidden="1">
+    <row r="19" spans="1:21" ht="41.4">
       <c r="A19" s="66"/>
       <c r="B19" s="71" t="s">
         <v>90</v>
@@ -6034,8 +5975,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="89">
+    <row r="20" spans="1:21" ht="97.95" customHeight="1">
+      <c r="A20" s="92">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6096,8 +6037,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A21" s="92"/>
       <c r="B21" s="71" t="s">
         <v>90</v>
       </c>
@@ -6154,11 +6095,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="27.6" hidden="1">
-      <c r="A22" s="89"/>
-      <c r="B22" s="71" t="s">
-        <v>90</v>
-      </c>
+    <row r="22" spans="1:21" ht="27.6">
+      <c r="A22" s="92"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="66" t="s">
         <v>91</v>
       </c>
@@ -6206,15 +6145,15 @@
       <c r="Q22" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R22" s="110"/>
-      <c r="S22" s="112"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="89"/>
       <c r="T22" s="80"/>
       <c r="U22" s="71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="13.8" hidden="1">
-      <c r="A23" s="89"/>
+    <row r="23" spans="1:21" ht="13.8">
+      <c r="A23" s="92"/>
       <c r="B23" s="71" t="s">
         <v>90</v>
       </c>
@@ -6270,8 +6209,8 @@
       </c>
       <c r="U23" s="71"/>
     </row>
-    <row r="24" spans="1:21" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="89">
+    <row r="24" spans="1:21" ht="66" customHeight="1">
+      <c r="A24" s="92">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6324,15 +6263,15 @@
       <c r="Q24" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R24" s="110"/>
-      <c r="S24" s="112"/>
+      <c r="R24" s="87"/>
+      <c r="S24" s="89"/>
       <c r="T24" s="80"/>
       <c r="U24" s="71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="13.8" hidden="1">
-      <c r="A25" s="89"/>
+    <row r="25" spans="1:21" ht="13.8">
+      <c r="A25" s="92"/>
       <c r="B25" s="71" t="s">
         <v>107</v>
       </c>
@@ -6387,8 +6326,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="89"/>
+    <row r="26" spans="1:21" ht="70.2" customHeight="1">
+      <c r="A26" s="92"/>
       <c r="B26" s="71" t="s">
         <v>107</v>
       </c>
@@ -6443,8 +6382,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="89"/>
+    <row r="27" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A27" s="92"/>
       <c r="B27" s="71" t="s">
         <v>107</v>
       </c>
@@ -6501,8 +6440,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="13.8" hidden="1">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:21" ht="13.8">
+      <c r="A28" s="92"/>
       <c r="B28" s="71" t="s">
         <v>107</v>
       </c>
@@ -6555,8 +6494,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A29" s="92"/>
       <c r="B29" s="71" t="s">
         <v>107</v>
       </c>
@@ -6611,8 +6550,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="89"/>
+    <row r="30" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A30" s="92"/>
       <c r="B30" s="71" t="s">
         <v>107</v>
       </c>
@@ -6663,8 +6602,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="89"/>
+    <row r="31" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A31" s="92"/>
       <c r="B31" s="71" t="s">
         <v>107</v>
       </c>
@@ -6721,8 +6660,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="89"/>
+    <row r="32" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A32" s="92"/>
       <c r="B32" s="71" t="s">
         <v>107</v>
       </c>
@@ -6781,8 +6720,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="89"/>
+    <row r="33" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A33" s="92"/>
       <c r="B33" s="71" t="s">
         <v>107</v>
       </c>
@@ -6837,8 +6776,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="89"/>
+    <row r="34" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A34" s="92"/>
       <c r="B34" s="71" t="s">
         <v>107</v>
       </c>
@@ -6897,8 +6836,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="13.8" hidden="1">
-      <c r="A35" s="100"/>
+    <row r="35" spans="1:21" ht="13.8">
+      <c r="A35" s="93"/>
       <c r="B35" s="71" t="s">
         <v>145</v>
       </c>
@@ -6932,8 +6871,8 @@
       <c r="T35" s="1"/>
       <c r="U35" s="71"/>
     </row>
-    <row r="36" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="96"/>
+    <row r="36" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>145</v>
       </c>
@@ -6985,7 +6924,7 @@
       </c>
       <c r="U36" s="66"/>
     </row>
-    <row r="37" spans="1:21" ht="72.599999999999994" hidden="1" customHeight="1">
+    <row r="37" spans="1:21" ht="72.599999999999994" customHeight="1">
       <c r="A37" s="66"/>
       <c r="B37" s="71" t="s">
         <v>148</v>
@@ -7044,8 +6983,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="89">
+    <row r="38" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A38" s="92">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7098,15 +7037,15 @@
       <c r="Q38" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="110"/>
-      <c r="S38" s="112"/>
+      <c r="R38" s="87"/>
+      <c r="S38" s="89"/>
       <c r="T38" s="80"/>
       <c r="U38" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="89"/>
+    <row r="39" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A39" s="92"/>
       <c r="B39" s="71" t="s">
         <v>148</v>
       </c>
@@ -7165,8 +7104,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="89"/>
+    <row r="40" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A40" s="92"/>
       <c r="B40" s="71" t="s">
         <v>148</v>
       </c>
@@ -7222,8 +7161,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="89">
+    <row r="41" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A41" s="92">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7282,8 +7221,8 @@
       </c>
       <c r="U41" s="71"/>
     </row>
-    <row r="42" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="89"/>
+    <row r="42" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A42" s="92"/>
       <c r="B42" s="71" t="s">
         <v>158</v>
       </c>
@@ -7331,8 +7270,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="89"/>
+    <row r="43" spans="1:21" ht="102" customHeight="1">
+      <c r="A43" s="92"/>
       <c r="B43" s="71" t="s">
         <v>158</v>
       </c>
@@ -7382,8 +7321,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="89"/>
+    <row r="44" spans="1:21" ht="102" customHeight="1">
+      <c r="A44" s="92"/>
       <c r="B44" s="71" t="s">
         <v>158</v>
       </c>
@@ -7430,8 +7369,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="27.6" hidden="1">
-      <c r="A45" s="89"/>
+    <row r="45" spans="1:21" ht="27.6">
+      <c r="A45" s="92"/>
       <c r="B45" s="71" t="s">
         <v>158</v>
       </c>
@@ -7486,8 +7425,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="89">
+    <row r="46" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A46" s="92">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7542,8 +7481,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="13.8" hidden="1">
-      <c r="A47" s="95"/>
+    <row r="47" spans="1:21" ht="13.8">
+      <c r="A47" s="98"/>
       <c r="B47" s="71" t="s">
         <v>173</v>
       </c>
@@ -7596,8 +7535,8 @@
       </c>
       <c r="U47" s="71"/>
     </row>
-    <row r="48" spans="1:21" ht="13.8" hidden="1">
-      <c r="A48" s="89"/>
+    <row r="48" spans="1:21" ht="13.8">
+      <c r="A48" s="92"/>
       <c r="B48" s="71" t="s">
         <v>180</v>
       </c>
@@ -7631,8 +7570,8 @@
       <c r="T48" s="80"/>
       <c r="U48" s="71"/>
     </row>
-    <row r="49" spans="1:21" ht="13.8" hidden="1">
-      <c r="A49" s="89"/>
+    <row r="49" spans="1:21" ht="13.8">
+      <c r="A49" s="92"/>
       <c r="B49" s="71" t="s">
         <v>180</v>
       </c>
@@ -7670,8 +7609,8 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="13.8" hidden="1">
-      <c r="A50" s="89"/>
+    <row r="50" spans="1:21" ht="13.8">
+      <c r="A50" s="92"/>
       <c r="B50" s="71" t="s">
         <v>180</v>
       </c>
@@ -7724,8 +7663,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="55.2" hidden="1">
-      <c r="A51" s="89"/>
+    <row r="51" spans="1:21" ht="55.2">
+      <c r="A51" s="92"/>
       <c r="B51" s="71" t="s">
         <v>180</v>
       </c>
@@ -7778,8 +7717,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="41.4" hidden="1">
-      <c r="A52" s="89"/>
+    <row r="52" spans="1:21" ht="41.4">
+      <c r="A52" s="92"/>
       <c r="B52" s="71" t="s">
         <v>180</v>
       </c>
@@ -7832,8 +7771,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="89"/>
+    <row r="53" spans="1:21" ht="45.6" customHeight="1">
+      <c r="A53" s="92"/>
       <c r="B53" s="71" t="s">
         <v>180</v>
       </c>
@@ -7886,8 +7825,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="89"/>
+    <row r="54" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A54" s="92"/>
       <c r="B54" s="71" t="s">
         <v>195</v>
       </c>
@@ -7939,8 +7878,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="89"/>
+    <row r="55" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A55" s="92"/>
       <c r="B55" s="71" t="s">
         <v>195</v>
       </c>
@@ -7993,8 +7932,8 @@
       </c>
       <c r="U55" s="66"/>
     </row>
-    <row r="56" spans="1:21" ht="41.4" hidden="1">
-      <c r="A56" s="89"/>
+    <row r="56" spans="1:21" ht="41.4">
+      <c r="A56" s="92"/>
       <c r="B56" s="71" t="s">
         <v>195</v>
       </c>
@@ -8051,8 +7990,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="89"/>
+    <row r="57" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A57" s="92"/>
       <c r="B57" s="71" t="s">
         <v>195</v>
       </c>
@@ -8107,8 +8046,8 @@
       </c>
       <c r="U57" s="71"/>
     </row>
-    <row r="58" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="89"/>
+    <row r="58" spans="1:21" ht="34.200000000000003" customHeight="1">
+      <c r="A58" s="92"/>
       <c r="B58" s="71" t="s">
         <v>195</v>
       </c>
@@ -8159,15 +8098,15 @@
       <c r="Q58" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R58" s="110"/>
-      <c r="S58" s="112"/>
+      <c r="R58" s="87"/>
+      <c r="S58" s="89"/>
       <c r="T58" s="80"/>
       <c r="U58" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A59" s="96"/>
+    <row r="59" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>207</v>
       </c>
@@ -8222,8 +8161,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A60" s="96"/>
+    <row r="60" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>207</v>
       </c>
@@ -8277,8 +8216,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="41.4" hidden="1">
-      <c r="A61" s="89"/>
+    <row r="61" spans="1:21" ht="41.4">
+      <c r="A61" s="92"/>
       <c r="B61" s="61" t="s">
         <v>207</v>
       </c>
@@ -8330,8 +8269,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="95">
+    <row r="62" spans="1:21" ht="33" customHeight="1">
+      <c r="A62" s="98">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8380,15 +8319,15 @@
       <c r="Q62" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R62" s="110"/>
-      <c r="S62" s="112"/>
+      <c r="R62" s="87"/>
+      <c r="S62" s="89"/>
       <c r="T62" s="80"/>
       <c r="U62" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="100"/>
+    <row r="63" spans="1:21" ht="102" customHeight="1">
+      <c r="A63" s="93"/>
       <c r="B63" s="71" t="s">
         <v>213</v>
       </c>
@@ -8443,8 +8382,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="96"/>
+    <row r="64" spans="1:21" ht="107.25" customHeight="1">
+      <c r="A64" s="94"/>
       <c r="B64" s="71" t="s">
         <v>213</v>
       </c>
@@ -8497,7 +8436,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="107.25" hidden="1" customHeight="1">
+    <row r="65" spans="1:21" ht="107.25" customHeight="1">
       <c r="A65" s="68"/>
       <c r="B65" s="71" t="s">
         <v>223</v>
@@ -8553,7 +8492,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="102" hidden="1" customHeight="1">
+    <row r="66" spans="1:21" ht="102" customHeight="1">
       <c r="A66" s="68"/>
       <c r="B66" s="71" t="s">
         <v>223</v>
@@ -8605,8 +8544,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="95">
+    <row r="67" spans="1:21" ht="102" customHeight="1">
+      <c r="A67" s="98">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8660,8 +8599,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="13.8" hidden="1">
-      <c r="A68" s="96"/>
+    <row r="68" spans="1:21" ht="13.8">
+      <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>228</v>
       </c>
@@ -8712,8 +8651,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="95">
+    <row r="69" spans="1:21" ht="51.6" customHeight="1">
+      <c r="A69" s="98">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8760,15 +8699,15 @@
       <c r="Q69" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R69" s="110"/>
-      <c r="S69" s="112"/>
+      <c r="R69" s="87"/>
+      <c r="S69" s="89"/>
       <c r="T69" s="80"/>
       <c r="U69" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="41.4" hidden="1">
-      <c r="A70" s="100"/>
+    <row r="70" spans="1:21" ht="41.4">
+      <c r="A70" s="93"/>
       <c r="B70" s="71" t="s">
         <v>234</v>
       </c>
@@ -8821,8 +8760,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="67.95" hidden="1" customHeight="1">
-      <c r="A71" s="100"/>
+    <row r="71" spans="1:21" ht="67.95" customHeight="1">
+      <c r="A71" s="93"/>
       <c r="B71" s="71" t="s">
         <v>240</v>
       </c>
@@ -8875,8 +8814,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="100"/>
+    <row r="72" spans="1:21" ht="174.6" customHeight="1">
+      <c r="A72" s="93"/>
       <c r="B72" s="71" t="s">
         <v>243</v>
       </c>
@@ -8930,8 +8869,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="100"/>
+    <row r="73" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A73" s="93"/>
       <c r="B73" s="71" t="s">
         <v>243</v>
       </c>
@@ -8982,8 +8921,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="100"/>
+    <row r="74" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A74" s="93"/>
       <c r="B74" s="71" t="s">
         <v>243</v>
       </c>
@@ -9036,8 +8975,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="100"/>
+    <row r="75" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A75" s="93"/>
       <c r="B75" s="71" t="s">
         <v>243</v>
       </c>
@@ -9096,8 +9035,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A76" s="100"/>
+    <row r="76" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A76" s="93"/>
       <c r="B76" s="71" t="s">
         <v>243</v>
       </c>
@@ -9148,8 +9087,8 @@
       <c r="T76" s="70"/>
       <c r="U76" s="71"/>
     </row>
-    <row r="77" spans="1:21" ht="13.8" hidden="1">
-      <c r="A77" s="96"/>
+    <row r="77" spans="1:21" ht="13.8">
+      <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>243</v>
       </c>
@@ -9204,8 +9143,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="100"/>
+    <row r="78" spans="1:21" ht="20.399999999999999" customHeight="1">
+      <c r="A78" s="93"/>
       <c r="B78" s="71" t="s">
         <v>254</v>
       </c>
@@ -9264,8 +9203,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="13.8" hidden="1">
-      <c r="A79" s="100"/>
+    <row r="79" spans="1:21" ht="13.8">
+      <c r="A79" s="93"/>
       <c r="B79" s="71" t="s">
         <v>254</v>
       </c>
@@ -9318,8 +9257,8 @@
       </c>
       <c r="U79" s="66"/>
     </row>
-    <row r="80" spans="1:21" ht="13.8" hidden="1">
-      <c r="A80" s="100"/>
+    <row r="80" spans="1:21" ht="13.8">
+      <c r="A80" s="93"/>
       <c r="B80" s="71" t="s">
         <v>254</v>
       </c>
@@ -9372,8 +9311,8 @@
       </c>
       <c r="U80" s="66"/>
     </row>
-    <row r="81" spans="1:22" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="100"/>
+    <row r="81" spans="1:22" ht="150.6" customHeight="1">
+      <c r="A81" s="93"/>
       <c r="B81" s="71" t="s">
         <v>254</v>
       </c>
@@ -9427,8 +9366,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="100"/>
+    <row r="82" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A82" s="93"/>
       <c r="B82" s="71" t="s">
         <v>263</v>
       </c>
@@ -9484,8 +9423,8 @@
       </c>
       <c r="V82" s="33"/>
     </row>
-    <row r="83" spans="1:22" ht="38.4" hidden="1" customHeight="1">
-      <c r="A83" s="100"/>
+    <row r="83" spans="1:22" ht="38.4" customHeight="1">
+      <c r="A83" s="93"/>
       <c r="B83" s="71" t="s">
         <v>263</v>
       </c>
@@ -9538,8 +9477,8 @@
       </c>
       <c r="V83" s="33"/>
     </row>
-    <row r="84" spans="1:22" ht="27.6" hidden="1">
-      <c r="A84" s="100"/>
+    <row r="84" spans="1:22" ht="27.6">
+      <c r="A84" s="93"/>
       <c r="B84" s="71" t="s">
         <v>263</v>
       </c>
@@ -9592,8 +9531,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:22" ht="55.2" hidden="1">
-      <c r="A85" s="100"/>
+    <row r="85" spans="1:22" ht="55.2">
+      <c r="A85" s="93"/>
       <c r="B85" s="71" t="s">
         <v>263</v>
       </c>
@@ -9645,8 +9584,8 @@
       </c>
       <c r="V85" s="33"/>
     </row>
-    <row r="86" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="100"/>
+    <row r="86" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A86" s="93"/>
       <c r="B86" s="71" t="s">
         <v>263</v>
       </c>
@@ -9702,8 +9641,8 @@
       </c>
       <c r="V86" s="33"/>
     </row>
-    <row r="87" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="100"/>
+    <row r="87" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A87" s="93"/>
       <c r="B87" s="71" t="s">
         <v>263</v>
       </c>
@@ -9759,8 +9698,8 @@
       </c>
       <c r="V87" s="33"/>
     </row>
-    <row r="88" spans="1:22" ht="13.8" hidden="1">
-      <c r="A88" s="100"/>
+    <row r="88" spans="1:22" ht="13.8">
+      <c r="A88" s="93"/>
       <c r="B88" s="71" t="s">
         <v>263</v>
       </c>
@@ -9816,8 +9755,8 @@
       </c>
       <c r="V88" s="33"/>
     </row>
-    <row r="89" spans="1:22" ht="13.8" hidden="1">
-      <c r="A89" s="100"/>
+    <row r="89" spans="1:22" ht="13.8">
+      <c r="A89" s="93"/>
       <c r="B89" s="71" t="s">
         <v>263</v>
       </c>
@@ -9871,8 +9810,8 @@
       <c r="U89" s="71"/>
       <c r="V89" s="33"/>
     </row>
-    <row r="90" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="100"/>
+    <row r="90" spans="1:22" ht="18" customHeight="1">
+      <c r="A90" s="93"/>
       <c r="B90" s="66" t="s">
         <v>263</v>
       </c>
@@ -9920,8 +9859,8 @@
       </c>
       <c r="V90" s="33"/>
     </row>
-    <row r="91" spans="1:22" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="100"/>
+    <row r="91" spans="1:22" ht="43.95" customHeight="1">
+      <c r="A91" s="93"/>
       <c r="B91" s="71" t="s">
         <v>283</v>
       </c>
@@ -9945,35 +9884,35 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="86"/>
-      <c r="L91" s="86">
+      <c r="K91" s="108"/>
+      <c r="L91" s="108">
         <v>0</v>
       </c>
-      <c r="M91" s="86"/>
-      <c r="N91" s="89" t="s">
+      <c r="M91" s="108"/>
+      <c r="N91" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="O91" s="89" t="s">
+      <c r="O91" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="P91" s="89">
+      <c r="P91" s="92">
         <v>2026</v>
       </c>
-      <c r="Q91" s="90" t="s">
+      <c r="Q91" s="97" t="s">
         <v>129</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
-      <c r="T91" s="91">
+      <c r="T91" s="111">
         <v>0</v>
       </c>
-      <c r="U91" s="90" t="s">
+      <c r="U91" s="97" t="s">
         <v>286</v>
       </c>
       <c r="V91" s="33"/>
     </row>
-    <row r="92" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A92" s="100"/>
+    <row r="92" spans="1:22" ht="40.950000000000003" customHeight="1">
+      <c r="A92" s="93"/>
       <c r="B92" s="71" t="s">
         <v>283</v>
       </c>
@@ -9997,20 +9936,20 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="87"/>
-      <c r="L92" s="87"/>
-      <c r="M92" s="87"/>
-      <c r="N92" s="89"/>
-      <c r="O92" s="89"/>
-      <c r="P92" s="89"/>
-      <c r="Q92" s="90"/>
+      <c r="K92" s="109"/>
+      <c r="L92" s="109"/>
+      <c r="M92" s="109"/>
+      <c r="N92" s="92"/>
+      <c r="O92" s="92"/>
+      <c r="P92" s="92"/>
+      <c r="Q92" s="97"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
-      <c r="T92" s="91"/>
-      <c r="U92" s="90"/>
-    </row>
-    <row r="93" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="100"/>
+      <c r="T92" s="111"/>
+      <c r="U92" s="97"/>
+    </row>
+    <row r="93" spans="1:22" ht="18" customHeight="1">
+      <c r="A93" s="93"/>
       <c r="B93" s="71" t="s">
         <v>283</v>
       </c>
@@ -10034,9 +9973,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="87"/>
-      <c r="L93" s="87"/>
-      <c r="M93" s="87"/>
+      <c r="K93" s="109"/>
+      <c r="L93" s="109"/>
+      <c r="M93" s="109"/>
       <c r="N93" s="66" t="s">
         <v>28</v>
       </c>
@@ -10058,8 +9997,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="100"/>
+    <row r="94" spans="1:22" ht="18" customHeight="1">
+      <c r="A94" s="93"/>
       <c r="B94" s="71" t="s">
         <v>283</v>
       </c>
@@ -10081,9 +10020,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="87"/>
-      <c r="L94" s="87"/>
-      <c r="M94" s="87"/>
+      <c r="K94" s="109"/>
+      <c r="L94" s="109"/>
+      <c r="M94" s="109"/>
       <c r="N94" s="66" t="s">
         <v>28</v>
       </c>
@@ -10105,8 +10044,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A95" s="100"/>
+    <row r="95" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A95" s="93"/>
       <c r="B95" s="71" t="s">
         <v>283</v>
       </c>
@@ -10130,9 +10069,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="87"/>
-      <c r="L95" s="87"/>
-      <c r="M95" s="87"/>
+      <c r="K95" s="109"/>
+      <c r="L95" s="109"/>
+      <c r="M95" s="109"/>
       <c r="N95" s="66" t="s">
         <v>147</v>
       </c>
@@ -10154,8 +10093,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A96" s="100"/>
+    <row r="96" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A96" s="93"/>
       <c r="B96" s="71" t="s">
         <v>291</v>
       </c>
@@ -10175,9 +10114,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="87"/>
-      <c r="L96" s="87"/>
-      <c r="M96" s="87"/>
+      <c r="K96" s="109"/>
+      <c r="L96" s="109"/>
+      <c r="M96" s="109"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10187,8 +10126,8 @@
       <c r="T96" s="70"/>
       <c r="U96" s="66"/>
     </row>
-    <row r="97" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A97" s="100"/>
+    <row r="97" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A97" s="93"/>
       <c r="B97" s="71" t="s">
         <v>291</v>
       </c>
@@ -10216,9 +10155,9 @@
       <c r="J97" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="K97" s="87"/>
-      <c r="L97" s="87"/>
-      <c r="M97" s="87"/>
+      <c r="K97" s="109"/>
+      <c r="L97" s="109"/>
+      <c r="M97" s="109"/>
       <c r="N97" s="66" t="s">
         <v>28</v>
       </c>
@@ -10231,15 +10170,15 @@
       <c r="Q97" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R97" s="110"/>
-      <c r="S97" s="112"/>
+      <c r="R97" s="87"/>
+      <c r="S97" s="89"/>
       <c r="T97" s="80"/>
       <c r="U97" s="71" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="100"/>
+    <row r="98" spans="1:21" ht="99.6" customHeight="1">
+      <c r="A98" s="93"/>
       <c r="B98" s="71" t="s">
         <v>291</v>
       </c>
@@ -10267,9 +10206,9 @@
       <c r="J98" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="K98" s="87"/>
-      <c r="L98" s="87"/>
-      <c r="M98" s="87"/>
+      <c r="K98" s="109"/>
+      <c r="L98" s="109"/>
+      <c r="M98" s="109"/>
       <c r="N98" s="66" t="s">
         <v>99</v>
       </c>
@@ -10291,8 +10230,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="100"/>
+    <row r="99" spans="1:21" ht="17.399999999999999" customHeight="1">
+      <c r="A99" s="93"/>
       <c r="B99" s="71" t="s">
         <v>300</v>
       </c>
@@ -10316,9 +10255,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="87"/>
-      <c r="L99" s="87"/>
-      <c r="M99" s="87"/>
+      <c r="K99" s="109"/>
+      <c r="L99" s="109"/>
+      <c r="M99" s="109"/>
       <c r="N99" s="66" t="s">
         <v>147</v>
       </c>
@@ -10340,8 +10279,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A100" s="100"/>
+    <row r="100" spans="1:21" ht="17.399999999999999" customHeight="1">
+      <c r="A100" s="93"/>
       <c r="B100" s="71" t="s">
         <v>300</v>
       </c>
@@ -10365,9 +10304,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="87"/>
-      <c r="L100" s="87"/>
-      <c r="M100" s="87"/>
+      <c r="K100" s="109"/>
+      <c r="L100" s="109"/>
+      <c r="M100" s="109"/>
       <c r="N100" s="66" t="s">
         <v>73</v>
       </c>
@@ -10389,8 +10328,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="100"/>
+    <row r="101" spans="1:21" ht="53.4" customHeight="1">
+      <c r="A101" s="93"/>
       <c r="B101" s="71" t="s">
         <v>300</v>
       </c>
@@ -10414,9 +10353,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="88"/>
-      <c r="L101" s="88"/>
-      <c r="M101" s="88"/>
+      <c r="K101" s="110"/>
+      <c r="L101" s="110"/>
+      <c r="M101" s="110"/>
       <c r="N101" s="66" t="s">
         <v>36</v>
       </c>
@@ -10438,8 +10377,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="100"/>
+    <row r="102" spans="1:21" ht="53.4" customHeight="1">
+      <c r="A102" s="93"/>
       <c r="B102" s="71" t="s">
         <v>300</v>
       </c>
@@ -10494,8 +10433,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="100"/>
+    <row r="103" spans="1:21" ht="53.4" customHeight="1">
+      <c r="A103" s="93"/>
       <c r="B103" s="71" t="s">
         <v>300</v>
       </c>
@@ -10545,8 +10484,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A104" s="100"/>
+    <row r="104" spans="1:21" ht="53.4" customHeight="1">
+      <c r="A104" s="93"/>
       <c r="B104" s="71" t="s">
         <v>300</v>
       </c>
@@ -10597,8 +10536,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A105" s="100"/>
+    <row r="105" spans="1:21" ht="53.4" customHeight="1">
+      <c r="A105" s="93"/>
       <c r="B105" s="71" t="s">
         <v>300</v>
       </c>
@@ -10651,8 +10590,8 @@
       </c>
       <c r="U105" s="66"/>
     </row>
-    <row r="106" spans="1:21" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="100"/>
+    <row r="106" spans="1:21" ht="34.5" customHeight="1">
+      <c r="A106" s="93"/>
       <c r="B106" s="71" t="s">
         <v>300</v>
       </c>
@@ -10705,8 +10644,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="96.6" hidden="1">
-      <c r="A107" s="100"/>
+    <row r="107" spans="1:21" ht="96.6">
+      <c r="A107" s="93"/>
       <c r="B107" s="71" t="s">
         <v>312</v>
       </c>
@@ -10756,8 +10695,8 @@
         <v>317</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A108" s="100"/>
+    <row r="108" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A108" s="93"/>
       <c r="B108" s="71" t="s">
         <v>318</v>
       </c>
@@ -10801,8 +10740,8 @@
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="13.8" hidden="1">
-      <c r="A109" s="100"/>
+    <row r="109" spans="1:21" ht="13.8">
+      <c r="A109" s="93"/>
       <c r="B109" s="71" t="s">
         <v>318</v>
       </c>
@@ -10853,8 +10792,8 @@
       <c r="T109" s="66"/>
       <c r="U109" s="66"/>
     </row>
-    <row r="110" spans="1:21" ht="13.8" hidden="1">
-      <c r="A110" s="100"/>
+    <row r="110" spans="1:21" ht="13.8">
+      <c r="A110" s="93"/>
       <c r="B110" s="71" t="s">
         <v>318</v>
       </c>
@@ -10907,8 +10846,8 @@
       </c>
       <c r="U110" s="71"/>
     </row>
-    <row r="111" spans="1:21" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="100"/>
+    <row r="111" spans="1:21" ht="60.6" customHeight="1">
+      <c r="A111" s="93"/>
       <c r="B111" s="71" t="s">
         <v>323</v>
       </c>
@@ -10965,8 +10904,8 @@
       </c>
       <c r="U111" s="71"/>
     </row>
-    <row r="112" spans="1:21" ht="13.8" hidden="1">
-      <c r="A112" s="100"/>
+    <row r="112" spans="1:21" ht="13.8">
+      <c r="A112" s="93"/>
       <c r="B112" s="71" t="s">
         <v>325</v>
       </c>
@@ -11017,8 +10956,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="13.8" hidden="1">
-      <c r="A113" s="100"/>
+    <row r="113" spans="1:21" ht="13.8">
+      <c r="A113" s="93"/>
       <c r="B113" s="71" t="s">
         <v>325</v>
       </c>
@@ -11069,8 +11008,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="41.4" hidden="1">
-      <c r="A114" s="100"/>
+    <row r="114" spans="1:21" ht="41.4">
+      <c r="A114" s="93"/>
       <c r="B114" s="71" t="s">
         <v>325</v>
       </c>
@@ -11110,8 +11049,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="22.95" hidden="1" customHeight="1">
-      <c r="A115" s="100"/>
+    <row r="115" spans="1:21" ht="22.95" customHeight="1">
+      <c r="A115" s="93"/>
       <c r="B115" s="71" t="s">
         <v>325</v>
       </c>
@@ -11166,8 +11105,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A116" s="100"/>
+    <row r="116" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A116" s="93"/>
       <c r="B116" s="71" t="s">
         <v>335</v>
       </c>
@@ -11226,8 +11165,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="55.2" hidden="1">
-      <c r="A117" s="96"/>
+    <row r="117" spans="1:21" ht="55.2">
+      <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>340</v>
       </c>
@@ -11282,7 +11221,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="13.8" hidden="1">
+    <row r="118" spans="1:21" ht="13.8">
       <c r="A118" s="72">
         <v>29</v>
       </c>
@@ -11338,8 +11277,8 @@
       </c>
       <c r="U118" s="71"/>
     </row>
-    <row r="119" spans="1:21" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="89">
+    <row r="119" spans="1:21" ht="39.6" customHeight="1">
+      <c r="A119" s="92">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11392,8 +11331,8 @@
       </c>
       <c r="U119" s="71"/>
     </row>
-    <row r="120" spans="1:21" ht="13.8" hidden="1">
-      <c r="A120" s="89"/>
+    <row r="120" spans="1:21" ht="13.8">
+      <c r="A120" s="92"/>
       <c r="B120" s="71" t="s">
         <v>345</v>
       </c>
@@ -11446,8 +11385,8 @@
       </c>
       <c r="U120" s="66"/>
     </row>
-    <row r="121" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="105">
+    <row r="121" spans="1:21" ht="37.200000000000003" customHeight="1">
+      <c r="A121" s="106">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11494,15 +11433,15 @@
       <c r="Q121" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R121" s="110"/>
-      <c r="S121" s="112"/>
+      <c r="R121" s="87"/>
+      <c r="S121" s="89"/>
       <c r="T121" s="80"/>
       <c r="U121" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A122" s="90"/>
+    <row r="122" spans="1:21" ht="37.200000000000003" customHeight="1">
+      <c r="A122" s="97"/>
       <c r="B122" s="71" t="s">
         <v>348</v>
       </c>
@@ -11547,15 +11486,15 @@
       <c r="Q122" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R122" s="110"/>
-      <c r="S122" s="112"/>
+      <c r="R122" s="87"/>
+      <c r="S122" s="89"/>
       <c r="T122" s="80"/>
       <c r="U122" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A123" s="90"/>
+    <row r="123" spans="1:21" ht="142.94999999999999" customHeight="1">
+      <c r="A123" s="97"/>
       <c r="B123" s="71" t="s">
         <v>348</v>
       </c>
@@ -11608,8 +11547,8 @@
         <v>355</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="13.8" hidden="1">
-      <c r="A124" s="90"/>
+    <row r="124" spans="1:21" ht="13.8">
+      <c r="A124" s="97"/>
       <c r="B124" s="71" t="s">
         <v>348</v>
       </c>
@@ -11664,7 +11603,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="131.25" hidden="1" customHeight="1">
+    <row r="125" spans="1:21" ht="131.25" customHeight="1">
       <c r="A125" s="66"/>
       <c r="B125" s="71" t="s">
         <v>357</v>
@@ -11716,7 +11655,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="27.6" hidden="1">
+    <row r="126" spans="1:21" ht="27.6">
       <c r="A126" s="66"/>
       <c r="B126" s="71" t="s">
         <v>357</v>
@@ -11770,7 +11709,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="27.6" hidden="1">
+    <row r="127" spans="1:21" ht="27.6">
       <c r="A127" s="66"/>
       <c r="B127" s="71" t="s">
         <v>357</v>
@@ -11821,7 +11760,7 @@
       <c r="T127" s="80"/>
       <c r="U127" s="71"/>
     </row>
-    <row r="128" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="128" spans="1:21" ht="37.950000000000003" customHeight="1">
       <c r="A128" s="66">
         <v>33</v>
       </c>
@@ -11877,7 +11816,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
+    <row r="129" spans="1:21" ht="37.950000000000003" customHeight="1">
       <c r="A129" s="68"/>
       <c r="B129" s="71" t="s">
         <v>367</v>
@@ -11931,7 +11870,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="13.8" hidden="1">
+    <row r="130" spans="1:21" ht="13.8">
       <c r="A130" s="68">
         <v>34</v>
       </c>
@@ -11987,7 +11926,7 @@
       </c>
       <c r="U130" s="66"/>
     </row>
-    <row r="131" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="131" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A131" s="68"/>
       <c r="B131" s="71" t="s">
         <v>372</v>
@@ -12041,7 +11980,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="132" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A132" s="68"/>
       <c r="B132" s="71" t="s">
         <v>372</v>
@@ -12095,8 +12034,8 @@
       </c>
       <c r="U132" s="66"/>
     </row>
-    <row r="133" spans="1:21" ht="13.8" hidden="1">
-      <c r="A133" s="89">
+    <row r="133" spans="1:21" ht="13.8">
+      <c r="A133" s="92">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12153,8 +12092,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="13.8" hidden="1">
-      <c r="A134" s="89"/>
+    <row r="134" spans="1:21" ht="13.8">
+      <c r="A134" s="92"/>
       <c r="B134" s="71" t="s">
         <v>372</v>
       </c>
@@ -12207,8 +12146,8 @@
       </c>
       <c r="U134" s="66"/>
     </row>
-    <row r="135" spans="1:21" ht="41.4" hidden="1">
-      <c r="A135" s="89"/>
+    <row r="135" spans="1:21" ht="41.4">
+      <c r="A135" s="92"/>
       <c r="B135" s="71" t="s">
         <v>372</v>
       </c>
@@ -12267,8 +12206,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="13.8" hidden="1">
-      <c r="A136" s="89"/>
+    <row r="136" spans="1:21" ht="13.8">
+      <c r="A136" s="92"/>
       <c r="B136" s="71" t="s">
         <v>372</v>
       </c>
@@ -12323,7 +12262,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="125.4" hidden="1" customHeight="1">
+    <row r="137" spans="1:21" ht="125.4" customHeight="1">
       <c r="A137" s="66"/>
       <c r="B137" s="71" t="s">
         <v>381</v>
@@ -12380,8 +12319,8 @@
       </c>
       <c r="U137" s="71"/>
     </row>
-    <row r="138" spans="1:21" ht="13.8" hidden="1">
-      <c r="A138" s="89">
+    <row r="138" spans="1:21" ht="13.8">
+      <c r="A138" s="92">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12436,8 +12375,8 @@
       </c>
       <c r="U138" s="71"/>
     </row>
-    <row r="139" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A139" s="89"/>
+    <row r="139" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A139" s="92"/>
       <c r="B139" s="71" t="s">
         <v>381</v>
       </c>
@@ -12490,8 +12429,8 @@
       </c>
       <c r="U139" s="71"/>
     </row>
-    <row r="140" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A140" s="89"/>
+    <row r="140" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A140" s="92"/>
       <c r="B140" s="71" t="s">
         <v>381</v>
       </c>
@@ -12544,8 +12483,8 @@
       </c>
       <c r="U140" s="71"/>
     </row>
-    <row r="141" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="89"/>
+    <row r="141" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A141" s="92"/>
       <c r="B141" s="71" t="s">
         <v>381</v>
       </c>
@@ -12597,8 +12536,8 @@
       </c>
       <c r="U141" s="71"/>
     </row>
-    <row r="142" spans="1:21" ht="13.8" hidden="1">
-      <c r="A142" s="89"/>
+    <row r="142" spans="1:21" ht="13.8">
+      <c r="A142" s="92"/>
       <c r="B142" s="71" t="s">
         <v>381</v>
       </c>
@@ -12651,8 +12590,8 @@
       </c>
       <c r="U142" s="71"/>
     </row>
-    <row r="143" spans="1:21" ht="13.8" hidden="1">
-      <c r="A143" s="89"/>
+    <row r="143" spans="1:21" ht="13.8">
+      <c r="A143" s="92"/>
       <c r="B143" s="71" t="s">
         <v>381</v>
       </c>
@@ -12705,8 +12644,8 @@
       </c>
       <c r="U143" s="66"/>
     </row>
-    <row r="144" spans="1:21" ht="13.8" hidden="1">
-      <c r="A144" s="89"/>
+    <row r="144" spans="1:21" ht="13.8">
+      <c r="A144" s="92"/>
       <c r="B144" s="71" t="s">
         <v>381</v>
       </c>
@@ -12759,8 +12698,8 @@
       </c>
       <c r="U144" s="71"/>
     </row>
-    <row r="145" spans="1:21" ht="13.8" hidden="1">
-      <c r="A145" s="89">
+    <row r="145" spans="1:21" ht="13.8">
+      <c r="A145" s="92">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12817,8 +12756,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="89"/>
+    <row r="146" spans="1:21" ht="102" customHeight="1">
+      <c r="A146" s="92"/>
       <c r="B146" s="71" t="s">
         <v>397</v>
       </c>
@@ -12869,8 +12808,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="89"/>
+    <row r="147" spans="1:21" ht="18.600000000000001" customHeight="1">
+      <c r="A147" s="92"/>
       <c r="B147" s="71" t="s">
         <v>397</v>
       </c>
@@ -12923,7 +12862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="18.600000000000001" hidden="1" customHeight="1">
+    <row r="148" spans="1:21" ht="18.600000000000001" customHeight="1">
       <c r="A148" s="67"/>
       <c r="B148" s="71" t="s">
         <v>402</v>
@@ -12977,8 +12916,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="35.4" hidden="1" customHeight="1">
-      <c r="A149" s="100"/>
+    <row r="149" spans="1:21" ht="35.4" customHeight="1">
+      <c r="A149" s="93"/>
       <c r="B149" s="71" t="s">
         <v>402</v>
       </c>
@@ -13023,15 +12962,15 @@
       <c r="Q149" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R149" s="110"/>
-      <c r="S149" s="112"/>
+      <c r="R149" s="87"/>
+      <c r="S149" s="89"/>
       <c r="T149" s="80"/>
       <c r="U149" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A150" s="96"/>
+    <row r="150" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>402</v>
       </c>
@@ -13085,7 +13024,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="151" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A151" s="68"/>
       <c r="B151" s="71" t="s">
         <v>407</v>
@@ -13139,7 +13078,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="13.8" hidden="1">
+    <row r="152" spans="1:21" ht="13.8">
       <c r="A152" s="66">
         <v>39</v>
       </c>
@@ -13197,8 +13136,8 @@
         <v>412</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A153" s="95">
+    <row r="153" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A153" s="98">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13255,8 +13194,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A154" s="100"/>
+    <row r="154" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A154" s="93"/>
       <c r="B154" s="71" t="s">
         <v>413</v>
       </c>
@@ -13306,8 +13245,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="100"/>
+    <row r="155" spans="1:21" ht="183.6" customHeight="1">
+      <c r="A155" s="93"/>
       <c r="B155" s="71" t="s">
         <v>413</v>
       </c>
@@ -13355,8 +13294,8 @@
         <v>422</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="100"/>
+    <row r="156" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A156" s="93"/>
       <c r="B156" s="71" t="s">
         <v>413</v>
       </c>
@@ -13406,8 +13345,8 @@
         <v>424</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A157" s="100"/>
+    <row r="157" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A157" s="93"/>
       <c r="B157" s="71" t="s">
         <v>413</v>
       </c>
@@ -13462,8 +13401,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="13.8" hidden="1">
-      <c r="A158" s="100"/>
+    <row r="158" spans="1:21" ht="13.8">
+      <c r="A158" s="93"/>
       <c r="B158" s="71" t="s">
         <v>413</v>
       </c>
@@ -13518,8 +13457,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="13.8" hidden="1">
-      <c r="A159" s="100"/>
+    <row r="159" spans="1:21" ht="13.8">
+      <c r="A159" s="93"/>
       <c r="B159" s="71" t="s">
         <v>413</v>
       </c>
@@ -13574,8 +13513,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="55.2" hidden="1">
-      <c r="A160" s="100"/>
+    <row r="160" spans="1:21" ht="55.2">
+      <c r="A160" s="93"/>
       <c r="B160" s="71" t="s">
         <v>427</v>
       </c>
@@ -13619,15 +13558,15 @@
       <c r="Q160" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R160" s="110"/>
-      <c r="S160" s="112"/>
+      <c r="R160" s="87"/>
+      <c r="S160" s="89"/>
       <c r="T160" s="80">
         <v>0.4</v>
       </c>
       <c r="U160" s="71"/>
     </row>
-    <row r="161" spans="1:21" ht="27.6" hidden="1">
-      <c r="A161" s="100"/>
+    <row r="161" spans="1:21" ht="27.6">
+      <c r="A161" s="93"/>
       <c r="B161" s="71" t="s">
         <v>427</v>
       </c>
@@ -13681,8 +13620,8 @@
       </c>
       <c r="U161" s="71"/>
     </row>
-    <row r="162" spans="1:21" ht="13.8" hidden="1">
-      <c r="A162" s="100"/>
+    <row r="162" spans="1:21" ht="13.8">
+      <c r="A162" s="93"/>
       <c r="B162" s="71" t="s">
         <v>427</v>
       </c>
@@ -13733,8 +13672,8 @@
       </c>
       <c r="U162" s="71"/>
     </row>
-    <row r="163" spans="1:21" ht="13.8" hidden="1">
-      <c r="A163" s="100"/>
+    <row r="163" spans="1:21" ht="13.8">
+      <c r="A163" s="93"/>
       <c r="B163" s="71" t="s">
         <v>427</v>
       </c>
@@ -13789,8 +13728,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="96"/>
+    <row r="164" spans="1:21" ht="27.75" customHeight="1">
+      <c r="A164" s="94"/>
       <c r="B164" s="71" t="s">
         <v>435</v>
       </c>
@@ -13835,15 +13774,15 @@
       <c r="Q164" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R164" s="110"/>
-      <c r="S164" s="112"/>
+      <c r="R164" s="87"/>
+      <c r="S164" s="89"/>
       <c r="T164" s="80"/>
       <c r="U164" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A165" s="100"/>
+    <row r="165" spans="1:21" ht="37.950000000000003" customHeight="1">
+      <c r="A165" s="93"/>
       <c r="B165" s="71" t="s">
         <v>435</v>
       </c>
@@ -13888,15 +13827,15 @@
       <c r="Q165" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R165" s="110"/>
-      <c r="S165" s="112"/>
+      <c r="R165" s="87"/>
+      <c r="S165" s="89"/>
       <c r="T165" s="80"/>
       <c r="U165" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="13.8" hidden="1">
-      <c r="A166" s="96"/>
+    <row r="166" spans="1:21" ht="13.8">
+      <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>435</v>
       </c>
@@ -13950,7 +13889,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="13.8" hidden="1">
+    <row r="167" spans="1:21" ht="13.8">
       <c r="A167" s="68"/>
       <c r="B167" s="71" t="s">
         <v>442</v>
@@ -14008,7 +13947,7 @@
       </c>
       <c r="U167" s="71"/>
     </row>
-    <row r="168" spans="1:21" ht="27.6" hidden="1">
+    <row r="168" spans="1:21" ht="27.6">
       <c r="A168" s="66">
         <v>43</v>
       </c>
@@ -14070,8 +14009,8 @@
         <v>448</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="41.4" hidden="1">
-      <c r="A169" s="101">
+    <row r="169" spans="1:21" ht="41.4">
+      <c r="A169" s="99">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14130,8 +14069,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="102"/>
+    <row r="170" spans="1:21" ht="45" customHeight="1">
+      <c r="A170" s="100"/>
       <c r="B170" s="71" t="s">
         <v>449</v>
       </c>
@@ -14181,8 +14120,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A171" s="102"/>
+    <row r="171" spans="1:21" ht="37.200000000000003" customHeight="1">
+      <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>449</v>
       </c>
@@ -14239,8 +14178,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="13.8" hidden="1">
-      <c r="A172" s="102"/>
+    <row r="172" spans="1:21" ht="13.8">
+      <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>449</v>
       </c>
@@ -14295,8 +14234,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="13.8" hidden="1">
-      <c r="A173" s="103"/>
+    <row r="173" spans="1:21" ht="13.8">
+      <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>456</v>
       </c>
@@ -14351,8 +14290,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A174" s="89">
+    <row r="174" spans="1:21" ht="40.200000000000003" customHeight="1">
+      <c r="A174" s="92">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14401,15 +14340,15 @@
       <c r="Q174" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R174" s="110"/>
-      <c r="S174" s="112"/>
+      <c r="R174" s="87"/>
+      <c r="S174" s="89"/>
       <c r="T174" s="80"/>
       <c r="U174" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="13.8" hidden="1">
-      <c r="A175" s="89"/>
+    <row r="175" spans="1:21" ht="13.8">
+      <c r="A175" s="92"/>
       <c r="B175" s="71" t="s">
         <v>458</v>
       </c>
@@ -14464,8 +14403,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="13.8" hidden="1">
-      <c r="A176" s="89"/>
+    <row r="176" spans="1:21" ht="13.8">
+      <c r="A176" s="92"/>
       <c r="B176" s="71" t="s">
         <v>458</v>
       </c>
@@ -14518,8 +14457,8 @@
       </c>
       <c r="U176" s="71"/>
     </row>
-    <row r="177" spans="1:21" ht="13.8" hidden="1">
-      <c r="A177" s="89"/>
+    <row r="177" spans="1:21" ht="13.8">
+      <c r="A177" s="92"/>
       <c r="B177" s="71" t="s">
         <v>458</v>
       </c>
@@ -14574,8 +14513,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="27.6" hidden="1">
-      <c r="A178" s="89"/>
+    <row r="178" spans="1:21" ht="27.6">
+      <c r="A178" s="92"/>
       <c r="B178" s="71" t="s">
         <v>458</v>
       </c>
@@ -14628,8 +14567,8 @@
       </c>
       <c r="U178" s="71"/>
     </row>
-    <row r="179" spans="1:21" ht="13.8" hidden="1">
-      <c r="A179" s="89"/>
+    <row r="179" spans="1:21" ht="13.8">
+      <c r="A179" s="92"/>
       <c r="B179" s="71" t="s">
         <v>466</v>
       </c>
@@ -14684,8 +14623,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="13.8" hidden="1">
-      <c r="A180" s="89"/>
+    <row r="180" spans="1:21" ht="13.8">
+      <c r="A180" s="92"/>
       <c r="B180" s="71" t="s">
         <v>468</v>
       </c>
@@ -14738,7 +14677,7 @@
       </c>
       <c r="U180" s="66"/>
     </row>
-    <row r="181" spans="1:21" ht="13.8" hidden="1">
+    <row r="181" spans="1:21" ht="13.8">
       <c r="A181" s="75"/>
       <c r="B181" s="71" t="s">
         <v>471</v>
@@ -14792,7 +14731,7 @@
       </c>
       <c r="U181" s="66"/>
     </row>
-    <row r="182" spans="1:21" ht="39.6" hidden="1" customHeight="1">
+    <row r="182" spans="1:21" ht="39.6" customHeight="1">
       <c r="A182" s="75"/>
       <c r="B182" s="71" t="s">
         <v>471</v>
@@ -14845,8 +14784,8 @@
       </c>
       <c r="U182" s="66"/>
     </row>
-    <row r="183" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A183" s="104">
+    <row r="183" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A183" s="102">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14899,8 +14838,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A184" s="104"/>
+    <row r="184" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>471</v>
       </c>
@@ -14953,8 +14892,8 @@
         <v>481</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="13.8" hidden="1">
-      <c r="A185" s="104"/>
+    <row r="185" spans="1:21" ht="13.8">
+      <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>471</v>
       </c>
@@ -15009,7 +14948,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="13.8" hidden="1">
+    <row r="186" spans="1:21" ht="13.8">
       <c r="A186" s="72"/>
       <c r="B186" s="71" t="s">
         <v>483</v>
@@ -15067,8 +15006,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="13.8" hidden="1">
-      <c r="A187" s="102"/>
+    <row r="187" spans="1:21" ht="13.8">
+      <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>483</v>
       </c>
@@ -15117,8 +15056,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="13.8" hidden="1">
-      <c r="A188" s="102"/>
+    <row r="188" spans="1:21" ht="13.8">
+      <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>483</v>
       </c>
@@ -15169,8 +15108,8 @@
       <c r="T188" s="80"/>
       <c r="U188" s="71"/>
     </row>
-    <row r="189" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A189" s="103"/>
+    <row r="189" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>483</v>
       </c>
@@ -15221,7 +15160,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="81" hidden="1" customHeight="1">
+    <row r="190" spans="1:21" ht="81" customHeight="1">
       <c r="A190" s="66"/>
       <c r="B190" s="71" t="s">
         <v>490</v>
@@ -15275,8 +15214,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="64.95" hidden="1" customHeight="1">
-      <c r="A191" s="89">
+    <row r="191" spans="1:21" ht="64.95" customHeight="1">
+      <c r="A191" s="92">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15323,15 +15262,15 @@
       <c r="Q191" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R191" s="110"/>
-      <c r="S191" s="112"/>
+      <c r="R191" s="87"/>
+      <c r="S191" s="89"/>
       <c r="T191" s="80"/>
       <c r="U191" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="89"/>
+    <row r="192" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A192" s="92"/>
       <c r="B192" s="71" t="s">
         <v>490</v>
       </c>
@@ -15383,8 +15322,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="13.8" hidden="1">
-      <c r="A193" s="89"/>
+    <row r="193" spans="1:21" ht="13.8">
+      <c r="A193" s="92"/>
       <c r="B193" s="71" t="s">
         <v>490</v>
       </c>
@@ -15439,7 +15378,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="13.8" hidden="1">
+    <row r="194" spans="1:21" ht="13.8">
       <c r="A194" s="66">
         <v>49</v>
       </c>
@@ -15468,8 +15407,8 @@
       <c r="T194" s="66"/>
       <c r="U194" s="66"/>
     </row>
-    <row r="195" spans="1:21" ht="13.8" hidden="1">
-      <c r="A195" s="100"/>
+    <row r="195" spans="1:21" ht="13.8">
+      <c r="A195" s="93"/>
       <c r="B195" s="71" t="s">
         <v>502</v>
       </c>
@@ -15522,8 +15461,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="24.6" hidden="1" customHeight="1">
-      <c r="A196" s="96"/>
+    <row r="196" spans="1:21" ht="24.6" customHeight="1">
+      <c r="A196" s="94"/>
       <c r="B196" s="71" t="s">
         <v>502</v>
       </c>
@@ -15576,8 +15515,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="13.8" hidden="1">
-      <c r="A197" s="89">
+    <row r="197" spans="1:21" ht="13.8">
+      <c r="A197" s="92">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15624,15 +15563,15 @@
       <c r="Q197" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R197" s="110"/>
-      <c r="S197" s="112"/>
+      <c r="R197" s="87"/>
+      <c r="S197" s="89"/>
       <c r="T197" s="80"/>
       <c r="U197" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="13.8" hidden="1">
-      <c r="A198" s="89"/>
+    <row r="198" spans="1:21" ht="13.8">
+      <c r="A198" s="92"/>
       <c r="B198" s="71" t="s">
         <v>506</v>
       </c>
@@ -15687,8 +15626,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="13.8" hidden="1">
-      <c r="A199" s="89"/>
+    <row r="199" spans="1:21" ht="13.8">
+      <c r="A199" s="92"/>
       <c r="B199" s="71" t="s">
         <v>506</v>
       </c>
@@ -15743,8 +15682,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A200" s="89"/>
+    <row r="200" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A200" s="92"/>
       <c r="B200" s="71" t="s">
         <v>506</v>
       </c>
@@ -15798,7 +15737,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="201" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="71" t="s">
         <v>513</v>
@@ -15852,7 +15791,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="202" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="71" t="s">
         <v>513</v>
@@ -15900,7 +15839,7 @@
       <c r="T202" s="70"/>
       <c r="U202" s="66"/>
     </row>
-    <row r="203" spans="1:21" ht="13.8" hidden="1">
+    <row r="203" spans="1:21" ht="13.8">
       <c r="A203" s="66">
         <v>52</v>
       </c>
@@ -15958,8 +15897,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A204" s="89">
+    <row r="204" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A204" s="92">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -16015,8 +15954,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="55.2" hidden="1">
-      <c r="A205" s="89"/>
+    <row r="205" spans="1:21" ht="55.2">
+      <c r="A205" s="92"/>
       <c r="B205" s="71" t="s">
         <v>518</v>
       </c>
@@ -16071,8 +16010,8 @@
         <v>521</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="13.8" hidden="1">
-      <c r="A206" s="89"/>
+    <row r="206" spans="1:21" ht="13.8">
+      <c r="A206" s="92"/>
       <c r="B206" s="66" t="s">
         <v>522</v>
       </c>
@@ -16127,8 +16066,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="13.8" hidden="1">
-      <c r="A207" s="89">
+    <row r="207" spans="1:21" ht="13.8">
+      <c r="A207" s="92">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16183,8 +16122,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="13.8" hidden="1">
-      <c r="A208" s="89"/>
+    <row r="208" spans="1:21" ht="13.8">
+      <c r="A208" s="92"/>
       <c r="B208" s="71" t="s">
         <v>525</v>
       </c>
@@ -16241,8 +16180,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="32.4" hidden="1" customHeight="1">
-      <c r="A209" s="89">
+    <row r="209" spans="1:21" ht="32.4" customHeight="1">
+      <c r="A209" s="92">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16291,15 +16230,15 @@
       <c r="Q209" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R209" s="110"/>
-      <c r="S209" s="112"/>
+      <c r="R209" s="87"/>
+      <c r="S209" s="89"/>
       <c r="T209" s="80"/>
       <c r="U209" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="13.8" hidden="1">
-      <c r="A210" s="89"/>
+    <row r="210" spans="1:21" ht="13.8">
+      <c r="A210" s="92"/>
       <c r="B210" s="71" t="s">
         <v>528</v>
       </c>
@@ -16352,8 +16291,8 @@
       </c>
       <c r="U210" s="71"/>
     </row>
-    <row r="211" spans="1:21" ht="16.2" hidden="1" customHeight="1">
-      <c r="A211" s="89"/>
+    <row r="211" spans="1:21" ht="16.2" customHeight="1">
+      <c r="A211" s="92"/>
       <c r="B211" s="71" t="s">
         <v>528</v>
       </c>
@@ -16406,8 +16345,8 @@
       </c>
       <c r="U211" s="66"/>
     </row>
-    <row r="212" spans="1:21" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A212" s="89">
+    <row r="212" spans="1:21" ht="80.400000000000006" customHeight="1">
+      <c r="A212" s="92">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16454,15 +16393,15 @@
       <c r="Q212" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R212" s="110"/>
-      <c r="S212" s="112"/>
+      <c r="R212" s="87"/>
+      <c r="S212" s="89"/>
       <c r="T212" s="80"/>
       <c r="U212" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="13.8" hidden="1">
-      <c r="A213" s="89"/>
+    <row r="213" spans="1:21" ht="13.8">
+      <c r="A213" s="92"/>
       <c r="B213" s="71" t="s">
         <v>537</v>
       </c>
@@ -16519,8 +16458,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="27.6" hidden="1">
-      <c r="A214" s="101">
+    <row r="214" spans="1:21" ht="27.6">
+      <c r="A214" s="99">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16575,7 +16514,7 @@
       </c>
     </row>
     <row r="215" spans="1:21" ht="13.8">
-      <c r="A215" s="102"/>
+      <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>539</v>
       </c>
@@ -16631,7 +16570,7 @@
       </c>
     </row>
     <row r="216" spans="1:21" ht="13.8">
-      <c r="A216" s="102"/>
+      <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>539</v>
       </c>
@@ -16687,7 +16626,7 @@
       </c>
     </row>
     <row r="217" spans="1:21" ht="41.4">
-      <c r="A217" s="100"/>
+      <c r="A217" s="93"/>
       <c r="B217" s="71" t="s">
         <v>539</v>
       </c>
@@ -16733,8 +16672,8 @@
       <c r="Q217" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R217" s="110"/>
-      <c r="S217" s="112"/>
+      <c r="R217" s="87"/>
+      <c r="S217" s="89"/>
       <c r="T217" s="80">
         <v>0.01</v>
       </c>
@@ -16743,7 +16682,7 @@
       </c>
     </row>
     <row r="218" spans="1:21" ht="13.8">
-      <c r="A218" s="103"/>
+      <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>539</v>
       </c>
@@ -16798,7 +16737,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="13.8" hidden="1">
+    <row r="219" spans="1:21" ht="13.8">
       <c r="A219" s="74"/>
       <c r="B219" s="71" t="s">
         <v>550</v>
@@ -16854,7 +16793,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="13.8" hidden="1">
+    <row r="220" spans="1:21" ht="13.8">
       <c r="A220" s="74"/>
       <c r="B220" s="71" t="s">
         <v>550</v>
@@ -16910,7 +16849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="13.8" hidden="1">
+    <row r="221" spans="1:21" ht="13.8">
       <c r="A221" s="74"/>
       <c r="B221" s="71" t="s">
         <v>550</v>
@@ -16963,7 +16902,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="222" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A222" s="66">
         <v>58</v>
       </c>
@@ -17021,8 +16960,8 @@
         <v>361</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A223" s="89">
+    <row r="223" spans="1:21" ht="34.200000000000003" customHeight="1">
+      <c r="A223" s="92">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17069,15 +17008,15 @@
       <c r="Q223" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R223" s="110"/>
-      <c r="S223" s="112"/>
+      <c r="R223" s="87"/>
+      <c r="S223" s="89"/>
       <c r="T223" s="80"/>
       <c r="U223" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A224" s="89"/>
+    <row r="224" spans="1:21" ht="34.200000000000003" customHeight="1">
+      <c r="A224" s="92"/>
       <c r="B224" s="71" t="s">
         <v>560</v>
       </c>
@@ -17132,8 +17071,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A225" s="89"/>
+    <row r="225" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A225" s="92"/>
       <c r="B225" s="71" t="s">
         <v>560</v>
       </c>
@@ -17183,8 +17122,8 @@
       </c>
       <c r="U225" s="71"/>
     </row>
-    <row r="226" spans="1:21" ht="13.8" hidden="1">
-      <c r="A226" s="89"/>
+    <row r="226" spans="1:21" ht="13.8">
+      <c r="A226" s="92"/>
       <c r="B226" s="71" t="s">
         <v>560</v>
       </c>
@@ -17239,8 +17178,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="27.6" hidden="1">
-      <c r="A227" s="89"/>
+    <row r="227" spans="1:21" ht="27.6">
+      <c r="A227" s="92"/>
       <c r="B227" s="71" t="s">
         <v>560</v>
       </c>
@@ -17291,8 +17230,8 @@
       <c r="T227" s="70"/>
       <c r="U227" s="66"/>
     </row>
-    <row r="228" spans="1:21" ht="13.8" hidden="1">
-      <c r="A228" s="89"/>
+    <row r="228" spans="1:21" ht="13.8">
+      <c r="A228" s="92"/>
       <c r="B228" s="71" t="s">
         <v>560</v>
       </c>
@@ -17347,7 +17286,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="229" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A229" s="66"/>
       <c r="B229" s="71" t="s">
         <v>572</v>
@@ -17401,7 +17340,7 @@
       </c>
       <c r="U229" s="66"/>
     </row>
-    <row r="230" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="230" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A230" s="66"/>
       <c r="B230" s="71" t="s">
         <v>572</v>
@@ -17455,7 +17394,7 @@
       </c>
       <c r="U230" s="66"/>
     </row>
-    <row r="231" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
+    <row r="231" spans="1:21" ht="20.399999999999999" customHeight="1">
       <c r="A231" s="66"/>
       <c r="B231" s="71" t="s">
         <v>572</v>
@@ -17509,7 +17448,7 @@
       </c>
       <c r="U231" s="66"/>
     </row>
-    <row r="232" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="232" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A232" s="66">
         <v>60</v>
       </c>
@@ -17564,7 +17503,7 @@
       </c>
       <c r="U232" s="66"/>
     </row>
-    <row r="233" spans="1:21" ht="13.8" hidden="1">
+    <row r="233" spans="1:21" ht="13.8">
       <c r="A233" s="66">
         <v>61</v>
       </c>
@@ -17593,7 +17532,7 @@
       <c r="T233" s="66"/>
       <c r="U233" s="66"/>
     </row>
-    <row r="234" spans="1:21" ht="224.4" hidden="1" customHeight="1">
+    <row r="234" spans="1:21" ht="224.4" customHeight="1">
       <c r="A234" s="66">
         <v>62</v>
       </c>
@@ -17649,8 +17588,8 @@
         <v>580</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="95">
+    <row r="235" spans="1:21" ht="102" customHeight="1">
+      <c r="A235" s="98">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17703,8 +17642,8 @@
         <v>585</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="100"/>
+    <row r="236" spans="1:21" ht="102" customHeight="1">
+      <c r="A236" s="93"/>
       <c r="B236" s="71" t="s">
         <v>581</v>
       </c>
@@ -17757,8 +17696,8 @@
         <v>588</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="100"/>
+    <row r="237" spans="1:21" ht="102" customHeight="1">
+      <c r="A237" s="93"/>
       <c r="B237" s="71" t="s">
         <v>581</v>
       </c>
@@ -17811,8 +17750,8 @@
         <v>591</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="100"/>
+    <row r="238" spans="1:21" ht="39.6" customHeight="1">
+      <c r="A238" s="93"/>
       <c r="B238" s="71" t="s">
         <v>581</v>
       </c>
@@ -17866,8 +17805,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A239" s="100"/>
+    <row r="239" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A239" s="93"/>
       <c r="B239" s="71" t="s">
         <v>581</v>
       </c>
@@ -17921,8 +17860,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="96"/>
+    <row r="240" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>595</v>
       </c>
@@ -17973,8 +17912,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="89">
+    <row r="241" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A241" s="92">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -18028,8 +17967,8 @@
       </c>
       <c r="U241" s="71"/>
     </row>
-    <row r="242" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="89"/>
+    <row r="242" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A242" s="92"/>
       <c r="B242" s="71" t="s">
         <v>598</v>
       </c>
@@ -18082,8 +18021,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A243" s="89"/>
+    <row r="243" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A243" s="92"/>
       <c r="B243" s="71" t="s">
         <v>598</v>
       </c>
@@ -18142,8 +18081,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="41.4" hidden="1">
-      <c r="A244" s="89"/>
+    <row r="244" spans="1:21" ht="41.4">
+      <c r="A244" s="92"/>
       <c r="B244" s="71" t="s">
         <v>598</v>
       </c>
@@ -18194,8 +18133,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="13.8" hidden="1">
-      <c r="A245" s="89"/>
+    <row r="245" spans="1:21" ht="13.8">
+      <c r="A245" s="92"/>
       <c r="B245" s="71" t="s">
         <v>598</v>
       </c>
@@ -18229,8 +18168,8 @@
       <c r="T245" s="80"/>
       <c r="U245" s="71"/>
     </row>
-    <row r="246" spans="1:21" ht="13.8" hidden="1">
-      <c r="A246" s="89"/>
+    <row r="246" spans="1:21" ht="13.8">
+      <c r="A246" s="92"/>
       <c r="B246" s="71" t="s">
         <v>598</v>
       </c>
@@ -18281,8 +18220,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A247" s="89"/>
+    <row r="247" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A247" s="92"/>
       <c r="B247" s="71" t="s">
         <v>598</v>
       </c>
@@ -18336,7 +18275,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="248" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A248" s="66"/>
       <c r="B248" s="71" t="s">
         <v>606</v>
@@ -18390,8 +18329,8 @@
       </c>
       <c r="U248" s="71"/>
     </row>
-    <row r="249" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A249" s="89">
+    <row r="249" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A249" s="92">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18445,8 +18384,8 @@
         <v>612</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A250" s="89"/>
+    <row r="250" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A250" s="92"/>
       <c r="B250" s="71" t="s">
         <v>606</v>
       </c>
@@ -18499,8 +18438,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A251" s="89"/>
+    <row r="251" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A251" s="92"/>
       <c r="B251" s="71" t="s">
         <v>606</v>
       </c>
@@ -18554,7 +18493,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="13.8" hidden="1">
+    <row r="252" spans="1:21" ht="13.8">
       <c r="A252" s="66">
         <v>66</v>
       </c>
@@ -18583,7 +18522,7 @@
       <c r="T252" s="66"/>
       <c r="U252" s="66"/>
     </row>
-    <row r="253" spans="1:21" ht="13.8" hidden="1">
+    <row r="253" spans="1:21" ht="13.8">
       <c r="A253" s="66"/>
       <c r="B253" s="71" t="s">
         <v>615</v>
@@ -18633,7 +18572,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="13.8" hidden="1">
+    <row r="254" spans="1:21" ht="13.8">
       <c r="A254" s="66">
         <v>67</v>
       </c>
@@ -18689,8 +18628,8 @@
       </c>
       <c r="U254" s="66"/>
     </row>
-    <row r="255" spans="1:21" ht="27.6" hidden="1">
-      <c r="A255" s="95">
+    <row r="255" spans="1:21" ht="27.6">
+      <c r="A255" s="98">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18743,8 +18682,8 @@
         <v>621</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="27.6" hidden="1">
-      <c r="A256" s="100"/>
+    <row r="256" spans="1:21" ht="27.6">
+      <c r="A256" s="93"/>
       <c r="B256" s="71" t="s">
         <v>619</v>
       </c>
@@ -18791,15 +18730,15 @@
       <c r="Q256" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R256" s="110"/>
-      <c r="S256" s="112"/>
+      <c r="R256" s="87"/>
+      <c r="S256" s="89"/>
       <c r="T256" s="80"/>
       <c r="U256" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="13.8" hidden="1">
-      <c r="A257" s="100"/>
+    <row r="257" spans="1:21" ht="13.8">
+      <c r="A257" s="93"/>
       <c r="B257" s="71" t="s">
         <v>619</v>
       </c>
@@ -18854,8 +18793,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="13.8" hidden="1">
-      <c r="A258" s="100"/>
+    <row r="258" spans="1:21" ht="13.8">
+      <c r="A258" s="93"/>
       <c r="B258" s="71" t="s">
         <v>619</v>
       </c>
@@ -18910,8 +18849,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="13.8" hidden="1">
-      <c r="A259" s="100"/>
+    <row r="259" spans="1:21" ht="13.8">
+      <c r="A259" s="93"/>
       <c r="B259" s="71" t="s">
         <v>619</v>
       </c>
@@ -18964,8 +18903,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A260" s="96"/>
+    <row r="260" spans="1:21" ht="34.200000000000003" customHeight="1">
+      <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>619</v>
       </c>
@@ -19020,8 +18959,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="55.2" hidden="1">
-      <c r="A261" s="95">
+    <row r="261" spans="1:21" ht="55.2">
+      <c r="A261" s="98">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19075,8 +19014,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="100"/>
+    <row r="262" spans="1:21" ht="102" customHeight="1">
+      <c r="A262" s="93"/>
       <c r="B262" s="71" t="s">
         <v>629</v>
       </c>
@@ -19127,8 +19066,8 @@
         <v>636</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="100"/>
+    <row r="263" spans="1:21" ht="102" customHeight="1">
+      <c r="A263" s="93"/>
       <c r="B263" s="71" t="s">
         <v>637</v>
       </c>
@@ -19175,8 +19114,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="55.2" hidden="1">
-      <c r="A264" s="100"/>
+    <row r="264" spans="1:21" ht="55.2">
+      <c r="A264" s="93"/>
       <c r="B264" s="71" t="s">
         <v>637</v>
       </c>
@@ -19225,8 +19164,8 @@
         <v>641</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="46.2" hidden="1" customHeight="1">
-      <c r="A265" s="100"/>
+    <row r="265" spans="1:21" ht="46.2" customHeight="1">
+      <c r="A265" s="93"/>
       <c r="B265" s="71" t="s">
         <v>629</v>
       </c>
@@ -19279,7 +19218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="46.2" hidden="1" customHeight="1">
+    <row r="266" spans="1:21" ht="46.2" customHeight="1">
       <c r="A266" s="67"/>
       <c r="B266" s="71" t="s">
         <v>643</v>
@@ -19336,8 +19275,8 @@
       </c>
       <c r="U266" s="71"/>
     </row>
-    <row r="267" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="89">
+    <row r="267" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A267" s="92">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19394,8 +19333,8 @@
       </c>
       <c r="U267" s="71"/>
     </row>
-    <row r="268" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="89"/>
+    <row r="268" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A268" s="92"/>
       <c r="B268" s="71" t="s">
         <v>643</v>
       </c>
@@ -19450,8 +19389,8 @@
       </c>
       <c r="U268" s="71"/>
     </row>
-    <row r="269" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A269" s="89"/>
+    <row r="269" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A269" s="92"/>
       <c r="B269" s="71" t="s">
         <v>643</v>
       </c>
@@ -19506,8 +19445,8 @@
       </c>
       <c r="U269" s="71"/>
     </row>
-    <row r="270" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A270" s="89"/>
+    <row r="270" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A270" s="92"/>
       <c r="B270" s="71" t="s">
         <v>643</v>
       </c>
@@ -19562,7 +19501,7 @@
       </c>
       <c r="U270" s="66"/>
     </row>
-    <row r="271" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="271" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A271" s="66"/>
       <c r="B271" s="71" t="s">
         <v>653</v>
@@ -19618,8 +19557,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="89">
+    <row r="272" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A272" s="92">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19674,8 +19613,8 @@
       </c>
       <c r="U272" s="71"/>
     </row>
-    <row r="273" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A273" s="89"/>
+    <row r="273" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A273" s="92"/>
       <c r="B273" s="71" t="s">
         <v>653</v>
       </c>
@@ -19730,8 +19669,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="13.8" hidden="1">
-      <c r="A274" s="89"/>
+    <row r="274" spans="1:21" ht="13.8">
+      <c r="A274" s="92"/>
       <c r="B274" s="71" t="s">
         <v>653</v>
       </c>
@@ -19786,8 +19725,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="13.8" hidden="1">
-      <c r="A275" s="89"/>
+    <row r="275" spans="1:21" ht="13.8">
+      <c r="A275" s="92"/>
       <c r="B275" s="71" t="s">
         <v>653</v>
       </c>
@@ -19842,8 +19781,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="13.8" hidden="1">
-      <c r="A276" s="89"/>
+    <row r="276" spans="1:21" ht="13.8">
+      <c r="A276" s="92"/>
       <c r="B276" s="66" t="s">
         <v>660</v>
       </c>
@@ -19898,7 +19837,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="13.8" hidden="1">
+    <row r="277" spans="1:21" ht="13.8">
       <c r="A277" s="66">
         <v>72</v>
       </c>
@@ -19954,7 +19893,7 @@
       </c>
       <c r="U277" s="66"/>
     </row>
-    <row r="278" spans="1:21" ht="13.8" hidden="1">
+    <row r="278" spans="1:21" ht="13.8">
       <c r="A278" s="66"/>
       <c r="B278" s="71" t="s">
         <v>665</v>
@@ -20010,7 +19949,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="13.8" hidden="1">
+    <row r="279" spans="1:21" ht="13.8">
       <c r="A279" s="66"/>
       <c r="B279" s="71" t="s">
         <v>665</v>
@@ -20062,7 +20001,7 @@
       <c r="T279" s="70"/>
       <c r="U279" s="66"/>
     </row>
-    <row r="280" spans="1:21" ht="13.8" hidden="1">
+    <row r="280" spans="1:21" ht="13.8">
       <c r="A280" s="66">
         <v>73</v>
       </c>
@@ -20118,8 +20057,8 @@
       </c>
       <c r="U280" s="66"/>
     </row>
-    <row r="281" spans="1:21" ht="27.6" hidden="1">
-      <c r="A281" s="89">
+    <row r="281" spans="1:21" ht="27.6">
+      <c r="A281" s="92">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20172,8 +20111,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="13.8" hidden="1">
-      <c r="A282" s="89"/>
+    <row r="282" spans="1:21" ht="13.8">
+      <c r="A282" s="92"/>
       <c r="B282" s="71" t="s">
         <v>669</v>
       </c>
@@ -20221,8 +20160,8 @@
       </c>
       <c r="U282" s="66"/>
     </row>
-    <row r="283" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A283" s="89">
+    <row r="283" spans="1:21" ht="37.200000000000003" customHeight="1">
+      <c r="A283" s="92">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20269,15 +20208,15 @@
       <c r="Q283" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R283" s="110"/>
-      <c r="S283" s="112"/>
+      <c r="R283" s="87"/>
+      <c r="S283" s="89"/>
       <c r="T283" s="80"/>
       <c r="U283" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="13.8" hidden="1">
-      <c r="A284" s="89"/>
+    <row r="284" spans="1:21" ht="13.8">
+      <c r="A284" s="92"/>
       <c r="B284" s="71" t="s">
         <v>672</v>
       </c>
@@ -20330,8 +20269,8 @@
       </c>
       <c r="U284" s="71"/>
     </row>
-    <row r="285" spans="1:21" ht="13.8" hidden="1">
-      <c r="A285" s="96">
+    <row r="285" spans="1:21" ht="13.8">
+      <c r="A285" s="94">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20388,8 +20327,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="286" spans="1:21" ht="13.8" hidden="1">
-      <c r="A286" s="96"/>
+    <row r="286" spans="1:21" ht="13.8">
+      <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>676</v>
       </c>
@@ -20444,8 +20383,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="13.8" hidden="1">
-      <c r="A287" s="96"/>
+    <row r="287" spans="1:21" ht="13.8">
+      <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>676</v>
       </c>
@@ -20500,8 +20439,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="13.8" hidden="1">
-      <c r="A288" s="96"/>
+    <row r="288" spans="1:21" ht="13.8">
+      <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>676</v>
       </c>
@@ -20556,8 +20495,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="13.8" hidden="1">
-      <c r="A289" s="89"/>
+    <row r="289" spans="1:21" ht="13.8">
+      <c r="A289" s="92"/>
       <c r="B289" s="71" t="s">
         <v>676</v>
       </c>
@@ -20609,8 +20548,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="27.6" hidden="1">
-      <c r="A290" s="89"/>
+    <row r="290" spans="1:21" ht="27.6">
+      <c r="A290" s="92"/>
       <c r="B290" s="71" t="s">
         <v>676</v>
       </c>
@@ -20663,8 +20602,8 @@
         <v>688</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="13.8" hidden="1">
-      <c r="A291" s="89"/>
+    <row r="291" spans="1:21" ht="13.8">
+      <c r="A291" s="92"/>
       <c r="B291" s="71" t="s">
         <v>676</v>
       </c>
@@ -20719,8 +20658,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="292" spans="1:21" ht="13.8" hidden="1">
-      <c r="A292" s="89"/>
+    <row r="292" spans="1:21" ht="13.8">
+      <c r="A292" s="92"/>
       <c r="B292" s="71" t="s">
         <v>676</v>
       </c>
@@ -20771,8 +20710,8 @@
       </c>
       <c r="U292" s="71"/>
     </row>
-    <row r="293" spans="1:21" ht="13.8" hidden="1">
-      <c r="A293" s="89"/>
+    <row r="293" spans="1:21" ht="13.8">
+      <c r="A293" s="92"/>
       <c r="B293" s="71" t="s">
         <v>676</v>
       </c>
@@ -20825,7 +20764,7 @@
       </c>
       <c r="U293" s="71"/>
     </row>
-    <row r="294" spans="1:21" ht="41.4" hidden="1">
+    <row r="294" spans="1:21" ht="41.4">
       <c r="A294" s="66"/>
       <c r="B294" s="71" t="s">
         <v>691</v>
@@ -20885,8 +20824,8 @@
         <v>695</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="96.6" hidden="1">
-      <c r="A295" s="89">
+    <row r="295" spans="1:21" ht="96.6">
+      <c r="A295" s="92">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -20947,8 +20886,8 @@
         <v>698</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="27.6" hidden="1">
-      <c r="A296" s="89"/>
+    <row r="296" spans="1:21" ht="27.6">
+      <c r="A296" s="92"/>
       <c r="B296" s="71" t="s">
         <v>691</v>
       </c>
@@ -21007,8 +20946,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="13.8" hidden="1">
-      <c r="A297" s="89"/>
+    <row r="297" spans="1:21" ht="13.8">
+      <c r="A297" s="92"/>
       <c r="B297" s="71" t="s">
         <v>691</v>
       </c>
@@ -21067,8 +21006,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="27.6" hidden="1">
-      <c r="A298" s="89">
+    <row r="298" spans="1:21" ht="27.6">
+      <c r="A298" s="92">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21115,15 +21054,15 @@
       <c r="Q298" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R298" s="110"/>
-      <c r="S298" s="112"/>
+      <c r="R298" s="87"/>
+      <c r="S298" s="89"/>
       <c r="T298" s="80"/>
       <c r="U298" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="13.8" hidden="1">
-      <c r="A299" s="89"/>
+    <row r="299" spans="1:21" ht="13.8">
+      <c r="A299" s="92"/>
       <c r="B299" s="71" t="s">
         <v>702</v>
       </c>
@@ -21176,8 +21115,8 @@
       </c>
       <c r="U299" s="71"/>
     </row>
-    <row r="300" spans="1:21" ht="13.8" hidden="1">
-      <c r="A300" s="89"/>
+    <row r="300" spans="1:21" ht="13.8">
+      <c r="A300" s="92"/>
       <c r="B300" s="71" t="s">
         <v>702</v>
       </c>
@@ -21232,8 +21171,8 @@
         <v>709</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="13.8" hidden="1">
-      <c r="A301" s="100"/>
+    <row r="301" spans="1:21" ht="13.8">
+      <c r="A301" s="93"/>
       <c r="B301" s="71" t="s">
         <v>637</v>
       </c>
@@ -21286,8 +21225,8 @@
       </c>
       <c r="U301" s="71"/>
     </row>
-    <row r="302" spans="1:21" ht="13.8" hidden="1">
-      <c r="A302" s="96"/>
+    <row r="302" spans="1:21" ht="13.8">
+      <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>637</v>
       </c>
@@ -21342,8 +21281,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="27.6" hidden="1">
-      <c r="A303" s="95">
+    <row r="303" spans="1:21" ht="27.6">
+      <c r="A303" s="98">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21397,8 +21336,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="13.8" hidden="1">
-      <c r="A304" s="100"/>
+    <row r="304" spans="1:21" ht="13.8">
+      <c r="A304" s="93"/>
       <c r="B304" s="71" t="s">
         <v>716</v>
       </c>
@@ -21451,8 +21390,8 @@
       </c>
       <c r="U304" s="71"/>
     </row>
-    <row r="305" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="95">
+    <row r="305" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A305" s="98">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21505,8 +21444,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="100"/>
+    <row r="306" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A306" s="93"/>
       <c r="B306" s="71" t="s">
         <v>718</v>
       </c>
@@ -21559,8 +21498,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="100"/>
+    <row r="307" spans="1:21" ht="81.599999999999994" customHeight="1">
+      <c r="A307" s="93"/>
       <c r="B307" s="71" t="s">
         <v>718</v>
       </c>
@@ -21605,15 +21544,15 @@
       <c r="Q307" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R307" s="110"/>
-      <c r="S307" s="112"/>
+      <c r="R307" s="87"/>
+      <c r="S307" s="89"/>
       <c r="T307" s="80"/>
       <c r="U307" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A308" s="96"/>
+    <row r="308" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>718</v>
       </c>
@@ -21665,7 +21604,7 @@
       </c>
       <c r="U308" s="66"/>
     </row>
-    <row r="309" spans="1:21" ht="126" hidden="1" customHeight="1">
+    <row r="309" spans="1:21" ht="126" customHeight="1">
       <c r="A309" s="66">
         <v>82</v>
       </c>
@@ -21719,14 +21658,14 @@
       <c r="Q309" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R309" s="110"/>
-      <c r="S309" s="112"/>
+      <c r="R309" s="87"/>
+      <c r="S309" s="89"/>
       <c r="T309" s="80"/>
       <c r="U309" s="71" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="310" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A310" s="66">
         <v>83</v>
       </c>
@@ -21739,56 +21678,56 @@
       <c r="D310" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E310" s="97">
+      <c r="E310" s="104">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="106" t="s">
+      <c r="F310" s="103" t="s">
         <v>729</v>
       </c>
-      <c r="G310" s="89" t="s">
+      <c r="G310" s="92" t="s">
         <v>730</v>
       </c>
-      <c r="H310" s="89">
+      <c r="H310" s="92">
         <v>13.3</v>
       </c>
-      <c r="I310" s="95" t="s">
+      <c r="I310" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="J310" s="95" t="s">
+      <c r="J310" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="K310" s="93">
+      <c r="K310" s="95">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="93">
+      <c r="L310" s="95">
         <v>0</v>
       </c>
-      <c r="M310" s="93">
+      <c r="M310" s="95">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="90" t="s">
+      <c r="N310" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="O310" s="90" t="s">
+      <c r="O310" s="97" t="s">
         <v>731</v>
       </c>
-      <c r="P310" s="89">
+      <c r="P310" s="92">
         <v>2025</v>
       </c>
-      <c r="Q310" s="90" t="s">
+      <c r="Q310" s="97" t="s">
         <v>37</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
-      <c r="T310" s="89"/>
-      <c r="U310" s="89" t="s">
+      <c r="T310" s="92"/>
+      <c r="U310" s="92" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="89">
+    <row r="311" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A311" s="92">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -21800,26 +21739,26 @@
       <c r="D311" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E311" s="98"/>
-      <c r="F311" s="90"/>
-      <c r="G311" s="89"/>
-      <c r="H311" s="89"/>
-      <c r="I311" s="96"/>
-      <c r="J311" s="96"/>
-      <c r="K311" s="93"/>
-      <c r="L311" s="93"/>
-      <c r="M311" s="93"/>
-      <c r="N311" s="90"/>
-      <c r="O311" s="90"/>
-      <c r="P311" s="89"/>
-      <c r="Q311" s="90"/>
+      <c r="E311" s="105"/>
+      <c r="F311" s="97"/>
+      <c r="G311" s="92"/>
+      <c r="H311" s="92"/>
+      <c r="I311" s="94"/>
+      <c r="J311" s="94"/>
+      <c r="K311" s="95"/>
+      <c r="L311" s="95"/>
+      <c r="M311" s="95"/>
+      <c r="N311" s="97"/>
+      <c r="O311" s="97"/>
+      <c r="P311" s="92"/>
+      <c r="Q311" s="97"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
-      <c r="T311" s="89"/>
-      <c r="U311" s="89"/>
-    </row>
-    <row r="312" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="89"/>
+      <c r="T311" s="92"/>
+      <c r="U311" s="92"/>
+    </row>
+    <row r="312" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A312" s="92"/>
       <c r="B312" s="71" t="s">
         <v>728</v>
       </c>
@@ -21829,57 +21768,57 @@
       <c r="D312" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E312" s="97">
+      <c r="E312" s="104">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="90" t="s">
+      <c r="F312" s="97" t="s">
         <v>733</v>
       </c>
-      <c r="G312" s="89" t="s">
+      <c r="G312" s="92" t="s">
         <v>734</v>
       </c>
-      <c r="H312" s="89">
+      <c r="H312" s="92">
         <v>31.12</v>
       </c>
-      <c r="I312" s="95" t="s">
+      <c r="I312" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="J312" s="95" t="s">
+      <c r="J312" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="K312" s="93">
+      <c r="K312" s="95">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="93">
+      <c r="L312" s="95">
         <v>0</v>
       </c>
-      <c r="M312" s="93">
+      <c r="M312" s="95">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="90" t="s">
+      <c r="N312" s="97" t="s">
         <v>735</v>
       </c>
-      <c r="O312" s="90" t="s">
+      <c r="O312" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="P312" s="89">
+      <c r="P312" s="92">
         <v>2019</v>
       </c>
-      <c r="Q312" s="90" t="s">
+      <c r="Q312" s="97" t="s">
         <v>51</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
-      <c r="T312" s="107">
+      <c r="T312" s="96">
         <v>1</v>
       </c>
-      <c r="U312" s="89" t="s">
+      <c r="U312" s="92" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="89"/>
+    <row r="313" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A313" s="92"/>
       <c r="B313" s="71" t="s">
         <v>732</v>
       </c>
@@ -21889,26 +21828,26 @@
       <c r="D313" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E313" s="98"/>
-      <c r="F313" s="90"/>
-      <c r="G313" s="89"/>
-      <c r="H313" s="89"/>
-      <c r="I313" s="96"/>
-      <c r="J313" s="96"/>
-      <c r="K313" s="93"/>
-      <c r="L313" s="93"/>
-      <c r="M313" s="93"/>
-      <c r="N313" s="90"/>
-      <c r="O313" s="90"/>
-      <c r="P313" s="89"/>
-      <c r="Q313" s="90"/>
+      <c r="E313" s="105"/>
+      <c r="F313" s="97"/>
+      <c r="G313" s="92"/>
+      <c r="H313" s="92"/>
+      <c r="I313" s="94"/>
+      <c r="J313" s="94"/>
+      <c r="K313" s="95"/>
+      <c r="L313" s="95"/>
+      <c r="M313" s="95"/>
+      <c r="N313" s="97"/>
+      <c r="O313" s="97"/>
+      <c r="P313" s="92"/>
+      <c r="Q313" s="97"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
-      <c r="T313" s="107"/>
-      <c r="U313" s="89"/>
-    </row>
-    <row r="314" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="89"/>
+      <c r="T313" s="96"/>
+      <c r="U313" s="92"/>
+    </row>
+    <row r="314" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A314" s="92"/>
       <c r="B314" s="71" t="s">
         <v>732</v>
       </c>
@@ -21965,8 +21904,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A315" s="89"/>
+    <row r="315" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A315" s="92"/>
       <c r="B315" s="71" t="s">
         <v>732</v>
       </c>
@@ -22021,8 +21960,8 @@
       </c>
       <c r="U315" s="71"/>
     </row>
-    <row r="316" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A316" s="89"/>
+    <row r="316" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A316" s="92"/>
       <c r="B316" s="71" t="s">
         <v>732</v>
       </c>
@@ -22078,7 +22017,7 @@
       </c>
       <c r="U316" s="71"/>
     </row>
-    <row r="317" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="317" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A317" s="72"/>
       <c r="B317" s="71" t="s">
         <v>738</v>
@@ -22132,7 +22071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
+    <row r="318" spans="1:21" ht="40.950000000000003" customHeight="1">
       <c r="A318" s="72"/>
       <c r="B318" s="71" t="s">
         <v>738</v>
@@ -22175,8 +22114,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A319" s="95">
+    <row r="319" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A319" s="98">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22224,8 +22163,8 @@
       <c r="T319" s="80"/>
       <c r="U319" s="71"/>
     </row>
-    <row r="320" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A320" s="96"/>
+    <row r="320" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>738</v>
       </c>
@@ -22270,15 +22209,15 @@
       <c r="Q320" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R320" s="110"/>
-      <c r="S320" s="112"/>
+      <c r="R320" s="87"/>
+      <c r="S320" s="89"/>
       <c r="T320" s="80"/>
       <c r="U320" s="71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A321" s="101">
+    <row r="321" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A321" s="99">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22331,8 +22270,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A322" s="102"/>
+    <row r="322" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>744</v>
       </c>
@@ -22381,8 +22320,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A323" s="102"/>
+    <row r="323" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>744</v>
       </c>
@@ -22435,8 +22374,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A324" s="102"/>
+    <row r="324" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>744</v>
       </c>
@@ -22489,8 +22428,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="100"/>
+    <row r="325" spans="1:21" ht="93" customHeight="1">
+      <c r="A325" s="93"/>
       <c r="B325" s="66" t="s">
         <v>744</v>
       </c>
@@ -22541,8 +22480,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A326" s="100"/>
+    <row r="326" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A326" s="93"/>
       <c r="B326" s="66" t="s">
         <v>744</v>
       </c>
@@ -22593,8 +22532,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A327" s="102"/>
+    <row r="327" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>744</v>
       </c>
@@ -22649,8 +22588,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A328" s="102"/>
+    <row r="328" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>744</v>
       </c>
@@ -22701,8 +22640,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A329" s="102"/>
+    <row r="329" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>744</v>
       </c>
@@ -22755,8 +22694,8 @@
       </c>
       <c r="U329" s="71"/>
     </row>
-    <row r="330" spans="1:21" ht="13.8" hidden="1">
-      <c r="A330" s="103"/>
+    <row r="330" spans="1:21" ht="13.8">
+      <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>744</v>
       </c>
@@ -22809,7 +22748,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="331" spans="1:21" ht="41.4" hidden="1" customHeight="1">
+    <row r="331" spans="1:21" ht="41.4" customHeight="1">
       <c r="A331" s="68"/>
       <c r="B331" s="71" t="s">
         <v>762</v>
@@ -22861,7 +22800,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="332" spans="1:21" ht="13.8" hidden="1">
+    <row r="332" spans="1:21" ht="13.8">
       <c r="A332" s="66">
         <v>88</v>
       </c>
@@ -22890,7 +22829,7 @@
       <c r="T332" s="66"/>
       <c r="U332" s="66"/>
     </row>
-    <row r="333" spans="1:21" ht="41.4" hidden="1">
+    <row r="333" spans="1:21" ht="41.4">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>765</v>
@@ -22942,7 +22881,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="334" spans="1:21" ht="13.8" hidden="1">
+    <row r="334" spans="1:21" ht="13.8">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>765</v>
@@ -22987,8 +22926,8 @@
         <v>588</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="41.4" hidden="1">
-      <c r="A335" s="95">
+    <row r="335" spans="1:21" ht="41.4">
+      <c r="A335" s="98">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -23049,8 +22988,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="336" spans="1:21" ht="44.4" hidden="1" customHeight="1">
-      <c r="A336" s="100"/>
+    <row r="336" spans="1:21" ht="44.4" customHeight="1">
+      <c r="A336" s="93"/>
       <c r="B336" s="71" t="s">
         <v>765</v>
       </c>
@@ -23095,15 +23034,15 @@
       <c r="Q336" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R336" s="110"/>
-      <c r="S336" s="112"/>
+      <c r="R336" s="87"/>
+      <c r="S336" s="89"/>
       <c r="T336" s="80"/>
       <c r="U336" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="337" spans="1:22" ht="155.4" hidden="1" customHeight="1">
-      <c r="A337" s="100"/>
+    <row r="337" spans="1:22" ht="155.4" customHeight="1">
+      <c r="A337" s="93"/>
       <c r="B337" s="71" t="s">
         <v>765</v>
       </c>
@@ -23155,8 +23094,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="338" spans="1:22" ht="13.8" hidden="1">
-      <c r="A338" s="96"/>
+    <row r="338" spans="1:22" ht="13.8">
+      <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>765</v>
       </c>
@@ -23211,7 +23150,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="339" spans="1:22" ht="27.6" hidden="1">
+    <row r="339" spans="1:22" ht="27.6">
       <c r="A339" s="68"/>
       <c r="B339" s="71" t="s">
         <v>773</v>
@@ -23257,8 +23196,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="340" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A340" s="89">
+    <row r="340" spans="1:22" ht="40.950000000000003" customHeight="1">
+      <c r="A340" s="92">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23315,8 +23254,8 @@
       </c>
       <c r="V340" s="33"/>
     </row>
-    <row r="341" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A341" s="89"/>
+    <row r="341" spans="1:22" ht="20.399999999999999" customHeight="1">
+      <c r="A341" s="92"/>
       <c r="B341" s="71" t="s">
         <v>773</v>
       </c>
@@ -23370,8 +23309,8 @@
       <c r="U341" s="66"/>
       <c r="V341" s="33"/>
     </row>
-    <row r="342" spans="1:22" ht="13.8" hidden="1">
-      <c r="A342" s="89">
+    <row r="342" spans="1:22" ht="13.8">
+      <c r="A342" s="92">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23428,8 +23367,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="343" spans="1:22" ht="13.8" hidden="1">
-      <c r="A343" s="89"/>
+    <row r="343" spans="1:22" ht="13.8">
+      <c r="A343" s="92"/>
       <c r="B343" s="71" t="s">
         <v>776</v>
       </c>
@@ -23484,8 +23423,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="344" spans="1:22" ht="27.6" hidden="1">
-      <c r="A344" s="89"/>
+    <row r="344" spans="1:22" ht="27.6">
+      <c r="A344" s="92"/>
       <c r="B344" s="71" t="s">
         <v>776</v>
       </c>
@@ -23536,8 +23475,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="345" spans="1:22" ht="13.8" hidden="1">
-      <c r="A345" s="89"/>
+    <row r="345" spans="1:22" ht="13.8">
+      <c r="A345" s="92"/>
       <c r="B345" s="71" t="s">
         <v>776</v>
       </c>
@@ -23592,8 +23531,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="346" spans="1:22" ht="27.6" hidden="1">
-      <c r="A346" s="89"/>
+    <row r="346" spans="1:22" ht="27.6">
+      <c r="A346" s="92"/>
       <c r="B346" s="71" t="s">
         <v>776</v>
       </c>
@@ -23645,8 +23584,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="347" spans="1:22" ht="27.6" hidden="1">
-      <c r="A347" s="89"/>
+    <row r="347" spans="1:22" ht="27.6">
+      <c r="A347" s="92"/>
       <c r="B347" s="71" t="s">
         <v>776</v>
       </c>
@@ -23691,8 +23630,8 @@
         <v>787</v>
       </c>
     </row>
-    <row r="348" spans="1:22" ht="13.8" hidden="1">
-      <c r="A348" s="89"/>
+    <row r="348" spans="1:22" ht="13.8">
+      <c r="A348" s="92"/>
       <c r="B348" s="71" t="s">
         <v>776</v>
       </c>
@@ -23747,8 +23686,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="349" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="89">
+    <row r="349" spans="1:22" ht="61.2" customHeight="1">
+      <c r="A349" s="92">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -23804,8 +23743,8 @@
       </c>
       <c r="U349" s="71"/>
     </row>
-    <row r="350" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A350" s="89"/>
+    <row r="350" spans="1:22" ht="61.2" customHeight="1">
+      <c r="A350" s="92"/>
       <c r="B350" s="71" t="s">
         <v>788</v>
       </c>
@@ -23858,8 +23797,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="351" spans="1:22" ht="13.8" hidden="1">
-      <c r="A351" s="89"/>
+    <row r="351" spans="1:22" ht="13.8">
+      <c r="A351" s="92"/>
       <c r="B351" s="71" t="s">
         <v>788</v>
       </c>
@@ -23914,8 +23853,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="352" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="89">
+    <row r="352" spans="1:22" ht="94.2" customHeight="1">
+      <c r="A352" s="92">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -23972,8 +23911,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="353" spans="1:21" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="89"/>
+    <row r="353" spans="1:21" ht="94.2" customHeight="1">
+      <c r="A353" s="92"/>
       <c r="B353" s="71" t="s">
         <v>793</v>
       </c>
@@ -24025,8 +23964,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="354" spans="1:21" ht="94.2" hidden="1" customHeight="1">
-      <c r="A354" s="89"/>
+    <row r="354" spans="1:21" ht="94.2" customHeight="1">
+      <c r="A354" s="92"/>
       <c r="B354" s="71" t="s">
         <v>793</v>
       </c>
@@ -24081,8 +24020,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="46.95" hidden="1" customHeight="1">
-      <c r="A355" s="89"/>
+    <row r="355" spans="1:21" ht="46.95" customHeight="1">
+      <c r="A355" s="92"/>
       <c r="B355" s="71" t="s">
         <v>793</v>
       </c>
@@ -24141,8 +24080,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="13.8" hidden="1">
-      <c r="A356" s="89"/>
+    <row r="356" spans="1:21" ht="13.8">
+      <c r="A356" s="92"/>
       <c r="B356" s="71" t="s">
         <v>793</v>
       </c>
@@ -24195,8 +24134,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="357" spans="1:21" ht="13.8" hidden="1">
-      <c r="A357" s="89"/>
+    <row r="357" spans="1:21" ht="13.8">
+      <c r="A357" s="92"/>
       <c r="B357" s="71" t="s">
         <v>793</v>
       </c>
@@ -24251,7 +24190,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
+    <row r="358" spans="1:21" ht="81.599999999999994" customHeight="1">
       <c r="A358" s="66"/>
       <c r="B358" s="71" t="s">
         <v>802</v>
@@ -24307,7 +24246,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
+    <row r="359" spans="1:21" ht="81.599999999999994" customHeight="1">
       <c r="A359" s="66"/>
       <c r="B359" s="71" t="s">
         <v>802</v>
@@ -24360,7 +24299,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="360" spans="1:21" ht="65.400000000000006" hidden="1" customHeight="1">
+    <row r="360" spans="1:21" ht="65.400000000000006" customHeight="1">
       <c r="A360" s="48">
         <v>94</v>
       </c>
@@ -24408,14 +24347,14 @@
       <c r="Q360" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R360" s="110"/>
-      <c r="S360" s="112"/>
+      <c r="R360" s="87"/>
+      <c r="S360" s="89"/>
       <c r="T360" s="80"/>
       <c r="U360" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="361" spans="1:21" ht="27.6" hidden="1">
+    <row r="361" spans="1:21" ht="27.6">
       <c r="A361" s="48"/>
       <c r="B361" s="71" t="s">
         <v>802</v>
@@ -24471,7 +24410,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="27.6" hidden="1">
+    <row r="362" spans="1:21" ht="27.6">
       <c r="A362" s="48"/>
       <c r="B362" s="71" t="s">
         <v>802</v>
@@ -24528,8 +24467,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="13.8" hidden="1">
-      <c r="A363" s="89"/>
+    <row r="363" spans="1:21" ht="13.8">
+      <c r="A363" s="92"/>
       <c r="B363" s="71" t="s">
         <v>813</v>
       </c>
@@ -24583,8 +24522,8 @@
       </c>
       <c r="U363" s="71"/>
     </row>
-    <row r="364" spans="1:21" ht="13.8" hidden="1">
-      <c r="A364" s="89"/>
+    <row r="364" spans="1:21" ht="13.8">
+      <c r="A364" s="92"/>
       <c r="B364" s="71" t="s">
         <v>813</v>
       </c>
@@ -24639,7 +24578,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="13.8" hidden="1">
+    <row r="365" spans="1:21" ht="13.8">
       <c r="A365" s="68">
         <v>96</v>
       </c>
@@ -24695,7 +24634,7 @@
       </c>
       <c r="U365" s="66"/>
     </row>
-    <row r="366" spans="1:21" ht="13.8" hidden="1">
+    <row r="366" spans="1:21" ht="13.8">
       <c r="A366" s="68"/>
       <c r="B366" s="71" t="s">
         <v>817</v>
@@ -24749,7 +24688,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="13.8" hidden="1">
+    <row r="367" spans="1:21" ht="13.8">
       <c r="A367" s="66">
         <v>96</v>
       </c>
@@ -24805,8 +24744,8 @@
       </c>
       <c r="U367" s="71"/>
     </row>
-    <row r="368" spans="1:21" ht="27.6" hidden="1">
-      <c r="A368" s="95">
+    <row r="368" spans="1:21" ht="27.6">
+      <c r="A368" s="98">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -24856,8 +24795,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="369" spans="1:21" ht="41.4" hidden="1">
-      <c r="A369" s="100"/>
+    <row r="369" spans="1:21" ht="41.4">
+      <c r="A369" s="93"/>
       <c r="B369" s="71" t="s">
         <v>820</v>
       </c>
@@ -24916,8 +24855,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="27.6" hidden="1">
-      <c r="A370" s="100"/>
+    <row r="370" spans="1:21" ht="27.6">
+      <c r="A370" s="93"/>
       <c r="B370" s="71" t="s">
         <v>820</v>
       </c>
@@ -24969,8 +24908,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="27.6" hidden="1">
-      <c r="A371" s="100"/>
+    <row r="371" spans="1:21" ht="27.6">
+      <c r="A371" s="93"/>
       <c r="B371" s="71" t="s">
         <v>820</v>
       </c>
@@ -25025,8 +24964,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="27.6" hidden="1">
-      <c r="A372" s="96"/>
+    <row r="372" spans="1:21" ht="27.6">
+      <c r="A372" s="94"/>
       <c r="B372" s="71" t="s">
         <v>820</v>
       </c>
@@ -25080,8 +25019,8 @@
       </c>
       <c r="U372" s="71"/>
     </row>
-    <row r="373" spans="1:21" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A373" s="89">
+    <row r="373" spans="1:21" ht="148.94999999999999" customHeight="1">
+      <c r="A373" s="92">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25135,8 +25074,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="89"/>
+    <row r="374" spans="1:21" ht="40.200000000000003" customHeight="1">
+      <c r="A374" s="92"/>
       <c r="B374" s="71" t="s">
         <v>826</v>
       </c>
@@ -25181,15 +25120,15 @@
       <c r="Q374" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R374" s="110"/>
-      <c r="S374" s="112"/>
+      <c r="R374" s="87"/>
+      <c r="S374" s="89"/>
       <c r="T374" s="80"/>
       <c r="U374" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="89"/>
+    <row r="375" spans="1:21" ht="34.950000000000003" customHeight="1">
+      <c r="A375" s="92"/>
       <c r="B375" s="71" t="s">
         <v>826</v>
       </c>
@@ -25234,15 +25173,15 @@
       <c r="Q375" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R375" s="110"/>
-      <c r="S375" s="112"/>
+      <c r="R375" s="87"/>
+      <c r="S375" s="89"/>
       <c r="T375" s="80"/>
       <c r="U375" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A376" s="89"/>
+    <row r="376" spans="1:21" ht="37.950000000000003" customHeight="1">
+      <c r="A376" s="92"/>
       <c r="B376" s="71" t="s">
         <v>826</v>
       </c>
@@ -25287,15 +25226,15 @@
       <c r="Q376" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R376" s="110"/>
-      <c r="S376" s="112"/>
+      <c r="R376" s="87"/>
+      <c r="S376" s="89"/>
       <c r="T376" s="80"/>
       <c r="U376" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A377" s="89"/>
+    <row r="377" spans="1:21" ht="122.4" customHeight="1">
+      <c r="A377" s="92"/>
       <c r="B377" s="71" t="s">
         <v>826</v>
       </c>
@@ -25337,8 +25276,8 @@
         <v>839</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A378" s="89"/>
+    <row r="378" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A378" s="92"/>
       <c r="B378" s="71" t="s">
         <v>826</v>
       </c>
@@ -25389,8 +25328,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A379" s="89"/>
+    <row r="379" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A379" s="92"/>
       <c r="B379" s="71" t="s">
         <v>826</v>
       </c>
@@ -25441,8 +25380,8 @@
         <v>842</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A380" s="89"/>
+    <row r="380" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A380" s="92"/>
       <c r="B380" s="71" t="s">
         <v>826</v>
       </c>
@@ -25487,8 +25426,8 @@
         <v>844</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="13.8" hidden="1">
-      <c r="A381" s="89"/>
+    <row r="381" spans="1:21" ht="13.8">
+      <c r="A381" s="92"/>
       <c r="B381" s="71" t="s">
         <v>826</v>
       </c>
@@ -25536,8 +25475,8 @@
       </c>
       <c r="U381" s="71"/>
     </row>
-    <row r="382" spans="1:21" ht="13.8" hidden="1">
-      <c r="A382" s="89"/>
+    <row r="382" spans="1:21" ht="13.8">
+      <c r="A382" s="92"/>
       <c r="B382" s="71" t="s">
         <v>826</v>
       </c>
@@ -25590,8 +25529,8 @@
       </c>
       <c r="U382" s="71"/>
     </row>
-    <row r="383" spans="1:21" ht="13.8" hidden="1">
-      <c r="A383" s="89"/>
+    <row r="383" spans="1:21" ht="13.8">
+      <c r="A383" s="92"/>
       <c r="B383" s="71" t="s">
         <v>826</v>
       </c>
@@ -25642,8 +25581,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="13.8" hidden="1">
-      <c r="A384" s="89"/>
+    <row r="384" spans="1:21" ht="13.8">
+      <c r="A384" s="92"/>
       <c r="B384" s="71" t="s">
         <v>826</v>
       </c>
@@ -25696,8 +25635,8 @@
       </c>
       <c r="U384" s="71"/>
     </row>
-    <row r="385" spans="1:21" ht="27.6" hidden="1">
-      <c r="A385" s="96">
+    <row r="385" spans="1:21" ht="27.6">
+      <c r="A385" s="94">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -25744,15 +25683,15 @@
       <c r="Q385" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="R385" s="110"/>
-      <c r="S385" s="112"/>
+      <c r="R385" s="87"/>
+      <c r="S385" s="89"/>
       <c r="T385" s="80"/>
       <c r="U385" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A386" s="89"/>
+    <row r="386" spans="1:21" ht="163.19999999999999" customHeight="1">
+      <c r="A386" s="92"/>
       <c r="B386" s="71" t="s">
         <v>854</v>
       </c>
@@ -25804,8 +25743,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A387" s="89"/>
+    <row r="387" spans="1:21" ht="61.2" customHeight="1">
+      <c r="A387" s="92"/>
       <c r="B387" s="71" t="s">
         <v>854</v>
       </c>
@@ -25860,8 +25799,8 @@
       </c>
       <c r="U387" s="71"/>
     </row>
-    <row r="388" spans="1:21" ht="13.8" hidden="1">
-      <c r="A388" s="89"/>
+    <row r="388" spans="1:21" ht="13.8">
+      <c r="A388" s="92"/>
       <c r="B388" s="71" t="s">
         <v>854</v>
       </c>
@@ -25914,8 +25853,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="13.8" hidden="1">
-      <c r="A389" s="89"/>
+    <row r="389" spans="1:21" ht="13.8">
+      <c r="A389" s="92"/>
       <c r="B389" s="71" t="s">
         <v>853</v>
       </c>
@@ -25968,8 +25907,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="13.8" hidden="1">
-      <c r="A390" s="89"/>
+    <row r="390" spans="1:21" ht="13.8">
+      <c r="A390" s="92"/>
       <c r="B390" s="71" t="s">
         <v>853</v>
       </c>
@@ -26024,8 +25963,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="13.8" hidden="1">
-      <c r="A391" s="89"/>
+    <row r="391" spans="1:21" ht="13.8">
+      <c r="A391" s="92"/>
       <c r="B391" s="71" t="s">
         <v>853</v>
       </c>
@@ -26065,8 +26004,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="13.8" hidden="1">
-      <c r="A392" s="89"/>
+    <row r="392" spans="1:21" ht="13.8">
+      <c r="A392" s="92"/>
       <c r="B392" s="66" t="s">
         <v>853</v>
       </c>
@@ -26119,7 +26058,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="148.19999999999999" hidden="1" customHeight="1">
+    <row r="393" spans="1:21" ht="148.19999999999999" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>863</v>
@@ -26172,8 +26111,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="58.2" hidden="1" customHeight="1">
-      <c r="A394" s="89">
+    <row r="394" spans="1:21" ht="58.2" customHeight="1">
+      <c r="A394" s="92">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26220,15 +26159,15 @@
       <c r="Q394" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R394" s="110"/>
-      <c r="S394" s="112"/>
+      <c r="R394" s="87"/>
+      <c r="S394" s="89"/>
       <c r="T394" s="80"/>
       <c r="U394" s="71" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="41.4" hidden="1">
-      <c r="A395" s="89"/>
+    <row r="395" spans="1:21" ht="41.4">
+      <c r="A395" s="92"/>
       <c r="B395" s="66" t="s">
         <v>863</v>
       </c>
@@ -26273,15 +26212,15 @@
       <c r="Q395" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R395" s="110"/>
-      <c r="S395" s="112"/>
+      <c r="R395" s="87"/>
+      <c r="S395" s="89"/>
       <c r="T395" s="80"/>
       <c r="U395" s="71" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="89"/>
+    <row r="396" spans="1:21" ht="18" customHeight="1">
+      <c r="A396" s="92"/>
       <c r="B396" s="71" t="s">
         <v>863</v>
       </c>
@@ -26336,8 +26275,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="27.6" hidden="1">
-      <c r="A397" s="89"/>
+    <row r="397" spans="1:21" ht="27.6">
+      <c r="A397" s="92"/>
       <c r="B397" s="71" t="s">
         <v>863</v>
       </c>
@@ -26388,8 +26327,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="18" hidden="1" customHeight="1">
-      <c r="A398" s="89"/>
+    <row r="398" spans="1:21" ht="18" customHeight="1">
+      <c r="A398" s="92"/>
       <c r="B398" s="71" t="s">
         <v>863</v>
       </c>
@@ -26442,8 +26381,8 @@
       </c>
       <c r="U398" s="71"/>
     </row>
-    <row r="399" spans="1:21" ht="13.8" hidden="1">
-      <c r="A399" s="89"/>
+    <row r="399" spans="1:21" ht="13.8">
+      <c r="A399" s="92"/>
       <c r="B399" s="71" t="s">
         <v>863</v>
       </c>
@@ -26496,8 +26435,8 @@
       </c>
       <c r="U399" s="71"/>
     </row>
-    <row r="400" spans="1:21" ht="27.6" hidden="1">
-      <c r="A400" s="104">
+    <row r="400" spans="1:21" ht="27.6">
+      <c r="A400" s="102">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26546,15 +26485,15 @@
       <c r="Q400" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="R400" s="110"/>
-      <c r="S400" s="112"/>
+      <c r="R400" s="87"/>
+      <c r="S400" s="89"/>
       <c r="T400" s="80"/>
       <c r="U400" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A401" s="104"/>
+    <row r="401" spans="1:21" ht="31.95" customHeight="1">
+      <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
         <v>873</v>
       </c>
@@ -26594,8 +26533,8 @@
       <c r="T401" s="80"/>
       <c r="U401" s="66"/>
     </row>
-    <row r="402" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A402" s="104"/>
+    <row r="402" spans="1:21" ht="31.95" customHeight="1">
+      <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
         <v>873</v>
       </c>
@@ -26648,8 +26587,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A403" s="104"/>
+    <row r="403" spans="1:21" ht="31.95" customHeight="1">
+      <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
         <v>873</v>
       </c>
@@ -26704,8 +26643,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A404" s="104"/>
+    <row r="404" spans="1:21" ht="31.95" customHeight="1">
+      <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
         <v>873</v>
       </c>
@@ -26758,8 +26697,8 @@
       </c>
       <c r="U404" s="71"/>
     </row>
-    <row r="405" spans="1:21" ht="13.8" hidden="1">
-      <c r="A405" s="104"/>
+    <row r="405" spans="1:21" ht="13.8">
+      <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
         <v>873</v>
       </c>
@@ -26814,8 +26753,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="89">
+    <row r="406" spans="1:21" ht="36" customHeight="1">
+      <c r="A406" s="92">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -26862,15 +26801,15 @@
       <c r="Q406" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="R406" s="110"/>
-      <c r="S406" s="112"/>
+      <c r="R406" s="87"/>
+      <c r="S406" s="89"/>
       <c r="T406" s="80"/>
       <c r="U406" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="13.8" hidden="1">
-      <c r="A407" s="89"/>
+    <row r="407" spans="1:21" ht="13.8">
+      <c r="A407" s="92"/>
       <c r="B407" s="71" t="s">
         <v>880</v>
       </c>
@@ -26925,8 +26864,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="89">
+    <row r="408" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A408" s="92">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -26981,8 +26920,8 @@
         <v>591</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="89"/>
+    <row r="409" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A409" s="92"/>
       <c r="B409" s="71" t="s">
         <v>884</v>
       </c>
@@ -27037,8 +26976,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A410" s="89"/>
+    <row r="410" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A410" s="92"/>
       <c r="B410" s="71" t="s">
         <v>884</v>
       </c>
@@ -27092,8 +27031,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="13.8" hidden="1">
-      <c r="A411" s="89"/>
+    <row r="411" spans="1:21" ht="13.8">
+      <c r="A411" s="92"/>
       <c r="B411" s="71" t="s">
         <v>884</v>
       </c>
@@ -27148,8 +27087,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="89">
+    <row r="412" spans="1:21" ht="60" customHeight="1">
+      <c r="A412" s="92">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27196,15 +27135,15 @@
       <c r="Q412" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R412" s="110"/>
-      <c r="S412" s="112"/>
+      <c r="R412" s="87"/>
+      <c r="S412" s="89"/>
       <c r="T412" s="80"/>
       <c r="U412" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="413" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="89"/>
+    <row r="413" spans="1:21" ht="60" customHeight="1">
+      <c r="A413" s="92"/>
       <c r="B413" s="71" t="s">
         <v>889</v>
       </c>
@@ -27263,8 +27202,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="414" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="89"/>
+    <row r="414" spans="1:21" ht="60" customHeight="1">
+      <c r="A414" s="92"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27286,8 +27225,8 @@
       <c r="T414" s="80"/>
       <c r="U414" s="71"/>
     </row>
-    <row r="415" spans="1:21" ht="55.2" hidden="1">
-      <c r="A415" s="89"/>
+    <row r="415" spans="1:21" ht="55.2">
+      <c r="A415" s="92"/>
       <c r="B415" s="71" t="s">
         <v>889</v>
       </c>
@@ -27339,8 +27278,8 @@
         <v>895</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A416" s="89"/>
+    <row r="416" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A416" s="92"/>
       <c r="B416" s="71" t="s">
         <v>889</v>
       </c>
@@ -27394,8 +27333,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="417" spans="1:21" ht="41.4" hidden="1">
-      <c r="A417" s="89">
+    <row r="417" spans="1:21" ht="41.4">
+      <c r="A417" s="92">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27442,15 +27381,15 @@
       <c r="Q417" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R417" s="110"/>
-      <c r="S417" s="112"/>
+      <c r="R417" s="87"/>
+      <c r="S417" s="89"/>
       <c r="T417" s="80"/>
       <c r="U417" s="71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A418" s="89"/>
+    <row r="418" spans="1:21" ht="142.94999999999999" customHeight="1">
+      <c r="A418" s="92"/>
       <c r="B418" s="71" t="s">
         <v>896</v>
       </c>
@@ -27496,8 +27435,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="13.8" hidden="1">
-      <c r="A419" s="89"/>
+    <row r="419" spans="1:21" ht="13.8">
+      <c r="A419" s="92"/>
       <c r="B419" s="71" t="s">
         <v>896</v>
       </c>
@@ -27552,8 +27491,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="13.8" hidden="1">
-      <c r="A420" s="89"/>
+    <row r="420" spans="1:21" ht="13.8">
+      <c r="A420" s="92"/>
       <c r="B420" s="71" t="s">
         <v>896</v>
       </c>
@@ -27608,8 +27547,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="13.8" hidden="1">
-      <c r="A421" s="89"/>
+    <row r="421" spans="1:21" ht="13.8">
+      <c r="A421" s="92"/>
       <c r="B421" s="71" t="s">
         <v>896</v>
       </c>
@@ -27664,8 +27603,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="27.6" hidden="1">
-      <c r="A422" s="89"/>
+    <row r="422" spans="1:21" ht="27.6">
+      <c r="A422" s="92"/>
       <c r="B422" s="71" t="s">
         <v>896</v>
       </c>
@@ -27707,8 +27646,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="423" spans="1:21" ht="13.8" hidden="1">
-      <c r="A423" s="89"/>
+    <row r="423" spans="1:21" ht="13.8">
+      <c r="A423" s="92"/>
       <c r="B423" s="71" t="s">
         <v>896</v>
       </c>
@@ -27757,8 +27696,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A424" s="89"/>
+    <row r="424" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A424" s="92"/>
       <c r="B424" s="71" t="s">
         <v>896</v>
       </c>
@@ -27812,7 +27751,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="27.6" hidden="1">
+    <row r="425" spans="1:21" ht="27.6">
       <c r="A425" s="66">
         <v>106</v>
       </c>
@@ -27861,7 +27800,7 @@
       <c r="T425" s="66"/>
       <c r="U425" s="71"/>
     </row>
-    <row r="426" spans="1:21" ht="27.6" hidden="1">
+    <row r="426" spans="1:21" ht="27.6">
       <c r="A426" s="66"/>
       <c r="B426" s="66" t="s">
         <v>912</v>
@@ -27913,8 +27852,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="27.6" hidden="1">
-      <c r="A427" s="89">
+    <row r="427" spans="1:21" ht="27.6">
+      <c r="A427" s="92">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -27963,15 +27902,15 @@
       <c r="Q427" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="R427" s="110"/>
-      <c r="S427" s="112"/>
+      <c r="R427" s="87"/>
+      <c r="S427" s="89"/>
       <c r="T427" s="80"/>
       <c r="U427" s="76" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="13.8" hidden="1">
-      <c r="A428" s="89"/>
+    <row r="428" spans="1:21" ht="13.8">
+      <c r="A428" s="92"/>
       <c r="B428" s="71" t="s">
         <v>913</v>
       </c>
@@ -28024,8 +27963,8 @@
       </c>
       <c r="U428" s="71"/>
     </row>
-    <row r="429" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="89"/>
+    <row r="429" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A429" s="92"/>
       <c r="B429" s="71" t="s">
         <v>913</v>
       </c>
@@ -28076,8 +28015,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="430" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="89"/>
+    <row r="430" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A430" s="92"/>
       <c r="B430" s="71" t="s">
         <v>912</v>
       </c>
@@ -28128,8 +28067,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A431" s="89"/>
+    <row r="431" spans="1:21" ht="40.950000000000003" customHeight="1">
+      <c r="A431" s="92"/>
       <c r="B431" s="71" t="s">
         <v>912</v>
       </c>
@@ -28180,8 +28119,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="13.8" hidden="1">
-      <c r="A432" s="89"/>
+    <row r="432" spans="1:21" ht="13.8">
+      <c r="A432" s="92"/>
       <c r="B432" s="71" t="s">
         <v>913</v>
       </c>
@@ -28234,8 +28173,8 @@
       </c>
       <c r="U432" s="71"/>
     </row>
-    <row r="433" spans="1:21" ht="13.8" hidden="1">
-      <c r="A433" s="89"/>
+    <row r="433" spans="1:21" ht="13.8">
+      <c r="A433" s="92"/>
       <c r="B433" s="71" t="s">
         <v>912</v>
       </c>
@@ -28288,8 +28227,8 @@
       </c>
       <c r="U433" s="66"/>
     </row>
-    <row r="434" spans="1:21" ht="13.8" hidden="1">
-      <c r="A434" s="100"/>
+    <row r="434" spans="1:21" ht="13.8">
+      <c r="A434" s="93"/>
       <c r="B434" s="71" t="s">
         <v>924</v>
       </c>
@@ -28311,37 +28250,37 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="93">
+      <c r="K434" s="95">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="93">
+      <c r="L434" s="95">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="93">
+      <c r="M434" s="95">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="90" t="s">
+      <c r="N434" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="O434" s="90" t="s">
+      <c r="O434" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="P434" s="89">
+      <c r="P434" s="92">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
-      <c r="T434" s="107">
+      <c r="T434" s="96">
         <v>0.65</v>
       </c>
-      <c r="U434" s="89" t="s">
+      <c r="U434" s="92" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="27.6" hidden="1">
-      <c r="A435" s="100"/>
+    <row r="435" spans="1:21" ht="27.6">
+      <c r="A435" s="93"/>
       <c r="B435" s="71" t="s">
         <v>924</v>
       </c>
@@ -28363,20 +28302,20 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="93"/>
-      <c r="L435" s="93"/>
-      <c r="M435" s="93"/>
-      <c r="N435" s="90"/>
-      <c r="O435" s="90"/>
-      <c r="P435" s="89"/>
+      <c r="K435" s="95"/>
+      <c r="L435" s="95"/>
+      <c r="M435" s="95"/>
+      <c r="N435" s="97"/>
+      <c r="O435" s="97"/>
+      <c r="P435" s="92"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
-      <c r="T435" s="107"/>
-      <c r="U435" s="89"/>
-    </row>
-    <row r="436" spans="1:21" ht="13.8" hidden="1">
-      <c r="A436" s="100"/>
+      <c r="T435" s="96"/>
+      <c r="U435" s="92"/>
+    </row>
+    <row r="436" spans="1:21" ht="13.8">
+      <c r="A436" s="93"/>
       <c r="B436" s="71" t="s">
         <v>924</v>
       </c>
@@ -28429,8 +28368,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="13.8" hidden="1">
-      <c r="A437" s="100"/>
+    <row r="437" spans="1:21" ht="13.8">
+      <c r="A437" s="93"/>
       <c r="B437" s="71" t="s">
         <v>928</v>
       </c>
@@ -28483,8 +28422,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="438" spans="1:21" ht="13.8" hidden="1">
-      <c r="A438" s="100"/>
+    <row r="438" spans="1:21" ht="13.8">
+      <c r="A438" s="93"/>
       <c r="B438" s="71" t="s">
         <v>924</v>
       </c>
@@ -28535,8 +28474,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="27.6" hidden="1">
-      <c r="A439" s="96"/>
+    <row r="439" spans="1:21" ht="27.6">
+      <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
         <v>924</v>
       </c>
@@ -28581,15 +28520,15 @@
       <c r="Q439" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R439" s="110"/>
-      <c r="S439" s="112"/>
+      <c r="R439" s="87"/>
+      <c r="S439" s="89"/>
       <c r="T439" s="80"/>
       <c r="U439" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="95">
+    <row r="440" spans="1:21" ht="57" customHeight="1">
+      <c r="A440" s="98">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28642,8 +28581,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="100"/>
+    <row r="441" spans="1:21" ht="57" customHeight="1">
+      <c r="A441" s="93"/>
       <c r="B441" s="71" t="s">
         <v>936</v>
       </c>
@@ -28686,15 +28625,15 @@
       <c r="Q441" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R441" s="110"/>
-      <c r="S441" s="112"/>
+      <c r="R441" s="87"/>
+      <c r="S441" s="89"/>
       <c r="T441" s="80"/>
       <c r="U441" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="100"/>
+    <row r="442" spans="1:21" ht="36.6" customHeight="1">
+      <c r="A442" s="93"/>
       <c r="B442" s="71" t="s">
         <v>936</v>
       </c>
@@ -28748,8 +28687,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="100"/>
+    <row r="443" spans="1:21" ht="36.6" customHeight="1">
+      <c r="A443" s="93"/>
       <c r="B443" s="71" t="s">
         <v>936</v>
       </c>
@@ -28802,8 +28741,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="64.95" hidden="1" customHeight="1">
-      <c r="A444" s="100"/>
+    <row r="444" spans="1:21" ht="64.95" customHeight="1">
+      <c r="A444" s="93"/>
       <c r="B444" s="71" t="s">
         <v>936</v>
       </c>
@@ -28854,8 +28793,8 @@
         <v>942</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="100"/>
+    <row r="445" spans="1:21" ht="36.6" customHeight="1">
+      <c r="A445" s="93"/>
       <c r="B445" s="71" t="s">
         <v>936</v>
       </c>
@@ -28904,8 +28843,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="100"/>
+    <row r="446" spans="1:21" ht="36.6" customHeight="1">
+      <c r="A446" s="93"/>
       <c r="B446" s="71" t="s">
         <v>936</v>
       </c>
@@ -28941,8 +28880,8 @@
       <c r="T446" s="80"/>
       <c r="U446" s="71"/>
     </row>
-    <row r="447" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="96"/>
+    <row r="447" spans="1:21" ht="15" customHeight="1">
+      <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
         <v>936</v>
       </c>
@@ -28995,8 +28934,8 @@
       </c>
       <c r="U447" s="44"/>
     </row>
-    <row r="448" spans="1:21" ht="27.6" hidden="1">
-      <c r="A448" s="89"/>
+    <row r="448" spans="1:21" ht="27.6">
+      <c r="A448" s="92"/>
       <c r="B448" s="71" t="s">
         <v>946</v>
       </c>
@@ -29051,8 +28990,8 @@
         <v>949</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="41.4" hidden="1">
-      <c r="A449" s="89"/>
+    <row r="449" spans="1:21" ht="41.4">
+      <c r="A449" s="92"/>
       <c r="B449" s="51" t="s">
         <v>946</v>
       </c>
@@ -29111,8 +29050,8 @@
         <v>952</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="27.6" hidden="1">
-      <c r="A450" s="95">
+    <row r="450" spans="1:21" ht="27.6">
+      <c r="A450" s="98">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29167,8 +29106,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="451" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="100"/>
+    <row r="451" spans="1:21" ht="15" customHeight="1">
+      <c r="A451" s="93"/>
       <c r="B451" s="71" t="s">
         <v>953</v>
       </c>
@@ -29221,8 +29160,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="100"/>
+    <row r="452" spans="1:21" ht="15" customHeight="1">
+      <c r="A452" s="93"/>
       <c r="B452" s="71" t="s">
         <v>953</v>
       </c>
@@ -29279,8 +29218,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="96"/>
+    <row r="453" spans="1:21" ht="15" customHeight="1">
+      <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
         <v>953</v>
       </c>
@@ -29333,8 +29272,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="454" spans="1:21" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="89">
+    <row r="454" spans="1:21" ht="42.6" customHeight="1">
+      <c r="A454" s="92">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29387,15 +29326,15 @@
       <c r="Q454" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="R454" s="110"/>
-      <c r="S454" s="112"/>
+      <c r="R454" s="87"/>
+      <c r="S454" s="89"/>
       <c r="T454" s="80"/>
       <c r="U454" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="13.8" hidden="1">
-      <c r="A455" s="89"/>
+    <row r="455" spans="1:21" ht="13.8">
+      <c r="A455" s="92"/>
       <c r="B455" s="71" t="s">
         <v>960</v>
       </c>
@@ -29449,8 +29388,8 @@
       </c>
       <c r="U455" s="71"/>
     </row>
-    <row r="456" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="89"/>
+    <row r="456" spans="1:21" ht="15" customHeight="1">
+      <c r="A456" s="92"/>
       <c r="B456" s="71" t="s">
         <v>960</v>
       </c>
@@ -29506,8 +29445,8 @@
       </c>
       <c r="U456" s="71"/>
     </row>
-    <row r="457" spans="1:21" ht="27.6" hidden="1">
-      <c r="A457" s="89">
+    <row r="457" spans="1:21" ht="27.6">
+      <c r="A457" s="92">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29559,8 +29498,8 @@
         <v>591</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="13.8" hidden="1">
-      <c r="A458" s="89"/>
+    <row r="458" spans="1:21" ht="13.8">
+      <c r="A458" s="92"/>
       <c r="B458" s="71" t="s">
         <v>964</v>
       </c>
@@ -29605,15 +29544,15 @@
       <c r="Q458" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R458" s="110"/>
-      <c r="S458" s="112"/>
+      <c r="R458" s="87"/>
+      <c r="S458" s="89"/>
       <c r="T458" s="80"/>
       <c r="U458" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="459" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A459" s="89"/>
+    <row r="459" spans="1:21" ht="37.950000000000003" customHeight="1">
+      <c r="A459" s="92"/>
       <c r="B459" s="71" t="s">
         <v>964</v>
       </c>
@@ -29666,8 +29605,8 @@
       </c>
       <c r="U459" s="66"/>
     </row>
-    <row r="460" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A460" s="89"/>
+    <row r="460" spans="1:21" ht="37.950000000000003" customHeight="1">
+      <c r="A460" s="92"/>
       <c r="B460" s="71" t="s">
         <v>964</v>
       </c>
@@ -29714,8 +29653,8 @@
       <c r="T460" s="80"/>
       <c r="U460" s="66"/>
     </row>
-    <row r="461" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="89"/>
+    <row r="461" spans="1:21" ht="15" customHeight="1">
+      <c r="A461" s="92"/>
       <c r="B461" s="71" t="s">
         <v>964</v>
       </c>
@@ -29770,7 +29709,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="462" spans="1:21" ht="55.2" hidden="1">
+    <row r="462" spans="1:21" ht="55.2">
       <c r="A462" s="66"/>
       <c r="B462" s="71" t="s">
         <v>971</v>
@@ -29826,7 +29765,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="43.2" hidden="1" customHeight="1">
+    <row r="463" spans="1:21" ht="43.2" customHeight="1">
       <c r="A463" s="66"/>
       <c r="B463" s="71" t="s">
         <v>971</v>
@@ -29880,7 +29819,7 @@
       </c>
       <c r="U463" s="71"/>
     </row>
-    <row r="464" spans="1:21" ht="43.2" hidden="1" customHeight="1">
+    <row r="464" spans="1:21" ht="43.2" customHeight="1">
       <c r="A464" s="66"/>
       <c r="B464" s="71" t="s">
         <v>971</v>
@@ -29934,7 +29873,7 @@
       </c>
       <c r="U464" s="71"/>
     </row>
-    <row r="465" spans="1:21" ht="43.2" hidden="1" customHeight="1">
+    <row r="465" spans="1:21" ht="43.2" customHeight="1">
       <c r="A465" s="66"/>
       <c r="B465" s="71" t="s">
         <v>971</v>
@@ -29986,7 +29925,7 @@
       <c r="T465" s="80"/>
       <c r="U465" s="71"/>
     </row>
-    <row r="466" spans="1:21" ht="43.2" hidden="1" customHeight="1">
+    <row r="466" spans="1:21" ht="43.2" customHeight="1">
       <c r="A466" s="66"/>
       <c r="B466" s="71" t="s">
         <v>971</v>
@@ -30040,7 +29979,7 @@
       </c>
       <c r="U466" s="71"/>
     </row>
-    <row r="467" spans="1:21" ht="33.6" hidden="1" customHeight="1">
+    <row r="467" spans="1:21" ht="33.6" customHeight="1">
       <c r="A467" s="66">
         <v>114</v>
       </c>
@@ -30088,15 +30027,15 @@
       <c r="Q467" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R467" s="110"/>
-      <c r="S467" s="112"/>
+      <c r="R467" s="87"/>
+      <c r="S467" s="89"/>
       <c r="T467" s="80"/>
       <c r="U467" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="468" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="100"/>
+    <row r="468" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A468" s="93"/>
       <c r="B468" s="71" t="s">
         <v>981</v>
       </c>
@@ -30146,8 +30085,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="469" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="100"/>
+    <row r="469" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A469" s="93"/>
       <c r="B469" s="71" t="s">
         <v>325</v>
       </c>
@@ -30200,8 +30139,8 @@
       </c>
       <c r="U469" s="71"/>
     </row>
-    <row r="470" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="100"/>
+    <row r="470" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A470" s="93"/>
       <c r="B470" s="71" t="s">
         <v>325</v>
       </c>
@@ -30254,8 +30193,8 @@
       </c>
       <c r="U470" s="71"/>
     </row>
-    <row r="471" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="100"/>
+    <row r="471" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A471" s="93"/>
       <c r="B471" s="71" t="s">
         <v>325</v>
       </c>
@@ -30308,8 +30247,8 @@
       </c>
       <c r="U471" s="71"/>
     </row>
-    <row r="472" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="100"/>
+    <row r="472" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A472" s="93"/>
       <c r="B472" s="71" t="s">
         <v>325</v>
       </c>
@@ -30364,8 +30303,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="473" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="100"/>
+    <row r="473" spans="1:21" ht="33.6" customHeight="1">
+      <c r="A473" s="93"/>
       <c r="B473" s="71" t="s">
         <v>325</v>
       </c>
@@ -30416,8 +30355,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="474" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="96"/>
+    <row r="474" spans="1:21" ht="39" customHeight="1">
+      <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
         <v>981</v>
       </c>
@@ -30466,8 +30405,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="475" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="89">
+    <row r="475" spans="1:21" ht="39" customHeight="1">
+      <c r="A475" s="92">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30479,7 +30418,7 @@
       <c r="D475" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="E475" s="92">
+      <c r="E475" s="112">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30493,14 +30432,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="94">
+      <c r="K475" s="113">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="94">
+      <c r="L475" s="113">
         <v>0</v>
       </c>
-      <c r="M475" s="93">
+      <c r="M475" s="95">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30518,12 +30457,12 @@
       <c r="R475" s="66"/>
       <c r="S475" s="66"/>
       <c r="T475" s="71"/>
-      <c r="U475" s="90" t="s">
+      <c r="U475" s="97" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="476" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="89"/>
+    <row r="476" spans="1:21" ht="39" customHeight="1">
+      <c r="A476" s="92"/>
       <c r="B476" s="71" t="s">
         <v>993</v>
       </c>
@@ -30533,7 +30472,7 @@
       <c r="D476" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="E476" s="92"/>
+      <c r="E476" s="112"/>
       <c r="F476" s="71" t="s">
         <v>175</v>
       </c>
@@ -30545,9 +30484,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="94"/>
-      <c r="L476" s="94"/>
-      <c r="M476" s="93"/>
+      <c r="K476" s="113"/>
+      <c r="L476" s="113"/>
+      <c r="M476" s="95"/>
       <c r="N476" s="71" t="s">
         <v>36</v>
       </c>
@@ -30563,10 +30502,10 @@
       <c r="R476" s="66"/>
       <c r="S476" s="66"/>
       <c r="T476" s="71"/>
-      <c r="U476" s="90"/>
-    </row>
-    <row r="477" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="89"/>
+      <c r="U476" s="97"/>
+    </row>
+    <row r="477" spans="1:21" ht="39" customHeight="1">
+      <c r="A477" s="92"/>
       <c r="B477" s="71" t="s">
         <v>993</v>
       </c>
@@ -30623,8 +30562,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="478" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="89"/>
+    <row r="478" spans="1:21" ht="36" customHeight="1">
+      <c r="A478" s="92"/>
       <c r="B478" s="71" t="s">
         <v>993</v>
       </c>
@@ -30678,7 +30617,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:21" ht="36" hidden="1" customHeight="1">
+    <row r="479" spans="1:21" ht="36" customHeight="1">
       <c r="A479" s="66">
         <v>118</v>
       </c>
@@ -30726,14 +30665,14 @@
       <c r="Q479" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R479" s="110"/>
-      <c r="S479" s="112"/>
+      <c r="R479" s="87"/>
+      <c r="S479" s="89"/>
       <c r="T479" s="80"/>
       <c r="U479" s="71" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="480" spans="1:21" ht="36" hidden="1" customHeight="1">
+    <row r="480" spans="1:21" ht="36" customHeight="1">
       <c r="A480" s="66"/>
       <c r="B480" s="71" t="s">
         <v>999</v>
@@ -30787,7 +30726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="481" spans="1:21" ht="36" hidden="1" customHeight="1">
+    <row r="481" spans="1:21" ht="36" customHeight="1">
       <c r="A481" s="66"/>
       <c r="B481" s="71" t="s">
         <v>1000</v>
@@ -30839,7 +30778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="482" spans="1:21" ht="15" hidden="1" customHeight="1">
+    <row r="482" spans="1:21" ht="15" customHeight="1">
       <c r="A482" s="66">
         <v>119</v>
       </c>
@@ -30897,7 +30836,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="483" spans="1:21" ht="35.4" hidden="1" customHeight="1">
+    <row r="483" spans="1:21" ht="35.4" customHeight="1">
       <c r="A483" s="66"/>
       <c r="B483" s="71" t="s">
         <v>1005</v>
@@ -30951,7 +30890,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="484" spans="1:21" ht="38.4" hidden="1" customHeight="1">
+    <row r="484" spans="1:21" ht="38.4" customHeight="1">
       <c r="A484" s="66"/>
       <c r="B484" s="71" t="s">
         <v>1005</v>
@@ -31003,7 +30942,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="485" spans="1:21" ht="36.6" hidden="1" customHeight="1">
+    <row r="485" spans="1:21" ht="36.6" customHeight="1">
       <c r="A485" s="66">
         <v>120</v>
       </c>
@@ -31058,8 +30997,8 @@
       </c>
       <c r="U485" s="66"/>
     </row>
-    <row r="486" spans="1:21" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="89">
+    <row r="486" spans="1:21" ht="35.25" customHeight="1">
+      <c r="A486" s="92">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31114,8 +31053,8 @@
       </c>
       <c r="U486" s="71"/>
     </row>
-    <row r="487" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="89"/>
+    <row r="487" spans="1:21" ht="36" customHeight="1">
+      <c r="A487" s="92"/>
       <c r="B487" s="71" t="s">
         <v>1009</v>
       </c>
@@ -31166,8 +31105,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="488" spans="1:21" ht="96.6" hidden="1">
-      <c r="A488" s="89"/>
+    <row r="488" spans="1:21" ht="96.6">
+      <c r="A488" s="92"/>
       <c r="B488" s="71" t="s">
         <v>1009</v>
       </c>
@@ -31220,7 +31159,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="489" spans="1:21" ht="36" hidden="1" customHeight="1">
+    <row r="489" spans="1:21" ht="36" customHeight="1">
       <c r="A489" s="68"/>
       <c r="B489" s="71" t="s">
         <v>1017</v>
@@ -31274,7 +31213,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="490" spans="1:21" ht="13.8" hidden="1">
+    <row r="490" spans="1:21" ht="13.8">
       <c r="A490" s="68">
         <v>122</v>
       </c>
@@ -31330,8 +31269,8 @@
       </c>
       <c r="U490" s="71"/>
     </row>
-    <row r="491" spans="1:21" ht="13.8" hidden="1">
-      <c r="A491" s="100"/>
+    <row r="491" spans="1:21" ht="13.8">
+      <c r="A491" s="93"/>
       <c r="B491" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31384,8 +31323,8 @@
       </c>
       <c r="U491" s="71"/>
     </row>
-    <row r="492" spans="1:21" ht="13.8" hidden="1">
-      <c r="A492" s="100"/>
+    <row r="492" spans="1:21" ht="13.8">
+      <c r="A492" s="93"/>
       <c r="B492" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31438,8 +31377,8 @@
       </c>
       <c r="U492" s="71"/>
     </row>
-    <row r="493" spans="1:21" ht="55.2" hidden="1">
-      <c r="A493" s="100"/>
+    <row r="493" spans="1:21" ht="55.2">
+      <c r="A493" s="93"/>
       <c r="B493" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31489,8 +31428,8 @@
         <v>895</v>
       </c>
     </row>
-    <row r="494" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="96"/>
+    <row r="494" spans="1:21" ht="15" customHeight="1">
+      <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31543,8 +31482,8 @@
       </c>
       <c r="U494" s="71"/>
     </row>
-    <row r="495" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="89">
+    <row r="495" spans="1:21" ht="15" customHeight="1">
+      <c r="A495" s="92">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -31601,8 +31540,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="496" spans="1:21" ht="27.6" hidden="1">
-      <c r="A496" s="89"/>
+    <row r="496" spans="1:21" ht="27.6">
+      <c r="A496" s="92"/>
       <c r="B496" s="71" t="s">
         <v>1026</v>
       </c>
@@ -31653,8 +31592,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="497" spans="1:21" ht="13.8" hidden="1">
-      <c r="A497" s="89"/>
+    <row r="497" spans="1:21" ht="13.8">
+      <c r="A497" s="92"/>
       <c r="B497" s="71" t="s">
         <v>1026</v>
       </c>
@@ -31707,8 +31646,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="498" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A498" s="89"/>
+    <row r="498" spans="1:21" ht="40.200000000000003" customHeight="1">
+      <c r="A498" s="92"/>
       <c r="B498" s="71" t="s">
         <v>1032</v>
       </c>
@@ -31762,7 +31701,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="499" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
+    <row r="499" spans="1:21" ht="40.200000000000003" customHeight="1">
       <c r="A499" s="66"/>
       <c r="B499" s="71" t="s">
         <v>1033</v>
@@ -31822,8 +31761,8 @@
         <v>695</v>
       </c>
     </row>
-    <row r="500" spans="1:21" ht="27.6" hidden="1">
-      <c r="A500" s="90">
+    <row r="500" spans="1:21" ht="27.6">
+      <c r="A500" s="97">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -31876,15 +31815,15 @@
       <c r="Q500" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="R500" s="110"/>
-      <c r="S500" s="112"/>
+      <c r="R500" s="87"/>
+      <c r="S500" s="89"/>
       <c r="T500" s="80"/>
       <c r="U500" s="71" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="501" spans="1:21" ht="13.8" hidden="1">
-      <c r="A501" s="90"/>
+    <row r="501" spans="1:21" ht="13.8">
+      <c r="A501" s="97"/>
       <c r="B501" s="71" t="s">
         <v>1033</v>
       </c>
@@ -31934,8 +31873,8 @@
       <c r="T501" s="80"/>
       <c r="U501" s="71"/>
     </row>
-    <row r="502" spans="1:21" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="90"/>
+    <row r="502" spans="1:21" ht="78" customHeight="1">
+      <c r="A502" s="97"/>
       <c r="B502" s="71" t="s">
         <v>1033</v>
       </c>
@@ -31990,8 +31929,8 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="503" spans="1:21" ht="41.4" hidden="1">
-      <c r="A503" s="89">
+    <row r="503" spans="1:21" ht="41.4">
+      <c r="A503" s="92">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -32052,8 +31991,8 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="504" spans="1:21" ht="13.8" hidden="1">
-      <c r="A504" s="89"/>
+    <row r="504" spans="1:21" ht="13.8">
+      <c r="A504" s="92"/>
       <c r="B504" s="71" t="s">
         <v>1041</v>
       </c>
@@ -32110,8 +32049,8 @@
       </c>
       <c r="U504" s="71"/>
     </row>
-    <row r="505" spans="1:21" ht="55.2" hidden="1">
-      <c r="A505" s="89"/>
+    <row r="505" spans="1:21" ht="55.2">
+      <c r="A505" s="92"/>
       <c r="B505" s="51" t="s">
         <v>1041</v>
       </c>
@@ -32168,14 +32107,14 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="506" spans="1:21" ht="55.95" hidden="1" customHeight="1">
+    <row r="506" spans="1:21" ht="55.95" customHeight="1">
       <c r="K506" s="27"/>
       <c r="M506" s="56"/>
       <c r="R506" s="33"/>
       <c r="S506" s="33"/>
       <c r="T506" s="57"/>
     </row>
-    <row r="507" spans="1:21" ht="13.8" hidden="1">
+    <row r="507" spans="1:21" ht="13.8">
       <c r="E507" s="55" t="s">
         <v>713</v>
       </c>
@@ -32187,7 +32126,7 @@
     <row r="508" spans="1:21" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>1.22</v>
+        <v>21930.376999999982</v>
       </c>
       <c r="K508" s="8"/>
       <c r="M508" s="58"/>
@@ -32243,26 +32182,109 @@
       <c r="K521" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Guarne"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:U507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}"/>
   <mergeCells count="137">
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="T434:T435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="T91:T92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="U475:U476"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A400:A405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="P310:P311"/>
+    <mergeCell ref="U310:U311"/>
+    <mergeCell ref="T310:T311"/>
+    <mergeCell ref="A311:A316"/>
+    <mergeCell ref="F312:F313"/>
+    <mergeCell ref="G312:G313"/>
+    <mergeCell ref="K312:K313"/>
+    <mergeCell ref="L312:L313"/>
+    <mergeCell ref="M312:M313"/>
+    <mergeCell ref="N312:N313"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="L310:L311"/>
+    <mergeCell ref="M310:M311"/>
+    <mergeCell ref="N310:N311"/>
+    <mergeCell ref="O310:O311"/>
+    <mergeCell ref="Q310:Q311"/>
+    <mergeCell ref="Q312:Q313"/>
+    <mergeCell ref="O312:O313"/>
+    <mergeCell ref="P312:P313"/>
+    <mergeCell ref="U312:U313"/>
+    <mergeCell ref="T312:T313"/>
     <mergeCell ref="A319:A320"/>
     <mergeCell ref="A321:A330"/>
     <mergeCell ref="A335:A338"/>
@@ -32287,107 +32309,18 @@
     <mergeCell ref="A373:A384"/>
     <mergeCell ref="A385:A392"/>
     <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A400:A405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="P310:P311"/>
-    <mergeCell ref="U310:U311"/>
-    <mergeCell ref="T310:T311"/>
-    <mergeCell ref="A311:A316"/>
-    <mergeCell ref="F312:F313"/>
-    <mergeCell ref="G312:G313"/>
-    <mergeCell ref="K312:K313"/>
-    <mergeCell ref="L312:L313"/>
-    <mergeCell ref="M312:M313"/>
-    <mergeCell ref="N312:N313"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="L310:L311"/>
-    <mergeCell ref="M310:M311"/>
-    <mergeCell ref="N310:N311"/>
-    <mergeCell ref="O310:O311"/>
-    <mergeCell ref="Q310:Q311"/>
-    <mergeCell ref="Q312:Q313"/>
-    <mergeCell ref="O312:O313"/>
-    <mergeCell ref="P312:P313"/>
-    <mergeCell ref="U312:U313"/>
-    <mergeCell ref="T312:T313"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="T91:T92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="U475:U476"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="T434:T435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -32399,74 +32332,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D990FC-899F-49AD-A982-A875499E939A}">
-  <dimension ref="G6:I10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="7:9">
-      <c r="G6" s="121" t="s">
-        <v>1072</v>
-      </c>
-      <c r="H6" s="122" t="s">
-        <v>1073</v>
-      </c>
-      <c r="I6" s="122" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="7" spans="7:9">
-      <c r="G7" s="118" t="s">
-        <v>1074</v>
-      </c>
-      <c r="H7" s="116" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I7" s="117">
-        <v>2947759</v>
-      </c>
-    </row>
-    <row r="8" spans="7:9">
-      <c r="G8" s="118" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H8" s="116" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I8" s="117">
-        <v>3477223</v>
-      </c>
-    </row>
-    <row r="9" spans="7:9" ht="28.8">
-      <c r="G9" s="119" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H9" s="116" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I9" s="117">
-        <v>1672188</v>
-      </c>
-    </row>
-    <row r="10" spans="7:9">
-      <c r="H10" s="115" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I10" s="120">
-        <f>SUM(I7:I9)</f>
-        <v>8097170</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE741C3-3798-4F4E-8B25-FDCA2ADDEF39}">
   <dimension ref="B2:I16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
@@ -32486,10 +32351,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="27.6">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="114" t="s">
         <v>1049</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="114"/>
       <c r="D2" s="23" t="s">
         <v>1050</v>
       </c>
@@ -32696,23 +32561,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -32868,25 +32716,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32902,4 +32749,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D27003-46A8-42AB-B7EE-81282E7FF8E8}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F81FC7FB-08BD-4A81-9417-11448392552F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4913,6 +4913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W521"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -5030,7 +5031,7 @@
       </c>
       <c r="W2" s="13"/>
     </row>
-    <row r="3" spans="1:23" ht="62.4" customHeight="1">
+    <row r="3" spans="1:23" ht="62.4" hidden="1" customHeight="1">
       <c r="A3" s="94">
         <v>1</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="62.4" customHeight="1">
+    <row r="4" spans="1:23" ht="62.4" hidden="1" customHeight="1">
       <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>21</v>
@@ -5160,7 +5161,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="41.4">
+    <row r="5" spans="1:23" ht="41.4" hidden="1">
       <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>21</v>
@@ -5216,7 +5217,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="27.6">
+    <row r="6" spans="1:23" ht="27.6" hidden="1">
       <c r="A6" s="72"/>
       <c r="B6" s="71" t="s">
         <v>39</v>
@@ -5268,7 +5269,7 @@
       </c>
       <c r="U6" s="66"/>
     </row>
-    <row r="7" spans="1:23" ht="13.8">
+    <row r="7" spans="1:23" ht="13.8" hidden="1">
       <c r="A7" s="98">
         <v>2</v>
       </c>
@@ -5303,7 +5304,7 @@
       <c r="T7" s="66"/>
       <c r="U7" s="66"/>
     </row>
-    <row r="8" spans="1:23" ht="13.8">
+    <row r="8" spans="1:23" ht="13.8" hidden="1">
       <c r="A8" s="93"/>
       <c r="B8" s="71" t="s">
         <v>39</v>
@@ -5355,7 +5356,7 @@
       </c>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:23" ht="41.4">
+    <row r="9" spans="1:23" ht="41.4" hidden="1">
       <c r="A9" s="93"/>
       <c r="B9" s="71" t="s">
         <v>39</v>
@@ -5413,7 +5414,7 @@
       </c>
       <c r="U9" s="66"/>
     </row>
-    <row r="10" spans="1:23" ht="41.4">
+    <row r="10" spans="1:23" ht="41.4" hidden="1">
       <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>39</v>
@@ -5471,7 +5472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="27.6">
+    <row r="11" spans="1:23" ht="27.6" hidden="1">
       <c r="A11" s="92">
         <v>3</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="52.95" customHeight="1">
+    <row r="12" spans="1:23" ht="52.95" hidden="1" customHeight="1">
       <c r="A12" s="92"/>
       <c r="B12" s="71" t="s">
         <v>57</v>
@@ -5590,7 +5591,7 @@
       </c>
       <c r="U12" s="76"/>
     </row>
-    <row r="13" spans="1:23" ht="13.8">
+    <row r="13" spans="1:23" ht="13.8" hidden="1">
       <c r="A13" s="92"/>
       <c r="B13" s="71" t="s">
         <v>57</v>
@@ -5646,7 +5647,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="13.8">
+    <row r="14" spans="1:23" ht="13.8" hidden="1">
       <c r="A14" s="92"/>
       <c r="B14" s="71" t="s">
         <v>57</v>
@@ -5702,7 +5703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="13.8">
+    <row r="15" spans="1:23" ht="13.8" hidden="1">
       <c r="A15" s="92"/>
       <c r="B15" s="71" t="s">
         <v>57</v>
@@ -5758,7 +5759,7 @@
       </c>
       <c r="U15" s="66"/>
     </row>
-    <row r="16" spans="1:23" ht="66.599999999999994" customHeight="1">
+    <row r="16" spans="1:23" ht="66.599999999999994" hidden="1" customHeight="1">
       <c r="A16" s="92"/>
       <c r="B16" s="71" t="s">
         <v>57</v>
@@ -5814,7 +5815,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.8">
+    <row r="17" spans="1:21" ht="13.8" hidden="1">
       <c r="A17" s="66"/>
       <c r="B17" s="71" t="s">
         <v>83</v>
@@ -5855,7 +5856,7 @@
       <c r="T17" s="80"/>
       <c r="U17" s="71"/>
     </row>
-    <row r="18" spans="1:21" ht="61.2" customHeight="1">
+    <row r="18" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A18" s="66">
         <v>4</v>
       </c>
@@ -5915,7 +5916,7 @@
       </c>
       <c r="U18" s="71"/>
     </row>
-    <row r="19" spans="1:21" ht="41.4">
+    <row r="19" spans="1:21" ht="41.4" hidden="1">
       <c r="A19" s="66"/>
       <c r="B19" s="71" t="s">
         <v>90</v>
@@ -5975,7 +5976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="97.95" customHeight="1">
+    <row r="20" spans="1:21" ht="97.95" hidden="1" customHeight="1">
       <c r="A20" s="92">
         <v>5</v>
       </c>
@@ -6037,7 +6038,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="122.4" customHeight="1">
+    <row r="21" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A21" s="92"/>
       <c r="B21" s="71" t="s">
         <v>90</v>
@@ -6095,7 +6096,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="27.6">
+    <row r="22" spans="1:21" ht="27.6" hidden="1">
       <c r="A22" s="92"/>
       <c r="B22" s="71"/>
       <c r="C22" s="66" t="s">
@@ -6152,7 +6153,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="13.8">
+    <row r="23" spans="1:21" ht="13.8" hidden="1">
       <c r="A23" s="92"/>
       <c r="B23" s="71" t="s">
         <v>90</v>
@@ -6209,7 +6210,7 @@
       </c>
       <c r="U23" s="71"/>
     </row>
-    <row r="24" spans="1:21" ht="66" customHeight="1">
+    <row r="24" spans="1:21" ht="66" hidden="1" customHeight="1">
       <c r="A24" s="92">
         <v>6</v>
       </c>
@@ -6270,7 +6271,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="13.8">
+    <row r="25" spans="1:21" ht="13.8" hidden="1">
       <c r="A25" s="92"/>
       <c r="B25" s="71" t="s">
         <v>107</v>
@@ -6326,7 +6327,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="70.2" customHeight="1">
+    <row r="26" spans="1:21" ht="70.2" hidden="1" customHeight="1">
       <c r="A26" s="92"/>
       <c r="B26" s="71" t="s">
         <v>107</v>
@@ -6382,7 +6383,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="61.2" customHeight="1">
+    <row r="27" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A27" s="92"/>
       <c r="B27" s="71" t="s">
         <v>107</v>
@@ -6440,7 +6441,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="13.8">
+    <row r="28" spans="1:21" ht="13.8" hidden="1">
       <c r="A28" s="92"/>
       <c r="B28" s="71" t="s">
         <v>107</v>
@@ -6494,7 +6495,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="29" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A29" s="92"/>
       <c r="B29" s="71" t="s">
         <v>107</v>
@@ -6550,7 +6551,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="30" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A30" s="92"/>
       <c r="B30" s="71" t="s">
         <v>107</v>
@@ -6602,7 +6603,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="31" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A31" s="92"/>
       <c r="B31" s="71" t="s">
         <v>107</v>
@@ -6660,7 +6661,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="32" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A32" s="92"/>
       <c r="B32" s="71" t="s">
         <v>107</v>
@@ -6720,7 +6721,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="33" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A33" s="92"/>
       <c r="B33" s="71" t="s">
         <v>107</v>
@@ -6776,7 +6777,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="34" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A34" s="92"/>
       <c r="B34" s="71" t="s">
         <v>107</v>
@@ -6836,7 +6837,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="13.8">
+    <row r="35" spans="1:21" ht="13.8" hidden="1">
       <c r="A35" s="93"/>
       <c r="B35" s="71" t="s">
         <v>145</v>
@@ -6871,7 +6872,7 @@
       <c r="T35" s="1"/>
       <c r="U35" s="71"/>
     </row>
-    <row r="36" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="36" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>145</v>
@@ -6924,7 +6925,7 @@
       </c>
       <c r="U36" s="66"/>
     </row>
-    <row r="37" spans="1:21" ht="72.599999999999994" customHeight="1">
+    <row r="37" spans="1:21" ht="72.599999999999994" hidden="1" customHeight="1">
       <c r="A37" s="66"/>
       <c r="B37" s="71" t="s">
         <v>148</v>
@@ -6983,7 +6984,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="38" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A38" s="92">
         <v>8</v>
       </c>
@@ -7044,7 +7045,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="39" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A39" s="92"/>
       <c r="B39" s="71" t="s">
         <v>148</v>
@@ -7104,7 +7105,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="40" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A40" s="92"/>
       <c r="B40" s="71" t="s">
         <v>148</v>
@@ -7161,7 +7162,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="61.2" customHeight="1">
+    <row r="41" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A41" s="92">
         <v>9</v>
       </c>
@@ -7221,7 +7222,7 @@
       </c>
       <c r="U41" s="71"/>
     </row>
-    <row r="42" spans="1:21" ht="61.2" customHeight="1">
+    <row r="42" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A42" s="92"/>
       <c r="B42" s="71" t="s">
         <v>158</v>
@@ -7270,7 +7271,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="102" customHeight="1">
+    <row r="43" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A43" s="92"/>
       <c r="B43" s="71" t="s">
         <v>158</v>
@@ -7321,7 +7322,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="102" customHeight="1">
+    <row r="44" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A44" s="92"/>
       <c r="B44" s="71" t="s">
         <v>158</v>
@@ -7369,7 +7370,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="27.6">
+    <row r="45" spans="1:21" ht="27.6" hidden="1">
       <c r="A45" s="92"/>
       <c r="B45" s="71" t="s">
         <v>158</v>
@@ -7425,7 +7426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="46" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A46" s="92">
         <v>10</v>
       </c>
@@ -7481,7 +7482,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="13.8">
+    <row r="47" spans="1:21" ht="13.8" hidden="1">
       <c r="A47" s="98"/>
       <c r="B47" s="71" t="s">
         <v>173</v>
@@ -7535,7 +7536,7 @@
       </c>
       <c r="U47" s="71"/>
     </row>
-    <row r="48" spans="1:21" ht="13.8">
+    <row r="48" spans="1:21" ht="13.8" hidden="1">
       <c r="A48" s="92"/>
       <c r="B48" s="71" t="s">
         <v>180</v>
@@ -7570,7 +7571,7 @@
       <c r="T48" s="80"/>
       <c r="U48" s="71"/>
     </row>
-    <row r="49" spans="1:21" ht="13.8">
+    <row r="49" spans="1:21" ht="13.8" hidden="1">
       <c r="A49" s="92"/>
       <c r="B49" s="71" t="s">
         <v>180</v>
@@ -7609,7 +7610,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="13.8">
+    <row r="50" spans="1:21" ht="13.8" hidden="1">
       <c r="A50" s="92"/>
       <c r="B50" s="71" t="s">
         <v>180</v>
@@ -7663,7 +7664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="55.2">
+    <row r="51" spans="1:21" ht="55.2" hidden="1">
       <c r="A51" s="92"/>
       <c r="B51" s="71" t="s">
         <v>180</v>
@@ -7717,7 +7718,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="41.4">
+    <row r="52" spans="1:21" ht="41.4" hidden="1">
       <c r="A52" s="92"/>
       <c r="B52" s="71" t="s">
         <v>180</v>
@@ -7771,7 +7772,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="45.6" customHeight="1">
+    <row r="53" spans="1:21" ht="45.6" hidden="1" customHeight="1">
       <c r="A53" s="92"/>
       <c r="B53" s="71" t="s">
         <v>180</v>
@@ -7825,7 +7826,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="54" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A54" s="92"/>
       <c r="B54" s="71" t="s">
         <v>195</v>
@@ -7878,7 +7879,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="55" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A55" s="92"/>
       <c r="B55" s="71" t="s">
         <v>195</v>
@@ -7932,7 +7933,7 @@
       </c>
       <c r="U55" s="66"/>
     </row>
-    <row r="56" spans="1:21" ht="41.4">
+    <row r="56" spans="1:21" ht="41.4" hidden="1">
       <c r="A56" s="92"/>
       <c r="B56" s="71" t="s">
         <v>195</v>
@@ -7990,7 +7991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="57" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A57" s="92"/>
       <c r="B57" s="71" t="s">
         <v>195</v>
@@ -8046,7 +8047,7 @@
       </c>
       <c r="U57" s="71"/>
     </row>
-    <row r="58" spans="1:21" ht="34.200000000000003" customHeight="1">
+    <row r="58" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A58" s="92"/>
       <c r="B58" s="71" t="s">
         <v>195</v>
@@ -8105,7 +8106,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="61.2" customHeight="1">
+    <row r="59" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>207</v>
@@ -8161,7 +8162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="61.2" customHeight="1">
+    <row r="60" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>207</v>
@@ -8216,7 +8217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="41.4">
+    <row r="61" spans="1:21" ht="41.4" hidden="1">
       <c r="A61" s="92"/>
       <c r="B61" s="61" t="s">
         <v>207</v>
@@ -8269,7 +8270,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="33" customHeight="1">
+    <row r="62" spans="1:21" ht="33" hidden="1" customHeight="1">
       <c r="A62" s="98">
         <v>14</v>
       </c>
@@ -8326,7 +8327,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="102" customHeight="1">
+    <row r="63" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A63" s="93"/>
       <c r="B63" s="71" t="s">
         <v>213</v>
@@ -8382,7 +8383,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="107.25" customHeight="1">
+    <row r="64" spans="1:21" ht="107.25" hidden="1" customHeight="1">
       <c r="A64" s="94"/>
       <c r="B64" s="71" t="s">
         <v>213</v>
@@ -8436,7 +8437,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="107.25" customHeight="1">
+    <row r="65" spans="1:21" ht="107.25" hidden="1" customHeight="1">
       <c r="A65" s="68"/>
       <c r="B65" s="71" t="s">
         <v>223</v>
@@ -8492,7 +8493,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="102" customHeight="1">
+    <row r="66" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A66" s="68"/>
       <c r="B66" s="71" t="s">
         <v>223</v>
@@ -8544,7 +8545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="102" customHeight="1">
+    <row r="67" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A67" s="98">
         <v>16</v>
       </c>
@@ -8599,7 +8600,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="13.8">
+    <row r="68" spans="1:21" ht="13.8" hidden="1">
       <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>228</v>
@@ -8651,7 +8652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="51.6" customHeight="1">
+    <row r="69" spans="1:21" ht="51.6" hidden="1" customHeight="1">
       <c r="A69" s="98">
         <v>17</v>
       </c>
@@ -8706,7 +8707,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="41.4">
+    <row r="70" spans="1:21" ht="41.4" hidden="1">
       <c r="A70" s="93"/>
       <c r="B70" s="71" t="s">
         <v>234</v>
@@ -8760,7 +8761,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="67.95" customHeight="1">
+    <row r="71" spans="1:21" ht="67.95" hidden="1" customHeight="1">
       <c r="A71" s="93"/>
       <c r="B71" s="71" t="s">
         <v>240</v>
@@ -8814,7 +8815,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="174.6" customHeight="1">
+    <row r="72" spans="1:21" ht="174.6" hidden="1" customHeight="1">
       <c r="A72" s="93"/>
       <c r="B72" s="71" t="s">
         <v>243</v>
@@ -8869,7 +8870,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="73" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A73" s="93"/>
       <c r="B73" s="71" t="s">
         <v>243</v>
@@ -8921,7 +8922,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="74" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A74" s="93"/>
       <c r="B74" s="71" t="s">
         <v>243</v>
@@ -8975,7 +8976,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="75" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A75" s="93"/>
       <c r="B75" s="71" t="s">
         <v>243</v>
@@ -9035,7 +9036,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="76" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A76" s="93"/>
       <c r="B76" s="71" t="s">
         <v>243</v>
@@ -9087,7 +9088,7 @@
       <c r="T76" s="70"/>
       <c r="U76" s="71"/>
     </row>
-    <row r="77" spans="1:21" ht="13.8">
+    <row r="77" spans="1:21" ht="13.8" hidden="1">
       <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>243</v>
@@ -9143,7 +9144,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="78" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A78" s="93"/>
       <c r="B78" s="71" t="s">
         <v>254</v>
@@ -9203,7 +9204,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="13.8">
+    <row r="79" spans="1:21" ht="13.8" hidden="1">
       <c r="A79" s="93"/>
       <c r="B79" s="71" t="s">
         <v>254</v>
@@ -9257,7 +9258,7 @@
       </c>
       <c r="U79" s="66"/>
     </row>
-    <row r="80" spans="1:21" ht="13.8">
+    <row r="80" spans="1:21" ht="13.8" hidden="1">
       <c r="A80" s="93"/>
       <c r="B80" s="71" t="s">
         <v>254</v>
@@ -9311,7 +9312,7 @@
       </c>
       <c r="U80" s="66"/>
     </row>
-    <row r="81" spans="1:22" ht="150.6" customHeight="1">
+    <row r="81" spans="1:22" ht="150.6" hidden="1" customHeight="1">
       <c r="A81" s="93"/>
       <c r="B81" s="71" t="s">
         <v>254</v>
@@ -9366,7 +9367,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="82" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A82" s="93"/>
       <c r="B82" s="71" t="s">
         <v>263</v>
@@ -9423,7 +9424,7 @@
       </c>
       <c r="V82" s="33"/>
     </row>
-    <row r="83" spans="1:22" ht="38.4" customHeight="1">
+    <row r="83" spans="1:22" ht="38.4" hidden="1" customHeight="1">
       <c r="A83" s="93"/>
       <c r="B83" s="71" t="s">
         <v>263</v>
@@ -9477,7 +9478,7 @@
       </c>
       <c r="V83" s="33"/>
     </row>
-    <row r="84" spans="1:22" ht="27.6">
+    <row r="84" spans="1:22" ht="27.6" hidden="1">
       <c r="A84" s="93"/>
       <c r="B84" s="71" t="s">
         <v>263</v>
@@ -9531,7 +9532,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:22" ht="55.2">
+    <row r="85" spans="1:22" ht="55.2" hidden="1">
       <c r="A85" s="93"/>
       <c r="B85" s="71" t="s">
         <v>263</v>
@@ -9584,7 +9585,7 @@
       </c>
       <c r="V85" s="33"/>
     </row>
-    <row r="86" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="86" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A86" s="93"/>
       <c r="B86" s="71" t="s">
         <v>263</v>
@@ -9641,7 +9642,7 @@
       </c>
       <c r="V86" s="33"/>
     </row>
-    <row r="87" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="87" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A87" s="93"/>
       <c r="B87" s="71" t="s">
         <v>263</v>
@@ -9698,7 +9699,7 @@
       </c>
       <c r="V87" s="33"/>
     </row>
-    <row r="88" spans="1:22" ht="13.8">
+    <row r="88" spans="1:22" ht="13.8" hidden="1">
       <c r="A88" s="93"/>
       <c r="B88" s="71" t="s">
         <v>263</v>
@@ -9755,7 +9756,7 @@
       </c>
       <c r="V88" s="33"/>
     </row>
-    <row r="89" spans="1:22" ht="13.8">
+    <row r="89" spans="1:22" ht="13.8" hidden="1">
       <c r="A89" s="93"/>
       <c r="B89" s="71" t="s">
         <v>263</v>
@@ -9810,7 +9811,7 @@
       <c r="U89" s="71"/>
       <c r="V89" s="33"/>
     </row>
-    <row r="90" spans="1:22" ht="18" customHeight="1">
+    <row r="90" spans="1:22" ht="18" hidden="1" customHeight="1">
       <c r="A90" s="93"/>
       <c r="B90" s="66" t="s">
         <v>263</v>
@@ -9859,7 +9860,7 @@
       </c>
       <c r="V90" s="33"/>
     </row>
-    <row r="91" spans="1:22" ht="43.95" customHeight="1">
+    <row r="91" spans="1:22" ht="43.95" hidden="1" customHeight="1">
       <c r="A91" s="93"/>
       <c r="B91" s="71" t="s">
         <v>283</v>
@@ -9911,7 +9912,7 @@
       </c>
       <c r="V91" s="33"/>
     </row>
-    <row r="92" spans="1:22" ht="40.950000000000003" customHeight="1">
+    <row r="92" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A92" s="93"/>
       <c r="B92" s="71" t="s">
         <v>283</v>
@@ -9948,7 +9949,7 @@
       <c r="T92" s="111"/>
       <c r="U92" s="97"/>
     </row>
-    <row r="93" spans="1:22" ht="18" customHeight="1">
+    <row r="93" spans="1:22" ht="18" hidden="1" customHeight="1">
       <c r="A93" s="93"/>
       <c r="B93" s="71" t="s">
         <v>283</v>
@@ -9997,7 +9998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:22" ht="18" customHeight="1">
+    <row r="94" spans="1:22" ht="18" hidden="1" customHeight="1">
       <c r="A94" s="93"/>
       <c r="B94" s="71" t="s">
         <v>283</v>
@@ -10044,7 +10045,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="95" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A95" s="93"/>
       <c r="B95" s="71" t="s">
         <v>283</v>
@@ -10093,7 +10094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="96" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A96" s="93"/>
       <c r="B96" s="71" t="s">
         <v>291</v>
@@ -10126,7 +10127,7 @@
       <c r="T96" s="70"/>
       <c r="U96" s="66"/>
     </row>
-    <row r="97" spans="1:21" ht="61.2" customHeight="1">
+    <row r="97" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A97" s="93"/>
       <c r="B97" s="71" t="s">
         <v>291</v>
@@ -10177,7 +10178,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="99.6" customHeight="1">
+    <row r="98" spans="1:21" ht="99.6" hidden="1" customHeight="1">
       <c r="A98" s="93"/>
       <c r="B98" s="71" t="s">
         <v>291</v>
@@ -10230,7 +10231,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="17.399999999999999" customHeight="1">
+    <row r="99" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
       <c r="A99" s="93"/>
       <c r="B99" s="71" t="s">
         <v>300</v>
@@ -10279,7 +10280,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="17.399999999999999" customHeight="1">
+    <row r="100" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
       <c r="A100" s="93"/>
       <c r="B100" s="71" t="s">
         <v>300</v>
@@ -10328,7 +10329,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="53.4" customHeight="1">
+    <row r="101" spans="1:21" ht="53.4" hidden="1" customHeight="1">
       <c r="A101" s="93"/>
       <c r="B101" s="71" t="s">
         <v>300</v>
@@ -10377,7 +10378,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="53.4" customHeight="1">
+    <row r="102" spans="1:21" ht="53.4" hidden="1" customHeight="1">
       <c r="A102" s="93"/>
       <c r="B102" s="71" t="s">
         <v>300</v>
@@ -10433,7 +10434,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="53.4" customHeight="1">
+    <row r="103" spans="1:21" ht="53.4" hidden="1" customHeight="1">
       <c r="A103" s="93"/>
       <c r="B103" s="71" t="s">
         <v>300</v>
@@ -10484,7 +10485,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="53.4" customHeight="1">
+    <row r="104" spans="1:21" ht="53.4" hidden="1" customHeight="1">
       <c r="A104" s="93"/>
       <c r="B104" s="71" t="s">
         <v>300</v>
@@ -10536,7 +10537,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="53.4" customHeight="1">
+    <row r="105" spans="1:21" ht="53.4" hidden="1" customHeight="1">
       <c r="A105" s="93"/>
       <c r="B105" s="71" t="s">
         <v>300</v>
@@ -10590,7 +10591,7 @@
       </c>
       <c r="U105" s="66"/>
     </row>
-    <row r="106" spans="1:21" ht="34.5" customHeight="1">
+    <row r="106" spans="1:21" ht="34.5" hidden="1" customHeight="1">
       <c r="A106" s="93"/>
       <c r="B106" s="71" t="s">
         <v>300</v>
@@ -10644,7 +10645,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="96.6">
+    <row r="107" spans="1:21" ht="96.6" hidden="1">
       <c r="A107" s="93"/>
       <c r="B107" s="71" t="s">
         <v>312</v>
@@ -10695,7 +10696,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="122.4" customHeight="1">
+    <row r="108" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A108" s="93"/>
       <c r="B108" s="71" t="s">
         <v>318</v>
@@ -10740,7 +10741,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="13.8">
+    <row r="109" spans="1:21" ht="13.8" hidden="1">
       <c r="A109" s="93"/>
       <c r="B109" s="71" t="s">
         <v>318</v>
@@ -10792,7 +10793,7 @@
       <c r="T109" s="66"/>
       <c r="U109" s="66"/>
     </row>
-    <row r="110" spans="1:21" ht="13.8">
+    <row r="110" spans="1:21" ht="13.8" hidden="1">
       <c r="A110" s="93"/>
       <c r="B110" s="71" t="s">
         <v>318</v>
@@ -10846,7 +10847,7 @@
       </c>
       <c r="U110" s="71"/>
     </row>
-    <row r="111" spans="1:21" ht="60.6" customHeight="1">
+    <row r="111" spans="1:21" ht="60.6" hidden="1" customHeight="1">
       <c r="A111" s="93"/>
       <c r="B111" s="71" t="s">
         <v>323</v>
@@ -10904,7 +10905,7 @@
       </c>
       <c r="U111" s="71"/>
     </row>
-    <row r="112" spans="1:21" ht="13.8">
+    <row r="112" spans="1:21" ht="13.8" hidden="1">
       <c r="A112" s="93"/>
       <c r="B112" s="71" t="s">
         <v>325</v>
@@ -10956,7 +10957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="13.8">
+    <row r="113" spans="1:21" ht="13.8" hidden="1">
       <c r="A113" s="93"/>
       <c r="B113" s="71" t="s">
         <v>325</v>
@@ -11008,7 +11009,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="41.4">
+    <row r="114" spans="1:21" ht="41.4" hidden="1">
       <c r="A114" s="93"/>
       <c r="B114" s="71" t="s">
         <v>325</v>
@@ -11049,7 +11050,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="22.95" customHeight="1">
+    <row r="115" spans="1:21" ht="22.95" hidden="1" customHeight="1">
       <c r="A115" s="93"/>
       <c r="B115" s="71" t="s">
         <v>325</v>
@@ -11105,7 +11106,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="116" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A116" s="93"/>
       <c r="B116" s="71" t="s">
         <v>335</v>
@@ -11165,7 +11166,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="55.2">
+    <row r="117" spans="1:21" ht="55.2" hidden="1">
       <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>340</v>
@@ -11221,7 +11222,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="13.8">
+    <row r="118" spans="1:21" ht="13.8" hidden="1">
       <c r="A118" s="72">
         <v>29</v>
       </c>
@@ -11277,7 +11278,7 @@
       </c>
       <c r="U118" s="71"/>
     </row>
-    <row r="119" spans="1:21" ht="39.6" customHeight="1">
+    <row r="119" spans="1:21" ht="39.6" hidden="1" customHeight="1">
       <c r="A119" s="92">
         <v>30</v>
       </c>
@@ -11331,7 +11332,7 @@
       </c>
       <c r="U119" s="71"/>
     </row>
-    <row r="120" spans="1:21" ht="13.8">
+    <row r="120" spans="1:21" ht="13.8" hidden="1">
       <c r="A120" s="92"/>
       <c r="B120" s="71" t="s">
         <v>345</v>
@@ -11385,7 +11386,7 @@
       </c>
       <c r="U120" s="66"/>
     </row>
-    <row r="121" spans="1:21" ht="37.200000000000003" customHeight="1">
+    <row r="121" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
       <c r="A121" s="106">
         <v>31</v>
       </c>
@@ -11440,7 +11441,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="37.200000000000003" customHeight="1">
+    <row r="122" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
       <c r="A122" s="97"/>
       <c r="B122" s="71" t="s">
         <v>348</v>
@@ -11493,7 +11494,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="142.94999999999999" customHeight="1">
+    <row r="123" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
       <c r="A123" s="97"/>
       <c r="B123" s="71" t="s">
         <v>348</v>
@@ -11547,7 +11548,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="13.8">
+    <row r="124" spans="1:21" ht="13.8" hidden="1">
       <c r="A124" s="97"/>
       <c r="B124" s="71" t="s">
         <v>348</v>
@@ -11816,7 +11817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="37.950000000000003" customHeight="1">
+    <row r="129" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A129" s="68"/>
       <c r="B129" s="71" t="s">
         <v>367</v>
@@ -11870,7 +11871,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="13.8">
+    <row r="130" spans="1:21" ht="13.8" hidden="1">
       <c r="A130" s="68">
         <v>34</v>
       </c>
@@ -11926,7 +11927,7 @@
       </c>
       <c r="U130" s="66"/>
     </row>
-    <row r="131" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="131" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A131" s="68"/>
       <c r="B131" s="71" t="s">
         <v>372</v>
@@ -11980,7 +11981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="132" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A132" s="68"/>
       <c r="B132" s="71" t="s">
         <v>372</v>
@@ -12034,7 +12035,7 @@
       </c>
       <c r="U132" s="66"/>
     </row>
-    <row r="133" spans="1:21" ht="13.8">
+    <row r="133" spans="1:21" ht="13.8" hidden="1">
       <c r="A133" s="92">
         <v>35</v>
       </c>
@@ -12092,7 +12093,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="13.8">
+    <row r="134" spans="1:21" ht="13.8" hidden="1">
       <c r="A134" s="92"/>
       <c r="B134" s="71" t="s">
         <v>372</v>
@@ -12146,7 +12147,7 @@
       </c>
       <c r="U134" s="66"/>
     </row>
-    <row r="135" spans="1:21" ht="41.4">
+    <row r="135" spans="1:21" ht="41.4" hidden="1">
       <c r="A135" s="92"/>
       <c r="B135" s="71" t="s">
         <v>372</v>
@@ -12206,7 +12207,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="13.8">
+    <row r="136" spans="1:21" ht="13.8" hidden="1">
       <c r="A136" s="92"/>
       <c r="B136" s="71" t="s">
         <v>372</v>
@@ -12262,7 +12263,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="125.4" customHeight="1">
+    <row r="137" spans="1:21" ht="125.4" hidden="1" customHeight="1">
       <c r="A137" s="66"/>
       <c r="B137" s="71" t="s">
         <v>381</v>
@@ -12319,7 +12320,7 @@
       </c>
       <c r="U137" s="71"/>
     </row>
-    <row r="138" spans="1:21" ht="13.8">
+    <row r="138" spans="1:21" ht="13.8" hidden="1">
       <c r="A138" s="92">
         <v>36</v>
       </c>
@@ -12375,7 +12376,7 @@
       </c>
       <c r="U138" s="71"/>
     </row>
-    <row r="139" spans="1:21" ht="61.2" customHeight="1">
+    <row r="139" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A139" s="92"/>
       <c r="B139" s="71" t="s">
         <v>381</v>
@@ -12429,7 +12430,7 @@
       </c>
       <c r="U139" s="71"/>
     </row>
-    <row r="140" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="140" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A140" s="92"/>
       <c r="B140" s="71" t="s">
         <v>381</v>
@@ -12483,7 +12484,7 @@
       </c>
       <c r="U140" s="71"/>
     </row>
-    <row r="141" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="141" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A141" s="92"/>
       <c r="B141" s="71" t="s">
         <v>381</v>
@@ -12536,7 +12537,7 @@
       </c>
       <c r="U141" s="71"/>
     </row>
-    <row r="142" spans="1:21" ht="13.8">
+    <row r="142" spans="1:21" ht="13.8" hidden="1">
       <c r="A142" s="92"/>
       <c r="B142" s="71" t="s">
         <v>381</v>
@@ -12590,7 +12591,7 @@
       </c>
       <c r="U142" s="71"/>
     </row>
-    <row r="143" spans="1:21" ht="13.8">
+    <row r="143" spans="1:21" ht="13.8" hidden="1">
       <c r="A143" s="92"/>
       <c r="B143" s="71" t="s">
         <v>381</v>
@@ -12644,7 +12645,7 @@
       </c>
       <c r="U143" s="66"/>
     </row>
-    <row r="144" spans="1:21" ht="13.8">
+    <row r="144" spans="1:21" ht="13.8" hidden="1">
       <c r="A144" s="92"/>
       <c r="B144" s="71" t="s">
         <v>381</v>
@@ -12698,7 +12699,7 @@
       </c>
       <c r="U144" s="71"/>
     </row>
-    <row r="145" spans="1:21" ht="13.8">
+    <row r="145" spans="1:21" ht="13.8" hidden="1">
       <c r="A145" s="92">
         <v>37</v>
       </c>
@@ -12756,7 +12757,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="102" customHeight="1">
+    <row r="146" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A146" s="92"/>
       <c r="B146" s="71" t="s">
         <v>397</v>
@@ -12808,7 +12809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="18.600000000000001" customHeight="1">
+    <row r="147" spans="1:21" ht="18.600000000000001" hidden="1" customHeight="1">
       <c r="A147" s="92"/>
       <c r="B147" s="71" t="s">
         <v>397</v>
@@ -12862,7 +12863,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="18.600000000000001" customHeight="1">
+    <row r="148" spans="1:21" ht="18.600000000000001" hidden="1" customHeight="1">
       <c r="A148" s="67"/>
       <c r="B148" s="71" t="s">
         <v>402</v>
@@ -12916,7 +12917,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="35.4" customHeight="1">
+    <row r="149" spans="1:21" ht="35.4" hidden="1" customHeight="1">
       <c r="A149" s="93"/>
       <c r="B149" s="71" t="s">
         <v>402</v>
@@ -12969,7 +12970,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="150" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>402</v>
@@ -13024,7 +13025,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="151" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A151" s="68"/>
       <c r="B151" s="71" t="s">
         <v>407</v>
@@ -13078,7 +13079,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="13.8">
+    <row r="152" spans="1:21" ht="13.8" hidden="1">
       <c r="A152" s="66">
         <v>39</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="153" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A153" s="98">
         <v>40</v>
       </c>
@@ -13194,7 +13195,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="122.4" customHeight="1">
+    <row r="154" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A154" s="93"/>
       <c r="B154" s="71" t="s">
         <v>413</v>
@@ -13245,7 +13246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="183.6" customHeight="1">
+    <row r="155" spans="1:21" ht="183.6" hidden="1" customHeight="1">
       <c r="A155" s="93"/>
       <c r="B155" s="71" t="s">
         <v>413</v>
@@ -13294,7 +13295,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="122.4" customHeight="1">
+    <row r="156" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A156" s="93"/>
       <c r="B156" s="71" t="s">
         <v>413</v>
@@ -13345,7 +13346,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="122.4" customHeight="1">
+    <row r="157" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A157" s="93"/>
       <c r="B157" s="71" t="s">
         <v>413</v>
@@ -13401,7 +13402,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="13.8">
+    <row r="158" spans="1:21" ht="13.8" hidden="1">
       <c r="A158" s="93"/>
       <c r="B158" s="71" t="s">
         <v>413</v>
@@ -13457,7 +13458,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="13.8">
+    <row r="159" spans="1:21" ht="13.8" hidden="1">
       <c r="A159" s="93"/>
       <c r="B159" s="71" t="s">
         <v>413</v>
@@ -13513,7 +13514,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="55.2">
+    <row r="160" spans="1:21" ht="55.2" hidden="1">
       <c r="A160" s="93"/>
       <c r="B160" s="71" t="s">
         <v>427</v>
@@ -13565,7 +13566,7 @@
       </c>
       <c r="U160" s="71"/>
     </row>
-    <row r="161" spans="1:21" ht="27.6">
+    <row r="161" spans="1:21" ht="27.6" hidden="1">
       <c r="A161" s="93"/>
       <c r="B161" s="71" t="s">
         <v>427</v>
@@ -13620,7 +13621,7 @@
       </c>
       <c r="U161" s="71"/>
     </row>
-    <row r="162" spans="1:21" ht="13.8">
+    <row r="162" spans="1:21" ht="13.8" hidden="1">
       <c r="A162" s="93"/>
       <c r="B162" s="71" t="s">
         <v>427</v>
@@ -13672,7 +13673,7 @@
       </c>
       <c r="U162" s="71"/>
     </row>
-    <row r="163" spans="1:21" ht="13.8">
+    <row r="163" spans="1:21" ht="13.8" hidden="1">
       <c r="A163" s="93"/>
       <c r="B163" s="71" t="s">
         <v>427</v>
@@ -13728,7 +13729,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="27.75" customHeight="1">
+    <row r="164" spans="1:21" ht="27.75" hidden="1" customHeight="1">
       <c r="A164" s="94"/>
       <c r="B164" s="71" t="s">
         <v>435</v>
@@ -13781,7 +13782,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="37.950000000000003" customHeight="1">
+    <row r="165" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A165" s="93"/>
       <c r="B165" s="71" t="s">
         <v>435</v>
@@ -13834,7 +13835,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="13.8">
+    <row r="166" spans="1:21" ht="13.8" hidden="1">
       <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>435</v>
@@ -13889,7 +13890,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="13.8">
+    <row r="167" spans="1:21" ht="13.8" hidden="1">
       <c r="A167" s="68"/>
       <c r="B167" s="71" t="s">
         <v>442</v>
@@ -13947,7 +13948,7 @@
       </c>
       <c r="U167" s="71"/>
     </row>
-    <row r="168" spans="1:21" ht="27.6">
+    <row r="168" spans="1:21" ht="27.6" hidden="1">
       <c r="A168" s="66">
         <v>43</v>
       </c>
@@ -14009,7 +14010,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="41.4">
+    <row r="169" spans="1:21" ht="41.4" hidden="1">
       <c r="A169" s="99">
         <v>44</v>
       </c>
@@ -14069,7 +14070,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="45" customHeight="1">
+    <row r="170" spans="1:21" ht="45" hidden="1" customHeight="1">
       <c r="A170" s="100"/>
       <c r="B170" s="71" t="s">
         <v>449</v>
@@ -14120,7 +14121,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="37.200000000000003" customHeight="1">
+    <row r="171" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
       <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>449</v>
@@ -14178,7 +14179,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="13.8">
+    <row r="172" spans="1:21" ht="13.8" hidden="1">
       <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>449</v>
@@ -14234,7 +14235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="13.8">
+    <row r="173" spans="1:21" ht="13.8" hidden="1">
       <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>456</v>
@@ -14290,7 +14291,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="40.200000000000003" customHeight="1">
+    <row r="174" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A174" s="92">
         <v>45</v>
       </c>
@@ -14347,7 +14348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="13.8">
+    <row r="175" spans="1:21" ht="13.8" hidden="1">
       <c r="A175" s="92"/>
       <c r="B175" s="71" t="s">
         <v>458</v>
@@ -14403,7 +14404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="13.8">
+    <row r="176" spans="1:21" ht="13.8" hidden="1">
       <c r="A176" s="92"/>
       <c r="B176" s="71" t="s">
         <v>458</v>
@@ -14457,7 +14458,7 @@
       </c>
       <c r="U176" s="71"/>
     </row>
-    <row r="177" spans="1:21" ht="13.8">
+    <row r="177" spans="1:21" ht="13.8" hidden="1">
       <c r="A177" s="92"/>
       <c r="B177" s="71" t="s">
         <v>458</v>
@@ -14513,7 +14514,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="27.6">
+    <row r="178" spans="1:21" ht="27.6" hidden="1">
       <c r="A178" s="92"/>
       <c r="B178" s="71" t="s">
         <v>458</v>
@@ -14567,7 +14568,7 @@
       </c>
       <c r="U178" s="71"/>
     </row>
-    <row r="179" spans="1:21" ht="13.8">
+    <row r="179" spans="1:21" ht="13.8" hidden="1">
       <c r="A179" s="92"/>
       <c r="B179" s="71" t="s">
         <v>466</v>
@@ -14623,7 +14624,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="13.8">
+    <row r="180" spans="1:21" ht="13.8" hidden="1">
       <c r="A180" s="92"/>
       <c r="B180" s="71" t="s">
         <v>468</v>
@@ -14677,7 +14678,7 @@
       </c>
       <c r="U180" s="66"/>
     </row>
-    <row r="181" spans="1:21" ht="13.8">
+    <row r="181" spans="1:21" ht="13.8" hidden="1">
       <c r="A181" s="75"/>
       <c r="B181" s="71" t="s">
         <v>471</v>
@@ -14731,7 +14732,7 @@
       </c>
       <c r="U181" s="66"/>
     </row>
-    <row r="182" spans="1:21" ht="39.6" customHeight="1">
+    <row r="182" spans="1:21" ht="39.6" hidden="1" customHeight="1">
       <c r="A182" s="75"/>
       <c r="B182" s="71" t="s">
         <v>471</v>
@@ -14784,7 +14785,7 @@
       </c>
       <c r="U182" s="66"/>
     </row>
-    <row r="183" spans="1:21" ht="61.2" customHeight="1">
+    <row r="183" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A183" s="102">
         <v>46</v>
       </c>
@@ -14838,7 +14839,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="61.2" customHeight="1">
+    <row r="184" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>471</v>
@@ -14892,7 +14893,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="13.8">
+    <row r="185" spans="1:21" ht="13.8" hidden="1">
       <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>471</v>
@@ -14948,7 +14949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="13.8">
+    <row r="186" spans="1:21" ht="13.8" hidden="1">
       <c r="A186" s="72"/>
       <c r="B186" s="71" t="s">
         <v>483</v>
@@ -15006,7 +15007,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="13.8">
+    <row r="187" spans="1:21" ht="13.8" hidden="1">
       <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>483</v>
@@ -15056,7 +15057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="13.8">
+    <row r="188" spans="1:21" ht="13.8" hidden="1">
       <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>483</v>
@@ -15108,7 +15109,7 @@
       <c r="T188" s="80"/>
       <c r="U188" s="71"/>
     </row>
-    <row r="189" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="189" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>483</v>
@@ -15160,7 +15161,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="81" customHeight="1">
+    <row r="190" spans="1:21" ht="81" hidden="1" customHeight="1">
       <c r="A190" s="66"/>
       <c r="B190" s="71" t="s">
         <v>490</v>
@@ -15214,7 +15215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="64.95" customHeight="1">
+    <row r="191" spans="1:21" ht="64.95" hidden="1" customHeight="1">
       <c r="A191" s="92">
         <v>48</v>
       </c>
@@ -15269,7 +15270,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="192" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A192" s="92"/>
       <c r="B192" s="71" t="s">
         <v>490</v>
@@ -15322,7 +15323,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="13.8">
+    <row r="193" spans="1:21" ht="13.8" hidden="1">
       <c r="A193" s="92"/>
       <c r="B193" s="71" t="s">
         <v>490</v>
@@ -15378,7 +15379,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="13.8">
+    <row r="194" spans="1:21" ht="13.8" hidden="1">
       <c r="A194" s="66">
         <v>49</v>
       </c>
@@ -15407,7 +15408,7 @@
       <c r="T194" s="66"/>
       <c r="U194" s="66"/>
     </row>
-    <row r="195" spans="1:21" ht="13.8">
+    <row r="195" spans="1:21" ht="13.8" hidden="1">
       <c r="A195" s="93"/>
       <c r="B195" s="71" t="s">
         <v>502</v>
@@ -15461,7 +15462,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="24.6" customHeight="1">
+    <row r="196" spans="1:21" ht="24.6" hidden="1" customHeight="1">
       <c r="A196" s="94"/>
       <c r="B196" s="71" t="s">
         <v>502</v>
@@ -15515,7 +15516,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="13.8">
+    <row r="197" spans="1:21" ht="13.8" hidden="1">
       <c r="A197" s="92">
         <v>51</v>
       </c>
@@ -15570,7 +15571,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="13.8">
+    <row r="198" spans="1:21" ht="13.8" hidden="1">
       <c r="A198" s="92"/>
       <c r="B198" s="71" t="s">
         <v>506</v>
@@ -15626,7 +15627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="13.8">
+    <row r="199" spans="1:21" ht="13.8" hidden="1">
       <c r="A199" s="92"/>
       <c r="B199" s="71" t="s">
         <v>506</v>
@@ -15682,7 +15683,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="200" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A200" s="92"/>
       <c r="B200" s="71" t="s">
         <v>506</v>
@@ -15737,7 +15738,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="201" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="71" t="s">
         <v>513</v>
@@ -15791,7 +15792,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="202" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="71" t="s">
         <v>513</v>
@@ -15839,7 +15840,7 @@
       <c r="T202" s="70"/>
       <c r="U202" s="66"/>
     </row>
-    <row r="203" spans="1:21" ht="13.8">
+    <row r="203" spans="1:21" ht="13.8" hidden="1">
       <c r="A203" s="66">
         <v>52</v>
       </c>
@@ -15897,7 +15898,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="204" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A204" s="92">
         <v>53</v>
       </c>
@@ -15954,7 +15955,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="55.2">
+    <row r="205" spans="1:21" ht="55.2" hidden="1">
       <c r="A205" s="92"/>
       <c r="B205" s="71" t="s">
         <v>518</v>
@@ -16010,7 +16011,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="13.8">
+    <row r="206" spans="1:21" ht="13.8" hidden="1">
       <c r="A206" s="92"/>
       <c r="B206" s="66" t="s">
         <v>522</v>
@@ -16066,7 +16067,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="13.8">
+    <row r="207" spans="1:21" ht="13.8" hidden="1">
       <c r="A207" s="92">
         <v>54</v>
       </c>
@@ -16122,7 +16123,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="13.8">
+    <row r="208" spans="1:21" ht="13.8" hidden="1">
       <c r="A208" s="92"/>
       <c r="B208" s="71" t="s">
         <v>525</v>
@@ -16180,7 +16181,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="32.4" customHeight="1">
+    <row r="209" spans="1:21" ht="32.4" hidden="1" customHeight="1">
       <c r="A209" s="92">
         <v>55</v>
       </c>
@@ -16237,7 +16238,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="13.8">
+    <row r="210" spans="1:21" ht="13.8" hidden="1">
       <c r="A210" s="92"/>
       <c r="B210" s="71" t="s">
         <v>528</v>
@@ -16291,7 +16292,7 @@
       </c>
       <c r="U210" s="71"/>
     </row>
-    <row r="211" spans="1:21" ht="16.2" customHeight="1">
+    <row r="211" spans="1:21" ht="16.2" hidden="1" customHeight="1">
       <c r="A211" s="92"/>
       <c r="B211" s="71" t="s">
         <v>528</v>
@@ -16345,7 +16346,7 @@
       </c>
       <c r="U211" s="66"/>
     </row>
-    <row r="212" spans="1:21" ht="80.400000000000006" customHeight="1">
+    <row r="212" spans="1:21" ht="80.400000000000006" hidden="1" customHeight="1">
       <c r="A212" s="92">
         <v>56</v>
       </c>
@@ -16400,7 +16401,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="13.8">
+    <row r="213" spans="1:21" ht="13.8" hidden="1">
       <c r="A213" s="92"/>
       <c r="B213" s="71" t="s">
         <v>537</v>
@@ -16458,7 +16459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="27.6">
+    <row r="214" spans="1:21" ht="27.6" hidden="1">
       <c r="A214" s="99">
         <v>57</v>
       </c>
@@ -16513,7 +16514,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="13.8">
+    <row r="215" spans="1:21" ht="13.8" hidden="1">
       <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>539</v>
@@ -16569,7 +16570,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="13.8">
+    <row r="216" spans="1:21" ht="13.8" hidden="1">
       <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>539</v>
@@ -16625,7 +16626,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="41.4">
+    <row r="217" spans="1:21" ht="41.4" hidden="1">
       <c r="A217" s="93"/>
       <c r="B217" s="71" t="s">
         <v>539</v>
@@ -16681,7 +16682,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="13.8">
+    <row r="218" spans="1:21" ht="13.8" hidden="1">
       <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>539</v>
@@ -16737,7 +16738,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="13.8">
+    <row r="219" spans="1:21" ht="13.8" hidden="1">
       <c r="A219" s="74"/>
       <c r="B219" s="71" t="s">
         <v>550</v>
@@ -16793,7 +16794,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="13.8">
+    <row r="220" spans="1:21" ht="13.8" hidden="1">
       <c r="A220" s="74"/>
       <c r="B220" s="71" t="s">
         <v>550</v>
@@ -16849,7 +16850,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="13.8">
+    <row r="221" spans="1:21" ht="13.8" hidden="1">
       <c r="A221" s="74"/>
       <c r="B221" s="71" t="s">
         <v>550</v>
@@ -16902,7 +16903,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="222" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A222" s="66">
         <v>58</v>
       </c>
@@ -16960,7 +16961,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="34.200000000000003" customHeight="1">
+    <row r="223" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A223" s="92">
         <v>59</v>
       </c>
@@ -17015,7 +17016,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="34.200000000000003" customHeight="1">
+    <row r="224" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A224" s="92"/>
       <c r="B224" s="71" t="s">
         <v>560</v>
@@ -17071,7 +17072,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="225" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A225" s="92"/>
       <c r="B225" s="71" t="s">
         <v>560</v>
@@ -17122,7 +17123,7 @@
       </c>
       <c r="U225" s="71"/>
     </row>
-    <row r="226" spans="1:21" ht="13.8">
+    <row r="226" spans="1:21" ht="13.8" hidden="1">
       <c r="A226" s="92"/>
       <c r="B226" s="71" t="s">
         <v>560</v>
@@ -17178,7 +17179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="27.6">
+    <row r="227" spans="1:21" ht="27.6" hidden="1">
       <c r="A227" s="92"/>
       <c r="B227" s="71" t="s">
         <v>560</v>
@@ -17230,7 +17231,7 @@
       <c r="T227" s="70"/>
       <c r="U227" s="66"/>
     </row>
-    <row r="228" spans="1:21" ht="13.8">
+    <row r="228" spans="1:21" ht="13.8" hidden="1">
       <c r="A228" s="92"/>
       <c r="B228" s="71" t="s">
         <v>560</v>
@@ -17286,7 +17287,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="229" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A229" s="66"/>
       <c r="B229" s="71" t="s">
         <v>572</v>
@@ -17340,7 +17341,7 @@
       </c>
       <c r="U229" s="66"/>
     </row>
-    <row r="230" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="230" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A230" s="66"/>
       <c r="B230" s="71" t="s">
         <v>572</v>
@@ -17394,7 +17395,7 @@
       </c>
       <c r="U230" s="66"/>
     </row>
-    <row r="231" spans="1:21" ht="20.399999999999999" customHeight="1">
+    <row r="231" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A231" s="66"/>
       <c r="B231" s="71" t="s">
         <v>572</v>
@@ -17448,7 +17449,7 @@
       </c>
       <c r="U231" s="66"/>
     </row>
-    <row r="232" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="232" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A232" s="66">
         <v>60</v>
       </c>
@@ -17503,7 +17504,7 @@
       </c>
       <c r="U232" s="66"/>
     </row>
-    <row r="233" spans="1:21" ht="13.8">
+    <row r="233" spans="1:21" ht="13.8" hidden="1">
       <c r="A233" s="66">
         <v>61</v>
       </c>
@@ -17532,7 +17533,7 @@
       <c r="T233" s="66"/>
       <c r="U233" s="66"/>
     </row>
-    <row r="234" spans="1:21" ht="224.4" customHeight="1">
+    <row r="234" spans="1:21" ht="224.4" hidden="1" customHeight="1">
       <c r="A234" s="66">
         <v>62</v>
       </c>
@@ -17588,7 +17589,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="102" customHeight="1">
+    <row r="235" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A235" s="98">
         <v>63</v>
       </c>
@@ -17642,7 +17643,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="102" customHeight="1">
+    <row r="236" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A236" s="93"/>
       <c r="B236" s="71" t="s">
         <v>581</v>
@@ -17696,7 +17697,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="102" customHeight="1">
+    <row r="237" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A237" s="93"/>
       <c r="B237" s="71" t="s">
         <v>581</v>
@@ -17750,7 +17751,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="39.6" customHeight="1">
+    <row r="238" spans="1:21" ht="39.6" hidden="1" customHeight="1">
       <c r="A238" s="93"/>
       <c r="B238" s="71" t="s">
         <v>581</v>
@@ -17805,7 +17806,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="239" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A239" s="93"/>
       <c r="B239" s="71" t="s">
         <v>581</v>
@@ -17860,7 +17861,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="240" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>595</v>
@@ -17912,7 +17913,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="241" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A241" s="92">
         <v>64</v>
       </c>
@@ -17967,7 +17968,7 @@
       </c>
       <c r="U241" s="71"/>
     </row>
-    <row r="242" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="242" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A242" s="92"/>
       <c r="B242" s="71" t="s">
         <v>598</v>
@@ -18021,7 +18022,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="243" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A243" s="92"/>
       <c r="B243" s="71" t="s">
         <v>598</v>
@@ -18081,7 +18082,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="41.4">
+    <row r="244" spans="1:21" ht="41.4" hidden="1">
       <c r="A244" s="92"/>
       <c r="B244" s="71" t="s">
         <v>598</v>
@@ -18133,7 +18134,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="13.8">
+    <row r="245" spans="1:21" ht="13.8" hidden="1">
       <c r="A245" s="92"/>
       <c r="B245" s="71" t="s">
         <v>598</v>
@@ -18168,7 +18169,7 @@
       <c r="T245" s="80"/>
       <c r="U245" s="71"/>
     </row>
-    <row r="246" spans="1:21" ht="13.8">
+    <row r="246" spans="1:21" ht="13.8" hidden="1">
       <c r="A246" s="92"/>
       <c r="B246" s="71" t="s">
         <v>598</v>
@@ -18220,7 +18221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="247" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A247" s="92"/>
       <c r="B247" s="71" t="s">
         <v>598</v>
@@ -18275,7 +18276,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="248" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A248" s="66"/>
       <c r="B248" s="71" t="s">
         <v>606</v>
@@ -18329,7 +18330,7 @@
       </c>
       <c r="U248" s="71"/>
     </row>
-    <row r="249" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="249" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A249" s="92">
         <v>65</v>
       </c>
@@ -18384,7 +18385,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="250" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A250" s="92"/>
       <c r="B250" s="71" t="s">
         <v>606</v>
@@ -18438,7 +18439,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="251" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A251" s="92"/>
       <c r="B251" s="71" t="s">
         <v>606</v>
@@ -18493,7 +18494,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="13.8">
+    <row r="252" spans="1:21" ht="13.8" hidden="1">
       <c r="A252" s="66">
         <v>66</v>
       </c>
@@ -18522,7 +18523,7 @@
       <c r="T252" s="66"/>
       <c r="U252" s="66"/>
     </row>
-    <row r="253" spans="1:21" ht="13.8">
+    <row r="253" spans="1:21" ht="13.8" hidden="1">
       <c r="A253" s="66"/>
       <c r="B253" s="71" t="s">
         <v>615</v>
@@ -18572,7 +18573,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="13.8">
+    <row r="254" spans="1:21" ht="13.8" hidden="1">
       <c r="A254" s="66">
         <v>67</v>
       </c>
@@ -18628,7 +18629,7 @@
       </c>
       <c r="U254" s="66"/>
     </row>
-    <row r="255" spans="1:21" ht="27.6">
+    <row r="255" spans="1:21" ht="27.6" hidden="1">
       <c r="A255" s="98">
         <v>68</v>
       </c>
@@ -18682,7 +18683,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="27.6">
+    <row r="256" spans="1:21" ht="27.6" hidden="1">
       <c r="A256" s="93"/>
       <c r="B256" s="71" t="s">
         <v>619</v>
@@ -18737,7 +18738,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="13.8">
+    <row r="257" spans="1:21" ht="13.8" hidden="1">
       <c r="A257" s="93"/>
       <c r="B257" s="71" t="s">
         <v>619</v>
@@ -18793,7 +18794,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="13.8">
+    <row r="258" spans="1:21" ht="13.8" hidden="1">
       <c r="A258" s="93"/>
       <c r="B258" s="71" t="s">
         <v>619</v>
@@ -18849,7 +18850,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="13.8">
+    <row r="259" spans="1:21" ht="13.8" hidden="1">
       <c r="A259" s="93"/>
       <c r="B259" s="71" t="s">
         <v>619</v>
@@ -18903,7 +18904,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="34.200000000000003" customHeight="1">
+    <row r="260" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>619</v>
@@ -18959,7 +18960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="55.2">
+    <row r="261" spans="1:21" ht="55.2" hidden="1">
       <c r="A261" s="98">
         <v>69</v>
       </c>
@@ -19014,7 +19015,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="102" customHeight="1">
+    <row r="262" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A262" s="93"/>
       <c r="B262" s="71" t="s">
         <v>629</v>
@@ -19066,7 +19067,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="102" customHeight="1">
+    <row r="263" spans="1:21" ht="102" hidden="1" customHeight="1">
       <c r="A263" s="93"/>
       <c r="B263" s="71" t="s">
         <v>637</v>
@@ -19114,7 +19115,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="55.2">
+    <row r="264" spans="1:21" ht="55.2" hidden="1">
       <c r="A264" s="93"/>
       <c r="B264" s="71" t="s">
         <v>637</v>
@@ -19164,7 +19165,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="46.2" customHeight="1">
+    <row r="265" spans="1:21" ht="46.2" hidden="1" customHeight="1">
       <c r="A265" s="93"/>
       <c r="B265" s="71" t="s">
         <v>629</v>
@@ -19218,7 +19219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="46.2" customHeight="1">
+    <row r="266" spans="1:21" ht="46.2" hidden="1" customHeight="1">
       <c r="A266" s="67"/>
       <c r="B266" s="71" t="s">
         <v>643</v>
@@ -19275,7 +19276,7 @@
       </c>
       <c r="U266" s="71"/>
     </row>
-    <row r="267" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="267" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A267" s="92">
         <v>70</v>
       </c>
@@ -19333,7 +19334,7 @@
       </c>
       <c r="U267" s="71"/>
     </row>
-    <row r="268" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="268" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A268" s="92"/>
       <c r="B268" s="71" t="s">
         <v>643</v>
@@ -19389,7 +19390,7 @@
       </c>
       <c r="U268" s="71"/>
     </row>
-    <row r="269" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="269" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A269" s="92"/>
       <c r="B269" s="71" t="s">
         <v>643</v>
@@ -19445,7 +19446,7 @@
       </c>
       <c r="U269" s="71"/>
     </row>
-    <row r="270" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="270" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A270" s="92"/>
       <c r="B270" s="71" t="s">
         <v>643</v>
@@ -19501,7 +19502,7 @@
       </c>
       <c r="U270" s="66"/>
     </row>
-    <row r="271" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="271" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A271" s="66"/>
       <c r="B271" s="71" t="s">
         <v>653</v>
@@ -19557,7 +19558,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="61.2" customHeight="1">
+    <row r="272" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A272" s="92">
         <v>71</v>
       </c>
@@ -19613,7 +19614,7 @@
       </c>
       <c r="U272" s="71"/>
     </row>
-    <row r="273" spans="1:21" ht="61.2" customHeight="1">
+    <row r="273" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A273" s="92"/>
       <c r="B273" s="71" t="s">
         <v>653</v>
@@ -19669,7 +19670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="13.8">
+    <row r="274" spans="1:21" ht="13.8" hidden="1">
       <c r="A274" s="92"/>
       <c r="B274" s="71" t="s">
         <v>653</v>
@@ -19725,7 +19726,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="13.8">
+    <row r="275" spans="1:21" ht="13.8" hidden="1">
       <c r="A275" s="92"/>
       <c r="B275" s="71" t="s">
         <v>653</v>
@@ -19781,7 +19782,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="13.8">
+    <row r="276" spans="1:21" ht="13.8" hidden="1">
       <c r="A276" s="92"/>
       <c r="B276" s="66" t="s">
         <v>660</v>
@@ -19837,7 +19838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="13.8">
+    <row r="277" spans="1:21" ht="13.8" hidden="1">
       <c r="A277" s="66">
         <v>72</v>
       </c>
@@ -19893,7 +19894,7 @@
       </c>
       <c r="U277" s="66"/>
     </row>
-    <row r="278" spans="1:21" ht="13.8">
+    <row r="278" spans="1:21" ht="13.8" hidden="1">
       <c r="A278" s="66"/>
       <c r="B278" s="71" t="s">
         <v>665</v>
@@ -19949,7 +19950,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="13.8">
+    <row r="279" spans="1:21" ht="13.8" hidden="1">
       <c r="A279" s="66"/>
       <c r="B279" s="71" t="s">
         <v>665</v>
@@ -20001,7 +20002,7 @@
       <c r="T279" s="70"/>
       <c r="U279" s="66"/>
     </row>
-    <row r="280" spans="1:21" ht="13.8">
+    <row r="280" spans="1:21" ht="13.8" hidden="1">
       <c r="A280" s="66">
         <v>73</v>
       </c>
@@ -20057,7 +20058,7 @@
       </c>
       <c r="U280" s="66"/>
     </row>
-    <row r="281" spans="1:21" ht="27.6">
+    <row r="281" spans="1:21" ht="27.6" hidden="1">
       <c r="A281" s="92">
         <v>74</v>
       </c>
@@ -20111,7 +20112,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="13.8">
+    <row r="282" spans="1:21" ht="13.8" hidden="1">
       <c r="A282" s="92"/>
       <c r="B282" s="71" t="s">
         <v>669</v>
@@ -20160,7 +20161,7 @@
       </c>
       <c r="U282" s="66"/>
     </row>
-    <row r="283" spans="1:21" ht="37.200000000000003" customHeight="1">
+    <row r="283" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
       <c r="A283" s="92">
         <v>75</v>
       </c>
@@ -20215,7 +20216,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="13.8">
+    <row r="284" spans="1:21" ht="13.8" hidden="1">
       <c r="A284" s="92"/>
       <c r="B284" s="71" t="s">
         <v>672</v>
@@ -20269,7 +20270,7 @@
       </c>
       <c r="U284" s="71"/>
     </row>
-    <row r="285" spans="1:21" ht="13.8">
+    <row r="285" spans="1:21" ht="13.8" hidden="1">
       <c r="A285" s="94">
         <v>76</v>
       </c>
@@ -20327,7 +20328,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="286" spans="1:21" ht="13.8">
+    <row r="286" spans="1:21" ht="13.8" hidden="1">
       <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>676</v>
@@ -20383,7 +20384,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="13.8">
+    <row r="287" spans="1:21" ht="13.8" hidden="1">
       <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>676</v>
@@ -20439,7 +20440,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="13.8">
+    <row r="288" spans="1:21" ht="13.8" hidden="1">
       <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>676</v>
@@ -20495,7 +20496,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="13.8">
+    <row r="289" spans="1:21" ht="13.8" hidden="1">
       <c r="A289" s="92"/>
       <c r="B289" s="71" t="s">
         <v>676</v>
@@ -20548,7 +20549,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="27.6">
+    <row r="290" spans="1:21" ht="27.6" hidden="1">
       <c r="A290" s="92"/>
       <c r="B290" s="71" t="s">
         <v>676</v>
@@ -20602,7 +20603,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="13.8">
+    <row r="291" spans="1:21" ht="13.8" hidden="1">
       <c r="A291" s="92"/>
       <c r="B291" s="71" t="s">
         <v>676</v>
@@ -20658,7 +20659,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="292" spans="1:21" ht="13.8">
+    <row r="292" spans="1:21" ht="13.8" hidden="1">
       <c r="A292" s="92"/>
       <c r="B292" s="71" t="s">
         <v>676</v>
@@ -20710,7 +20711,7 @@
       </c>
       <c r="U292" s="71"/>
     </row>
-    <row r="293" spans="1:21" ht="13.8">
+    <row r="293" spans="1:21" ht="13.8" hidden="1">
       <c r="A293" s="92"/>
       <c r="B293" s="71" t="s">
         <v>676</v>
@@ -20764,7 +20765,7 @@
       </c>
       <c r="U293" s="71"/>
     </row>
-    <row r="294" spans="1:21" ht="41.4">
+    <row r="294" spans="1:21" ht="41.4" hidden="1">
       <c r="A294" s="66"/>
       <c r="B294" s="71" t="s">
         <v>691</v>
@@ -20824,7 +20825,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="96.6">
+    <row r="295" spans="1:21" ht="96.6" hidden="1">
       <c r="A295" s="92">
         <v>77</v>
       </c>
@@ -20886,7 +20887,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="27.6">
+    <row r="296" spans="1:21" ht="27.6" hidden="1">
       <c r="A296" s="92"/>
       <c r="B296" s="71" t="s">
         <v>691</v>
@@ -20946,7 +20947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="13.8">
+    <row r="297" spans="1:21" ht="13.8" hidden="1">
       <c r="A297" s="92"/>
       <c r="B297" s="71" t="s">
         <v>691</v>
@@ -21006,7 +21007,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="27.6">
+    <row r="298" spans="1:21" ht="27.6" hidden="1">
       <c r="A298" s="92">
         <v>78</v>
       </c>
@@ -21061,7 +21062,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="13.8">
+    <row r="299" spans="1:21" ht="13.8" hidden="1">
       <c r="A299" s="92"/>
       <c r="B299" s="71" t="s">
         <v>702</v>
@@ -21115,7 +21116,7 @@
       </c>
       <c r="U299" s="71"/>
     </row>
-    <row r="300" spans="1:21" ht="13.8">
+    <row r="300" spans="1:21" ht="13.8" hidden="1">
       <c r="A300" s="92"/>
       <c r="B300" s="71" t="s">
         <v>702</v>
@@ -21171,7 +21172,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="13.8">
+    <row r="301" spans="1:21" ht="13.8" hidden="1">
       <c r="A301" s="93"/>
       <c r="B301" s="71" t="s">
         <v>637</v>
@@ -21225,7 +21226,7 @@
       </c>
       <c r="U301" s="71"/>
     </row>
-    <row r="302" spans="1:21" ht="13.8">
+    <row r="302" spans="1:21" ht="13.8" hidden="1">
       <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>637</v>
@@ -21281,7 +21282,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="27.6">
+    <row r="303" spans="1:21" ht="27.6" hidden="1">
       <c r="A303" s="98">
         <v>80</v>
       </c>
@@ -21336,7 +21337,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="13.8">
+    <row r="304" spans="1:21" ht="13.8" hidden="1">
       <c r="A304" s="93"/>
       <c r="B304" s="71" t="s">
         <v>716</v>
@@ -21390,7 +21391,7 @@
       </c>
       <c r="U304" s="71"/>
     </row>
-    <row r="305" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="305" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A305" s="98">
         <v>81</v>
       </c>
@@ -21444,7 +21445,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="306" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A306" s="93"/>
       <c r="B306" s="71" t="s">
         <v>718</v>
@@ -21498,7 +21499,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="307" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A307" s="93"/>
       <c r="B307" s="71" t="s">
         <v>718</v>
@@ -21551,7 +21552,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="308" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>718</v>
@@ -21604,7 +21605,7 @@
       </c>
       <c r="U308" s="66"/>
     </row>
-    <row r="309" spans="1:21" ht="126" customHeight="1">
+    <row r="309" spans="1:21" ht="126" hidden="1" customHeight="1">
       <c r="A309" s="66">
         <v>82</v>
       </c>
@@ -21665,7 +21666,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="310" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A310" s="66">
         <v>83</v>
       </c>
@@ -21726,7 +21727,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="311" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A311" s="92">
         <v>84</v>
       </c>
@@ -21757,7 +21758,7 @@
       <c r="T311" s="92"/>
       <c r="U311" s="92"/>
     </row>
-    <row r="312" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="312" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A312" s="92"/>
       <c r="B312" s="71" t="s">
         <v>728</v>
@@ -21817,7 +21818,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="313" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A313" s="92"/>
       <c r="B313" s="71" t="s">
         <v>732</v>
@@ -21846,7 +21847,7 @@
       <c r="T313" s="96"/>
       <c r="U313" s="92"/>
     </row>
-    <row r="314" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="314" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A314" s="92"/>
       <c r="B314" s="71" t="s">
         <v>732</v>
@@ -21904,7 +21905,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="315" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A315" s="92"/>
       <c r="B315" s="71" t="s">
         <v>732</v>
@@ -21960,7 +21961,7 @@
       </c>
       <c r="U315" s="71"/>
     </row>
-    <row r="316" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="316" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A316" s="92"/>
       <c r="B316" s="71" t="s">
         <v>732</v>
@@ -22017,7 +22018,7 @@
       </c>
       <c r="U316" s="71"/>
     </row>
-    <row r="317" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="317" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A317" s="72"/>
       <c r="B317" s="71" t="s">
         <v>738</v>
@@ -22071,7 +22072,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="318" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A318" s="72"/>
       <c r="B318" s="71" t="s">
         <v>738</v>
@@ -22114,7 +22115,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="319" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A319" s="98">
         <v>85</v>
       </c>
@@ -22163,7 +22164,7 @@
       <c r="T319" s="80"/>
       <c r="U319" s="71"/>
     </row>
-    <row r="320" spans="1:21" ht="61.2" customHeight="1">
+    <row r="320" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>738</v>
@@ -22216,7 +22217,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="61.2" customHeight="1">
+    <row r="321" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A321" s="99">
         <v>86</v>
       </c>
@@ -22270,7 +22271,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="61.2" customHeight="1">
+    <row r="322" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>744</v>
@@ -22320,7 +22321,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="61.2" customHeight="1">
+    <row r="323" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>744</v>
@@ -22374,7 +22375,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="61.2" customHeight="1">
+    <row r="324" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>744</v>
@@ -22428,7 +22429,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="93" customHeight="1">
+    <row r="325" spans="1:21" ht="93" hidden="1" customHeight="1">
       <c r="A325" s="93"/>
       <c r="B325" s="66" t="s">
         <v>744</v>
@@ -22480,7 +22481,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="61.2" customHeight="1">
+    <row r="326" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A326" s="93"/>
       <c r="B326" s="66" t="s">
         <v>744</v>
@@ -22532,7 +22533,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="61.2" customHeight="1">
+    <row r="327" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>744</v>
@@ -22588,7 +22589,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="61.2" customHeight="1">
+    <row r="328" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>744</v>
@@ -22640,7 +22641,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="61.2" customHeight="1">
+    <row r="329" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>744</v>
@@ -22694,7 +22695,7 @@
       </c>
       <c r="U329" s="71"/>
     </row>
-    <row r="330" spans="1:21" ht="13.8">
+    <row r="330" spans="1:21" ht="13.8" hidden="1">
       <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>744</v>
@@ -22748,7 +22749,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="331" spans="1:21" ht="41.4" customHeight="1">
+    <row r="331" spans="1:21" ht="41.4" hidden="1" customHeight="1">
       <c r="A331" s="68"/>
       <c r="B331" s="71" t="s">
         <v>762</v>
@@ -22800,7 +22801,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="332" spans="1:21" ht="13.8">
+    <row r="332" spans="1:21" ht="13.8" hidden="1">
       <c r="A332" s="66">
         <v>88</v>
       </c>
@@ -22829,7 +22830,7 @@
       <c r="T332" s="66"/>
       <c r="U332" s="66"/>
     </row>
-    <row r="333" spans="1:21" ht="41.4">
+    <row r="333" spans="1:21" ht="41.4" hidden="1">
       <c r="A333" s="72"/>
       <c r="B333" s="71" t="s">
         <v>765</v>
@@ -22881,7 +22882,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="334" spans="1:21" ht="13.8">
+    <row r="334" spans="1:21" ht="13.8" hidden="1">
       <c r="A334" s="72"/>
       <c r="B334" s="71" t="s">
         <v>765</v>
@@ -22926,7 +22927,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="41.4">
+    <row r="335" spans="1:21" ht="41.4" hidden="1">
       <c r="A335" s="98">
         <v>89</v>
       </c>
@@ -22988,7 +22989,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="336" spans="1:21" ht="44.4" customHeight="1">
+    <row r="336" spans="1:21" ht="44.4" hidden="1" customHeight="1">
       <c r="A336" s="93"/>
       <c r="B336" s="71" t="s">
         <v>765</v>
@@ -23041,7 +23042,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="337" spans="1:22" ht="155.4" customHeight="1">
+    <row r="337" spans="1:22" ht="155.4" hidden="1" customHeight="1">
       <c r="A337" s="93"/>
       <c r="B337" s="71" t="s">
         <v>765</v>
@@ -23094,7 +23095,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="338" spans="1:22" ht="13.8">
+    <row r="338" spans="1:22" ht="13.8" hidden="1">
       <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>765</v>
@@ -23150,7 +23151,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="339" spans="1:22" ht="27.6">
+    <row r="339" spans="1:22" ht="27.6" hidden="1">
       <c r="A339" s="68"/>
       <c r="B339" s="71" t="s">
         <v>773</v>
@@ -23196,7 +23197,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="340" spans="1:22" ht="40.950000000000003" customHeight="1">
+    <row r="340" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A340" s="92">
         <v>90</v>
       </c>
@@ -23254,7 +23255,7 @@
       </c>
       <c r="V340" s="33"/>
     </row>
-    <row r="341" spans="1:22" ht="20.399999999999999" customHeight="1">
+    <row r="341" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
       <c r="A341" s="92"/>
       <c r="B341" s="71" t="s">
         <v>773</v>
@@ -23309,7 +23310,7 @@
       <c r="U341" s="66"/>
       <c r="V341" s="33"/>
     </row>
-    <row r="342" spans="1:22" ht="13.8">
+    <row r="342" spans="1:22" ht="13.8" hidden="1">
       <c r="A342" s="92">
         <v>91</v>
       </c>
@@ -23367,7 +23368,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="343" spans="1:22" ht="13.8">
+    <row r="343" spans="1:22" ht="13.8" hidden="1">
       <c r="A343" s="92"/>
       <c r="B343" s="71" t="s">
         <v>776</v>
@@ -23423,7 +23424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="344" spans="1:22" ht="27.6">
+    <row r="344" spans="1:22" ht="27.6" hidden="1">
       <c r="A344" s="92"/>
       <c r="B344" s="71" t="s">
         <v>776</v>
@@ -23475,7 +23476,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="345" spans="1:22" ht="13.8">
+    <row r="345" spans="1:22" ht="13.8" hidden="1">
       <c r="A345" s="92"/>
       <c r="B345" s="71" t="s">
         <v>776</v>
@@ -23531,7 +23532,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="346" spans="1:22" ht="27.6">
+    <row r="346" spans="1:22" ht="27.6" hidden="1">
       <c r="A346" s="92"/>
       <c r="B346" s="71" t="s">
         <v>776</v>
@@ -23584,7 +23585,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="347" spans="1:22" ht="27.6">
+    <row r="347" spans="1:22" ht="27.6" hidden="1">
       <c r="A347" s="92"/>
       <c r="B347" s="71" t="s">
         <v>776</v>
@@ -23630,7 +23631,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="348" spans="1:22" ht="13.8">
+    <row r="348" spans="1:22" ht="13.8" hidden="1">
       <c r="A348" s="92"/>
       <c r="B348" s="71" t="s">
         <v>776</v>
@@ -23686,7 +23687,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="349" spans="1:22" ht="61.2" customHeight="1">
+    <row r="349" spans="1:22" ht="61.2" hidden="1" customHeight="1">
       <c r="A349" s="92">
         <v>92</v>
       </c>
@@ -23743,7 +23744,7 @@
       </c>
       <c r="U349" s="71"/>
     </row>
-    <row r="350" spans="1:22" ht="61.2" customHeight="1">
+    <row r="350" spans="1:22" ht="61.2" hidden="1" customHeight="1">
       <c r="A350" s="92"/>
       <c r="B350" s="71" t="s">
         <v>788</v>
@@ -23797,7 +23798,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="351" spans="1:22" ht="13.8">
+    <row r="351" spans="1:22" ht="13.8" hidden="1">
       <c r="A351" s="92"/>
       <c r="B351" s="71" t="s">
         <v>788</v>
@@ -23853,7 +23854,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="352" spans="1:22" ht="94.2" customHeight="1">
+    <row r="352" spans="1:22" ht="94.2" hidden="1" customHeight="1">
       <c r="A352" s="92">
         <v>93</v>
       </c>
@@ -23911,7 +23912,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="353" spans="1:21" ht="94.2" customHeight="1">
+    <row r="353" spans="1:21" ht="94.2" hidden="1" customHeight="1">
       <c r="A353" s="92"/>
       <c r="B353" s="71" t="s">
         <v>793</v>
@@ -23964,7 +23965,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="354" spans="1:21" ht="94.2" customHeight="1">
+    <row r="354" spans="1:21" ht="94.2" hidden="1" customHeight="1">
       <c r="A354" s="92"/>
       <c r="B354" s="71" t="s">
         <v>793</v>
@@ -24020,7 +24021,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="46.95" customHeight="1">
+    <row r="355" spans="1:21" ht="46.95" hidden="1" customHeight="1">
       <c r="A355" s="92"/>
       <c r="B355" s="71" t="s">
         <v>793</v>
@@ -24080,7 +24081,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="13.8">
+    <row r="356" spans="1:21" ht="13.8" hidden="1">
       <c r="A356" s="92"/>
       <c r="B356" s="71" t="s">
         <v>793</v>
@@ -24134,7 +24135,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="357" spans="1:21" ht="13.8">
+    <row r="357" spans="1:21" ht="13.8" hidden="1">
       <c r="A357" s="92"/>
       <c r="B357" s="71" t="s">
         <v>793</v>
@@ -24190,7 +24191,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="358" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A358" s="66"/>
       <c r="B358" s="71" t="s">
         <v>802</v>
@@ -24246,7 +24247,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="81.599999999999994" customHeight="1">
+    <row r="359" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
       <c r="A359" s="66"/>
       <c r="B359" s="71" t="s">
         <v>802</v>
@@ -24299,7 +24300,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="360" spans="1:21" ht="65.400000000000006" customHeight="1">
+    <row r="360" spans="1:21" ht="65.400000000000006" hidden="1" customHeight="1">
       <c r="A360" s="48">
         <v>94</v>
       </c>
@@ -24354,7 +24355,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="361" spans="1:21" ht="27.6">
+    <row r="361" spans="1:21" ht="27.6" hidden="1">
       <c r="A361" s="48"/>
       <c r="B361" s="71" t="s">
         <v>802</v>
@@ -24410,7 +24411,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="27.6">
+    <row r="362" spans="1:21" ht="27.6" hidden="1">
       <c r="A362" s="48"/>
       <c r="B362" s="71" t="s">
         <v>802</v>
@@ -24467,7 +24468,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="13.8">
+    <row r="363" spans="1:21" ht="13.8" hidden="1">
       <c r="A363" s="92"/>
       <c r="B363" s="71" t="s">
         <v>813</v>
@@ -24522,7 +24523,7 @@
       </c>
       <c r="U363" s="71"/>
     </row>
-    <row r="364" spans="1:21" ht="13.8">
+    <row r="364" spans="1:21" ht="13.8" hidden="1">
       <c r="A364" s="92"/>
       <c r="B364" s="71" t="s">
         <v>813</v>
@@ -24578,7 +24579,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="13.8">
+    <row r="365" spans="1:21" ht="13.8" hidden="1">
       <c r="A365" s="68">
         <v>96</v>
       </c>
@@ -24634,7 +24635,7 @@
       </c>
       <c r="U365" s="66"/>
     </row>
-    <row r="366" spans="1:21" ht="13.8">
+    <row r="366" spans="1:21" ht="13.8" hidden="1">
       <c r="A366" s="68"/>
       <c r="B366" s="71" t="s">
         <v>817</v>
@@ -24688,7 +24689,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="13.8">
+    <row r="367" spans="1:21" ht="13.8" hidden="1">
       <c r="A367" s="66">
         <v>96</v>
       </c>
@@ -24744,7 +24745,7 @@
       </c>
       <c r="U367" s="71"/>
     </row>
-    <row r="368" spans="1:21" ht="27.6">
+    <row r="368" spans="1:21" ht="27.6" hidden="1">
       <c r="A368" s="98">
         <v>97</v>
       </c>
@@ -24795,7 +24796,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="369" spans="1:21" ht="41.4">
+    <row r="369" spans="1:21" ht="41.4" hidden="1">
       <c r="A369" s="93"/>
       <c r="B369" s="71" t="s">
         <v>820</v>
@@ -24855,7 +24856,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="27.6">
+    <row r="370" spans="1:21" ht="27.6" hidden="1">
       <c r="A370" s="93"/>
       <c r="B370" s="71" t="s">
         <v>820</v>
@@ -24908,7 +24909,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="27.6">
+    <row r="371" spans="1:21" ht="27.6" hidden="1">
       <c r="A371" s="93"/>
       <c r="B371" s="71" t="s">
         <v>820</v>
@@ -24964,7 +24965,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="27.6">
+    <row r="372" spans="1:21" ht="27.6" hidden="1">
       <c r="A372" s="94"/>
       <c r="B372" s="71" t="s">
         <v>820</v>
@@ -25019,7 +25020,7 @@
       </c>
       <c r="U372" s="71"/>
     </row>
-    <row r="373" spans="1:21" ht="148.94999999999999" customHeight="1">
+    <row r="373" spans="1:21" ht="148.94999999999999" hidden="1" customHeight="1">
       <c r="A373" s="92">
         <v>98</v>
       </c>
@@ -25074,7 +25075,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="40.200000000000003" customHeight="1">
+    <row r="374" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A374" s="92"/>
       <c r="B374" s="71" t="s">
         <v>826</v>
@@ -25127,7 +25128,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="34.950000000000003" customHeight="1">
+    <row r="375" spans="1:21" ht="34.950000000000003" hidden="1" customHeight="1">
       <c r="A375" s="92"/>
       <c r="B375" s="71" t="s">
         <v>826</v>
@@ -25180,7 +25181,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="37.950000000000003" customHeight="1">
+    <row r="376" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A376" s="92"/>
       <c r="B376" s="71" t="s">
         <v>826</v>
@@ -25233,7 +25234,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="122.4" customHeight="1">
+    <row r="377" spans="1:21" ht="122.4" hidden="1" customHeight="1">
       <c r="A377" s="92"/>
       <c r="B377" s="71" t="s">
         <v>826</v>
@@ -25276,7 +25277,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="61.2" customHeight="1">
+    <row r="378" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A378" s="92"/>
       <c r="B378" s="71" t="s">
         <v>826</v>
@@ -25328,7 +25329,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="379" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A379" s="92"/>
       <c r="B379" s="71" t="s">
         <v>826</v>
@@ -25380,7 +25381,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="61.2" customHeight="1">
+    <row r="380" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A380" s="92"/>
       <c r="B380" s="71" t="s">
         <v>826</v>
@@ -25426,7 +25427,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="13.8">
+    <row r="381" spans="1:21" ht="13.8" hidden="1">
       <c r="A381" s="92"/>
       <c r="B381" s="71" t="s">
         <v>826</v>
@@ -25475,7 +25476,7 @@
       </c>
       <c r="U381" s="71"/>
     </row>
-    <row r="382" spans="1:21" ht="13.8">
+    <row r="382" spans="1:21" ht="13.8" hidden="1">
       <c r="A382" s="92"/>
       <c r="B382" s="71" t="s">
         <v>826</v>
@@ -25529,7 +25530,7 @@
       </c>
       <c r="U382" s="71"/>
     </row>
-    <row r="383" spans="1:21" ht="13.8">
+    <row r="383" spans="1:21" ht="13.8" hidden="1">
       <c r="A383" s="92"/>
       <c r="B383" s="71" t="s">
         <v>826</v>
@@ -25581,7 +25582,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="13.8">
+    <row r="384" spans="1:21" ht="13.8" hidden="1">
       <c r="A384" s="92"/>
       <c r="B384" s="71" t="s">
         <v>826</v>
@@ -25635,7 +25636,7 @@
       </c>
       <c r="U384" s="71"/>
     </row>
-    <row r="385" spans="1:21" ht="27.6">
+    <row r="385" spans="1:21" ht="27.6" hidden="1">
       <c r="A385" s="94">
         <v>99</v>
       </c>
@@ -25690,7 +25691,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="163.19999999999999" customHeight="1">
+    <row r="386" spans="1:21" ht="163.19999999999999" hidden="1" customHeight="1">
       <c r="A386" s="92"/>
       <c r="B386" s="71" t="s">
         <v>854</v>
@@ -25743,7 +25744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="61.2" customHeight="1">
+    <row r="387" spans="1:21" ht="61.2" hidden="1" customHeight="1">
       <c r="A387" s="92"/>
       <c r="B387" s="71" t="s">
         <v>854</v>
@@ -25799,7 +25800,7 @@
       </c>
       <c r="U387" s="71"/>
     </row>
-    <row r="388" spans="1:21" ht="13.8">
+    <row r="388" spans="1:21" ht="13.8" hidden="1">
       <c r="A388" s="92"/>
       <c r="B388" s="71" t="s">
         <v>854</v>
@@ -25853,7 +25854,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="13.8">
+    <row r="389" spans="1:21" ht="13.8" hidden="1">
       <c r="A389" s="92"/>
       <c r="B389" s="71" t="s">
         <v>853</v>
@@ -25907,7 +25908,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="13.8">
+    <row r="390" spans="1:21" ht="13.8" hidden="1">
       <c r="A390" s="92"/>
       <c r="B390" s="71" t="s">
         <v>853</v>
@@ -25963,7 +25964,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="13.8">
+    <row r="391" spans="1:21" ht="13.8" hidden="1">
       <c r="A391" s="92"/>
       <c r="B391" s="71" t="s">
         <v>853</v>
@@ -26004,7 +26005,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="13.8">
+    <row r="392" spans="1:21" ht="13.8" hidden="1">
       <c r="A392" s="92"/>
       <c r="B392" s="66" t="s">
         <v>853</v>
@@ -26058,7 +26059,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="148.19999999999999" customHeight="1">
+    <row r="393" spans="1:21" ht="148.19999999999999" hidden="1" customHeight="1">
       <c r="A393" s="66"/>
       <c r="B393" s="66" t="s">
         <v>863</v>
@@ -26111,7 +26112,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="58.2" customHeight="1">
+    <row r="394" spans="1:21" ht="58.2" hidden="1" customHeight="1">
       <c r="A394" s="92">
         <v>100</v>
       </c>
@@ -26166,7 +26167,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="41.4">
+    <row r="395" spans="1:21" ht="41.4" hidden="1">
       <c r="A395" s="92"/>
       <c r="B395" s="66" t="s">
         <v>863</v>
@@ -26219,7 +26220,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="18" customHeight="1">
+    <row r="396" spans="1:21" ht="18" hidden="1" customHeight="1">
       <c r="A396" s="92"/>
       <c r="B396" s="71" t="s">
         <v>863</v>
@@ -26275,7 +26276,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="27.6">
+    <row r="397" spans="1:21" ht="27.6" hidden="1">
       <c r="A397" s="92"/>
       <c r="B397" s="71" t="s">
         <v>863</v>
@@ -26327,7 +26328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="18" customHeight="1">
+    <row r="398" spans="1:21" ht="18" hidden="1" customHeight="1">
       <c r="A398" s="92"/>
       <c r="B398" s="71" t="s">
         <v>863</v>
@@ -26381,7 +26382,7 @@
       </c>
       <c r="U398" s="71"/>
     </row>
-    <row r="399" spans="1:21" ht="13.8">
+    <row r="399" spans="1:21" ht="13.8" hidden="1">
       <c r="A399" s="92"/>
       <c r="B399" s="71" t="s">
         <v>863</v>
@@ -26435,7 +26436,7 @@
       </c>
       <c r="U399" s="71"/>
     </row>
-    <row r="400" spans="1:21" ht="27.6">
+    <row r="400" spans="1:21" ht="27.6" hidden="1">
       <c r="A400" s="102">
         <v>101</v>
       </c>
@@ -26492,7 +26493,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="31.95" customHeight="1">
+    <row r="401" spans="1:21" ht="31.95" hidden="1" customHeight="1">
       <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
         <v>873</v>
@@ -26533,7 +26534,7 @@
       <c r="T401" s="80"/>
       <c r="U401" s="66"/>
     </row>
-    <row r="402" spans="1:21" ht="31.95" customHeight="1">
+    <row r="402" spans="1:21" ht="31.95" hidden="1" customHeight="1">
       <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
         <v>873</v>
@@ -26587,7 +26588,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="31.95" customHeight="1">
+    <row r="403" spans="1:21" ht="31.95" hidden="1" customHeight="1">
       <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
         <v>873</v>
@@ -26643,7 +26644,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="31.95" customHeight="1">
+    <row r="404" spans="1:21" ht="31.95" hidden="1" customHeight="1">
       <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
         <v>873</v>
@@ -26697,7 +26698,7 @@
       </c>
       <c r="U404" s="71"/>
     </row>
-    <row r="405" spans="1:21" ht="13.8">
+    <row r="405" spans="1:21" ht="13.8" hidden="1">
       <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
         <v>873</v>
@@ -26753,7 +26754,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="36" customHeight="1">
+    <row r="406" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A406" s="92">
         <v>102</v>
       </c>
@@ -26808,7 +26809,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="13.8">
+    <row r="407" spans="1:21" ht="13.8" hidden="1">
       <c r="A407" s="92"/>
       <c r="B407" s="71" t="s">
         <v>880</v>
@@ -26864,7 +26865,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="408" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A408" s="92">
         <v>103</v>
       </c>
@@ -26920,7 +26921,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="409" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A409" s="92"/>
       <c r="B409" s="71" t="s">
         <v>884</v>
@@ -26976,7 +26977,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="410" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A410" s="92"/>
       <c r="B410" s="71" t="s">
         <v>884</v>
@@ -27031,7 +27032,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="13.8">
+    <row r="411" spans="1:21" ht="13.8" hidden="1">
       <c r="A411" s="92"/>
       <c r="B411" s="71" t="s">
         <v>884</v>
@@ -27087,7 +27088,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="60" customHeight="1">
+    <row r="412" spans="1:21" ht="60" hidden="1" customHeight="1">
       <c r="A412" s="92">
         <v>104</v>
       </c>
@@ -27142,7 +27143,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="413" spans="1:21" ht="60" customHeight="1">
+    <row r="413" spans="1:21" ht="60" hidden="1" customHeight="1">
       <c r="A413" s="92"/>
       <c r="B413" s="71" t="s">
         <v>889</v>
@@ -27202,7 +27203,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="414" spans="1:21" ht="60" customHeight="1">
+    <row r="414" spans="1:21" ht="60" hidden="1" customHeight="1">
       <c r="A414" s="92"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
@@ -27225,7 +27226,7 @@
       <c r="T414" s="80"/>
       <c r="U414" s="71"/>
     </row>
-    <row r="415" spans="1:21" ht="55.2">
+    <row r="415" spans="1:21" ht="55.2" hidden="1">
       <c r="A415" s="92"/>
       <c r="B415" s="71" t="s">
         <v>889</v>
@@ -27278,7 +27279,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="416" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A416" s="92"/>
       <c r="B416" s="71" t="s">
         <v>889</v>
@@ -27333,7 +27334,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="417" spans="1:21" ht="41.4">
+    <row r="417" spans="1:21" ht="41.4" hidden="1">
       <c r="A417" s="92">
         <v>105</v>
       </c>
@@ -27388,7 +27389,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="142.94999999999999" customHeight="1">
+    <row r="418" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
       <c r="A418" s="92"/>
       <c r="B418" s="71" t="s">
         <v>896</v>
@@ -27435,7 +27436,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="13.8">
+    <row r="419" spans="1:21" ht="13.8" hidden="1">
       <c r="A419" s="92"/>
       <c r="B419" s="71" t="s">
         <v>896</v>
@@ -27491,7 +27492,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="13.8">
+    <row r="420" spans="1:21" ht="13.8" hidden="1">
       <c r="A420" s="92"/>
       <c r="B420" s="71" t="s">
         <v>896</v>
@@ -27547,7 +27548,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="13.8">
+    <row r="421" spans="1:21" ht="13.8" hidden="1">
       <c r="A421" s="92"/>
       <c r="B421" s="71" t="s">
         <v>896</v>
@@ -27603,7 +27604,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="27.6">
+    <row r="422" spans="1:21" ht="27.6" hidden="1">
       <c r="A422" s="92"/>
       <c r="B422" s="71" t="s">
         <v>896</v>
@@ -27646,7 +27647,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="423" spans="1:21" ht="13.8">
+    <row r="423" spans="1:21" ht="13.8" hidden="1">
       <c r="A423" s="92"/>
       <c r="B423" s="71" t="s">
         <v>896</v>
@@ -27696,7 +27697,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="424" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A424" s="92"/>
       <c r="B424" s="71" t="s">
         <v>896</v>
@@ -27751,7 +27752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="27.6">
+    <row r="425" spans="1:21" ht="27.6" hidden="1">
       <c r="A425" s="66">
         <v>106</v>
       </c>
@@ -27800,7 +27801,7 @@
       <c r="T425" s="66"/>
       <c r="U425" s="71"/>
     </row>
-    <row r="426" spans="1:21" ht="27.6">
+    <row r="426" spans="1:21" ht="27.6" hidden="1">
       <c r="A426" s="66"/>
       <c r="B426" s="66" t="s">
         <v>912</v>
@@ -27852,7 +27853,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="27.6">
+    <row r="427" spans="1:21" ht="27.6" hidden="1">
       <c r="A427" s="92">
         <v>107</v>
       </c>
@@ -27909,7 +27910,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="13.8">
+    <row r="428" spans="1:21" ht="13.8" hidden="1">
       <c r="A428" s="92"/>
       <c r="B428" s="71" t="s">
         <v>913</v>
@@ -27963,7 +27964,7 @@
       </c>
       <c r="U428" s="71"/>
     </row>
-    <row r="429" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="429" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A429" s="92"/>
       <c r="B429" s="71" t="s">
         <v>913</v>
@@ -28015,7 +28016,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="430" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="430" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A430" s="92"/>
       <c r="B430" s="71" t="s">
         <v>912</v>
@@ -28067,7 +28068,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="40.950000000000003" customHeight="1">
+    <row r="431" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
       <c r="A431" s="92"/>
       <c r="B431" s="71" t="s">
         <v>912</v>
@@ -28119,7 +28120,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="13.8">
+    <row r="432" spans="1:21" ht="13.8" hidden="1">
       <c r="A432" s="92"/>
       <c r="B432" s="71" t="s">
         <v>913</v>
@@ -28173,7 +28174,7 @@
       </c>
       <c r="U432" s="71"/>
     </row>
-    <row r="433" spans="1:21" ht="13.8">
+    <row r="433" spans="1:21" ht="13.8" hidden="1">
       <c r="A433" s="92"/>
       <c r="B433" s="71" t="s">
         <v>912</v>
@@ -28227,7 +28228,7 @@
       </c>
       <c r="U433" s="66"/>
     </row>
-    <row r="434" spans="1:21" ht="13.8">
+    <row r="434" spans="1:21" ht="13.8" hidden="1">
       <c r="A434" s="93"/>
       <c r="B434" s="71" t="s">
         <v>924</v>
@@ -28279,7 +28280,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="27.6">
+    <row r="435" spans="1:21" ht="27.6" hidden="1">
       <c r="A435" s="93"/>
       <c r="B435" s="71" t="s">
         <v>924</v>
@@ -28314,7 +28315,7 @@
       <c r="T435" s="96"/>
       <c r="U435" s="92"/>
     </row>
-    <row r="436" spans="1:21" ht="13.8">
+    <row r="436" spans="1:21" ht="13.8" hidden="1">
       <c r="A436" s="93"/>
       <c r="B436" s="71" t="s">
         <v>924</v>
@@ -28368,7 +28369,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="13.8">
+    <row r="437" spans="1:21" ht="13.8" hidden="1">
       <c r="A437" s="93"/>
       <c r="B437" s="71" t="s">
         <v>928</v>
@@ -28422,7 +28423,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="438" spans="1:21" ht="13.8">
+    <row r="438" spans="1:21" ht="13.8" hidden="1">
       <c r="A438" s="93"/>
       <c r="B438" s="71" t="s">
         <v>924</v>
@@ -28474,7 +28475,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="27.6">
+    <row r="439" spans="1:21" ht="27.6" hidden="1">
       <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
         <v>924</v>
@@ -28527,7 +28528,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="57" customHeight="1">
+    <row r="440" spans="1:21" ht="57" hidden="1" customHeight="1">
       <c r="A440" s="98">
         <v>109</v>
       </c>
@@ -28581,7 +28582,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="57" customHeight="1">
+    <row r="441" spans="1:21" ht="57" hidden="1" customHeight="1">
       <c r="A441" s="93"/>
       <c r="B441" s="71" t="s">
         <v>936</v>
@@ -28632,7 +28633,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="36.6" customHeight="1">
+    <row r="442" spans="1:21" ht="36.6" hidden="1" customHeight="1">
       <c r="A442" s="93"/>
       <c r="B442" s="71" t="s">
         <v>936</v>
@@ -28687,7 +28688,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="36.6" customHeight="1">
+    <row r="443" spans="1:21" ht="36.6" hidden="1" customHeight="1">
       <c r="A443" s="93"/>
       <c r="B443" s="71" t="s">
         <v>936</v>
@@ -28741,7 +28742,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="64.95" customHeight="1">
+    <row r="444" spans="1:21" ht="64.95" hidden="1" customHeight="1">
       <c r="A444" s="93"/>
       <c r="B444" s="71" t="s">
         <v>936</v>
@@ -28793,7 +28794,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="36.6" customHeight="1">
+    <row r="445" spans="1:21" ht="36.6" hidden="1" customHeight="1">
       <c r="A445" s="93"/>
       <c r="B445" s="71" t="s">
         <v>936</v>
@@ -28843,7 +28844,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="36.6" customHeight="1">
+    <row r="446" spans="1:21" ht="36.6" hidden="1" customHeight="1">
       <c r="A446" s="93"/>
       <c r="B446" s="71" t="s">
         <v>936</v>
@@ -28880,7 +28881,7 @@
       <c r="T446" s="80"/>
       <c r="U446" s="71"/>
     </row>
-    <row r="447" spans="1:21" ht="15" customHeight="1">
+    <row r="447" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
         <v>936</v>
@@ -28934,7 +28935,7 @@
       </c>
       <c r="U447" s="44"/>
     </row>
-    <row r="448" spans="1:21" ht="27.6">
+    <row r="448" spans="1:21" ht="27.6" hidden="1">
       <c r="A448" s="92"/>
       <c r="B448" s="71" t="s">
         <v>946</v>
@@ -28990,7 +28991,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="41.4">
+    <row r="449" spans="1:21" ht="41.4" hidden="1">
       <c r="A449" s="92"/>
       <c r="B449" s="51" t="s">
         <v>946</v>
@@ -29050,7 +29051,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="27.6">
+    <row r="450" spans="1:21" ht="27.6" hidden="1">
       <c r="A450" s="98">
         <v>111</v>
       </c>
@@ -29106,7 +29107,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="451" spans="1:21" ht="15" customHeight="1">
+    <row r="451" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A451" s="93"/>
       <c r="B451" s="71" t="s">
         <v>953</v>
@@ -29160,7 +29161,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="15" customHeight="1">
+    <row r="452" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A452" s="93"/>
       <c r="B452" s="71" t="s">
         <v>953</v>
@@ -29218,7 +29219,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="15" customHeight="1">
+    <row r="453" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
         <v>953</v>
@@ -29272,7 +29273,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="454" spans="1:21" ht="42.6" customHeight="1">
+    <row r="454" spans="1:21" ht="42.6" hidden="1" customHeight="1">
       <c r="A454" s="92">
         <v>112</v>
       </c>
@@ -29333,7 +29334,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="13.8">
+    <row r="455" spans="1:21" ht="13.8" hidden="1">
       <c r="A455" s="92"/>
       <c r="B455" s="71" t="s">
         <v>960</v>
@@ -29388,7 +29389,7 @@
       </c>
       <c r="U455" s="71"/>
     </row>
-    <row r="456" spans="1:21" ht="15" customHeight="1">
+    <row r="456" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A456" s="92"/>
       <c r="B456" s="71" t="s">
         <v>960</v>
@@ -29445,7 +29446,7 @@
       </c>
       <c r="U456" s="71"/>
     </row>
-    <row r="457" spans="1:21" ht="27.6">
+    <row r="457" spans="1:21" ht="27.6" hidden="1">
       <c r="A457" s="92">
         <v>113</v>
       </c>
@@ -29498,7 +29499,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="13.8">
+    <row r="458" spans="1:21" ht="13.8" hidden="1">
       <c r="A458" s="92"/>
       <c r="B458" s="71" t="s">
         <v>964</v>
@@ -29551,7 +29552,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="459" spans="1:21" ht="37.950000000000003" customHeight="1">
+    <row r="459" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A459" s="92"/>
       <c r="B459" s="71" t="s">
         <v>964</v>
@@ -29605,7 +29606,7 @@
       </c>
       <c r="U459" s="66"/>
     </row>
-    <row r="460" spans="1:21" ht="37.950000000000003" customHeight="1">
+    <row r="460" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
       <c r="A460" s="92"/>
       <c r="B460" s="71" t="s">
         <v>964</v>
@@ -29653,7 +29654,7 @@
       <c r="T460" s="80"/>
       <c r="U460" s="66"/>
     </row>
-    <row r="461" spans="1:21" ht="15" customHeight="1">
+    <row r="461" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A461" s="92"/>
       <c r="B461" s="71" t="s">
         <v>964</v>
@@ -29709,7 +29710,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="462" spans="1:21" ht="55.2">
+    <row r="462" spans="1:21" ht="55.2" hidden="1">
       <c r="A462" s="66"/>
       <c r="B462" s="71" t="s">
         <v>971</v>
@@ -29765,7 +29766,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="43.2" customHeight="1">
+    <row r="463" spans="1:21" ht="43.2" hidden="1" customHeight="1">
       <c r="A463" s="66"/>
       <c r="B463" s="71" t="s">
         <v>971</v>
@@ -29819,7 +29820,7 @@
       </c>
       <c r="U463" s="71"/>
     </row>
-    <row r="464" spans="1:21" ht="43.2" customHeight="1">
+    <row r="464" spans="1:21" ht="43.2" hidden="1" customHeight="1">
       <c r="A464" s="66"/>
       <c r="B464" s="71" t="s">
         <v>971</v>
@@ -29873,7 +29874,7 @@
       </c>
       <c r="U464" s="71"/>
     </row>
-    <row r="465" spans="1:21" ht="43.2" customHeight="1">
+    <row r="465" spans="1:21" ht="43.2" hidden="1" customHeight="1">
       <c r="A465" s="66"/>
       <c r="B465" s="71" t="s">
         <v>971</v>
@@ -29925,7 +29926,7 @@
       <c r="T465" s="80"/>
       <c r="U465" s="71"/>
     </row>
-    <row r="466" spans="1:21" ht="43.2" customHeight="1">
+    <row r="466" spans="1:21" ht="43.2" hidden="1" customHeight="1">
       <c r="A466" s="66"/>
       <c r="B466" s="71" t="s">
         <v>971</v>
@@ -29979,7 +29980,7 @@
       </c>
       <c r="U466" s="71"/>
     </row>
-    <row r="467" spans="1:21" ht="33.6" customHeight="1">
+    <row r="467" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A467" s="66">
         <v>114</v>
       </c>
@@ -30034,7 +30035,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="468" spans="1:21" ht="33.6" customHeight="1">
+    <row r="468" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A468" s="93"/>
       <c r="B468" s="71" t="s">
         <v>981</v>
@@ -30085,7 +30086,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="469" spans="1:21" ht="33.6" customHeight="1">
+    <row r="469" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A469" s="93"/>
       <c r="B469" s="71" t="s">
         <v>325</v>
@@ -30139,7 +30140,7 @@
       </c>
       <c r="U469" s="71"/>
     </row>
-    <row r="470" spans="1:21" ht="33.6" customHeight="1">
+    <row r="470" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A470" s="93"/>
       <c r="B470" s="71" t="s">
         <v>325</v>
@@ -30193,7 +30194,7 @@
       </c>
       <c r="U470" s="71"/>
     </row>
-    <row r="471" spans="1:21" ht="33.6" customHeight="1">
+    <row r="471" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A471" s="93"/>
       <c r="B471" s="71" t="s">
         <v>325</v>
@@ -30247,7 +30248,7 @@
       </c>
       <c r="U471" s="71"/>
     </row>
-    <row r="472" spans="1:21" ht="33.6" customHeight="1">
+    <row r="472" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A472" s="93"/>
       <c r="B472" s="71" t="s">
         <v>325</v>
@@ -30303,7 +30304,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="473" spans="1:21" ht="33.6" customHeight="1">
+    <row r="473" spans="1:21" ht="33.6" hidden="1" customHeight="1">
       <c r="A473" s="93"/>
       <c r="B473" s="71" t="s">
         <v>325</v>
@@ -30355,7 +30356,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="474" spans="1:21" ht="39" customHeight="1">
+    <row r="474" spans="1:21" ht="39" hidden="1" customHeight="1">
       <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
         <v>981</v>
@@ -30405,7 +30406,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="475" spans="1:21" ht="39" customHeight="1">
+    <row r="475" spans="1:21" ht="39" hidden="1" customHeight="1">
       <c r="A475" s="92">
         <v>116</v>
       </c>
@@ -30461,7 +30462,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="476" spans="1:21" ht="39" customHeight="1">
+    <row r="476" spans="1:21" ht="39" hidden="1" customHeight="1">
       <c r="A476" s="92"/>
       <c r="B476" s="71" t="s">
         <v>993</v>
@@ -30504,7 +30505,7 @@
       <c r="T476" s="71"/>
       <c r="U476" s="97"/>
     </row>
-    <row r="477" spans="1:21" ht="39" customHeight="1">
+    <row r="477" spans="1:21" ht="39" hidden="1" customHeight="1">
       <c r="A477" s="92"/>
       <c r="B477" s="71" t="s">
         <v>993</v>
@@ -30562,7 +30563,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="478" spans="1:21" ht="36" customHeight="1">
+    <row r="478" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A478" s="92"/>
       <c r="B478" s="71" t="s">
         <v>993</v>
@@ -30617,7 +30618,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:21" ht="36" customHeight="1">
+    <row r="479" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A479" s="66">
         <v>118</v>
       </c>
@@ -30672,7 +30673,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="480" spans="1:21" ht="36" customHeight="1">
+    <row r="480" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A480" s="66"/>
       <c r="B480" s="71" t="s">
         <v>999</v>
@@ -30726,7 +30727,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="481" spans="1:21" ht="36" customHeight="1">
+    <row r="481" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A481" s="66"/>
       <c r="B481" s="71" t="s">
         <v>1000</v>
@@ -30778,7 +30779,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="482" spans="1:21" ht="15" customHeight="1">
+    <row r="482" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A482" s="66">
         <v>119</v>
       </c>
@@ -30836,7 +30837,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="483" spans="1:21" ht="35.4" customHeight="1">
+    <row r="483" spans="1:21" ht="35.4" hidden="1" customHeight="1">
       <c r="A483" s="66"/>
       <c r="B483" s="71" t="s">
         <v>1005</v>
@@ -30890,7 +30891,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="484" spans="1:21" ht="38.4" customHeight="1">
+    <row r="484" spans="1:21" ht="38.4" hidden="1" customHeight="1">
       <c r="A484" s="66"/>
       <c r="B484" s="71" t="s">
         <v>1005</v>
@@ -30942,7 +30943,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="485" spans="1:21" ht="36.6" customHeight="1">
+    <row r="485" spans="1:21" ht="36.6" hidden="1" customHeight="1">
       <c r="A485" s="66">
         <v>120</v>
       </c>
@@ -30997,7 +30998,7 @@
       </c>
       <c r="U485" s="66"/>
     </row>
-    <row r="486" spans="1:21" ht="35.25" customHeight="1">
+    <row r="486" spans="1:21" ht="35.25" hidden="1" customHeight="1">
       <c r="A486" s="92">
         <v>121</v>
       </c>
@@ -31053,7 +31054,7 @@
       </c>
       <c r="U486" s="71"/>
     </row>
-    <row r="487" spans="1:21" ht="36" customHeight="1">
+    <row r="487" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A487" s="92"/>
       <c r="B487" s="71" t="s">
         <v>1009</v>
@@ -31105,7 +31106,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="488" spans="1:21" ht="96.6">
+    <row r="488" spans="1:21" ht="96.6" hidden="1">
       <c r="A488" s="92"/>
       <c r="B488" s="71" t="s">
         <v>1009</v>
@@ -31159,7 +31160,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="489" spans="1:21" ht="36" customHeight="1">
+    <row r="489" spans="1:21" ht="36" hidden="1" customHeight="1">
       <c r="A489" s="68"/>
       <c r="B489" s="71" t="s">
         <v>1017</v>
@@ -31213,7 +31214,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="490" spans="1:21" ht="13.8">
+    <row r="490" spans="1:21" ht="13.8" hidden="1">
       <c r="A490" s="68">
         <v>122</v>
       </c>
@@ -31269,7 +31270,7 @@
       </c>
       <c r="U490" s="71"/>
     </row>
-    <row r="491" spans="1:21" ht="13.8">
+    <row r="491" spans="1:21" ht="13.8" hidden="1">
       <c r="A491" s="93"/>
       <c r="B491" s="71" t="s">
         <v>1019</v>
@@ -31323,7 +31324,7 @@
       </c>
       <c r="U491" s="71"/>
     </row>
-    <row r="492" spans="1:21" ht="13.8">
+    <row r="492" spans="1:21" ht="13.8" hidden="1">
       <c r="A492" s="93"/>
       <c r="B492" s="71" t="s">
         <v>1019</v>
@@ -31377,7 +31378,7 @@
       </c>
       <c r="U492" s="71"/>
     </row>
-    <row r="493" spans="1:21" ht="55.2">
+    <row r="493" spans="1:21" ht="55.2" hidden="1">
       <c r="A493" s="93"/>
       <c r="B493" s="71" t="s">
         <v>1019</v>
@@ -31428,7 +31429,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="494" spans="1:21" ht="15" customHeight="1">
+    <row r="494" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
         <v>1019</v>
@@ -31482,7 +31483,7 @@
       </c>
       <c r="U494" s="71"/>
     </row>
-    <row r="495" spans="1:21" ht="15" customHeight="1">
+    <row r="495" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A495" s="92">
         <v>124</v>
       </c>
@@ -31540,7 +31541,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="496" spans="1:21" ht="27.6">
+    <row r="496" spans="1:21" ht="27.6" hidden="1">
       <c r="A496" s="92"/>
       <c r="B496" s="71" t="s">
         <v>1026</v>
@@ -31592,7 +31593,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="497" spans="1:21" ht="13.8">
+    <row r="497" spans="1:21" ht="13.8" hidden="1">
       <c r="A497" s="92"/>
       <c r="B497" s="71" t="s">
         <v>1026</v>
@@ -31646,7 +31647,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="498" spans="1:21" ht="40.200000000000003" customHeight="1">
+    <row r="498" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A498" s="92"/>
       <c r="B498" s="71" t="s">
         <v>1032</v>
@@ -31701,7 +31702,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="499" spans="1:21" ht="40.200000000000003" customHeight="1">
+    <row r="499" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A499" s="66"/>
       <c r="B499" s="71" t="s">
         <v>1033</v>
@@ -31761,7 +31762,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="500" spans="1:21" ht="27.6">
+    <row r="500" spans="1:21" ht="27.6" hidden="1">
       <c r="A500" s="97">
         <v>126</v>
       </c>
@@ -31822,7 +31823,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="501" spans="1:21" ht="13.8">
+    <row r="501" spans="1:21" ht="13.8" hidden="1">
       <c r="A501" s="97"/>
       <c r="B501" s="71" t="s">
         <v>1033</v>
@@ -31873,7 +31874,7 @@
       <c r="T501" s="80"/>
       <c r="U501" s="71"/>
     </row>
-    <row r="502" spans="1:21" ht="78" customHeight="1">
+    <row r="502" spans="1:21" ht="78" hidden="1" customHeight="1">
       <c r="A502" s="97"/>
       <c r="B502" s="71" t="s">
         <v>1033</v>
@@ -31929,7 +31930,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="503" spans="1:21" ht="41.4">
+    <row r="503" spans="1:21" ht="41.4" hidden="1">
       <c r="A503" s="92">
         <v>127</v>
       </c>
@@ -31991,7 +31992,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="504" spans="1:21" ht="13.8">
+    <row r="504" spans="1:21" ht="13.8" hidden="1">
       <c r="A504" s="92"/>
       <c r="B504" s="71" t="s">
         <v>1041</v>
@@ -32049,7 +32050,7 @@
       </c>
       <c r="U504" s="71"/>
     </row>
-    <row r="505" spans="1:21" ht="55.2">
+    <row r="505" spans="1:21" ht="55.2" hidden="1">
       <c r="A505" s="92"/>
       <c r="B505" s="51" t="s">
         <v>1041</v>
@@ -32107,14 +32108,14 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="506" spans="1:21" ht="55.95" customHeight="1">
+    <row r="506" spans="1:21" ht="55.95" hidden="1" customHeight="1">
       <c r="K506" s="27"/>
       <c r="M506" s="56"/>
       <c r="R506" s="33"/>
       <c r="S506" s="33"/>
       <c r="T506" s="57"/>
     </row>
-    <row r="507" spans="1:21" ht="13.8">
+    <row r="507" spans="1:21" ht="13.8" hidden="1">
       <c r="E507" s="55" t="s">
         <v>713</v>
       </c>
@@ -32126,7 +32127,7 @@
     <row r="508" spans="1:21" ht="15" customHeight="1">
       <c r="H508" s="33">
         <f>SUBTOTAL(9,H111:H507)</f>
-        <v>21930.376999999982</v>
+        <v>1.538</v>
       </c>
       <c r="K508" s="8"/>
       <c r="M508" s="58"/>
@@ -32182,7 +32183,13 @@
       <c r="K521" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}"/>
+  <autoFilter ref="A2:U507" xr:uid="{AE671324-A880-40DD-8209-9E3234F3C075}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Chigorodó"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="137">
     <mergeCell ref="M91:M101"/>
     <mergeCell ref="N91:N92"/>

--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F81FC7FB-08BD-4A81-9417-11448392552F}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF7219A-15B1-4DA2-958D-934E61186574}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1072">
   <si>
     <t>PROYECTOS SIF</t>
   </si>
@@ -4522,25 +4522,49 @@
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4555,38 +4579,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4921,7 +4921,7 @@
     <col min="2" max="2" width="22.33203125" style="33" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="33" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="19.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" style="55" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="55" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="49.109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="48.33203125" style="33" customWidth="1"/>
     <col min="8" max="8" width="35.5546875" style="33" hidden="1" customWidth="1"/>
@@ -4931,7 +4931,7 @@
     <col min="12" max="12" width="25.88671875" style="56" customWidth="1"/>
     <col min="13" max="13" width="24.33203125" style="33" customWidth="1"/>
     <col min="14" max="14" width="26" style="33" customWidth="1"/>
-    <col min="15" max="15" width="32.5546875" style="33" customWidth="1"/>
+    <col min="15" max="15" width="32.5546875" style="33" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="19.109375" style="33" customWidth="1"/>
     <col min="17" max="17" width="20.5546875" style="33" customWidth="1"/>
     <col min="18" max="18" width="23.5546875" style="88" hidden="1" customWidth="1"/>
@@ -4944,10 +4944,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.8" hidden="1">
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="107"/>
+      <c r="C1" s="105"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -5032,7 +5032,7 @@
       <c r="W2" s="13"/>
     </row>
     <row r="3" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="94">
+      <c r="A3" s="102">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5098,7 +5098,7 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="94"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="71" t="s">
         <v>21</v>
       </c>
@@ -5162,7 +5162,7 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="41.4" hidden="1">
-      <c r="A5" s="94"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="66" t="s">
         <v>21</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="U6" s="66"/>
     </row>
     <row r="7" spans="1:23" ht="13.8" hidden="1">
-      <c r="A7" s="98">
+      <c r="A7" s="101">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5305,7 +5305,7 @@
       <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:23" ht="13.8" hidden="1">
-      <c r="A8" s="93"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="71" t="s">
         <v>39</v>
       </c>
@@ -5357,7 +5357,7 @@
       <c r="U8" s="66"/>
     </row>
     <row r="9" spans="1:23" ht="41.4" hidden="1">
-      <c r="A9" s="93"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="71" t="s">
         <v>39</v>
       </c>
@@ -5415,7 +5415,7 @@
       <c r="U9" s="66"/>
     </row>
     <row r="10" spans="1:23" ht="41.4" hidden="1">
-      <c r="A10" s="94"/>
+      <c r="A10" s="102"/>
       <c r="B10" s="66" t="s">
         <v>39</v>
       </c>
@@ -5473,7 +5473,7 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="27.6" hidden="1">
-      <c r="A11" s="92">
+      <c r="A11" s="95">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5536,7 +5536,7 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="92"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="71" t="s">
         <v>57</v>
       </c>
@@ -5592,7 +5592,7 @@
       <c r="U12" s="76"/>
     </row>
     <row r="13" spans="1:23" ht="13.8" hidden="1">
-      <c r="A13" s="92"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="71" t="s">
         <v>57</v>
       </c>
@@ -5648,7 +5648,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="13.8" hidden="1">
-      <c r="A14" s="92"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="71" t="s">
         <v>57</v>
       </c>
@@ -5704,7 +5704,7 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="13.8" hidden="1">
-      <c r="A15" s="92"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="71" t="s">
         <v>57</v>
       </c>
@@ -5760,7 +5760,7 @@
       <c r="U15" s="66"/>
     </row>
     <row r="16" spans="1:23" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="92"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="71" t="s">
         <v>57</v>
       </c>
@@ -5977,7 +5977,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="92">
+      <c r="A20" s="95">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6039,7 +6039,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="92"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="71" t="s">
         <v>90</v>
       </c>
@@ -6097,7 +6097,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" hidden="1">
-      <c r="A22" s="92"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="71"/>
       <c r="C22" s="66" t="s">
         <v>91</v>
@@ -6154,7 +6154,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="13.8" hidden="1">
-      <c r="A23" s="92"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="71" t="s">
         <v>90</v>
       </c>
@@ -6211,7 +6211,7 @@
       <c r="U23" s="71"/>
     </row>
     <row r="24" spans="1:21" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="92">
+      <c r="A24" s="95">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6272,7 +6272,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="13.8" hidden="1">
-      <c r="A25" s="92"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="71" t="s">
         <v>107</v>
       </c>
@@ -6328,7 +6328,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="92"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="71" t="s">
         <v>107</v>
       </c>
@@ -6384,7 +6384,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="92"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="71" t="s">
         <v>107</v>
       </c>
@@ -6442,7 +6442,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="13.8" hidden="1">
-      <c r="A28" s="92"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="71" t="s">
         <v>107</v>
       </c>
@@ -6496,7 +6496,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="92"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="71" t="s">
         <v>107</v>
       </c>
@@ -6552,7 +6552,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="92"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="71" t="s">
         <v>107</v>
       </c>
@@ -6604,7 +6604,7 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="92"/>
+      <c r="A31" s="95"/>
       <c r="B31" s="71" t="s">
         <v>107</v>
       </c>
@@ -6662,7 +6662,7 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="92"/>
+      <c r="A32" s="95"/>
       <c r="B32" s="71" t="s">
         <v>107</v>
       </c>
@@ -6722,7 +6722,7 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="92"/>
+      <c r="A33" s="95"/>
       <c r="B33" s="71" t="s">
         <v>107</v>
       </c>
@@ -6778,7 +6778,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="92"/>
+      <c r="A34" s="95"/>
       <c r="B34" s="71" t="s">
         <v>107</v>
       </c>
@@ -6838,7 +6838,7 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="13.8" hidden="1">
-      <c r="A35" s="93"/>
+      <c r="A35" s="106"/>
       <c r="B35" s="71" t="s">
         <v>145</v>
       </c>
@@ -6873,7 +6873,7 @@
       <c r="U35" s="71"/>
     </row>
     <row r="36" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="94"/>
+      <c r="A36" s="102"/>
       <c r="B36" s="71" t="s">
         <v>145</v>
       </c>
@@ -6985,7 +6985,7 @@
       </c>
     </row>
     <row r="38" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="92">
+      <c r="A38" s="95">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7046,7 +7046,7 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="92"/>
+      <c r="A39" s="95"/>
       <c r="B39" s="71" t="s">
         <v>148</v>
       </c>
@@ -7106,7 +7106,7 @@
       </c>
     </row>
     <row r="40" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="92"/>
+      <c r="A40" s="95"/>
       <c r="B40" s="71" t="s">
         <v>148</v>
       </c>
@@ -7163,7 +7163,7 @@
       </c>
     </row>
     <row r="41" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="92">
+      <c r="A41" s="95">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7223,7 +7223,7 @@
       <c r="U41" s="71"/>
     </row>
     <row r="42" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="92"/>
+      <c r="A42" s="95"/>
       <c r="B42" s="71" t="s">
         <v>158</v>
       </c>
@@ -7272,7 +7272,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="92"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="71" t="s">
         <v>158</v>
       </c>
@@ -7323,7 +7323,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="92"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="71" t="s">
         <v>158</v>
       </c>
@@ -7371,7 +7371,7 @@
       </c>
     </row>
     <row r="45" spans="1:21" ht="27.6" hidden="1">
-      <c r="A45" s="92"/>
+      <c r="A45" s="95"/>
       <c r="B45" s="71" t="s">
         <v>158</v>
       </c>
@@ -7427,7 +7427,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="92">
+      <c r="A46" s="95">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7483,7 +7483,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" ht="13.8" hidden="1">
-      <c r="A47" s="98"/>
+      <c r="A47" s="101"/>
       <c r="B47" s="71" t="s">
         <v>173</v>
       </c>
@@ -7537,7 +7537,7 @@
       <c r="U47" s="71"/>
     </row>
     <row r="48" spans="1:21" ht="13.8" hidden="1">
-      <c r="A48" s="92"/>
+      <c r="A48" s="95"/>
       <c r="B48" s="71" t="s">
         <v>180</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="U48" s="71"/>
     </row>
     <row r="49" spans="1:21" ht="13.8" hidden="1">
-      <c r="A49" s="92"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="71" t="s">
         <v>180</v>
       </c>
@@ -7611,7 +7611,7 @@
       </c>
     </row>
     <row r="50" spans="1:21" ht="13.8" hidden="1">
-      <c r="A50" s="92"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="71" t="s">
         <v>180</v>
       </c>
@@ -7665,7 +7665,7 @@
       </c>
     </row>
     <row r="51" spans="1:21" ht="55.2" hidden="1">
-      <c r="A51" s="92"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="71" t="s">
         <v>180</v>
       </c>
@@ -7719,7 +7719,7 @@
       </c>
     </row>
     <row r